--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -5,17 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919ACB8D-611B-ED4E-B284-53643CDCB86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67790435-58F9-4644-8DFA-12F03F5D194D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26880" yWindow="500" windowWidth="40960" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="26880" windowHeight="15220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Supplementary File 1e vip" sheetId="1" r:id="rId3"/>
+    <sheet name="Supplementary File 1e vip" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$S$1:$S$77</definedName>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="113">
   <si>
     <t>sample</t>
   </si>
@@ -373,9 +372,6 @@
   </si>
   <si>
     <t>D=0.027_M</t>
-  </si>
-  <si>
-    <t>r_1992</t>
   </si>
 </sst>
 </file>
@@ -385,7 +381,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -527,11 +523,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri (Body)"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -565,7 +556,7 @@
       <name val="Times Roman"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -769,6 +760,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -953,63 +950,63 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4272,12 +4269,14 @@
         <v>0.42361575000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:23" s="20" customFormat="1">
-      <c r="A48" s="18" t="s">
+    <row r="48" spans="1:23" s="26" customFormat="1">
+      <c r="A48" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B48" s="19"/>
-      <c r="P48" s="21"/>
+      <c r="B48" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="P48" s="27"/>
     </row>
     <row r="49" spans="1:16" s="7" customFormat="1">
       <c r="A49" s="4" t="s">
@@ -4345,25 +4344,37 @@
       <c r="A53" s="1" t="s">
         <v>66</v>
       </c>
+      <c r="B53" s="12">
+        <v>0.1</v>
+      </c>
       <c r="P53" s="11"/>
     </row>
     <row r="54" spans="1:16" s="12" customFormat="1">
       <c r="A54" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D54" s="22"/>
+      <c r="B54" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="D54" s="18"/>
       <c r="P54" s="11"/>
     </row>
     <row r="55" spans="1:16" s="12" customFormat="1">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="B55" s="12">
+        <v>0.1</v>
+      </c>
       <c r="P55" s="11"/>
     </row>
     <row r="56" spans="1:16" s="12" customFormat="1">
       <c r="A56" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="B56" s="12">
+        <v>0.1</v>
+      </c>
       <c r="P56" s="11"/>
     </row>
     <row r="57" spans="1:16" s="12" customFormat="1">
@@ -4438,300 +4449,300 @@
       </c>
       <c r="P68" s="11"/>
     </row>
-    <row r="69" spans="1:23" s="23" customFormat="1">
+    <row r="69" spans="1:23" s="19" customFormat="1">
       <c r="A69" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B69" s="19">
         <v>2.7E-2</v>
       </c>
-      <c r="C69" s="24">
+      <c r="C69" s="20">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="D69" s="24">
+      <c r="D69" s="20">
         <v>-0.151308114750691</v>
       </c>
-      <c r="I69" s="24">
-        <v>0</v>
-      </c>
-      <c r="N69" s="24">
+      <c r="I69" s="20">
+        <v>0</v>
+      </c>
+      <c r="N69" s="20">
         <v>0.878</v>
       </c>
-      <c r="O69" s="25">
+      <c r="O69" s="21">
         <v>-0.86358170086251695</v>
       </c>
-      <c r="P69" s="26"/>
-      <c r="Q69" s="23" t="s">
+      <c r="P69" s="22"/>
+      <c r="Q69" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S69" s="23" t="s">
+      <c r="S69" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W69" s="23">
+      <c r="W69" s="19">
         <v>0.29899999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:23" s="25" customFormat="1">
+    <row r="70" spans="1:23" s="21" customFormat="1">
       <c r="A70" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B70" s="25">
+      <c r="B70" s="21">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="C70" s="24">
+      <c r="C70" s="20">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="D70" s="24">
+      <c r="D70" s="20">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="I70" s="24">
-        <v>0</v>
-      </c>
-      <c r="N70" s="24">
+      <c r="I70" s="20">
+        <v>0</v>
+      </c>
+      <c r="N70" s="20">
         <v>1.458</v>
       </c>
-      <c r="O70" s="25">
+      <c r="O70" s="21">
         <v>-1.4368262739973601</v>
       </c>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="23" t="s">
+      <c r="P70" s="23"/>
+      <c r="Q70" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S70" s="23" t="s">
+      <c r="S70" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W70" s="25">
+      <c r="W70" s="21">
         <v>0.312</v>
       </c>
     </row>
-    <row r="71" spans="1:23" s="25" customFormat="1">
+    <row r="71" spans="1:23" s="21" customFormat="1">
       <c r="A71" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="25">
+      <c r="B71" s="21">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C71" s="24">
+      <c r="C71" s="20">
         <v>-1.171</v>
       </c>
-      <c r="D71" s="24">
+      <c r="D71" s="20">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="I71" s="24">
-        <v>0</v>
-      </c>
-      <c r="N71" s="24">
+      <c r="I71" s="20">
+        <v>0</v>
+      </c>
+      <c r="N71" s="20">
         <v>2.5470000000000002</v>
       </c>
-      <c r="O71" s="25">
+      <c r="O71" s="21">
         <v>-2.4905493340587901</v>
       </c>
-      <c r="P71" s="27"/>
-      <c r="Q71" s="23" t="s">
+      <c r="P71" s="23"/>
+      <c r="Q71" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S71" s="23" t="s">
+      <c r="S71" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W71" s="25">
+      <c r="W71" s="21">
         <v>0.371</v>
       </c>
     </row>
-    <row r="72" spans="1:23" s="25" customFormat="1">
+    <row r="72" spans="1:23" s="21" customFormat="1">
       <c r="A72" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B72" s="25">
+      <c r="B72" s="21">
         <v>0.152</v>
       </c>
-      <c r="C72" s="24">
+      <c r="C72" s="20">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="D72" s="24">
+      <c r="D72" s="20">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="I72" s="24">
-        <v>0</v>
-      </c>
-      <c r="N72" s="24">
+      <c r="I72" s="20">
+        <v>0</v>
+      </c>
+      <c r="N72" s="20">
         <v>3.81518914277475</v>
       </c>
-      <c r="O72" s="25">
+      <c r="O72" s="21">
         <v>-3.855</v>
       </c>
-      <c r="P72" s="27"/>
-      <c r="Q72" s="23" t="s">
+      <c r="P72" s="23"/>
+      <c r="Q72" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S72" s="23" t="s">
+      <c r="S72" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W72" s="25">
+      <c r="W72" s="21">
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="73" spans="1:23" s="25" customFormat="1">
+    <row r="73" spans="1:23" s="21" customFormat="1">
       <c r="A73" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B73" s="25">
+      <c r="B73" s="21">
         <v>0.214</v>
       </c>
-      <c r="C73" s="24">
+      <c r="C73" s="20">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="D73" s="24">
+      <c r="D73" s="20">
         <v>-1.22567508688439</v>
       </c>
-      <c r="I73" s="24">
+      <c r="I73" s="20">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="N73" s="24">
+      <c r="N73" s="20">
         <v>5.5949999999999998</v>
       </c>
-      <c r="O73" s="25">
+      <c r="O73" s="21">
         <v>-5.4782042149448502</v>
       </c>
-      <c r="P73" s="27"/>
-      <c r="Q73" s="23" t="s">
+      <c r="P73" s="23"/>
+      <c r="Q73" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S73" s="23" t="s">
+      <c r="S73" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W73" s="25">
+      <c r="W73" s="21">
         <v>0.32</v>
       </c>
     </row>
-    <row r="74" spans="1:23" s="25" customFormat="1">
+    <row r="74" spans="1:23" s="21" customFormat="1">
       <c r="A74" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B74" s="25">
+      <c r="B74" s="21">
         <v>0.254</v>
       </c>
-      <c r="C74" s="24">
+      <c r="C74" s="20">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="D74" s="24">
+      <c r="D74" s="20">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="I74" s="24">
+      <c r="I74" s="20">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="N74" s="24">
+      <c r="N74" s="20">
         <v>6.484</v>
       </c>
-      <c r="O74" s="25">
+      <c r="O74" s="21">
         <v>-6.2489999999999997</v>
       </c>
-      <c r="P74" s="27"/>
-      <c r="Q74" s="23" t="s">
+      <c r="P74" s="23"/>
+      <c r="Q74" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S74" s="23" t="s">
+      <c r="S74" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W74" s="25">
+      <c r="W74" s="21">
         <v>0.37799999999999995</v>
       </c>
     </row>
-    <row r="75" spans="1:23" s="25" customFormat="1">
+    <row r="75" spans="1:23" s="21" customFormat="1">
       <c r="A75" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B75" s="25">
+      <c r="B75" s="21">
         <v>0.28399999999999997</v>
       </c>
-      <c r="C75" s="24">
+      <c r="C75" s="20">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="D75" s="24">
+      <c r="D75" s="20">
         <v>-1.47353470842518</v>
       </c>
-      <c r="I75" s="24">
+      <c r="I75" s="20">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="N75" s="24">
+      <c r="N75" s="20">
         <v>8.0890000000000004</v>
       </c>
-      <c r="O75" s="25">
+      <c r="O75" s="21">
         <v>-7.9485854277214001</v>
       </c>
-      <c r="P75" s="27"/>
-      <c r="Q75" s="23" t="s">
+      <c r="P75" s="23"/>
+      <c r="Q75" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S75" s="23" t="s">
+      <c r="S75" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W75" s="25">
+      <c r="W75" s="21">
         <v>0.39100000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:23" s="25" customFormat="1">
+    <row r="76" spans="1:23" s="21" customFormat="1">
       <c r="A76" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B76" s="25">
+      <c r="B76" s="21">
         <v>0.33400000000000002</v>
       </c>
-      <c r="C76" s="24">
+      <c r="C76" s="20">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="D76" s="24">
+      <c r="D76" s="20">
         <v>-1.99253212300414</v>
       </c>
-      <c r="I76" s="24">
+      <c r="I76" s="20">
         <v>2.0830000000081101</v>
       </c>
-      <c r="N76" s="24">
+      <c r="N76" s="20">
         <v>11.872999999999999</v>
       </c>
-      <c r="O76" s="25">
+      <c r="O76" s="21">
         <v>-9.6077296533960403</v>
       </c>
-      <c r="P76" s="27"/>
-      <c r="Q76" s="23" t="s">
+      <c r="P76" s="23"/>
+      <c r="Q76" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S76" s="23" t="s">
+      <c r="S76" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W76" s="25">
+      <c r="W76" s="21">
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:23" s="25" customFormat="1">
+    <row r="77" spans="1:23" s="21" customFormat="1">
       <c r="A77" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B77" s="25">
+      <c r="B77" s="21">
         <v>0.379</v>
       </c>
-      <c r="C77" s="24">
+      <c r="C77" s="20">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="D77" s="24">
+      <c r="D77" s="20">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="I77" s="24">
+      <c r="I77" s="20">
         <v>5.5389999999999997</v>
       </c>
-      <c r="N77" s="24">
+      <c r="N77" s="20">
         <v>14.304133448972699</v>
       </c>
-      <c r="O77" s="25">
+      <c r="O77" s="21">
         <v>-8.8979999999999997</v>
       </c>
-      <c r="P77" s="27"/>
-      <c r="Q77" s="23" t="s">
+      <c r="P77" s="23"/>
+      <c r="Q77" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S77" s="23" t="s">
+      <c r="S77" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W77" s="25">
+      <c r="W77" s="21">
         <v>0.39100000000000001</v>
       </c>
     </row>
@@ -4741,93 +4752,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49AD3A4-3FFD-6442-B843-C2A9D40041A1}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B1">
-        <v>-0.86358170086251695</v>
-      </c>
-      <c r="C1">
-        <v>-1.4368262739973601</v>
-      </c>
-      <c r="D1">
-        <v>-2.4905493340587901</v>
-      </c>
-      <c r="E1">
-        <v>-3.855</v>
-      </c>
-      <c r="F1">
-        <v>-5.4782042149448502</v>
-      </c>
-      <c r="G1">
-        <v>-6.2489999999999997</v>
-      </c>
-      <c r="H1">
-        <v>-7.9485854277214001</v>
-      </c>
-      <c r="I1">
-        <v>-9.6077296533960403</v>
-      </c>
-      <c r="J1">
-        <v>-8.8979999999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="D4">
-        <v>-0.86358170086251695</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="D5">
-        <v>-1.4368262739973601</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="D6">
-        <v>-2.4905493340587901</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="D7">
-        <v>-3.855</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="D8">
-        <v>-5.4782042149448502</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="D9">
-        <v>-6.2489999999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="D10">
-        <v>-7.9485854277214001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11">
-        <v>-9.6077296533960403</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="D12">
-        <v>-8.8979999999999997</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67790435-58F9-4644-8DFA-12F03F5D194D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CD058E-38E8-0946-888A-DB788D917361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="26880" windowHeight="15220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Supplementary File 1e vip" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$S$1:$S$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$T$1:$T$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="116">
   <si>
     <t>sample</t>
   </si>
@@ -372,6 +372,15 @@
   </si>
   <si>
     <t>D=0.027_M</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>sysbio</t>
+  </si>
+  <si>
+    <t>other_lab</t>
   </si>
 </sst>
 </file>
@@ -1364,3385 +1373,3617 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8F22EE-2E06-6741-B451-D4EA064EAB2E}">
-  <dimension ref="A1:Y77"/>
+  <dimension ref="A1:Z77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="37.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="28" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="23" customWidth="1"/>
+    <col min="2" max="2" width="32.1640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="12" customFormat="1">
+    <row r="1" spans="1:26" s="12" customFormat="1">
       <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="K1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="O1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="Q1" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="S1" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="T1" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="U1" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="V1" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="W1" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="X1" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="Y1" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Z1" s="12" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="12" customFormat="1">
+    <row r="2" spans="1:26" s="12" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="11"/>
-    </row>
-    <row r="3" spans="1:25" s="12" customFormat="1">
+      <c r="B2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q2" s="11"/>
+    </row>
+    <row r="3" spans="1:26" s="12" customFormat="1">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="11"/>
-    </row>
-    <row r="4" spans="1:25" s="12" customFormat="1">
+      <c r="B3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q3" s="11"/>
+    </row>
+    <row r="4" spans="1:26" s="12" customFormat="1">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="11"/>
-    </row>
-    <row r="5" spans="1:25" s="13" customFormat="1">
+      <c r="B4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q4" s="11"/>
+    </row>
+    <row r="5" spans="1:26" s="13" customFormat="1">
       <c r="A5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="13">
         <v>0.42399999999999999</v>
       </c>
-      <c r="C5" s="13">
+      <c r="D5" s="13">
         <v>18.79</v>
       </c>
-      <c r="I5" s="13">
+      <c r="J5" s="13">
         <v>26.97</v>
       </c>
-      <c r="J5" s="13">
+      <c r="K5" s="13">
         <v>0.56599999999999995</v>
       </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>0.16300000000000001</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>1.4690000000000001</v>
       </c>
-      <c r="N5" s="13">
+      <c r="O5" s="13">
         <v>24.501999999999999</v>
       </c>
-      <c r="O5" s="13">
+      <c r="P5" s="13">
         <v>2.919</v>
       </c>
-      <c r="P5" s="14"/>
-    </row>
-    <row r="6" spans="1:25" s="15" customFormat="1">
+      <c r="Q5" s="14"/>
+    </row>
+    <row r="6" spans="1:26" s="15" customFormat="1">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="15">
         <v>0.05</v>
       </c>
-      <c r="C6" s="16">
+      <c r="D6" s="16">
         <v>0.82299999999999995</v>
       </c>
-      <c r="D6" s="16">
+      <c r="E6" s="16">
         <v>0.13100000000000001</v>
       </c>
-      <c r="E6" s="16"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
-      <c r="H6" s="16">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16">
         <v>0.13100000000000001</v>
       </c>
-      <c r="I6" s="16">
-        <v>0</v>
-      </c>
       <c r="J6" s="16">
         <v>0</v>
       </c>
       <c r="K6" s="16">
+        <v>0</v>
+      </c>
+      <c r="L6" s="16">
         <v>7.2308500000000005E-4</v>
       </c>
-      <c r="L6" s="16">
-        <v>0</v>
-      </c>
       <c r="M6" s="16">
+        <v>0</v>
+      </c>
+      <c r="N6" s="16">
         <v>4.0285879999999996E-3</v>
       </c>
-      <c r="N6" s="16">
+      <c r="O6" s="16">
         <v>2.4449999999999998</v>
       </c>
-      <c r="O6" s="16">
+      <c r="P6" s="16">
         <v>2.3620000000000001</v>
       </c>
-      <c r="P6" s="17">
+      <c r="Q6" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q6" s="15" t="s">
+      <c r="R6" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R6" s="15">
+      <c r="S6" s="15">
         <v>0.5</v>
       </c>
-      <c r="S6" s="15" t="s">
+      <c r="T6" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T6" s="15">
+      <c r="U6" s="15">
         <v>30</v>
       </c>
-      <c r="U6" s="15" t="s">
+      <c r="V6" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V6" s="15">
+      <c r="W6" s="15">
         <v>2.1734E-2</v>
       </c>
-      <c r="W6" s="15">
+      <c r="X6" s="15">
         <v>0.27251471399999999</v>
       </c>
     </row>
-    <row r="7" spans="1:25" s="15" customFormat="1">
+    <row r="7" spans="1:26" s="15" customFormat="1">
       <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="15">
         <v>0.05</v>
       </c>
-      <c r="C7" s="16">
+      <c r="D7" s="16">
         <v>0.70399999999999996</v>
       </c>
-      <c r="D7" s="16">
+      <c r="E7" s="16">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
-      <c r="H7" s="16">
+      <c r="H7" s="16"/>
+      <c r="I7" s="16">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="I7" s="16">
-        <v>0</v>
-      </c>
       <c r="J7" s="16">
         <v>0</v>
       </c>
       <c r="K7" s="16">
+        <v>0</v>
+      </c>
+      <c r="L7" s="16">
         <v>1.6583900000000001E-4</v>
       </c>
-      <c r="L7" s="16">
-        <v>0</v>
-      </c>
       <c r="M7" s="16">
+        <v>0</v>
+      </c>
+      <c r="N7" s="16">
         <v>6.6796169999999997E-3</v>
       </c>
-      <c r="N7" s="16">
+      <c r="O7" s="16">
         <v>2.105</v>
       </c>
-      <c r="O7" s="16">
+      <c r="P7" s="16">
         <v>2.2759999999999998</v>
       </c>
-      <c r="P7" s="17">
+      <c r="Q7" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q7" s="15" t="s">
+      <c r="R7" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R7" s="15">
+      <c r="S7" s="15">
         <v>0.5</v>
       </c>
-      <c r="S7" s="15" t="s">
+      <c r="T7" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T7" s="15">
+      <c r="U7" s="15">
         <v>30</v>
       </c>
-      <c r="U7" s="15" t="s">
+      <c r="V7" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V7" s="15">
+      <c r="W7" s="15">
         <v>2.4941000000000001E-2</v>
       </c>
-      <c r="W7" s="15">
+      <c r="X7" s="15">
         <v>0.25082010700000001</v>
       </c>
     </row>
-    <row r="8" spans="1:25" s="15" customFormat="1">
+    <row r="8" spans="1:26" s="15" customFormat="1">
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="15">
         <v>0.05</v>
       </c>
-      <c r="C8" s="16">
+      <c r="D8" s="16">
         <v>0.76800000000000002</v>
       </c>
-      <c r="D8" s="16">
+      <c r="E8" s="16">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E8" s="16"/>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
-      <c r="H8" s="16">
+      <c r="H8" s="16"/>
+      <c r="I8" s="16">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I8" s="16">
-        <v>0</v>
-      </c>
       <c r="J8" s="16">
         <v>0</v>
       </c>
       <c r="K8" s="16">
+        <v>0</v>
+      </c>
+      <c r="L8" s="16">
         <v>3.81541E-4</v>
       </c>
-      <c r="L8" s="16">
-        <v>0</v>
-      </c>
       <c r="M8" s="16">
+        <v>0</v>
+      </c>
+      <c r="N8" s="16">
         <v>9.7823159999999992E-3</v>
       </c>
-      <c r="N8" s="16">
+      <c r="O8" s="16">
         <v>2.383</v>
       </c>
-      <c r="O8" s="16">
+      <c r="P8" s="16">
         <v>1.6240000000000001</v>
       </c>
-      <c r="P8" s="17">
+      <c r="Q8" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q8" s="15" t="s">
+      <c r="R8" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R8" s="15">
+      <c r="S8" s="15">
         <v>0.5</v>
       </c>
-      <c r="S8" s="15" t="s">
+      <c r="T8" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T8" s="15">
+      <c r="U8" s="15">
         <v>30</v>
       </c>
-      <c r="U8" s="15" t="s">
+      <c r="V8" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V8" s="15">
+      <c r="W8" s="15">
         <v>2.5831E-2</v>
       </c>
-      <c r="W8" s="15">
+      <c r="X8" s="15">
         <v>0.26109650000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:25" s="15" customFormat="1">
+    <row r="9" spans="1:26" s="15" customFormat="1">
       <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="15">
         <v>0.1</v>
       </c>
-      <c r="C9" s="16">
+      <c r="D9" s="16">
         <v>1.18</v>
       </c>
-      <c r="D9" s="16">
+      <c r="E9" s="16">
         <v>2.2029999999999998</v>
       </c>
-      <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
-      <c r="H9" s="16">
+      <c r="H9" s="16"/>
+      <c r="I9" s="16">
         <v>2.2029999999999998</v>
       </c>
-      <c r="I9" s="16">
-        <v>0</v>
-      </c>
       <c r="J9" s="16">
         <v>0</v>
       </c>
       <c r="K9" s="16">
+        <v>0</v>
+      </c>
+      <c r="L9" s="16">
         <v>1.2795499999999999E-4</v>
       </c>
-      <c r="L9" s="16">
-        <v>0</v>
-      </c>
       <c r="M9" s="16">
         <v>0</v>
       </c>
       <c r="N9" s="16">
+        <v>0</v>
+      </c>
+      <c r="O9" s="16">
         <v>1.93</v>
       </c>
-      <c r="O9" s="16">
+      <c r="P9" s="16">
         <v>2.44</v>
       </c>
-      <c r="P9" s="17">
+      <c r="Q9" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q9" s="15" t="s">
+      <c r="R9" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R9" s="15">
+      <c r="S9" s="15">
         <v>5</v>
       </c>
-      <c r="S9" s="15" t="s">
+      <c r="T9" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T9" s="15">
+      <c r="U9" s="15">
         <v>3</v>
       </c>
-      <c r="U9" s="15" t="s">
+      <c r="V9" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V9" s="15">
+      <c r="W9" s="15">
         <v>5.3443999999999998E-2</v>
       </c>
-      <c r="W9" s="15">
+      <c r="X9" s="15">
         <v>0.35967375000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:25" s="15" customFormat="1">
+    <row r="10" spans="1:26" s="15" customFormat="1">
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="15">
         <v>0.1</v>
       </c>
-      <c r="C10" s="16">
+      <c r="D10" s="16">
         <v>1.127</v>
       </c>
-      <c r="D10" s="16">
+      <c r="E10" s="16">
         <v>2.0979999999999999</v>
       </c>
-      <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
-      <c r="H10" s="16">
+      <c r="H10" s="16"/>
+      <c r="I10" s="16">
         <v>2.0979999999999999</v>
       </c>
-      <c r="I10" s="16">
+      <c r="J10" s="16">
         <v>1.6766474999999999E-2</v>
       </c>
-      <c r="J10" s="16">
-        <v>0</v>
-      </c>
       <c r="K10" s="16">
+        <v>0</v>
+      </c>
+      <c r="L10" s="16">
         <v>1.5726999999999999E-4</v>
       </c>
-      <c r="L10" s="16">
-        <v>0</v>
-      </c>
       <c r="M10" s="16">
         <v>0</v>
       </c>
       <c r="N10" s="16">
+        <v>0</v>
+      </c>
+      <c r="O10" s="16">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O10" s="16">
+      <c r="P10" s="16">
         <v>2.39</v>
       </c>
-      <c r="P10" s="17">
+      <c r="Q10" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q10" s="15" t="s">
+      <c r="R10" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R10" s="15">
+      <c r="S10" s="15">
         <v>5</v>
       </c>
-      <c r="S10" s="15" t="s">
+      <c r="T10" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T10" s="15">
+      <c r="U10" s="15">
         <v>3</v>
       </c>
-      <c r="U10" s="15" t="s">
+      <c r="V10" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V10" s="15">
+      <c r="W10" s="15">
         <v>5.0594E-2</v>
       </c>
-      <c r="W10" s="15">
+      <c r="X10" s="15">
         <v>0.377942893</v>
       </c>
     </row>
-    <row r="11" spans="1:25" s="15" customFormat="1">
+    <row r="11" spans="1:26" s="15" customFormat="1">
       <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="15">
         <v>0.1</v>
       </c>
-      <c r="C11" s="16">
+      <c r="D11" s="16">
         <v>1.0980000000000001</v>
       </c>
-      <c r="D11" s="16">
+      <c r="E11" s="16">
         <v>2.0550000000000002</v>
       </c>
-      <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
-      <c r="H11" s="16">
+      <c r="H11" s="16"/>
+      <c r="I11" s="16">
         <v>2.0550000000000002</v>
       </c>
-      <c r="I11" s="16">
-        <v>0</v>
-      </c>
       <c r="J11" s="16">
         <v>0</v>
       </c>
       <c r="K11" s="16">
+        <v>0</v>
+      </c>
+      <c r="L11" s="16">
         <v>1.3422099999999999E-4</v>
       </c>
-      <c r="L11" s="16">
-        <v>0</v>
-      </c>
       <c r="M11" s="16">
         <v>0</v>
       </c>
       <c r="N11" s="16">
+        <v>0</v>
+      </c>
+      <c r="O11" s="16">
         <v>1.97</v>
       </c>
-      <c r="O11" s="16">
+      <c r="P11" s="16">
         <v>2.1800000000000002</v>
       </c>
-      <c r="P11" s="17">
+      <c r="Q11" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q11" s="15" t="s">
+      <c r="R11" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R11" s="15">
+      <c r="S11" s="15">
         <v>5</v>
       </c>
-      <c r="S11" s="15" t="s">
+      <c r="T11" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T11" s="15">
+      <c r="U11" s="15">
         <v>3</v>
       </c>
-      <c r="U11" s="15" t="s">
+      <c r="V11" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V11" s="15">
+      <c r="W11" s="15">
         <v>4.5962000000000003E-2</v>
       </c>
-      <c r="W11" s="15">
+      <c r="X11" s="15">
         <v>0.33645671399999999</v>
       </c>
     </row>
-    <row r="12" spans="1:25" s="15" customFormat="1">
+    <row r="12" spans="1:26" s="15" customFormat="1">
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="15">
         <v>0.1</v>
       </c>
-      <c r="C12" s="16">
+      <c r="D12" s="16">
         <v>1.51</v>
       </c>
-      <c r="D12" s="16">
+      <c r="E12" s="16">
         <v>0.308</v>
       </c>
-      <c r="E12" s="16"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
-      <c r="H12" s="16">
+      <c r="H12" s="16"/>
+      <c r="I12" s="16">
         <v>0.308</v>
       </c>
-      <c r="I12" s="16">
-        <v>0</v>
-      </c>
       <c r="J12" s="16">
+        <v>0</v>
+      </c>
+      <c r="K12" s="16">
         <v>7.5614127000000003E-2</v>
       </c>
-      <c r="K12" s="16">
+      <c r="L12" s="16">
         <v>1.7982350000000001E-2</v>
       </c>
-      <c r="L12" s="16">
-        <v>0</v>
-      </c>
       <c r="M12" s="16">
         <v>0</v>
       </c>
       <c r="N12" s="16">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16">
         <v>3.4660000000000002</v>
       </c>
-      <c r="O12" s="16">
+      <c r="P12" s="16">
         <v>3.6160000000000001</v>
       </c>
-      <c r="P12" s="17">
+      <c r="Q12" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q12" s="15" t="s">
+      <c r="R12" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R12" s="15">
+      <c r="S12" s="15">
         <v>0.5</v>
       </c>
-      <c r="S12" s="15" t="s">
+      <c r="T12" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T12" s="15">
+      <c r="U12" s="15">
         <v>30</v>
       </c>
-      <c r="U12" s="15" t="s">
+      <c r="V12" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="V12" s="15">
+      <c r="W12" s="15">
         <v>2.2624999999999999E-2</v>
       </c>
-      <c r="W12" s="15">
+      <c r="X12" s="15">
         <v>0.209333929</v>
       </c>
     </row>
-    <row r="13" spans="1:25" s="15" customFormat="1">
+    <row r="13" spans="1:26" s="15" customFormat="1">
       <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="15">
         <v>0.1</v>
       </c>
-      <c r="C13" s="16">
+      <c r="D13" s="16">
         <v>1.5109999999999999</v>
       </c>
-      <c r="D13" s="16">
+      <c r="E13" s="16">
         <v>0.308</v>
       </c>
-      <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
-      <c r="H13" s="16">
+      <c r="H13" s="16"/>
+      <c r="I13" s="16">
         <v>0.308</v>
       </c>
-      <c r="I13" s="16">
-        <v>0</v>
-      </c>
       <c r="J13" s="16">
+        <v>0</v>
+      </c>
+      <c r="K13" s="16">
         <v>4.9087042999999997E-2</v>
       </c>
-      <c r="K13" s="16">
+      <c r="L13" s="16">
         <v>1.38432E-2</v>
       </c>
-      <c r="L13" s="16">
-        <v>0</v>
-      </c>
       <c r="M13" s="16">
         <v>0</v>
       </c>
       <c r="N13" s="16">
+        <v>0</v>
+      </c>
+      <c r="O13" s="16">
         <v>3.1360000000000001</v>
       </c>
-      <c r="O13" s="16">
+      <c r="P13" s="16">
         <v>3.5219999999999998</v>
       </c>
-      <c r="P13" s="17">
+      <c r="Q13" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q13" s="15" t="s">
+      <c r="R13" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R13" s="15">
+      <c r="S13" s="15">
         <v>0.5</v>
       </c>
-      <c r="S13" s="15" t="s">
+      <c r="T13" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T13" s="15">
+      <c r="U13" s="15">
         <v>30</v>
       </c>
-      <c r="U13" s="15" t="s">
+      <c r="V13" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="V13" s="15">
+      <c r="W13" s="15">
         <v>2.6009999999999998E-2</v>
       </c>
-      <c r="W13" s="15">
+      <c r="X13" s="15">
         <v>0.22151335699999999</v>
       </c>
     </row>
-    <row r="14" spans="1:25" s="15" customFormat="1">
+    <row r="14" spans="1:26" s="15" customFormat="1">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="15">
         <v>0.1</v>
       </c>
-      <c r="C14" s="16">
+      <c r="D14" s="16">
         <v>1.4890000000000001</v>
       </c>
-      <c r="D14" s="16">
+      <c r="E14" s="16">
         <v>0.30399999999999999</v>
       </c>
-      <c r="E14" s="16"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
-      <c r="H14" s="16">
+      <c r="H14" s="16"/>
+      <c r="I14" s="16">
         <v>0.30399999999999999</v>
       </c>
-      <c r="I14" s="16">
-        <v>0</v>
-      </c>
       <c r="J14" s="16">
+        <v>0</v>
+      </c>
+      <c r="K14" s="16">
         <v>6.6037847999999996E-2</v>
       </c>
-      <c r="K14" s="16">
+      <c r="L14" s="16">
         <v>1.602926E-2</v>
       </c>
-      <c r="L14" s="16">
-        <v>0</v>
-      </c>
       <c r="M14" s="16">
         <v>0</v>
       </c>
       <c r="N14" s="16">
+        <v>0</v>
+      </c>
+      <c r="O14" s="16">
         <v>3.161</v>
       </c>
-      <c r="O14" s="16">
+      <c r="P14" s="16">
         <v>3.8239999999999998</v>
       </c>
-      <c r="P14" s="17">
+      <c r="Q14" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q14" s="15" t="s">
+      <c r="R14" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R14" s="15">
+      <c r="S14" s="15">
         <v>0.5</v>
       </c>
-      <c r="S14" s="15" t="s">
+      <c r="T14" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T14" s="15">
+      <c r="U14" s="15">
         <v>30</v>
       </c>
-      <c r="U14" s="15" t="s">
+      <c r="V14" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="V14" s="15">
+      <c r="W14" s="15">
         <v>2.7257E-2</v>
       </c>
-      <c r="W14" s="15">
+      <c r="X14" s="15">
         <v>0.24587221400000001</v>
       </c>
     </row>
-    <row r="15" spans="1:25" s="15" customFormat="1">
+    <row r="15" spans="1:26" s="15" customFormat="1">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="15">
         <v>0.13</v>
       </c>
-      <c r="C15" s="16">
+      <c r="D15" s="16">
         <v>2.0190000000000001</v>
       </c>
-      <c r="D15" s="16">
+      <c r="E15" s="16">
         <v>0.41499999999999998</v>
       </c>
-      <c r="E15" s="16"/>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
-      <c r="H15" s="16">
+      <c r="H15" s="16"/>
+      <c r="I15" s="16">
         <v>0.41499999999999998</v>
       </c>
-      <c r="I15" s="16">
+      <c r="J15" s="16">
         <v>0.14387805000000001</v>
       </c>
-      <c r="J15" s="16">
+      <c r="K15" s="16">
         <v>0.23128044</v>
       </c>
-      <c r="K15" s="16">
+      <c r="L15" s="16">
         <v>2.4418572999999999E-2</v>
       </c>
-      <c r="L15" s="16">
+      <c r="M15" s="16">
         <v>7.3894399999999995E-4</v>
       </c>
-      <c r="M15" s="16">
+      <c r="N15" s="16">
         <v>4.2122905000000002E-2</v>
       </c>
-      <c r="N15" s="16">
+      <c r="O15" s="16">
         <v>5.51</v>
       </c>
-      <c r="O15" s="16">
+      <c r="P15" s="16">
         <v>5.2519999999999998</v>
       </c>
-      <c r="P15" s="17">
+      <c r="Q15" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q15" s="15" t="s">
+      <c r="R15" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R15" s="15">
+      <c r="S15" s="15">
         <v>0.5</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T15" s="15">
+      <c r="U15" s="15">
         <v>30</v>
       </c>
-      <c r="U15" s="15" t="s">
+      <c r="V15" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V15" s="15">
+      <c r="W15" s="15">
         <v>2.6366000000000001E-2</v>
       </c>
-      <c r="W15" s="15">
+      <c r="X15" s="15">
         <v>0.30372450000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:25" s="15" customFormat="1">
+    <row r="16" spans="1:26" s="15" customFormat="1">
       <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="15">
         <v>0.13</v>
       </c>
-      <c r="C16" s="16">
+      <c r="D16" s="16">
         <v>2.0590000000000002</v>
       </c>
-      <c r="D16" s="16">
+      <c r="E16" s="16">
         <v>0.42499999999999999</v>
       </c>
-      <c r="E16" s="16"/>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
-      <c r="H16" s="16">
+      <c r="H16" s="16"/>
+      <c r="I16" s="16">
         <v>0.42499999999999999</v>
       </c>
-      <c r="I16" s="16">
+      <c r="J16" s="16">
         <v>0.13916811300000001</v>
       </c>
-      <c r="J16" s="16">
+      <c r="K16" s="16">
         <v>0.22761730999999999</v>
       </c>
-      <c r="K16" s="16">
+      <c r="L16" s="16">
         <v>2.5077986E-2</v>
       </c>
-      <c r="L16" s="16">
+      <c r="M16" s="16">
         <v>2.152588E-3</v>
       </c>
-      <c r="M16" s="16">
+      <c r="N16" s="16">
         <v>3.3899711999999999E-2</v>
       </c>
-      <c r="N16" s="16">
+      <c r="O16" s="16">
         <v>5.3739999999999997</v>
       </c>
-      <c r="O16" s="16">
+      <c r="P16" s="16">
         <v>4.5460000000000003</v>
       </c>
-      <c r="P16" s="17">
+      <c r="Q16" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q16" s="15" t="s">
+      <c r="R16" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R16" s="15">
+      <c r="S16" s="15">
         <v>0.5</v>
       </c>
-      <c r="S16" s="15" t="s">
+      <c r="T16" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T16" s="15">
+      <c r="U16" s="15">
         <v>30</v>
       </c>
-      <c r="U16" s="15" t="s">
+      <c r="V16" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V16" s="15">
+      <c r="W16" s="15">
         <v>2.5831E-2</v>
       </c>
-      <c r="W16" s="15">
+      <c r="X16" s="15">
         <v>0.25690982099999998</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="15" customFormat="1">
+    <row r="17" spans="1:25" s="15" customFormat="1">
       <c r="A17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="15">
         <v>0.13</v>
       </c>
-      <c r="C17" s="16">
+      <c r="D17" s="16">
         <v>2.1349999999999998</v>
       </c>
-      <c r="D17" s="16">
+      <c r="E17" s="16">
         <v>0.438</v>
       </c>
-      <c r="E17" s="16"/>
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
-      <c r="H17" s="16">
+      <c r="H17" s="16"/>
+      <c r="I17" s="16">
         <v>0.438</v>
       </c>
-      <c r="I17" s="16">
+      <c r="J17" s="16">
         <v>0.13267562499999999</v>
       </c>
-      <c r="J17" s="16">
+      <c r="K17" s="16">
         <v>0.25727792100000002</v>
       </c>
-      <c r="K17" s="16">
+      <c r="L17" s="16">
         <v>2.6121129999999999E-2</v>
       </c>
-      <c r="L17" s="16">
-        <v>0</v>
-      </c>
       <c r="M17" s="16">
+        <v>0</v>
+      </c>
+      <c r="N17" s="16">
         <v>4.1071206999999998E-2</v>
       </c>
-      <c r="N17" s="16">
+      <c r="O17" s="16">
         <v>5.3019999999999996</v>
       </c>
-      <c r="O17" s="16">
+      <c r="P17" s="16">
         <v>5.07</v>
       </c>
-      <c r="P17" s="17">
+      <c r="Q17" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q17" s="15" t="s">
+      <c r="R17" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R17" s="15">
+      <c r="S17" s="15">
         <v>0.5</v>
       </c>
-      <c r="S17" s="15" t="s">
+      <c r="T17" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T17" s="15">
+      <c r="U17" s="15">
         <v>30</v>
       </c>
-      <c r="U17" s="15" t="s">
+      <c r="V17" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V17" s="15">
+      <c r="W17" s="15">
         <v>2.5297E-2</v>
       </c>
-      <c r="W17" s="15">
+      <c r="X17" s="15">
         <v>0.26642500000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="15" customFormat="1">
+    <row r="18" spans="1:25" s="15" customFormat="1">
       <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="15">
         <v>0.18</v>
       </c>
-      <c r="C18" s="16">
+      <c r="D18" s="16">
         <v>3.266</v>
       </c>
-      <c r="D18" s="16">
+      <c r="E18" s="16">
         <v>0.66900000000000004</v>
       </c>
-      <c r="E18" s="16"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="16">
+      <c r="H18" s="16"/>
+      <c r="I18" s="16">
         <v>0.66900000000000004</v>
       </c>
-      <c r="I18" s="16">
+      <c r="J18" s="16">
         <v>1.2813869950000001</v>
       </c>
-      <c r="J18" s="16">
+      <c r="K18" s="16">
         <v>0.18048138799999999</v>
       </c>
-      <c r="K18" s="16">
+      <c r="L18" s="16">
         <v>3.2745818000000003E-2</v>
       </c>
-      <c r="L18" s="16">
-        <v>0</v>
-      </c>
       <c r="M18" s="16">
+        <v>0</v>
+      </c>
+      <c r="N18" s="16">
         <v>5.6452840000000004E-3</v>
       </c>
-      <c r="N18" s="16">
+      <c r="O18" s="16">
         <v>7.2619999999999996</v>
       </c>
-      <c r="O18" s="16">
+      <c r="P18" s="16">
         <v>5.42</v>
       </c>
-      <c r="P18" s="17">
+      <c r="Q18" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q18" s="15" t="s">
+      <c r="R18" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R18" s="15">
+      <c r="S18" s="15">
         <v>0.5</v>
       </c>
-      <c r="S18" s="15" t="s">
+      <c r="T18" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T18" s="15">
+      <c r="U18" s="15">
         <v>30</v>
       </c>
-      <c r="U18" s="15" t="s">
+      <c r="V18" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V18" s="15">
+      <c r="W18" s="15">
         <v>3.9014E-2</v>
       </c>
-      <c r="W18" s="15">
+      <c r="X18" s="15">
         <v>0.28926142900000001</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="15" customFormat="1">
+    <row r="19" spans="1:25" s="15" customFormat="1">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="15">
         <v>0.18</v>
       </c>
-      <c r="C19" s="16">
+      <c r="D19" s="16">
         <v>3.202</v>
       </c>
-      <c r="D19" s="16">
+      <c r="E19" s="16">
         <v>0.65900000000000003</v>
       </c>
-      <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
-      <c r="H19" s="16">
+      <c r="H19" s="16"/>
+      <c r="I19" s="16">
         <v>0.65900000000000003</v>
       </c>
-      <c r="I19" s="16">
+      <c r="J19" s="16">
         <v>1.4870797280000001</v>
       </c>
-      <c r="J19" s="16">
+      <c r="K19" s="16">
         <v>0.41515672300000001</v>
       </c>
-      <c r="K19" s="16">
+      <c r="L19" s="16">
         <v>3.1272250000000001E-2</v>
       </c>
-      <c r="L19" s="16">
+      <c r="M19" s="16">
         <v>2.6969479999999998E-3</v>
       </c>
-      <c r="M19" s="16">
+      <c r="N19" s="16">
         <v>1.6418242E-2</v>
       </c>
-      <c r="N19" s="16">
+      <c r="O19" s="16">
         <v>7.3049999999999997</v>
       </c>
-      <c r="O19" s="16">
+      <c r="P19" s="16">
         <v>6.0170000000000003</v>
       </c>
-      <c r="P19" s="17">
+      <c r="Q19" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q19" s="15" t="s">
+      <c r="R19" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R19" s="15">
+      <c r="S19" s="15">
         <v>0.5</v>
       </c>
-      <c r="S19" s="15" t="s">
+      <c r="T19" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T19" s="15">
+      <c r="U19" s="15">
         <v>30</v>
       </c>
-      <c r="U19" s="15" t="s">
+      <c r="V19" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V19" s="15">
+      <c r="W19" s="15">
         <v>3.8657999999999998E-2</v>
       </c>
-      <c r="W19" s="15">
+      <c r="X19" s="15">
         <v>0.28202989299999998</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="15" customFormat="1">
+    <row r="20" spans="1:25" s="15" customFormat="1">
       <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="15">
         <v>0.18</v>
       </c>
-      <c r="C20" s="16">
+      <c r="D20" s="16">
         <v>2.83</v>
       </c>
-      <c r="D20" s="16">
+      <c r="E20" s="16">
         <v>0.58099999999999996</v>
       </c>
-      <c r="E20" s="16"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
-      <c r="H20" s="16">
+      <c r="H20" s="16"/>
+      <c r="I20" s="16">
         <v>0.58099999999999996</v>
       </c>
-      <c r="I20" s="16">
+      <c r="J20" s="16">
         <v>1.069367508</v>
       </c>
-      <c r="J20" s="16">
+      <c r="K20" s="16">
         <v>0.18424942899999999</v>
       </c>
-      <c r="K20" s="16">
+      <c r="L20" s="16">
         <v>2.652065E-2</v>
       </c>
-      <c r="L20" s="16">
-        <v>0</v>
-      </c>
       <c r="M20" s="16">
+        <v>0</v>
+      </c>
+      <c r="N20" s="16">
         <v>1.5674206999999999E-2</v>
       </c>
-      <c r="N20" s="16">
+      <c r="O20" s="16">
         <v>6.2510000000000003</v>
       </c>
-      <c r="O20" s="16">
+      <c r="P20" s="16">
         <v>5.2640000000000002</v>
       </c>
-      <c r="P20" s="17">
+      <c r="Q20" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q20" s="15" t="s">
+      <c r="R20" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R20" s="15">
+      <c r="S20" s="15">
         <v>0.5</v>
       </c>
-      <c r="S20" s="15" t="s">
+      <c r="T20" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T20" s="15">
+      <c r="U20" s="15">
         <v>30</v>
       </c>
-      <c r="U20" s="15" t="s">
+      <c r="V20" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V20" s="15">
+      <c r="W20" s="15">
         <v>3.7945E-2</v>
       </c>
-      <c r="W20" s="15">
+      <c r="X20" s="15">
         <v>0.288119607</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="15" customFormat="1">
+    <row r="21" spans="1:25" s="15" customFormat="1">
       <c r="A21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="15">
         <v>0.3</v>
       </c>
-      <c r="C21" s="16">
+      <c r="D21" s="16">
         <v>7.9909999999999997</v>
       </c>
-      <c r="D21" s="16">
+      <c r="E21" s="16">
         <v>1.6479999999999999</v>
       </c>
-      <c r="E21" s="16"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="16">
+      <c r="H21" s="16"/>
+      <c r="I21" s="16">
         <v>1.6479999999999999</v>
       </c>
-      <c r="I21" s="16">
+      <c r="J21" s="16">
         <v>7.0441347099999998</v>
       </c>
-      <c r="J21" s="16">
+      <c r="K21" s="16">
         <v>0.31251037799999998</v>
       </c>
-      <c r="K21" s="16">
+      <c r="L21" s="16">
         <v>5.1692219999999997E-2</v>
       </c>
-      <c r="L21" s="16">
+      <c r="M21" s="16">
         <v>1.1339925000000001E-2</v>
       </c>
-      <c r="M21" s="16">
-        <v>0</v>
-      </c>
       <c r="N21" s="16">
+        <v>0</v>
+      </c>
+      <c r="O21" s="16">
         <v>14.086</v>
       </c>
-      <c r="O21" s="16">
+      <c r="P21" s="16">
         <v>8.3010000000000002</v>
       </c>
-      <c r="P21" s="17">
+      <c r="Q21" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q21" s="15" t="s">
+      <c r="R21" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R21" s="15">
+      <c r="S21" s="15">
         <v>0.5</v>
       </c>
-      <c r="S21" s="15" t="s">
+      <c r="T21" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T21" s="15">
+      <c r="U21" s="15">
         <v>30</v>
       </c>
-      <c r="U21" s="15" t="s">
+      <c r="V21" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V21" s="15">
+      <c r="W21" s="15">
         <v>4.7031000000000003E-2</v>
       </c>
-      <c r="W21" s="15">
+      <c r="X21" s="15">
         <v>0.42247392900000003</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="15" customFormat="1">
+    <row r="22" spans="1:25" s="15" customFormat="1">
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="15">
         <v>0.3</v>
       </c>
-      <c r="C22" s="16">
+      <c r="D22" s="16">
         <v>8.2759999999999998</v>
       </c>
-      <c r="D22" s="16">
+      <c r="E22" s="16">
         <v>1.6950000000000001</v>
       </c>
-      <c r="E22" s="16"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="16">
+      <c r="H22" s="16"/>
+      <c r="I22" s="16">
         <v>1.6950000000000001</v>
       </c>
-      <c r="I22" s="16">
+      <c r="J22" s="16">
         <v>6.6847254490000001</v>
       </c>
-      <c r="J22" s="16">
+      <c r="K22" s="16">
         <v>0.27229536399999998</v>
       </c>
-      <c r="K22" s="16">
+      <c r="L22" s="16">
         <v>4.4478275999999997E-2</v>
       </c>
-      <c r="L22" s="16">
+      <c r="M22" s="16">
         <v>3.4668667E-2</v>
       </c>
-      <c r="M22" s="16">
-        <v>0</v>
-      </c>
       <c r="N22" s="16">
+        <v>0</v>
+      </c>
+      <c r="O22" s="16">
         <v>15.111000000000001</v>
       </c>
-      <c r="O22" s="16">
+      <c r="P22" s="16">
         <v>8.3870000000000005</v>
       </c>
-      <c r="P22" s="17">
+      <c r="Q22" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q22" s="15" t="s">
+      <c r="R22" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R22" s="15">
+      <c r="S22" s="15">
         <v>0.5</v>
       </c>
-      <c r="S22" s="15" t="s">
+      <c r="T22" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T22" s="15">
+      <c r="U22" s="15">
         <v>30</v>
       </c>
-      <c r="U22" s="15" t="s">
+      <c r="V22" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V22" s="15">
+      <c r="W22" s="15">
         <v>4.5606000000000001E-2</v>
       </c>
-      <c r="W22" s="15">
+      <c r="X22" s="15">
         <v>0.42133210700000001</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="15" customFormat="1">
+    <row r="23" spans="1:25" s="15" customFormat="1">
       <c r="A23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="15">
         <v>0.3</v>
       </c>
-      <c r="C23" s="16">
+      <c r="D23" s="16">
         <v>8.9320000000000004</v>
       </c>
-      <c r="D23" s="16">
+      <c r="E23" s="16">
         <v>1.8660000000000001</v>
       </c>
-      <c r="E23" s="16"/>
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
-      <c r="H23" s="16">
+      <c r="H23" s="16"/>
+      <c r="I23" s="16">
         <v>1.8660000000000001</v>
       </c>
-      <c r="I23" s="16">
+      <c r="J23" s="16">
         <v>8.2124218889999998</v>
       </c>
-      <c r="J23" s="16">
+      <c r="K23" s="16">
         <v>0.61718923199999998</v>
       </c>
-      <c r="K23" s="16">
+      <c r="L23" s="16">
         <v>6.4337543999999997E-2</v>
       </c>
-      <c r="L23" s="16">
+      <c r="M23" s="16">
         <v>2.9481279999999999E-2</v>
       </c>
-      <c r="M23" s="16">
-        <v>0</v>
-      </c>
       <c r="N23" s="16">
+        <v>0</v>
+      </c>
+      <c r="O23" s="16">
         <v>16.956</v>
       </c>
-      <c r="O23" s="16">
+      <c r="P23" s="16">
         <v>9.34</v>
       </c>
-      <c r="P23" s="17">
+      <c r="Q23" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q23" s="15" t="s">
+      <c r="R23" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R23" s="15">
+      <c r="S23" s="15">
         <v>0.5</v>
       </c>
-      <c r="S23" s="15" t="s">
+      <c r="T23" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T23" s="15">
+      <c r="U23" s="15">
         <v>30</v>
       </c>
-      <c r="U23" s="15" t="s">
+      <c r="V23" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V23" s="15">
+      <c r="W23" s="15">
         <v>5.2019000000000003E-2</v>
       </c>
-      <c r="W23" s="15">
+      <c r="X23" s="15">
         <v>0.39963749999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="15" customFormat="1">
+    <row r="24" spans="1:25" s="15" customFormat="1">
       <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="15">
         <v>0.35</v>
       </c>
-      <c r="C24" s="16">
+      <c r="D24" s="16">
         <v>12.936999999999999</v>
       </c>
-      <c r="D24" s="16">
+      <c r="E24" s="16">
         <v>2.7120000000000002</v>
       </c>
-      <c r="E24" s="16"/>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
-      <c r="H24" s="16">
+      <c r="H24" s="16"/>
+      <c r="I24" s="16">
         <v>2.7120000000000002</v>
       </c>
-      <c r="I24" s="16">
+      <c r="J24" s="16">
         <v>11.927306959999999</v>
       </c>
-      <c r="J24" s="16">
+      <c r="K24" s="16">
         <v>0.47269426599999997</v>
       </c>
-      <c r="K24" s="16">
+      <c r="L24" s="16">
         <v>8.9757966999999994E-2</v>
       </c>
-      <c r="L24" s="16">
+      <c r="M24" s="16">
         <v>3.5944587E-2</v>
       </c>
-      <c r="M24" s="16">
-        <v>0</v>
-      </c>
       <c r="N24" s="16">
+        <v>0</v>
+      </c>
+      <c r="O24" s="16">
         <v>20.902000000000001</v>
       </c>
-      <c r="O24" s="16">
+      <c r="P24" s="16">
         <v>12.682</v>
       </c>
-      <c r="P24" s="17">
+      <c r="Q24" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q24" s="15" t="s">
+      <c r="R24" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R24" s="15">
+      <c r="S24" s="15">
         <v>0.5</v>
       </c>
-      <c r="S24" s="15" t="s">
+      <c r="T24" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T24" s="15">
+      <c r="U24" s="15">
         <v>30</v>
       </c>
-      <c r="U24" s="15" t="s">
+      <c r="V24" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V24" s="15">
+      <c r="W24" s="15">
         <v>7.3219000000000006E-2</v>
       </c>
-      <c r="W24" s="15">
+      <c r="X24" s="15">
         <v>0.48415467400000001</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="15" customFormat="1">
+    <row r="25" spans="1:25" s="15" customFormat="1">
       <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="15">
         <v>0.35</v>
       </c>
-      <c r="C25" s="16">
+      <c r="D25" s="16">
         <v>13.23</v>
       </c>
-      <c r="D25" s="16">
+      <c r="E25" s="16">
         <v>2.786</v>
       </c>
-      <c r="E25" s="16"/>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
-      <c r="H25" s="16">
+      <c r="H25" s="16"/>
+      <c r="I25" s="16">
         <v>2.786</v>
       </c>
-      <c r="I25" s="16">
+      <c r="J25" s="16">
         <v>12.12470377</v>
       </c>
-      <c r="J25" s="16">
+      <c r="K25" s="16">
         <v>0.63692599999999999</v>
       </c>
-      <c r="K25" s="16">
+      <c r="L25" s="16">
         <v>0.104193063</v>
       </c>
-      <c r="L25" s="16">
+      <c r="M25" s="16">
         <v>3.3770889999999998E-2</v>
       </c>
-      <c r="M25" s="16">
-        <v>0</v>
-      </c>
       <c r="N25" s="16">
+        <v>0</v>
+      </c>
+      <c r="O25" s="16">
         <v>21.082999999999998</v>
       </c>
-      <c r="O25" s="16">
+      <c r="P25" s="16">
         <v>12.353999999999999</v>
       </c>
-      <c r="P25" s="17">
+      <c r="Q25" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q25" s="15" t="s">
+      <c r="R25" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R25" s="15">
+      <c r="S25" s="15">
         <v>0.5</v>
       </c>
-      <c r="S25" s="15" t="s">
+      <c r="T25" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T25" s="15">
+      <c r="U25" s="15">
         <v>30</v>
       </c>
-      <c r="U25" s="15" t="s">
+      <c r="V25" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V25" s="15">
+      <c r="W25" s="15">
         <v>7.0545999999999998E-2</v>
       </c>
-      <c r="W25" s="15">
+      <c r="X25" s="15">
         <v>0.48992198300000001</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="15" customFormat="1">
+    <row r="26" spans="1:25" s="15" customFormat="1">
       <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="15">
         <v>0.35</v>
       </c>
-      <c r="C26" s="16">
+      <c r="D26" s="16">
         <v>13.096</v>
       </c>
-      <c r="D26" s="16">
+      <c r="E26" s="16">
         <v>2.742</v>
       </c>
-      <c r="E26" s="16"/>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
-      <c r="H26" s="16">
+      <c r="H26" s="16"/>
+      <c r="I26" s="16">
         <v>2.742</v>
       </c>
-      <c r="I26" s="16">
+      <c r="J26" s="16">
         <v>11.84780602</v>
       </c>
-      <c r="J26" s="16">
+      <c r="K26" s="16">
         <v>0.47734259699999998</v>
       </c>
-      <c r="K26" s="16">
+      <c r="L26" s="16">
         <v>9.1823417000000004E-2</v>
       </c>
-      <c r="L26" s="16">
-        <v>0</v>
-      </c>
       <c r="M26" s="16">
         <v>0</v>
       </c>
       <c r="N26" s="16">
+        <v>0</v>
+      </c>
+      <c r="O26" s="16">
         <v>21.097999999999999</v>
       </c>
-      <c r="O26" s="16">
+      <c r="P26" s="16">
         <v>12.977</v>
       </c>
-      <c r="P26" s="17">
+      <c r="Q26" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q26" s="15" t="s">
+      <c r="R26" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="R26" s="15">
+      <c r="S26" s="15">
         <v>0.5</v>
       </c>
-      <c r="S26" s="15" t="s">
+      <c r="T26" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T26" s="15">
+      <c r="U26" s="15">
         <v>30</v>
       </c>
-      <c r="U26" s="15" t="s">
+      <c r="V26" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="V26" s="15">
+      <c r="W26" s="15">
         <v>8.8717000000000004E-2</v>
       </c>
-      <c r="W26" s="15">
+      <c r="X26" s="15">
         <v>0.50886425499999999</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="15" customFormat="1">
+    <row r="27" spans="1:25" s="15" customFormat="1">
       <c r="A27" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="15">
         <v>0.1</v>
       </c>
-      <c r="C27" s="16">
+      <c r="D27" s="16">
         <v>0.82699999999999996</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16">
+      <c r="E27" s="16"/>
+      <c r="F27" s="16">
         <v>0.747</v>
       </c>
-      <c r="F27" s="16"/>
       <c r="G27" s="16"/>
-      <c r="H27" s="16">
+      <c r="H27" s="16"/>
+      <c r="I27" s="16">
         <v>1.4930000000000001</v>
       </c>
-      <c r="I27" s="16">
-        <v>0</v>
-      </c>
       <c r="J27" s="16">
         <v>0</v>
       </c>
       <c r="K27" s="16">
+        <v>0</v>
+      </c>
+      <c r="L27" s="16">
         <v>8.7561730000000008E-3</v>
       </c>
-      <c r="L27" s="16">
-        <v>0</v>
-      </c>
       <c r="M27" s="16">
         <v>0</v>
       </c>
       <c r="N27" s="16">
+        <v>0</v>
+      </c>
+      <c r="O27" s="16">
         <v>2.7690000000000001</v>
       </c>
-      <c r="O27" s="16">
+      <c r="P27" s="16">
         <v>2.4500000000000002</v>
       </c>
-      <c r="P27" s="17">
+      <c r="Q27" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q27" s="15" t="s">
+      <c r="R27" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="R27" s="15">
+      <c r="S27" s="15">
         <v>5.53</v>
       </c>
-      <c r="S27" s="15" t="s">
+      <c r="T27" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T27" s="15">
+      <c r="U27" s="15">
         <v>5</v>
       </c>
-      <c r="U27" s="15" t="s">
+      <c r="V27" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V27" s="15">
+      <c r="W27" s="15">
         <v>7.1259000000000003E-2</v>
       </c>
-      <c r="W27" s="15">
+      <c r="X27" s="15">
         <v>0.49783414300000001</v>
       </c>
-      <c r="X27" s="15" t="s">
+      <c r="Y27" s="15" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="15" customFormat="1">
+    <row r="28" spans="1:25" s="15" customFormat="1">
       <c r="A28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="15">
         <v>0.1</v>
       </c>
-      <c r="C28" s="16">
+      <c r="D28" s="16">
         <v>0.78800000000000003</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16">
+      <c r="E28" s="16"/>
+      <c r="F28" s="16">
         <v>0.71199999999999997</v>
       </c>
-      <c r="F28" s="16"/>
       <c r="G28" s="16"/>
-      <c r="H28" s="16">
+      <c r="H28" s="16"/>
+      <c r="I28" s="16">
         <v>1.423</v>
       </c>
-      <c r="I28" s="16">
-        <v>0</v>
-      </c>
       <c r="J28" s="16">
         <v>0</v>
       </c>
       <c r="K28" s="16">
+        <v>0</v>
+      </c>
+      <c r="L28" s="16">
         <v>5.5182690000000001E-3</v>
       </c>
-      <c r="L28" s="16">
-        <v>0</v>
-      </c>
       <c r="M28" s="16">
         <v>0</v>
       </c>
       <c r="N28" s="16">
+        <v>0</v>
+      </c>
+      <c r="O28" s="16">
         <v>2.7170000000000001</v>
       </c>
-      <c r="O28" s="16">
+      <c r="P28" s="16">
         <v>2.3530000000000002</v>
       </c>
-      <c r="P28" s="17">
+      <c r="Q28" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q28" s="15" t="s">
+      <c r="R28" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="R28" s="15">
+      <c r="S28" s="15">
         <v>5.53</v>
       </c>
-      <c r="S28" s="15" t="s">
+      <c r="T28" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T28" s="15">
+      <c r="U28" s="15">
         <v>5</v>
       </c>
-      <c r="U28" s="15" t="s">
+      <c r="V28" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V28" s="15">
+      <c r="W28" s="15">
         <v>5.8789000000000001E-2</v>
       </c>
-      <c r="W28" s="15">
+      <c r="X28" s="15">
         <v>0.58385135700000002</v>
       </c>
-      <c r="X28" s="15" t="s">
+      <c r="Y28" s="15" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="15" customFormat="1">
+    <row r="29" spans="1:25" s="15" customFormat="1">
       <c r="A29" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="15">
         <v>0.1</v>
       </c>
-      <c r="C29" s="16">
+      <c r="D29" s="16">
         <v>0.76700000000000002</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16">
+      <c r="E29" s="16"/>
+      <c r="F29" s="16">
         <v>0.69099999999999995</v>
       </c>
-      <c r="F29" s="16"/>
       <c r="G29" s="16"/>
-      <c r="H29" s="16">
+      <c r="H29" s="16"/>
+      <c r="I29" s="16">
         <v>1.3819999999999999</v>
       </c>
-      <c r="I29" s="16">
-        <v>0</v>
-      </c>
       <c r="J29" s="16">
         <v>0</v>
       </c>
       <c r="K29" s="16">
+        <v>0</v>
+      </c>
+      <c r="L29" s="16">
         <v>1.9902549999999998E-3</v>
       </c>
-      <c r="L29" s="16">
-        <v>0</v>
-      </c>
       <c r="M29" s="16">
         <v>0</v>
       </c>
       <c r="N29" s="16">
+        <v>0</v>
+      </c>
+      <c r="O29" s="16">
         <v>2.5739999999999998</v>
       </c>
-      <c r="O29" s="16">
+      <c r="P29" s="16">
         <v>2.25</v>
       </c>
-      <c r="P29" s="17">
+      <c r="Q29" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q29" s="15" t="s">
+      <c r="R29" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="R29" s="15">
+      <c r="S29" s="15">
         <v>5.53</v>
       </c>
-      <c r="S29" s="15" t="s">
+      <c r="T29" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T29" s="15">
+      <c r="U29" s="15">
         <v>5</v>
       </c>
-      <c r="U29" s="15" t="s">
+      <c r="V29" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V29" s="15">
+      <c r="W29" s="15">
         <v>6.4132999999999996E-2</v>
       </c>
-      <c r="W29" s="15">
+      <c r="X29" s="15">
         <v>0.59412774999999995</v>
       </c>
-      <c r="X29" s="15" t="s">
+      <c r="Y29" s="15" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="15" customFormat="1">
+    <row r="30" spans="1:25" s="15" customFormat="1">
       <c r="A30" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="15">
         <v>0.1</v>
       </c>
-      <c r="C30" s="16">
+      <c r="D30" s="16">
         <v>0.80700000000000005</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16">
+      <c r="E30" s="16"/>
+      <c r="F30" s="16">
         <v>4.92</v>
       </c>
-      <c r="F30" s="16"/>
       <c r="G30" s="16"/>
-      <c r="H30" s="16">
+      <c r="H30" s="16"/>
+      <c r="I30" s="16">
         <v>9.8390000000000004</v>
       </c>
-      <c r="I30" s="16">
-        <v>0</v>
-      </c>
       <c r="J30" s="16">
         <v>0</v>
       </c>
       <c r="K30" s="16">
+        <v>0</v>
+      </c>
+      <c r="L30" s="16">
         <v>3.9436786000000001E-2</v>
       </c>
-      <c r="L30" s="16">
-        <v>0</v>
-      </c>
       <c r="M30" s="16">
+        <v>0</v>
+      </c>
+      <c r="N30" s="16">
         <v>1.3630471999999999E-2</v>
       </c>
-      <c r="N30" s="16">
+      <c r="O30" s="16">
         <v>3.032</v>
       </c>
-      <c r="O30" s="16">
+      <c r="P30" s="16">
         <v>1.7749999999999999</v>
       </c>
-      <c r="P30" s="17">
+      <c r="Q30" s="17">
         <v>1.21</v>
       </c>
-      <c r="Q30" s="15" t="s">
+      <c r="R30" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="R30" s="15">
+      <c r="S30" s="15">
         <v>5.53</v>
       </c>
-      <c r="S30" s="15" t="s">
+      <c r="T30" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T30" s="15">
+      <c r="U30" s="15">
         <v>3</v>
       </c>
-      <c r="U30" s="15" t="s">
+      <c r="V30" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V30" s="15">
+      <c r="W30" s="15">
         <v>5.5581999999999999E-2</v>
       </c>
-      <c r="W30" s="15">
+      <c r="X30" s="15">
         <v>0.510013571</v>
       </c>
-      <c r="X30" s="15" t="s">
+      <c r="Y30" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="15" customFormat="1">
+    <row r="31" spans="1:25" s="15" customFormat="1">
       <c r="A31" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="15">
         <v>0.1</v>
       </c>
-      <c r="C31" s="16">
+      <c r="D31" s="16">
         <v>0.64900000000000002</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16">
+      <c r="E31" s="16"/>
+      <c r="F31" s="16">
         <v>3.9620000000000002</v>
       </c>
-      <c r="F31" s="16"/>
       <c r="G31" s="16"/>
-      <c r="H31" s="16">
+      <c r="H31" s="16"/>
+      <c r="I31" s="16">
         <v>7.9240000000000004</v>
       </c>
-      <c r="I31" s="16">
-        <v>0</v>
-      </c>
       <c r="J31" s="16">
         <v>0</v>
       </c>
       <c r="K31" s="16">
+        <v>0</v>
+      </c>
+      <c r="L31" s="16">
         <v>3.0460814999999999E-2</v>
       </c>
-      <c r="L31" s="16">
-        <v>0</v>
-      </c>
       <c r="M31" s="16">
+        <v>0</v>
+      </c>
+      <c r="N31" s="16">
         <v>9.5061450000000006E-3</v>
       </c>
-      <c r="N31" s="16">
+      <c r="O31" s="16">
         <v>1.9590000000000001</v>
       </c>
-      <c r="O31" s="16">
+      <c r="P31" s="16">
         <v>1.623</v>
       </c>
-      <c r="P31" s="17">
+      <c r="Q31" s="17">
         <v>1.21</v>
       </c>
-      <c r="Q31" s="15" t="s">
+      <c r="R31" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="R31" s="15">
+      <c r="S31" s="15">
         <v>5.53</v>
       </c>
-      <c r="S31" s="15" t="s">
+      <c r="T31" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T31" s="15">
+      <c r="U31" s="15">
         <v>3</v>
       </c>
-      <c r="U31" s="15" t="s">
+      <c r="V31" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V31" s="15">
+      <c r="W31" s="15">
         <v>5.4869000000000001E-2</v>
       </c>
-      <c r="W31" s="15">
+      <c r="X31" s="15">
         <v>0.29420932100000002</v>
       </c>
-      <c r="X31" s="15" t="s">
+      <c r="Y31" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="15" customFormat="1">
+    <row r="32" spans="1:25" s="15" customFormat="1">
       <c r="A32" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="15">
         <v>0.1</v>
       </c>
-      <c r="C32" s="16">
+      <c r="D32" s="16">
         <v>0.76500000000000001</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16">
+      <c r="E32" s="16"/>
+      <c r="F32" s="16">
         <v>4.6159999999999997</v>
       </c>
-      <c r="F32" s="16"/>
       <c r="G32" s="16"/>
-      <c r="H32" s="16">
+      <c r="H32" s="16"/>
+      <c r="I32" s="16">
         <v>9.2319999999999993</v>
       </c>
-      <c r="I32" s="16">
-        <v>0</v>
-      </c>
       <c r="J32" s="16">
         <v>0</v>
       </c>
       <c r="K32" s="16">
+        <v>0</v>
+      </c>
+      <c r="L32" s="16">
         <v>2.5119712999999998E-2</v>
       </c>
-      <c r="L32" s="16">
-        <v>0</v>
-      </c>
       <c r="M32" s="16">
         <v>0</v>
       </c>
       <c r="N32" s="16">
+        <v>0</v>
+      </c>
+      <c r="O32" s="16">
         <v>2.569</v>
       </c>
-      <c r="O32" s="16">
+      <c r="P32" s="16">
         <v>1.2909999999999999</v>
       </c>
-      <c r="P32" s="17">
+      <c r="Q32" s="17">
         <v>1.21</v>
       </c>
-      <c r="Q32" s="15" t="s">
+      <c r="R32" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="R32" s="15">
+      <c r="S32" s="15">
         <v>5.53</v>
       </c>
-      <c r="S32" s="15" t="s">
+      <c r="T32" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T32" s="15">
+      <c r="U32" s="15">
         <v>3</v>
       </c>
-      <c r="U32" s="15" t="s">
+      <c r="V32" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V32" s="15">
+      <c r="W32" s="15">
         <v>5.1663000000000001E-2</v>
       </c>
-      <c r="W32" s="15">
+      <c r="X32" s="15">
         <v>0.358912536</v>
       </c>
-      <c r="X32" s="15" t="s">
+      <c r="Y32" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:23" s="15" customFormat="1">
+    <row r="33" spans="1:24" s="15" customFormat="1">
       <c r="A33" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="15">
         <v>0.1</v>
       </c>
-      <c r="C33" s="16">
+      <c r="D33" s="16">
         <v>1.381</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16">
+      <c r="E33" s="16"/>
+      <c r="F33" s="16">
         <v>0.158</v>
       </c>
-      <c r="F33" s="16"/>
       <c r="G33" s="16"/>
-      <c r="H33" s="16">
+      <c r="H33" s="16"/>
+      <c r="I33" s="16">
         <v>0.317</v>
       </c>
-      <c r="I33" s="16">
+      <c r="J33" s="16">
         <v>1.8073279000000001E-2</v>
       </c>
-      <c r="J33" s="16">
+      <c r="K33" s="16">
         <v>7.8381013999999999E-2</v>
       </c>
-      <c r="K33" s="16">
+      <c r="L33" s="16">
         <v>0.86713414300000002</v>
       </c>
-      <c r="L33" s="16">
+      <c r="M33" s="16">
         <v>5.4564440000000004E-3</v>
       </c>
-      <c r="M33" s="16">
+      <c r="N33" s="16">
         <v>4.6616212999999997E-2</v>
       </c>
-      <c r="N33" s="16">
+      <c r="O33" s="16">
         <v>4.3209999999999997</v>
       </c>
-      <c r="O33" s="16">
+      <c r="P33" s="16">
         <v>3.883</v>
       </c>
-      <c r="P33" s="17">
+      <c r="Q33" s="17">
         <v>6.87</v>
       </c>
-      <c r="Q33" s="15" t="s">
+      <c r="R33" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="R33" s="15">
+      <c r="S33" s="15">
         <v>0.55000000000000004</v>
       </c>
-      <c r="S33" s="15" t="s">
+      <c r="T33" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T33" s="15">
+      <c r="U33" s="15">
         <v>30</v>
       </c>
-      <c r="U33" s="15" t="s">
+      <c r="V33" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V33" s="15">
+      <c r="W33" s="15">
         <v>2.6366000000000001E-2</v>
       </c>
-      <c r="W33" s="15">
+      <c r="X33" s="15">
         <v>0.20552785700000001</v>
       </c>
     </row>
-    <row r="34" spans="1:23" s="15" customFormat="1">
+    <row r="34" spans="1:24" s="15" customFormat="1">
       <c r="A34" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="15">
         <v>0.1</v>
       </c>
-      <c r="C34" s="16">
+      <c r="D34" s="16">
         <v>1.2589999999999999</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16">
+      <c r="E34" s="16"/>
+      <c r="F34" s="16">
         <v>0.14199999999999999</v>
       </c>
-      <c r="F34" s="16"/>
       <c r="G34" s="16"/>
-      <c r="H34" s="16">
+      <c r="H34" s="16"/>
+      <c r="I34" s="16">
         <v>0.28399999999999997</v>
       </c>
-      <c r="I34" s="16">
-        <v>0</v>
-      </c>
       <c r="J34" s="16">
+        <v>0</v>
+      </c>
+      <c r="K34" s="16">
         <v>3.4333113999999998E-2</v>
       </c>
-      <c r="K34" s="16">
+      <c r="L34" s="16">
         <v>0.69158415699999998</v>
       </c>
-      <c r="L34" s="16">
-        <v>0</v>
-      </c>
       <c r="M34" s="16">
+        <v>0</v>
+      </c>
+      <c r="N34" s="16">
         <v>4.5041784000000001E-2</v>
       </c>
-      <c r="N34" s="16">
+      <c r="O34" s="16">
         <v>3.93</v>
       </c>
-      <c r="O34" s="16">
+      <c r="P34" s="16">
         <v>3.3959999999999999</v>
       </c>
-      <c r="P34" s="17">
+      <c r="Q34" s="17">
         <v>6.87</v>
       </c>
-      <c r="Q34" s="15" t="s">
+      <c r="R34" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="R34" s="15">
+      <c r="S34" s="15">
         <v>0.55000000000000004</v>
       </c>
-      <c r="S34" s="15" t="s">
+      <c r="T34" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T34" s="15">
+      <c r="U34" s="15">
         <v>30</v>
       </c>
-      <c r="U34" s="15" t="s">
+      <c r="V34" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V34" s="15">
+      <c r="W34" s="15">
         <v>2.2268E-2</v>
       </c>
-      <c r="W34" s="15">
+      <c r="X34" s="15">
         <v>0.35282282100000001</v>
       </c>
     </row>
-    <row r="35" spans="1:23" s="15" customFormat="1">
+    <row r="35" spans="1:24" s="15" customFormat="1">
       <c r="A35" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="15">
         <v>0.1</v>
       </c>
-      <c r="C35" s="16">
+      <c r="D35" s="16">
         <v>1.3</v>
       </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16">
+      <c r="E35" s="16"/>
+      <c r="F35" s="16">
         <v>0.14899999999999999</v>
       </c>
-      <c r="F35" s="16"/>
       <c r="G35" s="16"/>
-      <c r="H35" s="16">
+      <c r="H35" s="16"/>
+      <c r="I35" s="16">
         <v>0.29799999999999999</v>
       </c>
-      <c r="I35" s="16">
-        <v>0</v>
-      </c>
       <c r="J35" s="16">
+        <v>0</v>
+      </c>
+      <c r="K35" s="16">
         <v>7.6426068999999999E-2</v>
       </c>
-      <c r="K35" s="16">
+      <c r="L35" s="16">
         <v>0.84262339500000005</v>
       </c>
-      <c r="L35" s="16">
+      <c r="M35" s="16">
         <v>5.663179E-3</v>
       </c>
-      <c r="M35" s="16">
+      <c r="N35" s="16">
         <v>4.1991897E-2</v>
       </c>
-      <c r="N35" s="16">
+      <c r="O35" s="16">
         <v>4.077</v>
       </c>
-      <c r="O35" s="16">
+      <c r="P35" s="16">
         <v>3.3340000000000001</v>
       </c>
-      <c r="P35" s="17">
+      <c r="Q35" s="17">
         <v>6.87</v>
       </c>
-      <c r="Q35" s="15" t="s">
+      <c r="R35" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="R35" s="15">
+      <c r="S35" s="15">
         <v>0.55000000000000004</v>
       </c>
-      <c r="S35" s="15" t="s">
+      <c r="T35" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T35" s="15">
+      <c r="U35" s="15">
         <v>30</v>
       </c>
-      <c r="U35" s="15" t="s">
+      <c r="V35" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V35" s="15">
+      <c r="W35" s="15">
         <v>1.7815000000000001E-2</v>
       </c>
-      <c r="W35" s="15">
+      <c r="X35" s="15">
         <v>0.36195739300000002</v>
       </c>
     </row>
-    <row r="36" spans="1:23" s="15" customFormat="1">
+    <row r="36" spans="1:24" s="15" customFormat="1">
       <c r="A36" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" s="15">
         <v>0.1</v>
       </c>
-      <c r="C36" s="16">
+      <c r="D36" s="16">
         <v>1.4850000000000001</v>
       </c>
-      <c r="D36" s="16"/>
       <c r="E36" s="16"/>
-      <c r="F36" s="16">
+      <c r="F36" s="16"/>
+      <c r="G36" s="16">
         <v>2.8620000000000001</v>
       </c>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16">
+      <c r="H36" s="16"/>
+      <c r="I36" s="16">
         <v>2.8620000000000001</v>
       </c>
-      <c r="I36" s="16">
-        <v>0</v>
-      </c>
       <c r="J36" s="16">
         <v>0</v>
       </c>
       <c r="K36" s="16">
+        <v>0</v>
+      </c>
+      <c r="L36" s="16">
         <v>6.3162172000000003E-2</v>
       </c>
-      <c r="L36" s="16">
-        <v>0</v>
-      </c>
       <c r="M36" s="16">
         <v>0</v>
       </c>
       <c r="N36" s="16">
+        <v>0</v>
+      </c>
+      <c r="O36" s="16">
         <v>5.7110000000000003</v>
       </c>
-      <c r="O36" s="16">
+      <c r="P36" s="16">
         <v>5.6040000000000001</v>
       </c>
-      <c r="P36" s="17">
+      <c r="Q36" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q36" s="15" t="s">
+      <c r="R36" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="R36" s="15">
+      <c r="S36" s="15">
         <v>12.35</v>
       </c>
-      <c r="S36" s="15" t="s">
+      <c r="T36" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T36" s="15">
+      <c r="U36" s="15">
         <v>3</v>
       </c>
-      <c r="U36" s="15" t="s">
+      <c r="V36" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V36" s="15">
+      <c r="W36" s="15">
         <v>1.9595999999999999E-2</v>
       </c>
-      <c r="W36" s="15">
+      <c r="X36" s="15">
         <v>0.425138179</v>
       </c>
     </row>
-    <row r="37" spans="1:23" s="15" customFormat="1">
+    <row r="37" spans="1:24" s="15" customFormat="1">
       <c r="A37" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="15">
         <v>0.1</v>
       </c>
-      <c r="C37" s="16">
+      <c r="D37" s="16">
         <v>1.6</v>
       </c>
-      <c r="D37" s="16"/>
       <c r="E37" s="16"/>
-      <c r="F37" s="16">
+      <c r="F37" s="16"/>
+      <c r="G37" s="16">
         <v>3.0840000000000001</v>
       </c>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16">
+      <c r="H37" s="16"/>
+      <c r="I37" s="16">
         <v>3.0840000000000001</v>
       </c>
-      <c r="I37" s="16">
-        <v>0</v>
-      </c>
       <c r="J37" s="16">
         <v>0</v>
       </c>
       <c r="K37" s="16">
+        <v>0</v>
+      </c>
+      <c r="L37" s="16">
         <v>7.4209667000000007E-2</v>
       </c>
-      <c r="L37" s="16">
-        <v>0</v>
-      </c>
       <c r="M37" s="16">
         <v>0</v>
       </c>
       <c r="N37" s="16">
+        <v>0</v>
+      </c>
+      <c r="O37" s="16">
         <v>6.0389999999999997</v>
       </c>
-      <c r="O37" s="16">
+      <c r="P37" s="16">
         <v>5.8689999999999998</v>
       </c>
-      <c r="P37" s="17">
+      <c r="Q37" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q37" s="15" t="s">
+      <c r="R37" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="R37" s="15">
+      <c r="S37" s="15">
         <v>12.35</v>
       </c>
-      <c r="S37" s="15" t="s">
+      <c r="T37" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T37" s="15">
+      <c r="U37" s="15">
         <v>3</v>
       </c>
-      <c r="U37" s="15" t="s">
+      <c r="V37" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V37" s="15">
+      <c r="W37" s="15">
         <v>2.0309000000000001E-2</v>
       </c>
-      <c r="W37" s="15">
+      <c r="X37" s="15">
         <v>0.52028996400000005</v>
       </c>
     </row>
-    <row r="38" spans="1:23" s="15" customFormat="1">
+    <row r="38" spans="1:24" s="15" customFormat="1">
       <c r="A38" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" s="15">
         <v>0.1</v>
       </c>
-      <c r="C38" s="16">
+      <c r="D38" s="16">
         <v>1.4350000000000001</v>
       </c>
-      <c r="D38" s="16"/>
       <c r="E38" s="16"/>
-      <c r="F38" s="16">
+      <c r="F38" s="16"/>
+      <c r="G38" s="16">
         <v>2.7629999999999999</v>
       </c>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16">
+      <c r="H38" s="16"/>
+      <c r="I38" s="16">
         <v>2.7629999999999999</v>
       </c>
-      <c r="I38" s="16">
-        <v>0</v>
-      </c>
       <c r="J38" s="16">
         <v>0</v>
       </c>
       <c r="K38" s="16">
+        <v>0</v>
+      </c>
+      <c r="L38" s="16">
         <v>7.4921513999999995E-2</v>
       </c>
-      <c r="L38" s="16">
-        <v>0</v>
-      </c>
       <c r="M38" s="16">
         <v>0</v>
       </c>
       <c r="N38" s="16">
+        <v>0</v>
+      </c>
+      <c r="O38" s="16">
         <v>5.32</v>
       </c>
-      <c r="O38" s="16">
+      <c r="P38" s="16">
         <v>5.0789999999999997</v>
       </c>
-      <c r="P38" s="17">
+      <c r="Q38" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q38" s="15" t="s">
+      <c r="R38" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="R38" s="15">
+      <c r="S38" s="15">
         <v>12.35</v>
       </c>
-      <c r="S38" s="15" t="s">
+      <c r="T38" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T38" s="15">
+      <c r="U38" s="15">
         <v>3</v>
       </c>
-      <c r="U38" s="15" t="s">
+      <c r="V38" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V38" s="15">
+      <c r="W38" s="15">
         <v>1.8171E-2</v>
       </c>
-      <c r="W38" s="15">
+      <c r="X38" s="15">
         <v>0.452161286</v>
       </c>
     </row>
-    <row r="39" spans="1:23" s="15" customFormat="1">
+    <row r="39" spans="1:24" s="15" customFormat="1">
       <c r="A39" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="15">
         <v>0.1</v>
       </c>
-      <c r="C39" s="16">
+      <c r="D39" s="16">
         <v>1.6779999999999999</v>
       </c>
-      <c r="D39" s="16"/>
       <c r="E39" s="16"/>
-      <c r="F39" s="16">
+      <c r="F39" s="16"/>
+      <c r="G39" s="16">
         <v>0.33400000000000002</v>
       </c>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16">
+      <c r="H39" s="16"/>
+      <c r="I39" s="16">
         <v>0.33400000000000002</v>
       </c>
-      <c r="I39" s="16">
-        <v>0</v>
-      </c>
       <c r="J39" s="16">
         <v>0</v>
       </c>
       <c r="K39" s="16">
+        <v>0</v>
+      </c>
+      <c r="L39" s="16">
         <v>0.27117874199999997</v>
       </c>
-      <c r="L39" s="16">
-        <v>0</v>
-      </c>
       <c r="M39" s="16">
         <v>0</v>
       </c>
       <c r="N39" s="16">
+        <v>0</v>
+      </c>
+      <c r="O39" s="16">
         <v>5.7240000000000002</v>
       </c>
-      <c r="O39" s="16">
+      <c r="P39" s="16">
         <v>5.9080000000000004</v>
       </c>
-      <c r="P39" s="17">
+      <c r="Q39" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q39" s="15" t="s">
+      <c r="R39" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="R39" s="15">
+      <c r="S39" s="15">
         <v>1.24</v>
       </c>
-      <c r="S39" s="15" t="s">
+      <c r="T39" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T39" s="15">
+      <c r="U39" s="15">
         <v>30</v>
       </c>
-      <c r="U39" s="15" t="s">
+      <c r="V39" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V39" s="15">
+      <c r="W39" s="15">
         <v>2.3337E-2</v>
       </c>
-      <c r="W39" s="15">
+      <c r="X39" s="15">
         <v>0.41790664300000002</v>
       </c>
     </row>
-    <row r="40" spans="1:23" s="15" customFormat="1">
+    <row r="40" spans="1:24" s="15" customFormat="1">
       <c r="A40" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="15">
         <v>0.1</v>
       </c>
-      <c r="C40" s="16">
+      <c r="D40" s="16">
         <v>1.6930000000000001</v>
       </c>
-      <c r="D40" s="16"/>
       <c r="E40" s="16"/>
-      <c r="F40" s="16">
+      <c r="F40" s="16"/>
+      <c r="G40" s="16">
         <v>0.33700000000000002</v>
       </c>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16">
+      <c r="H40" s="16"/>
+      <c r="I40" s="16">
         <v>0.33700000000000002</v>
       </c>
-      <c r="I40" s="16">
-        <v>0</v>
-      </c>
       <c r="J40" s="16">
         <v>0</v>
       </c>
       <c r="K40" s="16">
+        <v>0</v>
+      </c>
+      <c r="L40" s="16">
         <v>0.30716928599999999</v>
       </c>
-      <c r="L40" s="16">
-        <v>0</v>
-      </c>
       <c r="M40" s="16">
         <v>0</v>
       </c>
       <c r="N40" s="16">
+        <v>0</v>
+      </c>
+      <c r="O40" s="16">
         <v>5.9720000000000004</v>
       </c>
-      <c r="O40" s="16">
+      <c r="P40" s="16">
         <v>5.29</v>
       </c>
-      <c r="P40" s="17">
+      <c r="Q40" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q40" s="15" t="s">
+      <c r="R40" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="R40" s="15">
+      <c r="S40" s="15">
         <v>1.24</v>
       </c>
-      <c r="S40" s="15" t="s">
+      <c r="T40" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T40" s="15">
+      <c r="U40" s="15">
         <v>30</v>
       </c>
-      <c r="U40" s="15" t="s">
+      <c r="V40" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V40" s="15">
+      <c r="W40" s="15">
         <v>2.4941000000000001E-2</v>
       </c>
-      <c r="W40" s="15">
+      <c r="X40" s="15">
         <v>0.37870410700000001</v>
       </c>
     </row>
-    <row r="41" spans="1:23" s="15" customFormat="1">
+    <row r="41" spans="1:24" s="15" customFormat="1">
       <c r="A41" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" s="15">
         <v>0.1</v>
       </c>
-      <c r="C41" s="16">
+      <c r="D41" s="16">
         <v>1.647</v>
       </c>
-      <c r="D41" s="16"/>
       <c r="E41" s="16"/>
-      <c r="F41" s="16">
+      <c r="F41" s="16"/>
+      <c r="G41" s="16">
         <v>0.32700000000000001</v>
       </c>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16">
+      <c r="H41" s="16"/>
+      <c r="I41" s="16">
         <v>0.32700000000000001</v>
       </c>
-      <c r="I41" s="16">
-        <v>0</v>
-      </c>
       <c r="J41" s="16">
         <v>0</v>
       </c>
       <c r="K41" s="16">
+        <v>0</v>
+      </c>
+      <c r="L41" s="16">
         <v>0.20397084300000001</v>
       </c>
-      <c r="L41" s="16">
-        <v>0</v>
-      </c>
       <c r="M41" s="16">
         <v>0</v>
       </c>
       <c r="N41" s="16">
+        <v>0</v>
+      </c>
+      <c r="O41" s="16">
         <v>6.1310000000000002</v>
       </c>
-      <c r="O41" s="16">
+      <c r="P41" s="16">
         <v>5.69</v>
       </c>
-      <c r="P41" s="17">
+      <c r="Q41" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q41" s="15" t="s">
+      <c r="R41" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="R41" s="15">
+      <c r="S41" s="15">
         <v>1.24</v>
       </c>
-      <c r="S41" s="15" t="s">
+      <c r="T41" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T41" s="15">
+      <c r="U41" s="15">
         <v>30</v>
       </c>
-      <c r="U41" s="15" t="s">
+      <c r="V41" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V41" s="15">
+      <c r="W41" s="15">
         <v>2.4406000000000001E-2</v>
       </c>
-      <c r="W41" s="15">
+      <c r="X41" s="15">
         <v>0.39887628600000002</v>
       </c>
     </row>
-    <row r="42" spans="1:23" s="15" customFormat="1">
+    <row r="42" spans="1:24" s="15" customFormat="1">
       <c r="A42" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" s="15">
         <v>0.1</v>
       </c>
-      <c r="C42" s="16">
+      <c r="D42" s="16">
         <v>1.4790000000000001</v>
       </c>
-      <c r="D42" s="16"/>
       <c r="E42" s="16"/>
       <c r="F42" s="16"/>
-      <c r="G42" s="16">
-        <v>2.919</v>
-      </c>
+      <c r="G42" s="16"/>
       <c r="H42" s="16">
         <v>2.919</v>
       </c>
       <c r="I42" s="16">
+        <v>2.919</v>
+      </c>
+      <c r="J42" s="16">
         <v>6.4434642E-2</v>
       </c>
-      <c r="J42" s="16">
-        <v>0</v>
-      </c>
       <c r="K42" s="16">
+        <v>0</v>
+      </c>
+      <c r="L42" s="16">
         <v>0.16559933199999999</v>
       </c>
-      <c r="L42" s="16">
-        <v>0</v>
-      </c>
       <c r="M42" s="16">
+        <v>0</v>
+      </c>
+      <c r="N42" s="16">
         <v>4.8736990000000004E-3</v>
       </c>
-      <c r="N42" s="16">
+      <c r="O42" s="16">
         <v>4.7869999999999999</v>
       </c>
-      <c r="O42" s="16">
+      <c r="P42" s="16">
         <v>4.5609999999999999</v>
       </c>
-      <c r="P42" s="17">
+      <c r="Q42" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q42" s="15" t="s">
+      <c r="R42" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="R42" s="15">
+      <c r="S42" s="15">
         <v>9.81</v>
       </c>
-      <c r="S42" s="15" t="s">
+      <c r="T42" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T42" s="15">
+      <c r="U42" s="15">
         <v>3</v>
       </c>
-      <c r="U42" s="15" t="s">
+      <c r="V42" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V42" s="15">
+      <c r="W42" s="15">
         <v>2.9215999999999999E-2</v>
       </c>
-      <c r="W42" s="15">
+      <c r="X42" s="15">
         <v>0.32085182099999998</v>
       </c>
     </row>
-    <row r="43" spans="1:23" s="15" customFormat="1">
+    <row r="43" spans="1:24" s="15" customFormat="1">
       <c r="A43" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="15">
         <v>0.1</v>
       </c>
-      <c r="C43" s="16">
+      <c r="D43" s="16">
         <v>1.633</v>
       </c>
-      <c r="D43" s="16"/>
       <c r="E43" s="16"/>
       <c r="F43" s="16"/>
-      <c r="G43" s="16">
-        <v>3.2</v>
-      </c>
+      <c r="G43" s="16"/>
       <c r="H43" s="16">
         <v>3.2</v>
       </c>
       <c r="I43" s="16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J43" s="16">
         <v>0</v>
       </c>
       <c r="K43" s="16">
+        <v>0</v>
+      </c>
+      <c r="L43" s="16">
         <v>0.156217087</v>
       </c>
-      <c r="L43" s="16">
-        <v>0</v>
-      </c>
       <c r="M43" s="16">
         <v>0</v>
       </c>
       <c r="N43" s="16">
+        <v>0</v>
+      </c>
+      <c r="O43" s="16">
         <v>5.1379999999999999</v>
       </c>
-      <c r="O43" s="16">
+      <c r="P43" s="16">
         <v>4.9089999999999998</v>
       </c>
-      <c r="P43" s="17">
+      <c r="Q43" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q43" s="15" t="s">
+      <c r="R43" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="R43" s="15">
+      <c r="S43" s="15">
         <v>9.81</v>
       </c>
-      <c r="S43" s="15" t="s">
+      <c r="T43" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T43" s="15">
+      <c r="U43" s="15">
         <v>3</v>
       </c>
-      <c r="U43" s="15" t="s">
+      <c r="V43" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V43" s="15">
+      <c r="W43" s="15">
         <v>3.4738999999999999E-2</v>
       </c>
-      <c r="W43" s="15">
+      <c r="X43" s="15">
         <v>0.41866785699999998</v>
       </c>
     </row>
-    <row r="44" spans="1:23" s="15" customFormat="1">
+    <row r="44" spans="1:24" s="15" customFormat="1">
       <c r="A44" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="15">
         <v>0.1</v>
       </c>
-      <c r="C44" s="16">
+      <c r="D44" s="16">
         <v>1.571</v>
       </c>
-      <c r="D44" s="16"/>
       <c r="E44" s="16"/>
       <c r="F44" s="16"/>
-      <c r="G44" s="16">
-        <v>3.0830000000000002</v>
-      </c>
+      <c r="G44" s="16"/>
       <c r="H44" s="16">
         <v>3.0830000000000002</v>
       </c>
       <c r="I44" s="16">
+        <v>3.0830000000000002</v>
+      </c>
+      <c r="J44" s="16">
         <v>6.4504826000000001E-2</v>
       </c>
-      <c r="J44" s="16">
-        <v>0</v>
-      </c>
       <c r="K44" s="16">
+        <v>0</v>
+      </c>
+      <c r="L44" s="16">
         <v>0.15037355499999999</v>
       </c>
-      <c r="L44" s="16">
-        <v>0</v>
-      </c>
       <c r="M44" s="16">
+        <v>0</v>
+      </c>
+      <c r="N44" s="16">
         <v>5.596462E-3</v>
       </c>
-      <c r="N44" s="16">
+      <c r="O44" s="16">
         <v>4.9610000000000003</v>
       </c>
-      <c r="O44" s="16">
+      <c r="P44" s="16">
         <v>4.5490000000000004</v>
       </c>
-      <c r="P44" s="17">
+      <c r="Q44" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q44" s="15" t="s">
+      <c r="R44" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="R44" s="15">
+      <c r="S44" s="15">
         <v>9.81</v>
       </c>
-      <c r="S44" s="15" t="s">
+      <c r="T44" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="T44" s="15">
+      <c r="U44" s="15">
         <v>3</v>
       </c>
-      <c r="U44" s="15" t="s">
+      <c r="V44" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V44" s="15">
+      <c r="W44" s="15">
         <v>3.0641000000000002E-2</v>
       </c>
-      <c r="W44" s="15">
+      <c r="X44" s="15">
         <v>0.33150882100000001</v>
       </c>
     </row>
-    <row r="45" spans="1:23" s="15" customFormat="1">
+    <row r="45" spans="1:24" s="15" customFormat="1">
       <c r="A45" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="15">
         <v>0.1</v>
       </c>
-      <c r="C45" s="16">
+      <c r="D45" s="16">
         <v>1.4510000000000001</v>
       </c>
-      <c r="D45" s="16"/>
       <c r="E45" s="16"/>
       <c r="F45" s="16"/>
-      <c r="G45" s="16">
-        <v>0.29199999999999998</v>
-      </c>
+      <c r="G45" s="16"/>
       <c r="H45" s="16">
         <v>0.29199999999999998</v>
       </c>
       <c r="I45" s="16">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="J45" s="16">
         <v>0.16597783599999999</v>
       </c>
-      <c r="J45" s="16">
+      <c r="K45" s="16">
         <v>6.6479359000000002E-2</v>
       </c>
-      <c r="K45" s="16">
+      <c r="L45" s="16">
         <v>0.60819290000000004</v>
       </c>
-      <c r="L45" s="16">
-        <v>0</v>
-      </c>
       <c r="M45" s="16">
+        <v>0</v>
+      </c>
+      <c r="N45" s="16">
         <v>2.5725250000000002E-2</v>
       </c>
-      <c r="N45" s="16">
+      <c r="O45" s="16">
         <v>4.18</v>
       </c>
-      <c r="O45" s="16">
+      <c r="P45" s="16">
         <v>4.0129999999999999</v>
       </c>
-      <c r="P45" s="17">
+      <c r="Q45" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q45" s="15" t="s">
+      <c r="R45" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="R45" s="15">
+      <c r="S45" s="15">
         <v>0.98</v>
       </c>
-      <c r="S45" s="15" t="s">
+      <c r="T45" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T45" s="15">
+      <c r="U45" s="15">
         <v>30</v>
       </c>
-      <c r="U45" s="15" t="s">
+      <c r="V45" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V45" s="15">
+      <c r="W45" s="15">
         <v>2.4761999999999999E-2</v>
       </c>
-      <c r="W45" s="15">
+      <c r="X45" s="15">
         <v>0.43998185699999998</v>
       </c>
     </row>
-    <row r="46" spans="1:23" s="15" customFormat="1">
+    <row r="46" spans="1:24" s="15" customFormat="1">
       <c r="A46" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="15">
         <v>0.1</v>
       </c>
-      <c r="C46" s="16">
+      <c r="D46" s="16">
         <v>1.7090000000000001</v>
       </c>
-      <c r="D46" s="16"/>
       <c r="E46" s="16"/>
       <c r="F46" s="16"/>
-      <c r="G46" s="16">
-        <v>0.33900000000000002</v>
-      </c>
+      <c r="G46" s="16"/>
       <c r="H46" s="16">
         <v>0.33900000000000002</v>
       </c>
       <c r="I46" s="16">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="J46" s="16">
         <v>6.0174350000000001E-2</v>
       </c>
-      <c r="J46" s="16">
+      <c r="K46" s="16">
         <v>7.8079274000000004E-2</v>
       </c>
-      <c r="K46" s="16">
+      <c r="L46" s="16">
         <v>0.66867871400000001</v>
       </c>
-      <c r="L46" s="16">
-        <v>0</v>
-      </c>
       <c r="M46" s="16">
+        <v>0</v>
+      </c>
+      <c r="N46" s="16">
         <v>3.5868012999999997E-2</v>
       </c>
-      <c r="N46" s="16">
+      <c r="O46" s="16">
         <v>4.9020000000000001</v>
       </c>
-      <c r="O46" s="16">
+      <c r="P46" s="16">
         <v>4.45</v>
       </c>
-      <c r="P46" s="17">
+      <c r="Q46" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q46" s="15" t="s">
+      <c r="R46" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="R46" s="15">
+      <c r="S46" s="15">
         <v>0.98</v>
       </c>
-      <c r="S46" s="15" t="s">
+      <c r="T46" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T46" s="15">
+      <c r="U46" s="15">
         <v>30</v>
       </c>
-      <c r="U46" s="15" t="s">
+      <c r="V46" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V46" s="15">
+      <c r="W46" s="15">
         <v>2.1912000000000001E-2</v>
       </c>
-      <c r="W46" s="15">
+      <c r="X46" s="15">
         <v>0.448355214</v>
       </c>
     </row>
-    <row r="47" spans="1:23" s="15" customFormat="1">
+    <row r="47" spans="1:24" s="15" customFormat="1">
       <c r="A47" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" s="15">
         <v>0.1</v>
       </c>
-      <c r="C47" s="16">
+      <c r="D47" s="16">
         <v>1.6220000000000001</v>
       </c>
-      <c r="D47" s="16"/>
       <c r="E47" s="16"/>
       <c r="F47" s="16"/>
-      <c r="G47" s="16">
-        <v>0.32900000000000001</v>
-      </c>
+      <c r="G47" s="16"/>
       <c r="H47" s="16">
         <v>0.32900000000000001</v>
       </c>
       <c r="I47" s="16">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="J47" s="16">
         <v>0.18362290100000001</v>
       </c>
-      <c r="J47" s="16">
+      <c r="K47" s="16">
         <v>0.16825845</v>
       </c>
-      <c r="K47" s="16">
+      <c r="L47" s="16">
         <v>0.92271634599999997</v>
       </c>
-      <c r="L47" s="16">
-        <v>0</v>
-      </c>
       <c r="M47" s="16">
+        <v>0</v>
+      </c>
+      <c r="N47" s="16">
         <v>4.8272586999999999E-2</v>
       </c>
-      <c r="N47" s="16">
+      <c r="O47" s="16">
         <v>4.5620000000000003</v>
       </c>
-      <c r="O47" s="16">
+      <c r="P47" s="16">
         <v>4.2300000000000004</v>
       </c>
-      <c r="P47" s="17">
+      <c r="Q47" s="17">
         <v>7.5</v>
       </c>
-      <c r="Q47" s="15" t="s">
+      <c r="R47" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="R47" s="15">
+      <c r="S47" s="15">
         <v>0.98</v>
       </c>
-      <c r="S47" s="15" t="s">
+      <c r="T47" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="T47" s="15">
+      <c r="U47" s="15">
         <v>30</v>
       </c>
-      <c r="U47" s="15" t="s">
+      <c r="V47" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="V47" s="15">
+      <c r="W47" s="15">
         <v>2.4761999999999999E-2</v>
       </c>
-      <c r="W47" s="15">
+      <c r="X47" s="15">
         <v>0.42361575000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:23" s="26" customFormat="1">
+    <row r="48" spans="1:24" s="26" customFormat="1">
       <c r="A48" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B48" s="25">
+      <c r="B48" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" s="25">
         <v>0.1</v>
       </c>
-      <c r="P48" s="27"/>
-    </row>
-    <row r="49" spans="1:16" s="7" customFormat="1">
+      <c r="Q48" s="27"/>
+    </row>
+    <row r="49" spans="1:17" s="7" customFormat="1">
       <c r="A49" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="5">
         <v>0.40653850000000002</v>
       </c>
-      <c r="C49" s="6">
+      <c r="D49" s="6">
         <v>-13.20185</v>
       </c>
-      <c r="I49" s="6">
+      <c r="J49" s="6">
         <v>15.979100000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:16" s="7" customFormat="1">
+    <row r="50" spans="1:17" s="7" customFormat="1">
       <c r="A50" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" s="5">
         <v>0.44837779999999999</v>
       </c>
-      <c r="C50" s="6">
+      <c r="D50" s="6">
         <v>-12.97245</v>
       </c>
-      <c r="I50" s="6">
+      <c r="J50" s="6">
         <v>17.642130000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:16" s="7" customFormat="1">
+    <row r="51" spans="1:17" s="7" customFormat="1">
       <c r="A51" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="5">
         <v>0.32723469999999999</v>
       </c>
-      <c r="C51" s="6">
+      <c r="D51" s="6">
         <v>-18.39499</v>
       </c>
-      <c r="I51" s="6">
+      <c r="J51" s="6">
         <v>27.157050000000002</v>
       </c>
-      <c r="M51" s="5">
+      <c r="N51" s="5">
         <v>3.6701839999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:16" s="7" customFormat="1">
+    <row r="52" spans="1:17" s="7" customFormat="1">
       <c r="A52" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="5">
         <v>0.32866410000000001</v>
       </c>
-      <c r="C52" s="6">
+      <c r="D52" s="6">
         <v>-14.408200000000001</v>
       </c>
-      <c r="I52" s="6">
+      <c r="J52" s="6">
         <v>22.896090000000001</v>
       </c>
-      <c r="M52" s="5">
+      <c r="N52" s="5">
         <v>1.9558949999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:16" s="12" customFormat="1">
+    <row r="53" spans="1:17" s="12" customFormat="1">
       <c r="A53" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" s="12">
         <v>0.1</v>
       </c>
-      <c r="P53" s="11"/>
-    </row>
-    <row r="54" spans="1:16" s="12" customFormat="1">
+      <c r="Q53" s="11"/>
+    </row>
+    <row r="54" spans="1:17" s="12" customFormat="1">
       <c r="A54" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="12">
+      <c r="B54" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="12">
         <v>0.1</v>
       </c>
-      <c r="D54" s="18"/>
-      <c r="P54" s="11"/>
-    </row>
-    <row r="55" spans="1:16" s="12" customFormat="1">
+      <c r="E54" s="18"/>
+      <c r="Q54" s="11"/>
+    </row>
+    <row r="55" spans="1:17" s="12" customFormat="1">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B55" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55" s="12">
         <v>0.1</v>
       </c>
-      <c r="P55" s="11"/>
-    </row>
-    <row r="56" spans="1:16" s="12" customFormat="1">
+      <c r="Q55" s="11"/>
+    </row>
+    <row r="56" spans="1:17" s="12" customFormat="1">
       <c r="A56" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B56" s="12">
+      <c r="B56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56" s="12">
         <v>0.1</v>
       </c>
-      <c r="P56" s="11"/>
-    </row>
-    <row r="57" spans="1:16" s="12" customFormat="1">
+      <c r="Q56" s="11"/>
+    </row>
+    <row r="57" spans="1:17" s="12" customFormat="1">
       <c r="A57" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P57" s="11"/>
-    </row>
-    <row r="58" spans="1:16" s="12" customFormat="1">
+      <c r="B57" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q57" s="11"/>
+    </row>
+    <row r="58" spans="1:17" s="12" customFormat="1">
       <c r="A58" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="P58" s="11"/>
-    </row>
-    <row r="59" spans="1:16" s="12" customFormat="1">
+      <c r="B58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q58" s="11"/>
+    </row>
+    <row r="59" spans="1:17" s="12" customFormat="1">
       <c r="A59" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="P59" s="11"/>
-    </row>
-    <row r="60" spans="1:16" s="12" customFormat="1">
+      <c r="B59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q59" s="11"/>
+    </row>
+    <row r="60" spans="1:17" s="12" customFormat="1">
       <c r="A60" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="P60" s="11"/>
-    </row>
-    <row r="61" spans="1:16" s="12" customFormat="1">
+      <c r="B60" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q60" s="11"/>
+    </row>
+    <row r="61" spans="1:17" s="12" customFormat="1">
       <c r="A61" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="P61" s="11"/>
-    </row>
-    <row r="62" spans="1:16" s="12" customFormat="1">
+      <c r="B61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q61" s="11"/>
+    </row>
+    <row r="62" spans="1:17" s="12" customFormat="1">
       <c r="A62" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="P62" s="11"/>
-    </row>
-    <row r="63" spans="1:16" s="12" customFormat="1">
+      <c r="B62" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q62" s="11"/>
+    </row>
+    <row r="63" spans="1:17" s="12" customFormat="1">
       <c r="A63" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="P63" s="11"/>
-    </row>
-    <row r="64" spans="1:16" s="12" customFormat="1">
+      <c r="B63" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q63" s="11"/>
+    </row>
+    <row r="64" spans="1:17" s="12" customFormat="1">
       <c r="A64" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="P64" s="11"/>
-    </row>
-    <row r="65" spans="1:23" s="12" customFormat="1">
+      <c r="B64" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q64" s="11"/>
+    </row>
+    <row r="65" spans="1:24" s="12" customFormat="1">
       <c r="A65" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="P65" s="11"/>
-    </row>
-    <row r="66" spans="1:23" s="12" customFormat="1">
+      <c r="B65" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q65" s="11"/>
+    </row>
+    <row r="66" spans="1:24" s="12" customFormat="1">
       <c r="A66" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="P66" s="11"/>
-    </row>
-    <row r="67" spans="1:23" s="12" customFormat="1">
+      <c r="B66" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q66" s="11"/>
+    </row>
+    <row r="67" spans="1:24" s="12" customFormat="1">
       <c r="A67" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="P67" s="11"/>
-    </row>
-    <row r="68" spans="1:23" s="12" customFormat="1">
+      <c r="B67" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q67" s="11"/>
+    </row>
+    <row r="68" spans="1:24" s="12" customFormat="1">
       <c r="A68" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="P68" s="11"/>
-    </row>
-    <row r="69" spans="1:23" s="19" customFormat="1">
+      <c r="B68" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q68" s="11"/>
+    </row>
+    <row r="69" spans="1:24" s="19" customFormat="1">
       <c r="A69" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B69" s="19">
+      <c r="B69" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C69" s="19">
         <v>2.7E-2</v>
       </c>
-      <c r="C69" s="20">
+      <c r="D69" s="20">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="D69" s="20">
+      <c r="E69" s="20">
         <v>-0.151308114750691</v>
       </c>
-      <c r="I69" s="20">
-        <v>0</v>
-      </c>
-      <c r="N69" s="20">
+      <c r="J69" s="20">
+        <v>0</v>
+      </c>
+      <c r="O69" s="20">
         <v>0.878</v>
       </c>
-      <c r="O69" s="21">
-        <v>-0.86358170086251695</v>
-      </c>
-      <c r="P69" s="22"/>
-      <c r="Q69" s="19" t="s">
+      <c r="P69" s="21">
+        <v>0.86358170086251695</v>
+      </c>
+      <c r="Q69" s="22"/>
+      <c r="R69" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S69" s="19" t="s">
+      <c r="T69" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W69" s="19">
+      <c r="X69" s="19">
         <v>0.29899999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:23" s="21" customFormat="1">
+    <row r="70" spans="1:24" s="21" customFormat="1">
       <c r="A70" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B70" s="21">
+      <c r="B70" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C70" s="21">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="C70" s="20">
+      <c r="D70" s="20">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="D70" s="20">
+      <c r="E70" s="20">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="I70" s="20">
-        <v>0</v>
-      </c>
-      <c r="N70" s="20">
+      <c r="J70" s="20">
+        <v>0</v>
+      </c>
+      <c r="O70" s="20">
         <v>1.458</v>
       </c>
-      <c r="O70" s="21">
-        <v>-1.4368262739973601</v>
-      </c>
-      <c r="P70" s="23"/>
-      <c r="Q70" s="19" t="s">
+      <c r="P70" s="21">
+        <v>1.4368262739973601</v>
+      </c>
+      <c r="Q70" s="23"/>
+      <c r="R70" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S70" s="19" t="s">
+      <c r="T70" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W70" s="21">
+      <c r="X70" s="21">
         <v>0.312</v>
       </c>
     </row>
-    <row r="71" spans="1:23" s="21" customFormat="1">
+    <row r="71" spans="1:24" s="21" customFormat="1">
       <c r="A71" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="21">
+      <c r="B71" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C71" s="21">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C71" s="20">
+      <c r="D71" s="20">
         <v>-1.171</v>
       </c>
-      <c r="D71" s="20">
+      <c r="E71" s="20">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="I71" s="20">
-        <v>0</v>
-      </c>
-      <c r="N71" s="20">
+      <c r="J71" s="20">
+        <v>0</v>
+      </c>
+      <c r="O71" s="20">
         <v>2.5470000000000002</v>
       </c>
-      <c r="O71" s="21">
-        <v>-2.4905493340587901</v>
-      </c>
-      <c r="P71" s="23"/>
-      <c r="Q71" s="19" t="s">
+      <c r="P71" s="21">
+        <v>2.4905493340587901</v>
+      </c>
+      <c r="Q71" s="23"/>
+      <c r="R71" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S71" s="19" t="s">
+      <c r="T71" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W71" s="21">
+      <c r="X71" s="21">
         <v>0.371</v>
       </c>
     </row>
-    <row r="72" spans="1:23" s="21" customFormat="1">
+    <row r="72" spans="1:24" s="21" customFormat="1">
       <c r="A72" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B72" s="21">
+      <c r="B72" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C72" s="21">
         <v>0.152</v>
       </c>
-      <c r="C72" s="20">
+      <c r="D72" s="20">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="D72" s="20">
+      <c r="E72" s="20">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="I72" s="20">
-        <v>0</v>
-      </c>
-      <c r="N72" s="20">
+      <c r="J72" s="20">
+        <v>0</v>
+      </c>
+      <c r="O72" s="20">
         <v>3.81518914277475</v>
       </c>
-      <c r="O72" s="21">
-        <v>-3.855</v>
-      </c>
-      <c r="P72" s="23"/>
-      <c r="Q72" s="19" t="s">
+      <c r="P72" s="21">
+        <v>3.855</v>
+      </c>
+      <c r="Q72" s="23"/>
+      <c r="R72" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S72" s="19" t="s">
+      <c r="T72" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W72" s="21">
+      <c r="X72" s="21">
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="73" spans="1:23" s="21" customFormat="1">
+    <row r="73" spans="1:24" s="21" customFormat="1">
       <c r="A73" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B73" s="21">
+      <c r="B73" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="21">
         <v>0.214</v>
       </c>
-      <c r="C73" s="20">
+      <c r="D73" s="20">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="D73" s="20">
+      <c r="E73" s="20">
         <v>-1.22567508688439</v>
       </c>
-      <c r="I73" s="20">
+      <c r="J73" s="20">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="N73" s="20">
+      <c r="O73" s="20">
         <v>5.5949999999999998</v>
       </c>
-      <c r="O73" s="21">
-        <v>-5.4782042149448502</v>
-      </c>
-      <c r="P73" s="23"/>
-      <c r="Q73" s="19" t="s">
+      <c r="P73" s="21">
+        <v>5.4782042149448502</v>
+      </c>
+      <c r="Q73" s="23"/>
+      <c r="R73" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S73" s="19" t="s">
+      <c r="T73" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W73" s="21">
+      <c r="X73" s="21">
         <v>0.32</v>
       </c>
     </row>
-    <row r="74" spans="1:23" s="21" customFormat="1">
+    <row r="74" spans="1:24" s="21" customFormat="1">
       <c r="A74" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B74" s="21">
+      <c r="B74" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C74" s="21">
         <v>0.254</v>
       </c>
-      <c r="C74" s="20">
+      <c r="D74" s="20">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="D74" s="20">
+      <c r="E74" s="20">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="I74" s="20">
+      <c r="J74" s="20">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="N74" s="20">
+      <c r="O74" s="20">
         <v>6.484</v>
       </c>
-      <c r="O74" s="21">
-        <v>-6.2489999999999997</v>
-      </c>
-      <c r="P74" s="23"/>
-      <c r="Q74" s="19" t="s">
+      <c r="P74" s="21">
+        <v>6.2489999999999997</v>
+      </c>
+      <c r="Q74" s="23"/>
+      <c r="R74" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S74" s="19" t="s">
+      <c r="T74" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W74" s="21">
+      <c r="X74" s="21">
         <v>0.37799999999999995</v>
       </c>
     </row>
-    <row r="75" spans="1:23" s="21" customFormat="1">
+    <row r="75" spans="1:24" s="21" customFormat="1">
       <c r="A75" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B75" s="21">
+      <c r="B75" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C75" s="21">
         <v>0.28399999999999997</v>
       </c>
-      <c r="C75" s="20">
+      <c r="D75" s="20">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="D75" s="20">
+      <c r="E75" s="20">
         <v>-1.47353470842518</v>
       </c>
-      <c r="I75" s="20">
+      <c r="J75" s="20">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="N75" s="20">
+      <c r="O75" s="20">
         <v>8.0890000000000004</v>
       </c>
-      <c r="O75" s="21">
-        <v>-7.9485854277214001</v>
-      </c>
-      <c r="P75" s="23"/>
-      <c r="Q75" s="19" t="s">
+      <c r="P75" s="21">
+        <v>7.9485854277214001</v>
+      </c>
+      <c r="Q75" s="23"/>
+      <c r="R75" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S75" s="19" t="s">
+      <c r="T75" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W75" s="21">
+      <c r="X75" s="21">
         <v>0.39100000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:23" s="21" customFormat="1">
+    <row r="76" spans="1:24" s="21" customFormat="1">
       <c r="A76" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B76" s="21">
+      <c r="B76" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C76" s="21">
         <v>0.33400000000000002</v>
       </c>
-      <c r="C76" s="20">
+      <c r="D76" s="20">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="D76" s="20">
+      <c r="E76" s="20">
         <v>-1.99253212300414</v>
       </c>
-      <c r="I76" s="20">
+      <c r="J76" s="20">
         <v>2.0830000000081101</v>
       </c>
-      <c r="N76" s="20">
+      <c r="O76" s="20">
         <v>11.872999999999999</v>
       </c>
-      <c r="O76" s="21">
-        <v>-9.6077296533960403</v>
-      </c>
-      <c r="P76" s="23"/>
-      <c r="Q76" s="19" t="s">
+      <c r="P76" s="21">
+        <v>9.6077296533960403</v>
+      </c>
+      <c r="Q76" s="23"/>
+      <c r="R76" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S76" s="19" t="s">
+      <c r="T76" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W76" s="21">
+      <c r="X76" s="21">
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:23" s="21" customFormat="1">
+    <row r="77" spans="1:24" s="21" customFormat="1">
       <c r="A77" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B77" s="21">
+      <c r="B77" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C77" s="21">
         <v>0.379</v>
       </c>
-      <c r="C77" s="20">
+      <c r="D77" s="20">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="D77" s="20">
+      <c r="E77" s="20">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="I77" s="20">
+      <c r="J77" s="20">
         <v>5.5389999999999997</v>
       </c>
-      <c r="N77" s="20">
+      <c r="O77" s="20">
         <v>14.304133448972699</v>
       </c>
-      <c r="O77" s="21">
-        <v>-8.8979999999999997</v>
-      </c>
-      <c r="P77" s="23"/>
-      <c r="Q77" s="19" t="s">
+      <c r="P77" s="21">
+        <v>8.8979999999999997</v>
+      </c>
+      <c r="Q77" s="23"/>
+      <c r="R77" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="S77" s="19" t="s">
+      <c r="T77" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="W77" s="21">
+      <c r="X77" s="21">
         <v>0.39100000000000001</v>
       </c>
     </row>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CD058E-38E8-0946-888A-DB788D917361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5066DF8-4453-A044-86EF-EF08044830BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26880" windowHeight="15220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2780" yWindow="500" windowWidth="32900" windowHeight="21440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$T$1:$T$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supplementary File 1e vip'!$T$1:$T$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="116">
   <si>
     <t>sample</t>
   </si>
@@ -565,7 +566,7 @@
       <name val="Times Roman"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -775,6 +776,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -951,7 +958,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1018,6 +1025,8 @@
     <xf numFmtId="0" fontId="21" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4994,1521 +5003,2435 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.33203125" customWidth="1"/>
+    <col min="18" max="18" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="Q1" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="C2">
         <v>0.82299999999999995</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.13100000000000001</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.13100000000000001</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>7.2308500000000005E-4</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
       <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
         <v>4.0285879999999996E-3</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>2.4449999999999998</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>2.3620000000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="Q2" s="15">
+        <v>0.27251471399999999</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S2" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T2" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U2" s="15">
+        <v>30</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="C3">
         <v>0.70399999999999996</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>1.6583900000000001E-4</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
       <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>6.6796169999999997E-3</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>2.105</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>2.2759999999999998</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="Q3" s="15">
+        <v>0.25082010700000001</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S3" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T3" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U3" s="15">
+        <v>30</v>
+      </c>
+      <c r="V3" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="C4">
         <v>0.76800000000000002</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>3.81541E-4</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
       <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>9.7823159999999992E-3</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>2.383</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>1.6240000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5">
+      <c r="Q4" s="15">
+        <v>0.26109650000000001</v>
+      </c>
+      <c r="R4" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S4" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T4" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U4" s="15">
+        <v>30</v>
+      </c>
+      <c r="V4" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" s="28" customFormat="1">
+      <c r="A5" s="28">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="28">
         <v>1.18</v>
       </c>
-      <c r="C5">
+      <c r="D5" s="28">
         <v>2.2029999999999998</v>
       </c>
-      <c r="G5">
+      <c r="H5" s="28">
         <v>2.2029999999999998</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
+      <c r="I5" s="28">
+        <v>0</v>
+      </c>
+      <c r="J5" s="28">
+        <v>0</v>
+      </c>
+      <c r="K5" s="28">
         <v>1.2795499999999999E-4</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="28">
+        <v>0</v>
+      </c>
+      <c r="M5" s="28">
+        <v>0</v>
+      </c>
+      <c r="N5" s="28">
         <v>1.93</v>
       </c>
-      <c r="N5">
+      <c r="O5" s="28">
         <v>2.44</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6">
+      <c r="Q5" s="29">
+        <v>0.35967375000000001</v>
+      </c>
+      <c r="R5" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="S5" s="29">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="T5" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="U5" s="29">
+        <v>3</v>
+      </c>
+      <c r="V5" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" s="28" customFormat="1">
+      <c r="A6" s="28">
+        <v>5</v>
+      </c>
+      <c r="B6" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="28">
         <v>1.127</v>
       </c>
-      <c r="C6">
+      <c r="D6" s="28">
         <v>2.0979999999999999</v>
       </c>
-      <c r="G6">
+      <c r="H6" s="28">
         <v>2.0979999999999999</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="28">
         <v>1.6766474999999999E-2</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
+      <c r="J6" s="28">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28">
         <v>1.5726999999999999E-4</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="28">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28">
+        <v>0</v>
+      </c>
+      <c r="N6" s="28">
         <v>2.0699999999999998</v>
       </c>
-      <c r="N6">
+      <c r="O6" s="28">
         <v>2.39</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7">
+      <c r="Q6" s="29">
+        <v>0.377942893</v>
+      </c>
+      <c r="R6" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="S6" s="29">
+        <v>5</v>
+      </c>
+      <c r="T6" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="U6" s="29">
+        <v>3</v>
+      </c>
+      <c r="V6" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" s="28" customFormat="1">
+      <c r="A7" s="28">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="28">
         <v>1.0980000000000001</v>
       </c>
-      <c r="C7">
+      <c r="D7" s="28">
         <v>2.0550000000000002</v>
       </c>
-      <c r="G7">
+      <c r="H7" s="28">
         <v>2.0550000000000002</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="I7" s="28">
+        <v>0</v>
+      </c>
+      <c r="J7" s="28">
+        <v>0</v>
+      </c>
+      <c r="K7" s="28">
         <v>1.3422099999999999E-4</v>
       </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="28">
+        <v>0</v>
+      </c>
+      <c r="M7" s="28">
+        <v>0</v>
+      </c>
+      <c r="N7" s="28">
         <v>1.97</v>
       </c>
-      <c r="N7">
+      <c r="O7" s="28">
         <v>2.1800000000000002</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="Q7" s="29">
+        <v>0.33645671399999999</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="S7" s="29">
+        <v>5</v>
+      </c>
+      <c r="T7" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="U7" s="29">
+        <v>3</v>
+      </c>
+      <c r="V7" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C8">
         <v>1.51</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.308</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.308</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
       <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
         <v>7.5614127000000003E-2</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>1.7982350000000001E-2</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
         <v>3.4660000000000002</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>3.6160000000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="Q8" s="15">
+        <v>0.209333929</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S8" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T8" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U8" s="15">
+        <v>30</v>
+      </c>
+      <c r="V8" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C9">
         <v>1.5109999999999999</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.308</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.308</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <v>4.9087042999999997E-2</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>1.38432E-2</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
         <v>3.1360000000000001</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>3.5219999999999998</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="Q9" s="15">
+        <v>0.22151335699999999</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S9" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T9" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U9" s="15">
+        <v>30</v>
+      </c>
+      <c r="V9" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C10">
         <v>1.4890000000000001</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.30399999999999999</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
       <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
         <v>6.6037847999999996E-2</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>1.602926E-2</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
         <v>3.161</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>3.8239999999999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="Q10" s="15">
+        <v>0.24587221400000001</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S10" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T10" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U10" s="15">
+        <v>30</v>
+      </c>
+      <c r="V10" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="C11">
         <v>2.0190000000000001</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.41499999999999998</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.41499999999999998</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.14387805000000001</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.23128044</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>2.4418572999999999E-2</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>7.3894399999999995E-4</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>4.2122905000000002E-2</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>5.51</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>5.2519999999999998</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="Q11" s="15">
+        <v>0.30372450000000001</v>
+      </c>
+      <c r="R11" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S11" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T11" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U11" s="15">
+        <v>30</v>
+      </c>
+      <c r="V11" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="C12">
         <v>2.0590000000000002</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.42499999999999999</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.42499999999999999</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.13916811300000001</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.22761730999999999</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>2.5077986E-2</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>2.152588E-3</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>3.3899711999999999E-2</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>5.3739999999999997</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>4.5460000000000003</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="Q12" s="15">
+        <v>0.25690982099999998</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S12" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T12" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U12" s="15">
+        <v>30</v>
+      </c>
+      <c r="V12" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="15">
+        <v>0.13</v>
+      </c>
+      <c r="C13">
         <v>2.1349999999999998</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.438</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.438</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.13267562499999999</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.25727792100000002</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>2.6121129999999999E-2</v>
       </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
       <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>4.1071206999999998E-2</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>5.3019999999999996</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>5.07</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="Q13" s="15">
+        <v>0.26642500000000002</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S13" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T13" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U13" s="15">
+        <v>30</v>
+      </c>
+      <c r="V13" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="15">
+        <v>0.18</v>
+      </c>
+      <c r="C14">
         <v>3.266</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.66900000000000004</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.66900000000000004</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>1.2813869950000001</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.18048138799999999</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>3.2745818000000003E-2</v>
       </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
       <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>5.6452840000000004E-3</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>7.2619999999999996</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>5.42</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="Q14" s="15">
+        <v>0.28926142900000001</v>
+      </c>
+      <c r="R14" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T14" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U14" s="15">
+        <v>30</v>
+      </c>
+      <c r="V14" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="15">
+        <v>0.18</v>
+      </c>
+      <c r="C15">
         <v>3.202</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.65900000000000003</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.65900000000000003</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>1.4870797280000001</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.41515672300000001</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>3.1272250000000001E-2</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>2.6969479999999998E-3</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>1.6418242E-2</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>7.3049999999999997</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>6.0170000000000003</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="Q15" s="15">
+        <v>0.28202989299999998</v>
+      </c>
+      <c r="R15" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S15" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T15" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U15" s="15">
+        <v>30</v>
+      </c>
+      <c r="V15" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="15">
+        <v>0.18</v>
+      </c>
+      <c r="C16">
         <v>2.83</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.58099999999999996</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.58099999999999996</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>1.069367508</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.18424942899999999</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>2.652065E-2</v>
       </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
       <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>1.5674206999999999E-2</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>6.2510000000000003</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>5.2640000000000002</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="Q16" s="15">
+        <v>0.288119607</v>
+      </c>
+      <c r="R16" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S16" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T16" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U16" s="15">
+        <v>30</v>
+      </c>
+      <c r="V16" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="C17">
         <v>7.9909999999999997</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>1.6479999999999999</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>1.6479999999999999</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>7.0441347099999998</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.31251037799999998</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>5.1692219999999997E-2</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>1.1339925000000001E-2</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
       <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
         <v>14.086</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>8.3010000000000002</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="Q17" s="15">
+        <v>0.42247392900000003</v>
+      </c>
+      <c r="R17" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S17" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T17" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U17" s="15">
+        <v>30</v>
+      </c>
+      <c r="V17" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="C18">
         <v>8.2759999999999998</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>1.6950000000000001</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>1.6950000000000001</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>6.6847254490000001</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.27229536399999998</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>4.4478275999999997E-2</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>3.4668667E-2</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
       <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
         <v>15.111000000000001</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>8.3870000000000005</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="Q18" s="15">
+        <v>0.42133210700000001</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S18" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T18" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U18" s="15">
+        <v>30</v>
+      </c>
+      <c r="V18" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="C19">
         <v>8.9320000000000004</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>1.8660000000000001</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>1.8660000000000001</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>8.2124218889999998</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.61718923199999998</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>6.4337543999999997E-2</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>2.9481279999999999E-2</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
       <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>16.956</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>9.34</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="Q19" s="15">
+        <v>0.39963749999999998</v>
+      </c>
+      <c r="R19" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S19" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T19" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U19" s="15">
+        <v>30</v>
+      </c>
+      <c r="V19" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="C20">
         <v>12.936999999999999</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>2.7120000000000002</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>2.7120000000000002</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>11.927306959999999</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.47269426599999997</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>8.9757966999999994E-2</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>3.5944587E-2</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
       <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
         <v>20.902000000000001</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>12.682</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="Q20" s="15">
+        <v>0.48415467400000001</v>
+      </c>
+      <c r="R20" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S20" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T20" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U20" s="15">
+        <v>30</v>
+      </c>
+      <c r="V20" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="C21">
         <v>13.23</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>2.786</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>2.786</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>12.12470377</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.63692599999999999</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.104193063</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>3.3770889999999998E-2</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
       <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
         <v>21.082999999999998</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>12.353999999999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="Q21" s="15">
+        <v>0.48992198300000001</v>
+      </c>
+      <c r="R21" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S21" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T21" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U21" s="15">
+        <v>30</v>
+      </c>
+      <c r="V21" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="15">
+        <v>0.35</v>
+      </c>
+      <c r="C22">
         <v>13.096</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>2.742</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>2.742</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>11.84780602</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.47734259699999998</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>9.1823417000000004E-2</v>
       </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
         <v>21.097999999999999</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>12.977</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="Q22" s="15">
+        <v>0.50886425499999999</v>
+      </c>
+      <c r="R22" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="S22" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T22" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U22" s="15">
+        <v>30</v>
+      </c>
+      <c r="V22" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C23">
         <v>0.82699999999999996</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.747</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>1.4930000000000001</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>8.7561730000000008E-3</v>
       </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
         <v>2.7690000000000001</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>2.4500000000000002</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="Q23" s="15">
+        <v>0.49783414300000001</v>
+      </c>
+      <c r="R23" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S23" s="15">
+        <v>5.53</v>
+      </c>
+      <c r="T23" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U23" s="15">
+        <v>5</v>
+      </c>
+      <c r="V23" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C24">
         <v>0.78800000000000003</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>0.71199999999999997</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>1.423</v>
       </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
         <v>5.5182690000000001E-3</v>
       </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
         <v>2.7170000000000001</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>2.3530000000000002</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="Q24" s="15">
+        <v>0.58385135700000002</v>
+      </c>
+      <c r="R24" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S24" s="15">
+        <v>5.53</v>
+      </c>
+      <c r="T24" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U24" s="15">
+        <v>5</v>
+      </c>
+      <c r="V24" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C25">
         <v>0.76700000000000002</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>0.69099999999999995</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>1.3819999999999999</v>
       </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>1.9902549999999998E-3</v>
       </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
         <v>2.5739999999999998</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>2.25</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="Q25" s="15">
+        <v>0.59412774999999995</v>
+      </c>
+      <c r="R25" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S25" s="15">
+        <v>5.53</v>
+      </c>
+      <c r="T25" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U25" s="15">
+        <v>5</v>
+      </c>
+      <c r="V25" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C26">
         <v>0.80700000000000005</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>4.92</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>9.8390000000000004</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
         <v>3.9436786000000001E-2</v>
       </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
       <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>1.3630471999999999E-2</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>3.032</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>1.7749999999999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="Q26" s="15">
+        <v>0.510013571</v>
+      </c>
+      <c r="R26" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S26" s="15">
+        <v>5.53</v>
+      </c>
+      <c r="T26" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U26" s="15">
+        <v>3</v>
+      </c>
+      <c r="V26" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C27">
         <v>0.64900000000000002</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>3.9620000000000002</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>7.9240000000000004</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
         <v>3.0460814999999999E-2</v>
       </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
       <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>9.5061450000000006E-3</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>1.9590000000000001</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>1.623</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="Q27" s="15">
+        <v>0.29420932100000002</v>
+      </c>
+      <c r="R27" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S27" s="15">
+        <v>5.53</v>
+      </c>
+      <c r="T27" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U27" s="15">
+        <v>3</v>
+      </c>
+      <c r="V27" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C28">
         <v>0.76500000000000001</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>4.6159999999999997</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>9.2319999999999993</v>
       </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
         <v>2.5119712999999998E-2</v>
       </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
         <v>2.569</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>1.2909999999999999</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="Q28" s="15">
+        <v>0.358912536</v>
+      </c>
+      <c r="R28" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S28" s="15">
+        <v>5.53</v>
+      </c>
+      <c r="T28" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U28" s="15">
+        <v>3</v>
+      </c>
+      <c r="V28" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C29">
         <v>1.381</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>0.158</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>0.317</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>1.8073279000000001E-2</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>7.8381013999999999E-2</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>0.86713414300000002</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>5.4564440000000004E-3</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>4.6616212999999997E-2</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>4.3209999999999997</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>3.883</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="Q29" s="15">
+        <v>0.20552785700000001</v>
+      </c>
+      <c r="R29" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S29" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T29" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U29" s="15">
+        <v>30</v>
+      </c>
+      <c r="V29" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C30">
         <v>1.2589999999999999</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>0.14199999999999999</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>0.28399999999999997</v>
       </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
       <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
         <v>3.4333113999999998E-2</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>0.69158415699999998</v>
       </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
       <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
         <v>4.5041784000000001E-2</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>3.93</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>3.3959999999999999</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="Q30" s="15">
+        <v>0.35282282100000001</v>
+      </c>
+      <c r="R30" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S30" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T30" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U30" s="15">
+        <v>30</v>
+      </c>
+      <c r="V30" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C31">
         <v>1.3</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>0.14899999999999999</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>0.29799999999999999</v>
       </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
       <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
         <v>7.6426068999999999E-2</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>0.84262339500000005</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>5.663179E-3</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>4.1991897E-2</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>4.077</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>3.3340000000000001</v>
       </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="Q31" s="15">
+        <v>0.36195739300000002</v>
+      </c>
+      <c r="R31" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S31" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T31" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U31" s="15">
+        <v>30</v>
+      </c>
+      <c r="V31" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C32">
         <v>1.4850000000000001</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>2.8620000000000001</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>2.8620000000000001</v>
       </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
         <v>6.3162172000000003E-2</v>
       </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
         <v>5.7110000000000003</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>5.6040000000000001</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="Q32" s="15">
+        <v>0.425138179</v>
+      </c>
+      <c r="R32" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="S32" s="15">
+        <v>12.35</v>
+      </c>
+      <c r="T32" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U32" s="15">
+        <v>3</v>
+      </c>
+      <c r="V32" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C33">
         <v>1.6</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>3.0840000000000001</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>3.0840000000000001</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
         <v>7.4209667000000007E-2</v>
       </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
         <v>6.0389999999999997</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>5.8689999999999998</v>
       </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="Q33" s="15">
+        <v>0.52028996400000005</v>
+      </c>
+      <c r="R33" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="S33" s="15">
+        <v>12.35</v>
+      </c>
+      <c r="T33" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U33" s="15">
+        <v>3</v>
+      </c>
+      <c r="V33" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C34">
         <v>1.4350000000000001</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>2.7629999999999999</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>2.7629999999999999</v>
       </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
         <v>7.4921513999999995E-2</v>
       </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
         <v>5.32</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>5.0789999999999997</v>
       </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="Q34" s="15">
+        <v>0.452161286</v>
+      </c>
+      <c r="R34" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="S34" s="15">
+        <v>12.35</v>
+      </c>
+      <c r="T34" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U34" s="15">
+        <v>3</v>
+      </c>
+      <c r="V34" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C35">
         <v>1.6779999999999999</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>0.33400000000000002</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>0.33400000000000002</v>
       </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
         <v>0.27117874199999997</v>
       </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
         <v>5.7240000000000002</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>5.9080000000000004</v>
       </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="Q35" s="15">
+        <v>0.41790664300000002</v>
+      </c>
+      <c r="R35" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="S35" s="15">
+        <v>1.24</v>
+      </c>
+      <c r="T35" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U35" s="15">
+        <v>30</v>
+      </c>
+      <c r="V35" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C36">
         <v>1.6930000000000001</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0.33700000000000002</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>0.33700000000000002</v>
       </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
         <v>0.30716928599999999</v>
       </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
         <v>5.9720000000000004</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>5.29</v>
       </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="Q36" s="15">
+        <v>0.37870410700000001</v>
+      </c>
+      <c r="R36" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="S36" s="15">
+        <v>1.24</v>
+      </c>
+      <c r="T36" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U36" s="15">
+        <v>30</v>
+      </c>
+      <c r="V36" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C37">
         <v>1.647</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>0.32700000000000001</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>0.32700000000000001</v>
       </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
         <v>0.20397084300000001</v>
       </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
         <v>6.1310000000000002</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>5.69</v>
       </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="Q37" s="15">
+        <v>0.39887628600000002</v>
+      </c>
+      <c r="R37" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="S37" s="15">
+        <v>1.24</v>
+      </c>
+      <c r="T37" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U37" s="15">
+        <v>30</v>
+      </c>
+      <c r="V37" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C38">
         <v>1.4790000000000001</v>
-      </c>
-      <c r="F38">
-        <v>2.919</v>
       </c>
       <c r="G38">
         <v>2.919</v>
       </c>
       <c r="H38">
+        <v>2.919</v>
+      </c>
+      <c r="I38">
         <v>6.4434642E-2</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
       <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
         <v>0.16559933199999999</v>
       </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
       <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
         <v>4.8736990000000004E-3</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>4.7869999999999999</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>4.5609999999999999</v>
       </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="Q38" s="15">
+        <v>0.32085182099999998</v>
+      </c>
+      <c r="R38" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="S38" s="15">
+        <v>9.81</v>
+      </c>
+      <c r="T38" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U38" s="15">
+        <v>3</v>
+      </c>
+      <c r="V38" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C39">
         <v>1.633</v>
-      </c>
-      <c r="F39">
-        <v>3.2</v>
       </c>
       <c r="G39">
         <v>3.2</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I39">
         <v>0</v>
       </c>
       <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
         <v>0.156217087</v>
       </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
         <v>5.1379999999999999</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>4.9089999999999998</v>
       </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="Q39" s="15">
+        <v>0.41866785699999998</v>
+      </c>
+      <c r="R39" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="S39" s="15">
+        <v>9.81</v>
+      </c>
+      <c r="T39" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U39" s="15">
+        <v>3</v>
+      </c>
+      <c r="V39" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C40">
         <v>1.571</v>
-      </c>
-      <c r="F40">
-        <v>3.0830000000000002</v>
       </c>
       <c r="G40">
         <v>3.0830000000000002</v>
       </c>
       <c r="H40">
+        <v>3.0830000000000002</v>
+      </c>
+      <c r="I40">
         <v>6.4504826000000001E-2</v>
       </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
       <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
         <v>0.15037355499999999</v>
       </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
       <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
         <v>5.596462E-3</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>4.9610000000000003</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>4.5490000000000004</v>
       </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="Q40" s="15">
+        <v>0.33150882100000001</v>
+      </c>
+      <c r="R40" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="S40" s="15">
+        <v>9.81</v>
+      </c>
+      <c r="T40" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="U40" s="15">
+        <v>3</v>
+      </c>
+      <c r="V40" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C41">
         <v>1.4510000000000001</v>
-      </c>
-      <c r="F41">
-        <v>0.29199999999999998</v>
       </c>
       <c r="G41">
         <v>0.29199999999999998</v>
       </c>
       <c r="H41">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="I41">
         <v>0.16597783599999999</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>6.6479359000000002E-2</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>0.60819290000000004</v>
       </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
       <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
         <v>2.5725250000000002E-2</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>4.18</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>4.0129999999999999</v>
       </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="Q41" s="15">
+        <v>0.43998185699999998</v>
+      </c>
+      <c r="R41" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="S41" s="15">
+        <v>0.98</v>
+      </c>
+      <c r="T41" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U41" s="15">
+        <v>30</v>
+      </c>
+      <c r="V41" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C42">
         <v>1.7090000000000001</v>
-      </c>
-      <c r="F42">
-        <v>0.33900000000000002</v>
       </c>
       <c r="G42">
         <v>0.33900000000000002</v>
       </c>
       <c r="H42">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="I42">
         <v>6.0174350000000001E-2</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>7.8079274000000004E-2</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>0.66867871400000001</v>
       </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
       <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
         <v>3.5868012999999997E-2</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>4.9020000000000001</v>
       </c>
-      <c r="N42">
+      <c r="O42">
         <v>4.45</v>
       </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="Q42" s="15">
+        <v>0.448355214</v>
+      </c>
+      <c r="R42" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="S42" s="15">
+        <v>0.98</v>
+      </c>
+      <c r="T42" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U42" s="15">
+        <v>30</v>
+      </c>
+      <c r="V42" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C43">
         <v>1.6220000000000001</v>
-      </c>
-      <c r="F43">
-        <v>0.32900000000000001</v>
       </c>
       <c r="G43">
         <v>0.32900000000000001</v>
       </c>
       <c r="H43">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="I43">
         <v>0.18362290100000001</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>0.16825845</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>0.92271634599999997</v>
       </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
       <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>4.8272586999999999E-2</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>4.5620000000000003</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>4.2300000000000004</v>
+      </c>
+      <c r="Q43" s="15">
+        <v>0.42361575000000001</v>
+      </c>
+      <c r="R43" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="S43" s="15">
+        <v>0.98</v>
+      </c>
+      <c r="T43" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U43" s="15">
+        <v>30</v>
+      </c>
+      <c r="V43" s="15" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5066DF8-4453-A044-86EF-EF08044830BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13969006-75B9-A247-900C-F5202197DEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="500" windowWidth="32900" windowHeight="21440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1440" windowWidth="26880" windowHeight="15220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$T$1:$T$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supplementary File 1e vip'!$T$1:$T$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supplementary File 1e vip'!$B$1:$B$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5003,6 +5003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -5082,7 +5083,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" hidden="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5138,7 +5139,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:22" hidden="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5194,7 +5195,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:22" hidden="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5586,7 +5587,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:22" hidden="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5642,7 +5643,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:22" hidden="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5698,7 +5699,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:22" hidden="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5754,7 +5755,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:22" hidden="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5810,7 +5811,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:22" hidden="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5866,7 +5867,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:22" hidden="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5922,7 +5923,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" hidden="1">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5978,7 +5979,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" hidden="1">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6034,7 +6035,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:22" hidden="1">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6090,7 +6091,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" hidden="1">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6146,7 +6147,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" hidden="1">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6202,7 +6203,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" hidden="1">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7435,6 +7436,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:B43" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="0.1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13969006-75B9-A247-900C-F5202197DEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD3D75D-BE95-5540-8EF8-954FC8521231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1440" windowWidth="26880" windowHeight="15220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1440" windowWidth="26060" windowHeight="15220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -958,7 +958,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1006,11 +1006,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1027,6 +1022,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4429,17 +4427,17 @@
         <v>0.42361575000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="26" customFormat="1">
-      <c r="A48" s="24" t="s">
+    <row r="48" spans="1:24" s="23" customFormat="1">
+      <c r="A48" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="22">
         <v>0.1</v>
       </c>
-      <c r="Q48" s="27"/>
+      <c r="Q48" s="24"/>
     </row>
     <row r="49" spans="1:17" s="7" customFormat="1">
       <c r="A49" s="4" t="s">
@@ -4682,22 +4680,21 @@
       <c r="C69" s="19">
         <v>2.7E-2</v>
       </c>
-      <c r="D69" s="20">
+      <c r="D69" s="27">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="E69" s="20">
+      <c r="E69" s="27">
         <v>-0.151308114750691</v>
       </c>
-      <c r="J69" s="20">
-        <v>0</v>
-      </c>
-      <c r="O69" s="20">
+      <c r="J69" s="27">
+        <v>0</v>
+      </c>
+      <c r="O69" s="27">
         <v>0.878</v>
       </c>
-      <c r="P69" s="21">
+      <c r="P69" s="20">
         <v>0.86358170086251695</v>
       </c>
-      <c r="Q69" s="22"/>
       <c r="R69" s="19" t="s">
         <v>100</v>
       </c>
@@ -4708,291 +4705,283 @@
         <v>0.29899999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:24" s="21" customFormat="1">
+    <row r="70" spans="1:24" s="20" customFormat="1">
       <c r="A70" s="9" t="s">
         <v>82</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C70" s="21">
+      <c r="C70" s="20">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="D70" s="20">
+      <c r="D70" s="27">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="E70" s="20">
+      <c r="E70" s="27">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="J70" s="20">
-        <v>0</v>
-      </c>
-      <c r="O70" s="20">
+      <c r="J70" s="27">
+        <v>0</v>
+      </c>
+      <c r="O70" s="27">
         <v>1.458</v>
       </c>
-      <c r="P70" s="21">
+      <c r="P70" s="20">
         <v>1.4368262739973601</v>
       </c>
-      <c r="Q70" s="23"/>
       <c r="R70" s="19" t="s">
         <v>100</v>
       </c>
       <c r="T70" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="X70" s="21">
+      <c r="X70" s="20">
         <v>0.312</v>
       </c>
     </row>
-    <row r="71" spans="1:24" s="21" customFormat="1">
+    <row r="71" spans="1:24" s="20" customFormat="1">
       <c r="A71" s="9" t="s">
         <v>83</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C71" s="21">
+      <c r="C71" s="20">
         <v>0.10199999999999999</v>
       </c>
-      <c r="D71" s="20">
+      <c r="D71" s="27">
         <v>-1.171</v>
       </c>
-      <c r="E71" s="20">
+      <c r="E71" s="27">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="J71" s="20">
-        <v>0</v>
-      </c>
-      <c r="O71" s="20">
+      <c r="J71" s="27">
+        <v>0</v>
+      </c>
+      <c r="O71" s="27">
         <v>2.5470000000000002</v>
       </c>
-      <c r="P71" s="21">
+      <c r="P71" s="20">
         <v>2.4905493340587901</v>
       </c>
-      <c r="Q71" s="23"/>
       <c r="R71" s="19" t="s">
         <v>100</v>
       </c>
       <c r="T71" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="X71" s="21">
+      <c r="X71" s="20">
         <v>0.371</v>
       </c>
     </row>
-    <row r="72" spans="1:24" s="21" customFormat="1">
+    <row r="72" spans="1:24" s="20" customFormat="1">
       <c r="A72" s="9" t="s">
         <v>84</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C72" s="21">
+      <c r="C72" s="20">
         <v>0.152</v>
       </c>
-      <c r="D72" s="20">
+      <c r="D72" s="27">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="E72" s="20">
+      <c r="E72" s="27">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="J72" s="20">
-        <v>0</v>
-      </c>
-      <c r="O72" s="20">
+      <c r="J72" s="27">
+        <v>0</v>
+      </c>
+      <c r="O72" s="27">
         <v>3.81518914277475</v>
       </c>
-      <c r="P72" s="21">
+      <c r="P72" s="20">
         <v>3.855</v>
       </c>
-      <c r="Q72" s="23"/>
       <c r="R72" s="19" t="s">
         <v>100</v>
       </c>
       <c r="T72" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="X72" s="21">
+      <c r="X72" s="20">
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="73" spans="1:24" s="21" customFormat="1">
+    <row r="73" spans="1:24" s="20" customFormat="1">
       <c r="A73" s="9" t="s">
         <v>85</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C73" s="21">
+      <c r="C73" s="20">
         <v>0.214</v>
       </c>
-      <c r="D73" s="20">
+      <c r="D73" s="27">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="E73" s="20">
+      <c r="E73" s="27">
         <v>-1.22567508688439</v>
       </c>
-      <c r="J73" s="20">
+      <c r="J73" s="27">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="O73" s="20">
+      <c r="O73" s="27">
         <v>5.5949999999999998</v>
       </c>
-      <c r="P73" s="21">
+      <c r="P73" s="20">
         <v>5.4782042149448502</v>
       </c>
-      <c r="Q73" s="23"/>
       <c r="R73" s="19" t="s">
         <v>100</v>
       </c>
       <c r="T73" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="X73" s="21">
+      <c r="X73" s="20">
         <v>0.32</v>
       </c>
     </row>
-    <row r="74" spans="1:24" s="21" customFormat="1">
+    <row r="74" spans="1:24" s="20" customFormat="1">
       <c r="A74" s="9" t="s">
         <v>86</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C74" s="21">
+      <c r="C74" s="20">
         <v>0.254</v>
       </c>
-      <c r="D74" s="20">
+      <c r="D74" s="27">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="E74" s="20">
+      <c r="E74" s="27">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="J74" s="20">
+      <c r="J74" s="27">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="O74" s="20">
+      <c r="O74" s="27">
         <v>6.484</v>
       </c>
-      <c r="P74" s="21">
+      <c r="P74" s="20">
         <v>6.2489999999999997</v>
       </c>
-      <c r="Q74" s="23"/>
       <c r="R74" s="19" t="s">
         <v>100</v>
       </c>
       <c r="T74" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="X74" s="21">
+      <c r="X74" s="20">
         <v>0.37799999999999995</v>
       </c>
     </row>
-    <row r="75" spans="1:24" s="21" customFormat="1">
+    <row r="75" spans="1:24" s="20" customFormat="1">
       <c r="A75" s="9" t="s">
         <v>87</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C75" s="21">
+      <c r="C75" s="20">
         <v>0.28399999999999997</v>
       </c>
-      <c r="D75" s="20">
+      <c r="D75" s="27">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="E75" s="20">
+      <c r="E75" s="27">
         <v>-1.47353470842518</v>
       </c>
-      <c r="J75" s="20">
+      <c r="J75" s="27">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="O75" s="20">
+      <c r="O75" s="27">
         <v>8.0890000000000004</v>
       </c>
-      <c r="P75" s="21">
+      <c r="P75" s="20">
         <v>7.9485854277214001</v>
       </c>
-      <c r="Q75" s="23"/>
       <c r="R75" s="19" t="s">
         <v>100</v>
       </c>
       <c r="T75" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="X75" s="21">
+      <c r="X75" s="20">
         <v>0.39100000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:24" s="21" customFormat="1">
+    <row r="76" spans="1:24" s="20" customFormat="1">
       <c r="A76" s="9" t="s">
         <v>88</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C76" s="21">
+      <c r="C76" s="20">
         <v>0.33400000000000002</v>
       </c>
-      <c r="D76" s="20">
+      <c r="D76" s="27">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="E76" s="20">
+      <c r="E76" s="27">
         <v>-1.99253212300414</v>
       </c>
-      <c r="J76" s="20">
+      <c r="J76" s="27">
         <v>2.0830000000081101</v>
       </c>
-      <c r="O76" s="20">
+      <c r="O76" s="27">
         <v>11.872999999999999</v>
       </c>
-      <c r="P76" s="21">
+      <c r="P76" s="20">
         <v>9.6077296533960403</v>
       </c>
-      <c r="Q76" s="23"/>
       <c r="R76" s="19" t="s">
         <v>100</v>
       </c>
       <c r="T76" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="X76" s="21">
+      <c r="X76" s="20">
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:24" s="21" customFormat="1">
+    <row r="77" spans="1:24" s="20" customFormat="1">
       <c r="A77" s="9" t="s">
         <v>89</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C77" s="21">
+      <c r="C77" s="20">
         <v>0.379</v>
       </c>
-      <c r="D77" s="20">
+      <c r="D77" s="27">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="E77" s="20">
+      <c r="E77" s="27">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="J77" s="20">
+      <c r="J77" s="27">
         <v>5.5389999999999997</v>
       </c>
-      <c r="O77" s="20">
+      <c r="O77" s="27">
         <v>14.304133448972699</v>
       </c>
-      <c r="P77" s="21">
+      <c r="P77" s="20">
         <v>8.8979999999999997</v>
       </c>
-      <c r="Q77" s="23"/>
       <c r="R77" s="19" t="s">
         <v>100</v>
       </c>
       <c r="T77" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="X77" s="21">
+      <c r="X77" s="20">
         <v>0.39100000000000001</v>
       </c>
     </row>
@@ -5251,171 +5240,171 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="28" customFormat="1">
-      <c r="A5" s="28">
+    <row r="5" spans="1:22" s="25" customFormat="1">
+      <c r="A5" s="25">
         <v>4</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="26">
         <v>0.1</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="25">
         <v>1.18</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="25">
         <v>2.2029999999999998</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="25">
         <v>2.2029999999999998</v>
       </c>
-      <c r="I5" s="28">
-        <v>0</v>
-      </c>
-      <c r="J5" s="28">
-        <v>0</v>
-      </c>
-      <c r="K5" s="28">
+      <c r="I5" s="25">
+        <v>0</v>
+      </c>
+      <c r="J5" s="25">
+        <v>0</v>
+      </c>
+      <c r="K5" s="25">
         <v>1.2795499999999999E-4</v>
       </c>
-      <c r="L5" s="28">
-        <v>0</v>
-      </c>
-      <c r="M5" s="28">
-        <v>0</v>
-      </c>
-      <c r="N5" s="28">
+      <c r="L5" s="25">
+        <v>0</v>
+      </c>
+      <c r="M5" s="25">
+        <v>0</v>
+      </c>
+      <c r="N5" s="25">
         <v>1.93</v>
       </c>
-      <c r="O5" s="28">
+      <c r="O5" s="25">
         <v>2.44</v>
       </c>
-      <c r="Q5" s="29">
+      <c r="Q5" s="26">
         <v>0.35967375000000001</v>
       </c>
-      <c r="R5" s="29" t="s">
+      <c r="R5" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="S5" s="29">
+      <c r="S5" s="26">
         <v>5</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="T5" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="U5" s="29">
+      <c r="U5" s="26">
         <v>3</v>
       </c>
-      <c r="V5" s="29" t="s">
+      <c r="V5" s="26" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="28" customFormat="1">
-      <c r="A6" s="28">
+    <row r="6" spans="1:22" s="25" customFormat="1">
+      <c r="A6" s="25">
         <v>5</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="26">
         <v>0.1</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="25">
         <v>1.127</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="25">
         <v>2.0979999999999999</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="25">
         <v>2.0979999999999999</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="25">
         <v>1.6766474999999999E-2</v>
       </c>
-      <c r="J6" s="28">
-        <v>0</v>
-      </c>
-      <c r="K6" s="28">
+      <c r="J6" s="25">
+        <v>0</v>
+      </c>
+      <c r="K6" s="25">
         <v>1.5726999999999999E-4</v>
       </c>
-      <c r="L6" s="28">
-        <v>0</v>
-      </c>
-      <c r="M6" s="28">
-        <v>0</v>
-      </c>
-      <c r="N6" s="28">
+      <c r="L6" s="25">
+        <v>0</v>
+      </c>
+      <c r="M6" s="25">
+        <v>0</v>
+      </c>
+      <c r="N6" s="25">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O6" s="28">
+      <c r="O6" s="25">
         <v>2.39</v>
       </c>
-      <c r="Q6" s="29">
+      <c r="Q6" s="26">
         <v>0.377942893</v>
       </c>
-      <c r="R6" s="29" t="s">
+      <c r="R6" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="S6" s="29">
+      <c r="S6" s="26">
         <v>5</v>
       </c>
-      <c r="T6" s="29" t="s">
+      <c r="T6" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="U6" s="29">
+      <c r="U6" s="26">
         <v>3</v>
       </c>
-      <c r="V6" s="29" t="s">
+      <c r="V6" s="26" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="28" customFormat="1">
-      <c r="A7" s="28">
+    <row r="7" spans="1:22" s="25" customFormat="1">
+      <c r="A7" s="25">
         <v>6</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="26">
         <v>0.1</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="25">
         <v>1.0980000000000001</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="25">
         <v>2.0550000000000002</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="25">
         <v>2.0550000000000002</v>
       </c>
-      <c r="I7" s="28">
-        <v>0</v>
-      </c>
-      <c r="J7" s="28">
-        <v>0</v>
-      </c>
-      <c r="K7" s="28">
+      <c r="I7" s="25">
+        <v>0</v>
+      </c>
+      <c r="J7" s="25">
+        <v>0</v>
+      </c>
+      <c r="K7" s="25">
         <v>1.3422099999999999E-4</v>
       </c>
-      <c r="L7" s="28">
-        <v>0</v>
-      </c>
-      <c r="M7" s="28">
-        <v>0</v>
-      </c>
-      <c r="N7" s="28">
+      <c r="L7" s="25">
+        <v>0</v>
+      </c>
+      <c r="M7" s="25">
+        <v>0</v>
+      </c>
+      <c r="N7" s="25">
         <v>1.97</v>
       </c>
-      <c r="O7" s="28">
+      <c r="O7" s="25">
         <v>2.1800000000000002</v>
       </c>
-      <c r="Q7" s="29">
+      <c r="Q7" s="26">
         <v>0.33645671399999999</v>
       </c>
-      <c r="R7" s="29" t="s">
+      <c r="R7" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="S7" s="29">
+      <c r="S7" s="26">
         <v>5</v>
       </c>
-      <c r="T7" s="29" t="s">
+      <c r="T7" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="U7" s="29">
+      <c r="U7" s="26">
         <v>3</v>
       </c>
-      <c r="V7" s="29" t="s">
+      <c r="V7" s="26" t="s">
         <v>104</v>
       </c>
     </row>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFD3D75D-BE95-5540-8EF8-954FC8521231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204D9642-9ED2-5146-9F94-D51ED0E73C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1440" windowWidth="26060" windowHeight="15220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11440" yWindow="2440" windowWidth="34960" windowHeight="18520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Supplementary File 1e vip" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$T$1:$T$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$Q$1:$Q$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supplementary File 1e vip'!$B$1:$B$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="126">
   <si>
     <t>sample</t>
   </si>
@@ -382,6 +382,36 @@
   </si>
   <si>
     <t>other_lab</t>
+  </si>
+  <si>
+    <t>REF</t>
+  </si>
+  <si>
+    <t>EtOH  20g/L</t>
+  </si>
+  <si>
+    <t>EtOH  40g/L</t>
+  </si>
+  <si>
+    <t>EtOH  60g/L</t>
+  </si>
+  <si>
+    <t>Osmo 0.2 M (NaCl)</t>
+  </si>
+  <si>
+    <t>Osmo 0.4 M (NaCl)</t>
+  </si>
+  <si>
+    <t>Osmo 0.6 M (NaCl)</t>
+  </si>
+  <si>
+    <t>Temp 33C</t>
+  </si>
+  <si>
+    <t>Temp 36C</t>
+  </si>
+  <si>
+    <t>Temp 38C</t>
   </si>
 </sst>
 </file>
@@ -958,7 +988,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1015,7 +1045,6 @@
     <xf numFmtId="0" fontId="18" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1024,6 +1053,24 @@
     <xf numFmtId="0" fontId="21" fillId="38" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1084,7 +1131,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1372,7 +1419,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1380,12 +1427,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8F22EE-2E06-6741-B451-D4EA064EAB2E}">
-  <dimension ref="A1:Z77"/>
+  <dimension ref="A1:Z87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="37.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="32.1640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" style="32" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -1417,7 +1464,7 @@
       <c r="B1" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="18" t="s">
         <v>91</v>
       </c>
       <c r="D1" s="12" t="s">
@@ -1497,6 +1544,7 @@
       <c r="B2" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="C2" s="18"/>
       <c r="Q2" s="11"/>
     </row>
     <row r="3" spans="1:26" s="12" customFormat="1">
@@ -1506,6 +1554,7 @@
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="C3" s="18"/>
       <c r="Q3" s="11"/>
     </row>
     <row r="4" spans="1:26" s="12" customFormat="1">
@@ -1515,6 +1564,7 @@
       <c r="B4" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="C4" s="18"/>
       <c r="Q4" s="11"/>
     </row>
     <row r="5" spans="1:26" s="13" customFormat="1">
@@ -1524,7 +1574,7 @@
       <c r="B5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="27">
         <v>0.42399999999999999</v>
       </c>
       <c r="D5" s="13">
@@ -1560,7 +1610,7 @@
       <c r="B6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="28">
         <v>0.05</v>
       </c>
       <c r="D6" s="16">
@@ -1628,7 +1678,7 @@
       <c r="B7" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="28">
         <v>0.05</v>
       </c>
       <c r="D7" s="16">
@@ -1696,7 +1746,7 @@
       <c r="B8" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="28">
         <v>0.05</v>
       </c>
       <c r="D8" s="16">
@@ -1764,7 +1814,7 @@
       <c r="B9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="28">
         <v>0.1</v>
       </c>
       <c r="D9" s="16">
@@ -1832,7 +1882,7 @@
       <c r="B10" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="28">
         <v>0.1</v>
       </c>
       <c r="D10" s="16">
@@ -1900,7 +1950,7 @@
       <c r="B11" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="28">
         <v>0.1</v>
       </c>
       <c r="D11" s="16">
@@ -1968,7 +2018,7 @@
       <c r="B12" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="28">
         <v>0.1</v>
       </c>
       <c r="D12" s="16">
@@ -2036,7 +2086,7 @@
       <c r="B13" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="28">
         <v>0.1</v>
       </c>
       <c r="D13" s="16">
@@ -2104,7 +2154,7 @@
       <c r="B14" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="28">
         <v>0.1</v>
       </c>
       <c r="D14" s="16">
@@ -2172,7 +2222,7 @@
       <c r="B15" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="28">
         <v>0.13</v>
       </c>
       <c r="D15" s="16">
@@ -2240,7 +2290,7 @@
       <c r="B16" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="28">
         <v>0.13</v>
       </c>
       <c r="D16" s="16">
@@ -2308,7 +2358,7 @@
       <c r="B17" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="28">
         <v>0.13</v>
       </c>
       <c r="D17" s="16">
@@ -2376,7 +2426,7 @@
       <c r="B18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="28">
         <v>0.18</v>
       </c>
       <c r="D18" s="16">
@@ -2444,7 +2494,7 @@
       <c r="B19" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="28">
         <v>0.18</v>
       </c>
       <c r="D19" s="16">
@@ -2512,7 +2562,7 @@
       <c r="B20" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="28">
         <v>0.18</v>
       </c>
       <c r="D20" s="16">
@@ -2580,7 +2630,7 @@
       <c r="B21" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="28">
         <v>0.3</v>
       </c>
       <c r="D21" s="16">
@@ -2648,7 +2698,7 @@
       <c r="B22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="28">
         <v>0.3</v>
       </c>
       <c r="D22" s="16">
@@ -2716,7 +2766,7 @@
       <c r="B23" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="28">
         <v>0.3</v>
       </c>
       <c r="D23" s="16">
@@ -2784,7 +2834,7 @@
       <c r="B24" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="28">
         <v>0.35</v>
       </c>
       <c r="D24" s="16">
@@ -2852,7 +2902,7 @@
       <c r="B25" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="28">
         <v>0.35</v>
       </c>
       <c r="D25" s="16">
@@ -2920,7 +2970,7 @@
       <c r="B26" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="28">
         <v>0.35</v>
       </c>
       <c r="D26" s="16">
@@ -2988,7 +3038,7 @@
       <c r="B27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="28">
         <v>0.1</v>
       </c>
       <c r="D27" s="16">
@@ -3059,7 +3109,7 @@
       <c r="B28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="28">
         <v>0.1</v>
       </c>
       <c r="D28" s="16">
@@ -3130,7 +3180,7 @@
       <c r="B29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="28">
         <v>0.1</v>
       </c>
       <c r="D29" s="16">
@@ -3201,7 +3251,7 @@
       <c r="B30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="28">
         <v>0.1</v>
       </c>
       <c r="D30" s="16">
@@ -3272,7 +3322,7 @@
       <c r="B31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="28">
         <v>0.1</v>
       </c>
       <c r="D31" s="16">
@@ -3343,7 +3393,7 @@
       <c r="B32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="28">
         <v>0.1</v>
       </c>
       <c r="D32" s="16">
@@ -3414,7 +3464,7 @@
       <c r="B33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="28">
         <v>0.1</v>
       </c>
       <c r="D33" s="16">
@@ -3482,7 +3532,7 @@
       <c r="B34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="28">
         <v>0.1</v>
       </c>
       <c r="D34" s="16">
@@ -3550,7 +3600,7 @@
       <c r="B35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="28">
         <v>0.1</v>
       </c>
       <c r="D35" s="16">
@@ -3618,7 +3668,7 @@
       <c r="B36" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="28">
         <v>0.1</v>
       </c>
       <c r="D36" s="16">
@@ -3686,7 +3736,7 @@
       <c r="B37" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="28">
         <v>0.1</v>
       </c>
       <c r="D37" s="16">
@@ -3754,7 +3804,7 @@
       <c r="B38" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="28">
         <v>0.1</v>
       </c>
       <c r="D38" s="16">
@@ -3822,7 +3872,7 @@
       <c r="B39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="28">
         <v>0.1</v>
       </c>
       <c r="D39" s="16">
@@ -3890,7 +3940,7 @@
       <c r="B40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="28">
         <v>0.1</v>
       </c>
       <c r="D40" s="16">
@@ -3958,7 +4008,7 @@
       <c r="B41" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="28">
         <v>0.1</v>
       </c>
       <c r="D41" s="16">
@@ -4026,7 +4076,7 @@
       <c r="B42" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="28">
         <v>0.1</v>
       </c>
       <c r="D42" s="16">
@@ -4094,7 +4144,7 @@
       <c r="B43" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="28">
         <v>0.1</v>
       </c>
       <c r="D43" s="16">
@@ -4162,7 +4212,7 @@
       <c r="B44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="28">
         <v>0.1</v>
       </c>
       <c r="D44" s="16">
@@ -4230,7 +4280,7 @@
       <c r="B45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="28">
         <v>0.1</v>
       </c>
       <c r="D45" s="16">
@@ -4298,7 +4348,7 @@
       <c r="B46" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="28">
         <v>0.1</v>
       </c>
       <c r="D46" s="16">
@@ -4366,7 +4416,7 @@
       <c r="B47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="28">
         <v>0.1</v>
       </c>
       <c r="D47" s="16">
@@ -4427,17 +4477,17 @@
         <v>0.42361575000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="23" customFormat="1">
+    <row r="48" spans="1:24" s="22" customFormat="1">
       <c r="A48" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="22">
+      <c r="C48" s="29">
         <v>0.1</v>
       </c>
-      <c r="Q48" s="24"/>
+      <c r="Q48" s="23"/>
     </row>
     <row r="49" spans="1:17" s="7" customFormat="1">
       <c r="A49" s="4" t="s">
@@ -4520,7 +4570,7 @@
       <c r="B53" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="18">
         <v>0.1</v>
       </c>
       <c r="Q53" s="11"/>
@@ -4532,7 +4582,7 @@
       <c r="B54" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="18">
         <v>0.1</v>
       </c>
       <c r="E54" s="18"/>
@@ -4545,7 +4595,7 @@
       <c r="B55" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="18">
         <v>0.1</v>
       </c>
       <c r="Q55" s="11"/>
@@ -4557,7 +4607,7 @@
       <c r="B56" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="18">
         <v>0.1</v>
       </c>
       <c r="Q56" s="11"/>
@@ -4569,6 +4619,7 @@
       <c r="B57" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C57" s="18"/>
       <c r="Q57" s="11"/>
     </row>
     <row r="58" spans="1:17" s="12" customFormat="1">
@@ -4578,6 +4629,7 @@
       <c r="B58" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C58" s="18"/>
       <c r="Q58" s="11"/>
     </row>
     <row r="59" spans="1:17" s="12" customFormat="1">
@@ -4587,6 +4639,7 @@
       <c r="B59" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C59" s="18"/>
       <c r="Q59" s="11"/>
     </row>
     <row r="60" spans="1:17" s="12" customFormat="1">
@@ -4596,6 +4649,7 @@
       <c r="B60" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C60" s="18"/>
       <c r="Q60" s="11"/>
     </row>
     <row r="61" spans="1:17" s="12" customFormat="1">
@@ -4605,6 +4659,7 @@
       <c r="B61" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C61" s="18"/>
       <c r="Q61" s="11"/>
     </row>
     <row r="62" spans="1:17" s="12" customFormat="1">
@@ -4614,6 +4669,7 @@
       <c r="B62" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C62" s="18"/>
       <c r="Q62" s="11"/>
     </row>
     <row r="63" spans="1:17" s="12" customFormat="1">
@@ -4623,6 +4679,7 @@
       <c r="B63" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C63" s="18"/>
       <c r="Q63" s="11"/>
     </row>
     <row r="64" spans="1:17" s="12" customFormat="1">
@@ -4632,6 +4689,7 @@
       <c r="B64" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C64" s="18"/>
       <c r="Q64" s="11"/>
     </row>
     <row r="65" spans="1:24" s="12" customFormat="1">
@@ -4641,6 +4699,7 @@
       <c r="B65" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C65" s="18"/>
       <c r="Q65" s="11"/>
     </row>
     <row r="66" spans="1:24" s="12" customFormat="1">
@@ -4650,6 +4709,7 @@
       <c r="B66" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C66" s="18"/>
       <c r="Q66" s="11"/>
     </row>
     <row r="67" spans="1:24" s="12" customFormat="1">
@@ -4659,6 +4719,7 @@
       <c r="B67" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C67" s="18"/>
       <c r="Q67" s="11"/>
     </row>
     <row r="68" spans="1:24" s="12" customFormat="1">
@@ -4668,6 +4729,7 @@
       <c r="B68" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="C68" s="18"/>
       <c r="Q68" s="11"/>
     </row>
     <row r="69" spans="1:24" s="19" customFormat="1">
@@ -4677,19 +4739,19 @@
       <c r="B69" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C69" s="19">
+      <c r="C69" s="30">
         <v>2.7E-2</v>
       </c>
-      <c r="D69" s="27">
+      <c r="D69" s="26">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="E69" s="27">
+      <c r="E69" s="26">
         <v>-0.151308114750691</v>
       </c>
-      <c r="J69" s="27">
-        <v>0</v>
-      </c>
-      <c r="O69" s="27">
+      <c r="J69" s="26">
+        <v>0</v>
+      </c>
+      <c r="O69" s="26">
         <v>0.878</v>
       </c>
       <c r="P69" s="20">
@@ -4712,19 +4774,19 @@
       <c r="B70" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C70" s="20">
+      <c r="C70" s="31">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="D70" s="27">
+      <c r="D70" s="26">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="E70" s="27">
+      <c r="E70" s="26">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="J70" s="27">
-        <v>0</v>
-      </c>
-      <c r="O70" s="27">
+      <c r="J70" s="26">
+        <v>0</v>
+      </c>
+      <c r="O70" s="26">
         <v>1.458</v>
       </c>
       <c r="P70" s="20">
@@ -4747,19 +4809,19 @@
       <c r="B71" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C71" s="20">
+      <c r="C71" s="31">
         <v>0.10199999999999999</v>
       </c>
-      <c r="D71" s="27">
+      <c r="D71" s="26">
         <v>-1.171</v>
       </c>
-      <c r="E71" s="27">
+      <c r="E71" s="26">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="J71" s="27">
-        <v>0</v>
-      </c>
-      <c r="O71" s="27">
+      <c r="J71" s="26">
+        <v>0</v>
+      </c>
+      <c r="O71" s="26">
         <v>2.5470000000000002</v>
       </c>
       <c r="P71" s="20">
@@ -4782,19 +4844,19 @@
       <c r="B72" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C72" s="20">
+      <c r="C72" s="31">
         <v>0.152</v>
       </c>
-      <c r="D72" s="27">
+      <c r="D72" s="26">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="E72" s="27">
+      <c r="E72" s="26">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="J72" s="27">
-        <v>0</v>
-      </c>
-      <c r="O72" s="27">
+      <c r="J72" s="26">
+        <v>0</v>
+      </c>
+      <c r="O72" s="26">
         <v>3.81518914277475</v>
       </c>
       <c r="P72" s="20">
@@ -4817,19 +4879,19 @@
       <c r="B73" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C73" s="20">
+      <c r="C73" s="31">
         <v>0.214</v>
       </c>
-      <c r="D73" s="27">
+      <c r="D73" s="26">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="E73" s="27">
+      <c r="E73" s="26">
         <v>-1.22567508688439</v>
       </c>
-      <c r="J73" s="27">
+      <c r="J73" s="26">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="O73" s="27">
+      <c r="O73" s="26">
         <v>5.5949999999999998</v>
       </c>
       <c r="P73" s="20">
@@ -4852,19 +4914,19 @@
       <c r="B74" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C74" s="20">
+      <c r="C74" s="31">
         <v>0.254</v>
       </c>
-      <c r="D74" s="27">
+      <c r="D74" s="26">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="E74" s="27">
+      <c r="E74" s="26">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="J74" s="27">
+      <c r="J74" s="26">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="O74" s="27">
+      <c r="O74" s="26">
         <v>6.484</v>
       </c>
       <c r="P74" s="20">
@@ -4887,19 +4949,19 @@
       <c r="B75" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C75" s="20">
+      <c r="C75" s="31">
         <v>0.28399999999999997</v>
       </c>
-      <c r="D75" s="27">
+      <c r="D75" s="26">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="E75" s="27">
+      <c r="E75" s="26">
         <v>-1.47353470842518</v>
       </c>
-      <c r="J75" s="27">
+      <c r="J75" s="26">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="O75" s="27">
+      <c r="O75" s="26">
         <v>8.0890000000000004</v>
       </c>
       <c r="P75" s="20">
@@ -4922,19 +4984,19 @@
       <c r="B76" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C76" s="20">
+      <c r="C76" s="31">
         <v>0.33400000000000002</v>
       </c>
-      <c r="D76" s="27">
+      <c r="D76" s="26">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="E76" s="27">
+      <c r="E76" s="26">
         <v>-1.99253212300414</v>
       </c>
-      <c r="J76" s="27">
+      <c r="J76" s="26">
         <v>2.0830000000081101</v>
       </c>
-      <c r="O76" s="27">
+      <c r="O76" s="26">
         <v>11.872999999999999</v>
       </c>
       <c r="P76" s="20">
@@ -4957,19 +5019,19 @@
       <c r="B77" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C77" s="20">
+      <c r="C77" s="31">
         <v>0.379</v>
       </c>
-      <c r="D77" s="27">
+      <c r="D77" s="26">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="E77" s="27">
+      <c r="E77" s="26">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="J77" s="27">
+      <c r="J77" s="26">
         <v>5.5389999999999997</v>
       </c>
-      <c r="O77" s="27">
+      <c r="O77" s="26">
         <v>14.304133448972699</v>
       </c>
       <c r="P77" s="20">
@@ -4983,6 +5045,116 @@
       </c>
       <c r="X77" s="20">
         <v>0.39100000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24">
+      <c r="A78" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C78" s="18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24">
+      <c r="A79" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C79" s="18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24">
+      <c r="A80" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C80" s="18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C81" s="18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C82" s="18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C83" s="18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C84" s="18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C85" s="18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C86" s="18">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C87" s="18">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -5240,171 +5412,171 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="25" customFormat="1">
-      <c r="A5" s="25">
+    <row r="5" spans="1:22" s="24" customFormat="1">
+      <c r="A5" s="24">
         <v>4</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="25">
         <v>0.1</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="24">
         <v>1.18</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="24">
         <v>2.2029999999999998</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="24">
         <v>2.2029999999999998</v>
       </c>
-      <c r="I5" s="25">
-        <v>0</v>
-      </c>
-      <c r="J5" s="25">
-        <v>0</v>
-      </c>
-      <c r="K5" s="25">
+      <c r="I5" s="24">
+        <v>0</v>
+      </c>
+      <c r="J5" s="24">
+        <v>0</v>
+      </c>
+      <c r="K5" s="24">
         <v>1.2795499999999999E-4</v>
       </c>
-      <c r="L5" s="25">
-        <v>0</v>
-      </c>
-      <c r="M5" s="25">
-        <v>0</v>
-      </c>
-      <c r="N5" s="25">
+      <c r="L5" s="24">
+        <v>0</v>
+      </c>
+      <c r="M5" s="24">
+        <v>0</v>
+      </c>
+      <c r="N5" s="24">
         <v>1.93</v>
       </c>
-      <c r="O5" s="25">
+      <c r="O5" s="24">
         <v>2.44</v>
       </c>
-      <c r="Q5" s="26">
+      <c r="Q5" s="25">
         <v>0.35967375000000001</v>
       </c>
-      <c r="R5" s="26" t="s">
+      <c r="R5" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="S5" s="26">
+      <c r="S5" s="25">
         <v>5</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="U5" s="26">
+      <c r="U5" s="25">
         <v>3</v>
       </c>
-      <c r="V5" s="26" t="s">
+      <c r="V5" s="25" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="25" customFormat="1">
-      <c r="A6" s="25">
+    <row r="6" spans="1:22" s="24" customFormat="1">
+      <c r="A6" s="24">
         <v>5</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="25">
         <v>0.1</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="24">
         <v>1.127</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="24">
         <v>2.0979999999999999</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="24">
         <v>2.0979999999999999</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <v>1.6766474999999999E-2</v>
       </c>
-      <c r="J6" s="25">
-        <v>0</v>
-      </c>
-      <c r="K6" s="25">
+      <c r="J6" s="24">
+        <v>0</v>
+      </c>
+      <c r="K6" s="24">
         <v>1.5726999999999999E-4</v>
       </c>
-      <c r="L6" s="25">
-        <v>0</v>
-      </c>
-      <c r="M6" s="25">
-        <v>0</v>
-      </c>
-      <c r="N6" s="25">
+      <c r="L6" s="24">
+        <v>0</v>
+      </c>
+      <c r="M6" s="24">
+        <v>0</v>
+      </c>
+      <c r="N6" s="24">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O6" s="25">
+      <c r="O6" s="24">
         <v>2.39</v>
       </c>
-      <c r="Q6" s="26">
+      <c r="Q6" s="25">
         <v>0.377942893</v>
       </c>
-      <c r="R6" s="26" t="s">
+      <c r="R6" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="S6" s="26">
+      <c r="S6" s="25">
         <v>5</v>
       </c>
-      <c r="T6" s="26" t="s">
+      <c r="T6" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="U6" s="26">
+      <c r="U6" s="25">
         <v>3</v>
       </c>
-      <c r="V6" s="26" t="s">
+      <c r="V6" s="25" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="25" customFormat="1">
-      <c r="A7" s="25">
+    <row r="7" spans="1:22" s="24" customFormat="1">
+      <c r="A7" s="24">
         <v>6</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="25">
         <v>0.1</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="24">
         <v>1.0980000000000001</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="24">
         <v>2.0550000000000002</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="24">
         <v>2.0550000000000002</v>
       </c>
-      <c r="I7" s="25">
-        <v>0</v>
-      </c>
-      <c r="J7" s="25">
-        <v>0</v>
-      </c>
-      <c r="K7" s="25">
+      <c r="I7" s="24">
+        <v>0</v>
+      </c>
+      <c r="J7" s="24">
+        <v>0</v>
+      </c>
+      <c r="K7" s="24">
         <v>1.3422099999999999E-4</v>
       </c>
-      <c r="L7" s="25">
-        <v>0</v>
-      </c>
-      <c r="M7" s="25">
-        <v>0</v>
-      </c>
-      <c r="N7" s="25">
+      <c r="L7" s="24">
+        <v>0</v>
+      </c>
+      <c r="M7" s="24">
+        <v>0</v>
+      </c>
+      <c r="N7" s="24">
         <v>1.97</v>
       </c>
-      <c r="O7" s="25">
+      <c r="O7" s="24">
         <v>2.1800000000000002</v>
       </c>
-      <c r="Q7" s="26">
+      <c r="Q7" s="25">
         <v>0.33645671399999999</v>
       </c>
-      <c r="R7" s="26" t="s">
+      <c r="R7" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="S7" s="26">
+      <c r="S7" s="25">
         <v>5</v>
       </c>
-      <c r="T7" s="26" t="s">
+      <c r="T7" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="U7" s="26">
+      <c r="U7" s="25">
         <v>3</v>
       </c>
-      <c r="V7" s="26" t="s">
+      <c r="V7" s="25" t="s">
         <v>104</v>
       </c>
     </row>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/proteomics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/large_scale_yeast_proteomics_analysis/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204D9642-9ED2-5146-9F94-D51ED0E73C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E31C51E-95C6-5F4F-9BCB-C4C959DD309C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11440" yWindow="2440" windowWidth="34960" windowHeight="18520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8360" yWindow="1660" windowWidth="34960" windowHeight="18520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Supplementary File 1e vip" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$Q$1:$Q$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AC$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supplementary File 1e vip'!$B$1:$B$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="187">
   <si>
     <t>sample</t>
   </si>
@@ -412,6 +412,202 @@
   </si>
   <si>
     <t>Temp 38C</t>
+  </si>
+  <si>
+    <t>maltose(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>oleate(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>fructose(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>sucrose(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>trehalose(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>lactate(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>acetate(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>pryuvate(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>glycerol(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>galactose(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>raffinose(mmol/gDW)</t>
+  </si>
+  <si>
+    <t>growth_mode</t>
+  </si>
+  <si>
+    <t>batch</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t>S5</t>
+  </si>
+  <si>
+    <t>S6</t>
+  </si>
+  <si>
+    <t>S7</t>
+  </si>
+  <si>
+    <t>S8</t>
+  </si>
+  <si>
+    <t>S9</t>
+  </si>
+  <si>
+    <t>S10</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>S19</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>S25</t>
+  </si>
+  <si>
+    <t>S26</t>
+  </si>
+  <si>
+    <t>S27</t>
+  </si>
+  <si>
+    <t>S28</t>
+  </si>
+  <si>
+    <t>S29</t>
+  </si>
+  <si>
+    <t>S30</t>
+  </si>
+  <si>
+    <t>C-lim rep1 prot (fmol mgDW-1)</t>
+  </si>
+  <si>
+    <t>C-lim rep2 prot (fmol mgDW-1)</t>
+  </si>
+  <si>
+    <t>C/N=115 rep1 prot (fmol mgDW-1)</t>
+  </si>
+  <si>
+    <t>C/N=115 rep2 prot (fmol mgDW-1)</t>
+  </si>
+  <si>
+    <t>C/N=30 rep1 prot (fmol mgDW-1)</t>
+  </si>
+  <si>
+    <t>C/N=30 rep2 prot (fmol mgDW-1)</t>
+  </si>
+  <si>
+    <t>C/N=50 rep1 prot (fmol mgDW-1)</t>
+  </si>
+  <si>
+    <t>C/N=50 rep2 prot (fmol mgDW-1)</t>
+  </si>
+  <si>
+    <t>chemostat</t>
+  </si>
+  <si>
+    <t>Simultation_with_ETFL</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>growth_media</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The yeast minimal media was comprised of yeast nitrogenous base with amino acids, ammonium sulfate, and the appropriate carbon </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>source, which containing either 2% glucose, 2% maltose, 0.125% oleate, 2% fructose, 2% sucrose, 2% trehalose, 2% lactate, 2% acetate, 2% pyruvate and 2% glycerol as the carbon source.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">minimal mineral medium </t>
+  </si>
+  <si>
+    <t xml:space="preserve">minimal mineral medium with the addition of the following amino acids: 0.19 g/L L-arginine; 0.4 g/L L-aspartate; 1.26 g/L L-glutamate; 0.13 g/L L-glycine; 0.14 g/L L-histidine; 0.29 g/L L-isoleucine; 0.4 g/L L-leucine; 0.44 g/L L-lysine; 0.108 g/L L-methionine; 0.2 g/L L-phenylalanine; 0.22 g/L L-threonine; 0.04 g/L L-tryptophan; 0.052 g/L L-tyro- sine; 0.38 g/L L-valine. </t>
+  </si>
+  <si>
+    <t>minimal mineral medium；additionally contained 0.0104 g/L ergosterol and 0.42 g/L Tween80 that had been dissolved in pure ethanol. Subsequently, medium used for anaerobic conditions contained 2.85 g/L ethanol</t>
+  </si>
+  <si>
+    <t>minimal mineral medium with the addition of the following amino acids: 0.19 g/L L-arginine; 0.4 g/L L-aspartate; 1.26 g/L L-glutamate; 0.13 g/L L-glycine; 0.14 g/L L-histidine; 0.29 g/L L-isoleucine; 0.4 g/L L-leucine; 0.44 g/L L-lysine; 0.108 g/L L-methionine; 0.2 g/L L-phenylalanine; 0.22 g/L L-threonine; 0.04 g/L L-tryptophan; 0.052 g/L L-tyro- sine; 0.38 g/L L-valine. additionally contained 0.0104 g/L ergosterol and 0.42 g/L Tween80 that had been dissolved in pure ethanol. Subsequently, medium used for anaerobic conditions contained 2.85 g/L ethanol</t>
   </si>
 </sst>
 </file>
@@ -421,7 +617,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -595,8 +791,14 @@
       <color rgb="FF000000"/>
       <name val="Times Roman"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -812,6 +1014,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -988,13 +1202,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1069,8 +1280,28 @@
     <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="40" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1131,7 +1362,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1419,7 +1650,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1427,3738 +1658,5333 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8F22EE-2E06-6741-B451-D4EA064EAB2E}">
-  <dimension ref="A1:Z87"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AC137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="37.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="32.1640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21.6640625" style="32" customWidth="1"/>
-    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23" customWidth="1"/>
+    <col min="1" max="1" width="29.6640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="32.1640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="42" style="10" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28" style="10" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="26" style="17" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="23" style="11" customWidth="1"/>
+    <col min="29" max="16384" width="10.83203125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="12" customFormat="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:29">
+      <c r="A1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="N1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="O1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="P1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="Q1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="R1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="S1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="T1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="U1" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="V1" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="W1" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="X1" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="Y1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="Z1" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="AA1" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="AB1" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="AC1" s="11" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="12" customFormat="1">
+    <row r="2" spans="1:29" hidden="1">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="Q2" s="11"/>
-    </row>
-    <row r="3" spans="1:26" s="12" customFormat="1">
+      <c r="C2" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="U2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="AA2" s="11"/>
+    </row>
+    <row r="3" spans="1:29" hidden="1">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="Q3" s="11"/>
-    </row>
-    <row r="4" spans="1:26" s="12" customFormat="1">
+      <c r="C3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="U3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="AA3" s="11"/>
+    </row>
+    <row r="4" spans="1:29" hidden="1">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="Q4" s="11"/>
-    </row>
-    <row r="5" spans="1:26" s="13" customFormat="1">
-      <c r="A5" s="10" t="s">
+      <c r="C4" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="U4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="AA4" s="11"/>
+    </row>
+    <row r="5" spans="1:29" s="12" customFormat="1">
+      <c r="A5" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F5" s="26">
         <v>0.42399999999999999</v>
       </c>
-      <c r="D5" s="13">
+      <c r="G5" s="12">
         <v>18.79</v>
       </c>
-      <c r="J5" s="13">
+      <c r="M5" s="12">
         <v>26.97</v>
       </c>
-      <c r="K5" s="13">
+      <c r="N5" s="12">
         <v>0.56599999999999995</v>
       </c>
-      <c r="L5" s="13">
+      <c r="O5" s="12">
         <v>0.16300000000000001</v>
       </c>
-      <c r="M5" s="13">
+      <c r="P5" s="12">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="N5" s="13">
+      <c r="Q5" s="12">
         <v>1.4690000000000001</v>
       </c>
-      <c r="O5" s="13">
+      <c r="R5" s="12">
         <v>24.501999999999999</v>
       </c>
-      <c r="P5" s="13">
+      <c r="S5" s="12">
         <v>2.919</v>
       </c>
-      <c r="Q5" s="14"/>
-    </row>
-    <row r="6" spans="1:26" s="15" customFormat="1">
-      <c r="A6" s="3" t="s">
+      <c r="T5" s="13"/>
+      <c r="U5" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="W5" s="13"/>
+      <c r="AA5" s="26"/>
+    </row>
+    <row r="6" spans="1:29" s="14" customFormat="1">
+      <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F6" s="27">
         <v>0.05</v>
       </c>
-      <c r="D6" s="16">
+      <c r="G6" s="15">
         <v>0.82299999999999995</v>
       </c>
-      <c r="E6" s="16">
+      <c r="H6" s="15">
         <v>0.13100000000000001</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16">
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15">
         <v>0.13100000000000001</v>
       </c>
-      <c r="J6" s="16">
-        <v>0</v>
-      </c>
-      <c r="K6" s="16">
-        <v>0</v>
-      </c>
-      <c r="L6" s="16">
+      <c r="M6" s="15">
+        <v>0</v>
+      </c>
+      <c r="N6" s="15">
+        <v>0</v>
+      </c>
+      <c r="O6" s="15">
         <v>7.2308500000000005E-4</v>
       </c>
-      <c r="M6" s="16">
-        <v>0</v>
-      </c>
-      <c r="N6" s="16">
+      <c r="P6" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="15">
         <v>4.0285879999999996E-3</v>
       </c>
-      <c r="O6" s="16">
+      <c r="R6" s="15">
         <v>2.4449999999999998</v>
       </c>
-      <c r="P6" s="16">
+      <c r="S6" s="15">
         <v>2.3620000000000001</v>
       </c>
-      <c r="Q6" s="17">
+      <c r="T6" s="16">
         <v>7.5</v>
       </c>
-      <c r="R6" s="15" t="s">
+      <c r="U6" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S6" s="15">
+      <c r="V6" s="14">
         <v>0.5</v>
       </c>
-      <c r="T6" s="15" t="s">
+      <c r="W6" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U6" s="15">
+      <c r="X6" s="14">
         <v>30</v>
       </c>
-      <c r="V6" s="15" t="s">
+      <c r="Y6" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W6" s="15">
+      <c r="Z6" s="14">
         <v>2.1734E-2</v>
       </c>
-      <c r="X6" s="15">
+      <c r="AA6" s="27">
         <v>0.27251471399999999</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="15" customFormat="1">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:29" s="14" customFormat="1">
+      <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7" s="27">
         <v>0.05</v>
       </c>
-      <c r="D7" s="16">
+      <c r="G7" s="15">
         <v>0.70399999999999996</v>
       </c>
-      <c r="E7" s="16">
+      <c r="H7" s="15">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16">
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="J7" s="16">
-        <v>0</v>
-      </c>
-      <c r="K7" s="16">
-        <v>0</v>
-      </c>
-      <c r="L7" s="16">
+      <c r="M7" s="15">
+        <v>0</v>
+      </c>
+      <c r="N7" s="15">
+        <v>0</v>
+      </c>
+      <c r="O7" s="15">
         <v>1.6583900000000001E-4</v>
       </c>
-      <c r="M7" s="16">
-        <v>0</v>
-      </c>
-      <c r="N7" s="16">
+      <c r="P7" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="15">
         <v>6.6796169999999997E-3</v>
       </c>
-      <c r="O7" s="16">
+      <c r="R7" s="15">
         <v>2.105</v>
       </c>
-      <c r="P7" s="16">
+      <c r="S7" s="15">
         <v>2.2759999999999998</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="T7" s="16">
         <v>7.5</v>
       </c>
-      <c r="R7" s="15" t="s">
+      <c r="U7" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S7" s="15">
+      <c r="V7" s="14">
         <v>0.5</v>
       </c>
-      <c r="T7" s="15" t="s">
+      <c r="W7" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U7" s="15">
+      <c r="X7" s="14">
         <v>30</v>
       </c>
-      <c r="V7" s="15" t="s">
+      <c r="Y7" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W7" s="15">
+      <c r="Z7" s="14">
         <v>2.4941000000000001E-2</v>
       </c>
-      <c r="X7" s="15">
+      <c r="AA7" s="27">
         <v>0.25082010700000001</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="15" customFormat="1">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:29" s="14" customFormat="1">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F8" s="27">
         <v>0.05</v>
       </c>
-      <c r="D8" s="16">
+      <c r="G8" s="15">
         <v>0.76800000000000002</v>
       </c>
-      <c r="E8" s="16">
+      <c r="H8" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16">
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="J8" s="16">
-        <v>0</v>
-      </c>
-      <c r="K8" s="16">
-        <v>0</v>
-      </c>
-      <c r="L8" s="16">
+      <c r="M8" s="15">
+        <v>0</v>
+      </c>
+      <c r="N8" s="15">
+        <v>0</v>
+      </c>
+      <c r="O8" s="15">
         <v>3.81541E-4</v>
       </c>
-      <c r="M8" s="16">
-        <v>0</v>
-      </c>
-      <c r="N8" s="16">
+      <c r="P8" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="15">
         <v>9.7823159999999992E-3</v>
       </c>
-      <c r="O8" s="16">
+      <c r="R8" s="15">
         <v>2.383</v>
       </c>
-      <c r="P8" s="16">
+      <c r="S8" s="15">
         <v>1.6240000000000001</v>
       </c>
-      <c r="Q8" s="17">
+      <c r="T8" s="16">
         <v>7.5</v>
       </c>
-      <c r="R8" s="15" t="s">
+      <c r="U8" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S8" s="15">
+      <c r="V8" s="14">
         <v>0.5</v>
       </c>
-      <c r="T8" s="15" t="s">
+      <c r="W8" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U8" s="15">
+      <c r="X8" s="14">
         <v>30</v>
       </c>
-      <c r="V8" s="15" t="s">
+      <c r="Y8" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W8" s="15">
+      <c r="Z8" s="14">
         <v>2.5831E-2</v>
       </c>
-      <c r="X8" s="15">
+      <c r="AA8" s="27">
         <v>0.26109650000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="15" customFormat="1">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:29" s="14" customFormat="1">
+      <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F9" s="27">
         <v>0.1</v>
       </c>
-      <c r="D9" s="16">
+      <c r="G9" s="15">
         <v>1.18</v>
       </c>
-      <c r="E9" s="16">
+      <c r="H9" s="15">
         <v>2.2029999999999998</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16">
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15">
         <v>2.2029999999999998</v>
       </c>
-      <c r="J9" s="16">
-        <v>0</v>
-      </c>
-      <c r="K9" s="16">
-        <v>0</v>
-      </c>
-      <c r="L9" s="16">
+      <c r="M9" s="15">
+        <v>0</v>
+      </c>
+      <c r="N9" s="15">
+        <v>0</v>
+      </c>
+      <c r="O9" s="15">
         <v>1.2795499999999999E-4</v>
       </c>
-      <c r="M9" s="16">
-        <v>0</v>
-      </c>
-      <c r="N9" s="16">
-        <v>0</v>
-      </c>
-      <c r="O9" s="16">
+      <c r="P9" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>0</v>
+      </c>
+      <c r="R9" s="15">
         <v>1.93</v>
       </c>
-      <c r="P9" s="16">
+      <c r="S9" s="15">
         <v>2.44</v>
       </c>
-      <c r="Q9" s="17">
+      <c r="T9" s="16">
         <v>7.5</v>
       </c>
-      <c r="R9" s="15" t="s">
+      <c r="U9" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S9" s="15">
+      <c r="V9" s="14">
         <v>5</v>
       </c>
-      <c r="T9" s="15" t="s">
+      <c r="W9" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U9" s="15">
+      <c r="X9" s="14">
         <v>3</v>
       </c>
-      <c r="V9" s="15" t="s">
+      <c r="Y9" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W9" s="15">
+      <c r="Z9" s="14">
         <v>5.3443999999999998E-2</v>
       </c>
-      <c r="X9" s="15">
+      <c r="AA9" s="27">
         <v>0.35967375000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="15" customFormat="1">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:29" s="14" customFormat="1">
+      <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" s="27">
         <v>0.1</v>
       </c>
-      <c r="D10" s="16">
+      <c r="G10" s="15">
         <v>1.127</v>
       </c>
-      <c r="E10" s="16">
+      <c r="H10" s="15">
         <v>2.0979999999999999</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16">
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15">
         <v>2.0979999999999999</v>
       </c>
-      <c r="J10" s="16">
+      <c r="M10" s="15">
         <v>1.6766474999999999E-2</v>
       </c>
-      <c r="K10" s="16">
-        <v>0</v>
-      </c>
-      <c r="L10" s="16">
+      <c r="N10" s="15">
+        <v>0</v>
+      </c>
+      <c r="O10" s="15">
         <v>1.5726999999999999E-4</v>
       </c>
-      <c r="M10" s="16">
-        <v>0</v>
-      </c>
-      <c r="N10" s="16">
-        <v>0</v>
-      </c>
-      <c r="O10" s="16">
+      <c r="P10" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>0</v>
+      </c>
+      <c r="R10" s="15">
         <v>2.0699999999999998</v>
       </c>
-      <c r="P10" s="16">
+      <c r="S10" s="15">
         <v>2.39</v>
       </c>
-      <c r="Q10" s="17">
+      <c r="T10" s="16">
         <v>7.5</v>
       </c>
-      <c r="R10" s="15" t="s">
+      <c r="U10" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S10" s="15">
+      <c r="V10" s="14">
         <v>5</v>
       </c>
-      <c r="T10" s="15" t="s">
+      <c r="W10" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U10" s="15">
+      <c r="X10" s="14">
         <v>3</v>
       </c>
-      <c r="V10" s="15" t="s">
+      <c r="Y10" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W10" s="15">
+      <c r="Z10" s="14">
         <v>5.0594E-2</v>
       </c>
-      <c r="X10" s="15">
+      <c r="AA10" s="27">
         <v>0.377942893</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="15" customFormat="1">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:29" s="14" customFormat="1">
+      <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11" s="27">
         <v>0.1</v>
       </c>
-      <c r="D11" s="16">
+      <c r="G11" s="15">
         <v>1.0980000000000001</v>
       </c>
-      <c r="E11" s="16">
+      <c r="H11" s="15">
         <v>2.0550000000000002</v>
       </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16">
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15">
         <v>2.0550000000000002</v>
       </c>
-      <c r="J11" s="16">
-        <v>0</v>
-      </c>
-      <c r="K11" s="16">
-        <v>0</v>
-      </c>
-      <c r="L11" s="16">
+      <c r="M11" s="15">
+        <v>0</v>
+      </c>
+      <c r="N11" s="15">
+        <v>0</v>
+      </c>
+      <c r="O11" s="15">
         <v>1.3422099999999999E-4</v>
       </c>
-      <c r="M11" s="16">
-        <v>0</v>
-      </c>
-      <c r="N11" s="16">
-        <v>0</v>
-      </c>
-      <c r="O11" s="16">
+      <c r="P11" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>0</v>
+      </c>
+      <c r="R11" s="15">
         <v>1.97</v>
       </c>
-      <c r="P11" s="16">
+      <c r="S11" s="15">
         <v>2.1800000000000002</v>
       </c>
-      <c r="Q11" s="17">
+      <c r="T11" s="16">
         <v>7.5</v>
       </c>
-      <c r="R11" s="15" t="s">
+      <c r="U11" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S11" s="15">
+      <c r="V11" s="14">
         <v>5</v>
       </c>
-      <c r="T11" s="15" t="s">
+      <c r="W11" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U11" s="15">
+      <c r="X11" s="14">
         <v>3</v>
       </c>
-      <c r="V11" s="15" t="s">
+      <c r="Y11" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W11" s="15">
+      <c r="Z11" s="14">
         <v>4.5962000000000003E-2</v>
       </c>
-      <c r="X11" s="15">
+      <c r="AA11" s="27">
         <v>0.33645671399999999</v>
       </c>
     </row>
-    <row r="12" spans="1:26" s="15" customFormat="1">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:29" s="14" customFormat="1">
+      <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F12" s="27">
         <v>0.1</v>
       </c>
-      <c r="D12" s="16">
+      <c r="G12" s="15">
         <v>1.51</v>
       </c>
-      <c r="E12" s="16">
+      <c r="H12" s="15">
         <v>0.308</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16">
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15">
         <v>0.308</v>
       </c>
-      <c r="J12" s="16">
-        <v>0</v>
-      </c>
-      <c r="K12" s="16">
+      <c r="M12" s="15">
+        <v>0</v>
+      </c>
+      <c r="N12" s="15">
         <v>7.5614127000000003E-2</v>
       </c>
-      <c r="L12" s="16">
+      <c r="O12" s="15">
         <v>1.7982350000000001E-2</v>
       </c>
-      <c r="M12" s="16">
-        <v>0</v>
-      </c>
-      <c r="N12" s="16">
-        <v>0</v>
-      </c>
-      <c r="O12" s="16">
+      <c r="P12" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>0</v>
+      </c>
+      <c r="R12" s="15">
         <v>3.4660000000000002</v>
       </c>
-      <c r="P12" s="16">
+      <c r="S12" s="15">
         <v>3.6160000000000001</v>
       </c>
-      <c r="Q12" s="17">
+      <c r="T12" s="16">
         <v>7.5</v>
       </c>
-      <c r="R12" s="15" t="s">
+      <c r="U12" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S12" s="15">
+      <c r="V12" s="14">
         <v>0.5</v>
       </c>
-      <c r="T12" s="15" t="s">
+      <c r="W12" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U12" s="15">
+      <c r="X12" s="14">
         <v>30</v>
       </c>
-      <c r="V12" s="15" t="s">
+      <c r="Y12" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="W12" s="15">
+      <c r="Z12" s="14">
         <v>2.2624999999999999E-2</v>
       </c>
-      <c r="X12" s="15">
+      <c r="AA12" s="27">
         <v>0.209333929</v>
       </c>
     </row>
-    <row r="13" spans="1:26" s="15" customFormat="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:29" s="14" customFormat="1">
+      <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13" s="27">
         <v>0.1</v>
       </c>
-      <c r="D13" s="16">
+      <c r="G13" s="15">
         <v>1.5109999999999999</v>
       </c>
-      <c r="E13" s="16">
+      <c r="H13" s="15">
         <v>0.308</v>
       </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16">
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15">
         <v>0.308</v>
       </c>
-      <c r="J13" s="16">
-        <v>0</v>
-      </c>
-      <c r="K13" s="16">
+      <c r="M13" s="15">
+        <v>0</v>
+      </c>
+      <c r="N13" s="15">
         <v>4.9087042999999997E-2</v>
       </c>
-      <c r="L13" s="16">
+      <c r="O13" s="15">
         <v>1.38432E-2</v>
       </c>
-      <c r="M13" s="16">
-        <v>0</v>
-      </c>
-      <c r="N13" s="16">
-        <v>0</v>
-      </c>
-      <c r="O13" s="16">
+      <c r="P13" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>0</v>
+      </c>
+      <c r="R13" s="15">
         <v>3.1360000000000001</v>
       </c>
-      <c r="P13" s="16">
+      <c r="S13" s="15">
         <v>3.5219999999999998</v>
       </c>
-      <c r="Q13" s="17">
+      <c r="T13" s="16">
         <v>7.5</v>
       </c>
-      <c r="R13" s="15" t="s">
+      <c r="U13" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S13" s="15">
+      <c r="V13" s="14">
         <v>0.5</v>
       </c>
-      <c r="T13" s="15" t="s">
+      <c r="W13" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U13" s="15">
+      <c r="X13" s="14">
         <v>30</v>
       </c>
-      <c r="V13" s="15" t="s">
+      <c r="Y13" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="W13" s="15">
+      <c r="Z13" s="14">
         <v>2.6009999999999998E-2</v>
       </c>
-      <c r="X13" s="15">
+      <c r="AA13" s="27">
         <v>0.22151335699999999</v>
       </c>
     </row>
-    <row r="14" spans="1:26" s="15" customFormat="1">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:29" s="14" customFormat="1">
+      <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F14" s="27">
         <v>0.1</v>
       </c>
-      <c r="D14" s="16">
+      <c r="G14" s="15">
         <v>1.4890000000000001</v>
       </c>
-      <c r="E14" s="16">
+      <c r="H14" s="15">
         <v>0.30399999999999999</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16">
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15">
         <v>0.30399999999999999</v>
       </c>
-      <c r="J14" s="16">
-        <v>0</v>
-      </c>
-      <c r="K14" s="16">
+      <c r="M14" s="15">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
         <v>6.6037847999999996E-2</v>
       </c>
-      <c r="L14" s="16">
+      <c r="O14" s="15">
         <v>1.602926E-2</v>
       </c>
-      <c r="M14" s="16">
-        <v>0</v>
-      </c>
-      <c r="N14" s="16">
-        <v>0</v>
-      </c>
-      <c r="O14" s="16">
+      <c r="P14" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>0</v>
+      </c>
+      <c r="R14" s="15">
         <v>3.161</v>
       </c>
-      <c r="P14" s="16">
+      <c r="S14" s="15">
         <v>3.8239999999999998</v>
       </c>
-      <c r="Q14" s="17">
+      <c r="T14" s="16">
         <v>7.5</v>
       </c>
-      <c r="R14" s="15" t="s">
+      <c r="U14" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S14" s="15">
+      <c r="V14" s="14">
         <v>0.5</v>
       </c>
-      <c r="T14" s="15" t="s">
+      <c r="W14" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U14" s="15">
+      <c r="X14" s="14">
         <v>30</v>
       </c>
-      <c r="V14" s="15" t="s">
+      <c r="Y14" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="W14" s="15">
+      <c r="Z14" s="14">
         <v>2.7257E-2</v>
       </c>
-      <c r="X14" s="15">
+      <c r="AA14" s="27">
         <v>0.24587221400000001</v>
       </c>
     </row>
-    <row r="15" spans="1:26" s="15" customFormat="1">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:29" s="14" customFormat="1">
+      <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="27">
         <v>0.13</v>
       </c>
-      <c r="D15" s="16">
+      <c r="G15" s="15">
         <v>2.0190000000000001</v>
       </c>
-      <c r="E15" s="16">
+      <c r="H15" s="15">
         <v>0.41499999999999998</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16">
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15">
         <v>0.41499999999999998</v>
       </c>
-      <c r="J15" s="16">
+      <c r="M15" s="15">
         <v>0.14387805000000001</v>
       </c>
-      <c r="K15" s="16">
+      <c r="N15" s="15">
         <v>0.23128044</v>
       </c>
-      <c r="L15" s="16">
+      <c r="O15" s="15">
         <v>2.4418572999999999E-2</v>
       </c>
-      <c r="M15" s="16">
+      <c r="P15" s="15">
         <v>7.3894399999999995E-4</v>
       </c>
-      <c r="N15" s="16">
+      <c r="Q15" s="15">
         <v>4.2122905000000002E-2</v>
       </c>
-      <c r="O15" s="16">
+      <c r="R15" s="15">
         <v>5.51</v>
       </c>
-      <c r="P15" s="16">
+      <c r="S15" s="15">
         <v>5.2519999999999998</v>
       </c>
-      <c r="Q15" s="17">
+      <c r="T15" s="16">
         <v>7.5</v>
       </c>
-      <c r="R15" s="15" t="s">
+      <c r="U15" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S15" s="15">
+      <c r="V15" s="14">
         <v>0.5</v>
       </c>
-      <c r="T15" s="15" t="s">
+      <c r="W15" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U15" s="15">
+      <c r="X15" s="14">
         <v>30</v>
       </c>
-      <c r="V15" s="15" t="s">
+      <c r="Y15" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W15" s="15">
+      <c r="Z15" s="14">
         <v>2.6366000000000001E-2</v>
       </c>
-      <c r="X15" s="15">
+      <c r="AA15" s="27">
         <v>0.30372450000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:26" s="15" customFormat="1">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:29" s="14" customFormat="1">
+      <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="27">
         <v>0.13</v>
       </c>
-      <c r="D16" s="16">
+      <c r="G16" s="15">
         <v>2.0590000000000002</v>
       </c>
-      <c r="E16" s="16">
+      <c r="H16" s="15">
         <v>0.42499999999999999</v>
       </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16">
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15">
         <v>0.42499999999999999</v>
       </c>
-      <c r="J16" s="16">
+      <c r="M16" s="15">
         <v>0.13916811300000001</v>
       </c>
-      <c r="K16" s="16">
+      <c r="N16" s="15">
         <v>0.22761730999999999</v>
       </c>
-      <c r="L16" s="16">
+      <c r="O16" s="15">
         <v>2.5077986E-2</v>
       </c>
-      <c r="M16" s="16">
+      <c r="P16" s="15">
         <v>2.152588E-3</v>
       </c>
-      <c r="N16" s="16">
+      <c r="Q16" s="15">
         <v>3.3899711999999999E-2</v>
       </c>
-      <c r="O16" s="16">
+      <c r="R16" s="15">
         <v>5.3739999999999997</v>
       </c>
-      <c r="P16" s="16">
+      <c r="S16" s="15">
         <v>4.5460000000000003</v>
       </c>
-      <c r="Q16" s="17">
+      <c r="T16" s="16">
         <v>7.5</v>
       </c>
-      <c r="R16" s="15" t="s">
+      <c r="U16" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S16" s="15">
+      <c r="V16" s="14">
         <v>0.5</v>
       </c>
-      <c r="T16" s="15" t="s">
+      <c r="W16" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U16" s="15">
+      <c r="X16" s="14">
         <v>30</v>
       </c>
-      <c r="V16" s="15" t="s">
+      <c r="Y16" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W16" s="15">
+      <c r="Z16" s="14">
         <v>2.5831E-2</v>
       </c>
-      <c r="X16" s="15">
+      <c r="AA16" s="27">
         <v>0.25690982099999998</v>
       </c>
     </row>
-    <row r="17" spans="1:25" s="15" customFormat="1">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:28" s="14" customFormat="1">
+      <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="27">
         <v>0.13</v>
       </c>
-      <c r="D17" s="16">
+      <c r="G17" s="15">
         <v>2.1349999999999998</v>
       </c>
-      <c r="E17" s="16">
+      <c r="H17" s="15">
         <v>0.438</v>
       </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16">
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15">
         <v>0.438</v>
       </c>
-      <c r="J17" s="16">
+      <c r="M17" s="15">
         <v>0.13267562499999999</v>
       </c>
-      <c r="K17" s="16">
+      <c r="N17" s="15">
         <v>0.25727792100000002</v>
       </c>
-      <c r="L17" s="16">
+      <c r="O17" s="15">
         <v>2.6121129999999999E-2</v>
       </c>
-      <c r="M17" s="16">
-        <v>0</v>
-      </c>
-      <c r="N17" s="16">
+      <c r="P17" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="15">
         <v>4.1071206999999998E-2</v>
       </c>
-      <c r="O17" s="16">
+      <c r="R17" s="15">
         <v>5.3019999999999996</v>
       </c>
-      <c r="P17" s="16">
+      <c r="S17" s="15">
         <v>5.07</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="T17" s="16">
         <v>7.5</v>
       </c>
-      <c r="R17" s="15" t="s">
+      <c r="U17" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S17" s="15">
+      <c r="V17" s="14">
         <v>0.5</v>
       </c>
-      <c r="T17" s="15" t="s">
+      <c r="W17" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U17" s="15">
+      <c r="X17" s="14">
         <v>30</v>
       </c>
-      <c r="V17" s="15" t="s">
+      <c r="Y17" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W17" s="15">
+      <c r="Z17" s="14">
         <v>2.5297E-2</v>
       </c>
-      <c r="X17" s="15">
+      <c r="AA17" s="27">
         <v>0.26642500000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:25" s="15" customFormat="1">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:28" s="14" customFormat="1">
+      <c r="A18" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F18" s="27">
         <v>0.18</v>
       </c>
-      <c r="D18" s="16">
+      <c r="G18" s="15">
         <v>3.266</v>
       </c>
-      <c r="E18" s="16">
+      <c r="H18" s="15">
         <v>0.66900000000000004</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16">
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15">
         <v>0.66900000000000004</v>
       </c>
-      <c r="J18" s="16">
+      <c r="M18" s="15">
         <v>1.2813869950000001</v>
       </c>
-      <c r="K18" s="16">
+      <c r="N18" s="15">
         <v>0.18048138799999999</v>
       </c>
-      <c r="L18" s="16">
+      <c r="O18" s="15">
         <v>3.2745818000000003E-2</v>
       </c>
-      <c r="M18" s="16">
-        <v>0</v>
-      </c>
-      <c r="N18" s="16">
+      <c r="P18" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="15">
         <v>5.6452840000000004E-3</v>
       </c>
-      <c r="O18" s="16">
+      <c r="R18" s="15">
         <v>7.2619999999999996</v>
       </c>
-      <c r="P18" s="16">
+      <c r="S18" s="15">
         <v>5.42</v>
       </c>
-      <c r="Q18" s="17">
+      <c r="T18" s="16">
         <v>7.5</v>
       </c>
-      <c r="R18" s="15" t="s">
+      <c r="U18" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S18" s="15">
+      <c r="V18" s="14">
         <v>0.5</v>
       </c>
-      <c r="T18" s="15" t="s">
+      <c r="W18" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U18" s="15">
+      <c r="X18" s="14">
         <v>30</v>
       </c>
-      <c r="V18" s="15" t="s">
+      <c r="Y18" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W18" s="15">
+      <c r="Z18" s="14">
         <v>3.9014E-2</v>
       </c>
-      <c r="X18" s="15">
+      <c r="AA18" s="27">
         <v>0.28926142900000001</v>
       </c>
     </row>
-    <row r="19" spans="1:25" s="15" customFormat="1">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:28" s="14" customFormat="1">
+      <c r="A19" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F19" s="27">
         <v>0.18</v>
       </c>
-      <c r="D19" s="16">
+      <c r="G19" s="15">
         <v>3.202</v>
       </c>
-      <c r="E19" s="16">
+      <c r="H19" s="15">
         <v>0.65900000000000003</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16">
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15">
         <v>0.65900000000000003</v>
       </c>
-      <c r="J19" s="16">
+      <c r="M19" s="15">
         <v>1.4870797280000001</v>
       </c>
-      <c r="K19" s="16">
+      <c r="N19" s="15">
         <v>0.41515672300000001</v>
       </c>
-      <c r="L19" s="16">
+      <c r="O19" s="15">
         <v>3.1272250000000001E-2</v>
       </c>
-      <c r="M19" s="16">
+      <c r="P19" s="15">
         <v>2.6969479999999998E-3</v>
       </c>
-      <c r="N19" s="16">
+      <c r="Q19" s="15">
         <v>1.6418242E-2</v>
       </c>
-      <c r="O19" s="16">
+      <c r="R19" s="15">
         <v>7.3049999999999997</v>
       </c>
-      <c r="P19" s="16">
+      <c r="S19" s="15">
         <v>6.0170000000000003</v>
       </c>
-      <c r="Q19" s="17">
+      <c r="T19" s="16">
         <v>7.5</v>
       </c>
-      <c r="R19" s="15" t="s">
+      <c r="U19" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S19" s="15">
+      <c r="V19" s="14">
         <v>0.5</v>
       </c>
-      <c r="T19" s="15" t="s">
+      <c r="W19" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U19" s="15">
+      <c r="X19" s="14">
         <v>30</v>
       </c>
-      <c r="V19" s="15" t="s">
+      <c r="Y19" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W19" s="15">
+      <c r="Z19" s="14">
         <v>3.8657999999999998E-2</v>
       </c>
-      <c r="X19" s="15">
+      <c r="AA19" s="27">
         <v>0.28202989299999998</v>
       </c>
     </row>
-    <row r="20" spans="1:25" s="15" customFormat="1">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:28" s="14" customFormat="1">
+      <c r="A20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F20" s="27">
         <v>0.18</v>
       </c>
-      <c r="D20" s="16">
+      <c r="G20" s="15">
         <v>2.83</v>
       </c>
-      <c r="E20" s="16">
+      <c r="H20" s="15">
         <v>0.58099999999999996</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16">
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15">
         <v>0.58099999999999996</v>
       </c>
-      <c r="J20" s="16">
+      <c r="M20" s="15">
         <v>1.069367508</v>
       </c>
-      <c r="K20" s="16">
+      <c r="N20" s="15">
         <v>0.18424942899999999</v>
       </c>
-      <c r="L20" s="16">
+      <c r="O20" s="15">
         <v>2.652065E-2</v>
       </c>
-      <c r="M20" s="16">
-        <v>0</v>
-      </c>
-      <c r="N20" s="16">
+      <c r="P20" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="15">
         <v>1.5674206999999999E-2</v>
       </c>
-      <c r="O20" s="16">
+      <c r="R20" s="15">
         <v>6.2510000000000003</v>
       </c>
-      <c r="P20" s="16">
+      <c r="S20" s="15">
         <v>5.2640000000000002</v>
       </c>
-      <c r="Q20" s="17">
+      <c r="T20" s="16">
         <v>7.5</v>
       </c>
-      <c r="R20" s="15" t="s">
+      <c r="U20" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S20" s="15">
+      <c r="V20" s="14">
         <v>0.5</v>
       </c>
-      <c r="T20" s="15" t="s">
+      <c r="W20" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U20" s="15">
+      <c r="X20" s="14">
         <v>30</v>
       </c>
-      <c r="V20" s="15" t="s">
+      <c r="Y20" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W20" s="15">
+      <c r="Z20" s="14">
         <v>3.7945E-2</v>
       </c>
-      <c r="X20" s="15">
+      <c r="AA20" s="27">
         <v>0.288119607</v>
       </c>
     </row>
-    <row r="21" spans="1:25" s="15" customFormat="1">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:28" s="14" customFormat="1">
+      <c r="A21" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F21" s="27">
         <v>0.3</v>
       </c>
-      <c r="D21" s="16">
+      <c r="G21" s="15">
         <v>7.9909999999999997</v>
       </c>
-      <c r="E21" s="16">
+      <c r="H21" s="15">
         <v>1.6479999999999999</v>
       </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16">
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15">
         <v>1.6479999999999999</v>
       </c>
-      <c r="J21" s="16">
+      <c r="M21" s="15">
         <v>7.0441347099999998</v>
       </c>
-      <c r="K21" s="16">
+      <c r="N21" s="15">
         <v>0.31251037799999998</v>
       </c>
-      <c r="L21" s="16">
+      <c r="O21" s="15">
         <v>5.1692219999999997E-2</v>
       </c>
-      <c r="M21" s="16">
+      <c r="P21" s="15">
         <v>1.1339925000000001E-2</v>
       </c>
-      <c r="N21" s="16">
-        <v>0</v>
-      </c>
-      <c r="O21" s="16">
+      <c r="Q21" s="15">
+        <v>0</v>
+      </c>
+      <c r="R21" s="15">
         <v>14.086</v>
       </c>
-      <c r="P21" s="16">
+      <c r="S21" s="15">
         <v>8.3010000000000002</v>
       </c>
-      <c r="Q21" s="17">
+      <c r="T21" s="16">
         <v>7.5</v>
       </c>
-      <c r="R21" s="15" t="s">
+      <c r="U21" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S21" s="15">
+      <c r="V21" s="14">
         <v>0.5</v>
       </c>
-      <c r="T21" s="15" t="s">
+      <c r="W21" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U21" s="15">
+      <c r="X21" s="14">
         <v>30</v>
       </c>
-      <c r="V21" s="15" t="s">
+      <c r="Y21" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W21" s="15">
+      <c r="Z21" s="14">
         <v>4.7031000000000003E-2</v>
       </c>
-      <c r="X21" s="15">
+      <c r="AA21" s="27">
         <v>0.42247392900000003</v>
       </c>
     </row>
-    <row r="22" spans="1:25" s="15" customFormat="1">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:28" s="14" customFormat="1">
+      <c r="A22" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F22" s="27">
         <v>0.3</v>
       </c>
-      <c r="D22" s="16">
+      <c r="G22" s="15">
         <v>8.2759999999999998</v>
       </c>
-      <c r="E22" s="16">
+      <c r="H22" s="15">
         <v>1.6950000000000001</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16">
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15">
         <v>1.6950000000000001</v>
       </c>
-      <c r="J22" s="16">
+      <c r="M22" s="15">
         <v>6.6847254490000001</v>
       </c>
-      <c r="K22" s="16">
+      <c r="N22" s="15">
         <v>0.27229536399999998</v>
       </c>
-      <c r="L22" s="16">
+      <c r="O22" s="15">
         <v>4.4478275999999997E-2</v>
       </c>
-      <c r="M22" s="16">
+      <c r="P22" s="15">
         <v>3.4668667E-2</v>
       </c>
-      <c r="N22" s="16">
-        <v>0</v>
-      </c>
-      <c r="O22" s="16">
+      <c r="Q22" s="15">
+        <v>0</v>
+      </c>
+      <c r="R22" s="15">
         <v>15.111000000000001</v>
       </c>
-      <c r="P22" s="16">
+      <c r="S22" s="15">
         <v>8.3870000000000005</v>
       </c>
-      <c r="Q22" s="17">
+      <c r="T22" s="16">
         <v>7.5</v>
       </c>
-      <c r="R22" s="15" t="s">
+      <c r="U22" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S22" s="15">
+      <c r="V22" s="14">
         <v>0.5</v>
       </c>
-      <c r="T22" s="15" t="s">
+      <c r="W22" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U22" s="15">
+      <c r="X22" s="14">
         <v>30</v>
       </c>
-      <c r="V22" s="15" t="s">
+      <c r="Y22" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W22" s="15">
+      <c r="Z22" s="14">
         <v>4.5606000000000001E-2</v>
       </c>
-      <c r="X22" s="15">
+      <c r="AA22" s="27">
         <v>0.42133210700000001</v>
       </c>
     </row>
-    <row r="23" spans="1:25" s="15" customFormat="1">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:28" s="14" customFormat="1">
+      <c r="A23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F23" s="27">
         <v>0.3</v>
       </c>
-      <c r="D23" s="16">
+      <c r="G23" s="15">
         <v>8.9320000000000004</v>
       </c>
-      <c r="E23" s="16">
+      <c r="H23" s="15">
         <v>1.8660000000000001</v>
       </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16">
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15">
         <v>1.8660000000000001</v>
       </c>
-      <c r="J23" s="16">
+      <c r="M23" s="15">
         <v>8.2124218889999998</v>
       </c>
-      <c r="K23" s="16">
+      <c r="N23" s="15">
         <v>0.61718923199999998</v>
       </c>
-      <c r="L23" s="16">
+      <c r="O23" s="15">
         <v>6.4337543999999997E-2</v>
       </c>
-      <c r="M23" s="16">
+      <c r="P23" s="15">
         <v>2.9481279999999999E-2</v>
       </c>
-      <c r="N23" s="16">
-        <v>0</v>
-      </c>
-      <c r="O23" s="16">
+      <c r="Q23" s="15">
+        <v>0</v>
+      </c>
+      <c r="R23" s="15">
         <v>16.956</v>
       </c>
-      <c r="P23" s="16">
+      <c r="S23" s="15">
         <v>9.34</v>
       </c>
-      <c r="Q23" s="17">
+      <c r="T23" s="16">
         <v>7.5</v>
       </c>
-      <c r="R23" s="15" t="s">
+      <c r="U23" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S23" s="15">
+      <c r="V23" s="14">
         <v>0.5</v>
       </c>
-      <c r="T23" s="15" t="s">
+      <c r="W23" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U23" s="15">
+      <c r="X23" s="14">
         <v>30</v>
       </c>
-      <c r="V23" s="15" t="s">
+      <c r="Y23" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W23" s="15">
+      <c r="Z23" s="14">
         <v>5.2019000000000003E-2</v>
       </c>
-      <c r="X23" s="15">
+      <c r="AA23" s="27">
         <v>0.39963749999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:25" s="15" customFormat="1">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:28" s="14" customFormat="1">
+      <c r="A24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="27">
         <v>0.35</v>
       </c>
-      <c r="D24" s="16">
+      <c r="G24" s="15">
         <v>12.936999999999999</v>
       </c>
-      <c r="E24" s="16">
+      <c r="H24" s="15">
         <v>2.7120000000000002</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16">
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15">
         <v>2.7120000000000002</v>
       </c>
-      <c r="J24" s="16">
+      <c r="M24" s="15">
         <v>11.927306959999999</v>
       </c>
-      <c r="K24" s="16">
+      <c r="N24" s="15">
         <v>0.47269426599999997</v>
       </c>
-      <c r="L24" s="16">
+      <c r="O24" s="15">
         <v>8.9757966999999994E-2</v>
       </c>
-      <c r="M24" s="16">
+      <c r="P24" s="15">
         <v>3.5944587E-2</v>
       </c>
-      <c r="N24" s="16">
-        <v>0</v>
-      </c>
-      <c r="O24" s="16">
+      <c r="Q24" s="15">
+        <v>0</v>
+      </c>
+      <c r="R24" s="15">
         <v>20.902000000000001</v>
       </c>
-      <c r="P24" s="16">
+      <c r="S24" s="15">
         <v>12.682</v>
       </c>
-      <c r="Q24" s="17">
+      <c r="T24" s="16">
         <v>7.5</v>
       </c>
-      <c r="R24" s="15" t="s">
+      <c r="U24" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S24" s="15">
+      <c r="V24" s="14">
         <v>0.5</v>
       </c>
-      <c r="T24" s="15" t="s">
+      <c r="W24" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U24" s="15">
+      <c r="X24" s="14">
         <v>30</v>
       </c>
-      <c r="V24" s="15" t="s">
+      <c r="Y24" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W24" s="15">
+      <c r="Z24" s="14">
         <v>7.3219000000000006E-2</v>
       </c>
-      <c r="X24" s="15">
+      <c r="AA24" s="27">
         <v>0.48415467400000001</v>
       </c>
     </row>
-    <row r="25" spans="1:25" s="15" customFormat="1">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:28" s="14" customFormat="1">
+      <c r="A25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F25" s="27">
         <v>0.35</v>
       </c>
-      <c r="D25" s="16">
+      <c r="G25" s="15">
         <v>13.23</v>
       </c>
-      <c r="E25" s="16">
+      <c r="H25" s="15">
         <v>2.786</v>
       </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16">
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15">
         <v>2.786</v>
       </c>
-      <c r="J25" s="16">
+      <c r="M25" s="15">
         <v>12.12470377</v>
       </c>
-      <c r="K25" s="16">
+      <c r="N25" s="15">
         <v>0.63692599999999999</v>
       </c>
-      <c r="L25" s="16">
+      <c r="O25" s="15">
         <v>0.104193063</v>
       </c>
-      <c r="M25" s="16">
+      <c r="P25" s="15">
         <v>3.3770889999999998E-2</v>
       </c>
-      <c r="N25" s="16">
-        <v>0</v>
-      </c>
-      <c r="O25" s="16">
+      <c r="Q25" s="15">
+        <v>0</v>
+      </c>
+      <c r="R25" s="15">
         <v>21.082999999999998</v>
       </c>
-      <c r="P25" s="16">
+      <c r="S25" s="15">
         <v>12.353999999999999</v>
       </c>
-      <c r="Q25" s="17">
+      <c r="T25" s="16">
         <v>7.5</v>
       </c>
-      <c r="R25" s="15" t="s">
+      <c r="U25" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S25" s="15">
+      <c r="V25" s="14">
         <v>0.5</v>
       </c>
-      <c r="T25" s="15" t="s">
+      <c r="W25" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U25" s="15">
+      <c r="X25" s="14">
         <v>30</v>
       </c>
-      <c r="V25" s="15" t="s">
+      <c r="Y25" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W25" s="15">
+      <c r="Z25" s="14">
         <v>7.0545999999999998E-2</v>
       </c>
-      <c r="X25" s="15">
+      <c r="AA25" s="27">
         <v>0.48992198300000001</v>
       </c>
     </row>
-    <row r="26" spans="1:25" s="15" customFormat="1">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:28" s="14" customFormat="1">
+      <c r="A26" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F26" s="27">
         <v>0.35</v>
       </c>
-      <c r="D26" s="16">
+      <c r="G26" s="15">
         <v>13.096</v>
       </c>
-      <c r="E26" s="16">
+      <c r="H26" s="15">
         <v>2.742</v>
       </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16">
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15">
         <v>2.742</v>
       </c>
-      <c r="J26" s="16">
+      <c r="M26" s="15">
         <v>11.84780602</v>
       </c>
-      <c r="K26" s="16">
+      <c r="N26" s="15">
         <v>0.47734259699999998</v>
       </c>
-      <c r="L26" s="16">
+      <c r="O26" s="15">
         <v>9.1823417000000004E-2</v>
       </c>
-      <c r="M26" s="16">
-        <v>0</v>
-      </c>
-      <c r="N26" s="16">
-        <v>0</v>
-      </c>
-      <c r="O26" s="16">
+      <c r="P26" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="15">
+        <v>0</v>
+      </c>
+      <c r="R26" s="15">
         <v>21.097999999999999</v>
       </c>
-      <c r="P26" s="16">
+      <c r="S26" s="15">
         <v>12.977</v>
       </c>
-      <c r="Q26" s="17">
+      <c r="T26" s="16">
         <v>7.5</v>
       </c>
-      <c r="R26" s="15" t="s">
+      <c r="U26" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="S26" s="15">
+      <c r="V26" s="14">
         <v>0.5</v>
       </c>
-      <c r="T26" s="15" t="s">
+      <c r="W26" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U26" s="15">
+      <c r="X26" s="14">
         <v>30</v>
       </c>
-      <c r="V26" s="15" t="s">
+      <c r="Y26" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="W26" s="15">
+      <c r="Z26" s="14">
         <v>8.8717000000000004E-2</v>
       </c>
-      <c r="X26" s="15">
+      <c r="AA26" s="27">
         <v>0.50886425499999999</v>
       </c>
     </row>
-    <row r="27" spans="1:25" s="15" customFormat="1">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:28" s="14" customFormat="1">
+      <c r="A27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F27" s="27">
         <v>0.1</v>
       </c>
-      <c r="D27" s="16">
+      <c r="G27" s="15">
         <v>0.82699999999999996</v>
       </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16">
+      <c r="H27" s="15"/>
+      <c r="I27" s="15">
         <v>0.747</v>
       </c>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16">
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15">
         <v>1.4930000000000001</v>
       </c>
-      <c r="J27" s="16">
-        <v>0</v>
-      </c>
-      <c r="K27" s="16">
-        <v>0</v>
-      </c>
-      <c r="L27" s="16">
+      <c r="M27" s="15">
+        <v>0</v>
+      </c>
+      <c r="N27" s="15">
+        <v>0</v>
+      </c>
+      <c r="O27" s="15">
         <v>8.7561730000000008E-3</v>
       </c>
-      <c r="M27" s="16">
-        <v>0</v>
-      </c>
-      <c r="N27" s="16">
-        <v>0</v>
-      </c>
-      <c r="O27" s="16">
+      <c r="P27" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="15">
+        <v>0</v>
+      </c>
+      <c r="R27" s="15">
         <v>2.7690000000000001</v>
       </c>
-      <c r="P27" s="16">
+      <c r="S27" s="15">
         <v>2.4500000000000002</v>
       </c>
-      <c r="Q27" s="17">
+      <c r="T27" s="16">
         <v>7.5</v>
       </c>
-      <c r="R27" s="15" t="s">
+      <c r="U27" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="S27" s="15">
+      <c r="V27" s="14">
         <v>5.53</v>
       </c>
-      <c r="T27" s="15" t="s">
+      <c r="W27" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U27" s="15">
+      <c r="X27" s="14">
         <v>5</v>
       </c>
-      <c r="V27" s="15" t="s">
+      <c r="Y27" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W27" s="15">
+      <c r="Z27" s="14">
         <v>7.1259000000000003E-2</v>
       </c>
-      <c r="X27" s="15">
+      <c r="AA27" s="27">
         <v>0.49783414300000001</v>
       </c>
-      <c r="Y27" s="15" t="s">
+      <c r="AB27" s="14" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:25" s="15" customFormat="1">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:28" s="14" customFormat="1">
+      <c r="A28" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F28" s="27">
         <v>0.1</v>
       </c>
-      <c r="D28" s="16">
+      <c r="G28" s="15">
         <v>0.78800000000000003</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16">
+      <c r="H28" s="15"/>
+      <c r="I28" s="15">
         <v>0.71199999999999997</v>
       </c>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16">
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15">
         <v>1.423</v>
       </c>
-      <c r="J28" s="16">
-        <v>0</v>
-      </c>
-      <c r="K28" s="16">
-        <v>0</v>
-      </c>
-      <c r="L28" s="16">
+      <c r="M28" s="15">
+        <v>0</v>
+      </c>
+      <c r="N28" s="15">
+        <v>0</v>
+      </c>
+      <c r="O28" s="15">
         <v>5.5182690000000001E-3</v>
       </c>
-      <c r="M28" s="16">
-        <v>0</v>
-      </c>
-      <c r="N28" s="16">
-        <v>0</v>
-      </c>
-      <c r="O28" s="16">
+      <c r="P28" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="15">
+        <v>0</v>
+      </c>
+      <c r="R28" s="15">
         <v>2.7170000000000001</v>
       </c>
-      <c r="P28" s="16">
+      <c r="S28" s="15">
         <v>2.3530000000000002</v>
       </c>
-      <c r="Q28" s="17">
+      <c r="T28" s="16">
         <v>7.5</v>
       </c>
-      <c r="R28" s="15" t="s">
+      <c r="U28" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="S28" s="15">
+      <c r="V28" s="14">
         <v>5.53</v>
       </c>
-      <c r="T28" s="15" t="s">
+      <c r="W28" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U28" s="15">
+      <c r="X28" s="14">
         <v>5</v>
       </c>
-      <c r="V28" s="15" t="s">
+      <c r="Y28" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W28" s="15">
+      <c r="Z28" s="14">
         <v>5.8789000000000001E-2</v>
       </c>
-      <c r="X28" s="15">
+      <c r="AA28" s="27">
         <v>0.58385135700000002</v>
       </c>
-      <c r="Y28" s="15" t="s">
+      <c r="AB28" s="14" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:25" s="15" customFormat="1">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:28" s="14" customFormat="1">
+      <c r="A29" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F29" s="27">
         <v>0.1</v>
       </c>
-      <c r="D29" s="16">
+      <c r="G29" s="15">
         <v>0.76700000000000002</v>
       </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16">
+      <c r="H29" s="15"/>
+      <c r="I29" s="15">
         <v>0.69099999999999995</v>
       </c>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16">
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15">
         <v>1.3819999999999999</v>
       </c>
-      <c r="J29" s="16">
-        <v>0</v>
-      </c>
-      <c r="K29" s="16">
-        <v>0</v>
-      </c>
-      <c r="L29" s="16">
+      <c r="M29" s="15">
+        <v>0</v>
+      </c>
+      <c r="N29" s="15">
+        <v>0</v>
+      </c>
+      <c r="O29" s="15">
         <v>1.9902549999999998E-3</v>
       </c>
-      <c r="M29" s="16">
-        <v>0</v>
-      </c>
-      <c r="N29" s="16">
-        <v>0</v>
-      </c>
-      <c r="O29" s="16">
+      <c r="P29" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="15">
+        <v>0</v>
+      </c>
+      <c r="R29" s="15">
         <v>2.5739999999999998</v>
       </c>
-      <c r="P29" s="16">
+      <c r="S29" s="15">
         <v>2.25</v>
       </c>
-      <c r="Q29" s="17">
+      <c r="T29" s="16">
         <v>7.5</v>
       </c>
-      <c r="R29" s="15" t="s">
+      <c r="U29" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="S29" s="15">
+      <c r="V29" s="14">
         <v>5.53</v>
       </c>
-      <c r="T29" s="15" t="s">
+      <c r="W29" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U29" s="15">
+      <c r="X29" s="14">
         <v>5</v>
       </c>
-      <c r="V29" s="15" t="s">
+      <c r="Y29" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W29" s="15">
+      <c r="Z29" s="14">
         <v>6.4132999999999996E-2</v>
       </c>
-      <c r="X29" s="15">
+      <c r="AA29" s="27">
         <v>0.59412774999999995</v>
       </c>
-      <c r="Y29" s="15" t="s">
+      <c r="AB29" s="14" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:25" s="15" customFormat="1">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:28" s="14" customFormat="1">
+      <c r="A30" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F30" s="27">
         <v>0.1</v>
       </c>
-      <c r="D30" s="16">
+      <c r="G30" s="15">
         <v>0.80700000000000005</v>
       </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16">
+      <c r="H30" s="15"/>
+      <c r="I30" s="15">
         <v>4.92</v>
       </c>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16">
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15">
         <v>9.8390000000000004</v>
       </c>
-      <c r="J30" s="16">
-        <v>0</v>
-      </c>
-      <c r="K30" s="16">
-        <v>0</v>
-      </c>
-      <c r="L30" s="16">
+      <c r="M30" s="15">
+        <v>0</v>
+      </c>
+      <c r="N30" s="15">
+        <v>0</v>
+      </c>
+      <c r="O30" s="15">
         <v>3.9436786000000001E-2</v>
       </c>
-      <c r="M30" s="16">
-        <v>0</v>
-      </c>
-      <c r="N30" s="16">
+      <c r="P30" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="15">
         <v>1.3630471999999999E-2</v>
       </c>
-      <c r="O30" s="16">
+      <c r="R30" s="15">
         <v>3.032</v>
       </c>
-      <c r="P30" s="16">
+      <c r="S30" s="15">
         <v>1.7749999999999999</v>
       </c>
-      <c r="Q30" s="17">
+      <c r="T30" s="16">
         <v>1.21</v>
       </c>
-      <c r="R30" s="15" t="s">
+      <c r="U30" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="S30" s="15">
+      <c r="V30" s="14">
         <v>5.53</v>
       </c>
-      <c r="T30" s="15" t="s">
+      <c r="W30" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U30" s="15">
+      <c r="X30" s="14">
         <v>3</v>
       </c>
-      <c r="V30" s="15" t="s">
+      <c r="Y30" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W30" s="15">
+      <c r="Z30" s="14">
         <v>5.5581999999999999E-2</v>
       </c>
-      <c r="X30" s="15">
+      <c r="AA30" s="27">
         <v>0.510013571</v>
       </c>
-      <c r="Y30" s="15" t="s">
+      <c r="AB30" s="14" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:25" s="15" customFormat="1">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:28" s="14" customFormat="1">
+      <c r="A31" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31" s="27">
         <v>0.1</v>
       </c>
-      <c r="D31" s="16">
+      <c r="G31" s="15">
         <v>0.64900000000000002</v>
       </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16">
+      <c r="H31" s="15"/>
+      <c r="I31" s="15">
         <v>3.9620000000000002</v>
       </c>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16">
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15">
         <v>7.9240000000000004</v>
       </c>
-      <c r="J31" s="16">
-        <v>0</v>
-      </c>
-      <c r="K31" s="16">
-        <v>0</v>
-      </c>
-      <c r="L31" s="16">
+      <c r="M31" s="15">
+        <v>0</v>
+      </c>
+      <c r="N31" s="15">
+        <v>0</v>
+      </c>
+      <c r="O31" s="15">
         <v>3.0460814999999999E-2</v>
       </c>
-      <c r="M31" s="16">
-        <v>0</v>
-      </c>
-      <c r="N31" s="16">
+      <c r="P31" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="15">
         <v>9.5061450000000006E-3</v>
       </c>
-      <c r="O31" s="16">
+      <c r="R31" s="15">
         <v>1.9590000000000001</v>
       </c>
-      <c r="P31" s="16">
+      <c r="S31" s="15">
         <v>1.623</v>
       </c>
-      <c r="Q31" s="17">
+      <c r="T31" s="16">
         <v>1.21</v>
       </c>
-      <c r="R31" s="15" t="s">
+      <c r="U31" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="S31" s="15">
+      <c r="V31" s="14">
         <v>5.53</v>
       </c>
-      <c r="T31" s="15" t="s">
+      <c r="W31" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U31" s="15">
+      <c r="X31" s="14">
         <v>3</v>
       </c>
-      <c r="V31" s="15" t="s">
+      <c r="Y31" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W31" s="15">
+      <c r="Z31" s="14">
         <v>5.4869000000000001E-2</v>
       </c>
-      <c r="X31" s="15">
+      <c r="AA31" s="27">
         <v>0.29420932100000002</v>
       </c>
-      <c r="Y31" s="15" t="s">
+      <c r="AB31" s="14" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="1:25" s="15" customFormat="1">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:28" s="14" customFormat="1">
+      <c r="A32" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F32" s="27">
         <v>0.1</v>
       </c>
-      <c r="D32" s="16">
+      <c r="G32" s="15">
         <v>0.76500000000000001</v>
       </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16">
+      <c r="H32" s="15"/>
+      <c r="I32" s="15">
         <v>4.6159999999999997</v>
       </c>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16">
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15">
         <v>9.2319999999999993</v>
       </c>
-      <c r="J32" s="16">
-        <v>0</v>
-      </c>
-      <c r="K32" s="16">
-        <v>0</v>
-      </c>
-      <c r="L32" s="16">
+      <c r="M32" s="15">
+        <v>0</v>
+      </c>
+      <c r="N32" s="15">
+        <v>0</v>
+      </c>
+      <c r="O32" s="15">
         <v>2.5119712999999998E-2</v>
       </c>
-      <c r="M32" s="16">
-        <v>0</v>
-      </c>
-      <c r="N32" s="16">
-        <v>0</v>
-      </c>
-      <c r="O32" s="16">
+      <c r="P32" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="15">
+        <v>0</v>
+      </c>
+      <c r="R32" s="15">
         <v>2.569</v>
       </c>
-      <c r="P32" s="16">
+      <c r="S32" s="15">
         <v>1.2909999999999999</v>
       </c>
-      <c r="Q32" s="17">
+      <c r="T32" s="16">
         <v>1.21</v>
       </c>
-      <c r="R32" s="15" t="s">
+      <c r="U32" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="S32" s="15">
+      <c r="V32" s="14">
         <v>5.53</v>
       </c>
-      <c r="T32" s="15" t="s">
+      <c r="W32" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U32" s="15">
+      <c r="X32" s="14">
         <v>3</v>
       </c>
-      <c r="V32" s="15" t="s">
+      <c r="Y32" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W32" s="15">
+      <c r="Z32" s="14">
         <v>5.1663000000000001E-2</v>
       </c>
-      <c r="X32" s="15">
+      <c r="AA32" s="27">
         <v>0.358912536</v>
       </c>
-      <c r="Y32" s="15" t="s">
+      <c r="AB32" s="14" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="15" customFormat="1">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:27" s="14" customFormat="1">
+      <c r="A33" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F33" s="27">
         <v>0.1</v>
       </c>
-      <c r="D33" s="16">
+      <c r="G33" s="15">
         <v>1.381</v>
       </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16">
+      <c r="H33" s="15"/>
+      <c r="I33" s="15">
         <v>0.158</v>
       </c>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16">
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15">
         <v>0.317</v>
       </c>
-      <c r="J33" s="16">
+      <c r="M33" s="15">
         <v>1.8073279000000001E-2</v>
       </c>
-      <c r="K33" s="16">
+      <c r="N33" s="15">
         <v>7.8381013999999999E-2</v>
       </c>
-      <c r="L33" s="16">
+      <c r="O33" s="15">
         <v>0.86713414300000002</v>
       </c>
-      <c r="M33" s="16">
+      <c r="P33" s="15">
         <v>5.4564440000000004E-3</v>
       </c>
-      <c r="N33" s="16">
+      <c r="Q33" s="15">
         <v>4.6616212999999997E-2</v>
       </c>
-      <c r="O33" s="16">
+      <c r="R33" s="15">
         <v>4.3209999999999997</v>
       </c>
-      <c r="P33" s="16">
+      <c r="S33" s="15">
         <v>3.883</v>
       </c>
-      <c r="Q33" s="17">
+      <c r="T33" s="16">
         <v>6.87</v>
       </c>
-      <c r="R33" s="15" t="s">
+      <c r="U33" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="S33" s="15">
+      <c r="V33" s="14">
         <v>0.55000000000000004</v>
       </c>
-      <c r="T33" s="15" t="s">
+      <c r="W33" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U33" s="15">
+      <c r="X33" s="14">
         <v>30</v>
       </c>
-      <c r="V33" s="15" t="s">
+      <c r="Y33" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W33" s="15">
+      <c r="Z33" s="14">
         <v>2.6366000000000001E-2</v>
       </c>
-      <c r="X33" s="15">
+      <c r="AA33" s="27">
         <v>0.20552785700000001</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="15" customFormat="1">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:27" s="14" customFormat="1">
+      <c r="A34" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="27">
         <v>0.1</v>
       </c>
-      <c r="D34" s="16">
+      <c r="G34" s="15">
         <v>1.2589999999999999</v>
       </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16">
+      <c r="H34" s="15"/>
+      <c r="I34" s="15">
         <v>0.14199999999999999</v>
       </c>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16">
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15">
         <v>0.28399999999999997</v>
       </c>
-      <c r="J34" s="16">
-        <v>0</v>
-      </c>
-      <c r="K34" s="16">
+      <c r="M34" s="15">
+        <v>0</v>
+      </c>
+      <c r="N34" s="15">
         <v>3.4333113999999998E-2</v>
       </c>
-      <c r="L34" s="16">
+      <c r="O34" s="15">
         <v>0.69158415699999998</v>
       </c>
-      <c r="M34" s="16">
-        <v>0</v>
-      </c>
-      <c r="N34" s="16">
+      <c r="P34" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="15">
         <v>4.5041784000000001E-2</v>
       </c>
-      <c r="O34" s="16">
+      <c r="R34" s="15">
         <v>3.93</v>
       </c>
-      <c r="P34" s="16">
+      <c r="S34" s="15">
         <v>3.3959999999999999</v>
       </c>
-      <c r="Q34" s="17">
+      <c r="T34" s="16">
         <v>6.87</v>
       </c>
-      <c r="R34" s="15" t="s">
+      <c r="U34" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="S34" s="15">
+      <c r="V34" s="14">
         <v>0.55000000000000004</v>
       </c>
-      <c r="T34" s="15" t="s">
+      <c r="W34" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U34" s="15">
+      <c r="X34" s="14">
         <v>30</v>
       </c>
-      <c r="V34" s="15" t="s">
+      <c r="Y34" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W34" s="15">
+      <c r="Z34" s="14">
         <v>2.2268E-2</v>
       </c>
-      <c r="X34" s="15">
+      <c r="AA34" s="27">
         <v>0.35282282100000001</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="15" customFormat="1">
-      <c r="A35" s="3" t="s">
+    <row r="35" spans="1:27" s="14" customFormat="1">
+      <c r="A35" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F35" s="27">
         <v>0.1</v>
       </c>
-      <c r="D35" s="16">
+      <c r="G35" s="15">
         <v>1.3</v>
       </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16">
+      <c r="H35" s="15"/>
+      <c r="I35" s="15">
         <v>0.14899999999999999</v>
       </c>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16">
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15">
         <v>0.29799999999999999</v>
       </c>
-      <c r="J35" s="16">
-        <v>0</v>
-      </c>
-      <c r="K35" s="16">
+      <c r="M35" s="15">
+        <v>0</v>
+      </c>
+      <c r="N35" s="15">
         <v>7.6426068999999999E-2</v>
       </c>
-      <c r="L35" s="16">
+      <c r="O35" s="15">
         <v>0.84262339500000005</v>
       </c>
-      <c r="M35" s="16">
+      <c r="P35" s="15">
         <v>5.663179E-3</v>
       </c>
-      <c r="N35" s="16">
+      <c r="Q35" s="15">
         <v>4.1991897E-2</v>
       </c>
-      <c r="O35" s="16">
+      <c r="R35" s="15">
         <v>4.077</v>
       </c>
-      <c r="P35" s="16">
+      <c r="S35" s="15">
         <v>3.3340000000000001</v>
       </c>
-      <c r="Q35" s="17">
+      <c r="T35" s="16">
         <v>6.87</v>
       </c>
-      <c r="R35" s="15" t="s">
+      <c r="U35" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="S35" s="15">
+      <c r="V35" s="14">
         <v>0.55000000000000004</v>
       </c>
-      <c r="T35" s="15" t="s">
+      <c r="W35" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U35" s="15">
+      <c r="X35" s="14">
         <v>30</v>
       </c>
-      <c r="V35" s="15" t="s">
+      <c r="Y35" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W35" s="15">
+      <c r="Z35" s="14">
         <v>1.7815000000000001E-2</v>
       </c>
-      <c r="X35" s="15">
+      <c r="AA35" s="27">
         <v>0.36195739300000002</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="15" customFormat="1">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:27" s="14" customFormat="1">
+      <c r="A36" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E36" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F36" s="27">
         <v>0.1</v>
       </c>
-      <c r="D36" s="16">
+      <c r="G36" s="15">
         <v>1.4850000000000001</v>
       </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16">
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15">
         <v>2.8620000000000001</v>
       </c>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16">
+      <c r="K36" s="15"/>
+      <c r="L36" s="15">
         <v>2.8620000000000001</v>
       </c>
-      <c r="J36" s="16">
-        <v>0</v>
-      </c>
-      <c r="K36" s="16">
-        <v>0</v>
-      </c>
-      <c r="L36" s="16">
+      <c r="M36" s="15">
+        <v>0</v>
+      </c>
+      <c r="N36" s="15">
+        <v>0</v>
+      </c>
+      <c r="O36" s="15">
         <v>6.3162172000000003E-2</v>
       </c>
-      <c r="M36" s="16">
-        <v>0</v>
-      </c>
-      <c r="N36" s="16">
-        <v>0</v>
-      </c>
-      <c r="O36" s="16">
+      <c r="P36" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="15">
+        <v>0</v>
+      </c>
+      <c r="R36" s="15">
         <v>5.7110000000000003</v>
       </c>
-      <c r="P36" s="16">
+      <c r="S36" s="15">
         <v>5.6040000000000001</v>
       </c>
-      <c r="Q36" s="17">
+      <c r="T36" s="16">
         <v>7.5</v>
       </c>
-      <c r="R36" s="15" t="s">
+      <c r="U36" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="S36" s="15">
+      <c r="V36" s="14">
         <v>12.35</v>
       </c>
-      <c r="T36" s="15" t="s">
+      <c r="W36" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U36" s="15">
+      <c r="X36" s="14">
         <v>3</v>
       </c>
-      <c r="V36" s="15" t="s">
+      <c r="Y36" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W36" s="15">
+      <c r="Z36" s="14">
         <v>1.9595999999999999E-2</v>
       </c>
-      <c r="X36" s="15">
+      <c r="AA36" s="27">
         <v>0.425138179</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="15" customFormat="1">
-      <c r="A37" s="3" t="s">
+    <row r="37" spans="1:27" s="14" customFormat="1">
+      <c r="A37" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E37" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F37" s="27">
         <v>0.1</v>
       </c>
-      <c r="D37" s="16">
+      <c r="G37" s="15">
         <v>1.6</v>
       </c>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16">
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15">
         <v>3.0840000000000001</v>
       </c>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16">
+      <c r="K37" s="15"/>
+      <c r="L37" s="15">
         <v>3.0840000000000001</v>
       </c>
-      <c r="J37" s="16">
-        <v>0</v>
-      </c>
-      <c r="K37" s="16">
-        <v>0</v>
-      </c>
-      <c r="L37" s="16">
+      <c r="M37" s="15">
+        <v>0</v>
+      </c>
+      <c r="N37" s="15">
+        <v>0</v>
+      </c>
+      <c r="O37" s="15">
         <v>7.4209667000000007E-2</v>
       </c>
-      <c r="M37" s="16">
-        <v>0</v>
-      </c>
-      <c r="N37" s="16">
-        <v>0</v>
-      </c>
-      <c r="O37" s="16">
+      <c r="P37" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="15">
+        <v>0</v>
+      </c>
+      <c r="R37" s="15">
         <v>6.0389999999999997</v>
       </c>
-      <c r="P37" s="16">
+      <c r="S37" s="15">
         <v>5.8689999999999998</v>
       </c>
-      <c r="Q37" s="17">
+      <c r="T37" s="16">
         <v>7.5</v>
       </c>
-      <c r="R37" s="15" t="s">
+      <c r="U37" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="S37" s="15">
+      <c r="V37" s="14">
         <v>12.35</v>
       </c>
-      <c r="T37" s="15" t="s">
+      <c r="W37" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U37" s="15">
+      <c r="X37" s="14">
         <v>3</v>
       </c>
-      <c r="V37" s="15" t="s">
+      <c r="Y37" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W37" s="15">
+      <c r="Z37" s="14">
         <v>2.0309000000000001E-2</v>
       </c>
-      <c r="X37" s="15">
+      <c r="AA37" s="27">
         <v>0.52028996400000005</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="15" customFormat="1">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:27" s="14" customFormat="1">
+      <c r="A38" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E38" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F38" s="27">
         <v>0.1</v>
       </c>
-      <c r="D38" s="16">
+      <c r="G38" s="15">
         <v>1.4350000000000001</v>
       </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16">
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15">
         <v>2.7629999999999999</v>
       </c>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16">
+      <c r="K38" s="15"/>
+      <c r="L38" s="15">
         <v>2.7629999999999999</v>
       </c>
-      <c r="J38" s="16">
-        <v>0</v>
-      </c>
-      <c r="K38" s="16">
-        <v>0</v>
-      </c>
-      <c r="L38" s="16">
+      <c r="M38" s="15">
+        <v>0</v>
+      </c>
+      <c r="N38" s="15">
+        <v>0</v>
+      </c>
+      <c r="O38" s="15">
         <v>7.4921513999999995E-2</v>
       </c>
-      <c r="M38" s="16">
-        <v>0</v>
-      </c>
-      <c r="N38" s="16">
-        <v>0</v>
-      </c>
-      <c r="O38" s="16">
+      <c r="P38" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="15">
+        <v>0</v>
+      </c>
+      <c r="R38" s="15">
         <v>5.32</v>
       </c>
-      <c r="P38" s="16">
+      <c r="S38" s="15">
         <v>5.0789999999999997</v>
       </c>
-      <c r="Q38" s="17">
+      <c r="T38" s="16">
         <v>7.5</v>
       </c>
-      <c r="R38" s="15" t="s">
+      <c r="U38" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="S38" s="15">
+      <c r="V38" s="14">
         <v>12.35</v>
       </c>
-      <c r="T38" s="15" t="s">
+      <c r="W38" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U38" s="15">
+      <c r="X38" s="14">
         <v>3</v>
       </c>
-      <c r="V38" s="15" t="s">
+      <c r="Y38" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W38" s="15">
+      <c r="Z38" s="14">
         <v>1.8171E-2</v>
       </c>
-      <c r="X38" s="15">
+      <c r="AA38" s="27">
         <v>0.452161286</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="15" customFormat="1">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:27" s="14" customFormat="1">
+      <c r="A39" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F39" s="27">
         <v>0.1</v>
       </c>
-      <c r="D39" s="16">
+      <c r="G39" s="15">
         <v>1.6779999999999999</v>
       </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16">
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15">
         <v>0.33400000000000002</v>
       </c>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16">
+      <c r="K39" s="15"/>
+      <c r="L39" s="15">
         <v>0.33400000000000002</v>
       </c>
-      <c r="J39" s="16">
-        <v>0</v>
-      </c>
-      <c r="K39" s="16">
-        <v>0</v>
-      </c>
-      <c r="L39" s="16">
+      <c r="M39" s="15">
+        <v>0</v>
+      </c>
+      <c r="N39" s="15">
+        <v>0</v>
+      </c>
+      <c r="O39" s="15">
         <v>0.27117874199999997</v>
       </c>
-      <c r="M39" s="16">
-        <v>0</v>
-      </c>
-      <c r="N39" s="16">
-        <v>0</v>
-      </c>
-      <c r="O39" s="16">
+      <c r="P39" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="15">
+        <v>0</v>
+      </c>
+      <c r="R39" s="15">
         <v>5.7240000000000002</v>
       </c>
-      <c r="P39" s="16">
+      <c r="S39" s="15">
         <v>5.9080000000000004</v>
       </c>
-      <c r="Q39" s="17">
+      <c r="T39" s="16">
         <v>7.5</v>
       </c>
-      <c r="R39" s="15" t="s">
+      <c r="U39" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="S39" s="15">
+      <c r="V39" s="14">
         <v>1.24</v>
       </c>
-      <c r="T39" s="15" t="s">
+      <c r="W39" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U39" s="15">
+      <c r="X39" s="14">
         <v>30</v>
       </c>
-      <c r="V39" s="15" t="s">
+      <c r="Y39" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W39" s="15">
+      <c r="Z39" s="14">
         <v>2.3337E-2</v>
       </c>
-      <c r="X39" s="15">
+      <c r="AA39" s="27">
         <v>0.41790664300000002</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="15" customFormat="1">
-      <c r="A40" s="3" t="s">
+    <row r="40" spans="1:27" s="14" customFormat="1">
+      <c r="A40" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F40" s="27">
         <v>0.1</v>
       </c>
-      <c r="D40" s="16">
+      <c r="G40" s="15">
         <v>1.6930000000000001</v>
       </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16">
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15">
         <v>0.33700000000000002</v>
       </c>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16">
+      <c r="K40" s="15"/>
+      <c r="L40" s="15">
         <v>0.33700000000000002</v>
       </c>
-      <c r="J40" s="16">
-        <v>0</v>
-      </c>
-      <c r="K40" s="16">
-        <v>0</v>
-      </c>
-      <c r="L40" s="16">
+      <c r="M40" s="15">
+        <v>0</v>
+      </c>
+      <c r="N40" s="15">
+        <v>0</v>
+      </c>
+      <c r="O40" s="15">
         <v>0.30716928599999999</v>
       </c>
-      <c r="M40" s="16">
-        <v>0</v>
-      </c>
-      <c r="N40" s="16">
-        <v>0</v>
-      </c>
-      <c r="O40" s="16">
+      <c r="P40" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="15">
+        <v>0</v>
+      </c>
+      <c r="R40" s="15">
         <v>5.9720000000000004</v>
       </c>
-      <c r="P40" s="16">
+      <c r="S40" s="15">
         <v>5.29</v>
       </c>
-      <c r="Q40" s="17">
+      <c r="T40" s="16">
         <v>7.5</v>
       </c>
-      <c r="R40" s="15" t="s">
+      <c r="U40" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="S40" s="15">
+      <c r="V40" s="14">
         <v>1.24</v>
       </c>
-      <c r="T40" s="15" t="s">
+      <c r="W40" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U40" s="15">
+      <c r="X40" s="14">
         <v>30</v>
       </c>
-      <c r="V40" s="15" t="s">
+      <c r="Y40" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W40" s="15">
+      <c r="Z40" s="14">
         <v>2.4941000000000001E-2</v>
       </c>
-      <c r="X40" s="15">
+      <c r="AA40" s="27">
         <v>0.37870410700000001</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="15" customFormat="1">
-      <c r="A41" s="3" t="s">
+    <row r="41" spans="1:27" s="14" customFormat="1">
+      <c r="A41" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F41" s="27">
         <v>0.1</v>
       </c>
-      <c r="D41" s="16">
+      <c r="G41" s="15">
         <v>1.647</v>
       </c>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16">
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15">
         <v>0.32700000000000001</v>
       </c>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16">
+      <c r="K41" s="15"/>
+      <c r="L41" s="15">
         <v>0.32700000000000001</v>
       </c>
-      <c r="J41" s="16">
-        <v>0</v>
-      </c>
-      <c r="K41" s="16">
-        <v>0</v>
-      </c>
-      <c r="L41" s="16">
+      <c r="M41" s="15">
+        <v>0</v>
+      </c>
+      <c r="N41" s="15">
+        <v>0</v>
+      </c>
+      <c r="O41" s="15">
         <v>0.20397084300000001</v>
       </c>
-      <c r="M41" s="16">
-        <v>0</v>
-      </c>
-      <c r="N41" s="16">
-        <v>0</v>
-      </c>
-      <c r="O41" s="16">
+      <c r="P41" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="15">
+        <v>0</v>
+      </c>
+      <c r="R41" s="15">
         <v>6.1310000000000002</v>
       </c>
-      <c r="P41" s="16">
+      <c r="S41" s="15">
         <v>5.69</v>
       </c>
-      <c r="Q41" s="17">
+      <c r="T41" s="16">
         <v>7.5</v>
       </c>
-      <c r="R41" s="15" t="s">
+      <c r="U41" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="S41" s="15">
+      <c r="V41" s="14">
         <v>1.24</v>
       </c>
-      <c r="T41" s="15" t="s">
+      <c r="W41" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U41" s="15">
+      <c r="X41" s="14">
         <v>30</v>
       </c>
-      <c r="V41" s="15" t="s">
+      <c r="Y41" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W41" s="15">
+      <c r="Z41" s="14">
         <v>2.4406000000000001E-2</v>
       </c>
-      <c r="X41" s="15">
+      <c r="AA41" s="27">
         <v>0.39887628600000002</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="15" customFormat="1">
-      <c r="A42" s="3" t="s">
+    <row r="42" spans="1:27" s="14" customFormat="1">
+      <c r="A42" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F42" s="27">
         <v>0.1</v>
       </c>
-      <c r="D42" s="16">
+      <c r="G42" s="15">
         <v>1.4790000000000001</v>
       </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16">
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15">
         <v>2.919</v>
       </c>
-      <c r="I42" s="16">
+      <c r="L42" s="15">
         <v>2.919</v>
       </c>
-      <c r="J42" s="16">
+      <c r="M42" s="15">
         <v>6.4434642E-2</v>
       </c>
-      <c r="K42" s="16">
-        <v>0</v>
-      </c>
-      <c r="L42" s="16">
+      <c r="N42" s="15">
+        <v>0</v>
+      </c>
+      <c r="O42" s="15">
         <v>0.16559933199999999</v>
       </c>
-      <c r="M42" s="16">
-        <v>0</v>
-      </c>
-      <c r="N42" s="16">
+      <c r="P42" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="15">
         <v>4.8736990000000004E-3</v>
       </c>
-      <c r="O42" s="16">
+      <c r="R42" s="15">
         <v>4.7869999999999999</v>
       </c>
-      <c r="P42" s="16">
+      <c r="S42" s="15">
         <v>4.5609999999999999</v>
       </c>
-      <c r="Q42" s="17">
+      <c r="T42" s="16">
         <v>7.5</v>
       </c>
-      <c r="R42" s="15" t="s">
+      <c r="U42" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="S42" s="15">
+      <c r="V42" s="14">
         <v>9.81</v>
       </c>
-      <c r="T42" s="15" t="s">
+      <c r="W42" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U42" s="15">
+      <c r="X42" s="14">
         <v>3</v>
       </c>
-      <c r="V42" s="15" t="s">
+      <c r="Y42" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W42" s="15">
+      <c r="Z42" s="14">
         <v>2.9215999999999999E-2</v>
       </c>
-      <c r="X42" s="15">
+      <c r="AA42" s="27">
         <v>0.32085182099999998</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="15" customFormat="1">
-      <c r="A43" s="3" t="s">
+    <row r="43" spans="1:27" s="14" customFormat="1">
+      <c r="A43" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F43" s="27">
         <v>0.1</v>
       </c>
-      <c r="D43" s="16">
+      <c r="G43" s="15">
         <v>1.633</v>
       </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16">
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15">
         <v>3.2</v>
       </c>
-      <c r="I43" s="16">
+      <c r="L43" s="15">
         <v>3.2</v>
       </c>
-      <c r="J43" s="16">
-        <v>0</v>
-      </c>
-      <c r="K43" s="16">
-        <v>0</v>
-      </c>
-      <c r="L43" s="16">
+      <c r="M43" s="15">
+        <v>0</v>
+      </c>
+      <c r="N43" s="15">
+        <v>0</v>
+      </c>
+      <c r="O43" s="15">
         <v>0.156217087</v>
       </c>
-      <c r="M43" s="16">
-        <v>0</v>
-      </c>
-      <c r="N43" s="16">
-        <v>0</v>
-      </c>
-      <c r="O43" s="16">
+      <c r="P43" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="15">
+        <v>0</v>
+      </c>
+      <c r="R43" s="15">
         <v>5.1379999999999999</v>
       </c>
-      <c r="P43" s="16">
+      <c r="S43" s="15">
         <v>4.9089999999999998</v>
       </c>
-      <c r="Q43" s="17">
+      <c r="T43" s="16">
         <v>7.5</v>
       </c>
-      <c r="R43" s="15" t="s">
+      <c r="U43" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="S43" s="15">
+      <c r="V43" s="14">
         <v>9.81</v>
       </c>
-      <c r="T43" s="15" t="s">
+      <c r="W43" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U43" s="15">
+      <c r="X43" s="14">
         <v>3</v>
       </c>
-      <c r="V43" s="15" t="s">
+      <c r="Y43" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W43" s="15">
+      <c r="Z43" s="14">
         <v>3.4738999999999999E-2</v>
       </c>
-      <c r="X43" s="15">
+      <c r="AA43" s="27">
         <v>0.41866785699999998</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="15" customFormat="1">
-      <c r="A44" s="3" t="s">
+    <row r="44" spans="1:27" s="14" customFormat="1">
+      <c r="A44" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F44" s="27">
         <v>0.1</v>
       </c>
-      <c r="D44" s="16">
+      <c r="G44" s="15">
         <v>1.571</v>
       </c>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16">
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15">
         <v>3.0830000000000002</v>
       </c>
-      <c r="I44" s="16">
+      <c r="L44" s="15">
         <v>3.0830000000000002</v>
       </c>
-      <c r="J44" s="16">
+      <c r="M44" s="15">
         <v>6.4504826000000001E-2</v>
       </c>
-      <c r="K44" s="16">
-        <v>0</v>
-      </c>
-      <c r="L44" s="16">
+      <c r="N44" s="15">
+        <v>0</v>
+      </c>
+      <c r="O44" s="15">
         <v>0.15037355499999999</v>
       </c>
-      <c r="M44" s="16">
-        <v>0</v>
-      </c>
-      <c r="N44" s="16">
+      <c r="P44" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="15">
         <v>5.596462E-3</v>
       </c>
-      <c r="O44" s="16">
+      <c r="R44" s="15">
         <v>4.9610000000000003</v>
       </c>
-      <c r="P44" s="16">
+      <c r="S44" s="15">
         <v>4.5490000000000004</v>
       </c>
-      <c r="Q44" s="17">
+      <c r="T44" s="16">
         <v>7.5</v>
       </c>
-      <c r="R44" s="15" t="s">
+      <c r="U44" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="S44" s="15">
+      <c r="V44" s="14">
         <v>9.81</v>
       </c>
-      <c r="T44" s="15" t="s">
+      <c r="W44" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="U44" s="15">
+      <c r="X44" s="14">
         <v>3</v>
       </c>
-      <c r="V44" s="15" t="s">
+      <c r="Y44" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W44" s="15">
+      <c r="Z44" s="14">
         <v>3.0641000000000002E-2</v>
       </c>
-      <c r="X44" s="15">
+      <c r="AA44" s="27">
         <v>0.33150882100000001</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="15" customFormat="1">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:27" s="14" customFormat="1">
+      <c r="A45" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F45" s="27">
         <v>0.1</v>
       </c>
-      <c r="D45" s="16">
+      <c r="G45" s="15">
         <v>1.4510000000000001</v>
       </c>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16">
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15">
         <v>0.29199999999999998</v>
       </c>
-      <c r="I45" s="16">
+      <c r="L45" s="15">
         <v>0.29199999999999998</v>
       </c>
-      <c r="J45" s="16">
+      <c r="M45" s="15">
         <v>0.16597783599999999</v>
       </c>
-      <c r="K45" s="16">
+      <c r="N45" s="15">
         <v>6.6479359000000002E-2</v>
       </c>
-      <c r="L45" s="16">
+      <c r="O45" s="15">
         <v>0.60819290000000004</v>
       </c>
-      <c r="M45" s="16">
-        <v>0</v>
-      </c>
-      <c r="N45" s="16">
+      <c r="P45" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="15">
         <v>2.5725250000000002E-2</v>
       </c>
-      <c r="O45" s="16">
+      <c r="R45" s="15">
         <v>4.18</v>
       </c>
-      <c r="P45" s="16">
+      <c r="S45" s="15">
         <v>4.0129999999999999</v>
       </c>
-      <c r="Q45" s="17">
+      <c r="T45" s="16">
         <v>7.5</v>
       </c>
-      <c r="R45" s="15" t="s">
+      <c r="U45" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="S45" s="15">
+      <c r="V45" s="14">
         <v>0.98</v>
       </c>
-      <c r="T45" s="15" t="s">
+      <c r="W45" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U45" s="15">
+      <c r="X45" s="14">
         <v>30</v>
       </c>
-      <c r="V45" s="15" t="s">
+      <c r="Y45" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W45" s="15">
+      <c r="Z45" s="14">
         <v>2.4761999999999999E-2</v>
       </c>
-      <c r="X45" s="15">
+      <c r="AA45" s="27">
         <v>0.43998185699999998</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="15" customFormat="1">
-      <c r="A46" s="3" t="s">
+    <row r="46" spans="1:27" s="14" customFormat="1">
+      <c r="A46" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E46" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F46" s="27">
         <v>0.1</v>
       </c>
-      <c r="D46" s="16">
+      <c r="G46" s="15">
         <v>1.7090000000000001</v>
       </c>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16">
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15">
         <v>0.33900000000000002</v>
       </c>
-      <c r="I46" s="16">
+      <c r="L46" s="15">
         <v>0.33900000000000002</v>
       </c>
-      <c r="J46" s="16">
+      <c r="M46" s="15">
         <v>6.0174350000000001E-2</v>
       </c>
-      <c r="K46" s="16">
+      <c r="N46" s="15">
         <v>7.8079274000000004E-2</v>
       </c>
-      <c r="L46" s="16">
+      <c r="O46" s="15">
         <v>0.66867871400000001</v>
       </c>
-      <c r="M46" s="16">
-        <v>0</v>
-      </c>
-      <c r="N46" s="16">
+      <c r="P46" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="15">
         <v>3.5868012999999997E-2</v>
       </c>
-      <c r="O46" s="16">
+      <c r="R46" s="15">
         <v>4.9020000000000001</v>
       </c>
-      <c r="P46" s="16">
+      <c r="S46" s="15">
         <v>4.45</v>
       </c>
-      <c r="Q46" s="17">
+      <c r="T46" s="16">
         <v>7.5</v>
       </c>
-      <c r="R46" s="15" t="s">
+      <c r="U46" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="S46" s="15">
+      <c r="V46" s="14">
         <v>0.98</v>
       </c>
-      <c r="T46" s="15" t="s">
+      <c r="W46" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U46" s="15">
+      <c r="X46" s="14">
         <v>30</v>
       </c>
-      <c r="V46" s="15" t="s">
+      <c r="Y46" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W46" s="15">
+      <c r="Z46" s="14">
         <v>2.1912000000000001E-2</v>
       </c>
-      <c r="X46" s="15">
+      <c r="AA46" s="27">
         <v>0.448355214</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="15" customFormat="1">
-      <c r="A47" s="3" t="s">
+    <row r="47" spans="1:27" s="14" customFormat="1">
+      <c r="A47" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F47" s="27">
         <v>0.1</v>
       </c>
-      <c r="D47" s="16">
+      <c r="G47" s="15">
         <v>1.6220000000000001</v>
       </c>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16">
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15">
         <v>0.32900000000000001</v>
       </c>
-      <c r="I47" s="16">
+      <c r="L47" s="15">
         <v>0.32900000000000001</v>
       </c>
-      <c r="J47" s="16">
+      <c r="M47" s="15">
         <v>0.18362290100000001</v>
       </c>
-      <c r="K47" s="16">
+      <c r="N47" s="15">
         <v>0.16825845</v>
       </c>
-      <c r="L47" s="16">
+      <c r="O47" s="15">
         <v>0.92271634599999997</v>
       </c>
-      <c r="M47" s="16">
-        <v>0</v>
-      </c>
-      <c r="N47" s="16">
+      <c r="P47" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="15">
         <v>4.8272586999999999E-2</v>
       </c>
-      <c r="O47" s="16">
+      <c r="R47" s="15">
         <v>4.5620000000000003</v>
       </c>
-      <c r="P47" s="16">
+      <c r="S47" s="15">
         <v>4.2300000000000004</v>
       </c>
-      <c r="Q47" s="17">
+      <c r="T47" s="16">
         <v>7.5</v>
       </c>
-      <c r="R47" s="15" t="s">
+      <c r="U47" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="S47" s="15">
+      <c r="V47" s="14">
         <v>0.98</v>
       </c>
-      <c r="T47" s="15" t="s">
+      <c r="W47" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="U47" s="15">
+      <c r="X47" s="14">
         <v>30</v>
       </c>
-      <c r="V47" s="15" t="s">
+      <c r="Y47" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="W47" s="15">
+      <c r="Z47" s="14">
         <v>2.4761999999999999E-2</v>
       </c>
-      <c r="X47" s="15">
+      <c r="AA47" s="27">
         <v>0.42361575000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="22" customFormat="1">
-      <c r="A48" s="21" t="s">
+    <row r="48" spans="1:27" s="21" customFormat="1" hidden="1">
+      <c r="A48" s="20" t="s">
         <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="28">
         <v>0.1</v>
       </c>
-      <c r="Q48" s="23"/>
-    </row>
-    <row r="49" spans="1:17" s="7" customFormat="1">
-      <c r="A49" s="4" t="s">
+      <c r="T48" s="22"/>
+    </row>
+    <row r="49" spans="1:23" s="6" customFormat="1">
+      <c r="A49" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F49" s="4">
         <v>0.40653850000000002</v>
       </c>
-      <c r="D49" s="6">
+      <c r="G49" s="5">
         <v>-13.20185</v>
       </c>
-      <c r="J49" s="6">
+      <c r="M49" s="5">
         <v>15.979100000000001</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" s="7" customFormat="1">
-      <c r="A50" s="4" t="s">
+      <c r="U49" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="W49" s="39"/>
+    </row>
+    <row r="50" spans="1:23" s="6" customFormat="1">
+      <c r="A50" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="4">
         <v>0.44837779999999999</v>
       </c>
-      <c r="D50" s="6">
+      <c r="G50" s="5">
         <v>-12.97245</v>
       </c>
-      <c r="J50" s="6">
+      <c r="M50" s="5">
         <v>17.642130000000002</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" s="7" customFormat="1">
-      <c r="A51" s="4" t="s">
+      <c r="U50" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="W50" s="39"/>
+    </row>
+    <row r="51" spans="1:23" s="6" customFormat="1">
+      <c r="A51" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="F51" s="4">
         <v>0.32723469999999999</v>
       </c>
-      <c r="D51" s="6">
+      <c r="G51" s="5">
         <v>-18.39499</v>
       </c>
-      <c r="J51" s="6">
+      <c r="M51" s="5">
         <v>27.157050000000002</v>
       </c>
-      <c r="N51" s="5">
+      <c r="Q51" s="4">
         <v>3.6701839999999999</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" s="7" customFormat="1">
-      <c r="A52" s="4" t="s">
+      <c r="U51" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="W51" s="39"/>
+    </row>
+    <row r="52" spans="1:23" s="6" customFormat="1">
+      <c r="A52" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E52" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F52" s="4">
         <v>0.32866410000000001</v>
       </c>
-      <c r="D52" s="6">
+      <c r="G52" s="5">
         <v>-14.408200000000001</v>
       </c>
-      <c r="J52" s="6">
+      <c r="M52" s="5">
         <v>22.896090000000001</v>
       </c>
-      <c r="N52" s="5">
+      <c r="Q52" s="4">
         <v>1.9558949999999999</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" s="12" customFormat="1">
+      <c r="U52" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="W52" s="39"/>
+    </row>
+    <row r="53" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A53" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C53" s="18">
+      <c r="C53" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="17">
         <v>0.1</v>
       </c>
-      <c r="Q53" s="11"/>
-    </row>
-    <row r="54" spans="1:17" s="12" customFormat="1">
+      <c r="T53" s="10"/>
+    </row>
+    <row r="54" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A54" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C54" s="18">
+      <c r="C54" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="17">
         <v>0.1</v>
       </c>
-      <c r="E54" s="18"/>
-      <c r="Q54" s="11"/>
-    </row>
-    <row r="55" spans="1:17" s="12" customFormat="1">
+      <c r="H54" s="17"/>
+      <c r="T54" s="10"/>
+    </row>
+    <row r="55" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C55" s="18">
+      <c r="C55" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="17">
         <v>0.1</v>
       </c>
-      <c r="Q55" s="11"/>
-    </row>
-    <row r="56" spans="1:17" s="12" customFormat="1">
+      <c r="T55" s="10"/>
+    </row>
+    <row r="56" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A56" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="18">
+      <c r="C56" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="17">
         <v>0.1</v>
       </c>
-      <c r="Q56" s="11"/>
-    </row>
-    <row r="57" spans="1:17" s="12" customFormat="1">
+      <c r="T56" s="10"/>
+    </row>
+    <row r="57" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A57" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C57" s="18"/>
-      <c r="Q57" s="11"/>
-    </row>
-    <row r="58" spans="1:17" s="12" customFormat="1">
+      <c r="C57" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E57" s="1"/>
+      <c r="F57" s="17"/>
+      <c r="T57" s="10"/>
+    </row>
+    <row r="58" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A58" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="18"/>
-      <c r="Q58" s="11"/>
-    </row>
-    <row r="59" spans="1:17" s="12" customFormat="1">
+      <c r="C58" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="17"/>
+      <c r="T58" s="10"/>
+    </row>
+    <row r="59" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A59" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C59" s="18"/>
-      <c r="Q59" s="11"/>
-    </row>
-    <row r="60" spans="1:17" s="12" customFormat="1">
+      <c r="C59" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="17"/>
+      <c r="T59" s="10"/>
+    </row>
+    <row r="60" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A60" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C60" s="18"/>
-      <c r="Q60" s="11"/>
-    </row>
-    <row r="61" spans="1:17" s="12" customFormat="1">
-      <c r="A61" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E60" s="1"/>
+      <c r="F60" s="17"/>
+      <c r="T60" s="10"/>
+    </row>
+    <row r="61" spans="1:23" s="33" customFormat="1" hidden="1">
+      <c r="A61" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="C61" s="18"/>
-      <c r="Q61" s="11"/>
-    </row>
-    <row r="62" spans="1:17" s="12" customFormat="1">
+      <c r="C61" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="32"/>
+      <c r="T61" s="34"/>
+    </row>
+    <row r="62" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A62" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C62" s="18"/>
-      <c r="Q62" s="11"/>
-    </row>
-    <row r="63" spans="1:17" s="12" customFormat="1">
+      <c r="C62" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="17"/>
+      <c r="T62" s="10"/>
+    </row>
+    <row r="63" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A63" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C63" s="18"/>
-      <c r="Q63" s="11"/>
-    </row>
-    <row r="64" spans="1:17" s="12" customFormat="1">
+      <c r="C63" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="17"/>
+      <c r="T63" s="10"/>
+    </row>
+    <row r="64" spans="1:23" s="11" customFormat="1" hidden="1">
       <c r="A64" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C64" s="18"/>
-      <c r="Q64" s="11"/>
-    </row>
-    <row r="65" spans="1:24" s="12" customFormat="1">
+      <c r="C64" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E64" s="1"/>
+      <c r="F64" s="17"/>
+      <c r="T64" s="10"/>
+    </row>
+    <row r="65" spans="1:27" hidden="1">
       <c r="A65" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C65" s="18"/>
-      <c r="Q65" s="11"/>
-    </row>
-    <row r="66" spans="1:24" s="12" customFormat="1">
+      <c r="C65" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E65" s="1"/>
+      <c r="U65" s="11"/>
+      <c r="W65" s="11"/>
+      <c r="AA65" s="11"/>
+    </row>
+    <row r="66" spans="1:27" hidden="1">
       <c r="A66" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C66" s="18"/>
-      <c r="Q66" s="11"/>
-    </row>
-    <row r="67" spans="1:24" s="12" customFormat="1">
-      <c r="A67" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E66" s="1"/>
+      <c r="U66" s="11"/>
+      <c r="W66" s="11"/>
+      <c r="AA66" s="11"/>
+    </row>
+    <row r="67" spans="1:27" s="33" customFormat="1" hidden="1">
+      <c r="A67" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="C67" s="18"/>
-      <c r="Q67" s="11"/>
-    </row>
-    <row r="68" spans="1:24" s="12" customFormat="1">
-      <c r="A68" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="32"/>
+      <c r="T67" s="34"/>
+    </row>
+    <row r="68" spans="1:27" s="33" customFormat="1" hidden="1">
+      <c r="A68" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="C68" s="18"/>
-      <c r="Q68" s="11"/>
-    </row>
-    <row r="69" spans="1:24" s="19" customFormat="1">
-      <c r="A69" s="8" t="s">
+      <c r="C68" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D68" s="31"/>
+      <c r="E68" s="31"/>
+      <c r="F68" s="32"/>
+      <c r="T68" s="34"/>
+    </row>
+    <row r="69" spans="1:27" s="18" customFormat="1">
+      <c r="A69" s="7" t="s">
         <v>112</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C69" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E69" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F69" s="29">
         <v>2.7E-2</v>
       </c>
-      <c r="D69" s="26">
+      <c r="G69" s="25">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="E69" s="26">
+      <c r="H69" s="25">
         <v>-0.151308114750691</v>
       </c>
-      <c r="J69" s="26">
-        <v>0</v>
-      </c>
-      <c r="O69" s="26">
+      <c r="M69" s="25">
+        <v>0</v>
+      </c>
+      <c r="R69" s="25">
         <v>0.878</v>
       </c>
-      <c r="P69" s="20">
+      <c r="S69" s="19">
         <v>0.86358170086251695</v>
       </c>
-      <c r="R69" s="19" t="s">
+      <c r="U69" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="T69" s="19" t="s">
+      <c r="W69" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="X69" s="19">
+      <c r="AA69" s="29">
         <v>0.29899999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:24" s="20" customFormat="1">
-      <c r="A70" s="9" t="s">
+    <row r="70" spans="1:27" s="19" customFormat="1">
+      <c r="A70" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C70" s="31">
+      <c r="C70" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E70" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F70" s="30">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="D70" s="26">
+      <c r="G70" s="25">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="E70" s="26">
+      <c r="H70" s="25">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="J70" s="26">
-        <v>0</v>
-      </c>
-      <c r="O70" s="26">
+      <c r="M70" s="25">
+        <v>0</v>
+      </c>
+      <c r="R70" s="25">
         <v>1.458</v>
       </c>
-      <c r="P70" s="20">
+      <c r="S70" s="19">
         <v>1.4368262739973601</v>
       </c>
-      <c r="R70" s="19" t="s">
+      <c r="U70" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="T70" s="19" t="s">
+      <c r="W70" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="X70" s="20">
+      <c r="AA70" s="30">
         <v>0.312</v>
       </c>
     </row>
-    <row r="71" spans="1:24" s="20" customFormat="1">
-      <c r="A71" s="9" t="s">
+    <row r="71" spans="1:27" s="19" customFormat="1">
+      <c r="A71" s="8" t="s">
         <v>83</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E71" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F71" s="30">
         <v>0.10199999999999999</v>
       </c>
-      <c r="D71" s="26">
+      <c r="G71" s="25">
         <v>-1.171</v>
       </c>
-      <c r="E71" s="26">
+      <c r="H71" s="25">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="J71" s="26">
-        <v>0</v>
-      </c>
-      <c r="O71" s="26">
+      <c r="M71" s="25">
+        <v>0</v>
+      </c>
+      <c r="R71" s="25">
         <v>2.5470000000000002</v>
       </c>
-      <c r="P71" s="20">
+      <c r="S71" s="19">
         <v>2.4905493340587901</v>
       </c>
-      <c r="R71" s="19" t="s">
+      <c r="U71" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="T71" s="19" t="s">
+      <c r="W71" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="X71" s="20">
+      <c r="AA71" s="30">
         <v>0.371</v>
       </c>
     </row>
-    <row r="72" spans="1:24" s="20" customFormat="1">
-      <c r="A72" s="9" t="s">
+    <row r="72" spans="1:27" s="19" customFormat="1">
+      <c r="A72" s="8" t="s">
         <v>84</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E72" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F72" s="30">
         <v>0.152</v>
       </c>
-      <c r="D72" s="26">
+      <c r="G72" s="25">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="E72" s="26">
+      <c r="H72" s="25">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="J72" s="26">
-        <v>0</v>
-      </c>
-      <c r="O72" s="26">
+      <c r="M72" s="25">
+        <v>0</v>
+      </c>
+      <c r="R72" s="25">
         <v>3.81518914277475</v>
       </c>
-      <c r="P72" s="20">
+      <c r="S72" s="19">
         <v>3.855</v>
       </c>
-      <c r="R72" s="19" t="s">
+      <c r="U72" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="T72" s="19" t="s">
+      <c r="W72" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="X72" s="20">
+      <c r="AA72" s="30">
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="73" spans="1:24" s="20" customFormat="1">
-      <c r="A73" s="9" t="s">
+    <row r="73" spans="1:27" s="19" customFormat="1">
+      <c r="A73" s="8" t="s">
         <v>85</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C73" s="31">
+      <c r="C73" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E73" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F73" s="30">
         <v>0.214</v>
       </c>
-      <c r="D73" s="26">
+      <c r="G73" s="25">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="E73" s="26">
+      <c r="H73" s="25">
         <v>-1.22567508688439</v>
       </c>
-      <c r="J73" s="26">
+      <c r="M73" s="25">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="O73" s="26">
+      <c r="R73" s="25">
         <v>5.5949999999999998</v>
       </c>
-      <c r="P73" s="20">
+      <c r="S73" s="19">
         <v>5.4782042149448502</v>
       </c>
-      <c r="R73" s="19" t="s">
+      <c r="U73" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="T73" s="19" t="s">
+      <c r="W73" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="X73" s="20">
+      <c r="AA73" s="30">
         <v>0.32</v>
       </c>
     </row>
-    <row r="74" spans="1:24" s="20" customFormat="1">
-      <c r="A74" s="9" t="s">
+    <row r="74" spans="1:27" s="19" customFormat="1">
+      <c r="A74" s="8" t="s">
         <v>86</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C74" s="31">
+      <c r="C74" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E74" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F74" s="30">
         <v>0.254</v>
       </c>
-      <c r="D74" s="26">
+      <c r="G74" s="25">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="E74" s="26">
+      <c r="H74" s="25">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="J74" s="26">
+      <c r="M74" s="25">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="O74" s="26">
+      <c r="R74" s="25">
         <v>6.484</v>
       </c>
-      <c r="P74" s="20">
+      <c r="S74" s="19">
         <v>6.2489999999999997</v>
       </c>
-      <c r="R74" s="19" t="s">
+      <c r="U74" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="T74" s="19" t="s">
+      <c r="W74" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="X74" s="20">
+      <c r="AA74" s="30">
         <v>0.37799999999999995</v>
       </c>
     </row>
-    <row r="75" spans="1:24" s="20" customFormat="1">
-      <c r="A75" s="9" t="s">
+    <row r="75" spans="1:27" s="19" customFormat="1">
+      <c r="A75" s="8" t="s">
         <v>87</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C75" s="31">
+      <c r="C75" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E75" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F75" s="30">
         <v>0.28399999999999997</v>
       </c>
-      <c r="D75" s="26">
+      <c r="G75" s="25">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="E75" s="26">
+      <c r="H75" s="25">
         <v>-1.47353470842518</v>
       </c>
-      <c r="J75" s="26">
+      <c r="M75" s="25">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="O75" s="26">
+      <c r="R75" s="25">
         <v>8.0890000000000004</v>
       </c>
-      <c r="P75" s="20">
+      <c r="S75" s="19">
         <v>7.9485854277214001</v>
       </c>
-      <c r="R75" s="19" t="s">
+      <c r="U75" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="T75" s="19" t="s">
+      <c r="W75" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="X75" s="20">
+      <c r="AA75" s="30">
         <v>0.39100000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:24" s="20" customFormat="1">
-      <c r="A76" s="9" t="s">
+    <row r="76" spans="1:27" s="19" customFormat="1">
+      <c r="A76" s="8" t="s">
         <v>88</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C76" s="31">
+      <c r="C76" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E76" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F76" s="30">
         <v>0.33400000000000002</v>
       </c>
-      <c r="D76" s="26">
+      <c r="G76" s="25">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="E76" s="26">
+      <c r="H76" s="25">
         <v>-1.99253212300414</v>
       </c>
-      <c r="J76" s="26">
+      <c r="M76" s="25">
         <v>2.0830000000081101</v>
       </c>
-      <c r="O76" s="26">
+      <c r="R76" s="25">
         <v>11.872999999999999</v>
       </c>
-      <c r="P76" s="20">
+      <c r="S76" s="19">
         <v>9.6077296533960403</v>
       </c>
-      <c r="R76" s="19" t="s">
+      <c r="U76" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="T76" s="19" t="s">
+      <c r="W76" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="X76" s="20">
+      <c r="AA76" s="30">
         <v>0.41899999999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:24" s="20" customFormat="1">
-      <c r="A77" s="9" t="s">
+    <row r="77" spans="1:27" s="19" customFormat="1">
+      <c r="A77" s="8" t="s">
         <v>89</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C77" s="31">
+      <c r="C77" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E77" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F77" s="30">
         <v>0.379</v>
       </c>
-      <c r="D77" s="26">
+      <c r="G77" s="25">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="E77" s="26">
+      <c r="H77" s="25">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="J77" s="26">
+      <c r="M77" s="25">
         <v>5.5389999999999997</v>
       </c>
-      <c r="O77" s="26">
+      <c r="R77" s="25">
         <v>14.304133448972699</v>
       </c>
-      <c r="P77" s="20">
+      <c r="S77" s="19">
         <v>8.8979999999999997</v>
       </c>
-      <c r="R77" s="19" t="s">
+      <c r="U77" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="T77" s="19" t="s">
+      <c r="W77" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="X77" s="20">
+      <c r="AA77" s="30">
         <v>0.39100000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:27" hidden="1">
       <c r="A78" s="1" t="s">
         <v>116</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C78" s="18">
+      <c r="C78" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E78" s="1"/>
+      <c r="F78" s="17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="79" spans="1:24">
+      <c r="U78" s="11"/>
+      <c r="W78" s="11"/>
+      <c r="AA78" s="11"/>
+    </row>
+    <row r="79" spans="1:27" hidden="1">
       <c r="A79" s="1" t="s">
         <v>117</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C79" s="18">
+      <c r="C79" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E79" s="1"/>
+      <c r="F79" s="17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="80" spans="1:24">
+      <c r="U79" s="11"/>
+      <c r="W79" s="11"/>
+      <c r="AA79" s="11"/>
+    </row>
+    <row r="80" spans="1:27" hidden="1">
       <c r="A80" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C80" s="18">
+      <c r="C80" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="U80" s="11"/>
+      <c r="W80" s="11"/>
+      <c r="AA80" s="11"/>
+    </row>
+    <row r="81" spans="1:27" hidden="1">
       <c r="A81" s="1" t="s">
         <v>119</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C81" s="18">
+      <c r="C81" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="U81" s="11"/>
+      <c r="W81" s="11"/>
+      <c r="AA81" s="11"/>
+    </row>
+    <row r="82" spans="1:27" hidden="1">
       <c r="A82" s="1" t="s">
         <v>120</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C82" s="18">
+      <c r="C82" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E82" s="1"/>
+      <c r="F82" s="17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="U82" s="11"/>
+      <c r="W82" s="11"/>
+      <c r="AA82" s="11"/>
+    </row>
+    <row r="83" spans="1:27" hidden="1">
       <c r="A83" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C83" s="18">
+      <c r="C83" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E83" s="1"/>
+      <c r="F83" s="17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="U83" s="11"/>
+      <c r="W83" s="11"/>
+      <c r="AA83" s="11"/>
+    </row>
+    <row r="84" spans="1:27" hidden="1">
       <c r="A84" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C84" s="18">
+      <c r="C84" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E84" s="1"/>
+      <c r="F84" s="17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="U84" s="11"/>
+      <c r="W84" s="11"/>
+      <c r="AA84" s="11"/>
+    </row>
+    <row r="85" spans="1:27" hidden="1">
       <c r="A85" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C85" s="18">
+      <c r="C85" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E85" s="1"/>
+      <c r="F85" s="17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="U85" s="11"/>
+      <c r="W85" s="11"/>
+      <c r="AA85" s="11"/>
+    </row>
+    <row r="86" spans="1:27" hidden="1">
       <c r="A86" s="1" t="s">
         <v>124</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C86" s="18">
+      <c r="C86" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E86" s="1"/>
+      <c r="F86" s="17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="U86" s="11"/>
+      <c r="W86" s="11"/>
+      <c r="AA86" s="11"/>
+    </row>
+    <row r="87" spans="1:27" hidden="1">
       <c r="A87" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C87" s="18">
+      <c r="C87" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E87" s="1"/>
+      <c r="F87" s="17">
         <v>0.1</v>
       </c>
+      <c r="U87" s="11"/>
+      <c r="W87" s="11"/>
+      <c r="AA87" s="11"/>
+    </row>
+    <row r="88" spans="1:27">
+      <c r="A88" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E88" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U88" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27">
+      <c r="A89" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U89" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27">
+      <c r="A90" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E90" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U90" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27">
+      <c r="A91" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U91" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27">
+      <c r="A92" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E92" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U92" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27">
+      <c r="A93" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E93" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U93" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27">
+      <c r="A94" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E94" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U94" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27">
+      <c r="A95" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E95" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U95" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27">
+      <c r="A96" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E96" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U96" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27">
+      <c r="A97" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E97" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U97" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27">
+      <c r="A98" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E98" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="U98" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" hidden="1">
+      <c r="A99" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U99" s="11"/>
+      <c r="W99" s="11"/>
+      <c r="AA99" s="11"/>
+    </row>
+    <row r="100" spans="1:27" hidden="1">
+      <c r="A100" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U100" s="11"/>
+      <c r="W100" s="11"/>
+      <c r="AA100" s="11"/>
+    </row>
+    <row r="101" spans="1:27" hidden="1">
+      <c r="A101" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U101" s="11"/>
+      <c r="W101" s="11"/>
+      <c r="AA101" s="11"/>
+    </row>
+    <row r="102" spans="1:27" hidden="1">
+      <c r="A102" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U102" s="11"/>
+      <c r="W102" s="11"/>
+      <c r="AA102" s="11"/>
+    </row>
+    <row r="103" spans="1:27" hidden="1">
+      <c r="A103" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U103" s="11"/>
+      <c r="W103" s="11"/>
+      <c r="AA103" s="11"/>
+    </row>
+    <row r="104" spans="1:27" hidden="1">
+      <c r="A104" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U104" s="11"/>
+      <c r="W104" s="11"/>
+      <c r="AA104" s="11"/>
+    </row>
+    <row r="105" spans="1:27" hidden="1">
+      <c r="A105" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U105" s="11"/>
+      <c r="W105" s="11"/>
+      <c r="AA105" s="11"/>
+    </row>
+    <row r="106" spans="1:27" hidden="1">
+      <c r="A106" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U106" s="11"/>
+      <c r="W106" s="11"/>
+      <c r="AA106" s="11"/>
+    </row>
+    <row r="107" spans="1:27" hidden="1">
+      <c r="A107" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U107" s="11"/>
+      <c r="W107" s="11"/>
+      <c r="AA107" s="11"/>
+    </row>
+    <row r="108" spans="1:27" hidden="1">
+      <c r="A108" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U108" s="11"/>
+      <c r="W108" s="11"/>
+      <c r="AA108" s="11"/>
+    </row>
+    <row r="109" spans="1:27" hidden="1">
+      <c r="A109" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U109" s="11"/>
+      <c r="W109" s="11"/>
+      <c r="AA109" s="11"/>
+    </row>
+    <row r="110" spans="1:27" hidden="1">
+      <c r="A110" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U110" s="11"/>
+      <c r="W110" s="11"/>
+      <c r="AA110" s="11"/>
+    </row>
+    <row r="111" spans="1:27" hidden="1">
+      <c r="A111" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U111" s="11"/>
+      <c r="W111" s="11"/>
+      <c r="AA111" s="11"/>
+    </row>
+    <row r="112" spans="1:27" hidden="1">
+      <c r="A112" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U112" s="11"/>
+      <c r="W112" s="11"/>
+      <c r="AA112" s="11"/>
+    </row>
+    <row r="113" spans="1:27" hidden="1">
+      <c r="A113" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U113" s="11"/>
+      <c r="W113" s="11"/>
+      <c r="AA113" s="11"/>
+    </row>
+    <row r="114" spans="1:27" hidden="1">
+      <c r="A114" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U114" s="11"/>
+      <c r="W114" s="11"/>
+      <c r="AA114" s="11"/>
+    </row>
+    <row r="115" spans="1:27" hidden="1">
+      <c r="A115" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U115" s="11"/>
+      <c r="W115" s="11"/>
+      <c r="AA115" s="11"/>
+    </row>
+    <row r="116" spans="1:27" hidden="1">
+      <c r="A116" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U116" s="11"/>
+      <c r="W116" s="11"/>
+      <c r="AA116" s="11"/>
+    </row>
+    <row r="117" spans="1:27" hidden="1">
+      <c r="A117" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U117" s="11"/>
+      <c r="W117" s="11"/>
+      <c r="AA117" s="11"/>
+    </row>
+    <row r="118" spans="1:27" hidden="1">
+      <c r="A118" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U118" s="11"/>
+      <c r="W118" s="11"/>
+      <c r="AA118" s="11"/>
+    </row>
+    <row r="119" spans="1:27" hidden="1">
+      <c r="A119" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U119" s="11"/>
+      <c r="W119" s="11"/>
+      <c r="AA119" s="11"/>
+    </row>
+    <row r="120" spans="1:27" hidden="1">
+      <c r="A120" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U120" s="11"/>
+      <c r="W120" s="11"/>
+      <c r="AA120" s="11"/>
+    </row>
+    <row r="121" spans="1:27" hidden="1">
+      <c r="A121" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U121" s="11"/>
+      <c r="W121" s="11"/>
+      <c r="AA121" s="11"/>
+    </row>
+    <row r="122" spans="1:27" hidden="1">
+      <c r="A122" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U122" s="11"/>
+      <c r="W122" s="11"/>
+      <c r="AA122" s="11"/>
+    </row>
+    <row r="123" spans="1:27" hidden="1">
+      <c r="A123" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U123" s="11"/>
+      <c r="W123" s="11"/>
+      <c r="AA123" s="11"/>
+    </row>
+    <row r="124" spans="1:27" hidden="1">
+      <c r="A124" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U124" s="11"/>
+      <c r="W124" s="11"/>
+      <c r="AA124" s="11"/>
+    </row>
+    <row r="125" spans="1:27" hidden="1">
+      <c r="A125" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U125" s="11"/>
+      <c r="W125" s="11"/>
+      <c r="AA125" s="11"/>
+    </row>
+    <row r="126" spans="1:27" hidden="1">
+      <c r="A126" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U126" s="11"/>
+      <c r="W126" s="11"/>
+      <c r="AA126" s="11"/>
+    </row>
+    <row r="127" spans="1:27" hidden="1">
+      <c r="A127" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U127" s="11"/>
+      <c r="W127" s="11"/>
+      <c r="AA127" s="11"/>
+    </row>
+    <row r="128" spans="1:27" hidden="1">
+      <c r="A128" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U128" s="11"/>
+      <c r="W128" s="11"/>
+      <c r="AA128" s="11"/>
+    </row>
+    <row r="129" spans="1:27" hidden="1">
+      <c r="A129" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="B129" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D129" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="E129" s="38"/>
+      <c r="F129" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="U129" s="11"/>
+      <c r="W129" s="11"/>
+      <c r="AA129" s="11"/>
+    </row>
+    <row r="130" spans="1:27" hidden="1">
+      <c r="A130" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="B130" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D130" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="E130" s="38"/>
+      <c r="F130" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="U130" s="11"/>
+      <c r="W130" s="11"/>
+      <c r="AA130" s="11"/>
+    </row>
+    <row r="131" spans="1:27" hidden="1">
+      <c r="A131" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="B131" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D131" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="E131" s="38"/>
+      <c r="F131" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="U131" s="11"/>
+      <c r="W131" s="11"/>
+      <c r="AA131" s="11"/>
+    </row>
+    <row r="132" spans="1:27" hidden="1">
+      <c r="A132" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="B132" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D132" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="E132" s="38"/>
+      <c r="F132" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="U132" s="11"/>
+      <c r="W132" s="11"/>
+      <c r="AA132" s="11"/>
+    </row>
+    <row r="133" spans="1:27" hidden="1">
+      <c r="A133" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="B133" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D133" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="E133" s="38"/>
+      <c r="F133" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="U133" s="11"/>
+      <c r="W133" s="11"/>
+      <c r="AA133" s="11"/>
+    </row>
+    <row r="134" spans="1:27" hidden="1">
+      <c r="A134" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="B134" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D134" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="E134" s="38"/>
+      <c r="F134" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="U134" s="11"/>
+      <c r="W134" s="11"/>
+      <c r="AA134" s="11"/>
+    </row>
+    <row r="135" spans="1:27" hidden="1">
+      <c r="A135" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="B135" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D135" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="E135" s="38"/>
+      <c r="F135" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="U135" s="11"/>
+      <c r="W135" s="11"/>
+      <c r="AA135" s="11"/>
+    </row>
+    <row r="136" spans="1:27" hidden="1">
+      <c r="A136" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="B136" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D136" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="E136" s="38"/>
+      <c r="F136" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="U136" s="11"/>
+      <c r="W136" s="11"/>
+      <c r="AA136" s="11"/>
+    </row>
+    <row r="137" spans="1:27">
+      <c r="U137" s="18" t="s">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AC136" xr:uid="{7E8F22EE-2E06-6741-B451-D4EA064EAB2E}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="YES"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -5183,7 +7009,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>91</v>
       </c>
       <c r="C1" t="s">
@@ -5225,22 +7051,22 @@
       <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="S1" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="T1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="V1" s="11" t="s">
         <v>96</v>
       </c>
     </row>
@@ -5248,7 +7074,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="14">
         <v>0.05</v>
       </c>
       <c r="C2">
@@ -5281,22 +7107,22 @@
       <c r="O2">
         <v>2.3620000000000001</v>
       </c>
-      <c r="Q2" s="15">
+      <c r="Q2" s="14">
         <v>0.27251471399999999</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S2" s="15">
+      <c r="S2" s="14">
         <v>0.5</v>
       </c>
-      <c r="T2" s="15" t="s">
+      <c r="T2" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U2" s="15">
+      <c r="U2" s="14">
         <v>30</v>
       </c>
-      <c r="V2" s="15" t="s">
+      <c r="V2" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5304,7 +7130,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="14">
         <v>0.05</v>
       </c>
       <c r="C3">
@@ -5337,22 +7163,22 @@
       <c r="O3">
         <v>2.2759999999999998</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="14">
         <v>0.25082010700000001</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="14">
         <v>0.5</v>
       </c>
-      <c r="T3" s="15" t="s">
+      <c r="T3" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U3" s="15">
+      <c r="U3" s="14">
         <v>30</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="V3" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5360,7 +7186,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="14">
         <v>0.05</v>
       </c>
       <c r="C4">
@@ -5393,190 +7219,190 @@
       <c r="O4">
         <v>1.6240000000000001</v>
       </c>
-      <c r="Q4" s="15">
+      <c r="Q4" s="14">
         <v>0.26109650000000001</v>
       </c>
-      <c r="R4" s="15" t="s">
+      <c r="R4" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S4" s="15">
+      <c r="S4" s="14">
         <v>0.5</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U4" s="15">
+      <c r="U4" s="14">
         <v>30</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="14" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="24" customFormat="1">
-      <c r="A5" s="24">
+    <row r="5" spans="1:22" s="23" customFormat="1">
+      <c r="A5" s="23">
         <v>4</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="24">
         <v>0.1</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="23">
         <v>1.18</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="23">
         <v>2.2029999999999998</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="23">
         <v>2.2029999999999998</v>
       </c>
-      <c r="I5" s="24">
-        <v>0</v>
-      </c>
-      <c r="J5" s="24">
-        <v>0</v>
-      </c>
-      <c r="K5" s="24">
+      <c r="I5" s="23">
+        <v>0</v>
+      </c>
+      <c r="J5" s="23">
+        <v>0</v>
+      </c>
+      <c r="K5" s="23">
         <v>1.2795499999999999E-4</v>
       </c>
-      <c r="L5" s="24">
-        <v>0</v>
-      </c>
-      <c r="M5" s="24">
-        <v>0</v>
-      </c>
-      <c r="N5" s="24">
+      <c r="L5" s="23">
+        <v>0</v>
+      </c>
+      <c r="M5" s="23">
+        <v>0</v>
+      </c>
+      <c r="N5" s="23">
         <v>1.93</v>
       </c>
-      <c r="O5" s="24">
+      <c r="O5" s="23">
         <v>2.44</v>
       </c>
-      <c r="Q5" s="25">
+      <c r="Q5" s="24">
         <v>0.35967375000000001</v>
       </c>
-      <c r="R5" s="25" t="s">
+      <c r="R5" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="S5" s="25">
+      <c r="S5" s="24">
         <v>5</v>
       </c>
-      <c r="T5" s="25" t="s">
+      <c r="T5" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="U5" s="25">
+      <c r="U5" s="24">
         <v>3</v>
       </c>
-      <c r="V5" s="25" t="s">
+      <c r="V5" s="24" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="24" customFormat="1">
-      <c r="A6" s="24">
+    <row r="6" spans="1:22" s="23" customFormat="1">
+      <c r="A6" s="23">
         <v>5</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="24">
         <v>0.1</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <v>1.127</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <v>2.0979999999999999</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="23">
         <v>2.0979999999999999</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="23">
         <v>1.6766474999999999E-2</v>
       </c>
-      <c r="J6" s="24">
-        <v>0</v>
-      </c>
-      <c r="K6" s="24">
+      <c r="J6" s="23">
+        <v>0</v>
+      </c>
+      <c r="K6" s="23">
         <v>1.5726999999999999E-4</v>
       </c>
-      <c r="L6" s="24">
-        <v>0</v>
-      </c>
-      <c r="M6" s="24">
-        <v>0</v>
-      </c>
-      <c r="N6" s="24">
+      <c r="L6" s="23">
+        <v>0</v>
+      </c>
+      <c r="M6" s="23">
+        <v>0</v>
+      </c>
+      <c r="N6" s="23">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O6" s="24">
+      <c r="O6" s="23">
         <v>2.39</v>
       </c>
-      <c r="Q6" s="25">
+      <c r="Q6" s="24">
         <v>0.377942893</v>
       </c>
-      <c r="R6" s="25" t="s">
+      <c r="R6" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="S6" s="25">
+      <c r="S6" s="24">
         <v>5</v>
       </c>
-      <c r="T6" s="25" t="s">
+      <c r="T6" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="U6" s="25">
+      <c r="U6" s="24">
         <v>3</v>
       </c>
-      <c r="V6" s="25" t="s">
+      <c r="V6" s="24" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="24" customFormat="1">
-      <c r="A7" s="24">
+    <row r="7" spans="1:22" s="23" customFormat="1">
+      <c r="A7" s="23">
         <v>6</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="24">
         <v>0.1</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="23">
         <v>1.0980000000000001</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="23">
         <v>2.0550000000000002</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="23">
         <v>2.0550000000000002</v>
       </c>
-      <c r="I7" s="24">
-        <v>0</v>
-      </c>
-      <c r="J7" s="24">
-        <v>0</v>
-      </c>
-      <c r="K7" s="24">
+      <c r="I7" s="23">
+        <v>0</v>
+      </c>
+      <c r="J7" s="23">
+        <v>0</v>
+      </c>
+      <c r="K7" s="23">
         <v>1.3422099999999999E-4</v>
       </c>
-      <c r="L7" s="24">
-        <v>0</v>
-      </c>
-      <c r="M7" s="24">
-        <v>0</v>
-      </c>
-      <c r="N7" s="24">
+      <c r="L7" s="23">
+        <v>0</v>
+      </c>
+      <c r="M7" s="23">
+        <v>0</v>
+      </c>
+      <c r="N7" s="23">
         <v>1.97</v>
       </c>
-      <c r="O7" s="24">
+      <c r="O7" s="23">
         <v>2.1800000000000002</v>
       </c>
-      <c r="Q7" s="25">
+      <c r="Q7" s="24">
         <v>0.33645671399999999</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="R7" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="S7" s="25">
+      <c r="S7" s="24">
         <v>5</v>
       </c>
-      <c r="T7" s="25" t="s">
+      <c r="T7" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="U7" s="25">
+      <c r="U7" s="24">
         <v>3</v>
       </c>
-      <c r="V7" s="25" t="s">
+      <c r="V7" s="24" t="s">
         <v>104</v>
       </c>
     </row>
@@ -5584,7 +7410,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>0.1</v>
       </c>
       <c r="C8">
@@ -5617,22 +7443,22 @@
       <c r="O8">
         <v>3.6160000000000001</v>
       </c>
-      <c r="Q8" s="15">
+      <c r="Q8" s="14">
         <v>0.209333929</v>
       </c>
-      <c r="R8" s="15" t="s">
+      <c r="R8" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S8" s="14">
         <v>0.5</v>
       </c>
-      <c r="T8" s="15" t="s">
+      <c r="T8" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U8" s="15">
+      <c r="U8" s="14">
         <v>30</v>
       </c>
-      <c r="V8" s="15" t="s">
+      <c r="V8" s="14" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5640,7 +7466,7 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>0.1</v>
       </c>
       <c r="C9">
@@ -5673,22 +7499,22 @@
       <c r="O9">
         <v>3.5219999999999998</v>
       </c>
-      <c r="Q9" s="15">
+      <c r="Q9" s="14">
         <v>0.22151335699999999</v>
       </c>
-      <c r="R9" s="15" t="s">
+      <c r="R9" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S9" s="15">
+      <c r="S9" s="14">
         <v>0.5</v>
       </c>
-      <c r="T9" s="15" t="s">
+      <c r="T9" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U9" s="15">
+      <c r="U9" s="14">
         <v>30</v>
       </c>
-      <c r="V9" s="15" t="s">
+      <c r="V9" s="14" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5696,7 +7522,7 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>0.1</v>
       </c>
       <c r="C10">
@@ -5729,22 +7555,22 @@
       <c r="O10">
         <v>3.8239999999999998</v>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q10" s="14">
         <v>0.24587221400000001</v>
       </c>
-      <c r="R10" s="15" t="s">
+      <c r="R10" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S10" s="15">
+      <c r="S10" s="14">
         <v>0.5</v>
       </c>
-      <c r="T10" s="15" t="s">
+      <c r="T10" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U10" s="15">
+      <c r="U10" s="14">
         <v>30</v>
       </c>
-      <c r="V10" s="15" t="s">
+      <c r="V10" s="14" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5752,7 +7578,7 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="14">
         <v>0.13</v>
       </c>
       <c r="C11">
@@ -5785,22 +7611,22 @@
       <c r="O11">
         <v>5.2519999999999998</v>
       </c>
-      <c r="Q11" s="15">
+      <c r="Q11" s="14">
         <v>0.30372450000000001</v>
       </c>
-      <c r="R11" s="15" t="s">
+      <c r="R11" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S11" s="15">
+      <c r="S11" s="14">
         <v>0.5</v>
       </c>
-      <c r="T11" s="15" t="s">
+      <c r="T11" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U11" s="15">
+      <c r="U11" s="14">
         <v>30</v>
       </c>
-      <c r="V11" s="15" t="s">
+      <c r="V11" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5808,7 +7634,7 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <v>0.13</v>
       </c>
       <c r="C12">
@@ -5841,22 +7667,22 @@
       <c r="O12">
         <v>4.5460000000000003</v>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="14">
         <v>0.25690982099999998</v>
       </c>
-      <c r="R12" s="15" t="s">
+      <c r="R12" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S12" s="15">
+      <c r="S12" s="14">
         <v>0.5</v>
       </c>
-      <c r="T12" s="15" t="s">
+      <c r="T12" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U12" s="15">
+      <c r="U12" s="14">
         <v>30</v>
       </c>
-      <c r="V12" s="15" t="s">
+      <c r="V12" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5864,7 +7690,7 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="14">
         <v>0.13</v>
       </c>
       <c r="C13">
@@ -5897,22 +7723,22 @@
       <c r="O13">
         <v>5.07</v>
       </c>
-      <c r="Q13" s="15">
+      <c r="Q13" s="14">
         <v>0.26642500000000002</v>
       </c>
-      <c r="R13" s="15" t="s">
+      <c r="R13" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S13" s="15">
+      <c r="S13" s="14">
         <v>0.5</v>
       </c>
-      <c r="T13" s="15" t="s">
+      <c r="T13" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U13" s="15">
+      <c r="U13" s="14">
         <v>30</v>
       </c>
-      <c r="V13" s="15" t="s">
+      <c r="V13" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5920,7 +7746,7 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <v>0.18</v>
       </c>
       <c r="C14">
@@ -5953,22 +7779,22 @@
       <c r="O14">
         <v>5.42</v>
       </c>
-      <c r="Q14" s="15">
+      <c r="Q14" s="14">
         <v>0.28926142900000001</v>
       </c>
-      <c r="R14" s="15" t="s">
+      <c r="R14" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S14" s="15">
+      <c r="S14" s="14">
         <v>0.5</v>
       </c>
-      <c r="T14" s="15" t="s">
+      <c r="T14" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U14" s="15">
+      <c r="U14" s="14">
         <v>30</v>
       </c>
-      <c r="V14" s="15" t="s">
+      <c r="V14" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5976,7 +7802,7 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="14">
         <v>0.18</v>
       </c>
       <c r="C15">
@@ -6009,22 +7835,22 @@
       <c r="O15">
         <v>6.0170000000000003</v>
       </c>
-      <c r="Q15" s="15">
+      <c r="Q15" s="14">
         <v>0.28202989299999998</v>
       </c>
-      <c r="R15" s="15" t="s">
+      <c r="R15" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S15" s="15">
+      <c r="S15" s="14">
         <v>0.5</v>
       </c>
-      <c r="T15" s="15" t="s">
+      <c r="T15" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U15" s="15">
+      <c r="U15" s="14">
         <v>30</v>
       </c>
-      <c r="V15" s="15" t="s">
+      <c r="V15" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -6032,7 +7858,7 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <v>0.18</v>
       </c>
       <c r="C16">
@@ -6065,22 +7891,22 @@
       <c r="O16">
         <v>5.2640000000000002</v>
       </c>
-      <c r="Q16" s="15">
+      <c r="Q16" s="14">
         <v>0.288119607</v>
       </c>
-      <c r="R16" s="15" t="s">
+      <c r="R16" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S16" s="15">
+      <c r="S16" s="14">
         <v>0.5</v>
       </c>
-      <c r="T16" s="15" t="s">
+      <c r="T16" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U16" s="15">
+      <c r="U16" s="14">
         <v>30</v>
       </c>
-      <c r="V16" s="15" t="s">
+      <c r="V16" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -6088,7 +7914,7 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <v>0.3</v>
       </c>
       <c r="C17">
@@ -6121,22 +7947,22 @@
       <c r="O17">
         <v>8.3010000000000002</v>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q17" s="14">
         <v>0.42247392900000003</v>
       </c>
-      <c r="R17" s="15" t="s">
+      <c r="R17" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S17" s="15">
+      <c r="S17" s="14">
         <v>0.5</v>
       </c>
-      <c r="T17" s="15" t="s">
+      <c r="T17" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U17" s="15">
+      <c r="U17" s="14">
         <v>30</v>
       </c>
-      <c r="V17" s="15" t="s">
+      <c r="V17" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -6144,7 +7970,7 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <v>0.3</v>
       </c>
       <c r="C18">
@@ -6177,22 +8003,22 @@
       <c r="O18">
         <v>8.3870000000000005</v>
       </c>
-      <c r="Q18" s="15">
+      <c r="Q18" s="14">
         <v>0.42133210700000001</v>
       </c>
-      <c r="R18" s="15" t="s">
+      <c r="R18" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S18" s="15">
+      <c r="S18" s="14">
         <v>0.5</v>
       </c>
-      <c r="T18" s="15" t="s">
+      <c r="T18" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U18" s="15">
+      <c r="U18" s="14">
         <v>30</v>
       </c>
-      <c r="V18" s="15" t="s">
+      <c r="V18" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -6200,7 +8026,7 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="14">
         <v>0.3</v>
       </c>
       <c r="C19">
@@ -6233,22 +8059,22 @@
       <c r="O19">
         <v>9.34</v>
       </c>
-      <c r="Q19" s="15">
+      <c r="Q19" s="14">
         <v>0.39963749999999998</v>
       </c>
-      <c r="R19" s="15" t="s">
+      <c r="R19" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S19" s="15">
+      <c r="S19" s="14">
         <v>0.5</v>
       </c>
-      <c r="T19" s="15" t="s">
+      <c r="T19" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U19" s="15">
+      <c r="U19" s="14">
         <v>30</v>
       </c>
-      <c r="V19" s="15" t="s">
+      <c r="V19" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -6256,7 +8082,7 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="14">
         <v>0.35</v>
       </c>
       <c r="C20">
@@ -6289,22 +8115,22 @@
       <c r="O20">
         <v>12.682</v>
       </c>
-      <c r="Q20" s="15">
+      <c r="Q20" s="14">
         <v>0.48415467400000001</v>
       </c>
-      <c r="R20" s="15" t="s">
+      <c r="R20" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S20" s="15">
+      <c r="S20" s="14">
         <v>0.5</v>
       </c>
-      <c r="T20" s="15" t="s">
+      <c r="T20" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U20" s="15">
+      <c r="U20" s="14">
         <v>30</v>
       </c>
-      <c r="V20" s="15" t="s">
+      <c r="V20" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -6312,7 +8138,7 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="14">
         <v>0.35</v>
       </c>
       <c r="C21">
@@ -6345,22 +8171,22 @@
       <c r="O21">
         <v>12.353999999999999</v>
       </c>
-      <c r="Q21" s="15">
+      <c r="Q21" s="14">
         <v>0.48992198300000001</v>
       </c>
-      <c r="R21" s="15" t="s">
+      <c r="R21" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S21" s="15">
+      <c r="S21" s="14">
         <v>0.5</v>
       </c>
-      <c r="T21" s="15" t="s">
+      <c r="T21" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U21" s="15">
+      <c r="U21" s="14">
         <v>30</v>
       </c>
-      <c r="V21" s="15" t="s">
+      <c r="V21" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -6368,7 +8194,7 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="14">
         <v>0.35</v>
       </c>
       <c r="C22">
@@ -6401,22 +8227,22 @@
       <c r="O22">
         <v>12.977</v>
       </c>
-      <c r="Q22" s="15">
+      <c r="Q22" s="14">
         <v>0.50886425499999999</v>
       </c>
-      <c r="R22" s="15" t="s">
+      <c r="R22" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="S22" s="15">
+      <c r="S22" s="14">
         <v>0.5</v>
       </c>
-      <c r="T22" s="15" t="s">
+      <c r="T22" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U22" s="15">
+      <c r="U22" s="14">
         <v>30</v>
       </c>
-      <c r="V22" s="15" t="s">
+      <c r="V22" s="14" t="s">
         <v>102</v>
       </c>
     </row>
@@ -6424,7 +8250,7 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="14">
         <v>0.1</v>
       </c>
       <c r="C23">
@@ -6457,22 +8283,22 @@
       <c r="O23">
         <v>2.4500000000000002</v>
       </c>
-      <c r="Q23" s="15">
+      <c r="Q23" s="14">
         <v>0.49783414300000001</v>
       </c>
-      <c r="R23" s="15" t="s">
+      <c r="R23" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="S23" s="15">
+      <c r="S23" s="14">
         <v>5.53</v>
       </c>
-      <c r="T23" s="15" t="s">
+      <c r="T23" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U23" s="15">
+      <c r="U23" s="14">
         <v>5</v>
       </c>
-      <c r="V23" s="15" t="s">
+      <c r="V23" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6480,7 +8306,7 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="14">
         <v>0.1</v>
       </c>
       <c r="C24">
@@ -6513,22 +8339,22 @@
       <c r="O24">
         <v>2.3530000000000002</v>
       </c>
-      <c r="Q24" s="15">
+      <c r="Q24" s="14">
         <v>0.58385135700000002</v>
       </c>
-      <c r="R24" s="15" t="s">
+      <c r="R24" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="S24" s="15">
+      <c r="S24" s="14">
         <v>5.53</v>
       </c>
-      <c r="T24" s="15" t="s">
+      <c r="T24" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U24" s="15">
+      <c r="U24" s="14">
         <v>5</v>
       </c>
-      <c r="V24" s="15" t="s">
+      <c r="V24" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6536,7 +8362,7 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="14">
         <v>0.1</v>
       </c>
       <c r="C25">
@@ -6569,22 +8395,22 @@
       <c r="O25">
         <v>2.25</v>
       </c>
-      <c r="Q25" s="15">
+      <c r="Q25" s="14">
         <v>0.59412774999999995</v>
       </c>
-      <c r="R25" s="15" t="s">
+      <c r="R25" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="S25" s="15">
+      <c r="S25" s="14">
         <v>5.53</v>
       </c>
-      <c r="T25" s="15" t="s">
+      <c r="T25" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U25" s="15">
+      <c r="U25" s="14">
         <v>5</v>
       </c>
-      <c r="V25" s="15" t="s">
+      <c r="V25" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6592,7 +8418,7 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="14">
         <v>0.1</v>
       </c>
       <c r="C26">
@@ -6625,22 +8451,22 @@
       <c r="O26">
         <v>1.7749999999999999</v>
       </c>
-      <c r="Q26" s="15">
+      <c r="Q26" s="14">
         <v>0.510013571</v>
       </c>
-      <c r="R26" s="15" t="s">
+      <c r="R26" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="S26" s="15">
+      <c r="S26" s="14">
         <v>5.53</v>
       </c>
-      <c r="T26" s="15" t="s">
+      <c r="T26" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U26" s="15">
+      <c r="U26" s="14">
         <v>3</v>
       </c>
-      <c r="V26" s="15" t="s">
+      <c r="V26" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6648,7 +8474,7 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="14">
         <v>0.1</v>
       </c>
       <c r="C27">
@@ -6681,22 +8507,22 @@
       <c r="O27">
         <v>1.623</v>
       </c>
-      <c r="Q27" s="15">
+      <c r="Q27" s="14">
         <v>0.29420932100000002</v>
       </c>
-      <c r="R27" s="15" t="s">
+      <c r="R27" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="S27" s="15">
+      <c r="S27" s="14">
         <v>5.53</v>
       </c>
-      <c r="T27" s="15" t="s">
+      <c r="T27" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U27" s="15">
+      <c r="U27" s="14">
         <v>3</v>
       </c>
-      <c r="V27" s="15" t="s">
+      <c r="V27" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6704,7 +8530,7 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="14">
         <v>0.1</v>
       </c>
       <c r="C28">
@@ -6737,22 +8563,22 @@
       <c r="O28">
         <v>1.2909999999999999</v>
       </c>
-      <c r="Q28" s="15">
+      <c r="Q28" s="14">
         <v>0.358912536</v>
       </c>
-      <c r="R28" s="15" t="s">
+      <c r="R28" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="S28" s="15">
+      <c r="S28" s="14">
         <v>5.53</v>
       </c>
-      <c r="T28" s="15" t="s">
+      <c r="T28" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U28" s="15">
+      <c r="U28" s="14">
         <v>3</v>
       </c>
-      <c r="V28" s="15" t="s">
+      <c r="V28" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6760,7 +8586,7 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="14">
         <v>0.1</v>
       </c>
       <c r="C29">
@@ -6793,22 +8619,22 @@
       <c r="O29">
         <v>3.883</v>
       </c>
-      <c r="Q29" s="15">
+      <c r="Q29" s="14">
         <v>0.20552785700000001</v>
       </c>
-      <c r="R29" s="15" t="s">
+      <c r="R29" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="S29" s="15">
+      <c r="S29" s="14">
         <v>0.55000000000000004</v>
       </c>
-      <c r="T29" s="15" t="s">
+      <c r="T29" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U29" s="15">
+      <c r="U29" s="14">
         <v>30</v>
       </c>
-      <c r="V29" s="15" t="s">
+      <c r="V29" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6816,7 +8642,7 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="14">
         <v>0.1</v>
       </c>
       <c r="C30">
@@ -6849,22 +8675,22 @@
       <c r="O30">
         <v>3.3959999999999999</v>
       </c>
-      <c r="Q30" s="15">
+      <c r="Q30" s="14">
         <v>0.35282282100000001</v>
       </c>
-      <c r="R30" s="15" t="s">
+      <c r="R30" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="S30" s="15">
+      <c r="S30" s="14">
         <v>0.55000000000000004</v>
       </c>
-      <c r="T30" s="15" t="s">
+      <c r="T30" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U30" s="15">
+      <c r="U30" s="14">
         <v>30</v>
       </c>
-      <c r="V30" s="15" t="s">
+      <c r="V30" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6872,7 +8698,7 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="14">
         <v>0.1</v>
       </c>
       <c r="C31">
@@ -6905,22 +8731,22 @@
       <c r="O31">
         <v>3.3340000000000001</v>
       </c>
-      <c r="Q31" s="15">
+      <c r="Q31" s="14">
         <v>0.36195739300000002</v>
       </c>
-      <c r="R31" s="15" t="s">
+      <c r="R31" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="S31" s="15">
+      <c r="S31" s="14">
         <v>0.55000000000000004</v>
       </c>
-      <c r="T31" s="15" t="s">
+      <c r="T31" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U31" s="15">
+      <c r="U31" s="14">
         <v>30</v>
       </c>
-      <c r="V31" s="15" t="s">
+      <c r="V31" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6928,7 +8754,7 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="14">
         <v>0.1</v>
       </c>
       <c r="C32">
@@ -6961,22 +8787,22 @@
       <c r="O32">
         <v>5.6040000000000001</v>
       </c>
-      <c r="Q32" s="15">
+      <c r="Q32" s="14">
         <v>0.425138179</v>
       </c>
-      <c r="R32" s="15" t="s">
+      <c r="R32" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="S32" s="15">
+      <c r="S32" s="14">
         <v>12.35</v>
       </c>
-      <c r="T32" s="15" t="s">
+      <c r="T32" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U32" s="15">
+      <c r="U32" s="14">
         <v>3</v>
       </c>
-      <c r="V32" s="15" t="s">
+      <c r="V32" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6984,7 +8810,7 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="14">
         <v>0.1</v>
       </c>
       <c r="C33">
@@ -7017,22 +8843,22 @@
       <c r="O33">
         <v>5.8689999999999998</v>
       </c>
-      <c r="Q33" s="15">
+      <c r="Q33" s="14">
         <v>0.52028996400000005</v>
       </c>
-      <c r="R33" s="15" t="s">
+      <c r="R33" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="S33" s="15">
+      <c r="S33" s="14">
         <v>12.35</v>
       </c>
-      <c r="T33" s="15" t="s">
+      <c r="T33" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U33" s="15">
+      <c r="U33" s="14">
         <v>3</v>
       </c>
-      <c r="V33" s="15" t="s">
+      <c r="V33" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7040,7 +8866,7 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="14">
         <v>0.1</v>
       </c>
       <c r="C34">
@@ -7073,22 +8899,22 @@
       <c r="O34">
         <v>5.0789999999999997</v>
       </c>
-      <c r="Q34" s="15">
+      <c r="Q34" s="14">
         <v>0.452161286</v>
       </c>
-      <c r="R34" s="15" t="s">
+      <c r="R34" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="S34" s="15">
+      <c r="S34" s="14">
         <v>12.35</v>
       </c>
-      <c r="T34" s="15" t="s">
+      <c r="T34" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U34" s="15">
+      <c r="U34" s="14">
         <v>3</v>
       </c>
-      <c r="V34" s="15" t="s">
+      <c r="V34" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7096,7 +8922,7 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="14">
         <v>0.1</v>
       </c>
       <c r="C35">
@@ -7129,22 +8955,22 @@
       <c r="O35">
         <v>5.9080000000000004</v>
       </c>
-      <c r="Q35" s="15">
+      <c r="Q35" s="14">
         <v>0.41790664300000002</v>
       </c>
-      <c r="R35" s="15" t="s">
+      <c r="R35" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="S35" s="15">
+      <c r="S35" s="14">
         <v>1.24</v>
       </c>
-      <c r="T35" s="15" t="s">
+      <c r="T35" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U35" s="15">
+      <c r="U35" s="14">
         <v>30</v>
       </c>
-      <c r="V35" s="15" t="s">
+      <c r="V35" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7152,7 +8978,7 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="14">
         <v>0.1</v>
       </c>
       <c r="C36">
@@ -7185,22 +9011,22 @@
       <c r="O36">
         <v>5.29</v>
       </c>
-      <c r="Q36" s="15">
+      <c r="Q36" s="14">
         <v>0.37870410700000001</v>
       </c>
-      <c r="R36" s="15" t="s">
+      <c r="R36" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="S36" s="15">
+      <c r="S36" s="14">
         <v>1.24</v>
       </c>
-      <c r="T36" s="15" t="s">
+      <c r="T36" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U36" s="15">
+      <c r="U36" s="14">
         <v>30</v>
       </c>
-      <c r="V36" s="15" t="s">
+      <c r="V36" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7208,7 +9034,7 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="14">
         <v>0.1</v>
       </c>
       <c r="C37">
@@ -7241,22 +9067,22 @@
       <c r="O37">
         <v>5.69</v>
       </c>
-      <c r="Q37" s="15">
+      <c r="Q37" s="14">
         <v>0.39887628600000002</v>
       </c>
-      <c r="R37" s="15" t="s">
+      <c r="R37" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="S37" s="15">
+      <c r="S37" s="14">
         <v>1.24</v>
       </c>
-      <c r="T37" s="15" t="s">
+      <c r="T37" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U37" s="15">
+      <c r="U37" s="14">
         <v>30</v>
       </c>
-      <c r="V37" s="15" t="s">
+      <c r="V37" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7264,7 +9090,7 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="14">
         <v>0.1</v>
       </c>
       <c r="C38">
@@ -7297,22 +9123,22 @@
       <c r="O38">
         <v>4.5609999999999999</v>
       </c>
-      <c r="Q38" s="15">
+      <c r="Q38" s="14">
         <v>0.32085182099999998</v>
       </c>
-      <c r="R38" s="15" t="s">
+      <c r="R38" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="S38" s="15">
+      <c r="S38" s="14">
         <v>9.81</v>
       </c>
-      <c r="T38" s="15" t="s">
+      <c r="T38" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U38" s="15">
+      <c r="U38" s="14">
         <v>3</v>
       </c>
-      <c r="V38" s="15" t="s">
+      <c r="V38" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7320,7 +9146,7 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="14">
         <v>0.1</v>
       </c>
       <c r="C39">
@@ -7353,22 +9179,22 @@
       <c r="O39">
         <v>4.9089999999999998</v>
       </c>
-      <c r="Q39" s="15">
+      <c r="Q39" s="14">
         <v>0.41866785699999998</v>
       </c>
-      <c r="R39" s="15" t="s">
+      <c r="R39" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="S39" s="15">
+      <c r="S39" s="14">
         <v>9.81</v>
       </c>
-      <c r="T39" s="15" t="s">
+      <c r="T39" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U39" s="15">
+      <c r="U39" s="14">
         <v>3</v>
       </c>
-      <c r="V39" s="15" t="s">
+      <c r="V39" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7376,7 +9202,7 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="14">
         <v>0.1</v>
       </c>
       <c r="C40">
@@ -7409,22 +9235,22 @@
       <c r="O40">
         <v>4.5490000000000004</v>
       </c>
-      <c r="Q40" s="15">
+      <c r="Q40" s="14">
         <v>0.33150882100000001</v>
       </c>
-      <c r="R40" s="15" t="s">
+      <c r="R40" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="S40" s="15">
+      <c r="S40" s="14">
         <v>9.81</v>
       </c>
-      <c r="T40" s="15" t="s">
+      <c r="T40" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="U40" s="15">
+      <c r="U40" s="14">
         <v>3</v>
       </c>
-      <c r="V40" s="15" t="s">
+      <c r="V40" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7432,7 +9258,7 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="14">
         <v>0.1</v>
       </c>
       <c r="C41">
@@ -7465,22 +9291,22 @@
       <c r="O41">
         <v>4.0129999999999999</v>
       </c>
-      <c r="Q41" s="15">
+      <c r="Q41" s="14">
         <v>0.43998185699999998</v>
       </c>
-      <c r="R41" s="15" t="s">
+      <c r="R41" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="S41" s="15">
+      <c r="S41" s="14">
         <v>0.98</v>
       </c>
-      <c r="T41" s="15" t="s">
+      <c r="T41" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U41" s="15">
+      <c r="U41" s="14">
         <v>30</v>
       </c>
-      <c r="V41" s="15" t="s">
+      <c r="V41" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7488,7 +9314,7 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="14">
         <v>0.1</v>
       </c>
       <c r="C42">
@@ -7521,22 +9347,22 @@
       <c r="O42">
         <v>4.45</v>
       </c>
-      <c r="Q42" s="15">
+      <c r="Q42" s="14">
         <v>0.448355214</v>
       </c>
-      <c r="R42" s="15" t="s">
+      <c r="R42" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="S42" s="15">
+      <c r="S42" s="14">
         <v>0.98</v>
       </c>
-      <c r="T42" s="15" t="s">
+      <c r="T42" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U42" s="15">
+      <c r="U42" s="14">
         <v>30</v>
       </c>
-      <c r="V42" s="15" t="s">
+      <c r="V42" s="14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -7544,7 +9370,7 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="14">
         <v>0.1</v>
       </c>
       <c r="C43">
@@ -7577,22 +9403,22 @@
       <c r="O43">
         <v>4.2300000000000004</v>
       </c>
-      <c r="Q43" s="15">
+      <c r="Q43" s="14">
         <v>0.42361575000000001</v>
       </c>
-      <c r="R43" s="15" t="s">
+      <c r="R43" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="S43" s="15">
+      <c r="S43" s="14">
         <v>0.98</v>
       </c>
-      <c r="T43" s="15" t="s">
+      <c r="T43" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U43" s="15">
+      <c r="U43" s="14">
         <v>30</v>
       </c>
-      <c r="V43" s="15" t="s">
+      <c r="V43" s="14" t="s">
         <v>104</v>
       </c>
     </row>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/large_scale_yeast_proteomics_analysis/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589C7C60-F4FD-884F-87AC-97AF67750547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6039210F-6BBB-8A47-8ED2-BF58D80FCDDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="500" windowWidth="25960" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="500" windowWidth="25960" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2856" uniqueCount="486">
   <si>
     <t>sample</t>
   </si>
@@ -1623,6 +1623,87 @@
       </rPr>
       <t>0.03% methyl methanesulfonate, 2h</t>
     </r>
+  </si>
+  <si>
+    <t>Copy number WT 0 hr 1</t>
+  </si>
+  <si>
+    <t>Copy number WT 0 hr 2</t>
+  </si>
+  <si>
+    <t>Copy number WT 0 hr 3</t>
+  </si>
+  <si>
+    <t>Copy number WT 4 hr 1</t>
+  </si>
+  <si>
+    <t>Copy number WT 4 hr 2</t>
+  </si>
+  <si>
+    <t>Copy number WT 4 hr 3</t>
+  </si>
+  <si>
+    <t>Copy number WT 4 hr 4</t>
+  </si>
+  <si>
+    <t>Copy number WT 8 hr 1</t>
+  </si>
+  <si>
+    <t>Copy number WT 8 hr 2</t>
+  </si>
+  <si>
+    <t>Copy number WT 8 hr 3</t>
+  </si>
+  <si>
+    <t>Copy number WT 8 hr 4</t>
+  </si>
+  <si>
+    <t>Copy number WT 12 hr 1</t>
+  </si>
+  <si>
+    <t>Copy number WT 12 hr 2</t>
+  </si>
+  <si>
+    <t>Copy number WT 12 hr 3</t>
+  </si>
+  <si>
+    <t>Copy number WT 12 hr 4</t>
+  </si>
+  <si>
+    <t>Copy number WT 16 hr 1</t>
+  </si>
+  <si>
+    <t>Copy number WT 16 hr 3</t>
+  </si>
+  <si>
+    <t>Copy number WT 16 hr 4</t>
+  </si>
+  <si>
+    <t>Yirong Wang</t>
+  </si>
+  <si>
+    <t>DOI: 10.1039/c8mt00269j</t>
+  </si>
+  <si>
+    <t>S. cerevisiae BY4743?</t>
+  </si>
+  <si>
+    <t>Copy number WT 0 hr_zinc deficiency</t>
+  </si>
+  <si>
+    <t>Copy number WT 4 hr_zinc deficiency</t>
+  </si>
+  <si>
+    <t>Copy number WT 8 hr_zinc deficiency</t>
+  </si>
+  <si>
+    <t>Copy number WT 12 hr_zinc deficiency</t>
+  </si>
+  <si>
+    <t>Copy number WT 16 hr_zinc deficiency</t>
+  </si>
+  <si>
+    <t>low zinc medium (LZM)</t>
   </si>
 </sst>
 </file>
@@ -2317,7 +2398,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2463,71 +2544,6 @@
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2580,6 +2596,54 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2938,10 +3002,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8F22EE-2E06-6741-B451-D4EA064EAB2E}">
-  <dimension ref="A1:AE283"/>
+  <dimension ref="A1:AE301"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" style="71" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" style="5" customWidth="1"/>
     <col min="2" max="2" width="22" style="5" customWidth="1"/>
     <col min="3" max="3" width="41.5" style="29" customWidth="1"/>
     <col min="4" max="4" width="26.5" style="5" customWidth="1"/>
@@ -2976,7 +3040,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" s="30" customFormat="1" ht="19">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="30" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="30" t="s">
@@ -3071,7 +3135,7 @@
       </c>
     </row>
     <row r="2" spans="1:31" s="13" customFormat="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="10" t="s">
         <v>388</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -3089,7 +3153,7 @@
       <c r="F2" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="86" t="s">
+      <c r="G2" s="63" t="s">
         <v>397</v>
       </c>
       <c r="H2" s="22" t="s">
@@ -3103,7 +3167,7 @@
       </c>
     </row>
     <row r="3" spans="1:31">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="6" t="s">
         <v>389</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -3121,7 +3185,7 @@
       <c r="F3" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="87" t="s">
+      <c r="G3" s="64" t="s">
         <v>397</v>
       </c>
       <c r="H3" s="12" t="s">
@@ -3135,7 +3199,7 @@
       </c>
     </row>
     <row r="4" spans="1:31">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="6" t="s">
         <v>390</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -3153,7 +3217,7 @@
       <c r="F4" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="87" t="s">
+      <c r="G4" s="64" t="s">
         <v>397</v>
       </c>
       <c r="H4" s="12" t="s">
@@ -3167,7 +3231,7 @@
       </c>
     </row>
     <row r="5" spans="1:31">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="6" t="s">
         <v>391</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -3183,7 +3247,7 @@
         <v>359</v>
       </c>
       <c r="F5" s="6"/>
-      <c r="G5" s="87" t="s">
+      <c r="G5" s="64" t="s">
         <v>398</v>
       </c>
       <c r="H5" s="12"/>
@@ -3191,7 +3255,7 @@
       <c r="X5" s="32"/>
     </row>
     <row r="6" spans="1:31">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="6" t="s">
         <v>392</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -3207,7 +3271,7 @@
         <v>359</v>
       </c>
       <c r="F6" s="6"/>
-      <c r="G6" s="87" t="s">
+      <c r="G6" s="64" t="s">
         <v>398</v>
       </c>
       <c r="H6" s="12"/>
@@ -3215,7 +3279,7 @@
       <c r="X6" s="32"/>
     </row>
     <row r="7" spans="1:31">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="6" t="s">
         <v>393</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -3231,7 +3295,7 @@
         <v>359</v>
       </c>
       <c r="F7" s="6"/>
-      <c r="G7" s="87" t="s">
+      <c r="G7" s="64" t="s">
         <v>398</v>
       </c>
       <c r="H7" s="12"/>
@@ -3239,7 +3303,7 @@
       <c r="X7" s="32"/>
     </row>
     <row r="8" spans="1:31">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="6" t="s">
         <v>394</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -3255,7 +3319,7 @@
         <v>359</v>
       </c>
       <c r="F8" s="6"/>
-      <c r="G8" s="87" t="s">
+      <c r="G8" s="64" t="s">
         <v>399</v>
       </c>
       <c r="H8" s="12"/>
@@ -3263,7 +3327,7 @@
       <c r="X8" s="32"/>
     </row>
     <row r="9" spans="1:31">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="6" t="s">
         <v>395</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -3279,7 +3343,7 @@
         <v>359</v>
       </c>
       <c r="F9" s="6"/>
-      <c r="G9" s="87" t="s">
+      <c r="G9" s="64" t="s">
         <v>399</v>
       </c>
       <c r="H9" s="12"/>
@@ -3287,7 +3351,7 @@
       <c r="X9" s="32"/>
     </row>
     <row r="10" spans="1:31" s="14" customFormat="1">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="11" t="s">
         <v>396</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -3303,7 +3367,7 @@
         <v>359</v>
       </c>
       <c r="F10" s="11"/>
-      <c r="G10" s="88" t="s">
+      <c r="G10" s="65" t="s">
         <v>399</v>
       </c>
       <c r="H10" s="23"/>
@@ -3329,7 +3393,7 @@
       <c r="F11" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="89"/>
+      <c r="G11" s="66"/>
       <c r="H11" s="28" t="s">
         <v>174</v>
       </c>
@@ -3368,7 +3432,7 @@
       </c>
     </row>
     <row r="12" spans="1:31">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="73" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -3386,7 +3450,7 @@
       <c r="F12" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G12" s="87" t="s">
+      <c r="G12" s="64" t="s">
         <v>364</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -3454,7 +3518,7 @@
       </c>
     </row>
     <row r="13" spans="1:31">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="73" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -3472,7 +3536,7 @@
       <c r="F13" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G13" s="87" t="s">
+      <c r="G13" s="64" t="s">
         <v>364</v>
       </c>
       <c r="H13" s="12" t="s">
@@ -3540,7 +3604,7 @@
       </c>
     </row>
     <row r="14" spans="1:31">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="73" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -3558,7 +3622,7 @@
       <c r="F14" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G14" s="87" t="s">
+      <c r="G14" s="64" t="s">
         <v>364</v>
       </c>
       <c r="H14" s="12" t="s">
@@ -3626,7 +3690,7 @@
       </c>
     </row>
     <row r="15" spans="1:31">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="73" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -3644,7 +3708,7 @@
       <c r="F15" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G15" s="87" t="s">
+      <c r="G15" s="64" t="s">
         <v>365</v>
       </c>
       <c r="H15" s="12" t="s">
@@ -3712,7 +3776,7 @@
       </c>
     </row>
     <row r="16" spans="1:31">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="73" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -3730,7 +3794,7 @@
       <c r="F16" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G16" s="87" t="s">
+      <c r="G16" s="64" t="s">
         <v>365</v>
       </c>
       <c r="H16" s="12" t="s">
@@ -3798,7 +3862,7 @@
       </c>
     </row>
     <row r="17" spans="1:30">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="73" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -3816,7 +3880,7 @@
       <c r="F17" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G17" s="87" t="s">
+      <c r="G17" s="64" t="s">
         <v>365</v>
       </c>
       <c r="H17" s="12" t="s">
@@ -3884,7 +3948,7 @@
       </c>
     </row>
     <row r="18" spans="1:30">
-      <c r="A18" s="54" t="s">
+      <c r="A18" s="73" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -3902,7 +3966,7 @@
       <c r="F18" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G18" s="87" t="s">
+      <c r="G18" s="64" t="s">
         <v>366</v>
       </c>
       <c r="H18" s="12" t="s">
@@ -3970,7 +4034,7 @@
       </c>
     </row>
     <row r="19" spans="1:30">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="73" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -3988,7 +4052,7 @@
       <c r="F19" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G19" s="87" t="s">
+      <c r="G19" s="64" t="s">
         <v>366</v>
       </c>
       <c r="H19" s="12" t="s">
@@ -4056,7 +4120,7 @@
       </c>
     </row>
     <row r="20" spans="1:30">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="73" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -4074,7 +4138,7 @@
       <c r="F20" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G20" s="87" t="s">
+      <c r="G20" s="64" t="s">
         <v>366</v>
       </c>
       <c r="H20" s="12" t="s">
@@ -4142,7 +4206,7 @@
       </c>
     </row>
     <row r="21" spans="1:30">
-      <c r="A21" s="54" t="s">
+      <c r="A21" s="73" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -4160,7 +4224,7 @@
       <c r="F21" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G21" s="87" t="s">
+      <c r="G21" s="64" t="s">
         <v>367</v>
       </c>
       <c r="H21" s="12" t="s">
@@ -4228,7 +4292,7 @@
       </c>
     </row>
     <row r="22" spans="1:30">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="73" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -4246,7 +4310,7 @@
       <c r="F22" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G22" s="87" t="s">
+      <c r="G22" s="64" t="s">
         <v>367</v>
       </c>
       <c r="H22" s="12" t="s">
@@ -4314,7 +4378,7 @@
       </c>
     </row>
     <row r="23" spans="1:30">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="73" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -4332,7 +4396,7 @@
       <c r="F23" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G23" s="87" t="s">
+      <c r="G23" s="64" t="s">
         <v>367</v>
       </c>
       <c r="H23" s="12" t="s">
@@ -4400,7 +4464,7 @@
       </c>
     </row>
     <row r="24" spans="1:30">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="73" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -4418,7 +4482,7 @@
       <c r="F24" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G24" s="87" t="s">
+      <c r="G24" s="64" t="s">
         <v>368</v>
       </c>
       <c r="H24" s="12" t="s">
@@ -4486,7 +4550,7 @@
       </c>
     </row>
     <row r="25" spans="1:30">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="73" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -4504,7 +4568,7 @@
       <c r="F25" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G25" s="87" t="s">
+      <c r="G25" s="64" t="s">
         <v>368</v>
       </c>
       <c r="H25" s="12" t="s">
@@ -4572,7 +4636,7 @@
       </c>
     </row>
     <row r="26" spans="1:30">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="73" t="s">
         <v>30</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -4590,7 +4654,7 @@
       <c r="F26" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G26" s="87" t="s">
+      <c r="G26" s="64" t="s">
         <v>368</v>
       </c>
       <c r="H26" s="12" t="s">
@@ -4658,7 +4722,7 @@
       </c>
     </row>
     <row r="27" spans="1:30">
-      <c r="A27" s="54" t="s">
+      <c r="A27" s="73" t="s">
         <v>31</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -4676,7 +4740,7 @@
       <c r="F27" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G27" s="87" t="s">
+      <c r="G27" s="64" t="s">
         <v>369</v>
       </c>
       <c r="H27" s="12" t="s">
@@ -4744,7 +4808,7 @@
       </c>
     </row>
     <row r="28" spans="1:30">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="73" t="s">
         <v>32</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -4762,7 +4826,7 @@
       <c r="F28" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G28" s="87" t="s">
+      <c r="G28" s="64" t="s">
         <v>369</v>
       </c>
       <c r="H28" s="12" t="s">
@@ -4830,7 +4894,7 @@
       </c>
     </row>
     <row r="29" spans="1:30">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="73" t="s">
         <v>33</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -4848,7 +4912,7 @@
       <c r="F29" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G29" s="87" t="s">
+      <c r="G29" s="64" t="s">
         <v>369</v>
       </c>
       <c r="H29" s="12" t="s">
@@ -4916,7 +4980,7 @@
       </c>
     </row>
     <row r="30" spans="1:30">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="73" t="s">
         <v>34</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -4934,7 +4998,7 @@
       <c r="F30" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G30" s="87" t="s">
+      <c r="G30" s="64" t="s">
         <v>370</v>
       </c>
       <c r="H30" s="12" t="s">
@@ -5002,7 +5066,7 @@
       </c>
     </row>
     <row r="31" spans="1:30">
-      <c r="A31" s="54" t="s">
+      <c r="A31" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -5020,7 +5084,7 @@
       <c r="F31" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G31" s="87" t="s">
+      <c r="G31" s="64" t="s">
         <v>370</v>
       </c>
       <c r="H31" s="12" t="s">
@@ -5088,7 +5152,7 @@
       </c>
     </row>
     <row r="32" spans="1:30">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="73" t="s">
         <v>36</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -5106,7 +5170,7 @@
       <c r="F32" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G32" s="87" t="s">
+      <c r="G32" s="64" t="s">
         <v>370</v>
       </c>
       <c r="H32" s="12" t="s">
@@ -5174,7 +5238,7 @@
       </c>
     </row>
     <row r="33" spans="1:31">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="73" t="s">
         <v>37</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -5192,7 +5256,7 @@
       <c r="F33" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G33" s="87" t="s">
+      <c r="G33" s="64" t="s">
         <v>371</v>
       </c>
       <c r="H33" s="12" t="s">
@@ -5263,7 +5327,7 @@
       </c>
     </row>
     <row r="34" spans="1:31">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="73" t="s">
         <v>38</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -5281,7 +5345,7 @@
       <c r="F34" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G34" s="87" t="s">
+      <c r="G34" s="64" t="s">
         <v>371</v>
       </c>
       <c r="H34" s="12" t="s">
@@ -5352,7 +5416,7 @@
       </c>
     </row>
     <row r="35" spans="1:31">
-      <c r="A35" s="54" t="s">
+      <c r="A35" s="73" t="s">
         <v>39</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -5370,7 +5434,7 @@
       <c r="F35" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G35" s="87" t="s">
+      <c r="G35" s="64" t="s">
         <v>371</v>
       </c>
       <c r="H35" s="12" t="s">
@@ -5441,7 +5505,7 @@
       </c>
     </row>
     <row r="36" spans="1:31">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="73" t="s">
         <v>40</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -5459,7 +5523,7 @@
       <c r="F36" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G36" s="87" t="s">
+      <c r="G36" s="64" t="s">
         <v>372</v>
       </c>
       <c r="H36" s="12" t="s">
@@ -5530,7 +5594,7 @@
       </c>
     </row>
     <row r="37" spans="1:31">
-      <c r="A37" s="54" t="s">
+      <c r="A37" s="73" t="s">
         <v>41</v>
       </c>
       <c r="B37" s="6" t="s">
@@ -5548,7 +5612,7 @@
       <c r="F37" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G37" s="87" t="s">
+      <c r="G37" s="64" t="s">
         <v>372</v>
       </c>
       <c r="H37" s="12" t="s">
@@ -5619,7 +5683,7 @@
       </c>
     </row>
     <row r="38" spans="1:31">
-      <c r="A38" s="54" t="s">
+      <c r="A38" s="73" t="s">
         <v>42</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -5637,7 +5701,7 @@
       <c r="F38" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G38" s="87" t="s">
+      <c r="G38" s="64" t="s">
         <v>372</v>
       </c>
       <c r="H38" s="12" t="s">
@@ -5708,7 +5772,7 @@
       </c>
     </row>
     <row r="39" spans="1:31">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="73" t="s">
         <v>43</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -5726,7 +5790,7 @@
       <c r="F39" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G39" s="87" t="s">
+      <c r="G39" s="64" t="s">
         <v>373</v>
       </c>
       <c r="H39" s="12" t="s">
@@ -5794,7 +5858,7 @@
       </c>
     </row>
     <row r="40" spans="1:31">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="73" t="s">
         <v>44</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -5812,7 +5876,7 @@
       <c r="F40" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G40" s="87" t="s">
+      <c r="G40" s="64" t="s">
         <v>373</v>
       </c>
       <c r="H40" s="12" t="s">
@@ -5880,7 +5944,7 @@
       </c>
     </row>
     <row r="41" spans="1:31">
-      <c r="A41" s="54" t="s">
+      <c r="A41" s="73" t="s">
         <v>45</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -5898,7 +5962,7 @@
       <c r="F41" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G41" s="87" t="s">
+      <c r="G41" s="64" t="s">
         <v>373</v>
       </c>
       <c r="H41" s="12" t="s">
@@ -5966,7 +6030,7 @@
       </c>
     </row>
     <row r="42" spans="1:31">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="73" t="s">
         <v>46</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -5984,7 +6048,7 @@
       <c r="F42" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G42" s="87" t="s">
+      <c r="G42" s="64" t="s">
         <v>374</v>
       </c>
       <c r="H42" s="12" t="s">
@@ -6052,7 +6116,7 @@
       </c>
     </row>
     <row r="43" spans="1:31">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="73" t="s">
         <v>47</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -6070,7 +6134,7 @@
       <c r="F43" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G43" s="87" t="s">
+      <c r="G43" s="64" t="s">
         <v>374</v>
       </c>
       <c r="H43" s="12" t="s">
@@ -6138,7 +6202,7 @@
       </c>
     </row>
     <row r="44" spans="1:31">
-      <c r="A44" s="54" t="s">
+      <c r="A44" s="73" t="s">
         <v>48</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -6156,7 +6220,7 @@
       <c r="F44" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G44" s="87" t="s">
+      <c r="G44" s="64" t="s">
         <v>374</v>
       </c>
       <c r="H44" s="12" t="s">
@@ -6224,7 +6288,7 @@
       </c>
     </row>
     <row r="45" spans="1:31">
-      <c r="A45" s="54" t="s">
+      <c r="A45" s="73" t="s">
         <v>49</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -6242,7 +6306,7 @@
       <c r="F45" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G45" s="87" t="s">
+      <c r="G45" s="64" t="s">
         <v>375</v>
       </c>
       <c r="H45" s="12" t="s">
@@ -6310,7 +6374,7 @@
       </c>
     </row>
     <row r="46" spans="1:31">
-      <c r="A46" s="54" t="s">
+      <c r="A46" s="73" t="s">
         <v>50</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -6328,7 +6392,7 @@
       <c r="F46" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G46" s="87" t="s">
+      <c r="G46" s="64" t="s">
         <v>375</v>
       </c>
       <c r="H46" s="12" t="s">
@@ -6396,7 +6460,7 @@
       </c>
     </row>
     <row r="47" spans="1:31">
-      <c r="A47" s="54" t="s">
+      <c r="A47" s="73" t="s">
         <v>51</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -6414,7 +6478,7 @@
       <c r="F47" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G47" s="87" t="s">
+      <c r="G47" s="64" t="s">
         <v>375</v>
       </c>
       <c r="H47" s="12" t="s">
@@ -6482,7 +6546,7 @@
       </c>
     </row>
     <row r="48" spans="1:31">
-      <c r="A48" s="54" t="s">
+      <c r="A48" s="73" t="s">
         <v>52</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -6500,7 +6564,7 @@
       <c r="F48" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G48" s="87" t="s">
+      <c r="G48" s="64" t="s">
         <v>376</v>
       </c>
       <c r="H48" s="12" t="s">
@@ -6568,7 +6632,7 @@
       </c>
     </row>
     <row r="49" spans="1:30">
-      <c r="A49" s="54" t="s">
+      <c r="A49" s="73" t="s">
         <v>53</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -6586,7 +6650,7 @@
       <c r="F49" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G49" s="87" t="s">
+      <c r="G49" s="64" t="s">
         <v>376</v>
       </c>
       <c r="H49" s="12" t="s">
@@ -6654,7 +6718,7 @@
       </c>
     </row>
     <row r="50" spans="1:30">
-      <c r="A50" s="54" t="s">
+      <c r="A50" s="73" t="s">
         <v>54</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -6672,7 +6736,7 @@
       <c r="F50" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G50" s="87" t="s">
+      <c r="G50" s="64" t="s">
         <v>376</v>
       </c>
       <c r="H50" s="12" t="s">
@@ -6740,7 +6804,7 @@
       </c>
     </row>
     <row r="51" spans="1:30">
-      <c r="A51" s="54" t="s">
+      <c r="A51" s="73" t="s">
         <v>55</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -6758,7 +6822,7 @@
       <c r="F51" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G51" s="87" t="s">
+      <c r="G51" s="64" t="s">
         <v>377</v>
       </c>
       <c r="H51" s="12" t="s">
@@ -6826,7 +6890,7 @@
       </c>
     </row>
     <row r="52" spans="1:30">
-      <c r="A52" s="54" t="s">
+      <c r="A52" s="73" t="s">
         <v>56</v>
       </c>
       <c r="B52" s="6" t="s">
@@ -6844,7 +6908,7 @@
       <c r="F52" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G52" s="87" t="s">
+      <c r="G52" s="64" t="s">
         <v>377</v>
       </c>
       <c r="H52" s="12" t="s">
@@ -6912,7 +6976,7 @@
       </c>
     </row>
     <row r="53" spans="1:30" s="14" customFormat="1">
-      <c r="A53" s="55" t="s">
+      <c r="A53" s="74" t="s">
         <v>57</v>
       </c>
       <c r="B53" s="11" t="s">
@@ -6930,7 +6994,7 @@
       <c r="F53" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="G53" s="88" t="s">
+      <c r="G53" s="65" t="s">
         <v>377</v>
       </c>
       <c r="H53" s="23" t="s">
@@ -6998,7 +7062,7 @@
       </c>
     </row>
     <row r="54" spans="1:30" s="46" customFormat="1">
-      <c r="A54" s="56" t="s">
+      <c r="A54" s="20" t="s">
         <v>58</v>
       </c>
       <c r="B54" s="20" t="s">
@@ -7016,14 +7080,14 @@
       <c r="F54" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G54" s="90"/>
+      <c r="G54" s="67"/>
       <c r="H54" s="20"/>
       <c r="I54" s="45">
         <v>0.1</v>
       </c>
     </row>
     <row r="55" spans="1:30" s="13" customFormat="1">
-      <c r="A55" s="57" t="s">
+      <c r="A55" s="10" t="s">
         <v>411</v>
       </c>
       <c r="B55" s="10" t="s">
@@ -7041,7 +7105,7 @@
       <c r="F55" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="G55" s="86" t="s">
+      <c r="G55" s="63" t="s">
         <v>59</v>
       </c>
       <c r="H55" s="22" t="s">
@@ -7061,7 +7125,7 @@
       </c>
     </row>
     <row r="56" spans="1:30">
-      <c r="A56" s="58" t="s">
+      <c r="A56" s="6" t="s">
         <v>412</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -7079,7 +7143,7 @@
       <c r="F56" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G56" s="87" t="s">
+      <c r="G56" s="64" t="s">
         <v>59</v>
       </c>
       <c r="H56" s="12" t="s">
@@ -7099,7 +7163,7 @@
       </c>
     </row>
     <row r="57" spans="1:30">
-      <c r="A57" s="58" t="s">
+      <c r="A57" s="6" t="s">
         <v>413</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -7117,7 +7181,7 @@
       <c r="F57" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G57" s="87" t="s">
+      <c r="G57" s="64" t="s">
         <v>60</v>
       </c>
       <c r="H57" s="12" t="s">
@@ -7137,7 +7201,7 @@
       </c>
     </row>
     <row r="58" spans="1:30">
-      <c r="A58" s="58" t="s">
+      <c r="A58" s="6" t="s">
         <v>414</v>
       </c>
       <c r="B58" s="6" t="s">
@@ -7155,7 +7219,7 @@
       <c r="F58" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G58" s="87" t="s">
+      <c r="G58" s="64" t="s">
         <v>60</v>
       </c>
       <c r="H58" s="12" t="s">
@@ -7175,7 +7239,7 @@
       </c>
     </row>
     <row r="59" spans="1:30">
-      <c r="A59" s="58" t="s">
+      <c r="A59" s="6" t="s">
         <v>415</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -7193,7 +7257,7 @@
       <c r="F59" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G59" s="87" t="s">
+      <c r="G59" s="64" t="s">
         <v>61</v>
       </c>
       <c r="H59" s="12" t="s">
@@ -7216,7 +7280,7 @@
       </c>
     </row>
     <row r="60" spans="1:30">
-      <c r="A60" s="58" t="s">
+      <c r="A60" s="6" t="s">
         <v>416</v>
       </c>
       <c r="B60" s="6" t="s">
@@ -7234,7 +7298,7 @@
       <c r="F60" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G60" s="87" t="s">
+      <c r="G60" s="64" t="s">
         <v>61</v>
       </c>
       <c r="H60" s="12" t="s">
@@ -7257,7 +7321,7 @@
       </c>
     </row>
     <row r="61" spans="1:30">
-      <c r="A61" s="58" t="s">
+      <c r="A61" s="6" t="s">
         <v>417</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -7275,7 +7339,7 @@
       <c r="F61" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G61" s="87" t="s">
+      <c r="G61" s="64" t="s">
         <v>61</v>
       </c>
       <c r="H61" s="12" t="s">
@@ -7298,7 +7362,7 @@
       </c>
     </row>
     <row r="62" spans="1:30">
-      <c r="A62" s="58" t="s">
+      <c r="A62" s="6" t="s">
         <v>418</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -7316,7 +7380,7 @@
       <c r="F62" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G62" s="87" t="s">
+      <c r="G62" s="64" t="s">
         <v>62</v>
       </c>
       <c r="H62" s="12" t="s">
@@ -7339,7 +7403,7 @@
       </c>
     </row>
     <row r="63" spans="1:30">
-      <c r="A63" s="58" t="s">
+      <c r="A63" s="6" t="s">
         <v>419</v>
       </c>
       <c r="B63" s="6" t="s">
@@ -7357,7 +7421,7 @@
       <c r="F63" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G63" s="87" t="s">
+      <c r="G63" s="64" t="s">
         <v>62</v>
       </c>
       <c r="H63" s="12" t="s">
@@ -7380,7 +7444,7 @@
       </c>
     </row>
     <row r="64" spans="1:30" s="14" customFormat="1">
-      <c r="A64" s="59" t="s">
+      <c r="A64" s="11" t="s">
         <v>420</v>
       </c>
       <c r="B64" s="11" t="s">
@@ -7398,7 +7462,7 @@
       <c r="F64" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G64" s="88" t="s">
+      <c r="G64" s="65" t="s">
         <v>62</v>
       </c>
       <c r="H64" s="23" t="s">
@@ -7421,7 +7485,7 @@
       </c>
     </row>
     <row r="65" spans="1:30" s="13" customFormat="1">
-      <c r="A65" s="60" t="s">
+      <c r="A65" s="75" t="s">
         <v>63</v>
       </c>
       <c r="B65" s="10" t="s">
@@ -7439,14 +7503,14 @@
       <c r="F65" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="G65" s="86"/>
+      <c r="G65" s="63"/>
       <c r="H65" s="10"/>
       <c r="I65" s="13">
         <v>0.1</v>
       </c>
     </row>
     <row r="66" spans="1:30">
-      <c r="A66" s="61" t="s">
+      <c r="A66" s="76" t="s">
         <v>64</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -7464,14 +7528,14 @@
       <c r="F66" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G66" s="87"/>
+      <c r="G66" s="64"/>
       <c r="H66" s="6"/>
       <c r="I66" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="67" spans="1:30">
-      <c r="A67" s="61" t="s">
+      <c r="A67" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -7489,14 +7553,14 @@
       <c r="F67" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G67" s="87"/>
+      <c r="G67" s="64"/>
       <c r="H67" s="6"/>
       <c r="I67" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="68" spans="1:30">
-      <c r="A68" s="61" t="s">
+      <c r="A68" s="76" t="s">
         <v>66</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -7514,14 +7578,14 @@
       <c r="F68" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G68" s="87"/>
+      <c r="G68" s="64"/>
       <c r="H68" s="6"/>
       <c r="I68" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="69" spans="1:30">
-      <c r="A69" s="61" t="s">
+      <c r="A69" s="76" t="s">
         <v>67</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -7539,11 +7603,11 @@
       <c r="F69" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G69" s="87"/>
+      <c r="G69" s="64"/>
       <c r="H69" s="6"/>
     </row>
     <row r="70" spans="1:30">
-      <c r="A70" s="61" t="s">
+      <c r="A70" s="76" t="s">
         <v>68</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -7561,11 +7625,11 @@
       <c r="F70" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G70" s="87"/>
+      <c r="G70" s="64"/>
       <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:30">
-      <c r="A71" s="61" t="s">
+      <c r="A71" s="76" t="s">
         <v>69</v>
       </c>
       <c r="B71" s="6" t="s">
@@ -7583,11 +7647,11 @@
       <c r="F71" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G71" s="87"/>
+      <c r="G71" s="64"/>
       <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:30">
-      <c r="A72" s="61" t="s">
+      <c r="A72" s="76" t="s">
         <v>70</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -7605,11 +7669,11 @@
       <c r="F72" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G72" s="87"/>
+      <c r="G72" s="64"/>
       <c r="H72" s="6"/>
     </row>
     <row r="73" spans="1:30" s="31" customFormat="1">
-      <c r="A73" s="75" t="s">
+      <c r="A73" s="77" t="s">
         <v>421</v>
       </c>
       <c r="B73" s="10" t="s">
@@ -7627,7 +7691,7 @@
       <c r="F73" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="G73" s="91" t="s">
+      <c r="G73" s="68" t="s">
         <v>105</v>
       </c>
       <c r="H73" s="22" t="s">
@@ -7636,16 +7700,16 @@
       <c r="I73" s="31">
         <v>2.7E-2</v>
       </c>
-      <c r="J73" s="76">
+      <c r="J73" s="53">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="K73" s="76">
+      <c r="K73" s="53">
         <v>-0.151308114750691</v>
       </c>
-      <c r="P73" s="76">
-        <v>0</v>
-      </c>
-      <c r="U73" s="76">
+      <c r="P73" s="53">
+        <v>0</v>
+      </c>
+      <c r="U73" s="53">
         <v>0.878</v>
       </c>
       <c r="V73" s="13">
@@ -7657,12 +7721,12 @@
       <c r="Z73" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="AD73" s="79">
+      <c r="AD73" s="56">
         <v>0.29899999999999999</v>
       </c>
     </row>
     <row r="74" spans="1:30" s="32" customFormat="1">
-      <c r="A74" s="73" t="s">
+      <c r="A74" s="78" t="s">
         <v>422</v>
       </c>
       <c r="B74" s="6" t="s">
@@ -7680,7 +7744,7 @@
       <c r="F74" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G74" s="92" t="s">
+      <c r="G74" s="69" t="s">
         <v>105</v>
       </c>
       <c r="H74" s="12" t="s">
@@ -7689,16 +7753,16 @@
       <c r="I74" s="32">
         <v>2.7E-2</v>
       </c>
-      <c r="J74" s="77">
+      <c r="J74" s="54">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="K74" s="77">
+      <c r="K74" s="54">
         <v>-0.151308114750691</v>
       </c>
-      <c r="P74" s="77">
-        <v>0</v>
-      </c>
-      <c r="U74" s="77">
+      <c r="P74" s="54">
+        <v>0</v>
+      </c>
+      <c r="U74" s="54">
         <v>0.878</v>
       </c>
       <c r="V74" s="5">
@@ -7710,12 +7774,12 @@
       <c r="Z74" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD74" s="80">
+      <c r="AD74" s="57">
         <v>0.29899999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:30" s="32" customFormat="1">
-      <c r="A75" s="73" t="s">
+      <c r="A75" s="78" t="s">
         <v>423</v>
       </c>
       <c r="B75" s="6" t="s">
@@ -7733,7 +7797,7 @@
       <c r="F75" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G75" s="92" t="s">
+      <c r="G75" s="69" t="s">
         <v>105</v>
       </c>
       <c r="H75" s="12" t="s">
@@ -7742,16 +7806,16 @@
       <c r="I75" s="32">
         <v>2.7E-2</v>
       </c>
-      <c r="J75" s="77">
+      <c r="J75" s="54">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="K75" s="77">
+      <c r="K75" s="54">
         <v>-0.151308114750691</v>
       </c>
-      <c r="P75" s="77">
-        <v>0</v>
-      </c>
-      <c r="U75" s="77">
+      <c r="P75" s="54">
+        <v>0</v>
+      </c>
+      <c r="U75" s="54">
         <v>0.878</v>
       </c>
       <c r="V75" s="5">
@@ -7763,12 +7827,12 @@
       <c r="Z75" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD75" s="80">
+      <c r="AD75" s="57">
         <v>0.29899999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:30">
-      <c r="A76" s="73" t="s">
+      <c r="A76" s="78" t="s">
         <v>424</v>
       </c>
       <c r="B76" s="6" t="s">
@@ -7786,7 +7850,7 @@
       <c r="F76" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G76" s="87" t="s">
+      <c r="G76" s="64" t="s">
         <v>76</v>
       </c>
       <c r="H76" s="12" t="s">
@@ -7795,16 +7859,16 @@
       <c r="I76" s="5">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="J76" s="77">
+      <c r="J76" s="54">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="K76" s="77">
+      <c r="K76" s="54">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="P76" s="77">
-        <v>0</v>
-      </c>
-      <c r="U76" s="77">
+      <c r="P76" s="54">
+        <v>0</v>
+      </c>
+      <c r="U76" s="54">
         <v>1.458</v>
       </c>
       <c r="V76" s="5">
@@ -7816,12 +7880,12 @@
       <c r="Z76" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD76" s="81">
+      <c r="AD76" s="58">
         <v>0.312</v>
       </c>
     </row>
     <row r="77" spans="1:30">
-      <c r="A77" s="73" t="s">
+      <c r="A77" s="78" t="s">
         <v>425</v>
       </c>
       <c r="B77" s="6" t="s">
@@ -7839,7 +7903,7 @@
       <c r="F77" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G77" s="87" t="s">
+      <c r="G77" s="64" t="s">
         <v>76</v>
       </c>
       <c r="H77" s="12" t="s">
@@ -7848,16 +7912,16 @@
       <c r="I77" s="5">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="J77" s="77">
+      <c r="J77" s="54">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="K77" s="77">
+      <c r="K77" s="54">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="P77" s="77">
-        <v>0</v>
-      </c>
-      <c r="U77" s="77">
+      <c r="P77" s="54">
+        <v>0</v>
+      </c>
+      <c r="U77" s="54">
         <v>1.458</v>
       </c>
       <c r="V77" s="5">
@@ -7869,12 +7933,12 @@
       <c r="Z77" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD77" s="81">
+      <c r="AD77" s="58">
         <v>0.312</v>
       </c>
     </row>
     <row r="78" spans="1:30">
-      <c r="A78" s="73" t="s">
+      <c r="A78" s="78" t="s">
         <v>426</v>
       </c>
       <c r="B78" s="6" t="s">
@@ -7892,7 +7956,7 @@
       <c r="F78" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G78" s="87" t="s">
+      <c r="G78" s="64" t="s">
         <v>76</v>
       </c>
       <c r="H78" s="12" t="s">
@@ -7901,16 +7965,16 @@
       <c r="I78" s="5">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="J78" s="77">
+      <c r="J78" s="54">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="K78" s="77">
+      <c r="K78" s="54">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="P78" s="77">
-        <v>0</v>
-      </c>
-      <c r="U78" s="77">
+      <c r="P78" s="54">
+        <v>0</v>
+      </c>
+      <c r="U78" s="54">
         <v>1.458</v>
       </c>
       <c r="V78" s="5">
@@ -7922,12 +7986,12 @@
       <c r="Z78" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD78" s="81">
+      <c r="AD78" s="58">
         <v>0.312</v>
       </c>
     </row>
     <row r="79" spans="1:30">
-      <c r="A79" s="73" t="s">
+      <c r="A79" s="78" t="s">
         <v>427</v>
       </c>
       <c r="B79" s="6" t="s">
@@ -7945,7 +8009,7 @@
       <c r="F79" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G79" s="87" t="s">
+      <c r="G79" s="64" t="s">
         <v>77</v>
       </c>
       <c r="H79" s="12" t="s">
@@ -7954,16 +8018,16 @@
       <c r="I79" s="5">
         <v>0.10199999999999999</v>
       </c>
-      <c r="J79" s="77">
+      <c r="J79" s="54">
         <v>-1.171</v>
       </c>
-      <c r="K79" s="77">
+      <c r="K79" s="54">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="P79" s="77">
-        <v>0</v>
-      </c>
-      <c r="U79" s="77">
+      <c r="P79" s="54">
+        <v>0</v>
+      </c>
+      <c r="U79" s="54">
         <v>2.5470000000000002</v>
       </c>
       <c r="V79" s="5">
@@ -7975,12 +8039,12 @@
       <c r="Z79" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD79" s="81">
+      <c r="AD79" s="58">
         <v>0.371</v>
       </c>
     </row>
     <row r="80" spans="1:30">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="78" t="s">
         <v>428</v>
       </c>
       <c r="B80" s="6" t="s">
@@ -7998,7 +8062,7 @@
       <c r="F80" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G80" s="87" t="s">
+      <c r="G80" s="64" t="s">
         <v>77</v>
       </c>
       <c r="H80" s="12" t="s">
@@ -8007,16 +8071,16 @@
       <c r="I80" s="5">
         <v>0.10199999999999999</v>
       </c>
-      <c r="J80" s="77">
+      <c r="J80" s="54">
         <v>-1.171</v>
       </c>
-      <c r="K80" s="77">
+      <c r="K80" s="54">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="P80" s="77">
-        <v>0</v>
-      </c>
-      <c r="U80" s="77">
+      <c r="P80" s="54">
+        <v>0</v>
+      </c>
+      <c r="U80" s="54">
         <v>2.5470000000000002</v>
       </c>
       <c r="V80" s="5">
@@ -8028,12 +8092,12 @@
       <c r="Z80" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD80" s="81">
+      <c r="AD80" s="58">
         <v>0.371</v>
       </c>
     </row>
     <row r="81" spans="1:30">
-      <c r="A81" s="73" t="s">
+      <c r="A81" s="78" t="s">
         <v>429</v>
       </c>
       <c r="B81" s="6" t="s">
@@ -8051,7 +8115,7 @@
       <c r="F81" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G81" s="87" t="s">
+      <c r="G81" s="64" t="s">
         <v>77</v>
       </c>
       <c r="H81" s="12" t="s">
@@ -8060,16 +8124,16 @@
       <c r="I81" s="5">
         <v>0.10199999999999999</v>
       </c>
-      <c r="J81" s="77">
+      <c r="J81" s="54">
         <v>-1.171</v>
       </c>
-      <c r="K81" s="77">
+      <c r="K81" s="54">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="P81" s="77">
-        <v>0</v>
-      </c>
-      <c r="U81" s="77">
+      <c r="P81" s="54">
+        <v>0</v>
+      </c>
+      <c r="U81" s="54">
         <v>2.5470000000000002</v>
       </c>
       <c r="V81" s="5">
@@ -8081,12 +8145,12 @@
       <c r="Z81" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD81" s="81">
+      <c r="AD81" s="58">
         <v>0.371</v>
       </c>
     </row>
     <row r="82" spans="1:30">
-      <c r="A82" s="73" t="s">
+      <c r="A82" s="78" t="s">
         <v>430</v>
       </c>
       <c r="B82" s="6" t="s">
@@ -8104,7 +8168,7 @@
       <c r="F82" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G82" s="87" t="s">
+      <c r="G82" s="64" t="s">
         <v>78</v>
       </c>
       <c r="H82" s="12" t="s">
@@ -8113,16 +8177,16 @@
       <c r="I82" s="5">
         <v>0.152</v>
       </c>
-      <c r="J82" s="77">
+      <c r="J82" s="54">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="K82" s="77">
+      <c r="K82" s="54">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="P82" s="77">
-        <v>0</v>
-      </c>
-      <c r="U82" s="77">
+      <c r="P82" s="54">
+        <v>0</v>
+      </c>
+      <c r="U82" s="54">
         <v>3.81518914277475</v>
       </c>
       <c r="V82" s="5">
@@ -8134,12 +8198,12 @@
       <c r="Z82" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD82" s="81">
+      <c r="AD82" s="58">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:30">
-      <c r="A83" s="73" t="s">
+      <c r="A83" s="78" t="s">
         <v>431</v>
       </c>
       <c r="B83" s="6" t="s">
@@ -8157,7 +8221,7 @@
       <c r="F83" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G83" s="87" t="s">
+      <c r="G83" s="64" t="s">
         <v>78</v>
       </c>
       <c r="H83" s="12" t="s">
@@ -8166,16 +8230,16 @@
       <c r="I83" s="5">
         <v>0.152</v>
       </c>
-      <c r="J83" s="77">
+      <c r="J83" s="54">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="K83" s="77">
+      <c r="K83" s="54">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="P83" s="77">
-        <v>0</v>
-      </c>
-      <c r="U83" s="77">
+      <c r="P83" s="54">
+        <v>0</v>
+      </c>
+      <c r="U83" s="54">
         <v>3.81518914277475</v>
       </c>
       <c r="V83" s="5">
@@ -8187,12 +8251,12 @@
       <c r="Z83" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD83" s="81">
+      <c r="AD83" s="58">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="84" spans="1:30">
-      <c r="A84" s="73" t="s">
+      <c r="A84" s="78" t="s">
         <v>432</v>
       </c>
       <c r="B84" s="6" t="s">
@@ -8210,7 +8274,7 @@
       <c r="F84" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G84" s="87" t="s">
+      <c r="G84" s="64" t="s">
         <v>78</v>
       </c>
       <c r="H84" s="12" t="s">
@@ -8219,16 +8283,16 @@
       <c r="I84" s="5">
         <v>0.152</v>
       </c>
-      <c r="J84" s="77">
+      <c r="J84" s="54">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="K84" s="77">
+      <c r="K84" s="54">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="P84" s="77">
-        <v>0</v>
-      </c>
-      <c r="U84" s="77">
+      <c r="P84" s="54">
+        <v>0</v>
+      </c>
+      <c r="U84" s="54">
         <v>3.81518914277475</v>
       </c>
       <c r="V84" s="5">
@@ -8240,12 +8304,12 @@
       <c r="Z84" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD84" s="81">
+      <c r="AD84" s="58">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="85" spans="1:30">
-      <c r="A85" s="73" t="s">
+      <c r="A85" s="78" t="s">
         <v>433</v>
       </c>
       <c r="B85" s="6" t="s">
@@ -8263,7 +8327,7 @@
       <c r="F85" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G85" s="87" t="s">
+      <c r="G85" s="64" t="s">
         <v>79</v>
       </c>
       <c r="H85" s="12" t="s">
@@ -8272,16 +8336,16 @@
       <c r="I85" s="5">
         <v>0.214</v>
       </c>
-      <c r="J85" s="77">
+      <c r="J85" s="54">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="K85" s="77">
+      <c r="K85" s="54">
         <v>-1.22567508688439</v>
       </c>
-      <c r="P85" s="77">
+      <c r="P85" s="54">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="U85" s="77">
+      <c r="U85" s="54">
         <v>5.5949999999999998</v>
       </c>
       <c r="V85" s="5">
@@ -8293,12 +8357,12 @@
       <c r="Z85" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD85" s="81">
+      <c r="AD85" s="58">
         <v>0.32</v>
       </c>
     </row>
     <row r="86" spans="1:30">
-      <c r="A86" s="73" t="s">
+      <c r="A86" s="78" t="s">
         <v>434</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -8316,7 +8380,7 @@
       <c r="F86" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G86" s="87" t="s">
+      <c r="G86" s="64" t="s">
         <v>79</v>
       </c>
       <c r="H86" s="12" t="s">
@@ -8325,16 +8389,16 @@
       <c r="I86" s="5">
         <v>0.214</v>
       </c>
-      <c r="J86" s="77">
+      <c r="J86" s="54">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="K86" s="77">
+      <c r="K86" s="54">
         <v>-1.22567508688439</v>
       </c>
-      <c r="P86" s="77">
+      <c r="P86" s="54">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="U86" s="77">
+      <c r="U86" s="54">
         <v>5.5949999999999998</v>
       </c>
       <c r="V86" s="5">
@@ -8346,12 +8410,12 @@
       <c r="Z86" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD86" s="81">
+      <c r="AD86" s="58">
         <v>0.32</v>
       </c>
     </row>
     <row r="87" spans="1:30">
-      <c r="A87" s="73" t="s">
+      <c r="A87" s="78" t="s">
         <v>435</v>
       </c>
       <c r="B87" s="6" t="s">
@@ -8369,7 +8433,7 @@
       <c r="F87" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G87" s="87" t="s">
+      <c r="G87" s="64" t="s">
         <v>79</v>
       </c>
       <c r="H87" s="12" t="s">
@@ -8378,16 +8442,16 @@
       <c r="I87" s="5">
         <v>0.214</v>
       </c>
-      <c r="J87" s="77">
+      <c r="J87" s="54">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="K87" s="77">
+      <c r="K87" s="54">
         <v>-1.22567508688439</v>
       </c>
-      <c r="P87" s="77">
+      <c r="P87" s="54">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="U87" s="77">
+      <c r="U87" s="54">
         <v>5.5949999999999998</v>
       </c>
       <c r="V87" s="5">
@@ -8399,12 +8463,12 @@
       <c r="Z87" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD87" s="81">
+      <c r="AD87" s="58">
         <v>0.32</v>
       </c>
     </row>
     <row r="88" spans="1:30">
-      <c r="A88" s="73" t="s">
+      <c r="A88" s="78" t="s">
         <v>436</v>
       </c>
       <c r="B88" s="6" t="s">
@@ -8422,7 +8486,7 @@
       <c r="F88" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G88" s="87" t="s">
+      <c r="G88" s="64" t="s">
         <v>80</v>
       </c>
       <c r="H88" s="12" t="s">
@@ -8431,16 +8495,16 @@
       <c r="I88" s="5">
         <v>0.254</v>
       </c>
-      <c r="J88" s="77">
+      <c r="J88" s="54">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="K88" s="77">
+      <c r="K88" s="54">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="P88" s="77">
+      <c r="P88" s="54">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="U88" s="77">
+      <c r="U88" s="54">
         <v>6.484</v>
       </c>
       <c r="V88" s="5">
@@ -8452,12 +8516,12 @@
       <c r="Z88" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD88" s="81">
+      <c r="AD88" s="58">
         <v>0.37799999999999995</v>
       </c>
     </row>
     <row r="89" spans="1:30">
-      <c r="A89" s="73" t="s">
+      <c r="A89" s="78" t="s">
         <v>437</v>
       </c>
       <c r="B89" s="6" t="s">
@@ -8475,7 +8539,7 @@
       <c r="F89" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G89" s="87" t="s">
+      <c r="G89" s="64" t="s">
         <v>80</v>
       </c>
       <c r="H89" s="12" t="s">
@@ -8484,16 +8548,16 @@
       <c r="I89" s="5">
         <v>0.254</v>
       </c>
-      <c r="J89" s="77">
+      <c r="J89" s="54">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="K89" s="77">
+      <c r="K89" s="54">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="P89" s="77">
+      <c r="P89" s="54">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="U89" s="77">
+      <c r="U89" s="54">
         <v>6.484</v>
       </c>
       <c r="V89" s="5">
@@ -8505,12 +8569,12 @@
       <c r="Z89" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD89" s="81">
+      <c r="AD89" s="58">
         <v>0.37799999999999995</v>
       </c>
     </row>
     <row r="90" spans="1:30">
-      <c r="A90" s="73" t="s">
+      <c r="A90" s="78" t="s">
         <v>438</v>
       </c>
       <c r="B90" s="6" t="s">
@@ -8528,7 +8592,7 @@
       <c r="F90" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G90" s="87" t="s">
+      <c r="G90" s="64" t="s">
         <v>80</v>
       </c>
       <c r="H90" s="12" t="s">
@@ -8537,16 +8601,16 @@
       <c r="I90" s="5">
         <v>0.254</v>
       </c>
-      <c r="J90" s="77">
+      <c r="J90" s="54">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="K90" s="77">
+      <c r="K90" s="54">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="P90" s="77">
+      <c r="P90" s="54">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="U90" s="77">
+      <c r="U90" s="54">
         <v>6.484</v>
       </c>
       <c r="V90" s="5">
@@ -8558,12 +8622,12 @@
       <c r="Z90" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD90" s="81">
+      <c r="AD90" s="58">
         <v>0.37799999999999995</v>
       </c>
     </row>
     <row r="91" spans="1:30">
-      <c r="A91" s="73" t="s">
+      <c r="A91" s="78" t="s">
         <v>439</v>
       </c>
       <c r="B91" s="6" t="s">
@@ -8581,7 +8645,7 @@
       <c r="F91" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G91" s="87" t="s">
+      <c r="G91" s="64" t="s">
         <v>81</v>
       </c>
       <c r="H91" s="12" t="s">
@@ -8590,16 +8654,16 @@
       <c r="I91" s="5">
         <v>0.28399999999999997</v>
       </c>
-      <c r="J91" s="77">
+      <c r="J91" s="54">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="K91" s="77">
+      <c r="K91" s="54">
         <v>-1.47353470842518</v>
       </c>
-      <c r="P91" s="77">
+      <c r="P91" s="54">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="U91" s="77">
+      <c r="U91" s="54">
         <v>8.0890000000000004</v>
       </c>
       <c r="V91" s="5">
@@ -8611,12 +8675,12 @@
       <c r="Z91" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD91" s="81">
+      <c r="AD91" s="58">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:30">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="78" t="s">
         <v>440</v>
       </c>
       <c r="B92" s="6" t="s">
@@ -8634,7 +8698,7 @@
       <c r="F92" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G92" s="87" t="s">
+      <c r="G92" s="64" t="s">
         <v>81</v>
       </c>
       <c r="H92" s="12" t="s">
@@ -8643,16 +8707,16 @@
       <c r="I92" s="5">
         <v>0.28399999999999997</v>
       </c>
-      <c r="J92" s="77">
+      <c r="J92" s="54">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="K92" s="77">
+      <c r="K92" s="54">
         <v>-1.47353470842518</v>
       </c>
-      <c r="P92" s="77">
+      <c r="P92" s="54">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="U92" s="77">
+      <c r="U92" s="54">
         <v>8.0890000000000004</v>
       </c>
       <c r="V92" s="5">
@@ -8664,12 +8728,12 @@
       <c r="Z92" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD92" s="81">
+      <c r="AD92" s="58">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:30">
-      <c r="A93" s="73" t="s">
+      <c r="A93" s="78" t="s">
         <v>441</v>
       </c>
       <c r="B93" s="6" t="s">
@@ -8687,7 +8751,7 @@
       <c r="F93" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G93" s="87" t="s">
+      <c r="G93" s="64" t="s">
         <v>81</v>
       </c>
       <c r="H93" s="12" t="s">
@@ -8696,16 +8760,16 @@
       <c r="I93" s="5">
         <v>0.28399999999999997</v>
       </c>
-      <c r="J93" s="77">
+      <c r="J93" s="54">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="K93" s="77">
+      <c r="K93" s="54">
         <v>-1.47353470842518</v>
       </c>
-      <c r="P93" s="77">
+      <c r="P93" s="54">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="U93" s="77">
+      <c r="U93" s="54">
         <v>8.0890000000000004</v>
       </c>
       <c r="V93" s="5">
@@ -8717,12 +8781,12 @@
       <c r="Z93" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD93" s="81">
+      <c r="AD93" s="58">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:30">
-      <c r="A94" s="73" t="s">
+      <c r="A94" s="78" t="s">
         <v>442</v>
       </c>
       <c r="B94" s="6" t="s">
@@ -8740,7 +8804,7 @@
       <c r="F94" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G94" s="87" t="s">
+      <c r="G94" s="64" t="s">
         <v>82</v>
       </c>
       <c r="H94" s="12" t="s">
@@ -8749,16 +8813,16 @@
       <c r="I94" s="5">
         <v>0.33400000000000002</v>
       </c>
-      <c r="J94" s="77">
+      <c r="J94" s="54">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="K94" s="77">
+      <c r="K94" s="54">
         <v>-1.99253212300414</v>
       </c>
-      <c r="P94" s="77">
+      <c r="P94" s="54">
         <v>2.0830000000081101</v>
       </c>
-      <c r="U94" s="77">
+      <c r="U94" s="54">
         <v>11.872999999999999</v>
       </c>
       <c r="V94" s="5">
@@ -8770,12 +8834,12 @@
       <c r="Z94" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD94" s="81">
+      <c r="AD94" s="58">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="95" spans="1:30">
-      <c r="A95" s="73" t="s">
+      <c r="A95" s="78" t="s">
         <v>443</v>
       </c>
       <c r="B95" s="6" t="s">
@@ -8793,7 +8857,7 @@
       <c r="F95" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G95" s="87" t="s">
+      <c r="G95" s="64" t="s">
         <v>82</v>
       </c>
       <c r="H95" s="12" t="s">
@@ -8802,16 +8866,16 @@
       <c r="I95" s="5">
         <v>0.33400000000000002</v>
       </c>
-      <c r="J95" s="77">
+      <c r="J95" s="54">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="K95" s="77">
+      <c r="K95" s="54">
         <v>-1.99253212300414</v>
       </c>
-      <c r="P95" s="77">
+      <c r="P95" s="54">
         <v>2.0830000000081101</v>
       </c>
-      <c r="U95" s="77">
+      <c r="U95" s="54">
         <v>11.872999999999999</v>
       </c>
       <c r="V95" s="5">
@@ -8823,12 +8887,12 @@
       <c r="Z95" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD95" s="81">
+      <c r="AD95" s="58">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="96" spans="1:30">
-      <c r="A96" s="73" t="s">
+      <c r="A96" s="78" t="s">
         <v>444</v>
       </c>
       <c r="B96" s="6" t="s">
@@ -8846,7 +8910,7 @@
       <c r="F96" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G96" s="87" t="s">
+      <c r="G96" s="64" t="s">
         <v>82</v>
       </c>
       <c r="H96" s="12" t="s">
@@ -8855,16 +8919,16 @@
       <c r="I96" s="5">
         <v>0.33400000000000002</v>
       </c>
-      <c r="J96" s="77">
+      <c r="J96" s="54">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="K96" s="77">
+      <c r="K96" s="54">
         <v>-1.99253212300414</v>
       </c>
-      <c r="P96" s="77">
+      <c r="P96" s="54">
         <v>2.0830000000081101</v>
       </c>
-      <c r="U96" s="77">
+      <c r="U96" s="54">
         <v>11.872999999999999</v>
       </c>
       <c r="V96" s="5">
@@ -8876,12 +8940,12 @@
       <c r="Z96" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD96" s="81">
+      <c r="AD96" s="58">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="97" spans="1:30">
-      <c r="A97" s="73" t="s">
+      <c r="A97" s="78" t="s">
         <v>445</v>
       </c>
       <c r="B97" s="6" t="s">
@@ -8899,7 +8963,7 @@
       <c r="F97" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G97" s="87" t="s">
+      <c r="G97" s="64" t="s">
         <v>83</v>
       </c>
       <c r="H97" s="12" t="s">
@@ -8908,16 +8972,16 @@
       <c r="I97" s="5">
         <v>0.379</v>
       </c>
-      <c r="J97" s="77">
+      <c r="J97" s="54">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="K97" s="77">
+      <c r="K97" s="54">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="P97" s="77">
+      <c r="P97" s="54">
         <v>5.5389999999999997</v>
       </c>
-      <c r="U97" s="77">
+      <c r="U97" s="54">
         <v>14.304133448972699</v>
       </c>
       <c r="V97" s="5">
@@ -8929,12 +8993,12 @@
       <c r="Z97" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD97" s="81">
+      <c r="AD97" s="58">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:30">
-      <c r="A98" s="73" t="s">
+      <c r="A98" s="78" t="s">
         <v>446</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -8952,7 +9016,7 @@
       <c r="F98" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G98" s="87" t="s">
+      <c r="G98" s="64" t="s">
         <v>83</v>
       </c>
       <c r="H98" s="12" t="s">
@@ -8961,16 +9025,16 @@
       <c r="I98" s="5">
         <v>0.379</v>
       </c>
-      <c r="J98" s="77">
+      <c r="J98" s="54">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="K98" s="77">
+      <c r="K98" s="54">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="P98" s="77">
+      <c r="P98" s="54">
         <v>5.5389999999999997</v>
       </c>
-      <c r="U98" s="77">
+      <c r="U98" s="54">
         <v>14.304133448972699</v>
       </c>
       <c r="V98" s="5">
@@ -8982,12 +9046,12 @@
       <c r="Z98" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AD98" s="81">
+      <c r="AD98" s="58">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="99" spans="1:30" s="14" customFormat="1">
-      <c r="A99" s="74" t="s">
+      <c r="A99" s="79" t="s">
         <v>447</v>
       </c>
       <c r="B99" s="11" t="s">
@@ -9005,7 +9069,7 @@
       <c r="F99" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="G99" s="88" t="s">
+      <c r="G99" s="65" t="s">
         <v>83</v>
       </c>
       <c r="H99" s="23" t="s">
@@ -9014,16 +9078,16 @@
       <c r="I99" s="14">
         <v>0.379</v>
       </c>
-      <c r="J99" s="78">
+      <c r="J99" s="55">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="K99" s="78">
+      <c r="K99" s="55">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="P99" s="78">
+      <c r="P99" s="55">
         <v>5.5389999999999997</v>
       </c>
-      <c r="U99" s="78">
+      <c r="U99" s="55">
         <v>14.304133448972699</v>
       </c>
       <c r="V99" s="14">
@@ -9035,12 +9099,12 @@
       <c r="Z99" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="AD99" s="82">
+      <c r="AD99" s="59">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="100" spans="1:30">
-      <c r="A100" s="62" t="s">
+      <c r="A100" s="80" t="s">
         <v>108</v>
       </c>
       <c r="B100" s="6" t="s">
@@ -9058,7 +9122,7 @@
       <c r="F100" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G100" s="87"/>
+      <c r="G100" s="64"/>
       <c r="H100" s="12" t="s">
         <v>174</v>
       </c>
@@ -9067,7 +9131,7 @@
       </c>
     </row>
     <row r="101" spans="1:30">
-      <c r="A101" s="62" t="s">
+      <c r="A101" s="80" t="s">
         <v>109</v>
       </c>
       <c r="B101" s="6" t="s">
@@ -9085,7 +9149,7 @@
       <c r="F101" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G101" s="87"/>
+      <c r="G101" s="64"/>
       <c r="H101" s="12" t="s">
         <v>174</v>
       </c>
@@ -9094,7 +9158,7 @@
       </c>
     </row>
     <row r="102" spans="1:30">
-      <c r="A102" s="62" t="s">
+      <c r="A102" s="80" t="s">
         <v>110</v>
       </c>
       <c r="B102" s="6" t="s">
@@ -9112,7 +9176,7 @@
       <c r="F102" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G102" s="87"/>
+      <c r="G102" s="64"/>
       <c r="H102" s="12" t="s">
         <v>174</v>
       </c>
@@ -9121,7 +9185,7 @@
       </c>
     </row>
     <row r="103" spans="1:30">
-      <c r="A103" s="62" t="s">
+      <c r="A103" s="80" t="s">
         <v>111</v>
       </c>
       <c r="B103" s="6" t="s">
@@ -9139,7 +9203,7 @@
       <c r="F103" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G103" s="87"/>
+      <c r="G103" s="64"/>
       <c r="H103" s="12" t="s">
         <v>174</v>
       </c>
@@ -9148,7 +9212,7 @@
       </c>
     </row>
     <row r="104" spans="1:30">
-      <c r="A104" s="62" t="s">
+      <c r="A104" s="80" t="s">
         <v>112</v>
       </c>
       <c r="B104" s="6" t="s">
@@ -9166,7 +9230,7 @@
       <c r="F104" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G104" s="87"/>
+      <c r="G104" s="64"/>
       <c r="H104" s="12" t="s">
         <v>174</v>
       </c>
@@ -9175,7 +9239,7 @@
       </c>
     </row>
     <row r="105" spans="1:30">
-      <c r="A105" s="62" t="s">
+      <c r="A105" s="80" t="s">
         <v>113</v>
       </c>
       <c r="B105" s="6" t="s">
@@ -9193,7 +9257,7 @@
       <c r="F105" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G105" s="87"/>
+      <c r="G105" s="64"/>
       <c r="H105" s="12" t="s">
         <v>174</v>
       </c>
@@ -9202,7 +9266,7 @@
       </c>
     </row>
     <row r="106" spans="1:30">
-      <c r="A106" s="62" t="s">
+      <c r="A106" s="80" t="s">
         <v>114</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -9220,7 +9284,7 @@
       <c r="F106" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G106" s="87"/>
+      <c r="G106" s="64"/>
       <c r="H106" s="12" t="s">
         <v>174</v>
       </c>
@@ -9229,7 +9293,7 @@
       </c>
     </row>
     <row r="107" spans="1:30">
-      <c r="A107" s="62" t="s">
+      <c r="A107" s="80" t="s">
         <v>115</v>
       </c>
       <c r="B107" s="6" t="s">
@@ -9247,7 +9311,7 @@
       <c r="F107" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G107" s="87"/>
+      <c r="G107" s="64"/>
       <c r="H107" s="12" t="s">
         <v>174</v>
       </c>
@@ -9256,7 +9320,7 @@
       </c>
     </row>
     <row r="108" spans="1:30">
-      <c r="A108" s="62" t="s">
+      <c r="A108" s="80" t="s">
         <v>116</v>
       </c>
       <c r="B108" s="6" t="s">
@@ -9274,7 +9338,7 @@
       <c r="F108" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G108" s="87"/>
+      <c r="G108" s="64"/>
       <c r="H108" s="12" t="s">
         <v>174</v>
       </c>
@@ -9283,7 +9347,7 @@
       </c>
     </row>
     <row r="109" spans="1:30" ht="14" customHeight="1">
-      <c r="A109" s="62" t="s">
+      <c r="A109" s="80" t="s">
         <v>117</v>
       </c>
       <c r="B109" s="6" t="s">
@@ -9301,7 +9365,7 @@
       <c r="F109" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G109" s="87"/>
+      <c r="G109" s="64"/>
       <c r="H109" s="12" t="s">
         <v>174</v>
       </c>
@@ -9310,7 +9374,7 @@
       </c>
     </row>
     <row r="110" spans="1:30" s="13" customFormat="1">
-      <c r="A110" s="57" t="s">
+      <c r="A110" s="10" t="s">
         <v>118</v>
       </c>
       <c r="B110" s="13" t="s">
@@ -9328,7 +9392,7 @@
       <c r="F110" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="G110" s="86"/>
+      <c r="G110" s="63"/>
       <c r="H110" s="13" t="s">
         <v>211</v>
       </c>
@@ -9340,7 +9404,7 @@
       </c>
     </row>
     <row r="111" spans="1:30">
-      <c r="A111" s="58" t="s">
+      <c r="A111" s="6" t="s">
         <v>119</v>
       </c>
       <c r="B111" s="5" t="s">
@@ -9358,7 +9422,7 @@
       <c r="F111" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G111" s="87"/>
+      <c r="G111" s="64"/>
       <c r="H111" s="5" t="s">
         <v>211</v>
       </c>
@@ -9370,7 +9434,7 @@
       </c>
     </row>
     <row r="112" spans="1:30">
-      <c r="A112" s="58" t="s">
+      <c r="A112" s="6" t="s">
         <v>120</v>
       </c>
       <c r="B112" s="5" t="s">
@@ -9388,7 +9452,7 @@
       <c r="F112" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G112" s="87"/>
+      <c r="G112" s="64"/>
       <c r="H112" s="5" t="s">
         <v>211</v>
       </c>
@@ -9400,7 +9464,7 @@
       </c>
     </row>
     <row r="113" spans="1:24">
-      <c r="A113" s="58" t="s">
+      <c r="A113" s="6" t="s">
         <v>121</v>
       </c>
       <c r="B113" s="5" t="s">
@@ -9418,7 +9482,7 @@
       <c r="F113" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G113" s="87"/>
+      <c r="G113" s="64"/>
       <c r="H113" s="5" t="s">
         <v>211</v>
       </c>
@@ -9430,7 +9494,7 @@
       </c>
     </row>
     <row r="114" spans="1:24">
-      <c r="A114" s="58" t="s">
+      <c r="A114" s="6" t="s">
         <v>122</v>
       </c>
       <c r="B114" s="5" t="s">
@@ -9448,7 +9512,7 @@
       <c r="F114" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G114" s="87"/>
+      <c r="G114" s="64"/>
       <c r="H114" s="5" t="s">
         <v>211</v>
       </c>
@@ -9460,7 +9524,7 @@
       </c>
     </row>
     <row r="115" spans="1:24">
-      <c r="A115" s="58" t="s">
+      <c r="A115" s="6" t="s">
         <v>123</v>
       </c>
       <c r="B115" s="5" t="s">
@@ -9478,7 +9542,7 @@
       <c r="F115" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G115" s="87"/>
+      <c r="G115" s="64"/>
       <c r="H115" s="5" t="s">
         <v>211</v>
       </c>
@@ -9490,7 +9554,7 @@
       </c>
     </row>
     <row r="116" spans="1:24">
-      <c r="A116" s="58" t="s">
+      <c r="A116" s="6" t="s">
         <v>124</v>
       </c>
       <c r="B116" s="5" t="s">
@@ -9508,7 +9572,7 @@
       <c r="F116" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G116" s="87"/>
+      <c r="G116" s="64"/>
       <c r="H116" s="5" t="s">
         <v>211</v>
       </c>
@@ -9520,7 +9584,7 @@
       </c>
     </row>
     <row r="117" spans="1:24">
-      <c r="A117" s="58" t="s">
+      <c r="A117" s="6" t="s">
         <v>125</v>
       </c>
       <c r="B117" s="5" t="s">
@@ -9538,7 +9602,7 @@
       <c r="F117" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G117" s="87"/>
+      <c r="G117" s="64"/>
       <c r="H117" s="5" t="s">
         <v>211</v>
       </c>
@@ -9550,7 +9614,7 @@
       </c>
     </row>
     <row r="118" spans="1:24">
-      <c r="A118" s="58" t="s">
+      <c r="A118" s="6" t="s">
         <v>126</v>
       </c>
       <c r="B118" s="5" t="s">
@@ -9568,7 +9632,7 @@
       <c r="F118" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G118" s="87"/>
+      <c r="G118" s="64"/>
       <c r="H118" s="5" t="s">
         <v>211</v>
       </c>
@@ -9580,7 +9644,7 @@
       </c>
     </row>
     <row r="119" spans="1:24">
-      <c r="A119" s="58" t="s">
+      <c r="A119" s="6" t="s">
         <v>127</v>
       </c>
       <c r="B119" s="5" t="s">
@@ -9598,7 +9662,7 @@
       <c r="F119" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G119" s="87"/>
+      <c r="G119" s="64"/>
       <c r="H119" s="5" t="s">
         <v>211</v>
       </c>
@@ -9610,7 +9674,7 @@
       </c>
     </row>
     <row r="120" spans="1:24" s="14" customFormat="1">
-      <c r="A120" s="59" t="s">
+      <c r="A120" s="11" t="s">
         <v>128</v>
       </c>
       <c r="B120" s="14" t="s">
@@ -9628,7 +9692,7 @@
       <c r="F120" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G120" s="88"/>
+      <c r="G120" s="65"/>
       <c r="H120" s="14" t="s">
         <v>211</v>
       </c>
@@ -9640,7 +9704,7 @@
       </c>
     </row>
     <row r="121" spans="1:24" s="13" customFormat="1">
-      <c r="A121" s="63" t="s">
+      <c r="A121" s="81" t="s">
         <v>131</v>
       </c>
       <c r="B121" s="10" t="s">
@@ -9666,7 +9730,7 @@
       </c>
     </row>
     <row r="122" spans="1:24">
-      <c r="A122" s="64" t="s">
+      <c r="A122" s="82" t="s">
         <v>132</v>
       </c>
       <c r="B122" s="10" t="s">
@@ -9692,7 +9756,7 @@
       </c>
     </row>
     <row r="123" spans="1:24">
-      <c r="A123" s="64" t="s">
+      <c r="A123" s="82" t="s">
         <v>133</v>
       </c>
       <c r="B123" s="10" t="s">
@@ -9718,7 +9782,7 @@
       </c>
     </row>
     <row r="124" spans="1:24">
-      <c r="A124" s="64" t="s">
+      <c r="A124" s="82" t="s">
         <v>134</v>
       </c>
       <c r="B124" s="10" t="s">
@@ -9744,7 +9808,7 @@
       </c>
     </row>
     <row r="125" spans="1:24">
-      <c r="A125" s="64" t="s">
+      <c r="A125" s="82" t="s">
         <v>135</v>
       </c>
       <c r="B125" s="10" t="s">
@@ -9770,7 +9834,7 @@
       </c>
     </row>
     <row r="126" spans="1:24">
-      <c r="A126" s="64" t="s">
+      <c r="A126" s="82" t="s">
         <v>136</v>
       </c>
       <c r="B126" s="10" t="s">
@@ -9796,7 +9860,7 @@
       </c>
     </row>
     <row r="127" spans="1:24">
-      <c r="A127" s="64" t="s">
+      <c r="A127" s="82" t="s">
         <v>137</v>
       </c>
       <c r="B127" s="10" t="s">
@@ -9822,7 +9886,7 @@
       </c>
     </row>
     <row r="128" spans="1:24">
-      <c r="A128" s="64" t="s">
+      <c r="A128" s="82" t="s">
         <v>138</v>
       </c>
       <c r="B128" s="10" t="s">
@@ -9848,7 +9912,7 @@
       </c>
     </row>
     <row r="129" spans="1:9">
-      <c r="A129" s="64" t="s">
+      <c r="A129" s="82" t="s">
         <v>139</v>
       </c>
       <c r="B129" s="10" t="s">
@@ -9874,7 +9938,7 @@
       </c>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="64" t="s">
+      <c r="A130" s="82" t="s">
         <v>140</v>
       </c>
       <c r="B130" s="10" t="s">
@@ -9900,7 +9964,7 @@
       </c>
     </row>
     <row r="131" spans="1:9">
-      <c r="A131" s="64" t="s">
+      <c r="A131" s="82" t="s">
         <v>141</v>
       </c>
       <c r="B131" s="10" t="s">
@@ -9926,7 +9990,7 @@
       </c>
     </row>
     <row r="132" spans="1:9">
-      <c r="A132" s="64" t="s">
+      <c r="A132" s="82" t="s">
         <v>142</v>
       </c>
       <c r="B132" s="10" t="s">
@@ -9952,7 +10016,7 @@
       </c>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="64" t="s">
+      <c r="A133" s="82" t="s">
         <v>143</v>
       </c>
       <c r="B133" s="10" t="s">
@@ -9978,7 +10042,7 @@
       </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="64" t="s">
+      <c r="A134" s="82" t="s">
         <v>144</v>
       </c>
       <c r="B134" s="10" t="s">
@@ -10004,7 +10068,7 @@
       </c>
     </row>
     <row r="135" spans="1:9">
-      <c r="A135" s="64" t="s">
+      <c r="A135" s="82" t="s">
         <v>145</v>
       </c>
       <c r="B135" s="10" t="s">
@@ -10030,7 +10094,7 @@
       </c>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="64" t="s">
+      <c r="A136" s="82" t="s">
         <v>146</v>
       </c>
       <c r="B136" s="10" t="s">
@@ -10056,7 +10120,7 @@
       </c>
     </row>
     <row r="137" spans="1:9">
-      <c r="A137" s="64" t="s">
+      <c r="A137" s="82" t="s">
         <v>147</v>
       </c>
       <c r="B137" s="10" t="s">
@@ -10082,7 +10146,7 @@
       </c>
     </row>
     <row r="138" spans="1:9">
-      <c r="A138" s="64" t="s">
+      <c r="A138" s="82" t="s">
         <v>148</v>
       </c>
       <c r="B138" s="10" t="s">
@@ -10108,7 +10172,7 @@
       </c>
     </row>
     <row r="139" spans="1:9">
-      <c r="A139" s="64" t="s">
+      <c r="A139" s="82" t="s">
         <v>149</v>
       </c>
       <c r="B139" s="10" t="s">
@@ -10134,7 +10198,7 @@
       </c>
     </row>
     <row r="140" spans="1:9">
-      <c r="A140" s="64" t="s">
+      <c r="A140" s="82" t="s">
         <v>150</v>
       </c>
       <c r="B140" s="10" t="s">
@@ -10160,7 +10224,7 @@
       </c>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="64" t="s">
+      <c r="A141" s="82" t="s">
         <v>151</v>
       </c>
       <c r="B141" s="10" t="s">
@@ -10186,7 +10250,7 @@
       </c>
     </row>
     <row r="142" spans="1:9">
-      <c r="A142" s="64" t="s">
+      <c r="A142" s="82" t="s">
         <v>152</v>
       </c>
       <c r="B142" s="10" t="s">
@@ -10212,7 +10276,7 @@
       </c>
     </row>
     <row r="143" spans="1:9">
-      <c r="A143" s="64" t="s">
+      <c r="A143" s="82" t="s">
         <v>153</v>
       </c>
       <c r="B143" s="10" t="s">
@@ -10238,7 +10302,7 @@
       </c>
     </row>
     <row r="144" spans="1:9">
-      <c r="A144" s="64" t="s">
+      <c r="A144" s="82" t="s">
         <v>154</v>
       </c>
       <c r="B144" s="10" t="s">
@@ -10264,7 +10328,7 @@
       </c>
     </row>
     <row r="145" spans="1:25">
-      <c r="A145" s="64" t="s">
+      <c r="A145" s="82" t="s">
         <v>155</v>
       </c>
       <c r="B145" s="10" t="s">
@@ -10290,7 +10354,7 @@
       </c>
     </row>
     <row r="146" spans="1:25">
-      <c r="A146" s="64" t="s">
+      <c r="A146" s="82" t="s">
         <v>156</v>
       </c>
       <c r="B146" s="10" t="s">
@@ -10316,7 +10380,7 @@
       </c>
     </row>
     <row r="147" spans="1:25">
-      <c r="A147" s="64" t="s">
+      <c r="A147" s="82" t="s">
         <v>157</v>
       </c>
       <c r="B147" s="10" t="s">
@@ -10342,7 +10406,7 @@
       </c>
     </row>
     <row r="148" spans="1:25">
-      <c r="A148" s="64" t="s">
+      <c r="A148" s="82" t="s">
         <v>158</v>
       </c>
       <c r="B148" s="10" t="s">
@@ -10368,7 +10432,7 @@
       </c>
     </row>
     <row r="149" spans="1:25">
-      <c r="A149" s="64" t="s">
+      <c r="A149" s="82" t="s">
         <v>159</v>
       </c>
       <c r="B149" s="10" t="s">
@@ -10394,7 +10458,7 @@
       </c>
     </row>
     <row r="150" spans="1:25" s="14" customFormat="1">
-      <c r="A150" s="65" t="s">
+      <c r="A150" s="83" t="s">
         <v>160</v>
       </c>
       <c r="B150" s="10" t="s">
@@ -10420,7 +10484,7 @@
       </c>
     </row>
     <row r="151" spans="1:25" s="13" customFormat="1">
-      <c r="A151" s="66" t="s">
+      <c r="A151" s="24" t="s">
         <v>161</v>
       </c>
       <c r="B151" s="10" t="s">
@@ -10438,7 +10502,7 @@
       <c r="F151" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="G151" s="86" t="s">
+      <c r="G151" s="63" t="s">
         <v>387</v>
       </c>
       <c r="I151" s="13">
@@ -10455,7 +10519,7 @@
       </c>
     </row>
     <row r="152" spans="1:25">
-      <c r="A152" s="67" t="s">
+      <c r="A152" s="9" t="s">
         <v>162</v>
       </c>
       <c r="B152" s="6" t="s">
@@ -10473,7 +10537,7 @@
       <c r="F152" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G152" s="87" t="s">
+      <c r="G152" s="64" t="s">
         <v>387</v>
       </c>
       <c r="I152" s="5">
@@ -10490,7 +10554,7 @@
       </c>
     </row>
     <row r="153" spans="1:25">
-      <c r="A153" s="67" t="s">
+      <c r="A153" s="9" t="s">
         <v>163</v>
       </c>
       <c r="B153" s="6" t="s">
@@ -10508,7 +10572,7 @@
       <c r="F153" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G153" s="87" t="s">
+      <c r="G153" s="64" t="s">
         <v>386</v>
       </c>
       <c r="I153" s="5">
@@ -10525,7 +10589,7 @@
       </c>
     </row>
     <row r="154" spans="1:25">
-      <c r="A154" s="67" t="s">
+      <c r="A154" s="9" t="s">
         <v>164</v>
       </c>
       <c r="B154" s="6" t="s">
@@ -10543,7 +10607,7 @@
       <c r="F154" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G154" s="87" t="s">
+      <c r="G154" s="64" t="s">
         <v>386</v>
       </c>
       <c r="I154" s="5">
@@ -10560,7 +10624,7 @@
       </c>
     </row>
     <row r="155" spans="1:25">
-      <c r="A155" s="67" t="s">
+      <c r="A155" s="9" t="s">
         <v>165</v>
       </c>
       <c r="B155" s="6" t="s">
@@ -10578,7 +10642,7 @@
       <c r="F155" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G155" s="87" t="s">
+      <c r="G155" s="64" t="s">
         <v>384</v>
       </c>
       <c r="I155" s="5">
@@ -10595,7 +10659,7 @@
       </c>
     </row>
     <row r="156" spans="1:25">
-      <c r="A156" s="67" t="s">
+      <c r="A156" s="9" t="s">
         <v>166</v>
       </c>
       <c r="B156" s="6" t="s">
@@ -10613,7 +10677,7 @@
       <c r="F156" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G156" s="87" t="s">
+      <c r="G156" s="64" t="s">
         <v>384</v>
       </c>
       <c r="I156" s="5">
@@ -10630,7 +10694,7 @@
       </c>
     </row>
     <row r="157" spans="1:25">
-      <c r="A157" s="67" t="s">
+      <c r="A157" s="9" t="s">
         <v>167</v>
       </c>
       <c r="B157" s="6" t="s">
@@ -10648,7 +10712,7 @@
       <c r="F157" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G157" s="87" t="s">
+      <c r="G157" s="64" t="s">
         <v>385</v>
       </c>
       <c r="I157" s="5">
@@ -10665,7 +10729,7 @@
       </c>
     </row>
     <row r="158" spans="1:25">
-      <c r="A158" s="67" t="s">
+      <c r="A158" s="9" t="s">
         <v>168</v>
       </c>
       <c r="B158" s="6" t="s">
@@ -10683,7 +10747,7 @@
       <c r="F158" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G158" s="87" t="s">
+      <c r="G158" s="64" t="s">
         <v>385</v>
       </c>
       <c r="I158" s="5">
@@ -10700,7 +10764,7 @@
       </c>
     </row>
     <row r="159" spans="1:25" s="13" customFormat="1">
-      <c r="A159" s="57" t="s">
+      <c r="A159" s="10" t="s">
         <v>178</v>
       </c>
       <c r="B159" s="13" t="s">
@@ -10724,7 +10788,7 @@
       <c r="X159" s="31"/>
     </row>
     <row r="160" spans="1:25">
-      <c r="A160" s="58" t="s">
+      <c r="A160" s="6" t="s">
         <v>179</v>
       </c>
       <c r="B160" s="5" t="s">
@@ -10747,7 +10811,7 @@
       </c>
     </row>
     <row r="161" spans="1:9">
-      <c r="A161" s="58" t="s">
+      <c r="A161" s="6" t="s">
         <v>180</v>
       </c>
       <c r="B161" s="5" t="s">
@@ -10770,7 +10834,7 @@
       </c>
     </row>
     <row r="162" spans="1:9">
-      <c r="A162" s="58" t="s">
+      <c r="A162" s="6" t="s">
         <v>181</v>
       </c>
       <c r="B162" s="5" t="s">
@@ -10793,7 +10857,7 @@
       </c>
     </row>
     <row r="163" spans="1:9">
-      <c r="A163" s="58" t="s">
+      <c r="A163" s="6" t="s">
         <v>182</v>
       </c>
       <c r="B163" s="5" t="s">
@@ -10816,7 +10880,7 @@
       </c>
     </row>
     <row r="164" spans="1:9">
-      <c r="A164" s="58" t="s">
+      <c r="A164" s="6" t="s">
         <v>183</v>
       </c>
       <c r="B164" s="5" t="s">
@@ -10839,7 +10903,7 @@
       </c>
     </row>
     <row r="165" spans="1:9">
-      <c r="A165" s="58" t="s">
+      <c r="A165" s="6" t="s">
         <v>184</v>
       </c>
       <c r="B165" s="5" t="s">
@@ -10862,7 +10926,7 @@
       </c>
     </row>
     <row r="166" spans="1:9">
-      <c r="A166" s="58" t="s">
+      <c r="A166" s="6" t="s">
         <v>185</v>
       </c>
       <c r="B166" s="5" t="s">
@@ -10885,7 +10949,7 @@
       </c>
     </row>
     <row r="167" spans="1:9">
-      <c r="A167" s="58" t="s">
+      <c r="A167" s="6" t="s">
         <v>186</v>
       </c>
       <c r="B167" s="5" t="s">
@@ -10908,7 +10972,7 @@
       </c>
     </row>
     <row r="168" spans="1:9">
-      <c r="A168" s="58" t="s">
+      <c r="A168" s="6" t="s">
         <v>187</v>
       </c>
       <c r="B168" s="5" t="s">
@@ -10931,7 +10995,7 @@
       </c>
     </row>
     <row r="169" spans="1:9">
-      <c r="A169" s="58" t="s">
+      <c r="A169" s="6" t="s">
         <v>188</v>
       </c>
       <c r="B169" s="5" t="s">
@@ -10954,7 +11018,7 @@
       </c>
     </row>
     <row r="170" spans="1:9">
-      <c r="A170" s="58" t="s">
+      <c r="A170" s="6" t="s">
         <v>189</v>
       </c>
       <c r="B170" s="5" t="s">
@@ -10977,7 +11041,7 @@
       </c>
     </row>
     <row r="171" spans="1:9">
-      <c r="A171" s="58" t="s">
+      <c r="A171" s="6" t="s">
         <v>190</v>
       </c>
       <c r="B171" s="5" t="s">
@@ -11000,7 +11064,7 @@
       </c>
     </row>
     <row r="172" spans="1:9">
-      <c r="A172" s="58" t="s">
+      <c r="A172" s="6" t="s">
         <v>191</v>
       </c>
       <c r="B172" s="5" t="s">
@@ -11023,7 +11087,7 @@
       </c>
     </row>
     <row r="173" spans="1:9">
-      <c r="A173" s="58" t="s">
+      <c r="A173" s="6" t="s">
         <v>192</v>
       </c>
       <c r="B173" s="5" t="s">
@@ -11046,7 +11110,7 @@
       </c>
     </row>
     <row r="174" spans="1:9">
-      <c r="A174" s="58" t="s">
+      <c r="A174" s="6" t="s">
         <v>193</v>
       </c>
       <c r="B174" s="5" t="s">
@@ -11069,7 +11133,7 @@
       </c>
     </row>
     <row r="175" spans="1:9">
-      <c r="A175" s="58" t="s">
+      <c r="A175" s="6" t="s">
         <v>194</v>
       </c>
       <c r="B175" s="5" t="s">
@@ -11092,7 +11156,7 @@
       </c>
     </row>
     <row r="176" spans="1:9">
-      <c r="A176" s="58" t="s">
+      <c r="A176" s="6" t="s">
         <v>195</v>
       </c>
       <c r="B176" s="5" t="s">
@@ -11115,7 +11179,7 @@
       </c>
     </row>
     <row r="177" spans="1:9">
-      <c r="A177" s="58" t="s">
+      <c r="A177" s="6" t="s">
         <v>196</v>
       </c>
       <c r="B177" s="5" t="s">
@@ -11138,7 +11202,7 @@
       </c>
     </row>
     <row r="178" spans="1:9">
-      <c r="A178" s="58" t="s">
+      <c r="A178" s="6" t="s">
         <v>197</v>
       </c>
       <c r="B178" s="5" t="s">
@@ -11161,7 +11225,7 @@
       </c>
     </row>
     <row r="179" spans="1:9">
-      <c r="A179" s="58" t="s">
+      <c r="A179" s="6" t="s">
         <v>198</v>
       </c>
       <c r="B179" s="5" t="s">
@@ -11184,7 +11248,7 @@
       </c>
     </row>
     <row r="180" spans="1:9">
-      <c r="A180" s="58" t="s">
+      <c r="A180" s="6" t="s">
         <v>199</v>
       </c>
       <c r="B180" s="5" t="s">
@@ -11207,7 +11271,7 @@
       </c>
     </row>
     <row r="181" spans="1:9">
-      <c r="A181" s="58" t="s">
+      <c r="A181" s="6" t="s">
         <v>200</v>
       </c>
       <c r="B181" s="5" t="s">
@@ -11230,7 +11294,7 @@
       </c>
     </row>
     <row r="182" spans="1:9">
-      <c r="A182" s="58" t="s">
+      <c r="A182" s="6" t="s">
         <v>201</v>
       </c>
       <c r="B182" s="5" t="s">
@@ -11253,7 +11317,7 @@
       </c>
     </row>
     <row r="183" spans="1:9">
-      <c r="A183" s="58" t="s">
+      <c r="A183" s="6" t="s">
         <v>202</v>
       </c>
       <c r="B183" s="5" t="s">
@@ -11276,7 +11340,7 @@
       </c>
     </row>
     <row r="184" spans="1:9">
-      <c r="A184" s="58" t="s">
+      <c r="A184" s="6" t="s">
         <v>203</v>
       </c>
       <c r="B184" s="5" t="s">
@@ -11299,7 +11363,7 @@
       </c>
     </row>
     <row r="185" spans="1:9">
-      <c r="A185" s="58" t="s">
+      <c r="A185" s="6" t="s">
         <v>204</v>
       </c>
       <c r="B185" s="5" t="s">
@@ -11322,7 +11386,7 @@
       </c>
     </row>
     <row r="186" spans="1:9">
-      <c r="A186" s="58" t="s">
+      <c r="A186" s="6" t="s">
         <v>205</v>
       </c>
       <c r="B186" s="5" t="s">
@@ -11345,7 +11409,7 @@
       </c>
     </row>
     <row r="187" spans="1:9">
-      <c r="A187" s="58" t="s">
+      <c r="A187" s="6" t="s">
         <v>206</v>
       </c>
       <c r="B187" s="5" t="s">
@@ -11368,7 +11432,7 @@
       </c>
     </row>
     <row r="188" spans="1:9">
-      <c r="A188" s="58" t="s">
+      <c r="A188" s="6" t="s">
         <v>207</v>
       </c>
       <c r="B188" s="5" t="s">
@@ -11391,7 +11455,7 @@
       </c>
     </row>
     <row r="189" spans="1:9">
-      <c r="A189" s="58" t="s">
+      <c r="A189" s="6" t="s">
         <v>208</v>
       </c>
       <c r="B189" s="5" t="s">
@@ -11414,7 +11478,7 @@
       </c>
     </row>
     <row r="190" spans="1:9" s="14" customFormat="1">
-      <c r="A190" s="59" t="s">
+      <c r="A190" s="11" t="s">
         <v>209</v>
       </c>
       <c r="B190" s="14" t="s">
@@ -11437,7 +11501,7 @@
       </c>
     </row>
     <row r="191" spans="1:9" s="13" customFormat="1">
-      <c r="A191" s="68" t="s">
+      <c r="A191" s="84" t="s">
         <v>212</v>
       </c>
       <c r="B191" s="13" t="s">
@@ -11460,7 +11524,7 @@
       </c>
     </row>
     <row r="192" spans="1:9">
-      <c r="A192" s="56" t="s">
+      <c r="A192" s="20" t="s">
         <v>213</v>
       </c>
       <c r="B192" s="5" t="s">
@@ -11483,7 +11547,7 @@
       </c>
     </row>
     <row r="193" spans="1:9">
-      <c r="A193" s="56" t="s">
+      <c r="A193" s="20" t="s">
         <v>214</v>
       </c>
       <c r="B193" s="5" t="s">
@@ -11506,7 +11570,7 @@
       </c>
     </row>
     <row r="194" spans="1:9">
-      <c r="A194" s="56" t="s">
+      <c r="A194" s="20" t="s">
         <v>215</v>
       </c>
       <c r="B194" s="5" t="s">
@@ -11529,7 +11593,7 @@
       </c>
     </row>
     <row r="195" spans="1:9">
-      <c r="A195" s="56" t="s">
+      <c r="A195" s="20" t="s">
         <v>216</v>
       </c>
       <c r="B195" s="5" t="s">
@@ -11552,7 +11616,7 @@
       </c>
     </row>
     <row r="196" spans="1:9">
-      <c r="A196" s="56" t="s">
+      <c r="A196" s="20" t="s">
         <v>217</v>
       </c>
       <c r="B196" s="5" t="s">
@@ -11575,7 +11639,7 @@
       </c>
     </row>
     <row r="197" spans="1:9">
-      <c r="A197" s="56" t="s">
+      <c r="A197" s="20" t="s">
         <v>218</v>
       </c>
       <c r="B197" s="5" t="s">
@@ -11598,7 +11662,7 @@
       </c>
     </row>
     <row r="198" spans="1:9">
-      <c r="A198" s="56" t="s">
+      <c r="A198" s="20" t="s">
         <v>219</v>
       </c>
       <c r="B198" s="5" t="s">
@@ -11621,7 +11685,7 @@
       </c>
     </row>
     <row r="199" spans="1:9">
-      <c r="A199" s="56" t="s">
+      <c r="A199" s="20" t="s">
         <v>220</v>
       </c>
       <c r="B199" s="5" t="s">
@@ -11644,7 +11708,7 @@
       </c>
     </row>
     <row r="200" spans="1:9">
-      <c r="A200" s="56" t="s">
+      <c r="A200" s="20" t="s">
         <v>221</v>
       </c>
       <c r="B200" s="5" t="s">
@@ -11667,7 +11731,7 @@
       </c>
     </row>
     <row r="201" spans="1:9">
-      <c r="A201" s="56" t="s">
+      <c r="A201" s="20" t="s">
         <v>222</v>
       </c>
       <c r="B201" s="5" t="s">
@@ -11690,7 +11754,7 @@
       </c>
     </row>
     <row r="202" spans="1:9">
-      <c r="A202" s="56" t="s">
+      <c r="A202" s="20" t="s">
         <v>223</v>
       </c>
       <c r="B202" s="5" t="s">
@@ -11713,7 +11777,7 @@
       </c>
     </row>
     <row r="203" spans="1:9">
-      <c r="A203" s="56" t="s">
+      <c r="A203" s="20" t="s">
         <v>224</v>
       </c>
       <c r="B203" s="5" t="s">
@@ -11736,7 +11800,7 @@
       </c>
     </row>
     <row r="204" spans="1:9">
-      <c r="A204" s="56" t="s">
+      <c r="A204" s="20" t="s">
         <v>225</v>
       </c>
       <c r="B204" s="5" t="s">
@@ -11754,7 +11818,7 @@
       <c r="F204" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G204" s="87" t="s">
+      <c r="G204" s="64" t="s">
         <v>225</v>
       </c>
       <c r="I204" s="17">
@@ -11762,7 +11826,7 @@
       </c>
     </row>
     <row r="205" spans="1:9">
-      <c r="A205" s="56" t="s">
+      <c r="A205" s="20" t="s">
         <v>226</v>
       </c>
       <c r="B205" s="5" t="s">
@@ -11780,12 +11844,12 @@
       <c r="F205" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G205" s="87" t="s">
+      <c r="G205" s="64" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="206" spans="1:9">
-      <c r="A206" s="56" t="s">
+      <c r="A206" s="20" t="s">
         <v>227</v>
       </c>
       <c r="B206" s="5" t="s">
@@ -11803,12 +11867,12 @@
       <c r="F206" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G206" s="87" t="s">
+      <c r="G206" s="64" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="207" spans="1:9">
-      <c r="A207" s="56" t="s">
+      <c r="A207" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B207" s="5" t="s">
@@ -11826,12 +11890,12 @@
       <c r="F207" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G207" s="87" t="s">
+      <c r="G207" s="64" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="208" spans="1:9">
-      <c r="A208" s="56" t="s">
+      <c r="A208" s="20" t="s">
         <v>229</v>
       </c>
       <c r="B208" s="5" t="s">
@@ -11849,12 +11913,12 @@
       <c r="F208" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G208" s="87" t="s">
+      <c r="G208" s="64" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="209" spans="1:7">
-      <c r="A209" s="56" t="s">
+      <c r="A209" s="20" t="s">
         <v>230</v>
       </c>
       <c r="B209" s="5" t="s">
@@ -11872,12 +11936,12 @@
       <c r="F209" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G209" s="87" t="s">
+      <c r="G209" s="64" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="210" spans="1:7">
-      <c r="A210" s="56" t="s">
+      <c r="A210" s="20" t="s">
         <v>231</v>
       </c>
       <c r="B210" s="5" t="s">
@@ -11895,12 +11959,12 @@
       <c r="F210" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G210" s="87" t="s">
+      <c r="G210" s="64" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="211" spans="1:7">
-      <c r="A211" s="56" t="s">
+      <c r="A211" s="20" t="s">
         <v>232</v>
       </c>
       <c r="B211" s="5" t="s">
@@ -11918,12 +11982,12 @@
       <c r="F211" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G211" s="87" t="s">
+      <c r="G211" s="64" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="212" spans="1:7" s="14" customFormat="1">
-      <c r="A212" s="69" t="s">
+      <c r="A212" s="85" t="s">
         <v>233</v>
       </c>
       <c r="B212" s="14" t="s">
@@ -11941,12 +12005,12 @@
       <c r="F212" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G212" s="88" t="s">
+      <c r="G212" s="65" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="213" spans="1:7">
-      <c r="A213" s="62" t="s">
+      <c r="A213" s="80" t="s">
         <v>234</v>
       </c>
       <c r="B213" s="5" t="s">
@@ -11963,7 +12027,7 @@
       </c>
     </row>
     <row r="214" spans="1:7">
-      <c r="A214" s="62" t="s">
+      <c r="A214" s="80" t="s">
         <v>235</v>
       </c>
       <c r="B214" s="5" t="s">
@@ -11980,7 +12044,7 @@
       </c>
     </row>
     <row r="215" spans="1:7">
-      <c r="A215" s="62" t="s">
+      <c r="A215" s="80" t="s">
         <v>236</v>
       </c>
       <c r="B215" s="5" t="s">
@@ -11997,7 +12061,7 @@
       </c>
     </row>
     <row r="216" spans="1:7">
-      <c r="A216" s="62" t="s">
+      <c r="A216" s="80" t="s">
         <v>237</v>
       </c>
       <c r="B216" s="5" t="s">
@@ -12014,7 +12078,7 @@
       </c>
     </row>
     <row r="217" spans="1:7">
-      <c r="A217" s="62" t="s">
+      <c r="A217" s="80" t="s">
         <v>238</v>
       </c>
       <c r="B217" s="5" t="s">
@@ -12031,7 +12095,7 @@
       </c>
     </row>
     <row r="218" spans="1:7">
-      <c r="A218" s="62" t="s">
+      <c r="A218" s="80" t="s">
         <v>239</v>
       </c>
       <c r="B218" s="5" t="s">
@@ -12048,7 +12112,7 @@
       </c>
     </row>
     <row r="219" spans="1:7">
-      <c r="A219" s="62" t="s">
+      <c r="A219" s="80" t="s">
         <v>240</v>
       </c>
       <c r="B219" s="5" t="s">
@@ -12065,7 +12129,7 @@
       </c>
     </row>
     <row r="220" spans="1:7">
-      <c r="A220" s="62" t="s">
+      <c r="A220" s="80" t="s">
         <v>241</v>
       </c>
       <c r="B220" s="5" t="s">
@@ -12082,7 +12146,7 @@
       </c>
     </row>
     <row r="221" spans="1:7">
-      <c r="A221" s="62" t="s">
+      <c r="A221" s="80" t="s">
         <v>242</v>
       </c>
       <c r="B221" s="5" t="s">
@@ -12099,7 +12163,7 @@
       </c>
     </row>
     <row r="222" spans="1:7">
-      <c r="A222" s="62" t="s">
+      <c r="A222" s="80" t="s">
         <v>243</v>
       </c>
       <c r="B222" s="5" t="s">
@@ -12116,7 +12180,7 @@
       </c>
     </row>
     <row r="223" spans="1:7">
-      <c r="A223" s="62" t="s">
+      <c r="A223" s="80" t="s">
         <v>244</v>
       </c>
       <c r="B223" s="5" t="s">
@@ -12133,7 +12197,7 @@
       </c>
     </row>
     <row r="224" spans="1:7">
-      <c r="A224" s="62" t="s">
+      <c r="A224" s="80" t="s">
         <v>245</v>
       </c>
       <c r="B224" s="5" t="s">
@@ -12150,7 +12214,7 @@
       </c>
     </row>
     <row r="225" spans="1:14">
-      <c r="A225" s="62" t="s">
+      <c r="A225" s="80" t="s">
         <v>246</v>
       </c>
       <c r="B225" s="5" t="s">
@@ -12167,7 +12231,7 @@
       </c>
     </row>
     <row r="226" spans="1:14">
-      <c r="A226" s="62" t="s">
+      <c r="A226" s="80" t="s">
         <v>247</v>
       </c>
       <c r="B226" s="5" t="s">
@@ -12184,7 +12248,7 @@
       </c>
     </row>
     <row r="227" spans="1:14">
-      <c r="A227" s="62" t="s">
+      <c r="A227" s="80" t="s">
         <v>248</v>
       </c>
       <c r="B227" s="5" t="s">
@@ -12201,7 +12265,7 @@
       </c>
     </row>
     <row r="228" spans="1:14">
-      <c r="A228" s="62" t="s">
+      <c r="A228" s="80" t="s">
         <v>249</v>
       </c>
       <c r="B228" s="5" t="s">
@@ -12218,7 +12282,7 @@
       </c>
     </row>
     <row r="229" spans="1:14">
-      <c r="A229" s="62" t="s">
+      <c r="A229" s="80" t="s">
         <v>250</v>
       </c>
       <c r="B229" s="5" t="s">
@@ -12235,7 +12299,7 @@
       </c>
     </row>
     <row r="230" spans="1:14">
-      <c r="A230" s="62" t="s">
+      <c r="A230" s="80" t="s">
         <v>251</v>
       </c>
       <c r="B230" s="5" t="s">
@@ -12252,7 +12316,7 @@
       </c>
     </row>
     <row r="231" spans="1:14">
-      <c r="A231" s="62" t="s">
+      <c r="A231" s="80" t="s">
         <v>252</v>
       </c>
       <c r="B231" s="5" t="s">
@@ -12269,7 +12333,7 @@
       </c>
     </row>
     <row r="232" spans="1:14">
-      <c r="A232" s="62" t="s">
+      <c r="A232" s="80" t="s">
         <v>253</v>
       </c>
       <c r="B232" s="5" t="s">
@@ -12286,7 +12350,7 @@
       </c>
     </row>
     <row r="233" spans="1:14">
-      <c r="A233" s="62" t="s">
+      <c r="A233" s="80" t="s">
         <v>254</v>
       </c>
       <c r="B233" s="5" t="s">
@@ -12303,7 +12367,7 @@
       </c>
     </row>
     <row r="234" spans="1:14">
-      <c r="A234" s="62" t="s">
+      <c r="A234" s="80" t="s">
         <v>255</v>
       </c>
       <c r="B234" s="5" t="s">
@@ -12320,7 +12384,7 @@
       </c>
     </row>
     <row r="235" spans="1:14">
-      <c r="A235" s="62" t="s">
+      <c r="A235" s="80" t="s">
         <v>256</v>
       </c>
       <c r="B235" s="5" t="s">
@@ -12337,7 +12401,7 @@
       </c>
     </row>
     <row r="236" spans="1:14">
-      <c r="A236" s="62" t="s">
+      <c r="A236" s="80" t="s">
         <v>257</v>
       </c>
       <c r="B236" s="5" t="s">
@@ -12354,7 +12418,7 @@
       </c>
     </row>
     <row r="237" spans="1:14" ht="18">
-      <c r="A237" s="62" t="s">
+      <c r="A237" s="80" t="s">
         <v>258</v>
       </c>
       <c r="B237" s="5" t="s">
@@ -12369,19 +12433,19 @@
       <c r="E237" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G237" s="83" t="s">
+      <c r="G237" s="60" t="s">
         <v>448</v>
       </c>
-      <c r="H237" s="83"/>
-      <c r="I237" s="83"/>
-      <c r="J237" s="83"/>
-      <c r="K237" s="83"/>
-      <c r="L237" s="83"/>
-      <c r="M237" s="83"/>
-      <c r="N237" s="83"/>
+      <c r="H237" s="60"/>
+      <c r="I237" s="60"/>
+      <c r="J237" s="60"/>
+      <c r="K237" s="60"/>
+      <c r="L237" s="60"/>
+      <c r="M237" s="60"/>
+      <c r="N237" s="60"/>
     </row>
     <row r="238" spans="1:14" ht="19">
-      <c r="A238" s="62" t="s">
+      <c r="A238" s="80" t="s">
         <v>259</v>
       </c>
       <c r="B238" s="5" t="s">
@@ -12396,19 +12460,19 @@
       <c r="E238" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G238" s="83" t="s">
+      <c r="G238" s="60" t="s">
         <v>449</v>
       </c>
-      <c r="H238" s="83"/>
-      <c r="I238" s="83"/>
-      <c r="J238" s="83"/>
-      <c r="K238" s="83"/>
-      <c r="L238" s="83"/>
-      <c r="M238" s="83"/>
-      <c r="N238" s="83"/>
+      <c r="H238" s="60"/>
+      <c r="I238" s="60"/>
+      <c r="J238" s="60"/>
+      <c r="K238" s="60"/>
+      <c r="L238" s="60"/>
+      <c r="M238" s="60"/>
+      <c r="N238" s="60"/>
     </row>
     <row r="239" spans="1:14" ht="18">
-      <c r="A239" s="62" t="s">
+      <c r="A239" s="80" t="s">
         <v>260</v>
       </c>
       <c r="B239" s="5" t="s">
@@ -12423,19 +12487,19 @@
       <c r="E239" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G239" s="83" t="s">
+      <c r="G239" s="60" t="s">
         <v>450</v>
       </c>
-      <c r="H239" s="83"/>
-      <c r="I239" s="83"/>
-      <c r="J239" s="83"/>
-      <c r="K239" s="83"/>
-      <c r="L239" s="83"/>
-      <c r="M239" s="83"/>
-      <c r="N239" s="83"/>
+      <c r="H239" s="60"/>
+      <c r="I239" s="60"/>
+      <c r="J239" s="60"/>
+      <c r="K239" s="60"/>
+      <c r="L239" s="60"/>
+      <c r="M239" s="60"/>
+      <c r="N239" s="60"/>
     </row>
     <row r="240" spans="1:14">
-      <c r="A240" s="62" t="s">
+      <c r="A240" s="80" t="s">
         <v>261</v>
       </c>
       <c r="B240" s="5" t="s">
@@ -12452,7 +12516,7 @@
       </c>
     </row>
     <row r="241" spans="1:14" ht="18">
-      <c r="A241" s="62" t="s">
+      <c r="A241" s="80" t="s">
         <v>262</v>
       </c>
       <c r="B241" s="5" t="s">
@@ -12467,19 +12531,19 @@
       <c r="E241" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G241" s="83" t="s">
+      <c r="G241" s="60" t="s">
         <v>451</v>
       </c>
-      <c r="H241" s="83"/>
-      <c r="I241" s="83"/>
-      <c r="J241" s="83"/>
-      <c r="K241" s="83"/>
-      <c r="L241" s="83"/>
-      <c r="M241" s="83"/>
-      <c r="N241" s="83"/>
+      <c r="H241" s="60"/>
+      <c r="I241" s="60"/>
+      <c r="J241" s="60"/>
+      <c r="K241" s="60"/>
+      <c r="L241" s="60"/>
+      <c r="M241" s="60"/>
+      <c r="N241" s="60"/>
     </row>
     <row r="242" spans="1:14" ht="18">
-      <c r="A242" s="62" t="s">
+      <c r="A242" s="80" t="s">
         <v>263</v>
       </c>
       <c r="B242" s="5" t="s">
@@ -12494,19 +12558,19 @@
       <c r="E242" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G242" s="83" t="s">
+      <c r="G242" s="60" t="s">
         <v>452</v>
       </c>
-      <c r="H242" s="83"/>
-      <c r="I242" s="83"/>
-      <c r="J242" s="83"/>
-      <c r="K242" s="83"/>
-      <c r="L242" s="83"/>
-      <c r="M242" s="83"/>
-      <c r="N242" s="83"/>
+      <c r="H242" s="60"/>
+      <c r="I242" s="60"/>
+      <c r="J242" s="60"/>
+      <c r="K242" s="60"/>
+      <c r="L242" s="60"/>
+      <c r="M242" s="60"/>
+      <c r="N242" s="60"/>
     </row>
     <row r="243" spans="1:14">
-      <c r="A243" s="62" t="s">
+      <c r="A243" s="80" t="s">
         <v>264</v>
       </c>
       <c r="B243" s="5" t="s">
@@ -12523,7 +12587,7 @@
       </c>
     </row>
     <row r="244" spans="1:14" ht="18">
-      <c r="A244" s="62" t="s">
+      <c r="A244" s="80" t="s">
         <v>265</v>
       </c>
       <c r="B244" s="5" t="s">
@@ -12538,19 +12602,19 @@
       <c r="E244" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G244" s="84" t="s">
+      <c r="G244" s="61" t="s">
         <v>453</v>
       </c>
-      <c r="H244" s="84"/>
-      <c r="I244" s="84"/>
-      <c r="J244" s="84"/>
-      <c r="K244" s="84"/>
-      <c r="L244" s="84"/>
-      <c r="M244" s="84"/>
-      <c r="N244" s="84"/>
+      <c r="H244" s="61"/>
+      <c r="I244" s="61"/>
+      <c r="J244" s="61"/>
+      <c r="K244" s="61"/>
+      <c r="L244" s="61"/>
+      <c r="M244" s="61"/>
+      <c r="N244" s="61"/>
     </row>
     <row r="245" spans="1:14">
-      <c r="A245" s="62" t="s">
+      <c r="A245" s="80" t="s">
         <v>266</v>
       </c>
       <c r="B245" s="5" t="s">
@@ -12567,7 +12631,7 @@
       </c>
     </row>
     <row r="246" spans="1:14" ht="18">
-      <c r="A246" s="62" t="s">
+      <c r="A246" s="80" t="s">
         <v>267</v>
       </c>
       <c r="B246" s="5" t="s">
@@ -12582,19 +12646,19 @@
       <c r="E246" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G246" s="85" t="s">
+      <c r="G246" s="62" t="s">
         <v>454</v>
       </c>
-      <c r="H246" s="85"/>
-      <c r="I246" s="85"/>
-      <c r="J246" s="85"/>
-      <c r="K246" s="85"/>
-      <c r="L246" s="85"/>
-      <c r="M246" s="85"/>
-      <c r="N246" s="85"/>
+      <c r="H246" s="62"/>
+      <c r="I246" s="62"/>
+      <c r="J246" s="62"/>
+      <c r="K246" s="62"/>
+      <c r="L246" s="62"/>
+      <c r="M246" s="62"/>
+      <c r="N246" s="62"/>
     </row>
     <row r="247" spans="1:14">
-      <c r="A247" s="62" t="s">
+      <c r="A247" s="80" t="s">
         <v>268</v>
       </c>
       <c r="B247" s="5" t="s">
@@ -12611,7 +12675,7 @@
       </c>
     </row>
     <row r="248" spans="1:14" ht="18">
-      <c r="A248" s="62" t="s">
+      <c r="A248" s="80" t="s">
         <v>269</v>
       </c>
       <c r="B248" s="5" t="s">
@@ -12626,19 +12690,19 @@
       <c r="E248" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G248" s="85" t="s">
+      <c r="G248" s="62" t="s">
         <v>455</v>
       </c>
-      <c r="H248" s="85"/>
-      <c r="I248" s="85"/>
-      <c r="J248" s="85"/>
-      <c r="K248" s="85"/>
-      <c r="L248" s="85"/>
-      <c r="M248" s="85"/>
-      <c r="N248" s="85"/>
+      <c r="H248" s="62"/>
+      <c r="I248" s="62"/>
+      <c r="J248" s="62"/>
+      <c r="K248" s="62"/>
+      <c r="L248" s="62"/>
+      <c r="M248" s="62"/>
+      <c r="N248" s="62"/>
     </row>
     <row r="249" spans="1:14">
-      <c r="A249" s="62" t="s">
+      <c r="A249" s="80" t="s">
         <v>270</v>
       </c>
       <c r="B249" s="5" t="s">
@@ -12655,7 +12719,7 @@
       </c>
     </row>
     <row r="250" spans="1:14" ht="18">
-      <c r="A250" s="62" t="s">
+      <c r="A250" s="80" t="s">
         <v>271</v>
       </c>
       <c r="B250" s="5" t="s">
@@ -12670,19 +12734,19 @@
       <c r="E250" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G250" s="85" t="s">
+      <c r="G250" s="62" t="s">
         <v>456</v>
       </c>
-      <c r="H250" s="85"/>
-      <c r="I250" s="85"/>
-      <c r="J250" s="85"/>
-      <c r="K250" s="85"/>
-      <c r="L250" s="85"/>
-      <c r="M250" s="85"/>
-      <c r="N250" s="85"/>
+      <c r="H250" s="62"/>
+      <c r="I250" s="62"/>
+      <c r="J250" s="62"/>
+      <c r="K250" s="62"/>
+      <c r="L250" s="62"/>
+      <c r="M250" s="62"/>
+      <c r="N250" s="62"/>
     </row>
     <row r="251" spans="1:14">
-      <c r="A251" s="62" t="s">
+      <c r="A251" s="80" t="s">
         <v>272</v>
       </c>
       <c r="B251" s="5" t="s">
@@ -12699,7 +12763,7 @@
       </c>
     </row>
     <row r="252" spans="1:14" ht="18">
-      <c r="A252" s="62" t="s">
+      <c r="A252" s="80" t="s">
         <v>273</v>
       </c>
       <c r="B252" s="5" t="s">
@@ -12714,19 +12778,19 @@
       <c r="E252" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G252" s="85" t="s">
+      <c r="G252" s="62" t="s">
         <v>457</v>
       </c>
-      <c r="H252" s="85"/>
-      <c r="I252" s="85"/>
-      <c r="J252" s="85"/>
-      <c r="K252" s="85"/>
-      <c r="L252" s="85"/>
-      <c r="M252" s="85"/>
-      <c r="N252" s="85"/>
+      <c r="H252" s="62"/>
+      <c r="I252" s="62"/>
+      <c r="J252" s="62"/>
+      <c r="K252" s="62"/>
+      <c r="L252" s="62"/>
+      <c r="M252" s="62"/>
+      <c r="N252" s="62"/>
     </row>
     <row r="253" spans="1:14" ht="18">
-      <c r="A253" s="62" t="s">
+      <c r="A253" s="80" t="s">
         <v>274</v>
       </c>
       <c r="B253" s="5" t="s">
@@ -12741,19 +12805,19 @@
       <c r="E253" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G253" s="85" t="s">
+      <c r="G253" s="62" t="s">
         <v>458</v>
       </c>
-      <c r="H253" s="85"/>
-      <c r="I253" s="85"/>
-      <c r="J253" s="85"/>
-      <c r="K253" s="85"/>
-      <c r="L253" s="85"/>
-      <c r="M253" s="85"/>
-      <c r="N253" s="85"/>
+      <c r="H253" s="62"/>
+      <c r="I253" s="62"/>
+      <c r="J253" s="62"/>
+      <c r="K253" s="62"/>
+      <c r="L253" s="62"/>
+      <c r="M253" s="62"/>
+      <c r="N253" s="62"/>
     </row>
     <row r="254" spans="1:14">
-      <c r="A254" s="62" t="s">
+      <c r="A254" s="80" t="s">
         <v>71</v>
       </c>
       <c r="B254" s="5" t="s">
@@ -12770,7 +12834,7 @@
       </c>
     </row>
     <row r="255" spans="1:14">
-      <c r="A255" s="62" t="s">
+      <c r="A255" s="80" t="s">
         <v>72</v>
       </c>
       <c r="B255" s="5" t="s">
@@ -12787,7 +12851,7 @@
       </c>
     </row>
     <row r="256" spans="1:14">
-      <c r="A256" s="62" t="s">
+      <c r="A256" s="80" t="s">
         <v>73</v>
       </c>
       <c r="B256" s="5" t="s">
@@ -12803,8 +12867,8 @@
         <v>303</v>
       </c>
     </row>
-    <row r="257" spans="1:9">
-      <c r="A257" s="62" t="s">
+    <row r="257" spans="1:8">
+      <c r="A257" s="80" t="s">
         <v>74</v>
       </c>
       <c r="B257" s="5" t="s">
@@ -12820,8 +12884,8 @@
         <v>303</v>
       </c>
     </row>
-    <row r="258" spans="1:9">
-      <c r="A258" s="62" t="s">
+    <row r="258" spans="1:8">
+      <c r="A258" s="80" t="s">
         <v>75</v>
       </c>
       <c r="B258" s="5" t="s">
@@ -12837,423 +12901,423 @@
         <v>303</v>
       </c>
     </row>
-    <row r="259" spans="1:9" s="15" customFormat="1">
-      <c r="A259" s="70" t="s">
+    <row r="259" spans="1:8" s="13" customFormat="1">
+      <c r="A259" s="86" t="s">
+        <v>459</v>
+      </c>
+      <c r="B259" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C259" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D259" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E259" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G259" s="86" t="s">
+        <v>480</v>
+      </c>
+      <c r="H259" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" s="71" customFormat="1">
+      <c r="A260" s="86" t="s">
+        <v>460</v>
+      </c>
+      <c r="B260" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C260" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D260" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E260" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G260" s="86" t="s">
+        <v>480</v>
+      </c>
+      <c r="H260" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" s="71" customFormat="1">
+      <c r="A261" s="86" t="s">
+        <v>461</v>
+      </c>
+      <c r="B261" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C261" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D261" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G261" s="86" t="s">
+        <v>480</v>
+      </c>
+      <c r="H261" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" s="71" customFormat="1">
+      <c r="A262" s="86" t="s">
+        <v>462</v>
+      </c>
+      <c r="B262" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C262" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D262" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G262" s="86" t="s">
+        <v>481</v>
+      </c>
+      <c r="H262" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" s="71" customFormat="1">
+      <c r="A263" s="86" t="s">
+        <v>463</v>
+      </c>
+      <c r="B263" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C263" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D263" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E263" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G263" s="86" t="s">
+        <v>481</v>
+      </c>
+      <c r="H263" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" s="71" customFormat="1">
+      <c r="A264" s="86" t="s">
+        <v>464</v>
+      </c>
+      <c r="B264" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C264" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D264" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E264" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G264" s="86" t="s">
+        <v>481</v>
+      </c>
+      <c r="H264" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" s="71" customFormat="1">
+      <c r="A265" s="86" t="s">
+        <v>465</v>
+      </c>
+      <c r="B265" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C265" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D265" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E265" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G265" s="86" t="s">
+        <v>481</v>
+      </c>
+      <c r="H265" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" s="71" customFormat="1">
+      <c r="A266" s="86" t="s">
+        <v>466</v>
+      </c>
+      <c r="B266" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C266" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D266" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E266" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G266" s="86" t="s">
+        <v>482</v>
+      </c>
+      <c r="H266" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" s="71" customFormat="1">
+      <c r="A267" s="86" t="s">
+        <v>467</v>
+      </c>
+      <c r="B267" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C267" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D267" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E267" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G267" s="86" t="s">
+        <v>482</v>
+      </c>
+      <c r="H267" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" s="71" customFormat="1">
+      <c r="A268" s="86" t="s">
+        <v>468</v>
+      </c>
+      <c r="B268" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C268" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D268" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E268" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G268" s="86" t="s">
+        <v>482</v>
+      </c>
+      <c r="H268" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" s="71" customFormat="1">
+      <c r="A269" s="86" t="s">
+        <v>469</v>
+      </c>
+      <c r="B269" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C269" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D269" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E269" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G269" s="86" t="s">
+        <v>482</v>
+      </c>
+      <c r="H269" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" s="71" customFormat="1">
+      <c r="A270" s="86" t="s">
+        <v>470</v>
+      </c>
+      <c r="B270" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C270" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D270" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E270" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G270" s="86" t="s">
+        <v>483</v>
+      </c>
+      <c r="H270" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" s="71" customFormat="1">
+      <c r="A271" s="86" t="s">
+        <v>471</v>
+      </c>
+      <c r="B271" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C271" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D271" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E271" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G271" s="86" t="s">
+        <v>483</v>
+      </c>
+      <c r="H271" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" s="71" customFormat="1">
+      <c r="A272" s="86" t="s">
+        <v>472</v>
+      </c>
+      <c r="B272" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C272" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D272" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E272" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G272" s="86" t="s">
+        <v>483</v>
+      </c>
+      <c r="H272" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" s="71" customFormat="1">
+      <c r="A273" s="86" t="s">
+        <v>473</v>
+      </c>
+      <c r="B273" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C273" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D273" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E273" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G273" s="86" t="s">
+        <v>483</v>
+      </c>
+      <c r="H273" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" s="71" customFormat="1">
+      <c r="A274" s="86" t="s">
+        <v>474</v>
+      </c>
+      <c r="B274" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C274" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D274" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E274" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G274" s="86" t="s">
+        <v>484</v>
+      </c>
+      <c r="H274" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" s="71" customFormat="1">
+      <c r="A275" s="86" t="s">
+        <v>475</v>
+      </c>
+      <c r="B275" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C275" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D275" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E275" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G275" s="86" t="s">
+        <v>484</v>
+      </c>
+      <c r="H275" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" s="71" customFormat="1">
+      <c r="A276" s="86" t="s">
+        <v>476</v>
+      </c>
+      <c r="B276" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C276" s="38" t="s">
+        <v>478</v>
+      </c>
+      <c r="D276" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E276" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="G276" s="86" t="s">
+        <v>484</v>
+      </c>
+      <c r="H276" s="13" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" s="15" customFormat="1">
+      <c r="A277" s="7" t="s">
         <v>278</v>
-      </c>
-      <c r="B259" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C259" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D259" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="E259" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F259" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="I259" s="44">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="260" spans="1:9" s="15" customFormat="1">
-      <c r="A260" s="70" t="s">
-        <v>279</v>
-      </c>
-      <c r="B260" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C260" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D260" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E260" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F260" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I260" s="44">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="261" spans="1:9" s="15" customFormat="1">
-      <c r="A261" s="70" t="s">
-        <v>280</v>
-      </c>
-      <c r="B261" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C261" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D261" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E261" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F261" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I261" s="44">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="262" spans="1:9" s="15" customFormat="1">
-      <c r="A262" s="70" t="s">
-        <v>281</v>
-      </c>
-      <c r="B262" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C262" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D262" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E262" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F262" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I262" s="44">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="263" spans="1:9" s="15" customFormat="1">
-      <c r="A263" s="70" t="s">
-        <v>282</v>
-      </c>
-      <c r="B263" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C263" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D263" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E263" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F263" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I263" s="44">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="264" spans="1:9" s="15" customFormat="1">
-      <c r="A264" s="70" t="s">
-        <v>283</v>
-      </c>
-      <c r="B264" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C264" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D264" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E264" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F264" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I264" s="44">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="265" spans="1:9" s="15" customFormat="1">
-      <c r="A265" s="70" t="s">
-        <v>284</v>
-      </c>
-      <c r="B265" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C265" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D265" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E265" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F265" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I265" s="44">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="266" spans="1:9" s="15" customFormat="1">
-      <c r="A266" s="70" t="s">
-        <v>285</v>
-      </c>
-      <c r="B266" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C266" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D266" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E266" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F266" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I266" s="44">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="267" spans="1:9" s="15" customFormat="1">
-      <c r="A267" s="70" t="s">
-        <v>286</v>
-      </c>
-      <c r="B267" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C267" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D267" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E267" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F267" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I267" s="44">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" s="15" customFormat="1">
-      <c r="A268" s="70" t="s">
-        <v>287</v>
-      </c>
-      <c r="B268" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C268" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D268" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E268" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F268" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I268" s="44">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9" s="15" customFormat="1">
-      <c r="A269" s="70" t="s">
-        <v>288</v>
-      </c>
-      <c r="B269" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C269" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D269" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E269" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F269" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I269" s="44">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9" s="15" customFormat="1">
-      <c r="A270" s="70" t="s">
-        <v>289</v>
-      </c>
-      <c r="B270" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C270" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D270" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E270" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F270" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I270" s="44">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9" s="15" customFormat="1">
-      <c r="A271" s="70" t="s">
-        <v>290</v>
-      </c>
-      <c r="B271" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C271" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D271" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E271" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F271" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I271" s="44">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9" s="15" customFormat="1">
-      <c r="A272" s="70" t="s">
-        <v>291</v>
-      </c>
-      <c r="B272" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C272" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D272" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E272" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F272" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I272" s="44">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9" s="15" customFormat="1">
-      <c r="A273" s="70" t="s">
-        <v>292</v>
-      </c>
-      <c r="B273" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C273" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D273" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E273" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F273" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I273" s="44">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" s="15" customFormat="1">
-      <c r="A274" s="70" t="s">
-        <v>293</v>
-      </c>
-      <c r="B274" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C274" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D274" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E274" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F274" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="I274" s="44">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" s="15" customFormat="1">
-      <c r="A275" s="70" t="s">
-        <v>294</v>
-      </c>
-      <c r="B275" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C275" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D275" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E275" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F275" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G275" s="93" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" s="15" customFormat="1">
-      <c r="A276" s="70" t="s">
-        <v>295</v>
-      </c>
-      <c r="B276" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C276" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="D276" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E276" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="F276" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G276" s="93" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" s="15" customFormat="1">
-      <c r="A277" s="70" t="s">
-        <v>296</v>
       </c>
       <c r="B277" s="15" t="s">
         <v>275</v>
@@ -13261,7 +13325,7 @@
       <c r="C277" s="43" t="s">
         <v>308</v>
       </c>
-      <c r="D277" s="37" t="s">
+      <c r="D277" s="39" t="s">
         <v>171</v>
       </c>
       <c r="E277" s="15" t="s">
@@ -13270,13 +13334,13 @@
       <c r="F277" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G277" s="93" t="s">
-        <v>378</v>
+      <c r="I277" s="44">
+        <v>0.52</v>
       </c>
     </row>
     <row r="278" spans="1:9" s="15" customFormat="1">
-      <c r="A278" s="70" t="s">
-        <v>297</v>
+      <c r="A278" s="7" t="s">
+        <v>279</v>
       </c>
       <c r="B278" s="15" t="s">
         <v>275</v>
@@ -13291,15 +13355,15 @@
         <v>304</v>
       </c>
       <c r="F278" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G278" s="93" t="s">
-        <v>379</v>
+        <v>169</v>
+      </c>
+      <c r="I278" s="44">
+        <v>0.12</v>
       </c>
     </row>
     <row r="279" spans="1:9" s="15" customFormat="1">
-      <c r="A279" s="70" t="s">
-        <v>298</v>
+      <c r="A279" s="7" t="s">
+        <v>280</v>
       </c>
       <c r="B279" s="15" t="s">
         <v>275</v>
@@ -13314,15 +13378,15 @@
         <v>304</v>
       </c>
       <c r="F279" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G279" s="93" t="s">
-        <v>379</v>
+        <v>169</v>
+      </c>
+      <c r="I279" s="44">
+        <v>0.18</v>
       </c>
     </row>
     <row r="280" spans="1:9" s="15" customFormat="1">
-      <c r="A280" s="70" t="s">
-        <v>299</v>
+      <c r="A280" s="7" t="s">
+        <v>281</v>
       </c>
       <c r="B280" s="15" t="s">
         <v>275</v>
@@ -13337,15 +13401,15 @@
         <v>304</v>
       </c>
       <c r="F280" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G280" s="93" t="s">
-        <v>379</v>
+        <v>169</v>
+      </c>
+      <c r="I280" s="44">
+        <v>0.23</v>
       </c>
     </row>
     <row r="281" spans="1:9" s="15" customFormat="1">
-      <c r="A281" s="70" t="s">
-        <v>300</v>
+      <c r="A281" s="7" t="s">
+        <v>282</v>
       </c>
       <c r="B281" s="15" t="s">
         <v>275</v>
@@ -13360,15 +13424,15 @@
         <v>304</v>
       </c>
       <c r="F281" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G281" s="93" t="s">
-        <v>380</v>
+        <v>169</v>
+      </c>
+      <c r="I281" s="44">
+        <v>0.34</v>
       </c>
     </row>
     <row r="282" spans="1:9" s="15" customFormat="1">
-      <c r="A282" s="70" t="s">
-        <v>301</v>
+      <c r="A282" s="7" t="s">
+        <v>283</v>
       </c>
       <c r="B282" s="15" t="s">
         <v>275</v>
@@ -13383,15 +13447,15 @@
         <v>304</v>
       </c>
       <c r="F282" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G282" s="93" t="s">
-        <v>380</v>
+        <v>169</v>
+      </c>
+      <c r="I282" s="44">
+        <v>0.45</v>
       </c>
     </row>
     <row r="283" spans="1:9" s="15" customFormat="1">
-      <c r="A283" s="70" t="s">
-        <v>302</v>
+      <c r="A283" s="7" t="s">
+        <v>284</v>
       </c>
       <c r="B283" s="15" t="s">
         <v>275</v>
@@ -13399,16 +13463,430 @@
       <c r="C283" s="43" t="s">
         <v>308</v>
       </c>
-      <c r="D283" s="42" t="s">
+      <c r="D283" s="37" t="s">
         <v>171</v>
       </c>
       <c r="E283" s="15" t="s">
         <v>304</v>
       </c>
       <c r="F283" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I283" s="44">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" s="15" customFormat="1">
+      <c r="A284" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B284" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C284" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D284" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E284" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F284" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I284" s="44">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" s="15" customFormat="1">
+      <c r="A285" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B285" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C285" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D285" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E285" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F285" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I285" s="44">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" s="15" customFormat="1">
+      <c r="A286" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B286" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C286" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D286" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E286" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F286" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I286" s="44">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" s="15" customFormat="1">
+      <c r="A287" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B287" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C287" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D287" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E287" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F287" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I287" s="44">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" s="15" customFormat="1">
+      <c r="A288" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B288" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C288" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D288" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E288" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F288" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I288" s="44">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" s="15" customFormat="1">
+      <c r="A289" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B289" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C289" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D289" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E289" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F289" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I289" s="44">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" s="15" customFormat="1">
+      <c r="A290" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B290" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C290" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D290" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E290" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F290" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I290" s="44">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" s="15" customFormat="1">
+      <c r="A291" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B291" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C291" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D291" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E291" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F291" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I291" s="44">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" s="15" customFormat="1">
+      <c r="A292" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="B292" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C292" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D292" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E292" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F292" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="I292" s="44">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" s="15" customFormat="1">
+      <c r="A293" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B293" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C293" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D293" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E293" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F293" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G283" s="93" t="s">
+      <c r="G293" s="70" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" s="15" customFormat="1">
+      <c r="A294" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B294" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C294" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D294" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E294" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F294" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G294" s="70" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" s="15" customFormat="1">
+      <c r="A295" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B295" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C295" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D295" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E295" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F295" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G295" s="70" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" s="15" customFormat="1">
+      <c r="A296" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B296" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C296" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D296" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E296" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F296" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G296" s="70" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" s="15" customFormat="1">
+      <c r="A297" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B297" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C297" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D297" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E297" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F297" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G297" s="70" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" s="15" customFormat="1">
+      <c r="A298" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B298" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C298" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D298" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E298" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F298" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G298" s="70" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" s="15" customFormat="1">
+      <c r="A299" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B299" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C299" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D299" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E299" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F299" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G299" s="70" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" s="15" customFormat="1">
+      <c r="A300" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B300" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C300" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D300" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E300" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F300" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G300" s="70" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" s="15" customFormat="1">
+      <c r="A301" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B301" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C301" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D301" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="E301" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F301" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G301" s="70" t="s">
         <v>380</v>
       </c>
     </row>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/large_scale_yeast_proteomics_analysis/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7A3013-0787-BF4A-A8A5-08C35CA4989A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5161104-FDE8-B740-B0AA-B4FB1B62A3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40040" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2360" yWindow="500" windowWidth="37660" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/large_scale_yeast_proteomics_analysis/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2207DB-0300-7D49-BAA7-86BDB2FF07A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6639D6A2-DB14-1A4A-A425-850FBF6C7C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2360" yWindow="500" windowWidth="37660" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2856" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2895" uniqueCount="511">
   <si>
     <t>sample</t>
   </si>
@@ -1722,6 +1722,63 @@
   </si>
   <si>
     <t>sysbio_Kate</t>
+  </si>
+  <si>
+    <t>Trehalose</t>
+  </si>
+  <si>
+    <t>Glucose</t>
+  </si>
+  <si>
+    <t>Maltose</t>
+  </si>
+  <si>
+    <t>Galactose</t>
+  </si>
+  <si>
+    <t>cycloheximide_inhibition_miu=0.12</t>
+  </si>
+  <si>
+    <t>cycloheximide_inhibition_miu=0.39</t>
+  </si>
+  <si>
+    <t>cycloheximide_inhibition_miu=0.32</t>
+  </si>
+  <si>
+    <t>cycloheximide_inhibition_miu=0.2</t>
+  </si>
+  <si>
+    <t>maltose</t>
+  </si>
+  <si>
+    <t>oleate</t>
+  </si>
+  <si>
+    <t>fructose</t>
+  </si>
+  <si>
+    <t>sucrose</t>
+  </si>
+  <si>
+    <t>trehalose</t>
+  </si>
+  <si>
+    <t>lactate</t>
+  </si>
+  <si>
+    <t>acetate</t>
+  </si>
+  <si>
+    <t>pryuvate</t>
+  </si>
+  <si>
+    <t>glycerol</t>
+  </si>
+  <si>
+    <t>galactose</t>
+  </si>
+  <si>
+    <t>raffinose</t>
   </si>
 </sst>
 </file>
@@ -1982,7 +2039,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2210,6 +2267,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -2416,7 +2479,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2659,6 +2722,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="41" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="42" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -9137,7 +9209,9 @@
       <c r="F100" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G100" s="61"/>
+      <c r="G100" s="74" t="s">
+        <v>106</v>
+      </c>
       <c r="H100" s="12" t="s">
         <v>172</v>
       </c>
@@ -9164,7 +9238,9 @@
       <c r="F101" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G101" s="61"/>
+      <c r="G101" s="74" t="s">
+        <v>107</v>
+      </c>
       <c r="H101" s="12" t="s">
         <v>172</v>
       </c>
@@ -9191,7 +9267,9 @@
       <c r="F102" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G102" s="61"/>
+      <c r="G102" s="74" t="s">
+        <v>108</v>
+      </c>
       <c r="H102" s="12" t="s">
         <v>172</v>
       </c>
@@ -9218,7 +9296,9 @@
       <c r="F103" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G103" s="61"/>
+      <c r="G103" s="74" t="s">
+        <v>109</v>
+      </c>
       <c r="H103" s="12" t="s">
         <v>172</v>
       </c>
@@ -9245,7 +9325,9 @@
       <c r="F104" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G104" s="61"/>
+      <c r="G104" s="74" t="s">
+        <v>110</v>
+      </c>
       <c r="H104" s="12" t="s">
         <v>172</v>
       </c>
@@ -9272,7 +9354,9 @@
       <c r="F105" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G105" s="61"/>
+      <c r="G105" s="74" t="s">
+        <v>111</v>
+      </c>
       <c r="H105" s="12" t="s">
         <v>172</v>
       </c>
@@ -9299,7 +9383,9 @@
       <c r="F106" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G106" s="61"/>
+      <c r="G106" s="74" t="s">
+        <v>112</v>
+      </c>
       <c r="H106" s="12" t="s">
         <v>172</v>
       </c>
@@ -9326,7 +9412,9 @@
       <c r="F107" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G107" s="61"/>
+      <c r="G107" s="74" t="s">
+        <v>113</v>
+      </c>
       <c r="H107" s="12" t="s">
         <v>172</v>
       </c>
@@ -9353,7 +9441,9 @@
       <c r="F108" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G108" s="61"/>
+      <c r="G108" s="74" t="s">
+        <v>114</v>
+      </c>
       <c r="H108" s="12" t="s">
         <v>172</v>
       </c>
@@ -9380,7 +9470,9 @@
       <c r="F109" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G109" s="61"/>
+      <c r="G109" s="74" t="s">
+        <v>115</v>
+      </c>
       <c r="H109" s="12" t="s">
         <v>172</v>
       </c>
@@ -9407,7 +9499,9 @@
       <c r="F110" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="G110" s="60"/>
+      <c r="G110" s="10" t="s">
+        <v>500</v>
+      </c>
       <c r="H110" s="13" t="s">
         <v>209</v>
       </c>
@@ -9437,7 +9531,9 @@
       <c r="F111" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G111" s="61"/>
+      <c r="G111" s="6" t="s">
+        <v>501</v>
+      </c>
       <c r="H111" s="5" t="s">
         <v>209</v>
       </c>
@@ -9467,7 +9563,9 @@
       <c r="F112" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G112" s="61"/>
+      <c r="G112" s="6" t="s">
+        <v>502</v>
+      </c>
       <c r="H112" s="5" t="s">
         <v>209</v>
       </c>
@@ -9497,7 +9595,9 @@
       <c r="F113" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G113" s="61"/>
+      <c r="G113" s="6" t="s">
+        <v>503</v>
+      </c>
       <c r="H113" s="5" t="s">
         <v>209</v>
       </c>
@@ -9527,7 +9627,9 @@
       <c r="F114" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G114" s="61"/>
+      <c r="G114" s="6" t="s">
+        <v>504</v>
+      </c>
       <c r="H114" s="5" t="s">
         <v>209</v>
       </c>
@@ -9557,7 +9659,9 @@
       <c r="F115" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G115" s="61"/>
+      <c r="G115" s="6" t="s">
+        <v>505</v>
+      </c>
       <c r="H115" s="5" t="s">
         <v>209</v>
       </c>
@@ -9587,7 +9691,9 @@
       <c r="F116" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G116" s="61"/>
+      <c r="G116" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="H116" s="5" t="s">
         <v>209</v>
       </c>
@@ -9617,7 +9723,9 @@
       <c r="F117" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G117" s="61"/>
+      <c r="G117" s="6" t="s">
+        <v>507</v>
+      </c>
       <c r="H117" s="5" t="s">
         <v>209</v>
       </c>
@@ -9647,7 +9755,9 @@
       <c r="F118" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G118" s="61"/>
+      <c r="G118" s="6" t="s">
+        <v>508</v>
+      </c>
       <c r="H118" s="5" t="s">
         <v>209</v>
       </c>
@@ -9677,7 +9787,9 @@
       <c r="F119" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G119" s="61"/>
+      <c r="G119" s="6" t="s">
+        <v>509</v>
+      </c>
       <c r="H119" s="5" t="s">
         <v>209</v>
       </c>
@@ -9707,7 +9819,9 @@
       <c r="F120" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G120" s="62"/>
+      <c r="G120" s="11" t="s">
+        <v>510</v>
+      </c>
       <c r="H120" s="14" t="s">
         <v>209</v>
       </c>
@@ -10785,7 +10899,7 @@
       <c r="B159" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="C159" s="37" t="s">
+      <c r="C159" s="88" t="s">
         <v>307</v>
       </c>
       <c r="D159" s="38" t="s">
@@ -10797,12 +10911,15 @@
       <c r="F159" s="13" t="s">
         <v>128</v>
       </c>
+      <c r="G159" s="86" t="s">
+        <v>492</v>
+      </c>
       <c r="I159" s="13">
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="X159" s="31"/>
     </row>
-    <row r="160" spans="1:25">
+    <row r="160" spans="1:25" ht="14" customHeight="1">
       <c r="A160" s="6" t="s">
         <v>177</v>
       </c>
@@ -10820,6 +10937,9 @@
       </c>
       <c r="F160" s="5" t="s">
         <v>128</v>
+      </c>
+      <c r="G160" s="87" t="s">
+        <v>492</v>
       </c>
       <c r="I160" s="5">
         <v>5.0999999999999997E-2</v>
@@ -10844,6 +10964,9 @@
       <c r="F161" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G161" s="87" t="s">
+        <v>492</v>
+      </c>
       <c r="I161" s="5">
         <v>4.8000000000000001E-2</v>
       </c>
@@ -10867,6 +10990,9 @@
       <c r="F162" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G162" s="87" t="s">
+        <v>492</v>
+      </c>
       <c r="I162" s="5">
         <v>4.7E-2</v>
       </c>
@@ -10890,6 +11016,9 @@
       <c r="F163" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G163" s="6" t="s">
+        <v>495</v>
+      </c>
       <c r="I163" s="5">
         <v>0.16500000000000001</v>
       </c>
@@ -10913,6 +11042,9 @@
       <c r="F164" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G164" s="6" t="s">
+        <v>495</v>
+      </c>
       <c r="I164" s="5">
         <v>0.182</v>
       </c>
@@ -10936,6 +11068,9 @@
       <c r="F165" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G165" s="6" t="s">
+        <v>494</v>
+      </c>
       <c r="I165" s="5">
         <v>0.27500000000000002</v>
       </c>
@@ -10959,6 +11094,9 @@
       <c r="F166" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G166" s="6" t="s">
+        <v>494</v>
+      </c>
       <c r="I166" s="5">
         <v>0.29099999999999998</v>
       </c>
@@ -10982,6 +11120,9 @@
       <c r="F167" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G167" s="6" t="s">
+        <v>493</v>
+      </c>
       <c r="I167" s="5">
         <v>0.373</v>
       </c>
@@ -11005,6 +11146,9 @@
       <c r="F168" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G168" s="6" t="s">
+        <v>493</v>
+      </c>
       <c r="I168" s="5">
         <v>0.36899999999999999</v>
       </c>
@@ -11028,6 +11172,9 @@
       <c r="F169" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G169" s="5" t="s">
+        <v>496</v>
+      </c>
       <c r="I169" s="5">
         <v>0.121</v>
       </c>
@@ -11051,6 +11198,9 @@
       <c r="F170" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G170" s="5" t="s">
+        <v>496</v>
+      </c>
       <c r="I170" s="5">
         <v>0.106</v>
       </c>
@@ -11074,6 +11224,9 @@
       <c r="F171" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G171" s="5" t="s">
+        <v>499</v>
+      </c>
       <c r="I171" s="5">
         <v>0.2</v>
       </c>
@@ -11097,6 +11250,9 @@
       <c r="F172" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G172" s="5" t="s">
+        <v>499</v>
+      </c>
       <c r="I172" s="5">
         <v>0.20100000000000001</v>
       </c>
@@ -11120,6 +11276,9 @@
       <c r="F173" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G173" s="5" t="s">
+        <v>498</v>
+      </c>
       <c r="I173" s="5">
         <v>0.32700000000000001</v>
       </c>
@@ -11143,6 +11302,9 @@
       <c r="F174" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G174" s="5" t="s">
+        <v>498</v>
+      </c>
       <c r="I174" s="5">
         <v>0.318</v>
       </c>
@@ -11166,6 +11328,9 @@
       <c r="F175" s="5" t="s">
         <v>128</v>
       </c>
+      <c r="G175" s="5" t="s">
+        <v>497</v>
+      </c>
       <c r="I175" s="5">
         <v>0.42099999999999999</v>
       </c>
@@ -11188,6 +11353,9 @@
       </c>
       <c r="F176" s="5" t="s">
         <v>128</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>497</v>
       </c>
       <c r="I176" s="5">
         <v>0.39900000000000002</v>
@@ -13907,6 +14075,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="26" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C159" r:id="rId1" xr:uid="{BF63034B-E53E-AA4F-9F22-3EC9CCE474BD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -8,20 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/large_scale_yeast_proteomics_analysis/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6639D6A2-DB14-1A4A-A425-850FBF6C7C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F2BCDA-BAE1-254D-A623-0104609C5D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2360" yWindow="500" windowWidth="37660" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet6" sheetId="9" r:id="rId2"/>
-    <sheet name="Sheet5" sheetId="8" r:id="rId3"/>
-    <sheet name="Supplementary File 1e vip" sheetId="1" r:id="rId4"/>
-    <sheet name="cell cycle_kate" sheetId="5" r:id="rId5"/>
+    <sheet name="Supplementary File 1e vip" sheetId="1" r:id="rId2"/>
+    <sheet name="cell cycle_kate" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AE$158</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Supplementary File 1e vip'!$B$1:$B$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supplementary File 1e vip'!$B$1:$B$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2895" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2870" uniqueCount="511">
   <si>
     <t>sample</t>
   </si>
@@ -2479,7 +2477,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2539,12 +2537,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="42" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3092,9 +3084,9 @@
   <dimension ref="A1:AE301"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="32.33203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" style="5" customWidth="1"/>
     <col min="2" max="2" width="22" style="5" customWidth="1"/>
-    <col min="3" max="3" width="41.5" style="29" customWidth="1"/>
+    <col min="3" max="3" width="41.5" style="27" customWidth="1"/>
     <col min="4" max="4" width="26.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="38.1640625" style="5" customWidth="1"/>
     <col min="6" max="6" width="25.33203125" style="5" customWidth="1"/>
@@ -3126,98 +3118,98 @@
     <col min="32" max="16384" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="30" customFormat="1" ht="19">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:31" s="28" customFormat="1" ht="19">
+      <c r="A1" s="28" t="s">
         <v>483</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="G1" s="81" t="s">
+      <c r="G1" s="79" t="s">
         <v>398</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="L1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="M1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="P1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="Q1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="R1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="S1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="T1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="30" t="s">
+      <c r="U1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="30" t="s">
+      <c r="V1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="30" t="s">
+      <c r="W1" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="X1" s="30" t="s">
+      <c r="X1" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="Y1" s="30" t="s">
+      <c r="Y1" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="Z1" s="30" t="s">
+      <c r="Z1" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="AA1" s="30" t="s">
+      <c r="AA1" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="AB1" s="30" t="s">
+      <c r="AB1" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="AC1" s="30" t="s">
+      <c r="AC1" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="AD1" s="30" t="s">
+      <c r="AD1" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="AE1" s="30" t="s">
+      <c r="AE1" s="28" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3240,16 +3232,16 @@
       <c r="F2" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="58" t="s">
         <v>395</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="W2" s="31">
+      <c r="W2" s="29">
         <v>20</v>
       </c>
-      <c r="X2" s="31" t="s">
+      <c r="X2" s="29" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3272,16 +3264,16 @@
       <c r="F3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G3" s="61" t="s">
+      <c r="G3" s="59" t="s">
         <v>395</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="W3" s="32">
+      <c r="W3" s="30">
         <v>20</v>
       </c>
-      <c r="X3" s="32" t="s">
+      <c r="X3" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3304,16 +3296,16 @@
       <c r="F4" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G4" s="61" t="s">
+      <c r="G4" s="59" t="s">
         <v>395</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="W4" s="32">
+      <c r="W4" s="30">
         <v>20</v>
       </c>
-      <c r="X4" s="32" t="s">
+      <c r="X4" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3334,12 +3326,12 @@
         <v>357</v>
       </c>
       <c r="F5" s="6"/>
-      <c r="G5" s="61" t="s">
+      <c r="G5" s="59" t="s">
         <v>396</v>
       </c>
       <c r="H5" s="12"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="32"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
     </row>
     <row r="6" spans="1:31">
       <c r="A6" s="6" t="s">
@@ -3358,12 +3350,12 @@
         <v>357</v>
       </c>
       <c r="F6" s="6"/>
-      <c r="G6" s="61" t="s">
+      <c r="G6" s="59" t="s">
         <v>396</v>
       </c>
       <c r="H6" s="12"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
     </row>
     <row r="7" spans="1:31">
       <c r="A7" s="6" t="s">
@@ -3382,12 +3374,12 @@
         <v>357</v>
       </c>
       <c r="F7" s="6"/>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="59" t="s">
         <v>396</v>
       </c>
       <c r="H7" s="12"/>
-      <c r="W7" s="32"/>
-      <c r="X7" s="32"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
     </row>
     <row r="8" spans="1:31">
       <c r="A8" s="6" t="s">
@@ -3406,12 +3398,12 @@
         <v>357</v>
       </c>
       <c r="F8" s="6"/>
-      <c r="G8" s="61" t="s">
+      <c r="G8" s="59" t="s">
         <v>397</v>
       </c>
       <c r="H8" s="12"/>
-      <c r="W8" s="32"/>
-      <c r="X8" s="32"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
     </row>
     <row r="9" spans="1:31">
       <c r="A9" s="6" t="s">
@@ -3430,12 +3422,12 @@
         <v>357</v>
       </c>
       <c r="F9" s="6"/>
-      <c r="G9" s="61" t="s">
+      <c r="G9" s="59" t="s">
         <v>397</v>
       </c>
       <c r="H9" s="12"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="32"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
     </row>
     <row r="10" spans="1:31" s="14" customFormat="1">
       <c r="A10" s="11" t="s">
@@ -3454,72 +3446,72 @@
         <v>357</v>
       </c>
       <c r="F10" s="11"/>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="60" t="s">
         <v>397</v>
       </c>
       <c r="H10" s="23"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-    </row>
-    <row r="11" spans="1:31" s="34" customFormat="1">
-      <c r="A11" s="67" t="s">
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+    </row>
+    <row r="11" spans="1:31" s="32" customFormat="1">
+      <c r="A11" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="25" t="s">
         <v>486</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="25" t="s">
         <v>358</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="G11" s="63"/>
-      <c r="H11" s="28" t="s">
+      <c r="G11" s="61"/>
+      <c r="H11" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="32">
         <v>0.42399999999999999</v>
       </c>
-      <c r="J11" s="34">
+      <c r="J11" s="32">
         <v>18.79</v>
       </c>
-      <c r="P11" s="34">
+      <c r="P11" s="32">
         <v>26.97</v>
       </c>
-      <c r="Q11" s="34">
+      <c r="Q11" s="32">
         <v>0.56599999999999995</v>
       </c>
-      <c r="R11" s="34">
+      <c r="R11" s="32">
         <v>0.16300000000000001</v>
       </c>
-      <c r="S11" s="34">
+      <c r="S11" s="32">
         <v>3.6499999999999998E-2</v>
       </c>
-      <c r="T11" s="34">
+      <c r="T11" s="32">
         <v>1.4690000000000001</v>
       </c>
-      <c r="U11" s="34">
+      <c r="U11" s="32">
         <v>24.501999999999999</v>
       </c>
-      <c r="V11" s="34">
+      <c r="V11" s="32">
         <v>2.919</v>
       </c>
-      <c r="W11" s="34">
+      <c r="W11" s="32">
         <v>20</v>
       </c>
-      <c r="X11" s="34" t="s">
+      <c r="X11" s="32" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:31">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="66" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -3537,7 +3529,7 @@
       <c r="F12" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G12" s="61" t="s">
+      <c r="G12" s="59" t="s">
         <v>362</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -3546,37 +3538,37 @@
       <c r="I12" s="5">
         <v>0.05</v>
       </c>
-      <c r="J12" s="35">
+      <c r="J12" s="33">
         <v>0.82299999999999995</v>
       </c>
-      <c r="K12" s="35">
+      <c r="K12" s="33">
         <v>0.13100000000000001</v>
       </c>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35">
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33">
         <v>0.13100000000000001</v>
       </c>
-      <c r="P12" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="35">
-        <v>0</v>
-      </c>
-      <c r="R12" s="35">
+      <c r="P12" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="33">
+        <v>0</v>
+      </c>
+      <c r="R12" s="33">
         <v>7.2308500000000005E-4</v>
       </c>
-      <c r="S12" s="35">
-        <v>0</v>
-      </c>
-      <c r="T12" s="35">
+      <c r="S12" s="33">
+        <v>0</v>
+      </c>
+      <c r="T12" s="33">
         <v>4.0285879999999996E-3</v>
       </c>
-      <c r="U12" s="35">
+      <c r="U12" s="33">
         <v>2.4449999999999998</v>
       </c>
-      <c r="V12" s="35">
+      <c r="V12" s="33">
         <v>2.3620000000000001</v>
       </c>
       <c r="W12" s="5">
@@ -3605,7 +3597,7 @@
       </c>
     </row>
     <row r="13" spans="1:31">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="66" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -3623,7 +3615,7 @@
       <c r="F13" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G13" s="61" t="s">
+      <c r="G13" s="59" t="s">
         <v>362</v>
       </c>
       <c r="H13" s="12" t="s">
@@ -3632,37 +3624,37 @@
       <c r="I13" s="5">
         <v>0.05</v>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="33">
         <v>0.70399999999999996</v>
       </c>
-      <c r="K13" s="35">
+      <c r="K13" s="33">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35">
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="P13" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="35">
-        <v>0</v>
-      </c>
-      <c r="R13" s="35">
+      <c r="P13" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="33">
+        <v>0</v>
+      </c>
+      <c r="R13" s="33">
         <v>1.6583900000000001E-4</v>
       </c>
-      <c r="S13" s="35">
-        <v>0</v>
-      </c>
-      <c r="T13" s="35">
+      <c r="S13" s="33">
+        <v>0</v>
+      </c>
+      <c r="T13" s="33">
         <v>6.6796169999999997E-3</v>
       </c>
-      <c r="U13" s="35">
+      <c r="U13" s="33">
         <v>2.105</v>
       </c>
-      <c r="V13" s="35">
+      <c r="V13" s="33">
         <v>2.2759999999999998</v>
       </c>
       <c r="W13" s="5">
@@ -3691,7 +3683,7 @@
       </c>
     </row>
     <row r="14" spans="1:31">
-      <c r="A14" s="68" t="s">
+      <c r="A14" s="66" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -3709,7 +3701,7 @@
       <c r="F14" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G14" s="61" t="s">
+      <c r="G14" s="59" t="s">
         <v>362</v>
       </c>
       <c r="H14" s="12" t="s">
@@ -3718,37 +3710,37 @@
       <c r="I14" s="5">
         <v>0.05</v>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="33">
         <v>0.76800000000000002</v>
       </c>
-      <c r="K14" s="35">
+      <c r="K14" s="33">
         <v>0.14000000000000001</v>
       </c>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35">
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33">
         <v>0.14000000000000001</v>
       </c>
-      <c r="P14" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="35">
-        <v>0</v>
-      </c>
-      <c r="R14" s="35">
+      <c r="P14" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="33">
+        <v>0</v>
+      </c>
+      <c r="R14" s="33">
         <v>3.81541E-4</v>
       </c>
-      <c r="S14" s="35">
-        <v>0</v>
-      </c>
-      <c r="T14" s="35">
+      <c r="S14" s="33">
+        <v>0</v>
+      </c>
+      <c r="T14" s="33">
         <v>9.7823159999999992E-3</v>
       </c>
-      <c r="U14" s="35">
+      <c r="U14" s="33">
         <v>2.383</v>
       </c>
-      <c r="V14" s="35">
+      <c r="V14" s="33">
         <v>1.6240000000000001</v>
       </c>
       <c r="W14" s="5">
@@ -3777,7 +3769,7 @@
       </c>
     </row>
     <row r="15" spans="1:31">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="66" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -3795,7 +3787,7 @@
       <c r="F15" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G15" s="61" t="s">
+      <c r="G15" s="59" t="s">
         <v>363</v>
       </c>
       <c r="H15" s="12" t="s">
@@ -3804,37 +3796,37 @@
       <c r="I15" s="5">
         <v>0.1</v>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="33">
         <v>1.18</v>
       </c>
-      <c r="K15" s="35">
+      <c r="K15" s="33">
         <v>2.2029999999999998</v>
       </c>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35">
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33">
         <v>2.2029999999999998</v>
       </c>
-      <c r="P15" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="35">
-        <v>0</v>
-      </c>
-      <c r="R15" s="35">
+      <c r="P15" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="33">
+        <v>0</v>
+      </c>
+      <c r="R15" s="33">
         <v>1.2795499999999999E-4</v>
       </c>
-      <c r="S15" s="35">
-        <v>0</v>
-      </c>
-      <c r="T15" s="35">
-        <v>0</v>
-      </c>
-      <c r="U15" s="35">
+      <c r="S15" s="33">
+        <v>0</v>
+      </c>
+      <c r="T15" s="33">
+        <v>0</v>
+      </c>
+      <c r="U15" s="33">
         <v>1.93</v>
       </c>
-      <c r="V15" s="35">
+      <c r="V15" s="33">
         <v>2.44</v>
       </c>
       <c r="W15" s="5">
@@ -3863,7 +3855,7 @@
       </c>
     </row>
     <row r="16" spans="1:31">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="66" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -3881,7 +3873,7 @@
       <c r="F16" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="59" t="s">
         <v>363</v>
       </c>
       <c r="H16" s="12" t="s">
@@ -3890,37 +3882,37 @@
       <c r="I16" s="5">
         <v>0.1</v>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="33">
         <v>1.127</v>
       </c>
-      <c r="K16" s="35">
+      <c r="K16" s="33">
         <v>2.0979999999999999</v>
       </c>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35">
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33">
         <v>2.0979999999999999</v>
       </c>
-      <c r="P16" s="35">
+      <c r="P16" s="33">
         <v>1.6766474999999999E-2</v>
       </c>
-      <c r="Q16" s="35">
-        <v>0</v>
-      </c>
-      <c r="R16" s="35">
+      <c r="Q16" s="33">
+        <v>0</v>
+      </c>
+      <c r="R16" s="33">
         <v>1.5726999999999999E-4</v>
       </c>
-      <c r="S16" s="35">
-        <v>0</v>
-      </c>
-      <c r="T16" s="35">
-        <v>0</v>
-      </c>
-      <c r="U16" s="35">
+      <c r="S16" s="33">
+        <v>0</v>
+      </c>
+      <c r="T16" s="33">
+        <v>0</v>
+      </c>
+      <c r="U16" s="33">
         <v>2.0699999999999998</v>
       </c>
-      <c r="V16" s="35">
+      <c r="V16" s="33">
         <v>2.39</v>
       </c>
       <c r="W16" s="5">
@@ -3949,7 +3941,7 @@
       </c>
     </row>
     <row r="17" spans="1:30">
-      <c r="A17" s="68" t="s">
+      <c r="A17" s="66" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -3967,7 +3959,7 @@
       <c r="F17" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G17" s="61" t="s">
+      <c r="G17" s="59" t="s">
         <v>363</v>
       </c>
       <c r="H17" s="12" t="s">
@@ -3976,37 +3968,37 @@
       <c r="I17" s="5">
         <v>0.1</v>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="33">
         <v>1.0980000000000001</v>
       </c>
-      <c r="K17" s="35">
+      <c r="K17" s="33">
         <v>2.0550000000000002</v>
       </c>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35">
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33">
         <v>2.0550000000000002</v>
       </c>
-      <c r="P17" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="35">
-        <v>0</v>
-      </c>
-      <c r="R17" s="35">
+      <c r="P17" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="33">
+        <v>0</v>
+      </c>
+      <c r="R17" s="33">
         <v>1.3422099999999999E-4</v>
       </c>
-      <c r="S17" s="35">
-        <v>0</v>
-      </c>
-      <c r="T17" s="35">
-        <v>0</v>
-      </c>
-      <c r="U17" s="35">
+      <c r="S17" s="33">
+        <v>0</v>
+      </c>
+      <c r="T17" s="33">
+        <v>0</v>
+      </c>
+      <c r="U17" s="33">
         <v>1.97</v>
       </c>
-      <c r="V17" s="35">
+      <c r="V17" s="33">
         <v>2.1800000000000002</v>
       </c>
       <c r="W17" s="5">
@@ -4035,7 +4027,7 @@
       </c>
     </row>
     <row r="18" spans="1:30">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="66" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -4053,7 +4045,7 @@
       <c r="F18" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G18" s="61" t="s">
+      <c r="G18" s="59" t="s">
         <v>364</v>
       </c>
       <c r="H18" s="12" t="s">
@@ -4062,37 +4054,37 @@
       <c r="I18" s="5">
         <v>0.1</v>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="33">
         <v>1.51</v>
       </c>
-      <c r="K18" s="35">
+      <c r="K18" s="33">
         <v>0.308</v>
       </c>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35">
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33">
         <v>0.308</v>
       </c>
-      <c r="P18" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="35">
+      <c r="P18" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="33">
         <v>7.5614127000000003E-2</v>
       </c>
-      <c r="R18" s="35">
+      <c r="R18" s="33">
         <v>1.7982350000000001E-2</v>
       </c>
-      <c r="S18" s="35">
-        <v>0</v>
-      </c>
-      <c r="T18" s="35">
-        <v>0</v>
-      </c>
-      <c r="U18" s="35">
+      <c r="S18" s="33">
+        <v>0</v>
+      </c>
+      <c r="T18" s="33">
+        <v>0</v>
+      </c>
+      <c r="U18" s="33">
         <v>3.4660000000000002</v>
       </c>
-      <c r="V18" s="35">
+      <c r="V18" s="33">
         <v>3.6160000000000001</v>
       </c>
       <c r="W18" s="5">
@@ -4121,7 +4113,7 @@
       </c>
     </row>
     <row r="19" spans="1:30">
-      <c r="A19" s="68" t="s">
+      <c r="A19" s="66" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -4139,7 +4131,7 @@
       <c r="F19" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G19" s="61" t="s">
+      <c r="G19" s="59" t="s">
         <v>364</v>
       </c>
       <c r="H19" s="12" t="s">
@@ -4148,37 +4140,37 @@
       <c r="I19" s="5">
         <v>0.1</v>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="33">
         <v>1.5109999999999999</v>
       </c>
-      <c r="K19" s="35">
+      <c r="K19" s="33">
         <v>0.308</v>
       </c>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35">
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33">
         <v>0.308</v>
       </c>
-      <c r="P19" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="35">
+      <c r="P19" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="33">
         <v>4.9087042999999997E-2</v>
       </c>
-      <c r="R19" s="35">
+      <c r="R19" s="33">
         <v>1.38432E-2</v>
       </c>
-      <c r="S19" s="35">
-        <v>0</v>
-      </c>
-      <c r="T19" s="35">
-        <v>0</v>
-      </c>
-      <c r="U19" s="35">
+      <c r="S19" s="33">
+        <v>0</v>
+      </c>
+      <c r="T19" s="33">
+        <v>0</v>
+      </c>
+      <c r="U19" s="33">
         <v>3.1360000000000001</v>
       </c>
-      <c r="V19" s="35">
+      <c r="V19" s="33">
         <v>3.5219999999999998</v>
       </c>
       <c r="W19" s="5">
@@ -4207,7 +4199,7 @@
       </c>
     </row>
     <row r="20" spans="1:30">
-      <c r="A20" s="68" t="s">
+      <c r="A20" s="66" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -4225,7 +4217,7 @@
       <c r="F20" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G20" s="61" t="s">
+      <c r="G20" s="59" t="s">
         <v>364</v>
       </c>
       <c r="H20" s="12" t="s">
@@ -4234,37 +4226,37 @@
       <c r="I20" s="5">
         <v>0.1</v>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="33">
         <v>1.4890000000000001</v>
       </c>
-      <c r="K20" s="35">
+      <c r="K20" s="33">
         <v>0.30399999999999999</v>
       </c>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35">
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33">
         <v>0.30399999999999999</v>
       </c>
-      <c r="P20" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="35">
+      <c r="P20" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="33">
         <v>6.6037847999999996E-2</v>
       </c>
-      <c r="R20" s="35">
+      <c r="R20" s="33">
         <v>1.602926E-2</v>
       </c>
-      <c r="S20" s="35">
-        <v>0</v>
-      </c>
-      <c r="T20" s="35">
-        <v>0</v>
-      </c>
-      <c r="U20" s="35">
+      <c r="S20" s="33">
+        <v>0</v>
+      </c>
+      <c r="T20" s="33">
+        <v>0</v>
+      </c>
+      <c r="U20" s="33">
         <v>3.161</v>
       </c>
-      <c r="V20" s="35">
+      <c r="V20" s="33">
         <v>3.8239999999999998</v>
       </c>
       <c r="W20" s="5">
@@ -4293,7 +4285,7 @@
       </c>
     </row>
     <row r="21" spans="1:30">
-      <c r="A21" s="68" t="s">
+      <c r="A21" s="66" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -4311,7 +4303,7 @@
       <c r="F21" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G21" s="61" t="s">
+      <c r="G21" s="59" t="s">
         <v>365</v>
       </c>
       <c r="H21" s="12" t="s">
@@ -4320,37 +4312,37 @@
       <c r="I21" s="5">
         <v>0.13</v>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="33">
         <v>2.0190000000000001</v>
       </c>
-      <c r="K21" s="35">
+      <c r="K21" s="33">
         <v>0.41499999999999998</v>
       </c>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35">
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33">
         <v>0.41499999999999998</v>
       </c>
-      <c r="P21" s="35">
+      <c r="P21" s="33">
         <v>0.14387805000000001</v>
       </c>
-      <c r="Q21" s="35">
+      <c r="Q21" s="33">
         <v>0.23128044</v>
       </c>
-      <c r="R21" s="35">
+      <c r="R21" s="33">
         <v>2.4418572999999999E-2</v>
       </c>
-      <c r="S21" s="35">
+      <c r="S21" s="33">
         <v>7.3894399999999995E-4</v>
       </c>
-      <c r="T21" s="35">
+      <c r="T21" s="33">
         <v>4.2122905000000002E-2</v>
       </c>
-      <c r="U21" s="35">
+      <c r="U21" s="33">
         <v>5.51</v>
       </c>
-      <c r="V21" s="35">
+      <c r="V21" s="33">
         <v>5.2519999999999998</v>
       </c>
       <c r="W21" s="5">
@@ -4379,7 +4371,7 @@
       </c>
     </row>
     <row r="22" spans="1:30">
-      <c r="A22" s="68" t="s">
+      <c r="A22" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -4397,7 +4389,7 @@
       <c r="F22" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G22" s="61" t="s">
+      <c r="G22" s="59" t="s">
         <v>365</v>
       </c>
       <c r="H22" s="12" t="s">
@@ -4406,37 +4398,37 @@
       <c r="I22" s="5">
         <v>0.13</v>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="33">
         <v>2.0590000000000002</v>
       </c>
-      <c r="K22" s="35">
+      <c r="K22" s="33">
         <v>0.42499999999999999</v>
       </c>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35">
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33">
         <v>0.42499999999999999</v>
       </c>
-      <c r="P22" s="35">
+      <c r="P22" s="33">
         <v>0.13916811300000001</v>
       </c>
-      <c r="Q22" s="35">
+      <c r="Q22" s="33">
         <v>0.22761730999999999</v>
       </c>
-      <c r="R22" s="35">
+      <c r="R22" s="33">
         <v>2.5077986E-2</v>
       </c>
-      <c r="S22" s="35">
+      <c r="S22" s="33">
         <v>2.152588E-3</v>
       </c>
-      <c r="T22" s="35">
+      <c r="T22" s="33">
         <v>3.3899711999999999E-2</v>
       </c>
-      <c r="U22" s="35">
+      <c r="U22" s="33">
         <v>5.3739999999999997</v>
       </c>
-      <c r="V22" s="35">
+      <c r="V22" s="33">
         <v>4.5460000000000003</v>
       </c>
       <c r="W22" s="5">
@@ -4465,7 +4457,7 @@
       </c>
     </row>
     <row r="23" spans="1:30">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="66" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -4483,7 +4475,7 @@
       <c r="F23" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G23" s="61" t="s">
+      <c r="G23" s="59" t="s">
         <v>365</v>
       </c>
       <c r="H23" s="12" t="s">
@@ -4492,37 +4484,37 @@
       <c r="I23" s="5">
         <v>0.13</v>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="33">
         <v>2.1349999999999998</v>
       </c>
-      <c r="K23" s="35">
+      <c r="K23" s="33">
         <v>0.438</v>
       </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35">
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33">
         <v>0.438</v>
       </c>
-      <c r="P23" s="35">
+      <c r="P23" s="33">
         <v>0.13267562499999999</v>
       </c>
-      <c r="Q23" s="35">
+      <c r="Q23" s="33">
         <v>0.25727792100000002</v>
       </c>
-      <c r="R23" s="35">
+      <c r="R23" s="33">
         <v>2.6121129999999999E-2</v>
       </c>
-      <c r="S23" s="35">
-        <v>0</v>
-      </c>
-      <c r="T23" s="35">
+      <c r="S23" s="33">
+        <v>0</v>
+      </c>
+      <c r="T23" s="33">
         <v>4.1071206999999998E-2</v>
       </c>
-      <c r="U23" s="35">
+      <c r="U23" s="33">
         <v>5.3019999999999996</v>
       </c>
-      <c r="V23" s="35">
+      <c r="V23" s="33">
         <v>5.07</v>
       </c>
       <c r="W23" s="5">
@@ -4551,7 +4543,7 @@
       </c>
     </row>
     <row r="24" spans="1:30">
-      <c r="A24" s="68" t="s">
+      <c r="A24" s="66" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -4569,7 +4561,7 @@
       <c r="F24" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G24" s="61" t="s">
+      <c r="G24" s="59" t="s">
         <v>366</v>
       </c>
       <c r="H24" s="12" t="s">
@@ -4578,37 +4570,37 @@
       <c r="I24" s="5">
         <v>0.18</v>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="33">
         <v>3.266</v>
       </c>
-      <c r="K24" s="35">
+      <c r="K24" s="33">
         <v>0.66900000000000004</v>
       </c>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35">
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33">
         <v>0.66900000000000004</v>
       </c>
-      <c r="P24" s="35">
+      <c r="P24" s="33">
         <v>1.2813869950000001</v>
       </c>
-      <c r="Q24" s="35">
+      <c r="Q24" s="33">
         <v>0.18048138799999999</v>
       </c>
-      <c r="R24" s="35">
+      <c r="R24" s="33">
         <v>3.2745818000000003E-2</v>
       </c>
-      <c r="S24" s="35">
-        <v>0</v>
-      </c>
-      <c r="T24" s="35">
+      <c r="S24" s="33">
+        <v>0</v>
+      </c>
+      <c r="T24" s="33">
         <v>5.6452840000000004E-3</v>
       </c>
-      <c r="U24" s="35">
+      <c r="U24" s="33">
         <v>7.2619999999999996</v>
       </c>
-      <c r="V24" s="35">
+      <c r="V24" s="33">
         <v>5.42</v>
       </c>
       <c r="W24" s="5">
@@ -4637,7 +4629,7 @@
       </c>
     </row>
     <row r="25" spans="1:30">
-      <c r="A25" s="68" t="s">
+      <c r="A25" s="66" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -4655,7 +4647,7 @@
       <c r="F25" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G25" s="61" t="s">
+      <c r="G25" s="59" t="s">
         <v>366</v>
       </c>
       <c r="H25" s="12" t="s">
@@ -4664,37 +4656,37 @@
       <c r="I25" s="5">
         <v>0.18</v>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="33">
         <v>3.202</v>
       </c>
-      <c r="K25" s="35">
+      <c r="K25" s="33">
         <v>0.65900000000000003</v>
       </c>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35">
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33">
         <v>0.65900000000000003</v>
       </c>
-      <c r="P25" s="35">
+      <c r="P25" s="33">
         <v>1.4870797280000001</v>
       </c>
-      <c r="Q25" s="35">
+      <c r="Q25" s="33">
         <v>0.41515672300000001</v>
       </c>
-      <c r="R25" s="35">
+      <c r="R25" s="33">
         <v>3.1272250000000001E-2</v>
       </c>
-      <c r="S25" s="35">
+      <c r="S25" s="33">
         <v>2.6969479999999998E-3</v>
       </c>
-      <c r="T25" s="35">
+      <c r="T25" s="33">
         <v>1.6418242E-2</v>
       </c>
-      <c r="U25" s="35">
+      <c r="U25" s="33">
         <v>7.3049999999999997</v>
       </c>
-      <c r="V25" s="35">
+      <c r="V25" s="33">
         <v>6.0170000000000003</v>
       </c>
       <c r="W25" s="5">
@@ -4723,7 +4715,7 @@
       </c>
     </row>
     <row r="26" spans="1:30">
-      <c r="A26" s="68" t="s">
+      <c r="A26" s="66" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -4741,7 +4733,7 @@
       <c r="F26" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G26" s="61" t="s">
+      <c r="G26" s="59" t="s">
         <v>366</v>
       </c>
       <c r="H26" s="12" t="s">
@@ -4750,37 +4742,37 @@
       <c r="I26" s="5">
         <v>0.18</v>
       </c>
-      <c r="J26" s="35">
+      <c r="J26" s="33">
         <v>2.83</v>
       </c>
-      <c r="K26" s="35">
+      <c r="K26" s="33">
         <v>0.58099999999999996</v>
       </c>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35">
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33">
         <v>0.58099999999999996</v>
       </c>
-      <c r="P26" s="35">
+      <c r="P26" s="33">
         <v>1.069367508</v>
       </c>
-      <c r="Q26" s="35">
+      <c r="Q26" s="33">
         <v>0.18424942899999999</v>
       </c>
-      <c r="R26" s="35">
+      <c r="R26" s="33">
         <v>2.652065E-2</v>
       </c>
-      <c r="S26" s="35">
-        <v>0</v>
-      </c>
-      <c r="T26" s="35">
+      <c r="S26" s="33">
+        <v>0</v>
+      </c>
+      <c r="T26" s="33">
         <v>1.5674206999999999E-2</v>
       </c>
-      <c r="U26" s="35">
+      <c r="U26" s="33">
         <v>6.2510000000000003</v>
       </c>
-      <c r="V26" s="35">
+      <c r="V26" s="33">
         <v>5.2640000000000002</v>
       </c>
       <c r="W26" s="5">
@@ -4809,7 +4801,7 @@
       </c>
     </row>
     <row r="27" spans="1:30">
-      <c r="A27" s="68" t="s">
+      <c r="A27" s="66" t="s">
         <v>30</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -4827,7 +4819,7 @@
       <c r="F27" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G27" s="61" t="s">
+      <c r="G27" s="59" t="s">
         <v>367</v>
       </c>
       <c r="H27" s="12" t="s">
@@ -4836,37 +4828,37 @@
       <c r="I27" s="5">
         <v>0.3</v>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="33">
         <v>7.9909999999999997</v>
       </c>
-      <c r="K27" s="35">
+      <c r="K27" s="33">
         <v>1.6479999999999999</v>
       </c>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35">
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33">
         <v>1.6479999999999999</v>
       </c>
-      <c r="P27" s="35">
+      <c r="P27" s="33">
         <v>7.0441347099999998</v>
       </c>
-      <c r="Q27" s="35">
+      <c r="Q27" s="33">
         <v>0.31251037799999998</v>
       </c>
-      <c r="R27" s="35">
+      <c r="R27" s="33">
         <v>5.1692219999999997E-2</v>
       </c>
-      <c r="S27" s="35">
+      <c r="S27" s="33">
         <v>1.1339925000000001E-2</v>
       </c>
-      <c r="T27" s="35">
-        <v>0</v>
-      </c>
-      <c r="U27" s="35">
+      <c r="T27" s="33">
+        <v>0</v>
+      </c>
+      <c r="U27" s="33">
         <v>14.086</v>
       </c>
-      <c r="V27" s="35">
+      <c r="V27" s="33">
         <v>8.3010000000000002</v>
       </c>
       <c r="W27" s="5">
@@ -4895,7 +4887,7 @@
       </c>
     </row>
     <row r="28" spans="1:30">
-      <c r="A28" s="68" t="s">
+      <c r="A28" s="66" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -4913,7 +4905,7 @@
       <c r="F28" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G28" s="61" t="s">
+      <c r="G28" s="59" t="s">
         <v>367</v>
       </c>
       <c r="H28" s="12" t="s">
@@ -4922,37 +4914,37 @@
       <c r="I28" s="5">
         <v>0.3</v>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="33">
         <v>8.2759999999999998</v>
       </c>
-      <c r="K28" s="35">
+      <c r="K28" s="33">
         <v>1.6950000000000001</v>
       </c>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35">
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33">
         <v>1.6950000000000001</v>
       </c>
-      <c r="P28" s="35">
+      <c r="P28" s="33">
         <v>6.6847254490000001</v>
       </c>
-      <c r="Q28" s="35">
+      <c r="Q28" s="33">
         <v>0.27229536399999998</v>
       </c>
-      <c r="R28" s="35">
+      <c r="R28" s="33">
         <v>4.4478275999999997E-2</v>
       </c>
-      <c r="S28" s="35">
+      <c r="S28" s="33">
         <v>3.4668667E-2</v>
       </c>
-      <c r="T28" s="35">
-        <v>0</v>
-      </c>
-      <c r="U28" s="35">
+      <c r="T28" s="33">
+        <v>0</v>
+      </c>
+      <c r="U28" s="33">
         <v>15.111000000000001</v>
       </c>
-      <c r="V28" s="35">
+      <c r="V28" s="33">
         <v>8.3870000000000005</v>
       </c>
       <c r="W28" s="5">
@@ -4981,7 +4973,7 @@
       </c>
     </row>
     <row r="29" spans="1:30">
-      <c r="A29" s="68" t="s">
+      <c r="A29" s="66" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -4999,7 +4991,7 @@
       <c r="F29" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G29" s="61" t="s">
+      <c r="G29" s="59" t="s">
         <v>367</v>
       </c>
       <c r="H29" s="12" t="s">
@@ -5008,37 +5000,37 @@
       <c r="I29" s="5">
         <v>0.3</v>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="33">
         <v>8.9320000000000004</v>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="33">
         <v>1.8660000000000001</v>
       </c>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35">
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33">
         <v>1.8660000000000001</v>
       </c>
-      <c r="P29" s="35">
+      <c r="P29" s="33">
         <v>8.2124218889999998</v>
       </c>
-      <c r="Q29" s="35">
+      <c r="Q29" s="33">
         <v>0.61718923199999998</v>
       </c>
-      <c r="R29" s="35">
+      <c r="R29" s="33">
         <v>6.4337543999999997E-2</v>
       </c>
-      <c r="S29" s="35">
+      <c r="S29" s="33">
         <v>2.9481279999999999E-2</v>
       </c>
-      <c r="T29" s="35">
-        <v>0</v>
-      </c>
-      <c r="U29" s="35">
+      <c r="T29" s="33">
+        <v>0</v>
+      </c>
+      <c r="U29" s="33">
         <v>16.956</v>
       </c>
-      <c r="V29" s="35">
+      <c r="V29" s="33">
         <v>9.34</v>
       </c>
       <c r="W29" s="5">
@@ -5067,7 +5059,7 @@
       </c>
     </row>
     <row r="30" spans="1:30">
-      <c r="A30" s="68" t="s">
+      <c r="A30" s="66" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -5085,7 +5077,7 @@
       <c r="F30" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="59" t="s">
         <v>368</v>
       </c>
       <c r="H30" s="12" t="s">
@@ -5094,37 +5086,37 @@
       <c r="I30" s="5">
         <v>0.35</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="33">
         <v>12.936999999999999</v>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="33">
         <v>2.7120000000000002</v>
       </c>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35">
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33">
         <v>2.7120000000000002</v>
       </c>
-      <c r="P30" s="35">
+      <c r="P30" s="33">
         <v>11.927306959999999</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="33">
         <v>0.47269426599999997</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="33">
         <v>8.9757966999999994E-2</v>
       </c>
-      <c r="S30" s="35">
+      <c r="S30" s="33">
         <v>3.5944587E-2</v>
       </c>
-      <c r="T30" s="35">
-        <v>0</v>
-      </c>
-      <c r="U30" s="35">
+      <c r="T30" s="33">
+        <v>0</v>
+      </c>
+      <c r="U30" s="33">
         <v>20.902000000000001</v>
       </c>
-      <c r="V30" s="35">
+      <c r="V30" s="33">
         <v>12.682</v>
       </c>
       <c r="W30" s="5">
@@ -5153,7 +5145,7 @@
       </c>
     </row>
     <row r="31" spans="1:30">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="66" t="s">
         <v>34</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -5171,7 +5163,7 @@
       <c r="F31" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G31" s="61" t="s">
+      <c r="G31" s="59" t="s">
         <v>368</v>
       </c>
       <c r="H31" s="12" t="s">
@@ -5180,37 +5172,37 @@
       <c r="I31" s="5">
         <v>0.35</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="33">
         <v>13.23</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="33">
         <v>2.786</v>
       </c>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35">
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33">
         <v>2.786</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="33">
         <v>12.12470377</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="33">
         <v>0.63692599999999999</v>
       </c>
-      <c r="R31" s="35">
+      <c r="R31" s="33">
         <v>0.104193063</v>
       </c>
-      <c r="S31" s="35">
+      <c r="S31" s="33">
         <v>3.3770889999999998E-2</v>
       </c>
-      <c r="T31" s="35">
-        <v>0</v>
-      </c>
-      <c r="U31" s="35">
+      <c r="T31" s="33">
+        <v>0</v>
+      </c>
+      <c r="U31" s="33">
         <v>21.082999999999998</v>
       </c>
-      <c r="V31" s="35">
+      <c r="V31" s="33">
         <v>12.353999999999999</v>
       </c>
       <c r="W31" s="5">
@@ -5239,7 +5231,7 @@
       </c>
     </row>
     <row r="32" spans="1:30">
-      <c r="A32" s="68" t="s">
+      <c r="A32" s="66" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -5257,7 +5249,7 @@
       <c r="F32" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G32" s="61" t="s">
+      <c r="G32" s="59" t="s">
         <v>368</v>
       </c>
       <c r="H32" s="12" t="s">
@@ -5266,37 +5258,37 @@
       <c r="I32" s="5">
         <v>0.35</v>
       </c>
-      <c r="J32" s="35">
+      <c r="J32" s="33">
         <v>13.096</v>
       </c>
-      <c r="K32" s="35">
+      <c r="K32" s="33">
         <v>2.742</v>
       </c>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35">
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33">
         <v>2.742</v>
       </c>
-      <c r="P32" s="35">
+      <c r="P32" s="33">
         <v>11.84780602</v>
       </c>
-      <c r="Q32" s="35">
+      <c r="Q32" s="33">
         <v>0.47734259699999998</v>
       </c>
-      <c r="R32" s="35">
+      <c r="R32" s="33">
         <v>9.1823417000000004E-2</v>
       </c>
-      <c r="S32" s="35">
-        <v>0</v>
-      </c>
-      <c r="T32" s="35">
-        <v>0</v>
-      </c>
-      <c r="U32" s="35">
+      <c r="S32" s="33">
+        <v>0</v>
+      </c>
+      <c r="T32" s="33">
+        <v>0</v>
+      </c>
+      <c r="U32" s="33">
         <v>21.097999999999999</v>
       </c>
-      <c r="V32" s="35">
+      <c r="V32" s="33">
         <v>12.977</v>
       </c>
       <c r="W32" s="5">
@@ -5325,7 +5317,7 @@
       </c>
     </row>
     <row r="33" spans="1:31">
-      <c r="A33" s="68" t="s">
+      <c r="A33" s="66" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -5343,7 +5335,7 @@
       <c r="F33" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G33" s="61" t="s">
+      <c r="G33" s="59" t="s">
         <v>369</v>
       </c>
       <c r="H33" s="12" t="s">
@@ -5352,37 +5344,37 @@
       <c r="I33" s="5">
         <v>0.1</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="33">
         <v>0.82699999999999996</v>
       </c>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35">
+      <c r="K33" s="33"/>
+      <c r="L33" s="33">
         <v>0.747</v>
       </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35">
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33">
         <v>1.4930000000000001</v>
       </c>
-      <c r="P33" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="35">
-        <v>0</v>
-      </c>
-      <c r="R33" s="35">
+      <c r="P33" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="33">
+        <v>0</v>
+      </c>
+      <c r="R33" s="33">
         <v>8.7561730000000008E-3</v>
       </c>
-      <c r="S33" s="35">
-        <v>0</v>
-      </c>
-      <c r="T33" s="35">
-        <v>0</v>
-      </c>
-      <c r="U33" s="35">
+      <c r="S33" s="33">
+        <v>0</v>
+      </c>
+      <c r="T33" s="33">
+        <v>0</v>
+      </c>
+      <c r="U33" s="33">
         <v>2.7690000000000001</v>
       </c>
-      <c r="V33" s="35">
+      <c r="V33" s="33">
         <v>2.4500000000000002</v>
       </c>
       <c r="W33" s="5">
@@ -5414,7 +5406,7 @@
       </c>
     </row>
     <row r="34" spans="1:31">
-      <c r="A34" s="68" t="s">
+      <c r="A34" s="66" t="s">
         <v>37</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -5432,7 +5424,7 @@
       <c r="F34" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G34" s="61" t="s">
+      <c r="G34" s="59" t="s">
         <v>369</v>
       </c>
       <c r="H34" s="12" t="s">
@@ -5441,37 +5433,37 @@
       <c r="I34" s="5">
         <v>0.1</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="33">
         <v>0.78800000000000003</v>
       </c>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35">
+      <c r="K34" s="33"/>
+      <c r="L34" s="33">
         <v>0.71199999999999997</v>
       </c>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35"/>
-      <c r="O34" s="35">
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33">
         <v>1.423</v>
       </c>
-      <c r="P34" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="35">
-        <v>0</v>
-      </c>
-      <c r="R34" s="35">
+      <c r="P34" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="33">
+        <v>0</v>
+      </c>
+      <c r="R34" s="33">
         <v>5.5182690000000001E-3</v>
       </c>
-      <c r="S34" s="35">
-        <v>0</v>
-      </c>
-      <c r="T34" s="35">
-        <v>0</v>
-      </c>
-      <c r="U34" s="35">
+      <c r="S34" s="33">
+        <v>0</v>
+      </c>
+      <c r="T34" s="33">
+        <v>0</v>
+      </c>
+      <c r="U34" s="33">
         <v>2.7170000000000001</v>
       </c>
-      <c r="V34" s="35">
+      <c r="V34" s="33">
         <v>2.3530000000000002</v>
       </c>
       <c r="W34" s="5">
@@ -5503,7 +5495,7 @@
       </c>
     </row>
     <row r="35" spans="1:31">
-      <c r="A35" s="68" t="s">
+      <c r="A35" s="66" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -5521,7 +5513,7 @@
       <c r="F35" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G35" s="61" t="s">
+      <c r="G35" s="59" t="s">
         <v>369</v>
       </c>
       <c r="H35" s="12" t="s">
@@ -5530,37 +5522,37 @@
       <c r="I35" s="5">
         <v>0.1</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="33">
         <v>0.76700000000000002</v>
       </c>
-      <c r="K35" s="35"/>
-      <c r="L35" s="35">
+      <c r="K35" s="33"/>
+      <c r="L35" s="33">
         <v>0.69099999999999995</v>
       </c>
-      <c r="M35" s="35"/>
-      <c r="N35" s="35"/>
-      <c r="O35" s="35">
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33">
         <v>1.3819999999999999</v>
       </c>
-      <c r="P35" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="35">
-        <v>0</v>
-      </c>
-      <c r="R35" s="35">
+      <c r="P35" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="33">
+        <v>0</v>
+      </c>
+      <c r="R35" s="33">
         <v>1.9902549999999998E-3</v>
       </c>
-      <c r="S35" s="35">
-        <v>0</v>
-      </c>
-      <c r="T35" s="35">
-        <v>0</v>
-      </c>
-      <c r="U35" s="35">
+      <c r="S35" s="33">
+        <v>0</v>
+      </c>
+      <c r="T35" s="33">
+        <v>0</v>
+      </c>
+      <c r="U35" s="33">
         <v>2.5739999999999998</v>
       </c>
-      <c r="V35" s="35">
+      <c r="V35" s="33">
         <v>2.25</v>
       </c>
       <c r="W35" s="5">
@@ -5592,7 +5584,7 @@
       </c>
     </row>
     <row r="36" spans="1:31">
-      <c r="A36" s="68" t="s">
+      <c r="A36" s="66" t="s">
         <v>39</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -5610,7 +5602,7 @@
       <c r="F36" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G36" s="61" t="s">
+      <c r="G36" s="59" t="s">
         <v>370</v>
       </c>
       <c r="H36" s="12" t="s">
@@ -5619,37 +5611,37 @@
       <c r="I36" s="5">
         <v>0.1</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="33">
         <v>0.80700000000000005</v>
       </c>
-      <c r="K36" s="35"/>
-      <c r="L36" s="35">
+      <c r="K36" s="33"/>
+      <c r="L36" s="33">
         <v>4.92</v>
       </c>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35">
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33">
         <v>9.8390000000000004</v>
       </c>
-      <c r="P36" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="35">
-        <v>0</v>
-      </c>
-      <c r="R36" s="35">
+      <c r="P36" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="33">
+        <v>0</v>
+      </c>
+      <c r="R36" s="33">
         <v>3.9436786000000001E-2</v>
       </c>
-      <c r="S36" s="35">
-        <v>0</v>
-      </c>
-      <c r="T36" s="35">
+      <c r="S36" s="33">
+        <v>0</v>
+      </c>
+      <c r="T36" s="33">
         <v>1.3630471999999999E-2</v>
       </c>
-      <c r="U36" s="35">
+      <c r="U36" s="33">
         <v>3.032</v>
       </c>
-      <c r="V36" s="35">
+      <c r="V36" s="33">
         <v>1.7749999999999999</v>
       </c>
       <c r="W36" s="5">
@@ -5681,7 +5673,7 @@
       </c>
     </row>
     <row r="37" spans="1:31">
-      <c r="A37" s="68" t="s">
+      <c r="A37" s="66" t="s">
         <v>40</v>
       </c>
       <c r="B37" s="6" t="s">
@@ -5699,7 +5691,7 @@
       <c r="F37" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G37" s="61" t="s">
+      <c r="G37" s="59" t="s">
         <v>370</v>
       </c>
       <c r="H37" s="12" t="s">
@@ -5708,37 +5700,37 @@
       <c r="I37" s="5">
         <v>0.1</v>
       </c>
-      <c r="J37" s="35">
+      <c r="J37" s="33">
         <v>0.64900000000000002</v>
       </c>
-      <c r="K37" s="35"/>
-      <c r="L37" s="35">
+      <c r="K37" s="33"/>
+      <c r="L37" s="33">
         <v>3.9620000000000002</v>
       </c>
-      <c r="M37" s="35"/>
-      <c r="N37" s="35"/>
-      <c r="O37" s="35">
+      <c r="M37" s="33"/>
+      <c r="N37" s="33"/>
+      <c r="O37" s="33">
         <v>7.9240000000000004</v>
       </c>
-      <c r="P37" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="35">
-        <v>0</v>
-      </c>
-      <c r="R37" s="35">
+      <c r="P37" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="33">
+        <v>0</v>
+      </c>
+      <c r="R37" s="33">
         <v>3.0460814999999999E-2</v>
       </c>
-      <c r="S37" s="35">
-        <v>0</v>
-      </c>
-      <c r="T37" s="35">
+      <c r="S37" s="33">
+        <v>0</v>
+      </c>
+      <c r="T37" s="33">
         <v>9.5061450000000006E-3</v>
       </c>
-      <c r="U37" s="35">
+      <c r="U37" s="33">
         <v>1.9590000000000001</v>
       </c>
-      <c r="V37" s="35">
+      <c r="V37" s="33">
         <v>1.623</v>
       </c>
       <c r="W37" s="5">
@@ -5770,7 +5762,7 @@
       </c>
     </row>
     <row r="38" spans="1:31">
-      <c r="A38" s="68" t="s">
+      <c r="A38" s="66" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -5788,7 +5780,7 @@
       <c r="F38" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G38" s="61" t="s">
+      <c r="G38" s="59" t="s">
         <v>370</v>
       </c>
       <c r="H38" s="12" t="s">
@@ -5797,37 +5789,37 @@
       <c r="I38" s="5">
         <v>0.1</v>
       </c>
-      <c r="J38" s="35">
+      <c r="J38" s="33">
         <v>0.76500000000000001</v>
       </c>
-      <c r="K38" s="35"/>
-      <c r="L38" s="35">
+      <c r="K38" s="33"/>
+      <c r="L38" s="33">
         <v>4.6159999999999997</v>
       </c>
-      <c r="M38" s="35"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="35">
+      <c r="M38" s="33"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33">
         <v>9.2319999999999993</v>
       </c>
-      <c r="P38" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="35">
-        <v>0</v>
-      </c>
-      <c r="R38" s="35">
+      <c r="P38" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="33">
+        <v>0</v>
+      </c>
+      <c r="R38" s="33">
         <v>2.5119712999999998E-2</v>
       </c>
-      <c r="S38" s="35">
-        <v>0</v>
-      </c>
-      <c r="T38" s="35">
-        <v>0</v>
-      </c>
-      <c r="U38" s="35">
+      <c r="S38" s="33">
+        <v>0</v>
+      </c>
+      <c r="T38" s="33">
+        <v>0</v>
+      </c>
+      <c r="U38" s="33">
         <v>2.569</v>
       </c>
-      <c r="V38" s="35">
+      <c r="V38" s="33">
         <v>1.2909999999999999</v>
       </c>
       <c r="W38" s="5">
@@ -5859,7 +5851,7 @@
       </c>
     </row>
     <row r="39" spans="1:31">
-      <c r="A39" s="68" t="s">
+      <c r="A39" s="66" t="s">
         <v>42</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -5877,7 +5869,7 @@
       <c r="F39" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G39" s="61" t="s">
+      <c r="G39" s="59" t="s">
         <v>371</v>
       </c>
       <c r="H39" s="12" t="s">
@@ -5886,37 +5878,37 @@
       <c r="I39" s="5">
         <v>0.1</v>
       </c>
-      <c r="J39" s="35">
+      <c r="J39" s="33">
         <v>1.381</v>
       </c>
-      <c r="K39" s="35"/>
-      <c r="L39" s="35">
+      <c r="K39" s="33"/>
+      <c r="L39" s="33">
         <v>0.158</v>
       </c>
-      <c r="M39" s="35"/>
-      <c r="N39" s="35"/>
-      <c r="O39" s="35">
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="33">
         <v>0.317</v>
       </c>
-      <c r="P39" s="35">
+      <c r="P39" s="33">
         <v>1.8073279000000001E-2</v>
       </c>
-      <c r="Q39" s="35">
+      <c r="Q39" s="33">
         <v>7.8381013999999999E-2</v>
       </c>
-      <c r="R39" s="35">
+      <c r="R39" s="33">
         <v>0.86713414300000002</v>
       </c>
-      <c r="S39" s="35">
+      <c r="S39" s="33">
         <v>5.4564440000000004E-3</v>
       </c>
-      <c r="T39" s="35">
+      <c r="T39" s="33">
         <v>4.6616212999999997E-2</v>
       </c>
-      <c r="U39" s="35">
+      <c r="U39" s="33">
         <v>4.3209999999999997</v>
       </c>
-      <c r="V39" s="35">
+      <c r="V39" s="33">
         <v>3.883</v>
       </c>
       <c r="W39" s="5">
@@ -5945,7 +5937,7 @@
       </c>
     </row>
     <row r="40" spans="1:31">
-      <c r="A40" s="68" t="s">
+      <c r="A40" s="66" t="s">
         <v>43</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -5963,7 +5955,7 @@
       <c r="F40" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G40" s="61" t="s">
+      <c r="G40" s="59" t="s">
         <v>371</v>
       </c>
       <c r="H40" s="12" t="s">
@@ -5972,37 +5964,37 @@
       <c r="I40" s="5">
         <v>0.1</v>
       </c>
-      <c r="J40" s="35">
+      <c r="J40" s="33">
         <v>1.2589999999999999</v>
       </c>
-      <c r="K40" s="35"/>
-      <c r="L40" s="35">
+      <c r="K40" s="33"/>
+      <c r="L40" s="33">
         <v>0.14199999999999999</v>
       </c>
-      <c r="M40" s="35"/>
-      <c r="N40" s="35"/>
-      <c r="O40" s="35">
+      <c r="M40" s="33"/>
+      <c r="N40" s="33"/>
+      <c r="O40" s="33">
         <v>0.28399999999999997</v>
       </c>
-      <c r="P40" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="35">
+      <c r="P40" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="33">
         <v>3.4333113999999998E-2</v>
       </c>
-      <c r="R40" s="35">
+      <c r="R40" s="33">
         <v>0.69158415699999998</v>
       </c>
-      <c r="S40" s="35">
-        <v>0</v>
-      </c>
-      <c r="T40" s="35">
+      <c r="S40" s="33">
+        <v>0</v>
+      </c>
+      <c r="T40" s="33">
         <v>4.5041784000000001E-2</v>
       </c>
-      <c r="U40" s="35">
+      <c r="U40" s="33">
         <v>3.93</v>
       </c>
-      <c r="V40" s="35">
+      <c r="V40" s="33">
         <v>3.3959999999999999</v>
       </c>
       <c r="W40" s="5">
@@ -6031,7 +6023,7 @@
       </c>
     </row>
     <row r="41" spans="1:31">
-      <c r="A41" s="68" t="s">
+      <c r="A41" s="66" t="s">
         <v>44</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -6049,7 +6041,7 @@
       <c r="F41" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G41" s="61" t="s">
+      <c r="G41" s="59" t="s">
         <v>371</v>
       </c>
       <c r="H41" s="12" t="s">
@@ -6058,37 +6050,37 @@
       <c r="I41" s="5">
         <v>0.1</v>
       </c>
-      <c r="J41" s="35">
+      <c r="J41" s="33">
         <v>1.3</v>
       </c>
-      <c r="K41" s="35"/>
-      <c r="L41" s="35">
+      <c r="K41" s="33"/>
+      <c r="L41" s="33">
         <v>0.14899999999999999</v>
       </c>
-      <c r="M41" s="35"/>
-      <c r="N41" s="35"/>
-      <c r="O41" s="35">
+      <c r="M41" s="33"/>
+      <c r="N41" s="33"/>
+      <c r="O41" s="33">
         <v>0.29799999999999999</v>
       </c>
-      <c r="P41" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="35">
+      <c r="P41" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="33">
         <v>7.6426068999999999E-2</v>
       </c>
-      <c r="R41" s="35">
+      <c r="R41" s="33">
         <v>0.84262339500000005</v>
       </c>
-      <c r="S41" s="35">
+      <c r="S41" s="33">
         <v>5.663179E-3</v>
       </c>
-      <c r="T41" s="35">
+      <c r="T41" s="33">
         <v>4.1991897E-2</v>
       </c>
-      <c r="U41" s="35">
+      <c r="U41" s="33">
         <v>4.077</v>
       </c>
-      <c r="V41" s="35">
+      <c r="V41" s="33">
         <v>3.3340000000000001</v>
       </c>
       <c r="W41" s="5">
@@ -6117,7 +6109,7 @@
       </c>
     </row>
     <row r="42" spans="1:31">
-      <c r="A42" s="68" t="s">
+      <c r="A42" s="66" t="s">
         <v>45</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -6135,7 +6127,7 @@
       <c r="F42" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G42" s="61" t="s">
+      <c r="G42" s="59" t="s">
         <v>372</v>
       </c>
       <c r="H42" s="12" t="s">
@@ -6144,37 +6136,37 @@
       <c r="I42" s="5">
         <v>0.1</v>
       </c>
-      <c r="J42" s="35">
+      <c r="J42" s="33">
         <v>1.4850000000000001</v>
       </c>
-      <c r="K42" s="35"/>
-      <c r="L42" s="35"/>
-      <c r="M42" s="35">
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33">
         <v>2.8620000000000001</v>
       </c>
-      <c r="N42" s="35"/>
-      <c r="O42" s="35">
+      <c r="N42" s="33"/>
+      <c r="O42" s="33">
         <v>2.8620000000000001</v>
       </c>
-      <c r="P42" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="35">
-        <v>0</v>
-      </c>
-      <c r="R42" s="35">
+      <c r="P42" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="33">
+        <v>0</v>
+      </c>
+      <c r="R42" s="33">
         <v>6.3162172000000003E-2</v>
       </c>
-      <c r="S42" s="35">
-        <v>0</v>
-      </c>
-      <c r="T42" s="35">
-        <v>0</v>
-      </c>
-      <c r="U42" s="35">
+      <c r="S42" s="33">
+        <v>0</v>
+      </c>
+      <c r="T42" s="33">
+        <v>0</v>
+      </c>
+      <c r="U42" s="33">
         <v>5.7110000000000003</v>
       </c>
-      <c r="V42" s="35">
+      <c r="V42" s="33">
         <v>5.6040000000000001</v>
       </c>
       <c r="W42" s="5">
@@ -6203,7 +6195,7 @@
       </c>
     </row>
     <row r="43" spans="1:31">
-      <c r="A43" s="68" t="s">
+      <c r="A43" s="66" t="s">
         <v>46</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -6221,7 +6213,7 @@
       <c r="F43" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G43" s="61" t="s">
+      <c r="G43" s="59" t="s">
         <v>372</v>
       </c>
       <c r="H43" s="12" t="s">
@@ -6230,37 +6222,37 @@
       <c r="I43" s="5">
         <v>0.1</v>
       </c>
-      <c r="J43" s="35">
+      <c r="J43" s="33">
         <v>1.6</v>
       </c>
-      <c r="K43" s="35"/>
-      <c r="L43" s="35"/>
-      <c r="M43" s="35">
+      <c r="K43" s="33"/>
+      <c r="L43" s="33"/>
+      <c r="M43" s="33">
         <v>3.0840000000000001</v>
       </c>
-      <c r="N43" s="35"/>
-      <c r="O43" s="35">
+      <c r="N43" s="33"/>
+      <c r="O43" s="33">
         <v>3.0840000000000001</v>
       </c>
-      <c r="P43" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="35">
-        <v>0</v>
-      </c>
-      <c r="R43" s="35">
+      <c r="P43" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="33">
+        <v>0</v>
+      </c>
+      <c r="R43" s="33">
         <v>7.4209667000000007E-2</v>
       </c>
-      <c r="S43" s="35">
-        <v>0</v>
-      </c>
-      <c r="T43" s="35">
-        <v>0</v>
-      </c>
-      <c r="U43" s="35">
+      <c r="S43" s="33">
+        <v>0</v>
+      </c>
+      <c r="T43" s="33">
+        <v>0</v>
+      </c>
+      <c r="U43" s="33">
         <v>6.0389999999999997</v>
       </c>
-      <c r="V43" s="35">
+      <c r="V43" s="33">
         <v>5.8689999999999998</v>
       </c>
       <c r="W43" s="5">
@@ -6289,7 +6281,7 @@
       </c>
     </row>
     <row r="44" spans="1:31">
-      <c r="A44" s="68" t="s">
+      <c r="A44" s="66" t="s">
         <v>47</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -6307,7 +6299,7 @@
       <c r="F44" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="59" t="s">
         <v>372</v>
       </c>
       <c r="H44" s="12" t="s">
@@ -6316,37 +6308,37 @@
       <c r="I44" s="5">
         <v>0.1</v>
       </c>
-      <c r="J44" s="35">
+      <c r="J44" s="33">
         <v>1.4350000000000001</v>
       </c>
-      <c r="K44" s="35"/>
-      <c r="L44" s="35"/>
-      <c r="M44" s="35">
+      <c r="K44" s="33"/>
+      <c r="L44" s="33"/>
+      <c r="M44" s="33">
         <v>2.7629999999999999</v>
       </c>
-      <c r="N44" s="35"/>
-      <c r="O44" s="35">
+      <c r="N44" s="33"/>
+      <c r="O44" s="33">
         <v>2.7629999999999999</v>
       </c>
-      <c r="P44" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="35">
-        <v>0</v>
-      </c>
-      <c r="R44" s="35">
+      <c r="P44" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="33">
+        <v>0</v>
+      </c>
+      <c r="R44" s="33">
         <v>7.4921513999999995E-2</v>
       </c>
-      <c r="S44" s="35">
-        <v>0</v>
-      </c>
-      <c r="T44" s="35">
-        <v>0</v>
-      </c>
-      <c r="U44" s="35">
+      <c r="S44" s="33">
+        <v>0</v>
+      </c>
+      <c r="T44" s="33">
+        <v>0</v>
+      </c>
+      <c r="U44" s="33">
         <v>5.32</v>
       </c>
-      <c r="V44" s="35">
+      <c r="V44" s="33">
         <v>5.0789999999999997</v>
       </c>
       <c r="W44" s="5">
@@ -6375,7 +6367,7 @@
       </c>
     </row>
     <row r="45" spans="1:31">
-      <c r="A45" s="68" t="s">
+      <c r="A45" s="66" t="s">
         <v>48</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -6393,7 +6385,7 @@
       <c r="F45" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G45" s="61" t="s">
+      <c r="G45" s="59" t="s">
         <v>373</v>
       </c>
       <c r="H45" s="12" t="s">
@@ -6402,37 +6394,37 @@
       <c r="I45" s="5">
         <v>0.1</v>
       </c>
-      <c r="J45" s="35">
+      <c r="J45" s="33">
         <v>1.6779999999999999</v>
       </c>
-      <c r="K45" s="35"/>
-      <c r="L45" s="35"/>
-      <c r="M45" s="35">
+      <c r="K45" s="33"/>
+      <c r="L45" s="33"/>
+      <c r="M45" s="33">
         <v>0.33400000000000002</v>
       </c>
-      <c r="N45" s="35"/>
-      <c r="O45" s="35">
+      <c r="N45" s="33"/>
+      <c r="O45" s="33">
         <v>0.33400000000000002</v>
       </c>
-      <c r="P45" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="35">
-        <v>0</v>
-      </c>
-      <c r="R45" s="35">
+      <c r="P45" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="33">
+        <v>0</v>
+      </c>
+      <c r="R45" s="33">
         <v>0.27117874199999997</v>
       </c>
-      <c r="S45" s="35">
-        <v>0</v>
-      </c>
-      <c r="T45" s="35">
-        <v>0</v>
-      </c>
-      <c r="U45" s="35">
+      <c r="S45" s="33">
+        <v>0</v>
+      </c>
+      <c r="T45" s="33">
+        <v>0</v>
+      </c>
+      <c r="U45" s="33">
         <v>5.7240000000000002</v>
       </c>
-      <c r="V45" s="35">
+      <c r="V45" s="33">
         <v>5.9080000000000004</v>
       </c>
       <c r="W45" s="5">
@@ -6461,7 +6453,7 @@
       </c>
     </row>
     <row r="46" spans="1:31">
-      <c r="A46" s="68" t="s">
+      <c r="A46" s="66" t="s">
         <v>49</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -6479,7 +6471,7 @@
       <c r="F46" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G46" s="61" t="s">
+      <c r="G46" s="59" t="s">
         <v>373</v>
       </c>
       <c r="H46" s="12" t="s">
@@ -6488,37 +6480,37 @@
       <c r="I46" s="5">
         <v>0.1</v>
       </c>
-      <c r="J46" s="35">
+      <c r="J46" s="33">
         <v>1.6930000000000001</v>
       </c>
-      <c r="K46" s="35"/>
-      <c r="L46" s="35"/>
-      <c r="M46" s="35">
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="33">
         <v>0.33700000000000002</v>
       </c>
-      <c r="N46" s="35"/>
-      <c r="O46" s="35">
+      <c r="N46" s="33"/>
+      <c r="O46" s="33">
         <v>0.33700000000000002</v>
       </c>
-      <c r="P46" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="35">
-        <v>0</v>
-      </c>
-      <c r="R46" s="35">
+      <c r="P46" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="33">
+        <v>0</v>
+      </c>
+      <c r="R46" s="33">
         <v>0.30716928599999999</v>
       </c>
-      <c r="S46" s="35">
-        <v>0</v>
-      </c>
-      <c r="T46" s="35">
-        <v>0</v>
-      </c>
-      <c r="U46" s="35">
+      <c r="S46" s="33">
+        <v>0</v>
+      </c>
+      <c r="T46" s="33">
+        <v>0</v>
+      </c>
+      <c r="U46" s="33">
         <v>5.9720000000000004</v>
       </c>
-      <c r="V46" s="35">
+      <c r="V46" s="33">
         <v>5.29</v>
       </c>
       <c r="W46" s="5">
@@ -6547,7 +6539,7 @@
       </c>
     </row>
     <row r="47" spans="1:31">
-      <c r="A47" s="68" t="s">
+      <c r="A47" s="66" t="s">
         <v>50</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -6565,7 +6557,7 @@
       <c r="F47" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G47" s="61" t="s">
+      <c r="G47" s="59" t="s">
         <v>373</v>
       </c>
       <c r="H47" s="12" t="s">
@@ -6574,37 +6566,37 @@
       <c r="I47" s="5">
         <v>0.1</v>
       </c>
-      <c r="J47" s="35">
+      <c r="J47" s="33">
         <v>1.647</v>
       </c>
-      <c r="K47" s="35"/>
-      <c r="L47" s="35"/>
-      <c r="M47" s="35">
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33">
         <v>0.32700000000000001</v>
       </c>
-      <c r="N47" s="35"/>
-      <c r="O47" s="35">
+      <c r="N47" s="33"/>
+      <c r="O47" s="33">
         <v>0.32700000000000001</v>
       </c>
-      <c r="P47" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="35">
-        <v>0</v>
-      </c>
-      <c r="R47" s="35">
+      <c r="P47" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="33">
+        <v>0</v>
+      </c>
+      <c r="R47" s="33">
         <v>0.20397084300000001</v>
       </c>
-      <c r="S47" s="35">
-        <v>0</v>
-      </c>
-      <c r="T47" s="35">
-        <v>0</v>
-      </c>
-      <c r="U47" s="35">
+      <c r="S47" s="33">
+        <v>0</v>
+      </c>
+      <c r="T47" s="33">
+        <v>0</v>
+      </c>
+      <c r="U47" s="33">
         <v>6.1310000000000002</v>
       </c>
-      <c r="V47" s="35">
+      <c r="V47" s="33">
         <v>5.69</v>
       </c>
       <c r="W47" s="5">
@@ -6633,7 +6625,7 @@
       </c>
     </row>
     <row r="48" spans="1:31">
-      <c r="A48" s="68" t="s">
+      <c r="A48" s="66" t="s">
         <v>51</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -6651,7 +6643,7 @@
       <c r="F48" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G48" s="61" t="s">
+      <c r="G48" s="59" t="s">
         <v>374</v>
       </c>
       <c r="H48" s="12" t="s">
@@ -6660,37 +6652,37 @@
       <c r="I48" s="5">
         <v>0.1</v>
       </c>
-      <c r="J48" s="35">
+      <c r="J48" s="33">
         <v>1.4790000000000001</v>
       </c>
-      <c r="K48" s="35"/>
-      <c r="L48" s="35"/>
-      <c r="M48" s="35"/>
-      <c r="N48" s="35">
+      <c r="K48" s="33"/>
+      <c r="L48" s="33"/>
+      <c r="M48" s="33"/>
+      <c r="N48" s="33">
         <v>2.919</v>
       </c>
-      <c r="O48" s="35">
+      <c r="O48" s="33">
         <v>2.919</v>
       </c>
-      <c r="P48" s="35">
+      <c r="P48" s="33">
         <v>6.4434642E-2</v>
       </c>
-      <c r="Q48" s="35">
-        <v>0</v>
-      </c>
-      <c r="R48" s="35">
+      <c r="Q48" s="33">
+        <v>0</v>
+      </c>
+      <c r="R48" s="33">
         <v>0.16559933199999999</v>
       </c>
-      <c r="S48" s="35">
-        <v>0</v>
-      </c>
-      <c r="T48" s="35">
+      <c r="S48" s="33">
+        <v>0</v>
+      </c>
+      <c r="T48" s="33">
         <v>4.8736990000000004E-3</v>
       </c>
-      <c r="U48" s="35">
+      <c r="U48" s="33">
         <v>4.7869999999999999</v>
       </c>
-      <c r="V48" s="35">
+      <c r="V48" s="33">
         <v>4.5609999999999999</v>
       </c>
       <c r="W48" s="5">
@@ -6719,7 +6711,7 @@
       </c>
     </row>
     <row r="49" spans="1:30">
-      <c r="A49" s="68" t="s">
+      <c r="A49" s="66" t="s">
         <v>52</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -6737,7 +6729,7 @@
       <c r="F49" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G49" s="61" t="s">
+      <c r="G49" s="59" t="s">
         <v>374</v>
       </c>
       <c r="H49" s="12" t="s">
@@ -6746,37 +6738,37 @@
       <c r="I49" s="5">
         <v>0.1</v>
       </c>
-      <c r="J49" s="35">
+      <c r="J49" s="33">
         <v>1.633</v>
       </c>
-      <c r="K49" s="35"/>
-      <c r="L49" s="35"/>
-      <c r="M49" s="35"/>
-      <c r="N49" s="35">
+      <c r="K49" s="33"/>
+      <c r="L49" s="33"/>
+      <c r="M49" s="33"/>
+      <c r="N49" s="33">
         <v>3.2</v>
       </c>
-      <c r="O49" s="35">
+      <c r="O49" s="33">
         <v>3.2</v>
       </c>
-      <c r="P49" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="35">
-        <v>0</v>
-      </c>
-      <c r="R49" s="35">
+      <c r="P49" s="33">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="33">
+        <v>0</v>
+      </c>
+      <c r="R49" s="33">
         <v>0.156217087</v>
       </c>
-      <c r="S49" s="35">
-        <v>0</v>
-      </c>
-      <c r="T49" s="35">
-        <v>0</v>
-      </c>
-      <c r="U49" s="35">
+      <c r="S49" s="33">
+        <v>0</v>
+      </c>
+      <c r="T49" s="33">
+        <v>0</v>
+      </c>
+      <c r="U49" s="33">
         <v>5.1379999999999999</v>
       </c>
-      <c r="V49" s="35">
+      <c r="V49" s="33">
         <v>4.9089999999999998</v>
       </c>
       <c r="W49" s="5">
@@ -6805,7 +6797,7 @@
       </c>
     </row>
     <row r="50" spans="1:30">
-      <c r="A50" s="68" t="s">
+      <c r="A50" s="66" t="s">
         <v>53</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -6823,7 +6815,7 @@
       <c r="F50" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G50" s="61" t="s">
+      <c r="G50" s="59" t="s">
         <v>374</v>
       </c>
       <c r="H50" s="12" t="s">
@@ -6832,37 +6824,37 @@
       <c r="I50" s="5">
         <v>0.1</v>
       </c>
-      <c r="J50" s="35">
+      <c r="J50" s="33">
         <v>1.571</v>
       </c>
-      <c r="K50" s="35"/>
-      <c r="L50" s="35"/>
-      <c r="M50" s="35"/>
-      <c r="N50" s="35">
+      <c r="K50" s="33"/>
+      <c r="L50" s="33"/>
+      <c r="M50" s="33"/>
+      <c r="N50" s="33">
         <v>3.0830000000000002</v>
       </c>
-      <c r="O50" s="35">
+      <c r="O50" s="33">
         <v>3.0830000000000002</v>
       </c>
-      <c r="P50" s="35">
+      <c r="P50" s="33">
         <v>6.4504826000000001E-2</v>
       </c>
-      <c r="Q50" s="35">
-        <v>0</v>
-      </c>
-      <c r="R50" s="35">
+      <c r="Q50" s="33">
+        <v>0</v>
+      </c>
+      <c r="R50" s="33">
         <v>0.15037355499999999</v>
       </c>
-      <c r="S50" s="35">
-        <v>0</v>
-      </c>
-      <c r="T50" s="35">
+      <c r="S50" s="33">
+        <v>0</v>
+      </c>
+      <c r="T50" s="33">
         <v>5.596462E-3</v>
       </c>
-      <c r="U50" s="35">
+      <c r="U50" s="33">
         <v>4.9610000000000003</v>
       </c>
-      <c r="V50" s="35">
+      <c r="V50" s="33">
         <v>4.5490000000000004</v>
       </c>
       <c r="W50" s="5">
@@ -6891,7 +6883,7 @@
       </c>
     </row>
     <row r="51" spans="1:30">
-      <c r="A51" s="68" t="s">
+      <c r="A51" s="66" t="s">
         <v>54</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -6909,7 +6901,7 @@
       <c r="F51" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G51" s="61" t="s">
+      <c r="G51" s="59" t="s">
         <v>375</v>
       </c>
       <c r="H51" s="12" t="s">
@@ -6918,37 +6910,37 @@
       <c r="I51" s="5">
         <v>0.1</v>
       </c>
-      <c r="J51" s="35">
+      <c r="J51" s="33">
         <v>1.4510000000000001</v>
       </c>
-      <c r="K51" s="35"/>
-      <c r="L51" s="35"/>
-      <c r="M51" s="35"/>
-      <c r="N51" s="35">
+      <c r="K51" s="33"/>
+      <c r="L51" s="33"/>
+      <c r="M51" s="33"/>
+      <c r="N51" s="33">
         <v>0.29199999999999998</v>
       </c>
-      <c r="O51" s="35">
+      <c r="O51" s="33">
         <v>0.29199999999999998</v>
       </c>
-      <c r="P51" s="35">
+      <c r="P51" s="33">
         <v>0.16597783599999999</v>
       </c>
-      <c r="Q51" s="35">
+      <c r="Q51" s="33">
         <v>6.6479359000000002E-2</v>
       </c>
-      <c r="R51" s="35">
+      <c r="R51" s="33">
         <v>0.60819290000000004</v>
       </c>
-      <c r="S51" s="35">
-        <v>0</v>
-      </c>
-      <c r="T51" s="35">
+      <c r="S51" s="33">
+        <v>0</v>
+      </c>
+      <c r="T51" s="33">
         <v>2.5725250000000002E-2</v>
       </c>
-      <c r="U51" s="35">
+      <c r="U51" s="33">
         <v>4.18</v>
       </c>
-      <c r="V51" s="35">
+      <c r="V51" s="33">
         <v>4.0129999999999999</v>
       </c>
       <c r="W51" s="5">
@@ -6977,7 +6969,7 @@
       </c>
     </row>
     <row r="52" spans="1:30">
-      <c r="A52" s="68" t="s">
+      <c r="A52" s="66" t="s">
         <v>55</v>
       </c>
       <c r="B52" s="6" t="s">
@@ -6995,7 +6987,7 @@
       <c r="F52" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G52" s="61" t="s">
+      <c r="G52" s="59" t="s">
         <v>375</v>
       </c>
       <c r="H52" s="12" t="s">
@@ -7004,37 +6996,37 @@
       <c r="I52" s="5">
         <v>0.1</v>
       </c>
-      <c r="J52" s="35">
+      <c r="J52" s="33">
         <v>1.7090000000000001</v>
       </c>
-      <c r="K52" s="35"/>
-      <c r="L52" s="35"/>
-      <c r="M52" s="35"/>
-      <c r="N52" s="35">
+      <c r="K52" s="33"/>
+      <c r="L52" s="33"/>
+      <c r="M52" s="33"/>
+      <c r="N52" s="33">
         <v>0.33900000000000002</v>
       </c>
-      <c r="O52" s="35">
+      <c r="O52" s="33">
         <v>0.33900000000000002</v>
       </c>
-      <c r="P52" s="35">
+      <c r="P52" s="33">
         <v>6.0174350000000001E-2</v>
       </c>
-      <c r="Q52" s="35">
+      <c r="Q52" s="33">
         <v>7.8079274000000004E-2</v>
       </c>
-      <c r="R52" s="35">
+      <c r="R52" s="33">
         <v>0.66867871400000001</v>
       </c>
-      <c r="S52" s="35">
-        <v>0</v>
-      </c>
-      <c r="T52" s="35">
+      <c r="S52" s="33">
+        <v>0</v>
+      </c>
+      <c r="T52" s="33">
         <v>3.5868012999999997E-2</v>
       </c>
-      <c r="U52" s="35">
+      <c r="U52" s="33">
         <v>4.9020000000000001</v>
       </c>
-      <c r="V52" s="35">
+      <c r="V52" s="33">
         <v>4.45</v>
       </c>
       <c r="W52" s="5">
@@ -7063,7 +7055,7 @@
       </c>
     </row>
     <row r="53" spans="1:30">
-      <c r="A53" s="68" t="s">
+      <c r="A53" s="66" t="s">
         <v>56</v>
       </c>
       <c r="B53" s="6" t="s">
@@ -7081,7 +7073,7 @@
       <c r="F53" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G53" s="61" t="s">
+      <c r="G53" s="59" t="s">
         <v>375</v>
       </c>
       <c r="H53" s="12" t="s">
@@ -7090,37 +7082,37 @@
       <c r="I53" s="5">
         <v>0.1</v>
       </c>
-      <c r="J53" s="35">
+      <c r="J53" s="33">
         <v>1.6220000000000001</v>
       </c>
-      <c r="K53" s="35"/>
-      <c r="L53" s="35"/>
-      <c r="M53" s="35"/>
-      <c r="N53" s="35">
+      <c r="K53" s="33"/>
+      <c r="L53" s="33"/>
+      <c r="M53" s="33"/>
+      <c r="N53" s="33">
         <v>0.32900000000000001</v>
       </c>
-      <c r="O53" s="35">
+      <c r="O53" s="33">
         <v>0.32900000000000001</v>
       </c>
-      <c r="P53" s="35">
+      <c r="P53" s="33">
         <v>0.18362290100000001</v>
       </c>
-      <c r="Q53" s="35">
+      <c r="Q53" s="33">
         <v>0.16825845</v>
       </c>
-      <c r="R53" s="35">
+      <c r="R53" s="33">
         <v>0.92271634599999997</v>
       </c>
-      <c r="S53" s="35">
-        <v>0</v>
-      </c>
-      <c r="T53" s="35">
+      <c r="S53" s="33">
+        <v>0</v>
+      </c>
+      <c r="T53" s="33">
         <v>4.8272586999999999E-2</v>
       </c>
-      <c r="U53" s="35">
+      <c r="U53" s="33">
         <v>4.5620000000000003</v>
       </c>
-      <c r="V53" s="35">
+      <c r="V53" s="33">
         <v>4.2300000000000004</v>
       </c>
       <c r="W53" s="5">
@@ -7148,28 +7140,28 @@
         <v>0.42361575000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:30" s="85" customFormat="1">
-      <c r="A54" s="82" t="s">
+    <row r="54" spans="1:30" s="83" customFormat="1">
+      <c r="A54" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="82" t="s">
+      <c r="B54" s="80" t="s">
         <v>488</v>
       </c>
-      <c r="C54" s="82" t="s">
+      <c r="C54" s="80" t="s">
         <v>339</v>
       </c>
-      <c r="D54" s="82" t="s">
-        <v>169</v>
-      </c>
-      <c r="E54" s="82" t="s">
+      <c r="D54" s="80" t="s">
+        <v>169</v>
+      </c>
+      <c r="E54" s="80" t="s">
         <v>301</v>
       </c>
-      <c r="F54" s="82" t="s">
+      <c r="F54" s="80" t="s">
         <v>167</v>
       </c>
-      <c r="G54" s="83"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="84">
+      <c r="G54" s="81"/>
+      <c r="H54" s="80"/>
+      <c r="I54" s="82">
         <v>0.1</v>
       </c>
     </row>
@@ -7192,22 +7184,22 @@
       <c r="F55" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="G55" s="60" t="s">
+      <c r="G55" s="58" t="s">
         <v>58</v>
       </c>
       <c r="H55" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="I55" s="44">
+      <c r="I55" s="42">
         <v>0.40653850000000002</v>
       </c>
-      <c r="J55" s="45">
+      <c r="J55" s="43">
         <v>-13.20185</v>
       </c>
-      <c r="P55" s="45">
+      <c r="P55" s="43">
         <v>15.979100000000001</v>
       </c>
-      <c r="X55" s="31" t="s">
+      <c r="X55" s="29" t="s">
         <v>93</v>
       </c>
     </row>
@@ -7230,22 +7222,22 @@
       <c r="F56" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G56" s="61" t="s">
+      <c r="G56" s="59" t="s">
         <v>58</v>
       </c>
       <c r="H56" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="I56" s="48">
+      <c r="I56" s="46">
         <v>0.40653850000000002</v>
       </c>
-      <c r="J56" s="49">
+      <c r="J56" s="47">
         <v>-13.20185</v>
       </c>
-      <c r="P56" s="49">
+      <c r="P56" s="47">
         <v>15.979100000000001</v>
       </c>
-      <c r="X56" s="32" t="s">
+      <c r="X56" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -7268,22 +7260,22 @@
       <c r="F57" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G57" s="61" t="s">
+      <c r="G57" s="59" t="s">
         <v>59</v>
       </c>
       <c r="H57" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="I57" s="48">
+      <c r="I57" s="46">
         <v>0.44837779999999999</v>
       </c>
-      <c r="J57" s="49">
+      <c r="J57" s="47">
         <v>-12.97245</v>
       </c>
-      <c r="P57" s="49">
+      <c r="P57" s="47">
         <v>17.642130000000002</v>
       </c>
-      <c r="X57" s="32" t="s">
+      <c r="X57" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -7306,22 +7298,22 @@
       <c r="F58" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="59" t="s">
         <v>59</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="I58" s="48">
+      <c r="I58" s="46">
         <v>0.44837779999999999</v>
       </c>
-      <c r="J58" s="49">
+      <c r="J58" s="47">
         <v>-12.97245</v>
       </c>
-      <c r="P58" s="49">
+      <c r="P58" s="47">
         <v>17.642130000000002</v>
       </c>
-      <c r="X58" s="32" t="s">
+      <c r="X58" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -7344,25 +7336,25 @@
       <c r="F59" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G59" s="61" t="s">
+      <c r="G59" s="59" t="s">
         <v>60</v>
       </c>
       <c r="H59" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="I59" s="48">
+      <c r="I59" s="46">
         <v>0.32723469999999999</v>
       </c>
-      <c r="J59" s="49">
+      <c r="J59" s="47">
         <v>-18.39499</v>
       </c>
-      <c r="P59" s="49">
+      <c r="P59" s="47">
         <v>27.157050000000002</v>
       </c>
-      <c r="T59" s="48">
+      <c r="T59" s="46">
         <v>3.6701839999999999</v>
       </c>
-      <c r="X59" s="32" t="s">
+      <c r="X59" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -7385,25 +7377,25 @@
       <c r="F60" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G60" s="61" t="s">
+      <c r="G60" s="59" t="s">
         <v>60</v>
       </c>
       <c r="H60" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="I60" s="48">
+      <c r="I60" s="46">
         <v>0.32723469999999999</v>
       </c>
-      <c r="J60" s="49">
+      <c r="J60" s="47">
         <v>-18.39499</v>
       </c>
-      <c r="P60" s="49">
+      <c r="P60" s="47">
         <v>27.157050000000002</v>
       </c>
-      <c r="T60" s="48">
+      <c r="T60" s="46">
         <v>3.6701839999999999</v>
       </c>
-      <c r="X60" s="32" t="s">
+      <c r="X60" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -7426,25 +7418,25 @@
       <c r="F61" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G61" s="61" t="s">
+      <c r="G61" s="59" t="s">
         <v>60</v>
       </c>
       <c r="H61" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="I61" s="48">
+      <c r="I61" s="46">
         <v>0.32723469999999999</v>
       </c>
-      <c r="J61" s="49">
+      <c r="J61" s="47">
         <v>-18.39499</v>
       </c>
-      <c r="P61" s="49">
+      <c r="P61" s="47">
         <v>27.157050000000002</v>
       </c>
-      <c r="T61" s="48">
+      <c r="T61" s="46">
         <v>3.6701839999999999</v>
       </c>
-      <c r="X61" s="32" t="s">
+      <c r="X61" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -7467,25 +7459,25 @@
       <c r="F62" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G62" s="61" t="s">
+      <c r="G62" s="59" t="s">
         <v>61</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="I62" s="48">
+      <c r="I62" s="46">
         <v>0.32866410000000001</v>
       </c>
-      <c r="J62" s="49">
+      <c r="J62" s="47">
         <v>-14.408200000000001</v>
       </c>
-      <c r="P62" s="49">
+      <c r="P62" s="47">
         <v>22.896090000000001</v>
       </c>
-      <c r="T62" s="48">
+      <c r="T62" s="46">
         <v>1.9558949999999999</v>
       </c>
-      <c r="X62" s="32" t="s">
+      <c r="X62" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -7508,25 +7500,25 @@
       <c r="F63" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G63" s="61" t="s">
+      <c r="G63" s="59" t="s">
         <v>61</v>
       </c>
       <c r="H63" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="I63" s="48">
+      <c r="I63" s="46">
         <v>0.32866410000000001</v>
       </c>
-      <c r="J63" s="49">
+      <c r="J63" s="47">
         <v>-14.408200000000001</v>
       </c>
-      <c r="P63" s="49">
+      <c r="P63" s="47">
         <v>22.896090000000001</v>
       </c>
-      <c r="T63" s="48">
+      <c r="T63" s="46">
         <v>1.9558949999999999</v>
       </c>
-      <c r="X63" s="32" t="s">
+      <c r="X63" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -7549,30 +7541,30 @@
       <c r="F64" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G64" s="62" t="s">
+      <c r="G64" s="60" t="s">
         <v>61</v>
       </c>
       <c r="H64" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="I64" s="46">
+      <c r="I64" s="44">
         <v>0.32866410000000001</v>
       </c>
-      <c r="J64" s="47">
+      <c r="J64" s="45">
         <v>-14.408200000000001</v>
       </c>
-      <c r="P64" s="47">
+      <c r="P64" s="45">
         <v>22.896090000000001</v>
       </c>
-      <c r="T64" s="46">
+      <c r="T64" s="44">
         <v>1.9558949999999999</v>
       </c>
-      <c r="X64" s="33" t="s">
+      <c r="X64" s="31" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:30" s="13" customFormat="1">
-      <c r="A65" s="69" t="s">
+      <c r="A65" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B65" s="10" t="s">
@@ -7590,14 +7582,14 @@
       <c r="F65" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="G65" s="60"/>
+      <c r="G65" s="58"/>
       <c r="H65" s="10"/>
       <c r="I65" s="13">
         <v>0.1</v>
       </c>
     </row>
     <row r="66" spans="1:30">
-      <c r="A66" s="70" t="s">
+      <c r="A66" s="68" t="s">
         <v>63</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -7615,14 +7607,14 @@
       <c r="F66" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G66" s="61"/>
+      <c r="G66" s="59"/>
       <c r="H66" s="6"/>
       <c r="I66" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="67" spans="1:30">
-      <c r="A67" s="70" t="s">
+      <c r="A67" s="68" t="s">
         <v>64</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -7640,14 +7632,14 @@
       <c r="F67" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G67" s="61"/>
+      <c r="G67" s="59"/>
       <c r="H67" s="6"/>
       <c r="I67" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="68" spans="1:30">
-      <c r="A68" s="70" t="s">
+      <c r="A68" s="68" t="s">
         <v>65</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -7665,14 +7657,14 @@
       <c r="F68" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G68" s="61"/>
+      <c r="G68" s="59"/>
       <c r="H68" s="6"/>
       <c r="I68" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="69" spans="1:30">
-      <c r="A69" s="70" t="s">
+      <c r="A69" s="68" t="s">
         <v>66</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -7690,11 +7682,11 @@
       <c r="F69" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G69" s="61"/>
+      <c r="G69" s="59"/>
       <c r="H69" s="6"/>
     </row>
     <row r="70" spans="1:30">
-      <c r="A70" s="70" t="s">
+      <c r="A70" s="68" t="s">
         <v>67</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -7712,11 +7704,11 @@
       <c r="F70" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G70" s="61"/>
+      <c r="G70" s="59"/>
       <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:30">
-      <c r="A71" s="70" t="s">
+      <c r="A71" s="68" t="s">
         <v>68</v>
       </c>
       <c r="B71" s="6" t="s">
@@ -7734,11 +7726,11 @@
       <c r="F71" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G71" s="61"/>
+      <c r="G71" s="59"/>
       <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:30">
-      <c r="A72" s="70" t="s">
+      <c r="A72" s="68" t="s">
         <v>69</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -7756,11 +7748,11 @@
       <c r="F72" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G72" s="61"/>
+      <c r="G72" s="59"/>
       <c r="H72" s="6"/>
     </row>
-    <row r="73" spans="1:30" s="31" customFormat="1">
-      <c r="A73" s="71" t="s">
+    <row r="73" spans="1:30" s="29" customFormat="1">
+      <c r="A73" s="69" t="s">
         <v>418</v>
       </c>
       <c r="B73" s="10" t="s">
@@ -7778,42 +7770,42 @@
       <c r="F73" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="G73" s="64" t="s">
+      <c r="G73" s="62" t="s">
         <v>104</v>
       </c>
       <c r="H73" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="I73" s="31">
+      <c r="I73" s="29">
         <v>2.7E-2</v>
       </c>
-      <c r="J73" s="50">
+      <c r="J73" s="48">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="K73" s="50">
+      <c r="K73" s="48">
         <v>-0.151308114750691</v>
       </c>
-      <c r="P73" s="50">
-        <v>0</v>
-      </c>
-      <c r="U73" s="50">
+      <c r="P73" s="48">
+        <v>0</v>
+      </c>
+      <c r="U73" s="48">
         <v>0.878</v>
       </c>
       <c r="V73" s="13">
         <v>0.86358170086251695</v>
       </c>
-      <c r="X73" s="31" t="s">
+      <c r="X73" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="Z73" s="31" t="s">
+      <c r="Z73" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="AD73" s="53">
+      <c r="AD73" s="51">
         <v>0.29899999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:30" s="32" customFormat="1">
-      <c r="A74" s="72" t="s">
+    <row r="74" spans="1:30" s="30" customFormat="1">
+      <c r="A74" s="70" t="s">
         <v>419</v>
       </c>
       <c r="B74" s="6" t="s">
@@ -7831,42 +7823,42 @@
       <c r="F74" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G74" s="65" t="s">
+      <c r="G74" s="63" t="s">
         <v>104</v>
       </c>
       <c r="H74" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="I74" s="32">
+      <c r="I74" s="30">
         <v>2.7E-2</v>
       </c>
-      <c r="J74" s="51">
+      <c r="J74" s="49">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="K74" s="51">
+      <c r="K74" s="49">
         <v>-0.151308114750691</v>
       </c>
-      <c r="P74" s="51">
-        <v>0</v>
-      </c>
-      <c r="U74" s="51">
+      <c r="P74" s="49">
+        <v>0</v>
+      </c>
+      <c r="U74" s="49">
         <v>0.878</v>
       </c>
       <c r="V74" s="5">
         <v>0.86358170086251695</v>
       </c>
-      <c r="X74" s="32" t="s">
+      <c r="X74" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z74" s="32" t="s">
+      <c r="Z74" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD74" s="54">
+      <c r="AD74" s="52">
         <v>0.29899999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:30" s="32" customFormat="1">
-      <c r="A75" s="72" t="s">
+    <row r="75" spans="1:30" s="30" customFormat="1">
+      <c r="A75" s="70" t="s">
         <v>420</v>
       </c>
       <c r="B75" s="6" t="s">
@@ -7884,42 +7876,42 @@
       <c r="F75" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G75" s="65" t="s">
+      <c r="G75" s="63" t="s">
         <v>104</v>
       </c>
       <c r="H75" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="I75" s="32">
+      <c r="I75" s="30">
         <v>2.7E-2</v>
       </c>
-      <c r="J75" s="51">
+      <c r="J75" s="49">
         <v>-0.33700000000000002</v>
       </c>
-      <c r="K75" s="51">
+      <c r="K75" s="49">
         <v>-0.151308114750691</v>
       </c>
-      <c r="P75" s="51">
-        <v>0</v>
-      </c>
-      <c r="U75" s="51">
+      <c r="P75" s="49">
+        <v>0</v>
+      </c>
+      <c r="U75" s="49">
         <v>0.878</v>
       </c>
       <c r="V75" s="5">
         <v>0.86358170086251695</v>
       </c>
-      <c r="X75" s="32" t="s">
+      <c r="X75" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z75" s="32" t="s">
+      <c r="Z75" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD75" s="54">
+      <c r="AD75" s="52">
         <v>0.29899999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:30">
-      <c r="A76" s="72" t="s">
+      <c r="A76" s="70" t="s">
         <v>421</v>
       </c>
       <c r="B76" s="6" t="s">
@@ -7937,7 +7929,7 @@
       <c r="F76" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G76" s="61" t="s">
+      <c r="G76" s="59" t="s">
         <v>75</v>
       </c>
       <c r="H76" s="12" t="s">
@@ -7946,33 +7938,33 @@
       <c r="I76" s="5">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="J76" s="51">
+      <c r="J76" s="49">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="K76" s="51">
+      <c r="K76" s="49">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="P76" s="51">
-        <v>0</v>
-      </c>
-      <c r="U76" s="51">
+      <c r="P76" s="49">
+        <v>0</v>
+      </c>
+      <c r="U76" s="49">
         <v>1.458</v>
       </c>
       <c r="V76" s="5">
         <v>1.4368262739973601</v>
       </c>
-      <c r="X76" s="32" t="s">
+      <c r="X76" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z76" s="32" t="s">
+      <c r="Z76" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD76" s="55">
+      <c r="AD76" s="53">
         <v>0.312</v>
       </c>
     </row>
     <row r="77" spans="1:30">
-      <c r="A77" s="72" t="s">
+      <c r="A77" s="70" t="s">
         <v>422</v>
       </c>
       <c r="B77" s="6" t="s">
@@ -7990,7 +7982,7 @@
       <c r="F77" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G77" s="61" t="s">
+      <c r="G77" s="59" t="s">
         <v>75</v>
       </c>
       <c r="H77" s="12" t="s">
@@ -7999,33 +7991,33 @@
       <c r="I77" s="5">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="J77" s="51">
+      <c r="J77" s="49">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="K77" s="51">
+      <c r="K77" s="49">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="P77" s="51">
-        <v>0</v>
-      </c>
-      <c r="U77" s="51">
+      <c r="P77" s="49">
+        <v>0</v>
+      </c>
+      <c r="U77" s="49">
         <v>1.458</v>
       </c>
       <c r="V77" s="5">
         <v>1.4368262739973601</v>
       </c>
-      <c r="X77" s="32" t="s">
+      <c r="X77" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z77" s="32" t="s">
+      <c r="Z77" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD77" s="55">
+      <c r="AD77" s="53">
         <v>0.312</v>
       </c>
     </row>
     <row r="78" spans="1:30">
-      <c r="A78" s="72" t="s">
+      <c r="A78" s="70" t="s">
         <v>423</v>
       </c>
       <c r="B78" s="6" t="s">
@@ -8043,7 +8035,7 @@
       <c r="F78" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G78" s="61" t="s">
+      <c r="G78" s="59" t="s">
         <v>75</v>
       </c>
       <c r="H78" s="12" t="s">
@@ -8052,33 +8044,33 @@
       <c r="I78" s="5">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="J78" s="51">
+      <c r="J78" s="49">
         <v>-0.52300000000000002</v>
       </c>
-      <c r="K78" s="51">
+      <c r="K78" s="49">
         <v>-0.22220072795676099</v>
       </c>
-      <c r="P78" s="51">
-        <v>0</v>
-      </c>
-      <c r="U78" s="51">
+      <c r="P78" s="49">
+        <v>0</v>
+      </c>
+      <c r="U78" s="49">
         <v>1.458</v>
       </c>
       <c r="V78" s="5">
         <v>1.4368262739973601</v>
       </c>
-      <c r="X78" s="32" t="s">
+      <c r="X78" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z78" s="32" t="s">
+      <c r="Z78" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD78" s="55">
+      <c r="AD78" s="53">
         <v>0.312</v>
       </c>
     </row>
     <row r="79" spans="1:30">
-      <c r="A79" s="72" t="s">
+      <c r="A79" s="70" t="s">
         <v>424</v>
       </c>
       <c r="B79" s="6" t="s">
@@ -8096,7 +8088,7 @@
       <c r="F79" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G79" s="61" t="s">
+      <c r="G79" s="59" t="s">
         <v>76</v>
       </c>
       <c r="H79" s="12" t="s">
@@ -8105,33 +8097,33 @@
       <c r="I79" s="5">
         <v>0.10199999999999999</v>
       </c>
-      <c r="J79" s="51">
+      <c r="J79" s="49">
         <v>-1.171</v>
       </c>
-      <c r="K79" s="51">
+      <c r="K79" s="49">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="P79" s="51">
-        <v>0</v>
-      </c>
-      <c r="U79" s="51">
+      <c r="P79" s="49">
+        <v>0</v>
+      </c>
+      <c r="U79" s="49">
         <v>2.5470000000000002</v>
       </c>
       <c r="V79" s="5">
         <v>2.4905493340587901</v>
       </c>
-      <c r="X79" s="32" t="s">
+      <c r="X79" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z79" s="32" t="s">
+      <c r="Z79" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD79" s="55">
+      <c r="AD79" s="53">
         <v>0.371</v>
       </c>
     </row>
     <row r="80" spans="1:30">
-      <c r="A80" s="72" t="s">
+      <c r="A80" s="70" t="s">
         <v>425</v>
       </c>
       <c r="B80" s="6" t="s">
@@ -8149,7 +8141,7 @@
       <c r="F80" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G80" s="61" t="s">
+      <c r="G80" s="59" t="s">
         <v>76</v>
       </c>
       <c r="H80" s="12" t="s">
@@ -8158,33 +8150,33 @@
       <c r="I80" s="5">
         <v>0.10199999999999999</v>
       </c>
-      <c r="J80" s="51">
+      <c r="J80" s="49">
         <v>-1.171</v>
       </c>
-      <c r="K80" s="51">
+      <c r="K80" s="49">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="P80" s="51">
-        <v>0</v>
-      </c>
-      <c r="U80" s="51">
+      <c r="P80" s="49">
+        <v>0</v>
+      </c>
+      <c r="U80" s="49">
         <v>2.5470000000000002</v>
       </c>
       <c r="V80" s="5">
         <v>2.4905493340587901</v>
       </c>
-      <c r="X80" s="32" t="s">
+      <c r="X80" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z80" s="32" t="s">
+      <c r="Z80" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD80" s="55">
+      <c r="AD80" s="53">
         <v>0.371</v>
       </c>
     </row>
     <row r="81" spans="1:30">
-      <c r="A81" s="72" t="s">
+      <c r="A81" s="70" t="s">
         <v>426</v>
       </c>
       <c r="B81" s="6" t="s">
@@ -8202,7 +8194,7 @@
       <c r="F81" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G81" s="61" t="s">
+      <c r="G81" s="59" t="s">
         <v>76</v>
       </c>
       <c r="H81" s="12" t="s">
@@ -8211,33 +8203,33 @@
       <c r="I81" s="5">
         <v>0.10199999999999999</v>
       </c>
-      <c r="J81" s="51">
+      <c r="J81" s="49">
         <v>-1.171</v>
       </c>
-      <c r="K81" s="51">
+      <c r="K81" s="49">
         <v>-0.59240301221006997</v>
       </c>
-      <c r="P81" s="51">
-        <v>0</v>
-      </c>
-      <c r="U81" s="51">
+      <c r="P81" s="49">
+        <v>0</v>
+      </c>
+      <c r="U81" s="49">
         <v>2.5470000000000002</v>
       </c>
       <c r="V81" s="5">
         <v>2.4905493340587901</v>
       </c>
-      <c r="X81" s="32" t="s">
+      <c r="X81" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z81" s="32" t="s">
+      <c r="Z81" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD81" s="55">
+      <c r="AD81" s="53">
         <v>0.371</v>
       </c>
     </row>
     <row r="82" spans="1:30">
-      <c r="A82" s="72" t="s">
+      <c r="A82" s="70" t="s">
         <v>427</v>
       </c>
       <c r="B82" s="6" t="s">
@@ -8255,7 +8247,7 @@
       <c r="F82" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G82" s="61" t="s">
+      <c r="G82" s="59" t="s">
         <v>77</v>
       </c>
       <c r="H82" s="12" t="s">
@@ -8264,33 +8256,33 @@
       <c r="I82" s="5">
         <v>0.152</v>
       </c>
-      <c r="J82" s="51">
+      <c r="J82" s="49">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="K82" s="51">
+      <c r="K82" s="49">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="P82" s="51">
-        <v>0</v>
-      </c>
-      <c r="U82" s="51">
+      <c r="P82" s="49">
+        <v>0</v>
+      </c>
+      <c r="U82" s="49">
         <v>3.81518914277475</v>
       </c>
       <c r="V82" s="5">
         <v>3.855</v>
       </c>
-      <c r="X82" s="32" t="s">
+      <c r="X82" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z82" s="32" t="s">
+      <c r="Z82" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD82" s="55">
+      <c r="AD82" s="53">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:30">
-      <c r="A83" s="72" t="s">
+      <c r="A83" s="70" t="s">
         <v>428</v>
       </c>
       <c r="B83" s="6" t="s">
@@ -8308,7 +8300,7 @@
       <c r="F83" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G83" s="61" t="s">
+      <c r="G83" s="59" t="s">
         <v>77</v>
       </c>
       <c r="H83" s="12" t="s">
@@ -8317,33 +8309,33 @@
       <c r="I83" s="5">
         <v>0.152</v>
       </c>
-      <c r="J83" s="51">
+      <c r="J83" s="49">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="K83" s="51">
+      <c r="K83" s="49">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="P83" s="51">
-        <v>0</v>
-      </c>
-      <c r="U83" s="51">
+      <c r="P83" s="49">
+        <v>0</v>
+      </c>
+      <c r="U83" s="49">
         <v>3.81518914277475</v>
       </c>
       <c r="V83" s="5">
         <v>3.855</v>
       </c>
-      <c r="X83" s="32" t="s">
+      <c r="X83" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z83" s="32" t="s">
+      <c r="Z83" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD83" s="55">
+      <c r="AD83" s="53">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="84" spans="1:30">
-      <c r="A84" s="72" t="s">
+      <c r="A84" s="70" t="s">
         <v>429</v>
       </c>
       <c r="B84" s="6" t="s">
@@ -8361,7 +8353,7 @@
       <c r="F84" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G84" s="61" t="s">
+      <c r="G84" s="59" t="s">
         <v>77</v>
       </c>
       <c r="H84" s="12" t="s">
@@ -8370,33 +8362,33 @@
       <c r="I84" s="5">
         <v>0.152</v>
       </c>
-      <c r="J84" s="51">
+      <c r="J84" s="49">
         <v>-1.6830000000000001</v>
       </c>
-      <c r="K84" s="51">
+      <c r="K84" s="49">
         <v>-0.81572561388224996</v>
       </c>
-      <c r="P84" s="51">
-        <v>0</v>
-      </c>
-      <c r="U84" s="51">
+      <c r="P84" s="49">
+        <v>0</v>
+      </c>
+      <c r="U84" s="49">
         <v>3.81518914277475</v>
       </c>
       <c r="V84" s="5">
         <v>3.855</v>
       </c>
-      <c r="X84" s="32" t="s">
+      <c r="X84" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z84" s="32" t="s">
+      <c r="Z84" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD84" s="55">
+      <c r="AD84" s="53">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="85" spans="1:30">
-      <c r="A85" s="72" t="s">
+      <c r="A85" s="70" t="s">
         <v>430</v>
       </c>
       <c r="B85" s="6" t="s">
@@ -8414,7 +8406,7 @@
       <c r="F85" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G85" s="61" t="s">
+      <c r="G85" s="59" t="s">
         <v>78</v>
       </c>
       <c r="H85" s="12" t="s">
@@ -8423,33 +8415,33 @@
       <c r="I85" s="5">
         <v>0.214</v>
       </c>
-      <c r="J85" s="51">
+      <c r="J85" s="49">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="K85" s="51">
+      <c r="K85" s="49">
         <v>-1.22567508688439</v>
       </c>
-      <c r="P85" s="51">
+      <c r="P85" s="49">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="U85" s="51">
+      <c r="U85" s="49">
         <v>5.5949999999999998</v>
       </c>
       <c r="V85" s="5">
         <v>5.4782042149448502</v>
       </c>
-      <c r="X85" s="32" t="s">
+      <c r="X85" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z85" s="32" t="s">
+      <c r="Z85" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD85" s="55">
+      <c r="AD85" s="53">
         <v>0.32</v>
       </c>
     </row>
     <row r="86" spans="1:30">
-      <c r="A86" s="72" t="s">
+      <c r="A86" s="70" t="s">
         <v>431</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -8467,7 +8459,7 @@
       <c r="F86" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G86" s="61" t="s">
+      <c r="G86" s="59" t="s">
         <v>78</v>
       </c>
       <c r="H86" s="12" t="s">
@@ -8476,33 +8468,33 @@
       <c r="I86" s="5">
         <v>0.214</v>
       </c>
-      <c r="J86" s="51">
+      <c r="J86" s="49">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="K86" s="51">
+      <c r="K86" s="49">
         <v>-1.22567508688439</v>
       </c>
-      <c r="P86" s="51">
+      <c r="P86" s="49">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="U86" s="51">
+      <c r="U86" s="49">
         <v>5.5949999999999998</v>
       </c>
       <c r="V86" s="5">
         <v>5.4782042149448502</v>
       </c>
-      <c r="X86" s="32" t="s">
+      <c r="X86" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z86" s="32" t="s">
+      <c r="Z86" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD86" s="55">
+      <c r="AD86" s="53">
         <v>0.32</v>
       </c>
     </row>
     <row r="87" spans="1:30">
-      <c r="A87" s="72" t="s">
+      <c r="A87" s="70" t="s">
         <v>432</v>
       </c>
       <c r="B87" s="6" t="s">
@@ -8520,7 +8512,7 @@
       <c r="F87" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G87" s="61" t="s">
+      <c r="G87" s="59" t="s">
         <v>78</v>
       </c>
       <c r="H87" s="12" t="s">
@@ -8529,33 +8521,33 @@
       <c r="I87" s="5">
         <v>0.214</v>
       </c>
-      <c r="J87" s="51">
+      <c r="J87" s="49">
         <v>-2.4769999999999999</v>
       </c>
-      <c r="K87" s="51">
+      <c r="K87" s="49">
         <v>-1.22567508688439</v>
       </c>
-      <c r="P87" s="51">
+      <c r="P87" s="49">
         <v>-3.4044364549679102E-12</v>
       </c>
-      <c r="U87" s="51">
+      <c r="U87" s="49">
         <v>5.5949999999999998</v>
       </c>
       <c r="V87" s="5">
         <v>5.4782042149448502</v>
       </c>
-      <c r="X87" s="32" t="s">
+      <c r="X87" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z87" s="32" t="s">
+      <c r="Z87" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD87" s="55">
+      <c r="AD87" s="53">
         <v>0.32</v>
       </c>
     </row>
     <row r="88" spans="1:30">
-      <c r="A88" s="72" t="s">
+      <c r="A88" s="70" t="s">
         <v>433</v>
       </c>
       <c r="B88" s="6" t="s">
@@ -8573,7 +8565,7 @@
       <c r="F88" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G88" s="61" t="s">
+      <c r="G88" s="59" t="s">
         <v>79</v>
       </c>
       <c r="H88" s="12" t="s">
@@ -8582,33 +8574,33 @@
       <c r="I88" s="5">
         <v>0.254</v>
       </c>
-      <c r="J88" s="51">
+      <c r="J88" s="49">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="K88" s="51">
+      <c r="K88" s="49">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="P88" s="51">
+      <c r="P88" s="49">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="U88" s="51">
+      <c r="U88" s="49">
         <v>6.484</v>
       </c>
       <c r="V88" s="5">
         <v>6.2489999999999997</v>
       </c>
-      <c r="X88" s="32" t="s">
+      <c r="X88" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z88" s="32" t="s">
+      <c r="Z88" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD88" s="55">
+      <c r="AD88" s="53">
         <v>0.37799999999999995</v>
       </c>
     </row>
     <row r="89" spans="1:30">
-      <c r="A89" s="72" t="s">
+      <c r="A89" s="70" t="s">
         <v>434</v>
       </c>
       <c r="B89" s="6" t="s">
@@ -8626,7 +8618,7 @@
       <c r="F89" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G89" s="61" t="s">
+      <c r="G89" s="59" t="s">
         <v>79</v>
       </c>
       <c r="H89" s="12" t="s">
@@ -8635,33 +8627,33 @@
       <c r="I89" s="5">
         <v>0.254</v>
       </c>
-      <c r="J89" s="51">
+      <c r="J89" s="49">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="K89" s="51">
+      <c r="K89" s="49">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="P89" s="51">
+      <c r="P89" s="49">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="U89" s="51">
+      <c r="U89" s="49">
         <v>6.484</v>
       </c>
       <c r="V89" s="5">
         <v>6.2489999999999997</v>
       </c>
-      <c r="X89" s="32" t="s">
+      <c r="X89" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z89" s="32" t="s">
+      <c r="Z89" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD89" s="55">
+      <c r="AD89" s="53">
         <v>0.37799999999999995</v>
       </c>
     </row>
     <row r="90" spans="1:30">
-      <c r="A90" s="72" t="s">
+      <c r="A90" s="70" t="s">
         <v>435</v>
       </c>
       <c r="B90" s="6" t="s">
@@ -8679,7 +8671,7 @@
       <c r="F90" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G90" s="61" t="s">
+      <c r="G90" s="59" t="s">
         <v>79</v>
       </c>
       <c r="H90" s="12" t="s">
@@ -8688,33 +8680,33 @@
       <c r="I90" s="5">
         <v>0.254</v>
       </c>
-      <c r="J90" s="51">
+      <c r="J90" s="49">
         <v>-2.8620000000000001</v>
       </c>
-      <c r="K90" s="51">
+      <c r="K90" s="49">
         <v>-1.4136198692773401</v>
       </c>
-      <c r="P90" s="51">
+      <c r="P90" s="49">
         <v>7.3805128675275E-12</v>
       </c>
-      <c r="U90" s="51">
+      <c r="U90" s="49">
         <v>6.484</v>
       </c>
       <c r="V90" s="5">
         <v>6.2489999999999997</v>
       </c>
-      <c r="X90" s="32" t="s">
+      <c r="X90" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z90" s="32" t="s">
+      <c r="Z90" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD90" s="55">
+      <c r="AD90" s="53">
         <v>0.37799999999999995</v>
       </c>
     </row>
     <row r="91" spans="1:30">
-      <c r="A91" s="72" t="s">
+      <c r="A91" s="70" t="s">
         <v>436</v>
       </c>
       <c r="B91" s="6" t="s">
@@ -8732,7 +8724,7 @@
       <c r="F91" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G91" s="61" t="s">
+      <c r="G91" s="59" t="s">
         <v>80</v>
       </c>
       <c r="H91" s="12" t="s">
@@ -8741,33 +8733,33 @@
       <c r="I91" s="5">
         <v>0.28399999999999997</v>
       </c>
-      <c r="J91" s="51">
+      <c r="J91" s="49">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="K91" s="51">
+      <c r="K91" s="49">
         <v>-1.47353470842518</v>
       </c>
-      <c r="P91" s="51">
+      <c r="P91" s="49">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="U91" s="51">
+      <c r="U91" s="49">
         <v>8.0890000000000004</v>
       </c>
       <c r="V91" s="5">
         <v>7.9485854277214001</v>
       </c>
-      <c r="X91" s="32" t="s">
+      <c r="X91" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z91" s="32" t="s">
+      <c r="Z91" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD91" s="55">
+      <c r="AD91" s="53">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:30">
-      <c r="A92" s="72" t="s">
+      <c r="A92" s="70" t="s">
         <v>437</v>
       </c>
       <c r="B92" s="6" t="s">
@@ -8785,7 +8777,7 @@
       <c r="F92" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G92" s="61" t="s">
+      <c r="G92" s="59" t="s">
         <v>80</v>
       </c>
       <c r="H92" s="12" t="s">
@@ -8794,33 +8786,33 @@
       <c r="I92" s="5">
         <v>0.28399999999999997</v>
       </c>
-      <c r="J92" s="51">
+      <c r="J92" s="49">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="K92" s="51">
+      <c r="K92" s="49">
         <v>-1.47353470842518</v>
       </c>
-      <c r="P92" s="51">
+      <c r="P92" s="49">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="U92" s="51">
+      <c r="U92" s="49">
         <v>8.0890000000000004</v>
       </c>
       <c r="V92" s="5">
         <v>7.9485854277214001</v>
       </c>
-      <c r="X92" s="32" t="s">
+      <c r="X92" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z92" s="32" t="s">
+      <c r="Z92" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD92" s="55">
+      <c r="AD92" s="53">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:30">
-      <c r="A93" s="72" t="s">
+      <c r="A93" s="70" t="s">
         <v>438</v>
       </c>
       <c r="B93" s="6" t="s">
@@ -8838,7 +8830,7 @@
       <c r="F93" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G93" s="61" t="s">
+      <c r="G93" s="59" t="s">
         <v>80</v>
       </c>
       <c r="H93" s="12" t="s">
@@ -8847,33 +8839,33 @@
       <c r="I93" s="5">
         <v>0.28399999999999997</v>
       </c>
-      <c r="J93" s="51">
+      <c r="J93" s="49">
         <v>-3.2050000000000001</v>
       </c>
-      <c r="K93" s="51">
+      <c r="K93" s="49">
         <v>-1.47353470842518</v>
       </c>
-      <c r="P93" s="51">
+      <c r="P93" s="49">
         <v>-3.4111879987364099E-12</v>
       </c>
-      <c r="U93" s="51">
+      <c r="U93" s="49">
         <v>8.0890000000000004</v>
       </c>
       <c r="V93" s="5">
         <v>7.9485854277214001</v>
       </c>
-      <c r="X93" s="32" t="s">
+      <c r="X93" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z93" s="32" t="s">
+      <c r="Z93" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD93" s="55">
+      <c r="AD93" s="53">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:30">
-      <c r="A94" s="72" t="s">
+      <c r="A94" s="70" t="s">
         <v>439</v>
       </c>
       <c r="B94" s="6" t="s">
@@ -8891,7 +8883,7 @@
       <c r="F94" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G94" s="61" t="s">
+      <c r="G94" s="59" t="s">
         <v>81</v>
       </c>
       <c r="H94" s="12" t="s">
@@ -8900,33 +8892,33 @@
       <c r="I94" s="5">
         <v>0.33400000000000002</v>
       </c>
-      <c r="J94" s="51">
+      <c r="J94" s="49">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="K94" s="51">
+      <c r="K94" s="49">
         <v>-1.99253212300414</v>
       </c>
-      <c r="P94" s="51">
+      <c r="P94" s="49">
         <v>2.0830000000081101</v>
       </c>
-      <c r="U94" s="51">
+      <c r="U94" s="49">
         <v>11.872999999999999</v>
       </c>
       <c r="V94" s="5">
         <v>9.6077296533960403</v>
       </c>
-      <c r="X94" s="32" t="s">
+      <c r="X94" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z94" s="32" t="s">
+      <c r="Z94" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD94" s="55">
+      <c r="AD94" s="53">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="95" spans="1:30">
-      <c r="A95" s="72" t="s">
+      <c r="A95" s="70" t="s">
         <v>440</v>
       </c>
       <c r="B95" s="6" t="s">
@@ -8944,7 +8936,7 @@
       <c r="F95" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G95" s="61" t="s">
+      <c r="G95" s="59" t="s">
         <v>81</v>
       </c>
       <c r="H95" s="12" t="s">
@@ -8953,33 +8945,33 @@
       <c r="I95" s="5">
         <v>0.33400000000000002</v>
       </c>
-      <c r="J95" s="51">
+      <c r="J95" s="49">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="K95" s="51">
+      <c r="K95" s="49">
         <v>-1.99253212300414</v>
       </c>
-      <c r="P95" s="51">
+      <c r="P95" s="49">
         <v>2.0830000000081101</v>
       </c>
-      <c r="U95" s="51">
+      <c r="U95" s="49">
         <v>11.872999999999999</v>
       </c>
       <c r="V95" s="5">
         <v>9.6077296533960403</v>
       </c>
-      <c r="X95" s="32" t="s">
+      <c r="X95" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z95" s="32" t="s">
+      <c r="Z95" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD95" s="55">
+      <c r="AD95" s="53">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="96" spans="1:30">
-      <c r="A96" s="72" t="s">
+      <c r="A96" s="70" t="s">
         <v>441</v>
       </c>
       <c r="B96" s="6" t="s">
@@ -8997,7 +8989,7 @@
       <c r="F96" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G96" s="61" t="s">
+      <c r="G96" s="59" t="s">
         <v>81</v>
       </c>
       <c r="H96" s="12" t="s">
@@ -9006,33 +8998,33 @@
       <c r="I96" s="5">
         <v>0.33400000000000002</v>
       </c>
-      <c r="J96" s="51">
+      <c r="J96" s="49">
         <v>-5.2350000000000003</v>
       </c>
-      <c r="K96" s="51">
+      <c r="K96" s="49">
         <v>-1.99253212300414</v>
       </c>
-      <c r="P96" s="51">
+      <c r="P96" s="49">
         <v>2.0830000000081101</v>
       </c>
-      <c r="U96" s="51">
+      <c r="U96" s="49">
         <v>11.872999999999999</v>
       </c>
       <c r="V96" s="5">
         <v>9.6077296533960403</v>
       </c>
-      <c r="X96" s="32" t="s">
+      <c r="X96" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z96" s="32" t="s">
+      <c r="Z96" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD96" s="55">
+      <c r="AD96" s="53">
         <v>0.41899999999999998</v>
       </c>
     </row>
     <row r="97" spans="1:30">
-      <c r="A97" s="72" t="s">
+      <c r="A97" s="70" t="s">
         <v>442</v>
       </c>
       <c r="B97" s="6" t="s">
@@ -9050,7 +9042,7 @@
       <c r="F97" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G97" s="61" t="s">
+      <c r="G97" s="59" t="s">
         <v>82</v>
       </c>
       <c r="H97" s="12" t="s">
@@ -9059,33 +9051,33 @@
       <c r="I97" s="5">
         <v>0.379</v>
       </c>
-      <c r="J97" s="51">
+      <c r="J97" s="49">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="K97" s="51">
+      <c r="K97" s="49">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="P97" s="51">
+      <c r="P97" s="49">
         <v>5.5389999999999997</v>
       </c>
-      <c r="U97" s="51">
+      <c r="U97" s="49">
         <v>14.304133448972699</v>
       </c>
       <c r="V97" s="5">
         <v>8.8979999999999997</v>
       </c>
-      <c r="X97" s="32" t="s">
+      <c r="X97" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z97" s="32" t="s">
+      <c r="Z97" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD97" s="55">
+      <c r="AD97" s="53">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:30">
-      <c r="A98" s="72" t="s">
+      <c r="A98" s="70" t="s">
         <v>443</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -9103,7 +9095,7 @@
       <c r="F98" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G98" s="61" t="s">
+      <c r="G98" s="59" t="s">
         <v>82</v>
       </c>
       <c r="H98" s="12" t="s">
@@ -9112,33 +9104,33 @@
       <c r="I98" s="5">
         <v>0.379</v>
       </c>
-      <c r="J98" s="51">
+      <c r="J98" s="49">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="K98" s="51">
+      <c r="K98" s="49">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="P98" s="51">
+      <c r="P98" s="49">
         <v>5.5389999999999997</v>
       </c>
-      <c r="U98" s="51">
+      <c r="U98" s="49">
         <v>14.304133448972699</v>
       </c>
       <c r="V98" s="5">
         <v>8.8979999999999997</v>
       </c>
-      <c r="X98" s="32" t="s">
+      <c r="X98" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="Z98" s="32" t="s">
+      <c r="Z98" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AD98" s="55">
+      <c r="AD98" s="53">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="99" spans="1:30" s="14" customFormat="1">
-      <c r="A99" s="73" t="s">
+      <c r="A99" s="71" t="s">
         <v>444</v>
       </c>
       <c r="B99" s="11" t="s">
@@ -9156,7 +9148,7 @@
       <c r="F99" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="G99" s="62" t="s">
+      <c r="G99" s="60" t="s">
         <v>82</v>
       </c>
       <c r="H99" s="23" t="s">
@@ -9165,33 +9157,33 @@
       <c r="I99" s="14">
         <v>0.379</v>
       </c>
-      <c r="J99" s="52">
+      <c r="J99" s="50">
         <v>-6.9569999999999999</v>
       </c>
-      <c r="K99" s="52">
+      <c r="K99" s="50">
         <v>-2.0155334705947299</v>
       </c>
-      <c r="P99" s="52">
+      <c r="P99" s="50">
         <v>5.5389999999999997</v>
       </c>
-      <c r="U99" s="52">
+      <c r="U99" s="50">
         <v>14.304133448972699</v>
       </c>
       <c r="V99" s="14">
         <v>8.8979999999999997</v>
       </c>
-      <c r="X99" s="33" t="s">
+      <c r="X99" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="Z99" s="33" t="s">
+      <c r="Z99" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="AD99" s="56">
+      <c r="AD99" s="54">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="100" spans="1:30">
-      <c r="A100" s="74" t="s">
+      <c r="A100" s="72" t="s">
         <v>106</v>
       </c>
       <c r="B100" s="6" t="s">
@@ -9209,7 +9201,7 @@
       <c r="F100" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G100" s="74" t="s">
+      <c r="G100" s="72" t="s">
         <v>106</v>
       </c>
       <c r="H100" s="12" t="s">
@@ -9220,7 +9212,7 @@
       </c>
     </row>
     <row r="101" spans="1:30">
-      <c r="A101" s="74" t="s">
+      <c r="A101" s="72" t="s">
         <v>107</v>
       </c>
       <c r="B101" s="6" t="s">
@@ -9238,7 +9230,7 @@
       <c r="F101" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G101" s="74" t="s">
+      <c r="G101" s="72" t="s">
         <v>107</v>
       </c>
       <c r="H101" s="12" t="s">
@@ -9249,7 +9241,7 @@
       </c>
     </row>
     <row r="102" spans="1:30">
-      <c r="A102" s="74" t="s">
+      <c r="A102" s="72" t="s">
         <v>108</v>
       </c>
       <c r="B102" s="6" t="s">
@@ -9267,7 +9259,7 @@
       <c r="F102" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G102" s="74" t="s">
+      <c r="G102" s="72" t="s">
         <v>108</v>
       </c>
       <c r="H102" s="12" t="s">
@@ -9278,7 +9270,7 @@
       </c>
     </row>
     <row r="103" spans="1:30">
-      <c r="A103" s="74" t="s">
+      <c r="A103" s="72" t="s">
         <v>109</v>
       </c>
       <c r="B103" s="6" t="s">
@@ -9296,7 +9288,7 @@
       <c r="F103" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G103" s="74" t="s">
+      <c r="G103" s="72" t="s">
         <v>109</v>
       </c>
       <c r="H103" s="12" t="s">
@@ -9307,7 +9299,7 @@
       </c>
     </row>
     <row r="104" spans="1:30">
-      <c r="A104" s="74" t="s">
+      <c r="A104" s="72" t="s">
         <v>110</v>
       </c>
       <c r="B104" s="6" t="s">
@@ -9325,7 +9317,7 @@
       <c r="F104" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G104" s="74" t="s">
+      <c r="G104" s="72" t="s">
         <v>110</v>
       </c>
       <c r="H104" s="12" t="s">
@@ -9336,7 +9328,7 @@
       </c>
     </row>
     <row r="105" spans="1:30">
-      <c r="A105" s="74" t="s">
+      <c r="A105" s="72" t="s">
         <v>111</v>
       </c>
       <c r="B105" s="6" t="s">
@@ -9354,7 +9346,7 @@
       <c r="F105" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G105" s="74" t="s">
+      <c r="G105" s="72" t="s">
         <v>111</v>
       </c>
       <c r="H105" s="12" t="s">
@@ -9365,7 +9357,7 @@
       </c>
     </row>
     <row r="106" spans="1:30">
-      <c r="A106" s="74" t="s">
+      <c r="A106" s="72" t="s">
         <v>112</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -9383,7 +9375,7 @@
       <c r="F106" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G106" s="74" t="s">
+      <c r="G106" s="72" t="s">
         <v>112</v>
       </c>
       <c r="H106" s="12" t="s">
@@ -9394,7 +9386,7 @@
       </c>
     </row>
     <row r="107" spans="1:30">
-      <c r="A107" s="74" t="s">
+      <c r="A107" s="72" t="s">
         <v>113</v>
       </c>
       <c r="B107" s="6" t="s">
@@ -9412,7 +9404,7 @@
       <c r="F107" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G107" s="74" t="s">
+      <c r="G107" s="72" t="s">
         <v>113</v>
       </c>
       <c r="H107" s="12" t="s">
@@ -9423,7 +9415,7 @@
       </c>
     </row>
     <row r="108" spans="1:30">
-      <c r="A108" s="74" t="s">
+      <c r="A108" s="72" t="s">
         <v>114</v>
       </c>
       <c r="B108" s="6" t="s">
@@ -9441,7 +9433,7 @@
       <c r="F108" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G108" s="74" t="s">
+      <c r="G108" s="72" t="s">
         <v>114</v>
       </c>
       <c r="H108" s="12" t="s">
@@ -9452,7 +9444,7 @@
       </c>
     </row>
     <row r="109" spans="1:30" ht="14" customHeight="1">
-      <c r="A109" s="74" t="s">
+      <c r="A109" s="72" t="s">
         <v>115</v>
       </c>
       <c r="B109" s="6" t="s">
@@ -9470,7 +9462,7 @@
       <c r="F109" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G109" s="74" t="s">
+      <c r="G109" s="72" t="s">
         <v>115</v>
       </c>
       <c r="H109" s="12" t="s">
@@ -9487,7 +9479,7 @@
       <c r="B110" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="C110" s="37" t="s">
+      <c r="C110" s="35" t="s">
         <v>331</v>
       </c>
       <c r="D110" s="10" t="s">
@@ -9508,7 +9500,7 @@
       <c r="I110" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="X110" s="31" t="s">
+      <c r="X110" s="29" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9519,7 +9511,7 @@
       <c r="B111" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C111" s="29" t="s">
+      <c r="C111" s="27" t="s">
         <v>331</v>
       </c>
       <c r="D111" s="6" t="s">
@@ -9540,7 +9532,7 @@
       <c r="I111" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="X111" s="32" t="s">
+      <c r="X111" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9551,7 +9543,7 @@
       <c r="B112" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C112" s="29" t="s">
+      <c r="C112" s="27" t="s">
         <v>331</v>
       </c>
       <c r="D112" s="6" t="s">
@@ -9572,7 +9564,7 @@
       <c r="I112" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="X112" s="32" t="s">
+      <c r="X112" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9583,7 +9575,7 @@
       <c r="B113" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C113" s="29" t="s">
+      <c r="C113" s="27" t="s">
         <v>331</v>
       </c>
       <c r="D113" s="6" t="s">
@@ -9604,7 +9596,7 @@
       <c r="I113" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="X113" s="32" t="s">
+      <c r="X113" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9615,7 +9607,7 @@
       <c r="B114" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C114" s="29" t="s">
+      <c r="C114" s="27" t="s">
         <v>331</v>
       </c>
       <c r="D114" s="6" t="s">
@@ -9636,7 +9628,7 @@
       <c r="I114" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="X114" s="32" t="s">
+      <c r="X114" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9647,7 +9639,7 @@
       <c r="B115" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C115" s="29" t="s">
+      <c r="C115" s="27" t="s">
         <v>331</v>
       </c>
       <c r="D115" s="6" t="s">
@@ -9668,7 +9660,7 @@
       <c r="I115" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="X115" s="32" t="s">
+      <c r="X115" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9679,7 +9671,7 @@
       <c r="B116" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C116" s="29" t="s">
+      <c r="C116" s="27" t="s">
         <v>331</v>
       </c>
       <c r="D116" s="6" t="s">
@@ -9700,7 +9692,7 @@
       <c r="I116" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="X116" s="32" t="s">
+      <c r="X116" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9711,7 +9703,7 @@
       <c r="B117" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C117" s="29" t="s">
+      <c r="C117" s="27" t="s">
         <v>331</v>
       </c>
       <c r="D117" s="6" t="s">
@@ -9732,7 +9724,7 @@
       <c r="I117" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="X117" s="32" t="s">
+      <c r="X117" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9743,7 +9735,7 @@
       <c r="B118" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C118" s="29" t="s">
+      <c r="C118" s="27" t="s">
         <v>331</v>
       </c>
       <c r="D118" s="6" t="s">
@@ -9764,7 +9756,7 @@
       <c r="I118" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="X118" s="32" t="s">
+      <c r="X118" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9775,7 +9767,7 @@
       <c r="B119" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="C119" s="29" t="s">
+      <c r="C119" s="27" t="s">
         <v>332</v>
       </c>
       <c r="D119" s="6" t="s">
@@ -9796,7 +9788,7 @@
       <c r="I119" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="X119" s="32" t="s">
+      <c r="X119" s="30" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9807,7 +9799,7 @@
       <c r="B120" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C120" s="40" t="s">
+      <c r="C120" s="38" t="s">
         <v>332</v>
       </c>
       <c r="D120" s="11" t="s">
@@ -9828,12 +9820,12 @@
       <c r="I120" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="X120" s="33" t="s">
+      <c r="X120" s="31" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="121" spans="1:24" s="13" customFormat="1">
-      <c r="A121" s="75" t="s">
+      <c r="A121" s="73" t="s">
         <v>129</v>
       </c>
       <c r="B121" s="10" t="s">
@@ -9859,7 +9851,7 @@
       </c>
     </row>
     <row r="122" spans="1:24">
-      <c r="A122" s="76" t="s">
+      <c r="A122" s="74" t="s">
         <v>130</v>
       </c>
       <c r="B122" s="10" t="s">
@@ -9885,7 +9877,7 @@
       </c>
     </row>
     <row r="123" spans="1:24">
-      <c r="A123" s="76" t="s">
+      <c r="A123" s="74" t="s">
         <v>131</v>
       </c>
       <c r="B123" s="10" t="s">
@@ -9911,7 +9903,7 @@
       </c>
     </row>
     <row r="124" spans="1:24">
-      <c r="A124" s="76" t="s">
+      <c r="A124" s="74" t="s">
         <v>132</v>
       </c>
       <c r="B124" s="10" t="s">
@@ -9937,7 +9929,7 @@
       </c>
     </row>
     <row r="125" spans="1:24">
-      <c r="A125" s="76" t="s">
+      <c r="A125" s="74" t="s">
         <v>133</v>
       </c>
       <c r="B125" s="10" t="s">
@@ -9963,7 +9955,7 @@
       </c>
     </row>
     <row r="126" spans="1:24">
-      <c r="A126" s="76" t="s">
+      <c r="A126" s="74" t="s">
         <v>134</v>
       </c>
       <c r="B126" s="10" t="s">
@@ -9989,7 +9981,7 @@
       </c>
     </row>
     <row r="127" spans="1:24">
-      <c r="A127" s="76" t="s">
+      <c r="A127" s="74" t="s">
         <v>135</v>
       </c>
       <c r="B127" s="10" t="s">
@@ -10015,7 +10007,7 @@
       </c>
     </row>
     <row r="128" spans="1:24">
-      <c r="A128" s="76" t="s">
+      <c r="A128" s="74" t="s">
         <v>136</v>
       </c>
       <c r="B128" s="10" t="s">
@@ -10041,7 +10033,7 @@
       </c>
     </row>
     <row r="129" spans="1:9">
-      <c r="A129" s="76" t="s">
+      <c r="A129" s="74" t="s">
         <v>137</v>
       </c>
       <c r="B129" s="10" t="s">
@@ -10067,7 +10059,7 @@
       </c>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="76" t="s">
+      <c r="A130" s="74" t="s">
         <v>138</v>
       </c>
       <c r="B130" s="10" t="s">
@@ -10093,7 +10085,7 @@
       </c>
     </row>
     <row r="131" spans="1:9">
-      <c r="A131" s="76" t="s">
+      <c r="A131" s="74" t="s">
         <v>139</v>
       </c>
       <c r="B131" s="10" t="s">
@@ -10119,7 +10111,7 @@
       </c>
     </row>
     <row r="132" spans="1:9">
-      <c r="A132" s="76" t="s">
+      <c r="A132" s="74" t="s">
         <v>140</v>
       </c>
       <c r="B132" s="10" t="s">
@@ -10145,7 +10137,7 @@
       </c>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="76" t="s">
+      <c r="A133" s="74" t="s">
         <v>141</v>
       </c>
       <c r="B133" s="10" t="s">
@@ -10171,7 +10163,7 @@
       </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="76" t="s">
+      <c r="A134" s="74" t="s">
         <v>142</v>
       </c>
       <c r="B134" s="10" t="s">
@@ -10197,7 +10189,7 @@
       </c>
     </row>
     <row r="135" spans="1:9">
-      <c r="A135" s="76" t="s">
+      <c r="A135" s="74" t="s">
         <v>143</v>
       </c>
       <c r="B135" s="10" t="s">
@@ -10223,7 +10215,7 @@
       </c>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="76" t="s">
+      <c r="A136" s="74" t="s">
         <v>144</v>
       </c>
       <c r="B136" s="10" t="s">
@@ -10249,7 +10241,7 @@
       </c>
     </row>
     <row r="137" spans="1:9">
-      <c r="A137" s="76" t="s">
+      <c r="A137" s="74" t="s">
         <v>145</v>
       </c>
       <c r="B137" s="10" t="s">
@@ -10275,7 +10267,7 @@
       </c>
     </row>
     <row r="138" spans="1:9">
-      <c r="A138" s="76" t="s">
+      <c r="A138" s="74" t="s">
         <v>146</v>
       </c>
       <c r="B138" s="10" t="s">
@@ -10301,7 +10293,7 @@
       </c>
     </row>
     <row r="139" spans="1:9">
-      <c r="A139" s="76" t="s">
+      <c r="A139" s="74" t="s">
         <v>147</v>
       </c>
       <c r="B139" s="10" t="s">
@@ -10327,7 +10319,7 @@
       </c>
     </row>
     <row r="140" spans="1:9">
-      <c r="A140" s="76" t="s">
+      <c r="A140" s="74" t="s">
         <v>148</v>
       </c>
       <c r="B140" s="10" t="s">
@@ -10353,7 +10345,7 @@
       </c>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="76" t="s">
+      <c r="A141" s="74" t="s">
         <v>149</v>
       </c>
       <c r="B141" s="10" t="s">
@@ -10379,7 +10371,7 @@
       </c>
     </row>
     <row r="142" spans="1:9">
-      <c r="A142" s="76" t="s">
+      <c r="A142" s="74" t="s">
         <v>150</v>
       </c>
       <c r="B142" s="10" t="s">
@@ -10405,7 +10397,7 @@
       </c>
     </row>
     <row r="143" spans="1:9">
-      <c r="A143" s="76" t="s">
+      <c r="A143" s="74" t="s">
         <v>151</v>
       </c>
       <c r="B143" s="10" t="s">
@@ -10431,7 +10423,7 @@
       </c>
     </row>
     <row r="144" spans="1:9">
-      <c r="A144" s="76" t="s">
+      <c r="A144" s="74" t="s">
         <v>152</v>
       </c>
       <c r="B144" s="10" t="s">
@@ -10457,7 +10449,7 @@
       </c>
     </row>
     <row r="145" spans="1:25">
-      <c r="A145" s="76" t="s">
+      <c r="A145" s="74" t="s">
         <v>153</v>
       </c>
       <c r="B145" s="10" t="s">
@@ -10483,7 +10475,7 @@
       </c>
     </row>
     <row r="146" spans="1:25">
-      <c r="A146" s="76" t="s">
+      <c r="A146" s="74" t="s">
         <v>154</v>
       </c>
       <c r="B146" s="10" t="s">
@@ -10509,7 +10501,7 @@
       </c>
     </row>
     <row r="147" spans="1:25">
-      <c r="A147" s="76" t="s">
+      <c r="A147" s="74" t="s">
         <v>155</v>
       </c>
       <c r="B147" s="10" t="s">
@@ -10535,7 +10527,7 @@
       </c>
     </row>
     <row r="148" spans="1:25">
-      <c r="A148" s="76" t="s">
+      <c r="A148" s="74" t="s">
         <v>156</v>
       </c>
       <c r="B148" s="10" t="s">
@@ -10561,7 +10553,7 @@
       </c>
     </row>
     <row r="149" spans="1:25">
-      <c r="A149" s="76" t="s">
+      <c r="A149" s="74" t="s">
         <v>157</v>
       </c>
       <c r="B149" s="10" t="s">
@@ -10587,7 +10579,7 @@
       </c>
     </row>
     <row r="150" spans="1:25" s="14" customFormat="1">
-      <c r="A150" s="77" t="s">
+      <c r="A150" s="75" t="s">
         <v>158</v>
       </c>
       <c r="B150" s="10" t="s">
@@ -10631,7 +10623,7 @@
       <c r="F151" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="G151" s="60" t="s">
+      <c r="G151" s="58" t="s">
         <v>385</v>
       </c>
       <c r="I151" s="13">
@@ -10640,7 +10632,7 @@
       <c r="W151" s="13">
         <v>7.5</v>
       </c>
-      <c r="X151" s="32" t="s">
+      <c r="X151" s="30" t="s">
         <v>93</v>
       </c>
       <c r="Y151" s="13">
@@ -10666,7 +10658,7 @@
       <c r="F152" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G152" s="61" t="s">
+      <c r="G152" s="59" t="s">
         <v>385</v>
       </c>
       <c r="I152" s="5">
@@ -10675,7 +10667,7 @@
       <c r="W152" s="13">
         <v>7.5</v>
       </c>
-      <c r="X152" s="32" t="s">
+      <c r="X152" s="30" t="s">
         <v>93</v>
       </c>
       <c r="Y152" s="5">
@@ -10701,7 +10693,7 @@
       <c r="F153" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G153" s="61" t="s">
+      <c r="G153" s="59" t="s">
         <v>384</v>
       </c>
       <c r="I153" s="5">
@@ -10710,7 +10702,7 @@
       <c r="W153" s="13">
         <v>7.5</v>
       </c>
-      <c r="X153" s="32" t="s">
+      <c r="X153" s="30" t="s">
         <v>93</v>
       </c>
       <c r="Y153" s="5">
@@ -10736,7 +10728,7 @@
       <c r="F154" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G154" s="61" t="s">
+      <c r="G154" s="59" t="s">
         <v>384</v>
       </c>
       <c r="I154" s="5">
@@ -10745,7 +10737,7 @@
       <c r="W154" s="13">
         <v>7.5</v>
       </c>
-      <c r="X154" s="32" t="s">
+      <c r="X154" s="30" t="s">
         <v>93</v>
       </c>
       <c r="Y154" s="5">
@@ -10771,7 +10763,7 @@
       <c r="F155" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G155" s="61" t="s">
+      <c r="G155" s="59" t="s">
         <v>382</v>
       </c>
       <c r="I155" s="5">
@@ -10780,7 +10772,7 @@
       <c r="W155" s="13">
         <v>7.5</v>
       </c>
-      <c r="X155" s="32" t="s">
+      <c r="X155" s="30" t="s">
         <v>93</v>
       </c>
       <c r="Y155" s="5">
@@ -10806,7 +10798,7 @@
       <c r="F156" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G156" s="61" t="s">
+      <c r="G156" s="59" t="s">
         <v>382</v>
       </c>
       <c r="I156" s="5">
@@ -10815,7 +10807,7 @@
       <c r="W156" s="13">
         <v>7.5</v>
       </c>
-      <c r="X156" s="32" t="s">
+      <c r="X156" s="30" t="s">
         <v>93</v>
       </c>
       <c r="Y156" s="5">
@@ -10841,7 +10833,7 @@
       <c r="F157" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G157" s="61" t="s">
+      <c r="G157" s="59" t="s">
         <v>383</v>
       </c>
       <c r="I157" s="5">
@@ -10850,7 +10842,7 @@
       <c r="W157" s="13">
         <v>7.5</v>
       </c>
-      <c r="X157" s="32" t="s">
+      <c r="X157" s="30" t="s">
         <v>93</v>
       </c>
       <c r="Y157" s="5">
@@ -10876,7 +10868,7 @@
       <c r="F158" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G158" s="61" t="s">
+      <c r="G158" s="59" t="s">
         <v>383</v>
       </c>
       <c r="I158" s="5">
@@ -10885,7 +10877,7 @@
       <c r="W158" s="13">
         <v>7.5</v>
       </c>
-      <c r="X158" s="32" t="s">
+      <c r="X158" s="30" t="s">
         <v>93</v>
       </c>
       <c r="Y158" s="5">
@@ -10899,10 +10891,10 @@
       <c r="B159" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="C159" s="88" t="s">
+      <c r="C159" s="86" t="s">
         <v>307</v>
       </c>
-      <c r="D159" s="38" t="s">
+      <c r="D159" s="36" t="s">
         <v>169</v>
       </c>
       <c r="E159" s="10" t="s">
@@ -10911,13 +10903,13 @@
       <c r="F159" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="G159" s="86" t="s">
+      <c r="G159" s="84" t="s">
         <v>492</v>
       </c>
       <c r="I159" s="13">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="X159" s="31"/>
+      <c r="X159" s="29"/>
     </row>
     <row r="160" spans="1:25" ht="14" customHeight="1">
       <c r="A160" s="6" t="s">
@@ -10926,10 +10918,10 @@
       <c r="B160" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C160" s="29" t="s">
+      <c r="C160" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D160" s="36" t="s">
+      <c r="D160" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E160" s="6" t="s">
@@ -10938,7 +10930,7 @@
       <c r="F160" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G160" s="87" t="s">
+      <c r="G160" s="85" t="s">
         <v>492</v>
       </c>
       <c r="I160" s="5">
@@ -10952,10 +10944,10 @@
       <c r="B161" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C161" s="29" t="s">
+      <c r="C161" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D161" s="36" t="s">
+      <c r="D161" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E161" s="6" t="s">
@@ -10964,7 +10956,7 @@
       <c r="F161" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G161" s="87" t="s">
+      <c r="G161" s="85" t="s">
         <v>492</v>
       </c>
       <c r="I161" s="5">
@@ -10978,10 +10970,10 @@
       <c r="B162" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C162" s="29" t="s">
+      <c r="C162" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D162" s="36" t="s">
+      <c r="D162" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E162" s="6" t="s">
@@ -10990,7 +10982,7 @@
       <c r="F162" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G162" s="87" t="s">
+      <c r="G162" s="85" t="s">
         <v>492</v>
       </c>
       <c r="I162" s="5">
@@ -11004,10 +10996,10 @@
       <c r="B163" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C163" s="29" t="s">
+      <c r="C163" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D163" s="36" t="s">
+      <c r="D163" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E163" s="6" t="s">
@@ -11030,10 +11022,10 @@
       <c r="B164" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C164" s="29" t="s">
+      <c r="C164" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D164" s="36" t="s">
+      <c r="D164" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E164" s="6" t="s">
@@ -11056,10 +11048,10 @@
       <c r="B165" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C165" s="29" t="s">
+      <c r="C165" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D165" s="36" t="s">
+      <c r="D165" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E165" s="6" t="s">
@@ -11082,10 +11074,10 @@
       <c r="B166" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C166" s="29" t="s">
+      <c r="C166" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D166" s="36" t="s">
+      <c r="D166" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E166" s="6" t="s">
@@ -11108,10 +11100,10 @@
       <c r="B167" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C167" s="29" t="s">
+      <c r="C167" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D167" s="36" t="s">
+      <c r="D167" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E167" s="6" t="s">
@@ -11134,10 +11126,10 @@
       <c r="B168" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C168" s="29" t="s">
+      <c r="C168" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D168" s="36" t="s">
+      <c r="D168" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E168" s="6" t="s">
@@ -11160,10 +11152,10 @@
       <c r="B169" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C169" s="29" t="s">
+      <c r="C169" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D169" s="36" t="s">
+      <c r="D169" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E169" s="6" t="s">
@@ -11186,10 +11178,10 @@
       <c r="B170" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C170" s="29" t="s">
+      <c r="C170" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D170" s="36" t="s">
+      <c r="D170" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E170" s="6" t="s">
@@ -11212,10 +11204,10 @@
       <c r="B171" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C171" s="29" t="s">
+      <c r="C171" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D171" s="36" t="s">
+      <c r="D171" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E171" s="6" t="s">
@@ -11238,10 +11230,10 @@
       <c r="B172" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C172" s="29" t="s">
+      <c r="C172" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D172" s="36" t="s">
+      <c r="D172" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E172" s="6" t="s">
@@ -11264,10 +11256,10 @@
       <c r="B173" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C173" s="29" t="s">
+      <c r="C173" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D173" s="36" t="s">
+      <c r="D173" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E173" s="6" t="s">
@@ -11290,10 +11282,10 @@
       <c r="B174" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C174" s="29" t="s">
+      <c r="C174" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D174" s="36" t="s">
+      <c r="D174" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E174" s="6" t="s">
@@ -11316,10 +11308,10 @@
       <c r="B175" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C175" s="29" t="s">
+      <c r="C175" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D175" s="36" t="s">
+      <c r="D175" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E175" s="6" t="s">
@@ -11342,10 +11334,10 @@
       <c r="B176" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C176" s="29" t="s">
+      <c r="C176" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D176" s="36" t="s">
+      <c r="D176" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E176" s="6" t="s">
@@ -11368,10 +11360,10 @@
       <c r="B177" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C177" s="29" t="s">
+      <c r="C177" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D177" s="36" t="s">
+      <c r="D177" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E177" s="6" t="s">
@@ -11391,10 +11383,10 @@
       <c r="B178" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C178" s="29" t="s">
+      <c r="C178" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D178" s="36" t="s">
+      <c r="D178" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E178" s="6" t="s">
@@ -11414,10 +11406,10 @@
       <c r="B179" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C179" s="29" t="s">
+      <c r="C179" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D179" s="36" t="s">
+      <c r="D179" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E179" s="6" t="s">
@@ -11437,10 +11429,10 @@
       <c r="B180" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C180" s="29" t="s">
+      <c r="C180" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D180" s="36" t="s">
+      <c r="D180" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E180" s="6" t="s">
@@ -11460,10 +11452,10 @@
       <c r="B181" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C181" s="29" t="s">
+      <c r="C181" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D181" s="36" t="s">
+      <c r="D181" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E181" s="6" t="s">
@@ -11483,10 +11475,10 @@
       <c r="B182" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C182" s="29" t="s">
+      <c r="C182" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D182" s="36" t="s">
+      <c r="D182" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E182" s="6" t="s">
@@ -11506,10 +11498,10 @@
       <c r="B183" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C183" s="29" t="s">
+      <c r="C183" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D183" s="36" t="s">
+      <c r="D183" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E183" s="6" t="s">
@@ -11529,10 +11521,10 @@
       <c r="B184" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C184" s="29" t="s">
+      <c r="C184" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D184" s="36" t="s">
+      <c r="D184" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E184" s="6" t="s">
@@ -11552,10 +11544,10 @@
       <c r="B185" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C185" s="29" t="s">
+      <c r="C185" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D185" s="36" t="s">
+      <c r="D185" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E185" s="6" t="s">
@@ -11575,10 +11567,10 @@
       <c r="B186" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C186" s="29" t="s">
+      <c r="C186" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D186" s="36" t="s">
+      <c r="D186" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E186" s="6" t="s">
@@ -11598,10 +11590,10 @@
       <c r="B187" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C187" s="29" t="s">
+      <c r="C187" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D187" s="36" t="s">
+      <c r="D187" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E187" s="6" t="s">
@@ -11621,10 +11613,10 @@
       <c r="B188" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C188" s="29" t="s">
+      <c r="C188" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D188" s="36" t="s">
+      <c r="D188" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E188" s="6" t="s">
@@ -11644,10 +11636,10 @@
       <c r="B189" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C189" s="29" t="s">
+      <c r="C189" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="D189" s="36" t="s">
+      <c r="D189" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E189" s="6" t="s">
@@ -11667,10 +11659,10 @@
       <c r="B190" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="C190" s="40" t="s">
+      <c r="C190" s="38" t="s">
         <v>307</v>
       </c>
-      <c r="D190" s="41" t="s">
+      <c r="D190" s="39" t="s">
         <v>169</v>
       </c>
       <c r="E190" s="11" t="s">
@@ -11684,16 +11676,16 @@
       </c>
     </row>
     <row r="191" spans="1:9" s="13" customFormat="1">
-      <c r="A191" s="78" t="s">
+      <c r="A191" s="76" t="s">
         <v>210</v>
       </c>
       <c r="B191" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="C191" s="37" t="s">
+      <c r="C191" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="D191" s="38" t="s">
+      <c r="D191" s="36" t="s">
         <v>169</v>
       </c>
       <c r="E191" s="10" t="s">
@@ -11702,7 +11694,7 @@
       <c r="F191" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="I191" s="39">
+      <c r="I191" s="37">
         <v>0.255</v>
       </c>
     </row>
@@ -11713,10 +11705,10 @@
       <c r="B192" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C192" s="29" t="s">
+      <c r="C192" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D192" s="36" t="s">
+      <c r="D192" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E192" s="6" t="s">
@@ -11736,10 +11728,10 @@
       <c r="B193" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C193" s="29" t="s">
+      <c r="C193" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D193" s="36" t="s">
+      <c r="D193" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E193" s="6" t="s">
@@ -11759,10 +11751,10 @@
       <c r="B194" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C194" s="29" t="s">
+      <c r="C194" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D194" s="36" t="s">
+      <c r="D194" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E194" s="6" t="s">
@@ -11782,10 +11774,10 @@
       <c r="B195" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C195" s="29" t="s">
+      <c r="C195" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D195" s="36" t="s">
+      <c r="D195" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E195" s="6" t="s">
@@ -11805,10 +11797,10 @@
       <c r="B196" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C196" s="29" t="s">
+      <c r="C196" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D196" s="36" t="s">
+      <c r="D196" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E196" s="6" t="s">
@@ -11828,10 +11820,10 @@
       <c r="B197" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C197" s="29" t="s">
+      <c r="C197" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D197" s="36" t="s">
+      <c r="D197" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E197" s="6" t="s">
@@ -11851,10 +11843,10 @@
       <c r="B198" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C198" s="29" t="s">
+      <c r="C198" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D198" s="36" t="s">
+      <c r="D198" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E198" s="6" t="s">
@@ -11874,10 +11866,10 @@
       <c r="B199" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C199" s="29" t="s">
+      <c r="C199" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D199" s="36" t="s">
+      <c r="D199" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E199" s="6" t="s">
@@ -11897,10 +11889,10 @@
       <c r="B200" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C200" s="29" t="s">
+      <c r="C200" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D200" s="36" t="s">
+      <c r="D200" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E200" s="6" t="s">
@@ -11920,10 +11912,10 @@
       <c r="B201" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C201" s="29" t="s">
+      <c r="C201" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D201" s="36" t="s">
+      <c r="D201" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E201" s="6" t="s">
@@ -11943,10 +11935,10 @@
       <c r="B202" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C202" s="29" t="s">
+      <c r="C202" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D202" s="36" t="s">
+      <c r="D202" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E202" s="6" t="s">
@@ -11966,10 +11958,10 @@
       <c r="B203" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C203" s="29" t="s">
+      <c r="C203" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D203" s="36" t="s">
+      <c r="D203" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E203" s="6" t="s">
@@ -11989,10 +11981,10 @@
       <c r="B204" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C204" s="29" t="s">
+      <c r="C204" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D204" s="36" t="s">
+      <c r="D204" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E204" s="6" t="s">
@@ -12001,7 +11993,7 @@
       <c r="F204" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G204" s="61" t="s">
+      <c r="G204" s="59" t="s">
         <v>223</v>
       </c>
       <c r="I204" s="17">
@@ -12015,10 +12007,10 @@
       <c r="B205" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C205" s="29" t="s">
+      <c r="C205" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D205" s="36" t="s">
+      <c r="D205" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E205" s="6" t="s">
@@ -12027,7 +12019,7 @@
       <c r="F205" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G205" s="61" t="s">
+      <c r="G205" s="59" t="s">
         <v>381</v>
       </c>
     </row>
@@ -12038,10 +12030,10 @@
       <c r="B206" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C206" s="29" t="s">
+      <c r="C206" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D206" s="36" t="s">
+      <c r="D206" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E206" s="6" t="s">
@@ -12050,7 +12042,7 @@
       <c r="F206" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G206" s="61" t="s">
+      <c r="G206" s="59" t="s">
         <v>381</v>
       </c>
     </row>
@@ -12061,10 +12053,10 @@
       <c r="B207" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C207" s="29" t="s">
+      <c r="C207" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D207" s="36" t="s">
+      <c r="D207" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E207" s="6" t="s">
@@ -12073,7 +12065,7 @@
       <c r="F207" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G207" s="61" t="s">
+      <c r="G207" s="59" t="s">
         <v>381</v>
       </c>
     </row>
@@ -12084,10 +12076,10 @@
       <c r="B208" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C208" s="29" t="s">
+      <c r="C208" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D208" s="36" t="s">
+      <c r="D208" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E208" s="6" t="s">
@@ -12096,7 +12088,7 @@
       <c r="F208" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G208" s="61" t="s">
+      <c r="G208" s="59" t="s">
         <v>380</v>
       </c>
     </row>
@@ -12107,10 +12099,10 @@
       <c r="B209" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C209" s="29" t="s">
+      <c r="C209" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D209" s="36" t="s">
+      <c r="D209" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E209" s="6" t="s">
@@ -12119,7 +12111,7 @@
       <c r="F209" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G209" s="61" t="s">
+      <c r="G209" s="59" t="s">
         <v>380</v>
       </c>
     </row>
@@ -12130,10 +12122,10 @@
       <c r="B210" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C210" s="29" t="s">
+      <c r="C210" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D210" s="36" t="s">
+      <c r="D210" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E210" s="6" t="s">
@@ -12142,7 +12134,7 @@
       <c r="F210" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G210" s="61" t="s">
+      <c r="G210" s="59" t="s">
         <v>380</v>
       </c>
     </row>
@@ -12153,10 +12145,10 @@
       <c r="B211" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C211" s="29" t="s">
+      <c r="C211" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="D211" s="36" t="s">
+      <c r="D211" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E211" s="6" t="s">
@@ -12165,21 +12157,21 @@
       <c r="F211" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G211" s="61" t="s">
+      <c r="G211" s="59" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="212" spans="1:7" s="14" customFormat="1">
-      <c r="A212" s="79" t="s">
+      <c r="A212" s="77" t="s">
         <v>231</v>
       </c>
       <c r="B212" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="C212" s="40" t="s">
+      <c r="C212" s="38" t="s">
         <v>306</v>
       </c>
-      <c r="D212" s="41" t="s">
+      <c r="D212" s="39" t="s">
         <v>169</v>
       </c>
       <c r="E212" s="11" t="s">
@@ -12188,21 +12180,21 @@
       <c r="F212" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G212" s="62" t="s">
+      <c r="G212" s="60" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="213" spans="1:7">
-      <c r="A213" s="74" t="s">
+      <c r="A213" s="72" t="s">
         <v>232</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C213" s="29" t="s">
+      <c r="C213" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D213" s="36" t="s">
+      <c r="D213" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E213" s="6" t="s">
@@ -12210,16 +12202,16 @@
       </c>
     </row>
     <row r="214" spans="1:7">
-      <c r="A214" s="74" t="s">
+      <c r="A214" s="72" t="s">
         <v>233</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C214" s="29" t="s">
+      <c r="C214" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D214" s="36" t="s">
+      <c r="D214" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E214" s="6" t="s">
@@ -12227,16 +12219,16 @@
       </c>
     </row>
     <row r="215" spans="1:7">
-      <c r="A215" s="74" t="s">
+      <c r="A215" s="72" t="s">
         <v>234</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C215" s="29" t="s">
+      <c r="C215" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D215" s="36" t="s">
+      <c r="D215" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E215" s="6" t="s">
@@ -12244,16 +12236,16 @@
       </c>
     </row>
     <row r="216" spans="1:7">
-      <c r="A216" s="74" t="s">
+      <c r="A216" s="72" t="s">
         <v>235</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C216" s="29" t="s">
+      <c r="C216" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D216" s="36" t="s">
+      <c r="D216" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E216" s="6" t="s">
@@ -12261,16 +12253,16 @@
       </c>
     </row>
     <row r="217" spans="1:7">
-      <c r="A217" s="74" t="s">
+      <c r="A217" s="72" t="s">
         <v>236</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C217" s="29" t="s">
+      <c r="C217" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D217" s="36" t="s">
+      <c r="D217" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E217" s="6" t="s">
@@ -12278,16 +12270,16 @@
       </c>
     </row>
     <row r="218" spans="1:7">
-      <c r="A218" s="74" t="s">
+      <c r="A218" s="72" t="s">
         <v>237</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C218" s="29" t="s">
+      <c r="C218" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D218" s="36" t="s">
+      <c r="D218" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E218" s="6" t="s">
@@ -12295,16 +12287,16 @@
       </c>
     </row>
     <row r="219" spans="1:7">
-      <c r="A219" s="74" t="s">
+      <c r="A219" s="72" t="s">
         <v>238</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C219" s="29" t="s">
+      <c r="C219" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D219" s="36" t="s">
+      <c r="D219" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E219" s="6" t="s">
@@ -12312,16 +12304,16 @@
       </c>
     </row>
     <row r="220" spans="1:7">
-      <c r="A220" s="74" t="s">
+      <c r="A220" s="72" t="s">
         <v>239</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C220" s="29" t="s">
+      <c r="C220" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D220" s="36" t="s">
+      <c r="D220" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E220" s="6" t="s">
@@ -12329,16 +12321,16 @@
       </c>
     </row>
     <row r="221" spans="1:7">
-      <c r="A221" s="74" t="s">
+      <c r="A221" s="72" t="s">
         <v>240</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C221" s="29" t="s">
+      <c r="C221" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D221" s="36" t="s">
+      <c r="D221" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E221" s="6" t="s">
@@ -12346,16 +12338,16 @@
       </c>
     </row>
     <row r="222" spans="1:7">
-      <c r="A222" s="74" t="s">
+      <c r="A222" s="72" t="s">
         <v>241</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C222" s="29" t="s">
+      <c r="C222" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D222" s="36" t="s">
+      <c r="D222" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E222" s="6" t="s">
@@ -12363,16 +12355,16 @@
       </c>
     </row>
     <row r="223" spans="1:7">
-      <c r="A223" s="74" t="s">
+      <c r="A223" s="72" t="s">
         <v>242</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C223" s="29" t="s">
+      <c r="C223" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D223" s="36" t="s">
+      <c r="D223" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E223" s="6" t="s">
@@ -12380,16 +12372,16 @@
       </c>
     </row>
     <row r="224" spans="1:7">
-      <c r="A224" s="74" t="s">
+      <c r="A224" s="72" t="s">
         <v>243</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C224" s="29" t="s">
+      <c r="C224" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D224" s="36" t="s">
+      <c r="D224" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E224" s="6" t="s">
@@ -12397,16 +12389,16 @@
       </c>
     </row>
     <row r="225" spans="1:14">
-      <c r="A225" s="74" t="s">
+      <c r="A225" s="72" t="s">
         <v>244</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C225" s="29" t="s">
+      <c r="C225" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D225" s="36" t="s">
+      <c r="D225" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E225" s="6" t="s">
@@ -12414,16 +12406,16 @@
       </c>
     </row>
     <row r="226" spans="1:14">
-      <c r="A226" s="74" t="s">
+      <c r="A226" s="72" t="s">
         <v>245</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C226" s="29" t="s">
+      <c r="C226" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D226" s="36" t="s">
+      <c r="D226" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E226" s="6" t="s">
@@ -12431,16 +12423,16 @@
       </c>
     </row>
     <row r="227" spans="1:14">
-      <c r="A227" s="74" t="s">
+      <c r="A227" s="72" t="s">
         <v>246</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C227" s="29" t="s">
+      <c r="C227" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D227" s="36" t="s">
+      <c r="D227" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E227" s="6" t="s">
@@ -12448,16 +12440,16 @@
       </c>
     </row>
     <row r="228" spans="1:14">
-      <c r="A228" s="74" t="s">
+      <c r="A228" s="72" t="s">
         <v>247</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C228" s="29" t="s">
+      <c r="C228" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D228" s="36" t="s">
+      <c r="D228" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E228" s="6" t="s">
@@ -12465,16 +12457,16 @@
       </c>
     </row>
     <row r="229" spans="1:14">
-      <c r="A229" s="74" t="s">
+      <c r="A229" s="72" t="s">
         <v>248</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C229" s="29" t="s">
+      <c r="C229" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D229" s="36" t="s">
+      <c r="D229" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E229" s="6" t="s">
@@ -12482,16 +12474,16 @@
       </c>
     </row>
     <row r="230" spans="1:14">
-      <c r="A230" s="74" t="s">
+      <c r="A230" s="72" t="s">
         <v>249</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C230" s="29" t="s">
+      <c r="C230" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D230" s="36" t="s">
+      <c r="D230" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E230" s="6" t="s">
@@ -12499,16 +12491,16 @@
       </c>
     </row>
     <row r="231" spans="1:14">
-      <c r="A231" s="74" t="s">
+      <c r="A231" s="72" t="s">
         <v>250</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C231" s="29" t="s">
+      <c r="C231" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D231" s="36" t="s">
+      <c r="D231" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E231" s="6" t="s">
@@ -12516,16 +12508,16 @@
       </c>
     </row>
     <row r="232" spans="1:14">
-      <c r="A232" s="74" t="s">
+      <c r="A232" s="72" t="s">
         <v>251</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C232" s="29" t="s">
+      <c r="C232" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D232" s="36" t="s">
+      <c r="D232" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E232" s="6" t="s">
@@ -12533,16 +12525,16 @@
       </c>
     </row>
     <row r="233" spans="1:14">
-      <c r="A233" s="74" t="s">
+      <c r="A233" s="72" t="s">
         <v>252</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C233" s="29" t="s">
+      <c r="C233" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D233" s="36" t="s">
+      <c r="D233" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E233" s="6" t="s">
@@ -12550,16 +12542,16 @@
       </c>
     </row>
     <row r="234" spans="1:14">
-      <c r="A234" s="74" t="s">
+      <c r="A234" s="72" t="s">
         <v>253</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C234" s="29" t="s">
+      <c r="C234" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D234" s="36" t="s">
+      <c r="D234" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E234" s="6" t="s">
@@ -12567,16 +12559,16 @@
       </c>
     </row>
     <row r="235" spans="1:14">
-      <c r="A235" s="74" t="s">
+      <c r="A235" s="72" t="s">
         <v>254</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C235" s="29" t="s">
+      <c r="C235" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D235" s="36" t="s">
+      <c r="D235" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E235" s="6" t="s">
@@ -12584,16 +12576,16 @@
       </c>
     </row>
     <row r="236" spans="1:14">
-      <c r="A236" s="74" t="s">
+      <c r="A236" s="72" t="s">
         <v>255</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C236" s="29" t="s">
+      <c r="C236" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D236" s="36" t="s">
+      <c r="D236" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E236" s="6" t="s">
@@ -12601,97 +12593,97 @@
       </c>
     </row>
     <row r="237" spans="1:14" ht="18">
-      <c r="A237" s="74" t="s">
+      <c r="A237" s="72" t="s">
         <v>256</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C237" s="29" t="s">
+      <c r="C237" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D237" s="36" t="s">
+      <c r="D237" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E237" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G237" s="57" t="s">
+      <c r="G237" s="55" t="s">
         <v>445</v>
       </c>
-      <c r="H237" s="57"/>
-      <c r="I237" s="57"/>
-      <c r="J237" s="57"/>
-      <c r="K237" s="57"/>
-      <c r="L237" s="57"/>
-      <c r="M237" s="57"/>
-      <c r="N237" s="57"/>
+      <c r="H237" s="55"/>
+      <c r="I237" s="55"/>
+      <c r="J237" s="55"/>
+      <c r="K237" s="55"/>
+      <c r="L237" s="55"/>
+      <c r="M237" s="55"/>
+      <c r="N237" s="55"/>
     </row>
     <row r="238" spans="1:14" ht="19">
-      <c r="A238" s="74" t="s">
+      <c r="A238" s="72" t="s">
         <v>257</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C238" s="29" t="s">
+      <c r="C238" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D238" s="36" t="s">
+      <c r="D238" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G238" s="57" t="s">
+      <c r="G238" s="55" t="s">
         <v>446</v>
       </c>
-      <c r="H238" s="57"/>
-      <c r="I238" s="57"/>
-      <c r="J238" s="57"/>
-      <c r="K238" s="57"/>
-      <c r="L238" s="57"/>
-      <c r="M238" s="57"/>
-      <c r="N238" s="57"/>
+      <c r="H238" s="55"/>
+      <c r="I238" s="55"/>
+      <c r="J238" s="55"/>
+      <c r="K238" s="55"/>
+      <c r="L238" s="55"/>
+      <c r="M238" s="55"/>
+      <c r="N238" s="55"/>
     </row>
     <row r="239" spans="1:14" ht="18">
-      <c r="A239" s="74" t="s">
+      <c r="A239" s="72" t="s">
         <v>258</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C239" s="29" t="s">
+      <c r="C239" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D239" s="36" t="s">
+      <c r="D239" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E239" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G239" s="57" t="s">
+      <c r="G239" s="55" t="s">
         <v>447</v>
       </c>
-      <c r="H239" s="57"/>
-      <c r="I239" s="57"/>
-      <c r="J239" s="57"/>
-      <c r="K239" s="57"/>
-      <c r="L239" s="57"/>
-      <c r="M239" s="57"/>
-      <c r="N239" s="57"/>
+      <c r="H239" s="55"/>
+      <c r="I239" s="55"/>
+      <c r="J239" s="55"/>
+      <c r="K239" s="55"/>
+      <c r="L239" s="55"/>
+      <c r="M239" s="55"/>
+      <c r="N239" s="55"/>
     </row>
     <row r="240" spans="1:14">
-      <c r="A240" s="74" t="s">
+      <c r="A240" s="72" t="s">
         <v>259</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C240" s="29" t="s">
+      <c r="C240" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D240" s="36" t="s">
+      <c r="D240" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E240" s="6" t="s">
@@ -12699,70 +12691,70 @@
       </c>
     </row>
     <row r="241" spans="1:14" ht="18">
-      <c r="A241" s="74" t="s">
+      <c r="A241" s="72" t="s">
         <v>260</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C241" s="29" t="s">
+      <c r="C241" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D241" s="36" t="s">
+      <c r="D241" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E241" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G241" s="57" t="s">
+      <c r="G241" s="55" t="s">
         <v>448</v>
       </c>
-      <c r="H241" s="57"/>
-      <c r="I241" s="57"/>
-      <c r="J241" s="57"/>
-      <c r="K241" s="57"/>
-      <c r="L241" s="57"/>
-      <c r="M241" s="57"/>
-      <c r="N241" s="57"/>
+      <c r="H241" s="55"/>
+      <c r="I241" s="55"/>
+      <c r="J241" s="55"/>
+      <c r="K241" s="55"/>
+      <c r="L241" s="55"/>
+      <c r="M241" s="55"/>
+      <c r="N241" s="55"/>
     </row>
     <row r="242" spans="1:14" ht="18">
-      <c r="A242" s="74" t="s">
+      <c r="A242" s="72" t="s">
         <v>261</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C242" s="29" t="s">
+      <c r="C242" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D242" s="36" t="s">
+      <c r="D242" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G242" s="57" t="s">
+      <c r="G242" s="55" t="s">
         <v>449</v>
       </c>
-      <c r="H242" s="57"/>
-      <c r="I242" s="57"/>
-      <c r="J242" s="57"/>
-      <c r="K242" s="57"/>
-      <c r="L242" s="57"/>
-      <c r="M242" s="57"/>
-      <c r="N242" s="57"/>
+      <c r="H242" s="55"/>
+      <c r="I242" s="55"/>
+      <c r="J242" s="55"/>
+      <c r="K242" s="55"/>
+      <c r="L242" s="55"/>
+      <c r="M242" s="55"/>
+      <c r="N242" s="55"/>
     </row>
     <row r="243" spans="1:14">
-      <c r="A243" s="74" t="s">
+      <c r="A243" s="72" t="s">
         <v>262</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C243" s="29" t="s">
+      <c r="C243" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D243" s="36" t="s">
+      <c r="D243" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E243" s="6" t="s">
@@ -12770,43 +12762,43 @@
       </c>
     </row>
     <row r="244" spans="1:14" ht="18">
-      <c r="A244" s="74" t="s">
+      <c r="A244" s="72" t="s">
         <v>263</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C244" s="29" t="s">
+      <c r="C244" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D244" s="36" t="s">
+      <c r="D244" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G244" s="58" t="s">
+      <c r="G244" s="56" t="s">
         <v>450</v>
       </c>
-      <c r="H244" s="58"/>
-      <c r="I244" s="58"/>
-      <c r="J244" s="58"/>
-      <c r="K244" s="58"/>
-      <c r="L244" s="58"/>
-      <c r="M244" s="58"/>
-      <c r="N244" s="58"/>
+      <c r="H244" s="56"/>
+      <c r="I244" s="56"/>
+      <c r="J244" s="56"/>
+      <c r="K244" s="56"/>
+      <c r="L244" s="56"/>
+      <c r="M244" s="56"/>
+      <c r="N244" s="56"/>
     </row>
     <row r="245" spans="1:14">
-      <c r="A245" s="74" t="s">
+      <c r="A245" s="72" t="s">
         <v>264</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C245" s="29" t="s">
+      <c r="C245" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D245" s="36" t="s">
+      <c r="D245" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E245" s="6" t="s">
@@ -12814,43 +12806,43 @@
       </c>
     </row>
     <row r="246" spans="1:14" ht="18">
-      <c r="A246" s="74" t="s">
+      <c r="A246" s="72" t="s">
         <v>265</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C246" s="29" t="s">
+      <c r="C246" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D246" s="36" t="s">
+      <c r="D246" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E246" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G246" s="59" t="s">
+      <c r="G246" s="57" t="s">
         <v>451</v>
       </c>
-      <c r="H246" s="59"/>
-      <c r="I246" s="59"/>
-      <c r="J246" s="59"/>
-      <c r="K246" s="59"/>
-      <c r="L246" s="59"/>
-      <c r="M246" s="59"/>
-      <c r="N246" s="59"/>
+      <c r="H246" s="57"/>
+      <c r="I246" s="57"/>
+      <c r="J246" s="57"/>
+      <c r="K246" s="57"/>
+      <c r="L246" s="57"/>
+      <c r="M246" s="57"/>
+      <c r="N246" s="57"/>
     </row>
     <row r="247" spans="1:14">
-      <c r="A247" s="74" t="s">
+      <c r="A247" s="72" t="s">
         <v>266</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C247" s="29" t="s">
+      <c r="C247" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D247" s="36" t="s">
+      <c r="D247" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E247" s="6" t="s">
@@ -12858,43 +12850,43 @@
       </c>
     </row>
     <row r="248" spans="1:14" ht="18">
-      <c r="A248" s="74" t="s">
+      <c r="A248" s="72" t="s">
         <v>267</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C248" s="29" t="s">
+      <c r="C248" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D248" s="36" t="s">
+      <c r="D248" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G248" s="59" t="s">
+      <c r="G248" s="57" t="s">
         <v>452</v>
       </c>
-      <c r="H248" s="59"/>
-      <c r="I248" s="59"/>
-      <c r="J248" s="59"/>
-      <c r="K248" s="59"/>
-      <c r="L248" s="59"/>
-      <c r="M248" s="59"/>
-      <c r="N248" s="59"/>
+      <c r="H248" s="57"/>
+      <c r="I248" s="57"/>
+      <c r="J248" s="57"/>
+      <c r="K248" s="57"/>
+      <c r="L248" s="57"/>
+      <c r="M248" s="57"/>
+      <c r="N248" s="57"/>
     </row>
     <row r="249" spans="1:14">
-      <c r="A249" s="74" t="s">
+      <c r="A249" s="72" t="s">
         <v>268</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C249" s="29" t="s">
+      <c r="C249" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D249" s="36" t="s">
+      <c r="D249" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E249" s="6" t="s">
@@ -12902,43 +12894,43 @@
       </c>
     </row>
     <row r="250" spans="1:14" ht="18">
-      <c r="A250" s="74" t="s">
+      <c r="A250" s="72" t="s">
         <v>269</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C250" s="29" t="s">
+      <c r="C250" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D250" s="36" t="s">
+      <c r="D250" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E250" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G250" s="59" t="s">
+      <c r="G250" s="57" t="s">
         <v>453</v>
       </c>
-      <c r="H250" s="59"/>
-      <c r="I250" s="59"/>
-      <c r="J250" s="59"/>
-      <c r="K250" s="59"/>
-      <c r="L250" s="59"/>
-      <c r="M250" s="59"/>
-      <c r="N250" s="59"/>
+      <c r="H250" s="57"/>
+      <c r="I250" s="57"/>
+      <c r="J250" s="57"/>
+      <c r="K250" s="57"/>
+      <c r="L250" s="57"/>
+      <c r="M250" s="57"/>
+      <c r="N250" s="57"/>
     </row>
     <row r="251" spans="1:14">
-      <c r="A251" s="74" t="s">
+      <c r="A251" s="72" t="s">
         <v>270</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C251" s="29" t="s">
+      <c r="C251" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D251" s="36" t="s">
+      <c r="D251" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E251" s="6" t="s">
@@ -12946,70 +12938,70 @@
       </c>
     </row>
     <row r="252" spans="1:14" ht="18">
-      <c r="A252" s="74" t="s">
+      <c r="A252" s="72" t="s">
         <v>271</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C252" s="29" t="s">
+      <c r="C252" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D252" s="36" t="s">
+      <c r="D252" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G252" s="59" t="s">
+      <c r="G252" s="57" t="s">
         <v>454</v>
       </c>
-      <c r="H252" s="59"/>
-      <c r="I252" s="59"/>
-      <c r="J252" s="59"/>
-      <c r="K252" s="59"/>
-      <c r="L252" s="59"/>
-      <c r="M252" s="59"/>
-      <c r="N252" s="59"/>
+      <c r="H252" s="57"/>
+      <c r="I252" s="57"/>
+      <c r="J252" s="57"/>
+      <c r="K252" s="57"/>
+      <c r="L252" s="57"/>
+      <c r="M252" s="57"/>
+      <c r="N252" s="57"/>
     </row>
     <row r="253" spans="1:14" ht="18">
-      <c r="A253" s="74" t="s">
+      <c r="A253" s="72" t="s">
         <v>272</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C253" s="29" t="s">
+      <c r="C253" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D253" s="36" t="s">
+      <c r="D253" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E253" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="G253" s="59" t="s">
+      <c r="G253" s="57" t="s">
         <v>455</v>
       </c>
-      <c r="H253" s="59"/>
-      <c r="I253" s="59"/>
-      <c r="J253" s="59"/>
-      <c r="K253" s="59"/>
-      <c r="L253" s="59"/>
-      <c r="M253" s="59"/>
-      <c r="N253" s="59"/>
+      <c r="H253" s="57"/>
+      <c r="I253" s="57"/>
+      <c r="J253" s="57"/>
+      <c r="K253" s="57"/>
+      <c r="L253" s="57"/>
+      <c r="M253" s="57"/>
+      <c r="N253" s="57"/>
     </row>
     <row r="254" spans="1:14">
-      <c r="A254" s="74" t="s">
+      <c r="A254" s="72" t="s">
         <v>70</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="C254" s="29" t="s">
+      <c r="C254" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="D254" s="36" t="s">
+      <c r="D254" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E254" s="6" t="s">
@@ -13017,16 +13009,16 @@
       </c>
     </row>
     <row r="255" spans="1:14">
-      <c r="A255" s="74" t="s">
+      <c r="A255" s="72" t="s">
         <v>71</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="C255" s="29" t="s">
+      <c r="C255" s="27" t="s">
         <v>337</v>
       </c>
-      <c r="D255" s="36" t="s">
+      <c r="D255" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E255" s="6" t="s">
@@ -13034,16 +13026,16 @@
       </c>
     </row>
     <row r="256" spans="1:14">
-      <c r="A256" s="74" t="s">
+      <c r="A256" s="72" t="s">
         <v>72</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C256" s="29" t="s">
+      <c r="C256" s="27" t="s">
         <v>333</v>
       </c>
-      <c r="D256" s="36" t="s">
+      <c r="D256" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E256" s="6" t="s">
@@ -13051,16 +13043,16 @@
       </c>
     </row>
     <row r="257" spans="1:8">
-      <c r="A257" s="74" t="s">
+      <c r="A257" s="72" t="s">
         <v>73</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C257" s="29" t="s">
+      <c r="C257" s="27" t="s">
         <v>333</v>
       </c>
-      <c r="D257" s="36" t="s">
+      <c r="D257" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E257" s="6" t="s">
@@ -13068,16 +13060,16 @@
       </c>
     </row>
     <row r="258" spans="1:8">
-      <c r="A258" s="74" t="s">
+      <c r="A258" s="72" t="s">
         <v>74</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C258" s="29" t="s">
+      <c r="C258" s="27" t="s">
         <v>333</v>
       </c>
-      <c r="D258" s="36" t="s">
+      <c r="D258" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E258" s="6" t="s">
@@ -13085,22 +13077,22 @@
       </c>
     </row>
     <row r="259" spans="1:8" s="13" customFormat="1">
-      <c r="A259" s="80" t="s">
+      <c r="A259" s="78" t="s">
         <v>456</v>
       </c>
       <c r="B259" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C259" s="37" t="s">
+      <c r="C259" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D259" s="36" t="s">
+      <c r="D259" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E259" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G259" s="80" t="s">
+      <c r="G259" s="78" t="s">
         <v>477</v>
       </c>
       <c r="H259" s="13" t="s">
@@ -13108,22 +13100,22 @@
       </c>
     </row>
     <row r="260" spans="1:8">
-      <c r="A260" s="80" t="s">
+      <c r="A260" s="78" t="s">
         <v>457</v>
       </c>
       <c r="B260" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C260" s="37" t="s">
+      <c r="C260" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D260" s="36" t="s">
+      <c r="D260" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E260" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G260" s="80" t="s">
+      <c r="G260" s="78" t="s">
         <v>477</v>
       </c>
       <c r="H260" s="13" t="s">
@@ -13131,22 +13123,22 @@
       </c>
     </row>
     <row r="261" spans="1:8">
-      <c r="A261" s="80" t="s">
+      <c r="A261" s="78" t="s">
         <v>458</v>
       </c>
       <c r="B261" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C261" s="37" t="s">
+      <c r="C261" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D261" s="36" t="s">
+      <c r="D261" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E261" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G261" s="80" t="s">
+      <c r="G261" s="78" t="s">
         <v>477</v>
       </c>
       <c r="H261" s="13" t="s">
@@ -13154,22 +13146,22 @@
       </c>
     </row>
     <row r="262" spans="1:8">
-      <c r="A262" s="80" t="s">
+      <c r="A262" s="78" t="s">
         <v>459</v>
       </c>
       <c r="B262" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C262" s="37" t="s">
+      <c r="C262" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D262" s="36" t="s">
+      <c r="D262" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E262" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G262" s="80" t="s">
+      <c r="G262" s="78" t="s">
         <v>478</v>
       </c>
       <c r="H262" s="13" t="s">
@@ -13177,22 +13169,22 @@
       </c>
     </row>
     <row r="263" spans="1:8">
-      <c r="A263" s="80" t="s">
+      <c r="A263" s="78" t="s">
         <v>460</v>
       </c>
       <c r="B263" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C263" s="37" t="s">
+      <c r="C263" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D263" s="36" t="s">
+      <c r="D263" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E263" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G263" s="80" t="s">
+      <c r="G263" s="78" t="s">
         <v>478</v>
       </c>
       <c r="H263" s="13" t="s">
@@ -13200,22 +13192,22 @@
       </c>
     </row>
     <row r="264" spans="1:8">
-      <c r="A264" s="80" t="s">
+      <c r="A264" s="78" t="s">
         <v>461</v>
       </c>
       <c r="B264" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C264" s="37" t="s">
+      <c r="C264" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D264" s="36" t="s">
+      <c r="D264" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E264" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G264" s="80" t="s">
+      <c r="G264" s="78" t="s">
         <v>478</v>
       </c>
       <c r="H264" s="13" t="s">
@@ -13223,22 +13215,22 @@
       </c>
     </row>
     <row r="265" spans="1:8">
-      <c r="A265" s="80" t="s">
+      <c r="A265" s="78" t="s">
         <v>462</v>
       </c>
       <c r="B265" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C265" s="37" t="s">
+      <c r="C265" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D265" s="36" t="s">
+      <c r="D265" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E265" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G265" s="80" t="s">
+      <c r="G265" s="78" t="s">
         <v>478</v>
       </c>
       <c r="H265" s="13" t="s">
@@ -13246,22 +13238,22 @@
       </c>
     </row>
     <row r="266" spans="1:8">
-      <c r="A266" s="80" t="s">
+      <c r="A266" s="78" t="s">
         <v>463</v>
       </c>
       <c r="B266" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C266" s="37" t="s">
+      <c r="C266" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D266" s="36" t="s">
+      <c r="D266" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E266" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G266" s="80" t="s">
+      <c r="G266" s="78" t="s">
         <v>479</v>
       </c>
       <c r="H266" s="13" t="s">
@@ -13269,22 +13261,22 @@
       </c>
     </row>
     <row r="267" spans="1:8">
-      <c r="A267" s="80" t="s">
+      <c r="A267" s="78" t="s">
         <v>464</v>
       </c>
       <c r="B267" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C267" s="37" t="s">
+      <c r="C267" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D267" s="36" t="s">
+      <c r="D267" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E267" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G267" s="80" t="s">
+      <c r="G267" s="78" t="s">
         <v>479</v>
       </c>
       <c r="H267" s="13" t="s">
@@ -13292,22 +13284,22 @@
       </c>
     </row>
     <row r="268" spans="1:8">
-      <c r="A268" s="80" t="s">
+      <c r="A268" s="78" t="s">
         <v>465</v>
       </c>
       <c r="B268" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C268" s="37" t="s">
+      <c r="C268" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D268" s="36" t="s">
+      <c r="D268" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E268" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G268" s="80" t="s">
+      <c r="G268" s="78" t="s">
         <v>479</v>
       </c>
       <c r="H268" s="13" t="s">
@@ -13315,22 +13307,22 @@
       </c>
     </row>
     <row r="269" spans="1:8">
-      <c r="A269" s="80" t="s">
+      <c r="A269" s="78" t="s">
         <v>466</v>
       </c>
       <c r="B269" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C269" s="37" t="s">
+      <c r="C269" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D269" s="36" t="s">
+      <c r="D269" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E269" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G269" s="80" t="s">
+      <c r="G269" s="78" t="s">
         <v>479</v>
       </c>
       <c r="H269" s="13" t="s">
@@ -13338,22 +13330,22 @@
       </c>
     </row>
     <row r="270" spans="1:8">
-      <c r="A270" s="80" t="s">
+      <c r="A270" s="78" t="s">
         <v>467</v>
       </c>
       <c r="B270" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C270" s="37" t="s">
+      <c r="C270" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D270" s="36" t="s">
+      <c r="D270" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E270" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G270" s="80" t="s">
+      <c r="G270" s="78" t="s">
         <v>480</v>
       </c>
       <c r="H270" s="13" t="s">
@@ -13361,22 +13353,22 @@
       </c>
     </row>
     <row r="271" spans="1:8">
-      <c r="A271" s="80" t="s">
+      <c r="A271" s="78" t="s">
         <v>468</v>
       </c>
       <c r="B271" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C271" s="37" t="s">
+      <c r="C271" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D271" s="36" t="s">
+      <c r="D271" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E271" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G271" s="80" t="s">
+      <c r="G271" s="78" t="s">
         <v>480</v>
       </c>
       <c r="H271" s="13" t="s">
@@ -13384,22 +13376,22 @@
       </c>
     </row>
     <row r="272" spans="1:8">
-      <c r="A272" s="80" t="s">
+      <c r="A272" s="78" t="s">
         <v>469</v>
       </c>
       <c r="B272" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C272" s="37" t="s">
+      <c r="C272" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D272" s="36" t="s">
+      <c r="D272" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E272" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G272" s="80" t="s">
+      <c r="G272" s="78" t="s">
         <v>480</v>
       </c>
       <c r="H272" s="13" t="s">
@@ -13407,22 +13399,22 @@
       </c>
     </row>
     <row r="273" spans="1:9">
-      <c r="A273" s="80" t="s">
+      <c r="A273" s="78" t="s">
         <v>470</v>
       </c>
       <c r="B273" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C273" s="37" t="s">
+      <c r="C273" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D273" s="36" t="s">
+      <c r="D273" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E273" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G273" s="80" t="s">
+      <c r="G273" s="78" t="s">
         <v>480</v>
       </c>
       <c r="H273" s="13" t="s">
@@ -13430,22 +13422,22 @@
       </c>
     </row>
     <row r="274" spans="1:9">
-      <c r="A274" s="80" t="s">
+      <c r="A274" s="78" t="s">
         <v>471</v>
       </c>
       <c r="B274" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C274" s="37" t="s">
+      <c r="C274" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D274" s="36" t="s">
+      <c r="D274" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E274" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G274" s="80" t="s">
+      <c r="G274" s="78" t="s">
         <v>481</v>
       </c>
       <c r="H274" s="13" t="s">
@@ -13453,22 +13445,22 @@
       </c>
     </row>
     <row r="275" spans="1:9">
-      <c r="A275" s="80" t="s">
+      <c r="A275" s="78" t="s">
         <v>472</v>
       </c>
       <c r="B275" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C275" s="37" t="s">
+      <c r="C275" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D275" s="36" t="s">
+      <c r="D275" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E275" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G275" s="80" t="s">
+      <c r="G275" s="78" t="s">
         <v>481</v>
       </c>
       <c r="H275" s="13" t="s">
@@ -13476,22 +13468,22 @@
       </c>
     </row>
     <row r="276" spans="1:9">
-      <c r="A276" s="80" t="s">
+      <c r="A276" s="78" t="s">
         <v>473</v>
       </c>
       <c r="B276" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C276" s="37" t="s">
+      <c r="C276" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="D276" s="36" t="s">
+      <c r="D276" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E276" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G276" s="80" t="s">
+      <c r="G276" s="78" t="s">
         <v>481</v>
       </c>
       <c r="H276" s="13" t="s">
@@ -13505,10 +13497,10 @@
       <c r="B277" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C277" s="42" t="s">
+      <c r="C277" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D277" s="38" t="s">
+      <c r="D277" s="36" t="s">
         <v>169</v>
       </c>
       <c r="E277" s="15" t="s">
@@ -13517,7 +13509,7 @@
       <c r="F277" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="I277" s="43">
+      <c r="I277" s="41">
         <v>0.52</v>
       </c>
     </row>
@@ -13528,10 +13520,10 @@
       <c r="B278" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C278" s="42" t="s">
+      <c r="C278" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D278" s="36" t="s">
+      <c r="D278" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E278" s="15" t="s">
@@ -13540,7 +13532,7 @@
       <c r="F278" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I278" s="43">
+      <c r="I278" s="41">
         <v>0.12</v>
       </c>
     </row>
@@ -13551,10 +13543,10 @@
       <c r="B279" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C279" s="42" t="s">
+      <c r="C279" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D279" s="36" t="s">
+      <c r="D279" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E279" s="15" t="s">
@@ -13563,7 +13555,7 @@
       <c r="F279" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I279" s="43">
+      <c r="I279" s="41">
         <v>0.18</v>
       </c>
     </row>
@@ -13574,10 +13566,10 @@
       <c r="B280" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C280" s="42" t="s">
+      <c r="C280" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D280" s="36" t="s">
+      <c r="D280" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E280" s="15" t="s">
@@ -13586,7 +13578,7 @@
       <c r="F280" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I280" s="43">
+      <c r="I280" s="41">
         <v>0.23</v>
       </c>
     </row>
@@ -13597,10 +13589,10 @@
       <c r="B281" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C281" s="42" t="s">
+      <c r="C281" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D281" s="36" t="s">
+      <c r="D281" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E281" s="15" t="s">
@@ -13609,7 +13601,7 @@
       <c r="F281" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I281" s="43">
+      <c r="I281" s="41">
         <v>0.34</v>
       </c>
     </row>
@@ -13620,10 +13612,10 @@
       <c r="B282" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C282" s="42" t="s">
+      <c r="C282" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D282" s="36" t="s">
+      <c r="D282" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E282" s="15" t="s">
@@ -13632,7 +13624,7 @@
       <c r="F282" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I282" s="43">
+      <c r="I282" s="41">
         <v>0.45</v>
       </c>
     </row>
@@ -13643,10 +13635,10 @@
       <c r="B283" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C283" s="42" t="s">
+      <c r="C283" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D283" s="36" t="s">
+      <c r="D283" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E283" s="15" t="s">
@@ -13655,7 +13647,7 @@
       <c r="F283" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I283" s="43">
+      <c r="I283" s="41">
         <v>0.12</v>
       </c>
     </row>
@@ -13666,10 +13658,10 @@
       <c r="B284" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C284" s="42" t="s">
+      <c r="C284" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D284" s="36" t="s">
+      <c r="D284" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E284" s="15" t="s">
@@ -13678,7 +13670,7 @@
       <c r="F284" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I284" s="43">
+      <c r="I284" s="41">
         <v>0.18</v>
       </c>
     </row>
@@ -13689,10 +13681,10 @@
       <c r="B285" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C285" s="42" t="s">
+      <c r="C285" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D285" s="36" t="s">
+      <c r="D285" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E285" s="15" t="s">
@@ -13701,7 +13693,7 @@
       <c r="F285" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I285" s="43">
+      <c r="I285" s="41">
         <v>0.23</v>
       </c>
     </row>
@@ -13712,10 +13704,10 @@
       <c r="B286" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C286" s="42" t="s">
+      <c r="C286" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D286" s="36" t="s">
+      <c r="D286" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E286" s="15" t="s">
@@ -13724,7 +13716,7 @@
       <c r="F286" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I286" s="43">
+      <c r="I286" s="41">
         <v>0.34</v>
       </c>
     </row>
@@ -13735,10 +13727,10 @@
       <c r="B287" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C287" s="42" t="s">
+      <c r="C287" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D287" s="36" t="s">
+      <c r="D287" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E287" s="15" t="s">
@@ -13747,7 +13739,7 @@
       <c r="F287" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I287" s="43">
+      <c r="I287" s="41">
         <v>0.45</v>
       </c>
     </row>
@@ -13758,10 +13750,10 @@
       <c r="B288" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C288" s="42" t="s">
+      <c r="C288" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D288" s="36" t="s">
+      <c r="D288" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E288" s="15" t="s">
@@ -13770,7 +13762,7 @@
       <c r="F288" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I288" s="43">
+      <c r="I288" s="41">
         <v>0.12</v>
       </c>
     </row>
@@ -13781,10 +13773,10 @@
       <c r="B289" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C289" s="42" t="s">
+      <c r="C289" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D289" s="36" t="s">
+      <c r="D289" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E289" s="15" t="s">
@@ -13793,7 +13785,7 @@
       <c r="F289" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I289" s="43">
+      <c r="I289" s="41">
         <v>0.18</v>
       </c>
     </row>
@@ -13804,10 +13796,10 @@
       <c r="B290" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C290" s="42" t="s">
+      <c r="C290" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D290" s="36" t="s">
+      <c r="D290" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E290" s="15" t="s">
@@ -13816,7 +13808,7 @@
       <c r="F290" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I290" s="43">
+      <c r="I290" s="41">
         <v>0.23</v>
       </c>
     </row>
@@ -13827,10 +13819,10 @@
       <c r="B291" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C291" s="42" t="s">
+      <c r="C291" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D291" s="36" t="s">
+      <c r="D291" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E291" s="15" t="s">
@@ -13839,7 +13831,7 @@
       <c r="F291" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I291" s="43">
+      <c r="I291" s="41">
         <v>0.34</v>
       </c>
     </row>
@@ -13850,10 +13842,10 @@
       <c r="B292" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C292" s="42" t="s">
+      <c r="C292" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D292" s="36" t="s">
+      <c r="D292" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E292" s="15" t="s">
@@ -13862,7 +13854,7 @@
       <c r="F292" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I292" s="43">
+      <c r="I292" s="41">
         <v>0.45</v>
       </c>
     </row>
@@ -13873,10 +13865,10 @@
       <c r="B293" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C293" s="42" t="s">
+      <c r="C293" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D293" s="36" t="s">
+      <c r="D293" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E293" s="15" t="s">
@@ -13885,7 +13877,7 @@
       <c r="F293" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G293" s="66" t="s">
+      <c r="G293" s="64" t="s">
         <v>376</v>
       </c>
     </row>
@@ -13896,10 +13888,10 @@
       <c r="B294" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C294" s="42" t="s">
+      <c r="C294" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D294" s="36" t="s">
+      <c r="D294" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E294" s="15" t="s">
@@ -13908,7 +13900,7 @@
       <c r="F294" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G294" s="66" t="s">
+      <c r="G294" s="64" t="s">
         <v>376</v>
       </c>
     </row>
@@ -13919,10 +13911,10 @@
       <c r="B295" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C295" s="42" t="s">
+      <c r="C295" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D295" s="36" t="s">
+      <c r="D295" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E295" s="15" t="s">
@@ -13931,7 +13923,7 @@
       <c r="F295" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G295" s="66" t="s">
+      <c r="G295" s="64" t="s">
         <v>376</v>
       </c>
     </row>
@@ -13942,10 +13934,10 @@
       <c r="B296" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C296" s="42" t="s">
+      <c r="C296" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D296" s="36" t="s">
+      <c r="D296" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E296" s="15" t="s">
@@ -13954,7 +13946,7 @@
       <c r="F296" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G296" s="66" t="s">
+      <c r="G296" s="64" t="s">
         <v>377</v>
       </c>
     </row>
@@ -13965,10 +13957,10 @@
       <c r="B297" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C297" s="42" t="s">
+      <c r="C297" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D297" s="36" t="s">
+      <c r="D297" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E297" s="15" t="s">
@@ -13977,7 +13969,7 @@
       <c r="F297" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G297" s="66" t="s">
+      <c r="G297" s="64" t="s">
         <v>377</v>
       </c>
     </row>
@@ -13988,10 +13980,10 @@
       <c r="B298" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C298" s="42" t="s">
+      <c r="C298" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D298" s="36" t="s">
+      <c r="D298" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E298" s="15" t="s">
@@ -14000,7 +13992,7 @@
       <c r="F298" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G298" s="66" t="s">
+      <c r="G298" s="64" t="s">
         <v>377</v>
       </c>
     </row>
@@ -14011,10 +14003,10 @@
       <c r="B299" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C299" s="42" t="s">
+      <c r="C299" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D299" s="36" t="s">
+      <c r="D299" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E299" s="15" t="s">
@@ -14023,7 +14015,7 @@
       <c r="F299" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G299" s="66" t="s">
+      <c r="G299" s="64" t="s">
         <v>378</v>
       </c>
     </row>
@@ -14034,10 +14026,10 @@
       <c r="B300" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C300" s="42" t="s">
+      <c r="C300" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D300" s="36" t="s">
+      <c r="D300" s="34" t="s">
         <v>169</v>
       </c>
       <c r="E300" s="15" t="s">
@@ -14046,7 +14038,7 @@
       <c r="F300" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G300" s="66" t="s">
+      <c r="G300" s="64" t="s">
         <v>378</v>
       </c>
     </row>
@@ -14057,10 +14049,10 @@
       <c r="B301" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C301" s="42" t="s">
+      <c r="C301" s="40" t="s">
         <v>306</v>
       </c>
-      <c r="D301" s="41" t="s">
+      <c r="D301" s="39" t="s">
         <v>169</v>
       </c>
       <c r="E301" s="15" t="s">
@@ -14069,7 +14061,7 @@
       <c r="F301" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G301" s="66" t="s">
+      <c r="G301" s="64" t="s">
         <v>378</v>
       </c>
     </row>
@@ -14084,152 +14076,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030F46DB-3E7E-8D4A-A202-14E93E939D46}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="39.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>383</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{D464E443-C139-0042-BCB7-56BDFB6ED537}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{89FD1E65-1D30-A345-80B0-EFF927BC9A82}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{3F203A36-2DAD-7046-909F-6605A4BBF214}"/>
-    <hyperlink ref="B6" r:id="rId4" xr:uid="{A118C9F9-FE69-FF43-B8C1-B2B773ABEA72}"/>
-    <hyperlink ref="B7" r:id="rId5" xr:uid="{542699E2-78B4-F048-A4C7-2A82C325DF06}"/>
-    <hyperlink ref="B8" r:id="rId6" xr:uid="{D95E9718-1658-A541-AD7B-F8AB9F29746D}"/>
-    <hyperlink ref="B1" r:id="rId7" xr:uid="{E95E2428-1320-024C-81B2-5F1E87717E5B}"/>
-    <hyperlink ref="B2" r:id="rId8" xr:uid="{E6F922E6-B077-1849-905C-648D98FBAA5E}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AA33F58-D3DA-914E-BB4C-5050B10E6A20}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="37.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="7" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="7" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="7" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -17469,7 +17315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBC2DBA3-3F2C-254D-A3E7-B7A29892530C}">
   <dimension ref="A1:AE13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/large_scale_yeast_proteomics_analysis/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F2BCDA-BAE1-254D-A623-0104609C5D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA4A4FF-7155-8F45-844E-1CF31281AA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2360" yWindow="500" windowWidth="37660" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="26000" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="cell cycle_kate" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AE$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$G$1:$G$301</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supplementary File 1e vip'!$B$1:$B$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2870" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="518">
   <si>
     <t>sample</t>
   </si>
@@ -1244,9 +1244,6 @@
   </si>
   <si>
     <t>Ethanol_phase</t>
-  </si>
-  <si>
-    <t>condition_detail</t>
   </si>
   <si>
     <t>https://doi.org/10.1038/s41467-022-30513-5</t>
@@ -1777,6 +1774,30 @@
   </si>
   <si>
     <t>raffinose</t>
+  </si>
+  <si>
+    <t>Chemostats_C_limit_miu=0.34</t>
+  </si>
+  <si>
+    <t>Chemostats_C_limit_miu=0.32</t>
+  </si>
+  <si>
+    <t>Chemostats_C_limit_miu=0.3</t>
+  </si>
+  <si>
+    <t>Chemostats_C_limit_miu=0.27</t>
+  </si>
+  <si>
+    <t>Chemostats_C_limit_miu=0.20</t>
+  </si>
+  <si>
+    <t>Chemostats_C_limit_miu=0.23</t>
+  </si>
+  <si>
+    <t>FG_CN4_D= 0.26 or 0.32</t>
+  </si>
+  <si>
+    <t>condition_unique</t>
   </si>
 </sst>
 </file>
@@ -2477,7 +2498,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2647,9 +2668,6 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2705,9 +2723,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3120,7 +3135,7 @@
   <sheetData>
     <row r="1" spans="1:31" s="28" customFormat="1" ht="19">
       <c r="A1" s="28" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B1" s="28" t="s">
         <v>105</v>
@@ -3137,8 +3152,8 @@
       <c r="F1" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="G1" s="79" t="s">
-        <v>398</v>
+      <c r="G1" s="78" t="s">
+        <v>517</v>
       </c>
       <c r="H1" s="28" t="s">
         <v>171</v>
@@ -3218,7 +3233,7 @@
         <v>386</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>325</v>
@@ -3250,7 +3265,7 @@
         <v>387</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>325</v>
@@ -3282,7 +3297,7 @@
         <v>388</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>325</v>
@@ -3314,7 +3329,7 @@
         <v>389</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>325</v>
@@ -3338,7 +3353,7 @@
         <v>390</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>325</v>
@@ -3362,7 +3377,7 @@
         <v>391</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>325</v>
@@ -3386,7 +3401,7 @@
         <v>392</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>325</v>
@@ -3410,7 +3425,7 @@
         <v>393</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>325</v>
@@ -3434,7 +3449,7 @@
         <v>394</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>325</v>
@@ -3454,11 +3469,11 @@
       <c r="X10" s="31"/>
     </row>
     <row r="11" spans="1:31" s="32" customFormat="1">
-      <c r="A11" s="65" t="s">
+      <c r="A11" s="64" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>310</v>
@@ -3472,7 +3487,9 @@
       <c r="F11" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="G11" s="61"/>
+      <c r="G11" s="64" t="s">
+        <v>14</v>
+      </c>
       <c r="H11" s="26" t="s">
         <v>172</v>
       </c>
@@ -3511,11 +3528,11 @@
       </c>
     </row>
     <row r="12" spans="1:31">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="65" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>324</v>
@@ -3597,11 +3614,11 @@
       </c>
     </row>
     <row r="13" spans="1:31">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="65" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>324</v>
@@ -3683,11 +3700,11 @@
       </c>
     </row>
     <row r="14" spans="1:31">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="65" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>324</v>
@@ -3769,11 +3786,11 @@
       </c>
     </row>
     <row r="15" spans="1:31">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="65" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>324</v>
@@ -3855,11 +3872,11 @@
       </c>
     </row>
     <row r="16" spans="1:31">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="65" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>324</v>
@@ -3941,11 +3958,11 @@
       </c>
     </row>
     <row r="17" spans="1:30">
-      <c r="A17" s="66" t="s">
+      <c r="A17" s="65" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>324</v>
@@ -4027,11 +4044,11 @@
       </c>
     </row>
     <row r="18" spans="1:30">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="65" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>324</v>
@@ -4113,11 +4130,11 @@
       </c>
     </row>
     <row r="19" spans="1:30">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="65" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>324</v>
@@ -4199,11 +4216,11 @@
       </c>
     </row>
     <row r="20" spans="1:30">
-      <c r="A20" s="66" t="s">
+      <c r="A20" s="65" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>324</v>
@@ -4285,11 +4302,11 @@
       </c>
     </row>
     <row r="21" spans="1:30">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="65" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>324</v>
@@ -4371,11 +4388,11 @@
       </c>
     </row>
     <row r="22" spans="1:30">
-      <c r="A22" s="66" t="s">
+      <c r="A22" s="65" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>324</v>
@@ -4457,11 +4474,11 @@
       </c>
     </row>
     <row r="23" spans="1:30">
-      <c r="A23" s="66" t="s">
+      <c r="A23" s="65" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>324</v>
@@ -4543,11 +4560,11 @@
       </c>
     </row>
     <row r="24" spans="1:30">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="65" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>324</v>
@@ -4629,11 +4646,11 @@
       </c>
     </row>
     <row r="25" spans="1:30">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="65" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>324</v>
@@ -4715,11 +4732,11 @@
       </c>
     </row>
     <row r="26" spans="1:30">
-      <c r="A26" s="66" t="s">
+      <c r="A26" s="65" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>324</v>
@@ -4801,11 +4818,11 @@
       </c>
     </row>
     <row r="27" spans="1:30">
-      <c r="A27" s="66" t="s">
+      <c r="A27" s="65" t="s">
         <v>30</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>324</v>
@@ -4887,11 +4904,11 @@
       </c>
     </row>
     <row r="28" spans="1:30">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="65" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>324</v>
@@ -4973,11 +4990,11 @@
       </c>
     </row>
     <row r="29" spans="1:30">
-      <c r="A29" s="66" t="s">
+      <c r="A29" s="65" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>324</v>
@@ -5059,11 +5076,11 @@
       </c>
     </row>
     <row r="30" spans="1:30">
-      <c r="A30" s="66" t="s">
+      <c r="A30" s="65" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>324</v>
@@ -5145,11 +5162,11 @@
       </c>
     </row>
     <row r="31" spans="1:30">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="65" t="s">
         <v>34</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>324</v>
@@ -5231,11 +5248,11 @@
       </c>
     </row>
     <row r="32" spans="1:30">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="65" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>324</v>
@@ -5317,11 +5334,11 @@
       </c>
     </row>
     <row r="33" spans="1:31">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="65" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>324</v>
@@ -5406,11 +5423,11 @@
       </c>
     </row>
     <row r="34" spans="1:31">
-      <c r="A34" s="66" t="s">
+      <c r="A34" s="65" t="s">
         <v>37</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>324</v>
@@ -5495,11 +5512,11 @@
       </c>
     </row>
     <row r="35" spans="1:31">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="65" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>324</v>
@@ -5584,11 +5601,11 @@
       </c>
     </row>
     <row r="36" spans="1:31">
-      <c r="A36" s="66" t="s">
+      <c r="A36" s="65" t="s">
         <v>39</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>324</v>
@@ -5673,11 +5690,11 @@
       </c>
     </row>
     <row r="37" spans="1:31">
-      <c r="A37" s="66" t="s">
+      <c r="A37" s="65" t="s">
         <v>40</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>324</v>
@@ -5762,11 +5779,11 @@
       </c>
     </row>
     <row r="38" spans="1:31">
-      <c r="A38" s="66" t="s">
+      <c r="A38" s="65" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>324</v>
@@ -5851,11 +5868,11 @@
       </c>
     </row>
     <row r="39" spans="1:31">
-      <c r="A39" s="66" t="s">
+      <c r="A39" s="65" t="s">
         <v>42</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>324</v>
@@ -5937,11 +5954,11 @@
       </c>
     </row>
     <row r="40" spans="1:31">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="65" t="s">
         <v>43</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>324</v>
@@ -6023,11 +6040,11 @@
       </c>
     </row>
     <row r="41" spans="1:31">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="65" t="s">
         <v>44</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>324</v>
@@ -6109,11 +6126,11 @@
       </c>
     </row>
     <row r="42" spans="1:31">
-      <c r="A42" s="66" t="s">
+      <c r="A42" s="65" t="s">
         <v>45</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>324</v>
@@ -6195,11 +6212,11 @@
       </c>
     </row>
     <row r="43" spans="1:31">
-      <c r="A43" s="66" t="s">
+      <c r="A43" s="65" t="s">
         <v>46</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>324</v>
@@ -6281,11 +6298,11 @@
       </c>
     </row>
     <row r="44" spans="1:31">
-      <c r="A44" s="66" t="s">
+      <c r="A44" s="65" t="s">
         <v>47</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>324</v>
@@ -6367,11 +6384,11 @@
       </c>
     </row>
     <row r="45" spans="1:31">
-      <c r="A45" s="66" t="s">
+      <c r="A45" s="65" t="s">
         <v>48</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>324</v>
@@ -6453,11 +6470,11 @@
       </c>
     </row>
     <row r="46" spans="1:31">
-      <c r="A46" s="66" t="s">
+      <c r="A46" s="65" t="s">
         <v>49</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>324</v>
@@ -6539,11 +6556,11 @@
       </c>
     </row>
     <row r="47" spans="1:31">
-      <c r="A47" s="66" t="s">
+      <c r="A47" s="65" t="s">
         <v>50</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>324</v>
@@ -6625,11 +6642,11 @@
       </c>
     </row>
     <row r="48" spans="1:31">
-      <c r="A48" s="66" t="s">
+      <c r="A48" s="65" t="s">
         <v>51</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>324</v>
@@ -6711,11 +6728,11 @@
       </c>
     </row>
     <row r="49" spans="1:30">
-      <c r="A49" s="66" t="s">
+      <c r="A49" s="65" t="s">
         <v>52</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>324</v>
@@ -6797,11 +6814,11 @@
       </c>
     </row>
     <row r="50" spans="1:30">
-      <c r="A50" s="66" t="s">
+      <c r="A50" s="65" t="s">
         <v>53</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>324</v>
@@ -6883,11 +6900,11 @@
       </c>
     </row>
     <row r="51" spans="1:30">
-      <c r="A51" s="66" t="s">
+      <c r="A51" s="65" t="s">
         <v>54</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>324</v>
@@ -6969,11 +6986,11 @@
       </c>
     </row>
     <row r="52" spans="1:30">
-      <c r="A52" s="66" t="s">
+      <c r="A52" s="65" t="s">
         <v>55</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>324</v>
@@ -7055,11 +7072,11 @@
       </c>
     </row>
     <row r="53" spans="1:30">
-      <c r="A53" s="66" t="s">
+      <c r="A53" s="65" t="s">
         <v>56</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>324</v>
@@ -7140,37 +7157,39 @@
         <v>0.42361575000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:30" s="83" customFormat="1">
-      <c r="A54" s="80" t="s">
+    <row r="54" spans="1:30" s="81" customFormat="1">
+      <c r="A54" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="80" t="s">
-        <v>488</v>
-      </c>
-      <c r="C54" s="80" t="s">
+      <c r="B54" s="79" t="s">
+        <v>487</v>
+      </c>
+      <c r="C54" s="79" t="s">
         <v>339</v>
       </c>
-      <c r="D54" s="80" t="s">
-        <v>169</v>
-      </c>
-      <c r="E54" s="80" t="s">
+      <c r="D54" s="79" t="s">
+        <v>169</v>
+      </c>
+      <c r="E54" s="79" t="s">
         <v>301</v>
       </c>
-      <c r="F54" s="80" t="s">
+      <c r="F54" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="G54" s="81"/>
-      <c r="H54" s="80"/>
-      <c r="I54" s="82">
+      <c r="G54" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="H54" s="79"/>
+      <c r="I54" s="80">
         <v>0.1</v>
       </c>
     </row>
     <row r="55" spans="1:30" s="13" customFormat="1">
       <c r="A55" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>326</v>
@@ -7205,10 +7224,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>326</v>
@@ -7243,10 +7262,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>326</v>
@@ -7281,10 +7300,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>326</v>
@@ -7319,10 +7338,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>326</v>
@@ -7360,10 +7379,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>326</v>
@@ -7401,10 +7420,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>326</v>
@@ -7442,10 +7461,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>326</v>
@@ -7483,10 +7502,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>326</v>
@@ -7524,10 +7543,10 @@
     </row>
     <row r="64" spans="1:30" s="14" customFormat="1">
       <c r="A64" s="11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>326</v>
@@ -7564,7 +7583,7 @@
       </c>
     </row>
     <row r="65" spans="1:30" s="13" customFormat="1">
-      <c r="A65" s="67" t="s">
+      <c r="A65" s="66" t="s">
         <v>62</v>
       </c>
       <c r="B65" s="10" t="s">
@@ -7582,14 +7601,16 @@
       <c r="F65" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="G65" s="58"/>
+      <c r="G65" s="66" t="s">
+        <v>62</v>
+      </c>
       <c r="H65" s="10"/>
       <c r="I65" s="13">
         <v>0.1</v>
       </c>
     </row>
     <row r="66" spans="1:30">
-      <c r="A66" s="68" t="s">
+      <c r="A66" s="67" t="s">
         <v>63</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -7607,14 +7628,16 @@
       <c r="F66" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G66" s="59"/>
+      <c r="G66" s="67" t="s">
+        <v>63</v>
+      </c>
       <c r="H66" s="6"/>
       <c r="I66" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="67" spans="1:30">
-      <c r="A67" s="68" t="s">
+      <c r="A67" s="67" t="s">
         <v>64</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -7632,14 +7655,16 @@
       <c r="F67" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G67" s="59"/>
+      <c r="G67" s="67" t="s">
+        <v>64</v>
+      </c>
       <c r="H67" s="6"/>
       <c r="I67" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="68" spans="1:30">
-      <c r="A68" s="68" t="s">
+      <c r="A68" s="67" t="s">
         <v>65</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -7657,14 +7682,16 @@
       <c r="F68" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G68" s="59"/>
+      <c r="G68" s="67" t="s">
+        <v>65</v>
+      </c>
       <c r="H68" s="6"/>
       <c r="I68" s="5">
         <v>0.1</v>
       </c>
     </row>
     <row r="69" spans="1:30">
-      <c r="A69" s="68" t="s">
+      <c r="A69" s="67" t="s">
         <v>66</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -7682,11 +7709,13 @@
       <c r="F69" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G69" s="59"/>
+      <c r="G69" s="67" t="s">
+        <v>516</v>
+      </c>
       <c r="H69" s="6"/>
     </row>
     <row r="70" spans="1:30">
-      <c r="A70" s="68" t="s">
+      <c r="A70" s="67" t="s">
         <v>67</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -7704,11 +7733,13 @@
       <c r="F70" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G70" s="59"/>
+      <c r="G70" s="67" t="s">
+        <v>516</v>
+      </c>
       <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:30">
-      <c r="A71" s="68" t="s">
+      <c r="A71" s="67" t="s">
         <v>68</v>
       </c>
       <c r="B71" s="6" t="s">
@@ -7726,11 +7757,13 @@
       <c r="F71" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G71" s="59"/>
+      <c r="G71" s="67" t="s">
+        <v>516</v>
+      </c>
       <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:30">
-      <c r="A72" s="68" t="s">
+      <c r="A72" s="67" t="s">
         <v>69</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -7748,15 +7781,17 @@
       <c r="F72" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G72" s="59"/>
+      <c r="G72" s="67" t="s">
+        <v>516</v>
+      </c>
       <c r="H72" s="6"/>
     </row>
     <row r="73" spans="1:30" s="29" customFormat="1">
-      <c r="A73" s="69" t="s">
-        <v>418</v>
+      <c r="A73" s="68" t="s">
+        <v>417</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>327</v>
@@ -7770,7 +7805,7 @@
       <c r="F73" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="G73" s="62" t="s">
+      <c r="G73" s="61" t="s">
         <v>104</v>
       </c>
       <c r="H73" s="22" t="s">
@@ -7805,11 +7840,11 @@
       </c>
     </row>
     <row r="74" spans="1:30" s="30" customFormat="1">
-      <c r="A74" s="70" t="s">
-        <v>419</v>
+      <c r="A74" s="69" t="s">
+        <v>418</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>327</v>
@@ -7823,7 +7858,7 @@
       <c r="F74" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G74" s="63" t="s">
+      <c r="G74" s="62" t="s">
         <v>104</v>
       </c>
       <c r="H74" s="12" t="s">
@@ -7858,11 +7893,11 @@
       </c>
     </row>
     <row r="75" spans="1:30" s="30" customFormat="1">
-      <c r="A75" s="70" t="s">
-        <v>420</v>
+      <c r="A75" s="69" t="s">
+        <v>419</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>327</v>
@@ -7876,7 +7911,7 @@
       <c r="F75" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G75" s="63" t="s">
+      <c r="G75" s="62" t="s">
         <v>104</v>
       </c>
       <c r="H75" s="12" t="s">
@@ -7911,14 +7946,14 @@
       </c>
     </row>
     <row r="76" spans="1:30">
-      <c r="A76" s="70" t="s">
-        <v>421</v>
+      <c r="A76" s="69" t="s">
+        <v>420</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>170</v>
@@ -7964,14 +7999,14 @@
       </c>
     </row>
     <row r="77" spans="1:30">
-      <c r="A77" s="70" t="s">
-        <v>422</v>
+      <c r="A77" s="69" t="s">
+        <v>421</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>170</v>
@@ -8017,14 +8052,14 @@
       </c>
     </row>
     <row r="78" spans="1:30">
-      <c r="A78" s="70" t="s">
-        <v>423</v>
+      <c r="A78" s="69" t="s">
+        <v>422</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>170</v>
@@ -8070,14 +8105,14 @@
       </c>
     </row>
     <row r="79" spans="1:30">
-      <c r="A79" s="70" t="s">
-        <v>424</v>
+      <c r="A79" s="69" t="s">
+        <v>423</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>170</v>
@@ -8123,14 +8158,14 @@
       </c>
     </row>
     <row r="80" spans="1:30">
-      <c r="A80" s="70" t="s">
-        <v>425</v>
+      <c r="A80" s="69" t="s">
+        <v>424</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>170</v>
@@ -8176,14 +8211,14 @@
       </c>
     </row>
     <row r="81" spans="1:30">
-      <c r="A81" s="70" t="s">
-        <v>426</v>
+      <c r="A81" s="69" t="s">
+        <v>425</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>170</v>
@@ -8229,14 +8264,14 @@
       </c>
     </row>
     <row r="82" spans="1:30">
-      <c r="A82" s="70" t="s">
-        <v>427</v>
+      <c r="A82" s="69" t="s">
+        <v>426</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>170</v>
@@ -8282,14 +8317,14 @@
       </c>
     </row>
     <row r="83" spans="1:30">
-      <c r="A83" s="70" t="s">
-        <v>428</v>
+      <c r="A83" s="69" t="s">
+        <v>427</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>170</v>
@@ -8335,14 +8370,14 @@
       </c>
     </row>
     <row r="84" spans="1:30">
-      <c r="A84" s="70" t="s">
-        <v>429</v>
+      <c r="A84" s="69" t="s">
+        <v>428</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>170</v>
@@ -8388,14 +8423,14 @@
       </c>
     </row>
     <row r="85" spans="1:30">
-      <c r="A85" s="70" t="s">
-        <v>430</v>
+      <c r="A85" s="69" t="s">
+        <v>429</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>170</v>
@@ -8441,14 +8476,14 @@
       </c>
     </row>
     <row r="86" spans="1:30">
-      <c r="A86" s="70" t="s">
-        <v>431</v>
+      <c r="A86" s="69" t="s">
+        <v>430</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>170</v>
@@ -8494,14 +8529,14 @@
       </c>
     </row>
     <row r="87" spans="1:30">
-      <c r="A87" s="70" t="s">
-        <v>432</v>
+      <c r="A87" s="69" t="s">
+        <v>431</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>170</v>
@@ -8547,14 +8582,14 @@
       </c>
     </row>
     <row r="88" spans="1:30">
-      <c r="A88" s="70" t="s">
-        <v>433</v>
+      <c r="A88" s="69" t="s">
+        <v>432</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>170</v>
@@ -8600,14 +8635,14 @@
       </c>
     </row>
     <row r="89" spans="1:30">
-      <c r="A89" s="70" t="s">
-        <v>434</v>
+      <c r="A89" s="69" t="s">
+        <v>433</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>170</v>
@@ -8653,14 +8688,14 @@
       </c>
     </row>
     <row r="90" spans="1:30">
-      <c r="A90" s="70" t="s">
-        <v>435</v>
+      <c r="A90" s="69" t="s">
+        <v>434</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>170</v>
@@ -8706,14 +8741,14 @@
       </c>
     </row>
     <row r="91" spans="1:30">
-      <c r="A91" s="70" t="s">
-        <v>436</v>
+      <c r="A91" s="69" t="s">
+        <v>435</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>170</v>
@@ -8759,14 +8794,14 @@
       </c>
     </row>
     <row r="92" spans="1:30">
-      <c r="A92" s="70" t="s">
-        <v>437</v>
+      <c r="A92" s="69" t="s">
+        <v>436</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>170</v>
@@ -8812,14 +8847,14 @@
       </c>
     </row>
     <row r="93" spans="1:30">
-      <c r="A93" s="70" t="s">
-        <v>438</v>
+      <c r="A93" s="69" t="s">
+        <v>437</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>170</v>
@@ -8865,14 +8900,14 @@
       </c>
     </row>
     <row r="94" spans="1:30">
-      <c r="A94" s="70" t="s">
-        <v>439</v>
+      <c r="A94" s="69" t="s">
+        <v>438</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>170</v>
@@ -8918,14 +8953,14 @@
       </c>
     </row>
     <row r="95" spans="1:30">
-      <c r="A95" s="70" t="s">
-        <v>440</v>
+      <c r="A95" s="69" t="s">
+        <v>439</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>170</v>
@@ -8971,14 +9006,14 @@
       </c>
     </row>
     <row r="96" spans="1:30">
-      <c r="A96" s="70" t="s">
-        <v>441</v>
+      <c r="A96" s="69" t="s">
+        <v>440</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>170</v>
@@ -9024,14 +9059,14 @@
       </c>
     </row>
     <row r="97" spans="1:30">
-      <c r="A97" s="70" t="s">
-        <v>442</v>
+      <c r="A97" s="69" t="s">
+        <v>441</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>170</v>
@@ -9077,14 +9112,14 @@
       </c>
     </row>
     <row r="98" spans="1:30">
-      <c r="A98" s="70" t="s">
-        <v>443</v>
+      <c r="A98" s="69" t="s">
+        <v>442</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>170</v>
@@ -9130,14 +9165,14 @@
       </c>
     </row>
     <row r="99" spans="1:30" s="14" customFormat="1">
-      <c r="A99" s="71" t="s">
-        <v>444</v>
+      <c r="A99" s="70" t="s">
+        <v>443</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D99" s="11" t="s">
         <v>170</v>
@@ -9183,11 +9218,11 @@
       </c>
     </row>
     <row r="100" spans="1:30">
-      <c r="A100" s="72" t="s">
+      <c r="A100" s="71" t="s">
         <v>106</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>328</v>
@@ -9201,7 +9236,7 @@
       <c r="F100" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G100" s="72" t="s">
+      <c r="G100" s="71" t="s">
         <v>106</v>
       </c>
       <c r="H100" s="12" t="s">
@@ -9212,11 +9247,11 @@
       </c>
     </row>
     <row r="101" spans="1:30">
-      <c r="A101" s="72" t="s">
+      <c r="A101" s="71" t="s">
         <v>107</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>328</v>
@@ -9230,7 +9265,7 @@
       <c r="F101" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G101" s="72" t="s">
+      <c r="G101" s="71" t="s">
         <v>107</v>
       </c>
       <c r="H101" s="12" t="s">
@@ -9241,11 +9276,11 @@
       </c>
     </row>
     <row r="102" spans="1:30">
-      <c r="A102" s="72" t="s">
+      <c r="A102" s="71" t="s">
         <v>108</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>328</v>
@@ -9259,7 +9294,7 @@
       <c r="F102" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G102" s="72" t="s">
+      <c r="G102" s="71" t="s">
         <v>108</v>
       </c>
       <c r="H102" s="12" t="s">
@@ -9270,11 +9305,11 @@
       </c>
     </row>
     <row r="103" spans="1:30">
-      <c r="A103" s="72" t="s">
+      <c r="A103" s="71" t="s">
         <v>109</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>328</v>
@@ -9288,7 +9323,7 @@
       <c r="F103" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G103" s="72" t="s">
+      <c r="G103" s="71" t="s">
         <v>109</v>
       </c>
       <c r="H103" s="12" t="s">
@@ -9299,11 +9334,11 @@
       </c>
     </row>
     <row r="104" spans="1:30">
-      <c r="A104" s="72" t="s">
+      <c r="A104" s="71" t="s">
         <v>110</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>328</v>
@@ -9317,7 +9352,7 @@
       <c r="F104" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G104" s="72" t="s">
+      <c r="G104" s="71" t="s">
         <v>110</v>
       </c>
       <c r="H104" s="12" t="s">
@@ -9328,11 +9363,11 @@
       </c>
     </row>
     <row r="105" spans="1:30">
-      <c r="A105" s="72" t="s">
+      <c r="A105" s="71" t="s">
         <v>111</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>328</v>
@@ -9346,7 +9381,7 @@
       <c r="F105" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G105" s="72" t="s">
+      <c r="G105" s="71" t="s">
         <v>111</v>
       </c>
       <c r="H105" s="12" t="s">
@@ -9357,11 +9392,11 @@
       </c>
     </row>
     <row r="106" spans="1:30">
-      <c r="A106" s="72" t="s">
+      <c r="A106" s="71" t="s">
         <v>112</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>328</v>
@@ -9375,7 +9410,7 @@
       <c r="F106" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G106" s="72" t="s">
+      <c r="G106" s="71" t="s">
         <v>112</v>
       </c>
       <c r="H106" s="12" t="s">
@@ -9386,11 +9421,11 @@
       </c>
     </row>
     <row r="107" spans="1:30">
-      <c r="A107" s="72" t="s">
+      <c r="A107" s="71" t="s">
         <v>113</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>328</v>
@@ -9404,7 +9439,7 @@
       <c r="F107" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G107" s="72" t="s">
+      <c r="G107" s="71" t="s">
         <v>113</v>
       </c>
       <c r="H107" s="12" t="s">
@@ -9415,11 +9450,11 @@
       </c>
     </row>
     <row r="108" spans="1:30">
-      <c r="A108" s="72" t="s">
+      <c r="A108" s="71" t="s">
         <v>114</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>328</v>
@@ -9433,7 +9468,7 @@
       <c r="F108" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G108" s="72" t="s">
+      <c r="G108" s="71" t="s">
         <v>114</v>
       </c>
       <c r="H108" s="12" t="s">
@@ -9444,11 +9479,11 @@
       </c>
     </row>
     <row r="109" spans="1:30" ht="14" customHeight="1">
-      <c r="A109" s="72" t="s">
+      <c r="A109" s="71" t="s">
         <v>115</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>328</v>
@@ -9462,7 +9497,7 @@
       <c r="F109" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G109" s="72" t="s">
+      <c r="G109" s="71" t="s">
         <v>115</v>
       </c>
       <c r="H109" s="12" t="s">
@@ -9492,7 +9527,7 @@
         <v>128</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H110" s="13" t="s">
         <v>209</v>
@@ -9524,7 +9559,7 @@
         <v>128</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>209</v>
@@ -9556,7 +9591,7 @@
         <v>128</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H112" s="5" t="s">
         <v>209</v>
@@ -9588,7 +9623,7 @@
         <v>128</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H113" s="5" t="s">
         <v>209</v>
@@ -9620,7 +9655,7 @@
         <v>128</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H114" s="5" t="s">
         <v>209</v>
@@ -9652,7 +9687,7 @@
         <v>128</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H115" s="5" t="s">
         <v>209</v>
@@ -9684,7 +9719,7 @@
         <v>128</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H116" s="5" t="s">
         <v>209</v>
@@ -9716,7 +9751,7 @@
         <v>128</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H117" s="5" t="s">
         <v>209</v>
@@ -9748,7 +9783,7 @@
         <v>128</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H118" s="5" t="s">
         <v>209</v>
@@ -9780,7 +9815,7 @@
         <v>128</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>209</v>
@@ -9812,7 +9847,7 @@
         <v>128</v>
       </c>
       <c r="G120" s="11" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H120" s="14" t="s">
         <v>209</v>
@@ -9825,11 +9860,11 @@
       </c>
     </row>
     <row r="121" spans="1:24" s="13" customFormat="1">
-      <c r="A121" s="73" t="s">
+      <c r="A121" s="72" t="s">
         <v>129</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>322</v>
@@ -9851,11 +9886,11 @@
       </c>
     </row>
     <row r="122" spans="1:24">
-      <c r="A122" s="74" t="s">
+      <c r="A122" s="73" t="s">
         <v>130</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>322</v>
@@ -9877,11 +9912,11 @@
       </c>
     </row>
     <row r="123" spans="1:24">
-      <c r="A123" s="74" t="s">
+      <c r="A123" s="73" t="s">
         <v>131</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>322</v>
@@ -9903,11 +9938,11 @@
       </c>
     </row>
     <row r="124" spans="1:24">
-      <c r="A124" s="74" t="s">
+      <c r="A124" s="73" t="s">
         <v>132</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>322</v>
@@ -9929,11 +9964,11 @@
       </c>
     </row>
     <row r="125" spans="1:24">
-      <c r="A125" s="74" t="s">
+      <c r="A125" s="73" t="s">
         <v>133</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>322</v>
@@ -9955,11 +9990,11 @@
       </c>
     </row>
     <row r="126" spans="1:24">
-      <c r="A126" s="74" t="s">
+      <c r="A126" s="73" t="s">
         <v>134</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>322</v>
@@ -9981,11 +10016,11 @@
       </c>
     </row>
     <row r="127" spans="1:24">
-      <c r="A127" s="74" t="s">
+      <c r="A127" s="73" t="s">
         <v>135</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>322</v>
@@ -10007,11 +10042,11 @@
       </c>
     </row>
     <row r="128" spans="1:24">
-      <c r="A128" s="74" t="s">
+      <c r="A128" s="73" t="s">
         <v>136</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>322</v>
@@ -10033,11 +10068,11 @@
       </c>
     </row>
     <row r="129" spans="1:9">
-      <c r="A129" s="74" t="s">
+      <c r="A129" s="73" t="s">
         <v>137</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>322</v>
@@ -10059,11 +10094,11 @@
       </c>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="74" t="s">
+      <c r="A130" s="73" t="s">
         <v>138</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>322</v>
@@ -10085,11 +10120,11 @@
       </c>
     </row>
     <row r="131" spans="1:9">
-      <c r="A131" s="74" t="s">
+      <c r="A131" s="73" t="s">
         <v>139</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>322</v>
@@ -10111,11 +10146,11 @@
       </c>
     </row>
     <row r="132" spans="1:9">
-      <c r="A132" s="74" t="s">
+      <c r="A132" s="73" t="s">
         <v>140</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>322</v>
@@ -10137,11 +10172,11 @@
       </c>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="74" t="s">
+      <c r="A133" s="73" t="s">
         <v>141</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>322</v>
@@ -10163,11 +10198,11 @@
       </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="74" t="s">
+      <c r="A134" s="73" t="s">
         <v>142</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>322</v>
@@ -10189,11 +10224,11 @@
       </c>
     </row>
     <row r="135" spans="1:9">
-      <c r="A135" s="74" t="s">
+      <c r="A135" s="73" t="s">
         <v>143</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>322</v>
@@ -10215,11 +10250,11 @@
       </c>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="74" t="s">
+      <c r="A136" s="73" t="s">
         <v>144</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>322</v>
@@ -10241,11 +10276,11 @@
       </c>
     </row>
     <row r="137" spans="1:9">
-      <c r="A137" s="74" t="s">
+      <c r="A137" s="73" t="s">
         <v>145</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>322</v>
@@ -10267,11 +10302,11 @@
       </c>
     </row>
     <row r="138" spans="1:9">
-      <c r="A138" s="74" t="s">
+      <c r="A138" s="73" t="s">
         <v>146</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>322</v>
@@ -10293,11 +10328,11 @@
       </c>
     </row>
     <row r="139" spans="1:9">
-      <c r="A139" s="74" t="s">
+      <c r="A139" s="73" t="s">
         <v>147</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>322</v>
@@ -10319,11 +10354,11 @@
       </c>
     </row>
     <row r="140" spans="1:9">
-      <c r="A140" s="74" t="s">
+      <c r="A140" s="73" t="s">
         <v>148</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>322</v>
@@ -10345,11 +10380,11 @@
       </c>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="74" t="s">
+      <c r="A141" s="73" t="s">
         <v>149</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>322</v>
@@ -10371,11 +10406,11 @@
       </c>
     </row>
     <row r="142" spans="1:9">
-      <c r="A142" s="74" t="s">
+      <c r="A142" s="73" t="s">
         <v>150</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>322</v>
@@ -10397,11 +10432,11 @@
       </c>
     </row>
     <row r="143" spans="1:9">
-      <c r="A143" s="74" t="s">
+      <c r="A143" s="73" t="s">
         <v>151</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>322</v>
@@ -10423,11 +10458,11 @@
       </c>
     </row>
     <row r="144" spans="1:9">
-      <c r="A144" s="74" t="s">
+      <c r="A144" s="73" t="s">
         <v>152</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>322</v>
@@ -10449,11 +10484,11 @@
       </c>
     </row>
     <row r="145" spans="1:25">
-      <c r="A145" s="74" t="s">
+      <c r="A145" s="73" t="s">
         <v>153</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>322</v>
@@ -10475,11 +10510,11 @@
       </c>
     </row>
     <row r="146" spans="1:25">
-      <c r="A146" s="74" t="s">
+      <c r="A146" s="73" t="s">
         <v>154</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>322</v>
@@ -10501,11 +10536,11 @@
       </c>
     </row>
     <row r="147" spans="1:25">
-      <c r="A147" s="74" t="s">
+      <c r="A147" s="73" t="s">
         <v>155</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>322</v>
@@ -10527,11 +10562,11 @@
       </c>
     </row>
     <row r="148" spans="1:25">
-      <c r="A148" s="74" t="s">
+      <c r="A148" s="73" t="s">
         <v>156</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>322</v>
@@ -10553,11 +10588,11 @@
       </c>
     </row>
     <row r="149" spans="1:25">
-      <c r="A149" s="74" t="s">
+      <c r="A149" s="73" t="s">
         <v>157</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>322</v>
@@ -10579,11 +10614,11 @@
       </c>
     </row>
     <row r="150" spans="1:25" s="14" customFormat="1">
-      <c r="A150" s="75" t="s">
+      <c r="A150" s="74" t="s">
         <v>158</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>322</v>
@@ -10609,7 +10644,7 @@
         <v>159</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>323</v>
@@ -10644,7 +10679,7 @@
         <v>160</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>323</v>
@@ -10679,7 +10714,7 @@
         <v>161</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>323</v>
@@ -10714,7 +10749,7 @@
         <v>162</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>323</v>
@@ -10749,7 +10784,7 @@
         <v>163</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>323</v>
@@ -10784,7 +10819,7 @@
         <v>164</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>323</v>
@@ -10819,7 +10854,7 @@
         <v>165</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>323</v>
@@ -10854,7 +10889,7 @@
         <v>166</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>323</v>
@@ -10891,7 +10926,7 @@
       <c r="B159" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="C159" s="86" t="s">
+      <c r="C159" s="84" t="s">
         <v>307</v>
       </c>
       <c r="D159" s="36" t="s">
@@ -10903,8 +10938,8 @@
       <c r="F159" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="G159" s="84" t="s">
-        <v>492</v>
+      <c r="G159" s="82" t="s">
+        <v>491</v>
       </c>
       <c r="I159" s="13">
         <v>5.1999999999999998E-2</v>
@@ -10930,8 +10965,8 @@
       <c r="F160" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G160" s="85" t="s">
-        <v>492</v>
+      <c r="G160" s="83" t="s">
+        <v>491</v>
       </c>
       <c r="I160" s="5">
         <v>5.0999999999999997E-2</v>
@@ -10956,8 +10991,8 @@
       <c r="F161" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G161" s="85" t="s">
-        <v>492</v>
+      <c r="G161" s="83" t="s">
+        <v>491</v>
       </c>
       <c r="I161" s="5">
         <v>4.8000000000000001E-2</v>
@@ -10982,8 +11017,8 @@
       <c r="F162" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G162" s="85" t="s">
-        <v>492</v>
+      <c r="G162" s="83" t="s">
+        <v>491</v>
       </c>
       <c r="I162" s="5">
         <v>4.7E-2</v>
@@ -11009,7 +11044,7 @@
         <v>128</v>
       </c>
       <c r="G163" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I163" s="5">
         <v>0.16500000000000001</v>
@@ -11035,7 +11070,7 @@
         <v>128</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I164" s="5">
         <v>0.182</v>
@@ -11061,7 +11096,7 @@
         <v>128</v>
       </c>
       <c r="G165" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I165" s="5">
         <v>0.27500000000000002</v>
@@ -11087,7 +11122,7 @@
         <v>128</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I166" s="5">
         <v>0.29099999999999998</v>
@@ -11113,7 +11148,7 @@
         <v>128</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I167" s="5">
         <v>0.373</v>
@@ -11139,7 +11174,7 @@
         <v>128</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I168" s="5">
         <v>0.36899999999999999</v>
@@ -11165,7 +11200,7 @@
         <v>128</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I169" s="5">
         <v>0.121</v>
@@ -11191,7 +11226,7 @@
         <v>128</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I170" s="5">
         <v>0.106</v>
@@ -11217,7 +11252,7 @@
         <v>128</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I171" s="5">
         <v>0.2</v>
@@ -11243,7 +11278,7 @@
         <v>128</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I172" s="5">
         <v>0.20100000000000001</v>
@@ -11269,7 +11304,7 @@
         <v>128</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I173" s="5">
         <v>0.32700000000000001</v>
@@ -11295,7 +11330,7 @@
         <v>128</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I174" s="5">
         <v>0.318</v>
@@ -11321,7 +11356,7 @@
         <v>128</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I175" s="5">
         <v>0.42099999999999999</v>
@@ -11347,7 +11382,7 @@
         <v>128</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I176" s="5">
         <v>0.39900000000000002</v>
@@ -11372,6 +11407,9 @@
       <c r="F177" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G177" s="6" t="s">
+        <v>514</v>
+      </c>
       <c r="I177" s="5">
         <v>0.19600000000000001</v>
       </c>
@@ -11395,6 +11433,9 @@
       <c r="F178" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G178" s="6" t="s">
+        <v>514</v>
+      </c>
       <c r="I178" s="5">
         <v>0.20200000000000001</v>
       </c>
@@ -11418,6 +11459,9 @@
       <c r="F179" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G179" s="6" t="s">
+        <v>515</v>
+      </c>
       <c r="I179" s="5">
         <v>0.22900000000000001</v>
       </c>
@@ -11441,6 +11485,9 @@
       <c r="F180" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G180" s="6" t="s">
+        <v>515</v>
+      </c>
       <c r="I180" s="5">
         <v>0.22500000000000001</v>
       </c>
@@ -11464,6 +11511,9 @@
       <c r="F181" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G181" s="6" t="s">
+        <v>513</v>
+      </c>
       <c r="I181" s="5">
         <v>0.26800000000000002</v>
       </c>
@@ -11487,6 +11537,9 @@
       <c r="F182" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G182" s="6" t="s">
+        <v>513</v>
+      </c>
       <c r="I182" s="5">
         <v>0.27300000000000002</v>
       </c>
@@ -11510,6 +11563,9 @@
       <c r="F183" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G183" s="6" t="s">
+        <v>512</v>
+      </c>
       <c r="I183" s="5">
         <v>0.30299999999999999</v>
       </c>
@@ -11533,6 +11589,9 @@
       <c r="F184" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G184" s="6" t="s">
+        <v>512</v>
+      </c>
       <c r="I184" s="5">
         <v>0.30199999999999999</v>
       </c>
@@ -11556,6 +11615,9 @@
       <c r="F185" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G185" s="6" t="s">
+        <v>512</v>
+      </c>
       <c r="I185" s="5">
         <v>0.3</v>
       </c>
@@ -11579,6 +11641,9 @@
       <c r="F186" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G186" s="6" t="s">
+        <v>512</v>
+      </c>
       <c r="I186" s="5">
         <v>0.30099999999999999</v>
       </c>
@@ -11602,6 +11667,9 @@
       <c r="F187" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G187" s="6" t="s">
+        <v>511</v>
+      </c>
       <c r="I187" s="5">
         <v>0.316</v>
       </c>
@@ -11625,6 +11693,9 @@
       <c r="F188" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G188" s="6" t="s">
+        <v>511</v>
+      </c>
       <c r="I188" s="5">
         <v>0.32</v>
       </c>
@@ -11648,6 +11719,9 @@
       <c r="F189" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G189" s="6" t="s">
+        <v>510</v>
+      </c>
       <c r="I189" s="5">
         <v>0.33700000000000002</v>
       </c>
@@ -11671,12 +11745,15 @@
       <c r="F190" s="14" t="s">
         <v>167</v>
       </c>
+      <c r="G190" s="11" t="s">
+        <v>510</v>
+      </c>
       <c r="I190" s="14">
         <v>0.34</v>
       </c>
     </row>
     <row r="191" spans="1:9" s="13" customFormat="1">
-      <c r="A191" s="76" t="s">
+      <c r="A191" s="75" t="s">
         <v>210</v>
       </c>
       <c r="B191" s="13" t="s">
@@ -11693,6 +11770,9 @@
       </c>
       <c r="F191" s="13" t="s">
         <v>128</v>
+      </c>
+      <c r="G191" s="75" t="s">
+        <v>210</v>
       </c>
       <c r="I191" s="37">
         <v>0.255</v>
@@ -11717,6 +11797,9 @@
       <c r="F192" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G192" s="20" t="s">
+        <v>211</v>
+      </c>
       <c r="I192" s="17">
         <v>0.08</v>
       </c>
@@ -11740,6 +11823,9 @@
       <c r="F193" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G193" s="20" t="s">
+        <v>212</v>
+      </c>
       <c r="I193" s="17">
         <v>0.16</v>
       </c>
@@ -11763,6 +11849,9 @@
       <c r="F194" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G194" s="20" t="s">
+        <v>213</v>
+      </c>
       <c r="I194" s="17">
         <v>0.22</v>
       </c>
@@ -11786,6 +11875,9 @@
       <c r="F195" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G195" s="20" t="s">
+        <v>214</v>
+      </c>
       <c r="I195" s="17">
         <v>0.28000000000000003</v>
       </c>
@@ -11809,6 +11901,9 @@
       <c r="F196" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G196" s="20" t="s">
+        <v>215</v>
+      </c>
       <c r="I196" s="17">
         <v>0.08</v>
       </c>
@@ -11832,6 +11927,9 @@
       <c r="F197" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G197" s="20" t="s">
+        <v>216</v>
+      </c>
       <c r="I197" s="17">
         <v>0.16</v>
       </c>
@@ -11855,6 +11953,9 @@
       <c r="F198" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G198" s="20" t="s">
+        <v>217</v>
+      </c>
       <c r="I198" s="17">
         <v>0.22</v>
       </c>
@@ -11878,6 +11979,9 @@
       <c r="F199" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G199" s="20" t="s">
+        <v>218</v>
+      </c>
       <c r="I199" s="17">
         <v>0.28000000000000003</v>
       </c>
@@ -11901,6 +12005,9 @@
       <c r="F200" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G200" s="20" t="s">
+        <v>219</v>
+      </c>
       <c r="I200" s="17">
         <v>0.08</v>
       </c>
@@ -11924,6 +12031,9 @@
       <c r="F201" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G201" s="20" t="s">
+        <v>220</v>
+      </c>
       <c r="I201" s="17">
         <v>0.16</v>
       </c>
@@ -11947,6 +12057,9 @@
       <c r="F202" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G202" s="20" t="s">
+        <v>221</v>
+      </c>
       <c r="I202" s="17">
         <v>0.22</v>
       </c>
@@ -11970,6 +12083,9 @@
       <c r="F203" s="5" t="s">
         <v>167</v>
       </c>
+      <c r="G203" s="20" t="s">
+        <v>222</v>
+      </c>
       <c r="I203" s="17">
         <v>0.28000000000000003</v>
       </c>
@@ -12162,7 +12278,7 @@
       </c>
     </row>
     <row r="212" spans="1:7" s="14" customFormat="1">
-      <c r="A212" s="77" t="s">
+      <c r="A212" s="76" t="s">
         <v>231</v>
       </c>
       <c r="B212" s="14" t="s">
@@ -12185,7 +12301,7 @@
       </c>
     </row>
     <row r="213" spans="1:7">
-      <c r="A213" s="72" t="s">
+      <c r="A213" s="71" t="s">
         <v>232</v>
       </c>
       <c r="B213" s="5" t="s">
@@ -12200,9 +12316,12 @@
       <c r="E213" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G213" s="71" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="214" spans="1:7">
-      <c r="A214" s="72" t="s">
+      <c r="A214" s="71" t="s">
         <v>233</v>
       </c>
       <c r="B214" s="5" t="s">
@@ -12217,9 +12336,12 @@
       <c r="E214" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G214" s="71" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="215" spans="1:7">
-      <c r="A215" s="72" t="s">
+      <c r="A215" s="71" t="s">
         <v>234</v>
       </c>
       <c r="B215" s="5" t="s">
@@ -12234,9 +12356,12 @@
       <c r="E215" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G215" s="71" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="216" spans="1:7">
-      <c r="A216" s="72" t="s">
+      <c r="A216" s="71" t="s">
         <v>235</v>
       </c>
       <c r="B216" s="5" t="s">
@@ -12251,9 +12376,12 @@
       <c r="E216" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G216" s="71" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="217" spans="1:7">
-      <c r="A217" s="72" t="s">
+      <c r="A217" s="71" t="s">
         <v>236</v>
       </c>
       <c r="B217" s="5" t="s">
@@ -12268,9 +12396,12 @@
       <c r="E217" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G217" s="71" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="218" spans="1:7">
-      <c r="A218" s="72" t="s">
+      <c r="A218" s="71" t="s">
         <v>237</v>
       </c>
       <c r="B218" s="5" t="s">
@@ -12285,9 +12416,12 @@
       <c r="E218" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G218" s="71" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="219" spans="1:7">
-      <c r="A219" s="72" t="s">
+      <c r="A219" s="71" t="s">
         <v>238</v>
       </c>
       <c r="B219" s="5" t="s">
@@ -12302,9 +12436,12 @@
       <c r="E219" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G219" s="71" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="220" spans="1:7">
-      <c r="A220" s="72" t="s">
+      <c r="A220" s="71" t="s">
         <v>239</v>
       </c>
       <c r="B220" s="5" t="s">
@@ -12319,9 +12456,12 @@
       <c r="E220" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G220" s="71" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="221" spans="1:7">
-      <c r="A221" s="72" t="s">
+      <c r="A221" s="71" t="s">
         <v>240</v>
       </c>
       <c r="B221" s="5" t="s">
@@ -12336,9 +12476,12 @@
       <c r="E221" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G221" s="71" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="222" spans="1:7">
-      <c r="A222" s="72" t="s">
+      <c r="A222" s="71" t="s">
         <v>241</v>
       </c>
       <c r="B222" s="5" t="s">
@@ -12353,9 +12496,12 @@
       <c r="E222" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G222" s="71" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="223" spans="1:7">
-      <c r="A223" s="72" t="s">
+      <c r="A223" s="71" t="s">
         <v>242</v>
       </c>
       <c r="B223" s="5" t="s">
@@ -12370,9 +12516,12 @@
       <c r="E223" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G223" s="71" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="224" spans="1:7">
-      <c r="A224" s="72" t="s">
+      <c r="A224" s="71" t="s">
         <v>243</v>
       </c>
       <c r="B224" s="5" t="s">
@@ -12387,9 +12536,12 @@
       <c r="E224" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G224" s="71" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="225" spans="1:14">
-      <c r="A225" s="72" t="s">
+      <c r="A225" s="71" t="s">
         <v>244</v>
       </c>
       <c r="B225" s="5" t="s">
@@ -12404,9 +12556,12 @@
       <c r="E225" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G225" s="71" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="226" spans="1:14">
-      <c r="A226" s="72" t="s">
+      <c r="A226" s="71" t="s">
         <v>245</v>
       </c>
       <c r="B226" s="5" t="s">
@@ -12421,9 +12576,12 @@
       <c r="E226" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G226" s="71" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="227" spans="1:14">
-      <c r="A227" s="72" t="s">
+      <c r="A227" s="71" t="s">
         <v>246</v>
       </c>
       <c r="B227" s="5" t="s">
@@ -12438,9 +12596,12 @@
       <c r="E227" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G227" s="71" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="228" spans="1:14">
-      <c r="A228" s="72" t="s">
+      <c r="A228" s="71" t="s">
         <v>247</v>
       </c>
       <c r="B228" s="5" t="s">
@@ -12455,9 +12616,12 @@
       <c r="E228" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G228" s="71" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="229" spans="1:14">
-      <c r="A229" s="72" t="s">
+      <c r="A229" s="71" t="s">
         <v>248</v>
       </c>
       <c r="B229" s="5" t="s">
@@ -12472,9 +12636,12 @@
       <c r="E229" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G229" s="71" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="230" spans="1:14">
-      <c r="A230" s="72" t="s">
+      <c r="A230" s="71" t="s">
         <v>249</v>
       </c>
       <c r="B230" s="5" t="s">
@@ -12489,9 +12656,12 @@
       <c r="E230" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G230" s="71" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="231" spans="1:14">
-      <c r="A231" s="72" t="s">
+      <c r="A231" s="71" t="s">
         <v>250</v>
       </c>
       <c r="B231" s="5" t="s">
@@ -12506,9 +12676,12 @@
       <c r="E231" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G231" s="71" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="232" spans="1:14">
-      <c r="A232" s="72" t="s">
+      <c r="A232" s="71" t="s">
         <v>251</v>
       </c>
       <c r="B232" s="5" t="s">
@@ -12523,9 +12696,12 @@
       <c r="E232" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G232" s="71" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="233" spans="1:14">
-      <c r="A233" s="72" t="s">
+      <c r="A233" s="71" t="s">
         <v>252</v>
       </c>
       <c r="B233" s="5" t="s">
@@ -12540,9 +12716,12 @@
       <c r="E233" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G233" s="71" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="234" spans="1:14">
-      <c r="A234" s="72" t="s">
+      <c r="A234" s="71" t="s">
         <v>253</v>
       </c>
       <c r="B234" s="5" t="s">
@@ -12557,9 +12736,12 @@
       <c r="E234" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G234" s="71" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="235" spans="1:14">
-      <c r="A235" s="72" t="s">
+      <c r="A235" s="71" t="s">
         <v>254</v>
       </c>
       <c r="B235" s="5" t="s">
@@ -12574,9 +12756,12 @@
       <c r="E235" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G235" s="71" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="236" spans="1:14">
-      <c r="A236" s="72" t="s">
+      <c r="A236" s="71" t="s">
         <v>255</v>
       </c>
       <c r="B236" s="5" t="s">
@@ -12591,9 +12776,12 @@
       <c r="E236" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G236" s="71" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="237" spans="1:14" ht="18">
-      <c r="A237" s="72" t="s">
+      <c r="A237" s="71" t="s">
         <v>256</v>
       </c>
       <c r="B237" s="5" t="s">
@@ -12609,7 +12797,7 @@
         <v>301</v>
       </c>
       <c r="G237" s="55" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H237" s="55"/>
       <c r="I237" s="55"/>
@@ -12620,7 +12808,7 @@
       <c r="N237" s="55"/>
     </row>
     <row r="238" spans="1:14" ht="19">
-      <c r="A238" s="72" t="s">
+      <c r="A238" s="71" t="s">
         <v>257</v>
       </c>
       <c r="B238" s="5" t="s">
@@ -12636,7 +12824,7 @@
         <v>301</v>
       </c>
       <c r="G238" s="55" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H238" s="55"/>
       <c r="I238" s="55"/>
@@ -12647,7 +12835,7 @@
       <c r="N238" s="55"/>
     </row>
     <row r="239" spans="1:14" ht="18">
-      <c r="A239" s="72" t="s">
+      <c r="A239" s="71" t="s">
         <v>258</v>
       </c>
       <c r="B239" s="5" t="s">
@@ -12663,7 +12851,7 @@
         <v>301</v>
       </c>
       <c r="G239" s="55" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H239" s="55"/>
       <c r="I239" s="55"/>
@@ -12674,7 +12862,7 @@
       <c r="N239" s="55"/>
     </row>
     <row r="240" spans="1:14">
-      <c r="A240" s="72" t="s">
+      <c r="A240" s="71" t="s">
         <v>259</v>
       </c>
       <c r="B240" s="5" t="s">
@@ -12689,9 +12877,12 @@
       <c r="E240" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G240" s="71" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="241" spans="1:14" ht="18">
-      <c r="A241" s="72" t="s">
+      <c r="A241" s="71" t="s">
         <v>260</v>
       </c>
       <c r="B241" s="5" t="s">
@@ -12707,7 +12898,7 @@
         <v>301</v>
       </c>
       <c r="G241" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H241" s="55"/>
       <c r="I241" s="55"/>
@@ -12718,7 +12909,7 @@
       <c r="N241" s="55"/>
     </row>
     <row r="242" spans="1:14" ht="18">
-      <c r="A242" s="72" t="s">
+      <c r="A242" s="71" t="s">
         <v>261</v>
       </c>
       <c r="B242" s="5" t="s">
@@ -12734,7 +12925,7 @@
         <v>301</v>
       </c>
       <c r="G242" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H242" s="55"/>
       <c r="I242" s="55"/>
@@ -12745,7 +12936,7 @@
       <c r="N242" s="55"/>
     </row>
     <row r="243" spans="1:14">
-      <c r="A243" s="72" t="s">
+      <c r="A243" s="71" t="s">
         <v>262</v>
       </c>
       <c r="B243" s="5" t="s">
@@ -12760,9 +12951,12 @@
       <c r="E243" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G243" s="71" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="244" spans="1:14" ht="18">
-      <c r="A244" s="72" t="s">
+      <c r="A244" s="71" t="s">
         <v>263</v>
       </c>
       <c r="B244" s="5" t="s">
@@ -12778,7 +12972,7 @@
         <v>301</v>
       </c>
       <c r="G244" s="56" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H244" s="56"/>
       <c r="I244" s="56"/>
@@ -12789,7 +12983,7 @@
       <c r="N244" s="56"/>
     </row>
     <row r="245" spans="1:14">
-      <c r="A245" s="72" t="s">
+      <c r="A245" s="71" t="s">
         <v>264</v>
       </c>
       <c r="B245" s="5" t="s">
@@ -12804,9 +12998,12 @@
       <c r="E245" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G245" s="71" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="246" spans="1:14" ht="18">
-      <c r="A246" s="72" t="s">
+      <c r="A246" s="71" t="s">
         <v>265</v>
       </c>
       <c r="B246" s="5" t="s">
@@ -12822,7 +13019,7 @@
         <v>301</v>
       </c>
       <c r="G246" s="57" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H246" s="57"/>
       <c r="I246" s="57"/>
@@ -12833,7 +13030,7 @@
       <c r="N246" s="57"/>
     </row>
     <row r="247" spans="1:14">
-      <c r="A247" s="72" t="s">
+      <c r="A247" s="71" t="s">
         <v>266</v>
       </c>
       <c r="B247" s="5" t="s">
@@ -12848,9 +13045,12 @@
       <c r="E247" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G247" s="71" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="248" spans="1:14" ht="18">
-      <c r="A248" s="72" t="s">
+      <c r="A248" s="71" t="s">
         <v>267</v>
       </c>
       <c r="B248" s="5" t="s">
@@ -12866,7 +13066,7 @@
         <v>301</v>
       </c>
       <c r="G248" s="57" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H248" s="57"/>
       <c r="I248" s="57"/>
@@ -12877,7 +13077,7 @@
       <c r="N248" s="57"/>
     </row>
     <row r="249" spans="1:14">
-      <c r="A249" s="72" t="s">
+      <c r="A249" s="71" t="s">
         <v>268</v>
       </c>
       <c r="B249" s="5" t="s">
@@ -12892,9 +13092,12 @@
       <c r="E249" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G249" s="71" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="250" spans="1:14" ht="18">
-      <c r="A250" s="72" t="s">
+      <c r="A250" s="71" t="s">
         <v>269</v>
       </c>
       <c r="B250" s="5" t="s">
@@ -12910,7 +13113,7 @@
         <v>301</v>
       </c>
       <c r="G250" s="57" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H250" s="57"/>
       <c r="I250" s="57"/>
@@ -12921,7 +13124,7 @@
       <c r="N250" s="57"/>
     </row>
     <row r="251" spans="1:14">
-      <c r="A251" s="72" t="s">
+      <c r="A251" s="71" t="s">
         <v>270</v>
       </c>
       <c r="B251" s="5" t="s">
@@ -12936,9 +13139,12 @@
       <c r="E251" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G251" s="71" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="252" spans="1:14" ht="18">
-      <c r="A252" s="72" t="s">
+      <c r="A252" s="71" t="s">
         <v>271</v>
       </c>
       <c r="B252" s="5" t="s">
@@ -12954,7 +13160,7 @@
         <v>301</v>
       </c>
       <c r="G252" s="57" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H252" s="57"/>
       <c r="I252" s="57"/>
@@ -12965,7 +13171,7 @@
       <c r="N252" s="57"/>
     </row>
     <row r="253" spans="1:14" ht="18">
-      <c r="A253" s="72" t="s">
+      <c r="A253" s="71" t="s">
         <v>272</v>
       </c>
       <c r="B253" s="5" t="s">
@@ -12981,7 +13187,7 @@
         <v>301</v>
       </c>
       <c r="G253" s="57" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H253" s="57"/>
       <c r="I253" s="57"/>
@@ -12992,7 +13198,7 @@
       <c r="N253" s="57"/>
     </row>
     <row r="254" spans="1:14">
-      <c r="A254" s="72" t="s">
+      <c r="A254" s="71" t="s">
         <v>70</v>
       </c>
       <c r="B254" s="5" t="s">
@@ -13007,9 +13213,12 @@
       <c r="E254" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G254" s="71" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="255" spans="1:14">
-      <c r="A255" s="72" t="s">
+      <c r="A255" s="71" t="s">
         <v>71</v>
       </c>
       <c r="B255" s="5" t="s">
@@ -13024,9 +13233,12 @@
       <c r="E255" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G255" s="71" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="256" spans="1:14">
-      <c r="A256" s="72" t="s">
+      <c r="A256" s="71" t="s">
         <v>72</v>
       </c>
       <c r="B256" s="5" t="s">
@@ -13041,9 +13253,12 @@
       <c r="E256" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G256" s="71" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="257" spans="1:8">
-      <c r="A257" s="72" t="s">
+      <c r="A257" s="71" t="s">
         <v>73</v>
       </c>
       <c r="B257" s="5" t="s">
@@ -13058,9 +13273,12 @@
       <c r="E257" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G257" s="71" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="258" spans="1:8">
-      <c r="A258" s="72" t="s">
+      <c r="A258" s="71" t="s">
         <v>74</v>
       </c>
       <c r="B258" s="5" t="s">
@@ -13075,419 +13293,422 @@
       <c r="E258" s="6" t="s">
         <v>301</v>
       </c>
+      <c r="G258" s="71" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="259" spans="1:8" s="13" customFormat="1">
-      <c r="A259" s="78" t="s">
+      <c r="A259" s="77" t="s">
+        <v>455</v>
+      </c>
+      <c r="B259" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C259" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D259" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E259" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="G259" s="77" t="s">
+        <v>476</v>
+      </c>
+      <c r="H259" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260" s="77" t="s">
         <v>456</v>
       </c>
-      <c r="B259" s="13" t="s">
+      <c r="B260" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C260" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C259" s="35" t="s">
+      <c r="D260" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E260" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D259" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E259" s="6" t="s">
+      <c r="G260" s="77" t="s">
         <v>476</v>
       </c>
-      <c r="G259" s="78" t="s">
+      <c r="H260" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261" s="77" t="s">
+        <v>457</v>
+      </c>
+      <c r="B261" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C261" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D261" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="G261" s="77" t="s">
+        <v>476</v>
+      </c>
+      <c r="H261" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262" s="77" t="s">
+        <v>458</v>
+      </c>
+      <c r="B262" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C262" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D262" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="G262" s="77" t="s">
         <v>477</v>
       </c>
-      <c r="H259" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8">
-      <c r="A260" s="78" t="s">
-        <v>457</v>
-      </c>
-      <c r="B260" s="13" t="s">
+      <c r="H262" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" s="77" t="s">
+        <v>459</v>
+      </c>
+      <c r="B263" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C263" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C260" s="35" t="s">
+      <c r="D263" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E263" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D260" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E260" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G260" s="78" t="s">
+      <c r="G263" s="77" t="s">
         <v>477</v>
       </c>
-      <c r="H260" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8">
-      <c r="A261" s="78" t="s">
-        <v>458</v>
-      </c>
-      <c r="B261" s="13" t="s">
+      <c r="H263" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264" s="77" t="s">
+        <v>460</v>
+      </c>
+      <c r="B264" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C264" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C261" s="35" t="s">
+      <c r="D264" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E264" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D261" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E261" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G261" s="78" t="s">
+      <c r="G264" s="77" t="s">
         <v>477</v>
       </c>
-      <c r="H261" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8">
-      <c r="A262" s="78" t="s">
-        <v>459</v>
-      </c>
-      <c r="B262" s="13" t="s">
+      <c r="H264" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265" s="77" t="s">
+        <v>461</v>
+      </c>
+      <c r="B265" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C265" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C262" s="35" t="s">
+      <c r="D265" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E265" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D262" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E262" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G262" s="78" t="s">
+      <c r="G265" s="77" t="s">
+        <v>477</v>
+      </c>
+      <c r="H265" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" s="77" t="s">
+        <v>462</v>
+      </c>
+      <c r="B266" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C266" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="D266" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E266" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="G266" s="77" t="s">
         <v>478</v>
       </c>
-      <c r="H262" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8">
-      <c r="A263" s="78" t="s">
-        <v>460</v>
-      </c>
-      <c r="B263" s="13" t="s">
+      <c r="H266" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" s="77" t="s">
+        <v>463</v>
+      </c>
+      <c r="B267" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C267" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C263" s="35" t="s">
+      <c r="D267" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E267" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D263" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E263" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G263" s="78" t="s">
+      <c r="G267" s="77" t="s">
         <v>478</v>
       </c>
-      <c r="H263" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8">
-      <c r="A264" s="78" t="s">
-        <v>461</v>
-      </c>
-      <c r="B264" s="13" t="s">
+      <c r="H267" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268" s="77" t="s">
+        <v>464</v>
+      </c>
+      <c r="B268" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C268" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C264" s="35" t="s">
+      <c r="D268" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E268" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D264" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E264" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G264" s="78" t="s">
+      <c r="G268" s="77" t="s">
         <v>478</v>
       </c>
-      <c r="H264" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8">
-      <c r="A265" s="78" t="s">
-        <v>462</v>
-      </c>
-      <c r="B265" s="13" t="s">
+      <c r="H268" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8">
+      <c r="A269" s="77" t="s">
+        <v>465</v>
+      </c>
+      <c r="B269" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C269" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C265" s="35" t="s">
+      <c r="D269" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E269" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D265" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E265" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G265" s="78" t="s">
+      <c r="G269" s="77" t="s">
         <v>478</v>
       </c>
-      <c r="H265" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8">
-      <c r="A266" s="78" t="s">
-        <v>463</v>
-      </c>
-      <c r="B266" s="13" t="s">
+      <c r="H269" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8">
+      <c r="A270" s="77" t="s">
+        <v>466</v>
+      </c>
+      <c r="B270" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C270" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C266" s="35" t="s">
+      <c r="D270" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E270" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D266" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E266" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G266" s="78" t="s">
+      <c r="G270" s="77" t="s">
         <v>479</v>
       </c>
-      <c r="H266" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8">
-      <c r="A267" s="78" t="s">
-        <v>464</v>
-      </c>
-      <c r="B267" s="13" t="s">
+      <c r="H270" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8">
+      <c r="A271" s="77" t="s">
+        <v>467</v>
+      </c>
+      <c r="B271" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C271" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C267" s="35" t="s">
+      <c r="D271" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E271" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D267" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E267" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G267" s="78" t="s">
+      <c r="G271" s="77" t="s">
         <v>479</v>
       </c>
-      <c r="H267" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8">
-      <c r="A268" s="78" t="s">
-        <v>465</v>
-      </c>
-      <c r="B268" s="13" t="s">
+      <c r="H271" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8">
+      <c r="A272" s="77" t="s">
+        <v>468</v>
+      </c>
+      <c r="B272" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C272" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C268" s="35" t="s">
+      <c r="D272" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E272" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D268" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E268" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G268" s="78" t="s">
+      <c r="G272" s="77" t="s">
         <v>479</v>
       </c>
-      <c r="H268" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8">
-      <c r="A269" s="78" t="s">
-        <v>466</v>
-      </c>
-      <c r="B269" s="13" t="s">
+      <c r="H272" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9">
+      <c r="A273" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="B273" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C273" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C269" s="35" t="s">
+      <c r="D273" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E273" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D269" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E269" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G269" s="78" t="s">
+      <c r="G273" s="77" t="s">
         <v>479</v>
       </c>
-      <c r="H269" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8">
-      <c r="A270" s="78" t="s">
-        <v>467</v>
-      </c>
-      <c r="B270" s="13" t="s">
+      <c r="H273" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9">
+      <c r="A274" s="77" t="s">
+        <v>470</v>
+      </c>
+      <c r="B274" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C274" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C270" s="35" t="s">
+      <c r="D274" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E274" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D270" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E270" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G270" s="78" t="s">
+      <c r="G274" s="77" t="s">
         <v>480</v>
       </c>
-      <c r="H270" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8">
-      <c r="A271" s="78" t="s">
-        <v>468</v>
-      </c>
-      <c r="B271" s="13" t="s">
+      <c r="H274" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9">
+      <c r="A275" s="77" t="s">
+        <v>471</v>
+      </c>
+      <c r="B275" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C275" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C271" s="35" t="s">
+      <c r="D275" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E275" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D271" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E271" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G271" s="78" t="s">
+      <c r="G275" s="77" t="s">
         <v>480</v>
       </c>
-      <c r="H271" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8">
-      <c r="A272" s="78" t="s">
-        <v>469</v>
-      </c>
-      <c r="B272" s="13" t="s">
+      <c r="H275" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9">
+      <c r="A276" s="77" t="s">
+        <v>472</v>
+      </c>
+      <c r="B276" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="C276" s="35" t="s">
         <v>474</v>
       </c>
-      <c r="C272" s="35" t="s">
+      <c r="D276" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E276" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="D272" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E272" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G272" s="78" t="s">
+      <c r="G276" s="77" t="s">
         <v>480</v>
       </c>
-      <c r="H272" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9">
-      <c r="A273" s="78" t="s">
-        <v>470</v>
-      </c>
-      <c r="B273" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="C273" s="35" t="s">
-        <v>475</v>
-      </c>
-      <c r="D273" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E273" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G273" s="78" t="s">
-        <v>480</v>
-      </c>
-      <c r="H273" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9">
-      <c r="A274" s="78" t="s">
-        <v>471</v>
-      </c>
-      <c r="B274" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="C274" s="35" t="s">
-        <v>475</v>
-      </c>
-      <c r="D274" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E274" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G274" s="78" t="s">
+      <c r="H276" s="13" t="s">
         <v>481</v>
-      </c>
-      <c r="H274" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9">
-      <c r="A275" s="78" t="s">
-        <v>472</v>
-      </c>
-      <c r="B275" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="C275" s="35" t="s">
-        <v>475</v>
-      </c>
-      <c r="D275" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E275" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G275" s="78" t="s">
-        <v>481</v>
-      </c>
-      <c r="H275" s="13" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9">
-      <c r="A276" s="78" t="s">
-        <v>473</v>
-      </c>
-      <c r="B276" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="C276" s="35" t="s">
-        <v>475</v>
-      </c>
-      <c r="D276" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E276" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G276" s="78" t="s">
-        <v>481</v>
-      </c>
-      <c r="H276" s="13" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="277" spans="1:9" s="15" customFormat="1">
@@ -13509,6 +13730,9 @@
       <c r="F277" s="15" t="s">
         <v>128</v>
       </c>
+      <c r="G277" s="7" t="s">
+        <v>276</v>
+      </c>
       <c r="I277" s="41">
         <v>0.52</v>
       </c>
@@ -13532,6 +13756,9 @@
       <c r="F278" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G278" s="7" t="s">
+        <v>277</v>
+      </c>
       <c r="I278" s="41">
         <v>0.12</v>
       </c>
@@ -13555,6 +13782,9 @@
       <c r="F279" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G279" s="7" t="s">
+        <v>278</v>
+      </c>
       <c r="I279" s="41">
         <v>0.18</v>
       </c>
@@ -13578,6 +13808,9 @@
       <c r="F280" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G280" s="7" t="s">
+        <v>279</v>
+      </c>
       <c r="I280" s="41">
         <v>0.23</v>
       </c>
@@ -13601,6 +13834,9 @@
       <c r="F281" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G281" s="7" t="s">
+        <v>280</v>
+      </c>
       <c r="I281" s="41">
         <v>0.34</v>
       </c>
@@ -13624,6 +13860,9 @@
       <c r="F282" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G282" s="7" t="s">
+        <v>281</v>
+      </c>
       <c r="I282" s="41">
         <v>0.45</v>
       </c>
@@ -13647,6 +13886,9 @@
       <c r="F283" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G283" s="7" t="s">
+        <v>282</v>
+      </c>
       <c r="I283" s="41">
         <v>0.12</v>
       </c>
@@ -13670,6 +13912,9 @@
       <c r="F284" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G284" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="I284" s="41">
         <v>0.18</v>
       </c>
@@ -13693,6 +13938,9 @@
       <c r="F285" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G285" s="7" t="s">
+        <v>284</v>
+      </c>
       <c r="I285" s="41">
         <v>0.23</v>
       </c>
@@ -13716,6 +13964,9 @@
       <c r="F286" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G286" s="7" t="s">
+        <v>285</v>
+      </c>
       <c r="I286" s="41">
         <v>0.34</v>
       </c>
@@ -13739,6 +13990,9 @@
       <c r="F287" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G287" s="7" t="s">
+        <v>286</v>
+      </c>
       <c r="I287" s="41">
         <v>0.45</v>
       </c>
@@ -13762,6 +14016,9 @@
       <c r="F288" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G288" s="7" t="s">
+        <v>287</v>
+      </c>
       <c r="I288" s="41">
         <v>0.12</v>
       </c>
@@ -13785,6 +14042,9 @@
       <c r="F289" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G289" s="7" t="s">
+        <v>288</v>
+      </c>
       <c r="I289" s="41">
         <v>0.18</v>
       </c>
@@ -13808,6 +14068,9 @@
       <c r="F290" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G290" s="7" t="s">
+        <v>289</v>
+      </c>
       <c r="I290" s="41">
         <v>0.23</v>
       </c>
@@ -13831,6 +14094,9 @@
       <c r="F291" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G291" s="7" t="s">
+        <v>290</v>
+      </c>
       <c r="I291" s="41">
         <v>0.34</v>
       </c>
@@ -13854,6 +14120,9 @@
       <c r="F292" s="15" t="s">
         <v>167</v>
       </c>
+      <c r="G292" s="7" t="s">
+        <v>291</v>
+      </c>
       <c r="I292" s="41">
         <v>0.45</v>
       </c>
@@ -13877,7 +14146,7 @@
       <c r="F293" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G293" s="64" t="s">
+      <c r="G293" s="63" t="s">
         <v>376</v>
       </c>
     </row>
@@ -13900,7 +14169,7 @@
       <c r="F294" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G294" s="64" t="s">
+      <c r="G294" s="63" t="s">
         <v>376</v>
       </c>
     </row>
@@ -13923,7 +14192,7 @@
       <c r="F295" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G295" s="64" t="s">
+      <c r="G295" s="63" t="s">
         <v>376</v>
       </c>
     </row>
@@ -13946,7 +14215,7 @@
       <c r="F296" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G296" s="64" t="s">
+      <c r="G296" s="63" t="s">
         <v>377</v>
       </c>
     </row>
@@ -13969,7 +14238,7 @@
       <c r="F297" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G297" s="64" t="s">
+      <c r="G297" s="63" t="s">
         <v>377</v>
       </c>
     </row>
@@ -13992,7 +14261,7 @@
       <c r="F298" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G298" s="64" t="s">
+      <c r="G298" s="63" t="s">
         <v>377</v>
       </c>
     </row>
@@ -14015,7 +14284,7 @@
       <c r="F299" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G299" s="64" t="s">
+      <c r="G299" s="63" t="s">
         <v>378</v>
       </c>
     </row>
@@ -14038,7 +14307,7 @@
       <c r="F300" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G300" s="64" t="s">
+      <c r="G300" s="63" t="s">
         <v>378</v>
       </c>
     </row>
@@ -14061,11 +14330,12 @@
       <c r="F301" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G301" s="64" t="s">
+      <c r="G301" s="63" t="s">
         <v>378</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="G1:G301" xr:uid="{7E8F22EE-2E06-6741-B451-D4EA064EAB2E}"/>
   <phoneticPr fontId="26" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C159" r:id="rId1" xr:uid="{BF63034B-E53E-AA4F-9F22-3EC9CCE474BD}"/>

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/large_scale_yeast_proteomics_analysis/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA4A4FF-7155-8F45-844E-1CF31281AA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303BC07C-3556-1F49-99C3-9F24995A3E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="26000" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="517">
   <si>
     <t>sample</t>
   </si>
@@ -1040,9 +1040,6 @@
   </si>
   <si>
     <t>Joao A Paulo</t>
-  </si>
-  <si>
-    <t>Joao A. Paulo</t>
   </si>
   <si>
     <t>https://doi.org/10.1016/j.jprot.2016.07.005</t>
@@ -3135,7 +3132,7 @@
   <sheetData>
     <row r="1" spans="1:31" s="28" customFormat="1" ht="19">
       <c r="A1" s="28" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B1" s="28" t="s">
         <v>105</v>
@@ -3153,7 +3150,7 @@
         <v>127</v>
       </c>
       <c r="G1" s="78" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1" s="28" t="s">
         <v>171</v>
@@ -3230,10 +3227,10 @@
     </row>
     <row r="2" spans="1:31" s="13" customFormat="1">
       <c r="A2" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>325</v>
@@ -3242,13 +3239,13 @@
         <v>169</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>128</v>
       </c>
       <c r="G2" s="58" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>172</v>
@@ -3262,10 +3259,10 @@
     </row>
     <row r="3" spans="1:31">
       <c r="A3" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>325</v>
@@ -3274,13 +3271,13 @@
         <v>169</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>128</v>
       </c>
       <c r="G3" s="59" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>172</v>
@@ -3294,10 +3291,10 @@
     </row>
     <row r="4" spans="1:31">
       <c r="A4" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>325</v>
@@ -3306,13 +3303,13 @@
         <v>169</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>128</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>172</v>
@@ -3326,10 +3323,10 @@
     </row>
     <row r="5" spans="1:31">
       <c r="A5" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>325</v>
@@ -3338,11 +3335,11 @@
         <v>169</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="59" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H5" s="12"/>
       <c r="W5" s="30"/>
@@ -3350,10 +3347,10 @@
     </row>
     <row r="6" spans="1:31">
       <c r="A6" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>325</v>
@@ -3362,11 +3359,11 @@
         <v>169</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="59" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H6" s="12"/>
       <c r="W6" s="30"/>
@@ -3374,10 +3371,10 @@
     </row>
     <row r="7" spans="1:31">
       <c r="A7" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>325</v>
@@ -3386,11 +3383,11 @@
         <v>169</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="59" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H7" s="12"/>
       <c r="W7" s="30"/>
@@ -3398,10 +3395,10 @@
     </row>
     <row r="8" spans="1:31">
       <c r="A8" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>325</v>
@@ -3410,11 +3407,11 @@
         <v>169</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="59" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H8" s="12"/>
       <c r="W8" s="30"/>
@@ -3422,10 +3419,10 @@
     </row>
     <row r="9" spans="1:31">
       <c r="A9" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>325</v>
@@ -3434,11 +3431,11 @@
         <v>169</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="59" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H9" s="12"/>
       <c r="W9" s="30"/>
@@ -3446,10 +3443,10 @@
     </row>
     <row r="10" spans="1:31" s="14" customFormat="1">
       <c r="A10" s="11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>325</v>
@@ -3458,11 +3455,11 @@
         <v>169</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="60" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H10" s="23"/>
       <c r="W10" s="31"/>
@@ -3473,7 +3470,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C11" s="25" t="s">
         <v>310</v>
@@ -3482,7 +3479,7 @@
         <v>170</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F11" s="25" t="s">
         <v>128</v>
@@ -3532,7 +3529,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>324</v>
@@ -3541,13 +3538,13 @@
         <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>172</v>
@@ -3618,7 +3615,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>324</v>
@@ -3627,13 +3624,13 @@
         <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G13" s="59" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>172</v>
@@ -3704,7 +3701,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>324</v>
@@ -3713,13 +3710,13 @@
         <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>172</v>
@@ -3790,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>324</v>
@@ -3799,13 +3796,13 @@
         <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>172</v>
@@ -3876,7 +3873,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>324</v>
@@ -3885,13 +3882,13 @@
         <v>170</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G16" s="59" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>172</v>
@@ -3962,7 +3959,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>324</v>
@@ -3971,13 +3968,13 @@
         <v>170</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G17" s="59" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>172</v>
@@ -4048,7 +4045,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>324</v>
@@ -4057,13 +4054,13 @@
         <v>170</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>172</v>
@@ -4134,7 +4131,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>324</v>
@@ -4143,13 +4140,13 @@
         <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G19" s="59" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>172</v>
@@ -4220,7 +4217,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>324</v>
@@ -4229,13 +4226,13 @@
         <v>170</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>172</v>
@@ -4306,7 +4303,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>324</v>
@@ -4315,13 +4312,13 @@
         <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G21" s="59" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>172</v>
@@ -4392,7 +4389,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>324</v>
@@ -4401,13 +4398,13 @@
         <v>170</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>172</v>
@@ -4478,7 +4475,7 @@
         <v>26</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>324</v>
@@ -4487,13 +4484,13 @@
         <v>170</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G23" s="59" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>172</v>
@@ -4564,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>324</v>
@@ -4573,13 +4570,13 @@
         <v>170</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G24" s="59" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>172</v>
@@ -4650,7 +4647,7 @@
         <v>28</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>324</v>
@@ -4659,13 +4656,13 @@
         <v>170</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G25" s="59" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>172</v>
@@ -4736,7 +4733,7 @@
         <v>29</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>324</v>
@@ -4745,13 +4742,13 @@
         <v>170</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G26" s="59" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>172</v>
@@ -4822,7 +4819,7 @@
         <v>30</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>324</v>
@@ -4831,13 +4828,13 @@
         <v>170</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G27" s="59" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>172</v>
@@ -4908,7 +4905,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>324</v>
@@ -4917,13 +4914,13 @@
         <v>170</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G28" s="59" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>172</v>
@@ -4994,7 +4991,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>324</v>
@@ -5003,13 +5000,13 @@
         <v>170</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G29" s="59" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>172</v>
@@ -5080,7 +5077,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>324</v>
@@ -5089,13 +5086,13 @@
         <v>170</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G30" s="59" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>172</v>
@@ -5166,7 +5163,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>324</v>
@@ -5175,13 +5172,13 @@
         <v>170</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G31" s="59" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>172</v>
@@ -5252,7 +5249,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>324</v>
@@ -5261,13 +5258,13 @@
         <v>170</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G32" s="59" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>172</v>
@@ -5338,7 +5335,7 @@
         <v>36</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>324</v>
@@ -5347,13 +5344,13 @@
         <v>170</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G33" s="59" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>172</v>
@@ -5427,7 +5424,7 @@
         <v>37</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>324</v>
@@ -5436,13 +5433,13 @@
         <v>170</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G34" s="59" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>172</v>
@@ -5516,7 +5513,7 @@
         <v>38</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>324</v>
@@ -5525,13 +5522,13 @@
         <v>170</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G35" s="59" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>172</v>
@@ -5605,7 +5602,7 @@
         <v>39</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>324</v>
@@ -5614,13 +5611,13 @@
         <v>170</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G36" s="59" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>172</v>
@@ -5694,7 +5691,7 @@
         <v>40</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>324</v>
@@ -5703,13 +5700,13 @@
         <v>170</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G37" s="59" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>172</v>
@@ -5783,7 +5780,7 @@
         <v>41</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>324</v>
@@ -5792,13 +5789,13 @@
         <v>170</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G38" s="59" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>172</v>
@@ -5872,7 +5869,7 @@
         <v>42</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>324</v>
@@ -5881,13 +5878,13 @@
         <v>170</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G39" s="59" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H39" s="12" t="s">
         <v>172</v>
@@ -5958,7 +5955,7 @@
         <v>43</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>324</v>
@@ -5967,13 +5964,13 @@
         <v>170</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G40" s="59" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>172</v>
@@ -6044,7 +6041,7 @@
         <v>44</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>324</v>
@@ -6053,13 +6050,13 @@
         <v>170</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G41" s="59" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>172</v>
@@ -6130,7 +6127,7 @@
         <v>45</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>324</v>
@@ -6139,13 +6136,13 @@
         <v>170</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G42" s="59" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>172</v>
@@ -6216,7 +6213,7 @@
         <v>46</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>324</v>
@@ -6225,13 +6222,13 @@
         <v>170</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G43" s="59" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>172</v>
@@ -6302,7 +6299,7 @@
         <v>47</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>324</v>
@@ -6311,13 +6308,13 @@
         <v>170</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G44" s="59" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>172</v>
@@ -6388,7 +6385,7 @@
         <v>48</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>324</v>
@@ -6397,13 +6394,13 @@
         <v>170</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G45" s="59" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>172</v>
@@ -6474,7 +6471,7 @@
         <v>49</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>324</v>
@@ -6483,13 +6480,13 @@
         <v>170</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G46" s="59" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>172</v>
@@ -6560,7 +6557,7 @@
         <v>50</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>324</v>
@@ -6569,13 +6566,13 @@
         <v>170</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G47" s="59" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>172</v>
@@ -6646,7 +6643,7 @@
         <v>51</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>324</v>
@@ -6655,13 +6652,13 @@
         <v>170</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G48" s="59" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H48" s="12" t="s">
         <v>172</v>
@@ -6732,7 +6729,7 @@
         <v>52</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>324</v>
@@ -6741,13 +6738,13 @@
         <v>170</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G49" s="59" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H49" s="12" t="s">
         <v>172</v>
@@ -6818,7 +6815,7 @@
         <v>53</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>324</v>
@@ -6827,13 +6824,13 @@
         <v>170</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G50" s="59" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H50" s="12" t="s">
         <v>172</v>
@@ -6904,7 +6901,7 @@
         <v>54</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>324</v>
@@ -6913,13 +6910,13 @@
         <v>170</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G51" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H51" s="12" t="s">
         <v>172</v>
@@ -6990,7 +6987,7 @@
         <v>55</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>324</v>
@@ -6999,13 +6996,13 @@
         <v>170</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G52" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H52" s="12" t="s">
         <v>172</v>
@@ -7076,7 +7073,7 @@
         <v>56</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>324</v>
@@ -7085,13 +7082,13 @@
         <v>170</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>167</v>
       </c>
       <c r="G53" s="59" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H53" s="12" t="s">
         <v>172</v>
@@ -7162,10 +7159,10 @@
         <v>57</v>
       </c>
       <c r="B54" s="79" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C54" s="79" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D54" s="79" t="s">
         <v>169</v>
@@ -7186,10 +7183,10 @@
     </row>
     <row r="55" spans="1:30" s="13" customFormat="1">
       <c r="A55" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>326</v>
@@ -7224,10 +7221,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>326</v>
@@ -7262,10 +7259,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>326</v>
@@ -7300,10 +7297,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>326</v>
@@ -7338,10 +7335,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>326</v>
@@ -7379,10 +7376,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>326</v>
@@ -7420,10 +7417,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>326</v>
@@ -7461,10 +7458,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>326</v>
@@ -7502,10 +7499,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>326</v>
@@ -7543,10 +7540,10 @@
     </row>
     <row r="64" spans="1:30" s="14" customFormat="1">
       <c r="A64" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>326</v>
@@ -7710,7 +7707,7 @@
         <v>167</v>
       </c>
       <c r="G69" s="67" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H69" s="6"/>
     </row>
@@ -7734,7 +7731,7 @@
         <v>167</v>
       </c>
       <c r="G70" s="67" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H70" s="6"/>
     </row>
@@ -7758,7 +7755,7 @@
         <v>167</v>
       </c>
       <c r="G71" s="67" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H71" s="6"/>
     </row>
@@ -7782,16 +7779,16 @@
         <v>167</v>
       </c>
       <c r="G72" s="67" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H72" s="6"/>
     </row>
     <row r="73" spans="1:30" s="29" customFormat="1">
       <c r="A73" s="68" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>327</v>
@@ -7841,10 +7838,10 @@
     </row>
     <row r="74" spans="1:30" s="30" customFormat="1">
       <c r="A74" s="69" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>327</v>
@@ -7894,10 +7891,10 @@
     </row>
     <row r="75" spans="1:30" s="30" customFormat="1">
       <c r="A75" s="69" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>327</v>
@@ -7947,13 +7944,13 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" s="69" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>170</v>
@@ -8000,13 +7997,13 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" s="69" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>170</v>
@@ -8053,13 +8050,13 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" s="69" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>170</v>
@@ -8106,13 +8103,13 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" s="69" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>170</v>
@@ -8159,13 +8156,13 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" s="69" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>170</v>
@@ -8212,13 +8209,13 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" s="69" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>170</v>
@@ -8265,13 +8262,13 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>170</v>
@@ -8318,13 +8315,13 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" s="69" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>170</v>
@@ -8371,13 +8368,13 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" s="69" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>170</v>
@@ -8424,13 +8421,13 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" s="69" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>170</v>
@@ -8477,13 +8474,13 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" s="69" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>170</v>
@@ -8530,13 +8527,13 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" s="69" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>170</v>
@@ -8583,13 +8580,13 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" s="69" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>170</v>
@@ -8636,13 +8633,13 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" s="69" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>170</v>
@@ -8689,13 +8686,13 @@
     </row>
     <row r="90" spans="1:30">
       <c r="A90" s="69" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>170</v>
@@ -8742,13 +8739,13 @@
     </row>
     <row r="91" spans="1:30">
       <c r="A91" s="69" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>170</v>
@@ -8795,13 +8792,13 @@
     </row>
     <row r="92" spans="1:30">
       <c r="A92" s="69" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>170</v>
@@ -8848,13 +8845,13 @@
     </row>
     <row r="93" spans="1:30">
       <c r="A93" s="69" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>170</v>
@@ -8901,13 +8898,13 @@
     </row>
     <row r="94" spans="1:30">
       <c r="A94" s="69" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>170</v>
@@ -8954,13 +8951,13 @@
     </row>
     <row r="95" spans="1:30">
       <c r="A95" s="69" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>170</v>
@@ -9007,13 +9004,13 @@
     </row>
     <row r="96" spans="1:30">
       <c r="A96" s="69" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>170</v>
@@ -9060,13 +9057,13 @@
     </row>
     <row r="97" spans="1:30">
       <c r="A97" s="69" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>170</v>
@@ -9113,13 +9110,13 @@
     </row>
     <row r="98" spans="1:30">
       <c r="A98" s="69" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>170</v>
@@ -9166,13 +9163,13 @@
     </row>
     <row r="99" spans="1:30" s="14" customFormat="1">
       <c r="A99" s="70" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D99" s="11" t="s">
         <v>170</v>
@@ -9222,7 +9219,7 @@
         <v>106</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>328</v>
@@ -9251,7 +9248,7 @@
         <v>107</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>328</v>
@@ -9280,7 +9277,7 @@
         <v>108</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>328</v>
@@ -9309,7 +9306,7 @@
         <v>109</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>328</v>
@@ -9338,7 +9335,7 @@
         <v>110</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>328</v>
@@ -9367,7 +9364,7 @@
         <v>111</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>328</v>
@@ -9396,7 +9393,7 @@
         <v>112</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>328</v>
@@ -9425,7 +9422,7 @@
         <v>113</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>328</v>
@@ -9454,7 +9451,7 @@
         <v>114</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>328</v>
@@ -9483,7 +9480,7 @@
         <v>115</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>328</v>
@@ -9511,11 +9508,11 @@
       <c r="A110" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B110" s="13" t="s">
+      <c r="B110" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C110" s="35" t="s">
         <v>330</v>
-      </c>
-      <c r="C110" s="35" t="s">
-        <v>331</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>170</v>
@@ -9527,7 +9524,7 @@
         <v>128</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H110" s="13" t="s">
         <v>209</v>
@@ -9544,10 +9541,10 @@
         <v>117</v>
       </c>
       <c r="B111" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C111" s="27" t="s">
         <v>330</v>
-      </c>
-      <c r="C111" s="27" t="s">
-        <v>331</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>170</v>
@@ -9559,7 +9556,7 @@
         <v>128</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>209</v>
@@ -9576,10 +9573,10 @@
         <v>118</v>
       </c>
       <c r="B112" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C112" s="27" t="s">
         <v>330</v>
-      </c>
-      <c r="C112" s="27" t="s">
-        <v>331</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>170</v>
@@ -9591,7 +9588,7 @@
         <v>128</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H112" s="5" t="s">
         <v>209</v>
@@ -9608,10 +9605,10 @@
         <v>119</v>
       </c>
       <c r="B113" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C113" s="27" t="s">
         <v>330</v>
-      </c>
-      <c r="C113" s="27" t="s">
-        <v>331</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>170</v>
@@ -9623,7 +9620,7 @@
         <v>128</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H113" s="5" t="s">
         <v>209</v>
@@ -9640,10 +9637,10 @@
         <v>120</v>
       </c>
       <c r="B114" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C114" s="27" t="s">
         <v>330</v>
-      </c>
-      <c r="C114" s="27" t="s">
-        <v>331</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>170</v>
@@ -9655,7 +9652,7 @@
         <v>128</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H114" s="5" t="s">
         <v>209</v>
@@ -9672,10 +9669,10 @@
         <v>121</v>
       </c>
       <c r="B115" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C115" s="27" t="s">
         <v>330</v>
-      </c>
-      <c r="C115" s="27" t="s">
-        <v>331</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>170</v>
@@ -9687,7 +9684,7 @@
         <v>128</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H115" s="5" t="s">
         <v>209</v>
@@ -9704,10 +9701,10 @@
         <v>122</v>
       </c>
       <c r="B116" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C116" s="27" t="s">
         <v>330</v>
-      </c>
-      <c r="C116" s="27" t="s">
-        <v>331</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>170</v>
@@ -9719,7 +9716,7 @@
         <v>128</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H116" s="5" t="s">
         <v>209</v>
@@ -9736,10 +9733,10 @@
         <v>123</v>
       </c>
       <c r="B117" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C117" s="27" t="s">
         <v>330</v>
-      </c>
-      <c r="C117" s="27" t="s">
-        <v>331</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>170</v>
@@ -9751,7 +9748,7 @@
         <v>128</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H117" s="5" t="s">
         <v>209</v>
@@ -9768,10 +9765,10 @@
         <v>124</v>
       </c>
       <c r="B118" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C118" s="27" t="s">
         <v>330</v>
-      </c>
-      <c r="C118" s="27" t="s">
-        <v>331</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>170</v>
@@ -9783,7 +9780,7 @@
         <v>128</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H118" s="5" t="s">
         <v>209</v>
@@ -9803,7 +9800,7 @@
         <v>329</v>
       </c>
       <c r="C119" s="27" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>170</v>
@@ -9815,7 +9812,7 @@
         <v>128</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>209</v>
@@ -9835,7 +9832,7 @@
         <v>329</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D120" s="11" t="s">
         <v>170</v>
@@ -9847,7 +9844,7 @@
         <v>128</v>
       </c>
       <c r="G120" s="11" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H120" s="14" t="s">
         <v>209</v>
@@ -9864,7 +9861,7 @@
         <v>129</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>322</v>
@@ -9873,13 +9870,13 @@
         <v>169</v>
       </c>
       <c r="E121" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G121" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="H121" s="13" t="s">
         <v>340</v>
-      </c>
-      <c r="G121" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="H121" s="13" t="s">
-        <v>341</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>303</v>
@@ -9890,7 +9887,7 @@
         <v>130</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>322</v>
@@ -9899,13 +9896,13 @@
         <v>169</v>
       </c>
       <c r="E122" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H122" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="H122" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I122" s="5" t="s">
         <v>303</v>
@@ -9916,7 +9913,7 @@
         <v>131</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>322</v>
@@ -9925,13 +9922,13 @@
         <v>169</v>
       </c>
       <c r="E123" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H123" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="H123" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>303</v>
@@ -9942,7 +9939,7 @@
         <v>132</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>322</v>
@@ -9951,13 +9948,13 @@
         <v>169</v>
       </c>
       <c r="E124" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H124" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G124" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H124" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I124" s="5" t="s">
         <v>303</v>
@@ -9968,7 +9965,7 @@
         <v>133</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>322</v>
@@ -9977,13 +9974,13 @@
         <v>169</v>
       </c>
       <c r="E125" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H125" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H125" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I125" s="5" t="s">
         <v>303</v>
@@ -9994,7 +9991,7 @@
         <v>134</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>322</v>
@@ -10003,13 +10000,13 @@
         <v>169</v>
       </c>
       <c r="E126" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H126" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H126" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I126" s="5" t="s">
         <v>303</v>
@@ -10020,7 +10017,7 @@
         <v>135</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>322</v>
@@ -10029,13 +10026,13 @@
         <v>169</v>
       </c>
       <c r="E127" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G127" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H127" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G127" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="H127" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I127" s="5" t="s">
         <v>303</v>
@@ -10046,7 +10043,7 @@
         <v>136</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>322</v>
@@ -10055,13 +10052,13 @@
         <v>169</v>
       </c>
       <c r="E128" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H128" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="H128" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I128" s="5" t="s">
         <v>303</v>
@@ -10072,7 +10069,7 @@
         <v>137</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>322</v>
@@ -10081,13 +10078,13 @@
         <v>169</v>
       </c>
       <c r="E129" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H129" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="H129" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I129" s="5" t="s">
         <v>303</v>
@@ -10098,7 +10095,7 @@
         <v>138</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>322</v>
@@ -10107,13 +10104,13 @@
         <v>169</v>
       </c>
       <c r="E130" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="H130" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="H130" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I130" s="5" t="s">
         <v>303</v>
@@ -10124,7 +10121,7 @@
         <v>139</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>322</v>
@@ -10133,13 +10130,13 @@
         <v>169</v>
       </c>
       <c r="E131" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="H131" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="H131" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I131" s="5" t="s">
         <v>303</v>
@@ -10150,7 +10147,7 @@
         <v>140</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>322</v>
@@ -10159,13 +10156,13 @@
         <v>169</v>
       </c>
       <c r="E132" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="H132" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="H132" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I132" s="5" t="s">
         <v>303</v>
@@ -10176,7 +10173,7 @@
         <v>141</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>322</v>
@@ -10185,13 +10182,13 @@
         <v>169</v>
       </c>
       <c r="E133" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="H133" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="H133" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I133" s="5" t="s">
         <v>303</v>
@@ -10202,7 +10199,7 @@
         <v>142</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>322</v>
@@ -10211,13 +10208,13 @@
         <v>169</v>
       </c>
       <c r="E134" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="H134" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G134" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="H134" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I134" s="5" t="s">
         <v>303</v>
@@ -10228,7 +10225,7 @@
         <v>143</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>322</v>
@@ -10237,13 +10234,13 @@
         <v>169</v>
       </c>
       <c r="E135" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="H135" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G135" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="H135" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I135" s="5" t="s">
         <v>303</v>
@@ -10254,7 +10251,7 @@
         <v>144</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>322</v>
@@ -10263,13 +10260,13 @@
         <v>169</v>
       </c>
       <c r="E136" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H136" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G136" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="H136" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I136" s="5" t="s">
         <v>303</v>
@@ -10280,7 +10277,7 @@
         <v>145</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>322</v>
@@ -10289,13 +10286,13 @@
         <v>169</v>
       </c>
       <c r="E137" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H137" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G137" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="H137" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>303</v>
@@ -10306,7 +10303,7 @@
         <v>146</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>322</v>
@@ -10315,13 +10312,13 @@
         <v>169</v>
       </c>
       <c r="E138" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H138" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G138" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="H138" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>303</v>
@@ -10332,7 +10329,7 @@
         <v>147</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>322</v>
@@ -10341,13 +10338,13 @@
         <v>169</v>
       </c>
       <c r="E139" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H139" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="H139" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>303</v>
@@ -10358,7 +10355,7 @@
         <v>148</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>322</v>
@@ -10367,13 +10364,13 @@
         <v>169</v>
       </c>
       <c r="E140" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H140" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G140" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="H140" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I140" s="5" t="s">
         <v>303</v>
@@ -10384,7 +10381,7 @@
         <v>149</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>322</v>
@@ -10393,13 +10390,13 @@
         <v>169</v>
       </c>
       <c r="E141" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H141" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="H141" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I141" s="5" t="s">
         <v>303</v>
@@ -10410,7 +10407,7 @@
         <v>150</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>322</v>
@@ -10419,13 +10416,13 @@
         <v>169</v>
       </c>
       <c r="E142" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="H142" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="H142" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I142" s="5" t="s">
         <v>303</v>
@@ -10436,7 +10433,7 @@
         <v>151</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>322</v>
@@ -10445,13 +10442,13 @@
         <v>169</v>
       </c>
       <c r="E143" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="H143" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G143" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="H143" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I143" s="5" t="s">
         <v>303</v>
@@ -10462,7 +10459,7 @@
         <v>152</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>322</v>
@@ -10471,13 +10468,13 @@
         <v>169</v>
       </c>
       <c r="E144" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H144" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="H144" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I144" s="5" t="s">
         <v>303</v>
@@ -10488,7 +10485,7 @@
         <v>153</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>322</v>
@@ -10497,13 +10494,13 @@
         <v>169</v>
       </c>
       <c r="E145" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="H145" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="H145" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I145" s="5" t="s">
         <v>303</v>
@@ -10514,7 +10511,7 @@
         <v>154</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>322</v>
@@ -10523,13 +10520,13 @@
         <v>169</v>
       </c>
       <c r="E146" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="H146" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="H146" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I146" s="5" t="s">
         <v>303</v>
@@ -10540,7 +10537,7 @@
         <v>155</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>322</v>
@@ -10549,13 +10546,13 @@
         <v>169</v>
       </c>
       <c r="E147" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="H147" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G147" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="H147" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I147" s="5" t="s">
         <v>303</v>
@@ -10566,7 +10563,7 @@
         <v>156</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>322</v>
@@ -10575,13 +10572,13 @@
         <v>169</v>
       </c>
       <c r="E148" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="H148" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G148" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="H148" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>303</v>
@@ -10592,7 +10589,7 @@
         <v>157</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>322</v>
@@ -10601,13 +10598,13 @@
         <v>169</v>
       </c>
       <c r="E149" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="H149" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="H149" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="I149" s="5" t="s">
         <v>303</v>
@@ -10618,7 +10615,7 @@
         <v>158</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>322</v>
@@ -10627,13 +10624,13 @@
         <v>169</v>
       </c>
       <c r="E150" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="G150" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="H150" s="14" t="s">
         <v>340</v>
-      </c>
-      <c r="G150" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="H150" s="14" t="s">
-        <v>341</v>
       </c>
       <c r="I150" s="14" t="s">
         <v>303</v>
@@ -10644,7 +10641,7 @@
         <v>159</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>323</v>
@@ -10653,13 +10650,13 @@
         <v>169</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F151" s="13" t="s">
         <v>167</v>
       </c>
       <c r="G151" s="58" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I151" s="13">
         <v>0.2</v>
@@ -10679,7 +10676,7 @@
         <v>160</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>323</v>
@@ -10688,13 +10685,13 @@
         <v>169</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>167</v>
       </c>
       <c r="G152" s="59" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I152" s="5">
         <v>0.2</v>
@@ -10714,7 +10711,7 @@
         <v>161</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>323</v>
@@ -10723,13 +10720,13 @@
         <v>169</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>167</v>
       </c>
       <c r="G153" s="59" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I153" s="5">
         <v>0.2</v>
@@ -10749,7 +10746,7 @@
         <v>162</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>323</v>
@@ -10758,13 +10755,13 @@
         <v>169</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>167</v>
       </c>
       <c r="G154" s="59" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I154" s="5">
         <v>0.2</v>
@@ -10784,7 +10781,7 @@
         <v>163</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>323</v>
@@ -10793,13 +10790,13 @@
         <v>169</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>167</v>
       </c>
       <c r="G155" s="59" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I155" s="5">
         <v>0.2</v>
@@ -10819,7 +10816,7 @@
         <v>164</v>
       </c>
       <c r="B156" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>323</v>
@@ -10828,13 +10825,13 @@
         <v>169</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>167</v>
       </c>
       <c r="G156" s="59" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I156" s="5">
         <v>0.2</v>
@@ -10854,7 +10851,7 @@
         <v>165</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>323</v>
@@ -10863,13 +10860,13 @@
         <v>169</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>167</v>
       </c>
       <c r="G157" s="59" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I157" s="5">
         <v>0.2</v>
@@ -10889,7 +10886,7 @@
         <v>166</v>
       </c>
       <c r="B158" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>323</v>
@@ -10898,13 +10895,13 @@
         <v>169</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>167</v>
       </c>
       <c r="G158" s="59" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I158" s="5">
         <v>0.2</v>
@@ -10939,7 +10936,7 @@
         <v>128</v>
       </c>
       <c r="G159" s="82" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I159" s="13">
         <v>5.1999999999999998E-2</v>
@@ -10966,7 +10963,7 @@
         <v>128</v>
       </c>
       <c r="G160" s="83" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I160" s="5">
         <v>5.0999999999999997E-2</v>
@@ -10992,7 +10989,7 @@
         <v>128</v>
       </c>
       <c r="G161" s="83" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I161" s="5">
         <v>4.8000000000000001E-2</v>
@@ -11018,7 +11015,7 @@
         <v>128</v>
       </c>
       <c r="G162" s="83" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I162" s="5">
         <v>4.7E-2</v>
@@ -11044,7 +11041,7 @@
         <v>128</v>
       </c>
       <c r="G163" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I163" s="5">
         <v>0.16500000000000001</v>
@@ -11070,7 +11067,7 @@
         <v>128</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I164" s="5">
         <v>0.182</v>
@@ -11096,7 +11093,7 @@
         <v>128</v>
       </c>
       <c r="G165" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I165" s="5">
         <v>0.27500000000000002</v>
@@ -11122,7 +11119,7 @@
         <v>128</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I166" s="5">
         <v>0.29099999999999998</v>
@@ -11148,7 +11145,7 @@
         <v>128</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I167" s="5">
         <v>0.373</v>
@@ -11174,7 +11171,7 @@
         <v>128</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I168" s="5">
         <v>0.36899999999999999</v>
@@ -11200,7 +11197,7 @@
         <v>128</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I169" s="5">
         <v>0.121</v>
@@ -11226,7 +11223,7 @@
         <v>128</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="I170" s="5">
         <v>0.106</v>
@@ -11252,7 +11249,7 @@
         <v>128</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I171" s="5">
         <v>0.2</v>
@@ -11278,7 +11275,7 @@
         <v>128</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I172" s="5">
         <v>0.20100000000000001</v>
@@ -11304,7 +11301,7 @@
         <v>128</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I173" s="5">
         <v>0.32700000000000001</v>
@@ -11330,7 +11327,7 @@
         <v>128</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I174" s="5">
         <v>0.318</v>
@@ -11356,7 +11353,7 @@
         <v>128</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I175" s="5">
         <v>0.42099999999999999</v>
@@ -11382,7 +11379,7 @@
         <v>128</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I176" s="5">
         <v>0.39900000000000002</v>
@@ -11408,7 +11405,7 @@
         <v>167</v>
       </c>
       <c r="G177" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I177" s="5">
         <v>0.19600000000000001</v>
@@ -11434,7 +11431,7 @@
         <v>167</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I178" s="5">
         <v>0.20200000000000001</v>
@@ -11460,7 +11457,7 @@
         <v>167</v>
       </c>
       <c r="G179" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I179" s="5">
         <v>0.22900000000000001</v>
@@ -11486,7 +11483,7 @@
         <v>167</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I180" s="5">
         <v>0.22500000000000001</v>
@@ -11512,7 +11509,7 @@
         <v>167</v>
       </c>
       <c r="G181" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I181" s="5">
         <v>0.26800000000000002</v>
@@ -11538,7 +11535,7 @@
         <v>167</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I182" s="5">
         <v>0.27300000000000002</v>
@@ -11564,7 +11561,7 @@
         <v>167</v>
       </c>
       <c r="G183" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I183" s="5">
         <v>0.30299999999999999</v>
@@ -11590,7 +11587,7 @@
         <v>167</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I184" s="5">
         <v>0.30199999999999999</v>
@@ -11616,7 +11613,7 @@
         <v>167</v>
       </c>
       <c r="G185" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I185" s="5">
         <v>0.3</v>
@@ -11642,7 +11639,7 @@
         <v>167</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I186" s="5">
         <v>0.30099999999999999</v>
@@ -11668,7 +11665,7 @@
         <v>167</v>
       </c>
       <c r="G187" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I187" s="5">
         <v>0.316</v>
@@ -11694,7 +11691,7 @@
         <v>167</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I188" s="5">
         <v>0.32</v>
@@ -11720,7 +11717,7 @@
         <v>167</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I189" s="5">
         <v>0.33700000000000002</v>
@@ -11746,7 +11743,7 @@
         <v>167</v>
       </c>
       <c r="G190" s="11" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I190" s="14">
         <v>0.34</v>
@@ -12136,7 +12133,7 @@
         <v>128</v>
       </c>
       <c r="G205" s="59" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -12159,7 +12156,7 @@
         <v>128</v>
       </c>
       <c r="G206" s="59" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -12182,7 +12179,7 @@
         <v>128</v>
       </c>
       <c r="G207" s="59" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -12205,7 +12202,7 @@
         <v>128</v>
       </c>
       <c r="G208" s="59" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -12228,7 +12225,7 @@
         <v>128</v>
       </c>
       <c r="G209" s="59" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -12251,7 +12248,7 @@
         <v>128</v>
       </c>
       <c r="G210" s="59" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -12274,7 +12271,7 @@
         <v>128</v>
       </c>
       <c r="G211" s="59" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="212" spans="1:7" s="14" customFormat="1">
@@ -12297,7 +12294,7 @@
         <v>128</v>
       </c>
       <c r="G212" s="60" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -12797,7 +12794,7 @@
         <v>301</v>
       </c>
       <c r="G237" s="55" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H237" s="55"/>
       <c r="I237" s="55"/>
@@ -12824,7 +12821,7 @@
         <v>301</v>
       </c>
       <c r="G238" s="55" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H238" s="55"/>
       <c r="I238" s="55"/>
@@ -12851,7 +12848,7 @@
         <v>301</v>
       </c>
       <c r="G239" s="55" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H239" s="55"/>
       <c r="I239" s="55"/>
@@ -12898,7 +12895,7 @@
         <v>301</v>
       </c>
       <c r="G241" s="55" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H241" s="55"/>
       <c r="I241" s="55"/>
@@ -12925,7 +12922,7 @@
         <v>301</v>
       </c>
       <c r="G242" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H242" s="55"/>
       <c r="I242" s="55"/>
@@ -12972,7 +12969,7 @@
         <v>301</v>
       </c>
       <c r="G244" s="56" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H244" s="56"/>
       <c r="I244" s="56"/>
@@ -13019,7 +13016,7 @@
         <v>301</v>
       </c>
       <c r="G246" s="57" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H246" s="57"/>
       <c r="I246" s="57"/>
@@ -13066,7 +13063,7 @@
         <v>301</v>
       </c>
       <c r="G248" s="57" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H248" s="57"/>
       <c r="I248" s="57"/>
@@ -13113,7 +13110,7 @@
         <v>301</v>
       </c>
       <c r="G250" s="57" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H250" s="57"/>
       <c r="I250" s="57"/>
@@ -13160,7 +13157,7 @@
         <v>301</v>
       </c>
       <c r="G252" s="57" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H252" s="57"/>
       <c r="I252" s="57"/>
@@ -13187,7 +13184,7 @@
         <v>301</v>
       </c>
       <c r="G253" s="57" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H253" s="57"/>
       <c r="I253" s="57"/>
@@ -13202,10 +13199,10 @@
         <v>70</v>
       </c>
       <c r="B254" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C254" s="27" t="s">
         <v>335</v>
-      </c>
-      <c r="C254" s="27" t="s">
-        <v>336</v>
       </c>
       <c r="D254" s="34" t="s">
         <v>169</v>
@@ -13222,10 +13219,10 @@
         <v>71</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C255" s="27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D255" s="34" t="s">
         <v>169</v>
@@ -13242,10 +13239,10 @@
         <v>72</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C256" s="27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D256" s="34" t="s">
         <v>169</v>
@@ -13262,10 +13259,10 @@
         <v>73</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C257" s="27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D257" s="34" t="s">
         <v>169</v>
@@ -13282,10 +13279,10 @@
         <v>74</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C258" s="27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D258" s="34" t="s">
         <v>169</v>
@@ -13299,416 +13296,416 @@
     </row>
     <row r="259" spans="1:8" s="13" customFormat="1">
       <c r="A259" s="77" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B259" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C259" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C259" s="35" t="s">
+      <c r="D259" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E259" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D259" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E259" s="6" t="s">
+      <c r="G259" s="77" t="s">
         <v>475</v>
       </c>
-      <c r="G259" s="77" t="s">
-        <v>476</v>
-      </c>
       <c r="H259" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="260" spans="1:8">
       <c r="A260" s="77" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B260" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C260" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C260" s="35" t="s">
+      <c r="D260" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E260" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D260" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E260" s="6" t="s">
+      <c r="G260" s="77" t="s">
         <v>475</v>
       </c>
-      <c r="G260" s="77" t="s">
-        <v>476</v>
-      </c>
       <c r="H260" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="261" spans="1:8">
       <c r="A261" s="77" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B261" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C261" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C261" s="35" t="s">
+      <c r="D261" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E261" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D261" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E261" s="6" t="s">
+      <c r="G261" s="77" t="s">
         <v>475</v>
       </c>
-      <c r="G261" s="77" t="s">
-        <v>476</v>
-      </c>
       <c r="H261" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="262" spans="1:8">
       <c r="A262" s="77" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B262" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C262" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C262" s="35" t="s">
+      <c r="D262" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E262" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D262" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E262" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G262" s="77" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H262" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="263" spans="1:8">
       <c r="A263" s="77" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B263" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C263" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C263" s="35" t="s">
+      <c r="D263" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E263" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D263" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E263" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G263" s="77" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H263" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="77" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B264" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C264" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C264" s="35" t="s">
+      <c r="D264" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E264" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D264" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E264" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G264" s="77" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H264" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="77" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B265" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C265" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C265" s="35" t="s">
+      <c r="D265" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E265" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D265" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E265" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G265" s="77" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H265" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="77" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B266" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C266" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C266" s="35" t="s">
+      <c r="D266" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E266" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D266" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E266" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G266" s="77" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H266" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="77" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B267" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C267" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C267" s="35" t="s">
+      <c r="D267" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E267" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D267" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E267" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G267" s="77" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H267" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="77" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B268" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C268" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C268" s="35" t="s">
+      <c r="D268" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E268" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D268" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E268" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G268" s="77" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H268" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="77" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B269" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C269" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C269" s="35" t="s">
+      <c r="D269" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E269" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D269" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E269" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G269" s="77" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H269" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="77" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B270" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C270" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C270" s="35" t="s">
+      <c r="D270" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E270" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D270" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E270" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G270" s="77" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H270" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" s="77" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B271" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C271" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C271" s="35" t="s">
+      <c r="D271" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E271" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D271" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E271" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G271" s="77" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H271" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" s="77" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B272" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C272" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C272" s="35" t="s">
+      <c r="D272" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E272" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D272" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E272" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G272" s="77" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H272" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" s="77" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B273" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C273" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C273" s="35" t="s">
+      <c r="D273" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E273" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D273" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E273" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G273" s="77" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H273" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" s="77" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B274" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C274" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C274" s="35" t="s">
+      <c r="D274" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E274" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D274" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E274" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G274" s="77" t="s">
+        <v>479</v>
+      </c>
+      <c r="H274" s="13" t="s">
         <v>480</v>
-      </c>
-      <c r="H274" s="13" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" s="77" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B275" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="C275" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C275" s="35" t="s">
+      <c r="D275" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E275" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D275" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E275" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G275" s="77" t="s">
+        <v>479</v>
+      </c>
+      <c r="H275" s="13" t="s">
         <v>480</v>
-      </c>
-      <c r="H275" s="13" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" s="77" t="s">
+        <v>471</v>
+      </c>
+      <c r="B276" s="13" t="s">
         <v>472</v>
       </c>
-      <c r="B276" s="13" t="s">
+      <c r="C276" s="35" t="s">
         <v>473</v>
       </c>
-      <c r="C276" s="35" t="s">
+      <c r="D276" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E276" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D276" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E276" s="6" t="s">
-        <v>475</v>
-      </c>
       <c r="G276" s="77" t="s">
+        <v>479</v>
+      </c>
+      <c r="H276" s="13" t="s">
         <v>480</v>
-      </c>
-      <c r="H276" s="13" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="277" spans="1:9" s="15" customFormat="1">
@@ -14147,7 +14144,7 @@
         <v>128</v>
       </c>
       <c r="G293" s="63" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="294" spans="1:9" s="15" customFormat="1">
@@ -14170,7 +14167,7 @@
         <v>128</v>
       </c>
       <c r="G294" s="63" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="295" spans="1:9" s="15" customFormat="1">
@@ -14193,7 +14190,7 @@
         <v>128</v>
       </c>
       <c r="G295" s="63" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="296" spans="1:9" s="15" customFormat="1">
@@ -14216,7 +14213,7 @@
         <v>128</v>
       </c>
       <c r="G296" s="63" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="297" spans="1:9" s="15" customFormat="1">
@@ -14239,7 +14236,7 @@
         <v>128</v>
       </c>
       <c r="G297" s="63" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="298" spans="1:9" s="15" customFormat="1">
@@ -14262,7 +14259,7 @@
         <v>128</v>
       </c>
       <c r="G298" s="63" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="299" spans="1:9" s="15" customFormat="1">
@@ -14285,7 +14282,7 @@
         <v>128</v>
       </c>
       <c r="G299" s="63" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="300" spans="1:9" s="15" customFormat="1">
@@ -14308,7 +14305,7 @@
         <v>128</v>
       </c>
       <c r="G300" s="63" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="301" spans="1:9" s="15" customFormat="1">
@@ -14331,7 +14328,7 @@
         <v>128</v>
       </c>
       <c r="G301" s="63" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -14485,19 +14482,19 @@
         <v>95</v>
       </c>
       <c r="W2" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X2" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y2" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z2" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA2" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X2" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y2" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z2" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA2" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB2" t="str">
         <f>W2&amp;B2&amp;X2&amp;R2&amp;Y2&amp;T2&amp;Z2&amp;X2&amp;AA2&amp;U2</f>
@@ -14560,19 +14557,19 @@
         <v>95</v>
       </c>
       <c r="W3" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA3" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X3" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y3" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z3" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA3" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB3" t="str">
         <f t="shared" ref="AB3:AB43" si="0">W3&amp;B3&amp;X3&amp;R3&amp;Y3&amp;T3&amp;Z3&amp;X3&amp;AA3&amp;U3</f>
@@ -14635,19 +14632,19 @@
         <v>95</v>
       </c>
       <c r="W4" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X4" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y4" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z4" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA4" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X4" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y4" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z4" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA4" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB4" t="str">
         <f t="shared" si="0"/>
@@ -14710,19 +14707,19 @@
         <v>97</v>
       </c>
       <c r="W5" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X5" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y5" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z5" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA5" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X5" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y5" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z5" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA5" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB5" t="str">
         <f t="shared" si="0"/>
@@ -14785,19 +14782,19 @@
         <v>97</v>
       </c>
       <c r="W6" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X6" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y6" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z6" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA6" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X6" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y6" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z6" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA6" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB6" t="str">
         <f t="shared" si="0"/>
@@ -14860,19 +14857,19 @@
         <v>97</v>
       </c>
       <c r="W7" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X7" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y7" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z7" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA7" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X7" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y7" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z7" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA7" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB7" t="str">
         <f t="shared" si="0"/>
@@ -14935,19 +14932,19 @@
         <v>98</v>
       </c>
       <c r="W8" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X8" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y8" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z8" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA8" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X8" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y8" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z8" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA8" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB8" t="str">
         <f t="shared" si="0"/>
@@ -15010,19 +15007,19 @@
         <v>98</v>
       </c>
       <c r="W9" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X9" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y9" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z9" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA9" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X9" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y9" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z9" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA9" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB9" t="str">
         <f t="shared" si="0"/>
@@ -15085,19 +15082,19 @@
         <v>98</v>
       </c>
       <c r="W10" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X10" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y10" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z10" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA10" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X10" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y10" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z10" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA10" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB10" t="str">
         <f t="shared" si="0"/>
@@ -15160,19 +15157,19 @@
         <v>95</v>
       </c>
       <c r="W11" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X11" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y11" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z11" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA11" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X11" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y11" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z11" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA11" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB11" t="str">
         <f t="shared" si="0"/>
@@ -15235,19 +15232,19 @@
         <v>95</v>
       </c>
       <c r="W12" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X12" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y12" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z12" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA12" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X12" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y12" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z12" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA12" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB12" t="str">
         <f t="shared" si="0"/>
@@ -15310,19 +15307,19 @@
         <v>95</v>
       </c>
       <c r="W13" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X13" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y13" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z13" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA13" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X13" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y13" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z13" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA13" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB13" t="str">
         <f t="shared" si="0"/>
@@ -15385,19 +15382,19 @@
         <v>95</v>
       </c>
       <c r="W14" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X14" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y14" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z14" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA14" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X14" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y14" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z14" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA14" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB14" t="str">
         <f t="shared" si="0"/>
@@ -15460,19 +15457,19 @@
         <v>95</v>
       </c>
       <c r="W15" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X15" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y15" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z15" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA15" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X15" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y15" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z15" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA15" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB15" t="str">
         <f t="shared" si="0"/>
@@ -15535,19 +15532,19 @@
         <v>95</v>
       </c>
       <c r="W16" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X16" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y16" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z16" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA16" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X16" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y16" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z16" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA16" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB16" t="str">
         <f t="shared" si="0"/>
@@ -15610,19 +15607,19 @@
         <v>95</v>
       </c>
       <c r="W17" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X17" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y17" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z17" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA17" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X17" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y17" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z17" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA17" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB17" t="str">
         <f t="shared" si="0"/>
@@ -15685,19 +15682,19 @@
         <v>95</v>
       </c>
       <c r="W18" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X18" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y18" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z18" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA18" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X18" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y18" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z18" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA18" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB18" t="str">
         <f t="shared" si="0"/>
@@ -15760,19 +15757,19 @@
         <v>95</v>
       </c>
       <c r="W19" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X19" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y19" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z19" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA19" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X19" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y19" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z19" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA19" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB19" t="str">
         <f t="shared" si="0"/>
@@ -15835,19 +15832,19 @@
         <v>95</v>
       </c>
       <c r="W20" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X20" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y20" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z20" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA20" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X20" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y20" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z20" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA20" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB20" t="str">
         <f t="shared" si="0"/>
@@ -15910,19 +15907,19 @@
         <v>95</v>
       </c>
       <c r="W21" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X21" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y21" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z21" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA21" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X21" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y21" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z21" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA21" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB21" t="str">
         <f t="shared" si="0"/>
@@ -15985,19 +15982,19 @@
         <v>95</v>
       </c>
       <c r="W22" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X22" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y22" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z22" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA22" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X22" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y22" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z22" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA22" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB22" t="str">
         <f t="shared" si="0"/>
@@ -16060,19 +16057,19 @@
         <v>97</v>
       </c>
       <c r="W23" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X23" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y23" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z23" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA23" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X23" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y23" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z23" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA23" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB23" t="str">
         <f t="shared" si="0"/>
@@ -16135,19 +16132,19 @@
         <v>97</v>
       </c>
       <c r="W24" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X24" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y24" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z24" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA24" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X24" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y24" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z24" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA24" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB24" t="str">
         <f t="shared" si="0"/>
@@ -16210,19 +16207,19 @@
         <v>97</v>
       </c>
       <c r="W25" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X25" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y25" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z25" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA25" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X25" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y25" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z25" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA25" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB25" t="str">
         <f t="shared" si="0"/>
@@ -16285,19 +16282,19 @@
         <v>97</v>
       </c>
       <c r="W26" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X26" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y26" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z26" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA26" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X26" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y26" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z26" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA26" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB26" t="str">
         <f t="shared" si="0"/>
@@ -16360,19 +16357,19 @@
         <v>97</v>
       </c>
       <c r="W27" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X27" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y27" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z27" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA27" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X27" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y27" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z27" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA27" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB27" t="str">
         <f t="shared" si="0"/>
@@ -16435,19 +16432,19 @@
         <v>97</v>
       </c>
       <c r="W28" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X28" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y28" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z28" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA28" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X28" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y28" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z28" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA28" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB28" t="str">
         <f t="shared" si="0"/>
@@ -16510,19 +16507,19 @@
         <v>97</v>
       </c>
       <c r="W29" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X29" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y29" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z29" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA29" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X29" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y29" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z29" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA29" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB29" t="str">
         <f t="shared" si="0"/>
@@ -16585,19 +16582,19 @@
         <v>97</v>
       </c>
       <c r="W30" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X30" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y30" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z30" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA30" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X30" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y30" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z30" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA30" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB30" t="str">
         <f t="shared" si="0"/>
@@ -16660,19 +16657,19 @@
         <v>97</v>
       </c>
       <c r="W31" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X31" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y31" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z31" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA31" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X31" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y31" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z31" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA31" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB31" t="str">
         <f t="shared" si="0"/>
@@ -16735,19 +16732,19 @@
         <v>97</v>
       </c>
       <c r="W32" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X32" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y32" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z32" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA32" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X32" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y32" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z32" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA32" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB32" t="str">
         <f t="shared" si="0"/>
@@ -16810,19 +16807,19 @@
         <v>97</v>
       </c>
       <c r="W33" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X33" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y33" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z33" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA33" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X33" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y33" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z33" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA33" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB33" t="str">
         <f t="shared" si="0"/>
@@ -16885,19 +16882,19 @@
         <v>97</v>
       </c>
       <c r="W34" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X34" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y34" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z34" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA34" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X34" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y34" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z34" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA34" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB34" t="str">
         <f t="shared" si="0"/>
@@ -16960,19 +16957,19 @@
         <v>97</v>
       </c>
       <c r="W35" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X35" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y35" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z35" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA35" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X35" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y35" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z35" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA35" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB35" t="str">
         <f t="shared" si="0"/>
@@ -17035,19 +17032,19 @@
         <v>97</v>
       </c>
       <c r="W36" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X36" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y36" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z36" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA36" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X36" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y36" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z36" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA36" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB36" t="str">
         <f t="shared" si="0"/>
@@ -17110,19 +17107,19 @@
         <v>97</v>
       </c>
       <c r="W37" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X37" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y37" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z37" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA37" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X37" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y37" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z37" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA37" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB37" t="str">
         <f t="shared" si="0"/>
@@ -17185,19 +17182,19 @@
         <v>97</v>
       </c>
       <c r="W38" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X38" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y38" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z38" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA38" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X38" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y38" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z38" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA38" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB38" t="str">
         <f t="shared" si="0"/>
@@ -17260,19 +17257,19 @@
         <v>97</v>
       </c>
       <c r="W39" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X39" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y39" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z39" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA39" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X39" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y39" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z39" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA39" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB39" t="str">
         <f t="shared" si="0"/>
@@ -17335,19 +17332,19 @@
         <v>97</v>
       </c>
       <c r="W40" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X40" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y40" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z40" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA40" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X40" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y40" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z40" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA40" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB40" t="str">
         <f t="shared" si="0"/>
@@ -17410,19 +17407,19 @@
         <v>97</v>
       </c>
       <c r="W41" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X41" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y41" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z41" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA41" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X41" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y41" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z41" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA41" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB41" t="str">
         <f t="shared" si="0"/>
@@ -17485,19 +17482,19 @@
         <v>97</v>
       </c>
       <c r="W42" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X42" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y42" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z42" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA42" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X42" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y42" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z42" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA42" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB42" t="str">
         <f t="shared" si="0"/>
@@ -17560,19 +17557,19 @@
         <v>97</v>
       </c>
       <c r="W43" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="X43" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y43" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z43" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA43" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="X43" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y43" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="Z43" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="AA43" s="21" t="s">
-        <v>361</v>
       </c>
       <c r="AB43" t="str">
         <f t="shared" si="0"/>
@@ -18363,187 +18360,187 @@
     <row r="9" spans="1:31">
       <c r="A9" s="17"/>
       <c r="B9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="S9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="V9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="W9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="X9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Y9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Z9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AB9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AC9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AD9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AE9" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:31">
       <c r="A10" s="17"/>
       <c r="B10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="V10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="W10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="X10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Z10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AB10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AC10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AD10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AE10" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -18671,94 +18668,94 @@
     </row>
     <row r="12" spans="1:31">
       <c r="B12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="M12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="T12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="U12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="V12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="W12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="X12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Y12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Z12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AA12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AB12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AC12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AD12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AE12" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:31">

--- a/data/proteomics/physiology_collection.xlsx
+++ b/data/proteomics/physiology_collection.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/large_scale_yeast_proteomics_analysis/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158912C5-4F89-B541-B71F-9FF268E8B43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDDE420-EBCA-C84C-A568-1452BD85F02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2900" windowWidth="26000" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2360" windowWidth="34480" windowHeight="18700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="8" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="7" r:id="rId4"/>
-    <sheet name="Supplementary File 1e vip" sheetId="1" r:id="rId5"/>
-    <sheet name="cell cycle_kate" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="9" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="8" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId5"/>
+    <sheet name="Supplementary File 1e vip" sheetId="1" r:id="rId6"/>
+    <sheet name="cell cycle_kate" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$B$301</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Supplementary File 1e vip'!$B$1:$B$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Supplementary File 1e vip'!$B$1:$B$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3497" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3645" uniqueCount="528">
   <si>
     <t>sample</t>
   </si>
@@ -2537,7 +2538,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2793,6 +2794,36 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -4673,7 +4704,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8F22EE-2E06-6741-B451-D4EA064EAB2E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AF301"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -9352,7 +9382,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="65" spans="1:31" s="13" customFormat="1" hidden="1">
+    <row r="65" spans="1:31" s="13" customFormat="1">
       <c r="A65" s="66" t="s">
         <v>62</v>
       </c>
@@ -9382,7 +9412,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="66" spans="1:31" hidden="1">
+    <row r="66" spans="1:31">
       <c r="A66" s="67" t="s">
         <v>63</v>
       </c>
@@ -9412,7 +9442,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="67" spans="1:31" hidden="1">
+    <row r="67" spans="1:31">
       <c r="A67" s="67" t="s">
         <v>64</v>
       </c>
@@ -9442,7 +9472,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="68" spans="1:31" hidden="1">
+    <row r="68" spans="1:31">
       <c r="A68" s="67" t="s">
         <v>65</v>
       </c>
@@ -9472,7 +9502,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="69" spans="1:31" hidden="1">
+    <row r="69" spans="1:31">
       <c r="A69" s="67" t="s">
         <v>66</v>
       </c>
@@ -9499,7 +9529,7 @@
       </c>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:31" hidden="1">
+    <row r="70" spans="1:31">
       <c r="A70" s="67" t="s">
         <v>67</v>
       </c>
@@ -9526,7 +9556,7 @@
       </c>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:31" hidden="1">
+    <row r="71" spans="1:31">
       <c r="A71" s="67" t="s">
         <v>68</v>
       </c>
@@ -9553,7 +9583,7 @@
       </c>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:31" hidden="1">
+    <row r="72" spans="1:31">
       <c r="A72" s="67" t="s">
         <v>69</v>
       </c>
@@ -11412,7 +11442,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="110" spans="1:31" s="13" customFormat="1" hidden="1">
+    <row r="110" spans="1:31" s="13" customFormat="1">
       <c r="A110" s="10" t="s">
         <v>116</v>
       </c>
@@ -11447,7 +11477,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="111" spans="1:31" hidden="1">
+    <row r="111" spans="1:31">
       <c r="A111" s="6" t="s">
         <v>117</v>
       </c>
@@ -11482,7 +11512,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="112" spans="1:31" hidden="1">
+    <row r="112" spans="1:31">
       <c r="A112" s="6" t="s">
         <v>118</v>
       </c>
@@ -11517,7 +11547,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="113" spans="1:25" hidden="1">
+    <row r="113" spans="1:25">
       <c r="A113" s="6" t="s">
         <v>119</v>
       </c>
@@ -11552,7 +11582,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="114" spans="1:25" hidden="1">
+    <row r="114" spans="1:25">
       <c r="A114" s="6" t="s">
         <v>120</v>
       </c>
@@ -11587,7 +11617,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="115" spans="1:25" hidden="1">
+    <row r="115" spans="1:25">
       <c r="A115" s="6" t="s">
         <v>121</v>
       </c>
@@ -11622,7 +11652,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="116" spans="1:25" hidden="1">
+    <row r="116" spans="1:25">
       <c r="A116" s="6" t="s">
         <v>122</v>
       </c>
@@ -11657,7 +11687,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="117" spans="1:25" hidden="1">
+    <row r="117" spans="1:25">
       <c r="A117" s="6" t="s">
         <v>123</v>
       </c>
@@ -11692,7 +11722,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="118" spans="1:25" hidden="1">
+    <row r="118" spans="1:25">
       <c r="A118" s="6" t="s">
         <v>124</v>
       </c>
@@ -11727,7 +11757,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="119" spans="1:25" hidden="1">
+    <row r="119" spans="1:25">
       <c r="A119" s="6" t="s">
         <v>125</v>
       </c>
@@ -11762,7 +11792,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="120" spans="1:25" s="14" customFormat="1" hidden="1">
+    <row r="120" spans="1:25" s="14" customFormat="1">
       <c r="A120" s="11" t="s">
         <v>126</v>
       </c>
@@ -12971,7 +13001,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="159" spans="1:26" s="13" customFormat="1" hidden="1">
+    <row r="159" spans="1:26" s="13" customFormat="1">
       <c r="A159" s="10" t="s">
         <v>176</v>
       </c>
@@ -13001,7 +13031,7 @@
       </c>
       <c r="Y159" s="29"/>
     </row>
-    <row r="160" spans="1:26" ht="14" hidden="1" customHeight="1">
+    <row r="160" spans="1:26" ht="14" customHeight="1">
       <c r="A160" s="6" t="s">
         <v>177</v>
       </c>
@@ -13030,7 +13060,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1">
+    <row r="161" spans="1:10">
       <c r="A161" s="6" t="s">
         <v>178</v>
       </c>
@@ -13059,7 +13089,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1">
+    <row r="162" spans="1:10">
       <c r="A162" s="6" t="s">
         <v>179</v>
       </c>
@@ -13088,7 +13118,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1">
+    <row r="163" spans="1:10">
       <c r="A163" s="6" t="s">
         <v>180</v>
       </c>
@@ -13117,7 +13147,7 @@
         <v>0.16500000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1">
+    <row r="164" spans="1:10">
       <c r="A164" s="6" t="s">
         <v>181</v>
       </c>
@@ -13146,7 +13176,7 @@
         <v>0.182</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1">
+    <row r="165" spans="1:10">
       <c r="A165" s="6" t="s">
         <v>182</v>
       </c>
@@ -13175,7 +13205,7 @@
         <v>0.27500000000000002</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1">
+    <row r="166" spans="1:10">
       <c r="A166" s="6" t="s">
         <v>183</v>
       </c>
@@ -13204,7 +13234,7 @@
         <v>0.29099999999999998</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1">
+    <row r="167" spans="1:10">
       <c r="A167" s="6" t="s">
         <v>184</v>
       </c>
@@ -13233,7 +13263,7 @@
         <v>0.373</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1">
+    <row r="168" spans="1:10">
       <c r="A168" s="6" t="s">
         <v>185</v>
       </c>
@@ -13262,7 +13292,7 @@
         <v>0.36899999999999999</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1">
+    <row r="169" spans="1:10">
       <c r="A169" s="6" t="s">
         <v>186</v>
       </c>
@@ -13291,7 +13321,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1">
+    <row r="170" spans="1:10">
       <c r="A170" s="6" t="s">
         <v>187</v>
       </c>
@@ -13320,7 +13350,7 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1">
+    <row r="171" spans="1:10">
       <c r="A171" s="6" t="s">
         <v>188</v>
       </c>
@@ -13349,7 +13379,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1">
+    <row r="172" spans="1:10">
       <c r="A172" s="6" t="s">
         <v>189</v>
       </c>
@@ -13378,7 +13408,7 @@
         <v>0.20100000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1">
+    <row r="173" spans="1:10">
       <c r="A173" s="6" t="s">
         <v>190</v>
       </c>
@@ -13407,7 +13437,7 @@
         <v>0.32700000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1">
+    <row r="174" spans="1:10">
       <c r="A174" s="6" t="s">
         <v>191</v>
       </c>
@@ -13436,7 +13466,7 @@
         <v>0.318</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1">
+    <row r="175" spans="1:10">
       <c r="A175" s="6" t="s">
         <v>192</v>
       </c>
@@ -13465,7 +13495,7 @@
         <v>0.42099999999999999</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1">
+    <row r="176" spans="1:10">
       <c r="A176" s="6" t="s">
         <v>193</v>
       </c>
@@ -13494,7 +13524,7 @@
         <v>0.39900000000000002</v>
       </c>
     </row>
-    <row r="177" spans="1:10" hidden="1">
+    <row r="177" spans="1:10">
       <c r="A177" s="6" t="s">
         <v>194</v>
       </c>
@@ -13523,7 +13553,7 @@
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:10" hidden="1">
+    <row r="178" spans="1:10">
       <c r="A178" s="6" t="s">
         <v>195</v>
       </c>
@@ -13552,7 +13582,7 @@
         <v>0.20200000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1">
+    <row r="179" spans="1:10">
       <c r="A179" s="6" t="s">
         <v>196</v>
       </c>
@@ -13581,7 +13611,7 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1">
+    <row r="180" spans="1:10">
       <c r="A180" s="6" t="s">
         <v>197</v>
       </c>
@@ -13610,7 +13640,7 @@
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1">
+    <row r="181" spans="1:10">
       <c r="A181" s="6" t="s">
         <v>198</v>
       </c>
@@ -13639,7 +13669,7 @@
         <v>0.26800000000000002</v>
       </c>
     </row>
-    <row r="182" spans="1:10" hidden="1">
+    <row r="182" spans="1:10">
       <c r="A182" s="6" t="s">
         <v>199</v>
       </c>
@@ -13668,7 +13698,7 @@
         <v>0.27300000000000002</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1">
+    <row r="183" spans="1:10">
       <c r="A183" s="6" t="s">
         <v>200</v>
       </c>
@@ -13697,7 +13727,7 @@
         <v>0.30299999999999999</v>
       </c>
     </row>
-    <row r="184" spans="1:10" hidden="1">
+    <row r="184" spans="1:10">
       <c r="A184" s="6" t="s">
         <v>201</v>
       </c>
@@ -13726,7 +13756,7 @@
         <v>0.30199999999999999</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1">
+    <row r="185" spans="1:10">
       <c r="A185" s="6" t="s">
         <v>202</v>
       </c>
@@ -13755,7 +13785,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1">
+    <row r="186" spans="1:10">
       <c r="A186" s="6" t="s">
         <v>203</v>
       </c>
@@ -13784,7 +13814,7 @@
         <v>0.30099999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:10" hidden="1">
+    <row r="187" spans="1:10">
       <c r="A187" s="6" t="s">
         <v>204</v>
       </c>
@@ -13813,7 +13843,7 @@
         <v>0.316</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1">
+    <row r="188" spans="1:10">
       <c r="A188" s="6" t="s">
         <v>205</v>
       </c>
@@ -13842,7 +13872,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1">
+    <row r="189" spans="1:10">
       <c r="A189" s="6" t="s">
         <v>206</v>
       </c>
@@ -13871,7 +13901,7 @@
         <v>0.33700000000000002</v>
       </c>
     </row>
-    <row r="190" spans="1:10" s="14" customFormat="1" hidden="1">
+    <row r="190" spans="1:10" s="14" customFormat="1">
       <c r="A190" s="11" t="s">
         <v>207</v>
       </c>
@@ -13900,7 +13930,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="191" spans="1:10" s="13" customFormat="1" hidden="1">
+    <row r="191" spans="1:10" s="13" customFormat="1">
       <c r="A191" s="75" t="s">
         <v>210</v>
       </c>
@@ -13929,7 +13959,7 @@
         <v>0.255</v>
       </c>
     </row>
-    <row r="192" spans="1:10" hidden="1">
+    <row r="192" spans="1:10">
       <c r="A192" s="20" t="s">
         <v>211</v>
       </c>
@@ -13958,7 +13988,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1">
+    <row r="193" spans="1:10">
       <c r="A193" s="20" t="s">
         <v>212</v>
       </c>
@@ -13987,7 +14017,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1">
+    <row r="194" spans="1:10">
       <c r="A194" s="20" t="s">
         <v>213</v>
       </c>
@@ -14016,7 +14046,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1">
+    <row r="195" spans="1:10">
       <c r="A195" s="20" t="s">
         <v>214</v>
       </c>
@@ -14045,7 +14075,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1">
+    <row r="196" spans="1:10">
       <c r="A196" s="20" t="s">
         <v>215</v>
       </c>
@@ -14074,7 +14104,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1">
+    <row r="197" spans="1:10">
       <c r="A197" s="20" t="s">
         <v>216</v>
       </c>
@@ -14103,7 +14133,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1">
+    <row r="198" spans="1:10">
       <c r="A198" s="20" t="s">
         <v>217</v>
       </c>
@@ -14132,7 +14162,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1">
+    <row r="199" spans="1:10">
       <c r="A199" s="20" t="s">
         <v>218</v>
       </c>
@@ -14161,7 +14191,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1">
+    <row r="200" spans="1:10">
       <c r="A200" s="20" t="s">
         <v>219</v>
       </c>
@@ -14190,7 +14220,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1">
+    <row r="201" spans="1:10">
       <c r="A201" s="20" t="s">
         <v>220</v>
       </c>
@@ -14219,7 +14249,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1">
+    <row r="202" spans="1:10">
       <c r="A202" s="20" t="s">
         <v>221</v>
       </c>
@@ -14248,7 +14278,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1">
+    <row r="203" spans="1:10">
       <c r="A203" s="20" t="s">
         <v>222</v>
       </c>
@@ -14277,7 +14307,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1">
+    <row r="204" spans="1:10">
       <c r="A204" s="20" t="s">
         <v>223</v>
       </c>
@@ -14306,7 +14336,7 @@
         <v>0.39100000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1">
+    <row r="205" spans="1:10">
       <c r="A205" s="20" t="s">
         <v>224</v>
       </c>
@@ -14332,7 +14362,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1">
+    <row r="206" spans="1:10">
       <c r="A206" s="20" t="s">
         <v>225</v>
       </c>
@@ -14358,7 +14388,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1">
+    <row r="207" spans="1:10">
       <c r="A207" s="20" t="s">
         <v>226</v>
       </c>
@@ -14384,7 +14414,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1">
+    <row r="208" spans="1:10">
       <c r="A208" s="20" t="s">
         <v>227</v>
       </c>
@@ -14410,7 +14440,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1">
+    <row r="209" spans="1:8">
       <c r="A209" s="20" t="s">
         <v>228</v>
       </c>
@@ -14436,7 +14466,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1">
+    <row r="210" spans="1:8">
       <c r="A210" s="20" t="s">
         <v>229</v>
       </c>
@@ -14462,7 +14492,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1">
+    <row r="211" spans="1:8">
       <c r="A211" s="20" t="s">
         <v>230</v>
       </c>
@@ -14488,7 +14518,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="212" spans="1:8" s="14" customFormat="1" hidden="1">
+    <row r="212" spans="1:8" s="14" customFormat="1">
       <c r="A212" s="76" t="s">
         <v>231</v>
       </c>
@@ -14514,7 +14544,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1">
+    <row r="213" spans="1:8">
       <c r="A213" s="71" t="s">
         <v>232</v>
       </c>
@@ -14537,7 +14567,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1">
+    <row r="214" spans="1:8">
       <c r="A214" s="71" t="s">
         <v>233</v>
       </c>
@@ -14560,7 +14590,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1">
+    <row r="215" spans="1:8">
       <c r="A215" s="71" t="s">
         <v>234</v>
       </c>
@@ -14583,7 +14613,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1">
+    <row r="216" spans="1:8">
       <c r="A216" s="71" t="s">
         <v>235</v>
       </c>
@@ -14606,7 +14636,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="1">
+    <row r="217" spans="1:8">
       <c r="A217" s="71" t="s">
         <v>236</v>
       </c>
@@ -14629,7 +14659,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1">
+    <row r="218" spans="1:8">
       <c r="A218" s="71" t="s">
         <v>237</v>
       </c>
@@ -14652,7 +14682,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1">
+    <row r="219" spans="1:8">
       <c r="A219" s="71" t="s">
         <v>238</v>
       </c>
@@ -14675,7 +14705,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1">
+    <row r="220" spans="1:8">
       <c r="A220" s="71" t="s">
         <v>239</v>
       </c>
@@ -14698,7 +14728,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1">
+    <row r="221" spans="1:8">
       <c r="A221" s="71" t="s">
         <v>240</v>
       </c>
@@ -14721,7 +14751,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="1">
+    <row r="222" spans="1:8">
       <c r="A222" s="71" t="s">
         <v>241</v>
       </c>
@@ -14744,7 +14774,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="1">
+    <row r="223" spans="1:8">
       <c r="A223" s="71" t="s">
         <v>242</v>
       </c>
@@ -14767,7 +14797,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1">
+    <row r="224" spans="1:8">
       <c r="A224" s="71" t="s">
         <v>243</v>
       </c>
@@ -14790,7 +14820,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="225" spans="1:15" hidden="1">
+    <row r="225" spans="1:15">
       <c r="A225" s="71" t="s">
         <v>244</v>
       </c>
@@ -14813,7 +14843,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="226" spans="1:15" hidden="1">
+    <row r="226" spans="1:15">
       <c r="A226" s="71" t="s">
         <v>245</v>
       </c>
@@ -14836,7 +14866,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="227" spans="1:15" hidden="1">
+    <row r="227" spans="1:15">
       <c r="A227" s="71" t="s">
         <v>246</v>
       </c>
@@ -14859,7 +14889,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="228" spans="1:15" hidden="1">
+    <row r="228" spans="1:15">
       <c r="A228" s="71" t="s">
         <v>247</v>
       </c>
@@ -14882,7 +14912,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="229" spans="1:15" hidden="1">
+    <row r="229" spans="1:15">
       <c r="A229" s="71" t="s">
         <v>248</v>
       </c>
@@ -14905,7 +14935,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="230" spans="1:15" hidden="1">
+    <row r="230" spans="1:15">
       <c r="A230" s="71" t="s">
         <v>249</v>
       </c>
@@ -14928,7 +14958,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="231" spans="1:15" hidden="1">
+    <row r="231" spans="1:15">
       <c r="A231" s="71" t="s">
         <v>250</v>
       </c>
@@ -14951,7 +14981,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="232" spans="1:15" hidden="1">
+    <row r="232" spans="1:15">
       <c r="A232" s="71" t="s">
         <v>251</v>
       </c>
@@ -14974,7 +15004,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="233" spans="1:15" hidden="1">
+    <row r="233" spans="1:15">
       <c r="A233" s="71" t="s">
         <v>252</v>
       </c>
@@ -14997,7 +15027,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="234" spans="1:15" hidden="1">
+    <row r="234" spans="1:15">
       <c r="A234" s="71" t="s">
         <v>253</v>
       </c>
@@ -15020,7 +15050,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="235" spans="1:15" hidden="1">
+    <row r="235" spans="1:15">
       <c r="A235" s="71" t="s">
         <v>254</v>
       </c>
@@ -15043,7 +15073,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="236" spans="1:15" hidden="1">
+    <row r="236" spans="1:15">
       <c r="A236" s="71" t="s">
         <v>255</v>
       </c>
@@ -15066,7 +15096,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="237" spans="1:15" ht="18" hidden="1">
+    <row r="237" spans="1:15" ht="18">
       <c r="A237" s="71" t="s">
         <v>256</v>
       </c>
@@ -15096,7 +15126,7 @@
       <c r="N237" s="55"/>
       <c r="O237" s="55"/>
     </row>
-    <row r="238" spans="1:15" ht="19" hidden="1">
+    <row r="238" spans="1:15" ht="19">
       <c r="A238" s="71" t="s">
         <v>257</v>
       </c>
@@ -15126,7 +15156,7 @@
       <c r="N238" s="55"/>
       <c r="O238" s="55"/>
     </row>
-    <row r="239" spans="1:15" ht="18" hidden="1">
+    <row r="239" spans="1:15" ht="18">
       <c r="A239" s="71" t="s">
         <v>258</v>
       </c>
@@ -15156,7 +15186,7 @@
       <c r="N239" s="55"/>
       <c r="O239" s="55"/>
     </row>
-    <row r="240" spans="1:15" hidden="1">
+    <row r="240" spans="1:15">
       <c r="A240" s="71" t="s">
         <v>259</v>
       </c>
@@ -15179,7 +15209,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="241" spans="1:15" ht="18" hidden="1">
+    <row r="241" spans="1:15" ht="18">
       <c r="A241" s="71" t="s">
         <v>260</v>
       </c>
@@ -15209,7 +15239,7 @@
       <c r="N241" s="55"/>
       <c r="O241" s="55"/>
     </row>
-    <row r="242" spans="1:15" ht="18" hidden="1">
+    <row r="242" spans="1:15" ht="18">
       <c r="A242" s="71" t="s">
         <v>261</v>
       </c>
@@ -15239,7 +15269,7 @@
       <c r="N242" s="55"/>
       <c r="O242" s="55"/>
     </row>
-    <row r="243" spans="1:15" hidden="1">
+    <row r="243" spans="1:15">
       <c r="A243" s="71" t="s">
         <v>262</v>
       </c>
@@ -15262,7 +15292,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="244" spans="1:15" ht="18" hidden="1">
+    <row r="244" spans="1:15" ht="18">
       <c r="A244" s="71" t="s">
         <v>263</v>
       </c>
@@ -15292,7 +15322,7 @@
       <c r="N244" s="56"/>
       <c r="O244" s="56"/>
     </row>
-    <row r="245" spans="1:15" hidden="1">
+    <row r="245" spans="1:15">
       <c r="A245" s="71" t="s">
         <v>264</v>
       </c>
@@ -15315,7 +15345,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="246" spans="1:15" ht="18" hidden="1">
+    <row r="246" spans="1:15" ht="18">
       <c r="A246" s="71" t="s">
         <v>265</v>
       </c>
@@ -15345,7 +15375,7 @@
       <c r="N246" s="57"/>
       <c r="O246" s="57"/>
     </row>
-    <row r="247" spans="1:15" hidden="1">
+    <row r="247" spans="1:15">
       <c r="A247" s="71" t="s">
         <v>266</v>
       </c>
@@ -15368,7 +15398,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="248" spans="1:15" ht="18" hidden="1">
+    <row r="248" spans="1:15" ht="18">
       <c r="A248" s="71" t="s">
         <v>267</v>
       </c>
@@ -15398,7 +15428,7 @@
       <c r="N248" s="57"/>
       <c r="O248" s="57"/>
     </row>
-    <row r="249" spans="1:15" hidden="1">
+    <row r="249" spans="1:15">
       <c r="A249" s="71" t="s">
         <v>268</v>
       </c>
@@ -15421,7 +15451,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="250" spans="1:15" ht="18" hidden="1">
+    <row r="250" spans="1:15" ht="18">
       <c r="A250" s="71" t="s">
         <v>269</v>
       </c>
@@ -15451,7 +15481,7 @@
       <c r="N250" s="57"/>
       <c r="O250" s="57"/>
     </row>
-    <row r="251" spans="1:15" hidden="1">
+    <row r="251" spans="1:15">
       <c r="A251" s="71" t="s">
         <v>270</v>
       </c>
@@ -15474,7 +15504,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="252" spans="1:15" ht="18" hidden="1">
+    <row r="252" spans="1:15" ht="18">
       <c r="A252" s="71" t="s">
         <v>271</v>
       </c>
@@ -15504,7 +15534,7 @@
       <c r="N252" s="57"/>
       <c r="O252" s="57"/>
     </row>
-    <row r="253" spans="1:15" ht="18" hidden="1">
+    <row r="253" spans="1:15" ht="18">
       <c r="A253" s="71" t="s">
         <v>272</v>
       </c>
@@ -15534,7 +15564,7 @@
       <c r="N253" s="57"/>
       <c r="O253" s="57"/>
     </row>
-    <row r="254" spans="1:15" hidden="1">
+    <row r="254" spans="1:15">
       <c r="A254" s="71" t="s">
         <v>70</v>
       </c>
@@ -15557,7 +15587,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="255" spans="1:15" hidden="1">
+    <row r="255" spans="1:15">
       <c r="A255" s="71" t="s">
         <v>71</v>
       </c>
@@ -15580,7 +15610,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="256" spans="1:15" hidden="1">
+    <row r="256" spans="1:15">
       <c r="A256" s="71" t="s">
         <v>72</v>
       </c>
@@ -15603,7 +15633,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1">
+    <row r="257" spans="1:9">
       <c r="A257" s="71" t="s">
         <v>73</v>
       </c>
@@ -15626,7 +15656,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1">
+    <row r="258" spans="1:9">
       <c r="A258" s="71" t="s">
         <v>74</v>
       </c>
@@ -15649,7 +15679,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="259" spans="1:9" s="13" customFormat="1" hidden="1">
+    <row r="259" spans="1:9" s="13" customFormat="1">
       <c r="A259" s="77" t="s">
         <v>454</v>
       </c>
@@ -15675,7 +15705,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1">
+    <row r="260" spans="1:9">
       <c r="A260" s="77" t="s">
         <v>455</v>
       </c>
@@ -15701,7 +15731,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1">
+    <row r="261" spans="1:9">
       <c r="A261" s="77" t="s">
         <v>456</v>
       </c>
@@ -15727,7 +15757,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1">
+    <row r="262" spans="1:9">
       <c r="A262" s="77" t="s">
         <v>457</v>
       </c>
@@ -15753,7 +15783,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1">
+    <row r="263" spans="1:9">
       <c r="A263" s="77" t="s">
         <v>458</v>
       </c>
@@ -15779,7 +15809,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1">
+    <row r="264" spans="1:9">
       <c r="A264" s="77" t="s">
         <v>459</v>
       </c>
@@ -15805,7 +15835,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1">
+    <row r="265" spans="1:9">
       <c r="A265" s="77" t="s">
         <v>460</v>
       </c>
@@ -15831,7 +15861,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1">
+    <row r="266" spans="1:9">
       <c r="A266" s="77" t="s">
         <v>461</v>
       </c>
@@ -15857,7 +15887,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1">
+    <row r="267" spans="1:9">
       <c r="A267" s="77" t="s">
         <v>462</v>
       </c>
@@ -15883,7 +15913,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1">
+    <row r="268" spans="1:9">
       <c r="A268" s="77" t="s">
         <v>463</v>
       </c>
@@ -15909,7 +15939,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1">
+    <row r="269" spans="1:9">
       <c r="A269" s="77" t="s">
         <v>464</v>
       </c>
@@ -15935,7 +15965,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1">
+    <row r="270" spans="1:9">
       <c r="A270" s="77" t="s">
         <v>465</v>
       </c>
@@ -15961,7 +15991,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1">
+    <row r="271" spans="1:9">
       <c r="A271" s="77" t="s">
         <v>466</v>
       </c>
@@ -15987,7 +16017,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1">
+    <row r="272" spans="1:9">
       <c r="A272" s="77" t="s">
         <v>467</v>
       </c>
@@ -16013,7 +16043,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="273" spans="1:10" hidden="1">
+    <row r="273" spans="1:10">
       <c r="A273" s="77" t="s">
         <v>468</v>
       </c>
@@ -16039,7 +16069,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="274" spans="1:10" hidden="1">
+    <row r="274" spans="1:10">
       <c r="A274" s="77" t="s">
         <v>469</v>
       </c>
@@ -16065,7 +16095,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="275" spans="1:10" hidden="1">
+    <row r="275" spans="1:10">
       <c r="A275" s="77" t="s">
         <v>470</v>
       </c>
@@ -16091,7 +16121,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="276" spans="1:10" hidden="1">
+    <row r="276" spans="1:10">
       <c r="A276" s="77" t="s">
         <v>471</v>
       </c>
@@ -16117,7 +16147,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="277" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="277" spans="1:10" s="15" customFormat="1">
       <c r="A277" s="7" t="s">
         <v>276</v>
       </c>
@@ -16146,7 +16176,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="278" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="278" spans="1:10" s="15" customFormat="1">
       <c r="A278" s="7" t="s">
         <v>277</v>
       </c>
@@ -16175,7 +16205,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="279" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="279" spans="1:10" s="15" customFormat="1">
       <c r="A279" s="7" t="s">
         <v>278</v>
       </c>
@@ -16204,7 +16234,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="280" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="280" spans="1:10" s="15" customFormat="1">
       <c r="A280" s="7" t="s">
         <v>279</v>
       </c>
@@ -16233,7 +16263,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="281" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="281" spans="1:10" s="15" customFormat="1">
       <c r="A281" s="7" t="s">
         <v>280</v>
       </c>
@@ -16262,7 +16292,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="282" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="282" spans="1:10" s="15" customFormat="1">
       <c r="A282" s="7" t="s">
         <v>281</v>
       </c>
@@ -16291,7 +16321,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="283" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="283" spans="1:10" s="15" customFormat="1">
       <c r="A283" s="7" t="s">
         <v>282</v>
       </c>
@@ -16320,7 +16350,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="284" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="284" spans="1:10" s="15" customFormat="1">
       <c r="A284" s="7" t="s">
         <v>283</v>
       </c>
@@ -16349,7 +16379,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="285" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="285" spans="1:10" s="15" customFormat="1">
       <c r="A285" s="7" t="s">
         <v>284</v>
       </c>
@@ -16378,7 +16408,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="286" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="286" spans="1:10" s="15" customFormat="1">
       <c r="A286" s="7" t="s">
         <v>285</v>
       </c>
@@ -16407,7 +16437,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="287" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="287" spans="1:10" s="15" customFormat="1">
       <c r="A287" s="7" t="s">
         <v>286</v>
       </c>
@@ -16436,7 +16466,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="288" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="288" spans="1:10" s="15" customFormat="1">
       <c r="A288" s="7" t="s">
         <v>287</v>
       </c>
@@ -16465,7 +16495,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="289" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="289" spans="1:10" s="15" customFormat="1">
       <c r="A289" s="7" t="s">
         <v>288</v>
       </c>
@@ -16494,7 +16524,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="290" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="290" spans="1:10" s="15" customFormat="1">
       <c r="A290" s="7" t="s">
         <v>289</v>
       </c>
@@ -16523,7 +16553,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="291" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="291" spans="1:10" s="15" customFormat="1">
       <c r="A291" s="7" t="s">
         <v>290</v>
       </c>
@@ -16552,7 +16582,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="292" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="292" spans="1:10" s="15" customFormat="1">
       <c r="A292" s="7" t="s">
         <v>291</v>
       </c>
@@ -16581,7 +16611,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="293" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="293" spans="1:10" s="15" customFormat="1">
       <c r="A293" s="7" t="s">
         <v>292</v>
       </c>
@@ -16607,7 +16637,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="294" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="294" spans="1:10" s="15" customFormat="1">
       <c r="A294" s="7" t="s">
         <v>293</v>
       </c>
@@ -16633,7 +16663,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="295" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="295" spans="1:10" s="15" customFormat="1">
       <c r="A295" s="7" t="s">
         <v>294</v>
       </c>
@@ -16659,7 +16689,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="296" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="296" spans="1:10" s="15" customFormat="1">
       <c r="A296" s="7" t="s">
         <v>295</v>
       </c>
@@ -16685,7 +16715,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="297" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="297" spans="1:10" s="15" customFormat="1">
       <c r="A297" s="7" t="s">
         <v>296</v>
       </c>
@@ -16711,7 +16741,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="298" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="298" spans="1:10" s="15" customFormat="1">
       <c r="A298" s="7" t="s">
         <v>297</v>
       </c>
@@ -16737,7 +16767,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="299" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="299" spans="1:10" s="15" customFormat="1">
       <c r="A299" s="7" t="s">
         <v>298</v>
       </c>
@@ -16763,7 +16793,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="300" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="300" spans="1:10" s="15" customFormat="1">
       <c r="A300" s="7" t="s">
         <v>299</v>
       </c>
@@ -16789,7 +16819,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="301" spans="1:10" s="15" customFormat="1" hidden="1">
+    <row r="301" spans="1:10" s="15" customFormat="1">
       <c r="A301" s="7" t="s">
         <v>300</v>
       </c>
@@ -16816,13 +16846,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B301" xr:uid="{7E8F22EE-2E06-6741-B451-D4EA064EAB2E}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Nielson lab"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="26" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D159" r:id="rId1" xr:uid="{BF63034B-E53E-AA4F-9F22-3EC9CCE474BD}"/>
@@ -16840,6 +16863,919 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181A6340-544E-644E-8C04-4BDDB8CC372C}">
+  <dimension ref="A1:A276"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="37.1640625" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="78" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="58" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="59" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="59" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="90" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="59" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="59" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="59" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="59" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="60" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="91" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="59" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="59" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="59" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="59" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="59" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="59" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="59" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="59" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="94" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="92" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="59" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="59" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="98" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="67" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="67" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="67" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="67" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="95" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="59" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="59" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="59" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="59" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="59" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="59" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="59" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="71" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="71" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="71" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="71" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="71" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="71" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="71" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="71" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="71" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="71" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="93" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="6" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="6" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="25" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="10" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="6" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="6" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="6" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="93" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="96" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="13" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="92" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="58" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="59" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="59" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="6" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="5" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="5" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="6" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="6" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="6" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="6" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="94" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="20" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="20" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="20" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="20" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="20" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="20" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="20" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="20" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="76" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="59" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="59" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="59" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="59" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="71" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="71" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="71" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="71" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="71" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="71" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="97" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="71" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="71" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="71" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="71" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="71" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="71" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="71" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="71" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="71" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="99" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="97" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="71" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="71" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="71" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="71" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="71" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="71" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="18">
+      <c r="A128" s="55" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="19">
+      <c r="A129" s="55" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="18">
+      <c r="A130" s="55" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="18">
+      <c r="A131" s="55" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="18">
+      <c r="A132" s="55" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="18">
+      <c r="A133" s="56" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="18">
+      <c r="A134" s="57" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="18">
+      <c r="A135" s="57" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="18">
+      <c r="A136" s="57" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="18">
+      <c r="A137" s="57" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="18">
+      <c r="A138" s="57" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="71" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="71" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="71" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="93" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="93" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="93" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="93" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="93" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149"/>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150"/>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151"/>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152"/>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153"/>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154"/>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155"/>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156"/>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157"/>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158"/>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159"/>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160"/>
+    </row>
+    <row r="161" customFormat="1"/>
+    <row r="162" customFormat="1"/>
+    <row r="163" customFormat="1"/>
+    <row r="164" customFormat="1"/>
+    <row r="165" customFormat="1"/>
+    <row r="166" customFormat="1"/>
+    <row r="167" customFormat="1"/>
+    <row r="168" customFormat="1"/>
+    <row r="169" customFormat="1"/>
+    <row r="170" customFormat="1"/>
+    <row r="171" customFormat="1"/>
+    <row r="172" customFormat="1"/>
+    <row r="173" customFormat="1"/>
+    <row r="174" customFormat="1"/>
+    <row r="175" customFormat="1"/>
+    <row r="176" customFormat="1"/>
+    <row r="177" customFormat="1"/>
+    <row r="178" customFormat="1"/>
+    <row r="179" customFormat="1"/>
+    <row r="180" customFormat="1"/>
+    <row r="181" customFormat="1"/>
+    <row r="182" customFormat="1"/>
+    <row r="183" customFormat="1"/>
+    <row r="184" customFormat="1"/>
+    <row r="185" customFormat="1"/>
+    <row r="186" customFormat="1"/>
+    <row r="187" customFormat="1"/>
+    <row r="188" customFormat="1"/>
+    <row r="189" customFormat="1"/>
+    <row r="190" customFormat="1"/>
+    <row r="191" customFormat="1"/>
+    <row r="192" customFormat="1"/>
+    <row r="193" customFormat="1"/>
+    <row r="194" customFormat="1"/>
+    <row r="195" customFormat="1"/>
+    <row r="196" customFormat="1"/>
+    <row r="197" customFormat="1"/>
+    <row r="198" customFormat="1"/>
+    <row r="199" customFormat="1"/>
+    <row r="200" customFormat="1"/>
+    <row r="201" customFormat="1"/>
+    <row r="202" customFormat="1"/>
+    <row r="203" customFormat="1"/>
+    <row r="204" customFormat="1"/>
+    <row r="205" customFormat="1"/>
+    <row r="206" customFormat="1"/>
+    <row r="207" customFormat="1"/>
+    <row r="208" customFormat="1"/>
+    <row r="209" customFormat="1"/>
+    <row r="210" customFormat="1"/>
+    <row r="211" customFormat="1"/>
+    <row r="212" customFormat="1"/>
+    <row r="213" customFormat="1"/>
+    <row r="214" customFormat="1"/>
+    <row r="215" customFormat="1"/>
+    <row r="216" customFormat="1"/>
+    <row r="217" customFormat="1"/>
+    <row r="218" customFormat="1"/>
+    <row r="219" customFormat="1"/>
+    <row r="220" customFormat="1"/>
+    <row r="221" customFormat="1"/>
+    <row r="222" customFormat="1"/>
+    <row r="223" customFormat="1"/>
+    <row r="224" customFormat="1"/>
+    <row r="225" customFormat="1"/>
+    <row r="226" customFormat="1"/>
+    <row r="227" customFormat="1"/>
+    <row r="228" customFormat="1"/>
+    <row r="229" customFormat="1"/>
+    <row r="230" customFormat="1"/>
+    <row r="231" customFormat="1"/>
+    <row r="232" customFormat="1"/>
+    <row r="233" customFormat="1"/>
+    <row r="234" customFormat="1"/>
+    <row r="235" customFormat="1"/>
+    <row r="236" customFormat="1"/>
+    <row r="237" customFormat="1"/>
+    <row r="238" customFormat="1"/>
+    <row r="239" customFormat="1"/>
+    <row r="240" customFormat="1"/>
+    <row r="241" customFormat="1"/>
+    <row r="242" customFormat="1"/>
+    <row r="243" customFormat="1"/>
+    <row r="244" customFormat="1"/>
+    <row r="245" customFormat="1"/>
+    <row r="246" customFormat="1"/>
+    <row r="247" customFormat="1"/>
+    <row r="248" customFormat="1"/>
+    <row r="249" customFormat="1"/>
+    <row r="250" customFormat="1"/>
+    <row r="251" customFormat="1"/>
+    <row r="252" customFormat="1"/>
+    <row r="253" customFormat="1"/>
+    <row r="254" customFormat="1"/>
+    <row r="255" customFormat="1"/>
+    <row r="256" customFormat="1"/>
+    <row r="257" customFormat="1"/>
+    <row r="258" customFormat="1"/>
+    <row r="259" customFormat="1"/>
+    <row r="260" customFormat="1"/>
+    <row r="261" customFormat="1"/>
+    <row r="262" customFormat="1"/>
+    <row r="263" customFormat="1"/>
+    <row r="264" customFormat="1"/>
+    <row r="265" customFormat="1"/>
+    <row r="266" customFormat="1"/>
+    <row r="267" customFormat="1"/>
+    <row r="268" customFormat="1"/>
+    <row r="269" customFormat="1"/>
+    <row r="270" customFormat="1"/>
+    <row r="271" customFormat="1"/>
+    <row r="272" customFormat="1"/>
+    <row r="273" spans="1:1">
+      <c r="A273"/>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274"/>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275"/>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A92C697-178C-F34D-9746-37532600BF2F}">
   <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -16905,7 +17841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{585F3E79-0845-3641-8545-95D8A6348BF3}">
   <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -17984,7 +18920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{794CDE12-2CCB-1F4B-AA82-4D0D38BE0B4E}">
   <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -18237,7 +19173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -21477,7 +22413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBC2DBA3-3F2C-254D-A3E7-B7A29892530C}">
   <dimension ref="A1:AE13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
